--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="943">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -2825,6 +2825,84 @@
   </si>
   <si>
     <t>Optional reductions not applied: sold options and sold protection are calculated as ordinary trades, which gives a higher EAD (permitted).</t>
+  </si>
+  <si>
+    <t>EAD = alpha x (RC + PFE)  [CRE52.1 / Art. 274(2)]; margined EAD capped at the unmargined EAD, with C = NICA only in both regimes [CRE52.2, CRE52.10; Art. 274(3), EBA Q&amp;A 2023_6962]</t>
+  </si>
+  <si>
+    <t>Floor 10 BD bilateral, 20 BD if &gt; 5,000 trades or illiquid collateral, 5 BD (configurable) for client clearing: the clearing member in both regimes, the client under CRR only [CRE54.12; Art. 279c(1)]; + (N - 1) for remargining every N days; the result doubled for disputes [CRE52.50-52.52; Art. 285]</t>
+  </si>
+  <si>
+    <t>VM and NICA are netting-set totals in reporting currency; positive = held, negative = posted. VM held on an unmargined netting set is rejected; VM posted on one is a one-way agreement, included in C under BCBS and rejected under CRR, where the netting set is margined.</t>
+  </si>
+  <si>
+    <t>MPOR floor, client clearing (BD)</t>
+  </si>
+  <si>
+    <t>One row per legally enforceable netting set. Collateral after haircuts, reporting currency; VM / NICA positive = held, negative = posted. Client clearing role: N, CM (the bank is the clearing member) or CLIENT. Margin agreements: blank for one agreement, or none, covering only this netting set; MIXED or SHARED declares a structure the engine rejects.</t>
+  </si>
+  <si>
+    <t>Client clearing role (N/CM/CLIENT)</t>
+  </si>
+  <si>
+    <t>Margin agreements (blank/MIXED/SHARED)</t>
+  </si>
+  <si>
+    <t>Posted VM: Basel cap uses NICA only -&gt; cap binds (~41)</t>
+  </si>
+  <si>
+    <t>CRE52.2, CRE52.10</t>
+  </si>
+  <si>
+    <t>Same as T17 since #39: cap ~41 &lt; margined ~377</t>
+  </si>
+  <si>
+    <t>Not yet in the catalogue: CRE99 margin-agreement / RC examples (segregated vs non-segregated IM), unrated credit mapping. One-way CSA, the client clearing role and the margin-agreement structures are tested in TEST_InputValidation (#39); several margin agreements per netting set and one agreement over several netting sets are rejected, not modelled.</t>
+  </si>
+  <si>
+    <t>Capped at the EAD of the same netting set "calculated on an unmargined basis" [CRE52.2]; unmargined C is the NICA collateral [CRE52.10], so the cap uses NICA only.</t>
+  </si>
+  <si>
+    <t>None since #39: both caps use NICA (posted-VM scenario ~41m in both regimes).</t>
+  </si>
+  <si>
+    <t>Implemented. Cap: C(cap) = NICA for RC and multiplier in both regimes. Results shows C, RC and multiplier on the cap basis.</t>
+  </si>
+  <si>
+    <t>VERIFIED (CRE52.2, CRE52.10; CRR, Q&amp;A)</t>
+  </si>
+  <si>
+    <t>RC = max(V - C, 0) [CRE52.10]; a one-way agreement where only the bank posts VM is unmargined, and C includes that VM with a negative sign [CRE52.2, CRE52.10 footnote 2].</t>
+  </si>
+  <si>
+    <t>RC = max(CMV - NICA, 0) [Art. 275(1)]; collateral per CRR definitions (Art. 272(12a), 276). A one-way margin agreement is a margin agreement [Art. 272(7a)]: the netting set is margined.</t>
+  </si>
+  <si>
+    <t>Different (one-way agreement)</t>
+  </si>
+  <si>
+    <t>One-way agreements where the bank posts VM</t>
+  </si>
+  <si>
+    <t>Enter collateral after haircuts, in NICA. VM held on an unmargined set is rejected. VM posted (one-way agreement): BCBS includes it in C; CRR rejects it - set Margined = Y.</t>
+  </si>
+  <si>
+    <t>Different (client role)</t>
+  </si>
+  <si>
+    <t>Client facing its clearing member: 5 BD under CRR, 10 BD under BCBS</t>
+  </si>
+  <si>
+    <t>Common core; MPOR floors are parameters. Client clearing role N / CM / CLIENT: 5 BD for CM in both regimes and for CLIENT under CRR [CRE54.12; Art. 279c(1)]; a BCBS client keeps 10 BD [CRE54.8, CRE54.14]. Disputes double F + N - 1; a large or illiquid set takes 20 + N - 1.</t>
+  </si>
+  <si>
+    <t>Not implemented: declare MIXED under Margin agreements; the netting set is rejected.</t>
+  </si>
+  <si>
+    <t>Art. 275(3) (RC) and Art. 278(2) (PFE as sum of unmargined PFEs).</t>
+  </si>
+  <si>
+    <t>Not implemented: declare SHARED under Margin agreements; the netting set is rejected.</t>
   </si>
 </sst>
 </file>
@@ -3693,7 +3771,7 @@
         <v>33</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>34</v>
+        <v>917</v>
       </c>
     </row>
     <row r="25" spans="2:3">
@@ -3733,7 +3811,7 @@
         <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>44</v>
+        <v>918</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="28" customHeight="1">
@@ -3983,7 +4061,7 @@
         <v>103</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>104</v>
+        <v>919</v>
       </c>
     </row>
     <row r="65" spans="2:3">
@@ -4929,10 +5007,10 @@
         <v>695</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>701</v>
+        <v>924</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>702</v>
+        <v>925</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>703</v>
@@ -4950,7 +5028,7 @@
         <v>33</v>
       </c>
       <c r="J20" s="41">
-        <v>376592788.3471456</v>
+        <v>40774849.34860364</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>704</v>
@@ -4960,7 +5038,7 @@
       </c>
       <c r="M20" s="43">
         <f>IFERROR(INDEX(Results!$A$5:$AA$3000,MATCH($H20,Results!$A$5:$A$3000,0),MATCH($I20,Results!$A$4:$AA$4,0)),"n/a")</f>
-        <v>376592788.3471456</v>
+        <v>40774849.348603636</v>
       </c>
       <c r="N20" s="42">
         <f>IF(AND(ISNUMBER(M20),ISNUMBER(J20)),M20-J20,"")</f>
@@ -4971,7 +5049,7 @@
         <v>PASS</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>705</v>
+        <v>926</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -5659,7 +5737,7 @@
     </row>
     <row r="38" spans="2:16" ht="30" customHeight="1">
       <c r="B38" s="5" t="s">
-        <v>753</v>
+        <v>927</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -6382,25 +6460,25 @@
         <v>777</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>778</v>
+        <v>928</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>779</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>780</v>
+        <v>929</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>781</v>
+        <v>930</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>782</v>
       </c>
       <c r="I7" s="54" t="s">
-        <v>783</v>
+        <v>931</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1">
@@ -6411,19 +6489,19 @@
         <v>784</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>785</v>
+        <v>932</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>786</v>
+        <v>933</v>
       </c>
       <c r="E8" s="53" t="s">
-        <v>787</v>
+        <v>934</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>788</v>
+        <v>935</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>789</v>
+        <v>936</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>675</v>
@@ -6765,13 +6843,13 @@
         <v>856</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>774</v>
+        <v>937</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>775</v>
+        <v>938</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>857</v>
+        <v>939</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>684</v>
@@ -6945,7 +7023,7 @@
         <v>888</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>889</v>
+        <v>940</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>769</v>
@@ -6965,7 +7043,7 @@
         <v>891</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>892</v>
+        <v>941</v>
       </c>
       <c r="E27" s="52" t="s">
         <v>887</v>
@@ -6974,7 +7052,7 @@
         <v>888</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>889</v>
+        <v>942</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>769</v>
@@ -7221,7 +7299,7 @@
         <v>144</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>145</v>
+        <v>920</v>
       </c>
       <c r="C14" s="12">
         <v>5</v>
@@ -8208,7 +8286,7 @@
     <tabColor rgb="FFBF9000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N204"/>
+  <dimension ref="A1:O204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -8223,19 +8301,20 @@
     <col min="11" max="12" width="13.7109375" customWidth="1"/>
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="42" customHeight="1">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="42" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>259</v>
       </c>
@@ -8246,7 +8325,7 @@
         <v>261</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>262</v>
+        <v>922</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>263</v>
@@ -8278,8 +8357,11 @@
       <c r="N4" s="6" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" s="6" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="11" t="s">
         <v>273</v>
       </c>
@@ -8316,8 +8398,9 @@
       <c r="N5" s="11" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" s="11"/>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="11" t="s">
         <v>277</v>
       </c>
@@ -8354,8 +8437,9 @@
       <c r="N6" s="11" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" s="11"/>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="11" t="s">
         <v>279</v>
       </c>
@@ -8392,8 +8476,9 @@
       <c r="N7" s="11" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" s="11"/>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="11" t="s">
         <v>281</v>
       </c>
@@ -8430,8 +8515,9 @@
       <c r="N8" s="11" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" s="11"/>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="11" t="s">
         <v>283</v>
       </c>
@@ -8470,8 +8556,9 @@
       <c r="N9" s="11" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" s="11"/>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="11" t="s">
         <v>286</v>
       </c>
@@ -8510,8 +8597,9 @@
       <c r="N10" s="11" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" s="11"/>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="11" t="s">
         <v>288</v>
       </c>
@@ -8550,8 +8638,9 @@
       <c r="N11" s="11" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" s="11"/>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="11" t="s">
         <v>290</v>
       </c>
@@ -8590,8 +8679,9 @@
       <c r="N12" s="11" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" s="11"/>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="11" t="s">
         <v>292</v>
       </c>
@@ -8628,8 +8718,9 @@
       <c r="N13" s="11" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" s="11"/>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="11" t="s">
         <v>294</v>
       </c>
@@ -8666,8 +8757,9 @@
       <c r="N14" s="11" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" s="11"/>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="11" t="s">
         <v>296</v>
       </c>
@@ -8704,8 +8796,9 @@
       <c r="N15" s="11" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" s="11"/>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="11" t="s">
         <v>298</v>
       </c>
@@ -8742,8 +8835,9 @@
       <c r="N16" s="11" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" s="11"/>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="11" t="s">
         <v>300</v>
       </c>
@@ -8780,8 +8874,9 @@
       <c r="N17" s="11" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" s="11"/>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="11" t="s">
         <v>302</v>
       </c>
@@ -8818,8 +8913,9 @@
       <c r="N18" s="11" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" s="11"/>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="11" t="s">
         <v>304</v>
       </c>
@@ -8854,8 +8950,9 @@
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="11"/>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" s="11"/>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="11" t="s">
         <v>306</v>
       </c>
@@ -8892,8 +8989,9 @@
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="11"/>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" s="11"/>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>DEMO-REJECTED</t>
@@ -8944,8 +9042,9 @@
           <t>BCBS</t>
         </is>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" s="11"/>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="11"/>
       <c r="B22" s="14"/>
       <c r="C22" s="11"/>
@@ -8960,8 +9059,9 @@
       <c r="L22" s="21"/>
       <c r="M22" s="22"/>
       <c r="N22" s="11"/>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" s="11"/>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="11"/>
       <c r="B23" s="14"/>
       <c r="C23" s="11"/>
@@ -8976,8 +9076,9 @@
       <c r="L23" s="21"/>
       <c r="M23" s="22"/>
       <c r="N23" s="11"/>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" s="11"/>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="11"/>
       <c r="B24" s="14"/>
       <c r="C24" s="11"/>
@@ -8992,8 +9093,9 @@
       <c r="L24" s="21"/>
       <c r="M24" s="22"/>
       <c r="N24" s="11"/>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" s="11"/>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="11"/>
       <c r="B25" s="14"/>
       <c r="C25" s="11"/>
@@ -9008,8 +9110,9 @@
       <c r="L25" s="21"/>
       <c r="M25" s="22"/>
       <c r="N25" s="11"/>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" s="11"/>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="11"/>
       <c r="B26" s="14"/>
       <c r="C26" s="11"/>
@@ -9024,8 +9127,9 @@
       <c r="L26" s="21"/>
       <c r="M26" s="22"/>
       <c r="N26" s="11"/>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" s="11"/>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="11"/>
       <c r="B27" s="14"/>
       <c r="C27" s="11"/>
@@ -9040,8 +9144,9 @@
       <c r="L27" s="21"/>
       <c r="M27" s="22"/>
       <c r="N27" s="11"/>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" s="11"/>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="11"/>
       <c r="B28" s="14"/>
       <c r="C28" s="11"/>
@@ -9056,8 +9161,9 @@
       <c r="L28" s="21"/>
       <c r="M28" s="22"/>
       <c r="N28" s="11"/>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" s="11"/>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="11"/>
       <c r="B29" s="14"/>
       <c r="C29" s="11"/>
@@ -9072,8 +9178,9 @@
       <c r="L29" s="21"/>
       <c r="M29" s="22"/>
       <c r="N29" s="11"/>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29" s="11"/>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="11"/>
       <c r="B30" s="14"/>
       <c r="C30" s="11"/>
@@ -9088,8 +9195,9 @@
       <c r="L30" s="21"/>
       <c r="M30" s="22"/>
       <c r="N30" s="11"/>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30" s="11"/>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="11"/>
       <c r="B31" s="14"/>
       <c r="C31" s="11"/>
@@ -9104,8 +9212,9 @@
       <c r="L31" s="21"/>
       <c r="M31" s="22"/>
       <c r="N31" s="11"/>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31" s="11"/>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="11"/>
       <c r="B32" s="14"/>
       <c r="C32" s="11"/>
@@ -9120,8 +9229,9 @@
       <c r="L32" s="21"/>
       <c r="M32" s="22"/>
       <c r="N32" s="11"/>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" s="11"/>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="11"/>
       <c r="B33" s="14"/>
       <c r="C33" s="11"/>
@@ -9136,8 +9246,9 @@
       <c r="L33" s="21"/>
       <c r="M33" s="22"/>
       <c r="N33" s="11"/>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33" s="11"/>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" s="11"/>
       <c r="B34" s="14"/>
       <c r="C34" s="11"/>
@@ -9152,8 +9263,9 @@
       <c r="L34" s="21"/>
       <c r="M34" s="22"/>
       <c r="N34" s="11"/>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34" s="11"/>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" s="11"/>
       <c r="B35" s="14"/>
       <c r="C35" s="11"/>
@@ -9168,8 +9280,9 @@
       <c r="L35" s="21"/>
       <c r="M35" s="22"/>
       <c r="N35" s="11"/>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35" s="11"/>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" s="11"/>
       <c r="B36" s="14"/>
       <c r="C36" s="11"/>
@@ -9184,8 +9297,9 @@
       <c r="L36" s="21"/>
       <c r="M36" s="22"/>
       <c r="N36" s="11"/>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36" s="11"/>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" s="11"/>
       <c r="B37" s="14"/>
       <c r="C37" s="11"/>
@@ -9200,8 +9314,9 @@
       <c r="L37" s="21"/>
       <c r="M37" s="22"/>
       <c r="N37" s="11"/>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37" s="11"/>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" s="11"/>
       <c r="B38" s="14"/>
       <c r="C38" s="11"/>
@@ -9216,8 +9331,9 @@
       <c r="L38" s="21"/>
       <c r="M38" s="22"/>
       <c r="N38" s="11"/>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38" s="11"/>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" s="11"/>
       <c r="B39" s="14"/>
       <c r="C39" s="11"/>
@@ -9232,8 +9348,9 @@
       <c r="L39" s="21"/>
       <c r="M39" s="22"/>
       <c r="N39" s="11"/>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39" s="11"/>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" s="11"/>
       <c r="B40" s="14"/>
       <c r="C40" s="11"/>
@@ -9248,8 +9365,9 @@
       <c r="L40" s="21"/>
       <c r="M40" s="22"/>
       <c r="N40" s="11"/>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" s="11"/>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" s="11"/>
       <c r="B41" s="14"/>
       <c r="C41" s="11"/>
@@ -9264,8 +9382,9 @@
       <c r="L41" s="21"/>
       <c r="M41" s="22"/>
       <c r="N41" s="11"/>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" s="11"/>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" s="11"/>
       <c r="B42" s="14"/>
       <c r="C42" s="11"/>
@@ -9280,8 +9399,9 @@
       <c r="L42" s="21"/>
       <c r="M42" s="22"/>
       <c r="N42" s="11"/>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42" s="11"/>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" s="11"/>
       <c r="B43" s="14"/>
       <c r="C43" s="11"/>
@@ -9296,8 +9416,9 @@
       <c r="L43" s="21"/>
       <c r="M43" s="22"/>
       <c r="N43" s="11"/>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43" s="11"/>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="11"/>
       <c r="B44" s="14"/>
       <c r="C44" s="11"/>
@@ -9312,8 +9433,9 @@
       <c r="L44" s="21"/>
       <c r="M44" s="22"/>
       <c r="N44" s="11"/>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44" s="11"/>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" s="11"/>
       <c r="B45" s="14"/>
       <c r="C45" s="11"/>
@@ -9328,8 +9450,9 @@
       <c r="L45" s="21"/>
       <c r="M45" s="22"/>
       <c r="N45" s="11"/>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45" s="11"/>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" s="11"/>
       <c r="B46" s="14"/>
       <c r="C46" s="11"/>
@@ -9344,8 +9467,9 @@
       <c r="L46" s="21"/>
       <c r="M46" s="22"/>
       <c r="N46" s="11"/>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" s="11"/>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="11"/>
       <c r="B47" s="14"/>
       <c r="C47" s="11"/>
@@ -9360,8 +9484,9 @@
       <c r="L47" s="21"/>
       <c r="M47" s="22"/>
       <c r="N47" s="11"/>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" s="11"/>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" s="11"/>
       <c r="B48" s="14"/>
       <c r="C48" s="11"/>
@@ -9376,8 +9501,9 @@
       <c r="L48" s="21"/>
       <c r="M48" s="22"/>
       <c r="N48" s="11"/>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="O48" s="11"/>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" s="11"/>
       <c r="B49" s="14"/>
       <c r="C49" s="11"/>
@@ -9392,8 +9518,9 @@
       <c r="L49" s="21"/>
       <c r="M49" s="22"/>
       <c r="N49" s="11"/>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49" s="11"/>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" s="11"/>
       <c r="B50" s="14"/>
       <c r="C50" s="11"/>
@@ -9408,8 +9535,9 @@
       <c r="L50" s="21"/>
       <c r="M50" s="22"/>
       <c r="N50" s="11"/>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50" s="11"/>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" s="11"/>
       <c r="B51" s="14"/>
       <c r="C51" s="11"/>
@@ -9424,8 +9552,9 @@
       <c r="L51" s="21"/>
       <c r="M51" s="22"/>
       <c r="N51" s="11"/>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51" s="11"/>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" s="11"/>
       <c r="B52" s="14"/>
       <c r="C52" s="11"/>
@@ -9440,8 +9569,9 @@
       <c r="L52" s="21"/>
       <c r="M52" s="22"/>
       <c r="N52" s="11"/>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52" s="11"/>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" s="11"/>
       <c r="B53" s="14"/>
       <c r="C53" s="11"/>
@@ -9456,8 +9586,9 @@
       <c r="L53" s="21"/>
       <c r="M53" s="22"/>
       <c r="N53" s="11"/>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53" s="11"/>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="11"/>
       <c r="B54" s="14"/>
       <c r="C54" s="11"/>
@@ -9472,8 +9603,9 @@
       <c r="L54" s="21"/>
       <c r="M54" s="22"/>
       <c r="N54" s="11"/>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54" s="11"/>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" s="11"/>
       <c r="B55" s="14"/>
       <c r="C55" s="11"/>
@@ -9488,8 +9620,9 @@
       <c r="L55" s="21"/>
       <c r="M55" s="22"/>
       <c r="N55" s="11"/>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="O55" s="11"/>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" s="11"/>
       <c r="B56" s="14"/>
       <c r="C56" s="11"/>
@@ -9504,8 +9637,9 @@
       <c r="L56" s="21"/>
       <c r="M56" s="22"/>
       <c r="N56" s="11"/>
-    </row>
-    <row r="57" spans="1:14">
+      <c r="O56" s="11"/>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" s="11"/>
       <c r="B57" s="14"/>
       <c r="C57" s="11"/>
@@ -9520,8 +9654,9 @@
       <c r="L57" s="21"/>
       <c r="M57" s="22"/>
       <c r="N57" s="11"/>
-    </row>
-    <row r="58" spans="1:14">
+      <c r="O57" s="11"/>
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58" s="11"/>
       <c r="B58" s="14"/>
       <c r="C58" s="11"/>
@@ -9536,8 +9671,9 @@
       <c r="L58" s="21"/>
       <c r="M58" s="22"/>
       <c r="N58" s="11"/>
-    </row>
-    <row r="59" spans="1:14">
+      <c r="O58" s="11"/>
+    </row>
+    <row r="59" spans="1:15">
       <c r="A59" s="11"/>
       <c r="B59" s="14"/>
       <c r="C59" s="11"/>
@@ -9552,8 +9688,9 @@
       <c r="L59" s="21"/>
       <c r="M59" s="22"/>
       <c r="N59" s="11"/>
-    </row>
-    <row r="60" spans="1:14">
+      <c r="O59" s="11"/>
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60" s="11"/>
       <c r="B60" s="14"/>
       <c r="C60" s="11"/>
@@ -9568,8 +9705,9 @@
       <c r="L60" s="21"/>
       <c r="M60" s="22"/>
       <c r="N60" s="11"/>
-    </row>
-    <row r="61" spans="1:14">
+      <c r="O60" s="11"/>
+    </row>
+    <row r="61" spans="1:15">
       <c r="A61" s="11"/>
       <c r="B61" s="14"/>
       <c r="C61" s="11"/>
@@ -9584,8 +9722,9 @@
       <c r="L61" s="21"/>
       <c r="M61" s="22"/>
       <c r="N61" s="11"/>
-    </row>
-    <row r="62" spans="1:14">
+      <c r="O61" s="11"/>
+    </row>
+    <row r="62" spans="1:15">
       <c r="A62" s="11"/>
       <c r="B62" s="14"/>
       <c r="C62" s="11"/>
@@ -9600,8 +9739,9 @@
       <c r="L62" s="21"/>
       <c r="M62" s="22"/>
       <c r="N62" s="11"/>
-    </row>
-    <row r="63" spans="1:14">
+      <c r="O62" s="11"/>
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63" s="11"/>
       <c r="B63" s="14"/>
       <c r="C63" s="11"/>
@@ -9616,8 +9756,9 @@
       <c r="L63" s="21"/>
       <c r="M63" s="22"/>
       <c r="N63" s="11"/>
-    </row>
-    <row r="64" spans="1:14">
+      <c r="O63" s="11"/>
+    </row>
+    <row r="64" spans="1:15">
       <c r="A64" s="11"/>
       <c r="B64" s="14"/>
       <c r="C64" s="11"/>
@@ -9632,8 +9773,9 @@
       <c r="L64" s="21"/>
       <c r="M64" s="22"/>
       <c r="N64" s="11"/>
-    </row>
-    <row r="65" spans="1:14">
+      <c r="O64" s="11"/>
+    </row>
+    <row r="65" spans="1:15">
       <c r="A65" s="11"/>
       <c r="B65" s="14"/>
       <c r="C65" s="11"/>
@@ -9648,8 +9790,9 @@
       <c r="L65" s="21"/>
       <c r="M65" s="22"/>
       <c r="N65" s="11"/>
-    </row>
-    <row r="66" spans="1:14">
+      <c r="O65" s="11"/>
+    </row>
+    <row r="66" spans="1:15">
       <c r="A66" s="11"/>
       <c r="B66" s="14"/>
       <c r="C66" s="11"/>
@@ -9664,8 +9807,9 @@
       <c r="L66" s="21"/>
       <c r="M66" s="22"/>
       <c r="N66" s="11"/>
-    </row>
-    <row r="67" spans="1:14">
+      <c r="O66" s="11"/>
+    </row>
+    <row r="67" spans="1:15">
       <c r="A67" s="11"/>
       <c r="B67" s="14"/>
       <c r="C67" s="11"/>
@@ -9680,8 +9824,9 @@
       <c r="L67" s="21"/>
       <c r="M67" s="22"/>
       <c r="N67" s="11"/>
-    </row>
-    <row r="68" spans="1:14">
+      <c r="O67" s="11"/>
+    </row>
+    <row r="68" spans="1:15">
       <c r="A68" s="11"/>
       <c r="B68" s="14"/>
       <c r="C68" s="11"/>
@@ -9696,8 +9841,9 @@
       <c r="L68" s="21"/>
       <c r="M68" s="22"/>
       <c r="N68" s="11"/>
-    </row>
-    <row r="69" spans="1:14">
+      <c r="O68" s="11"/>
+    </row>
+    <row r="69" spans="1:15">
       <c r="A69" s="11"/>
       <c r="B69" s="14"/>
       <c r="C69" s="11"/>
@@ -9712,8 +9858,9 @@
       <c r="L69" s="21"/>
       <c r="M69" s="22"/>
       <c r="N69" s="11"/>
-    </row>
-    <row r="70" spans="1:14">
+      <c r="O69" s="11"/>
+    </row>
+    <row r="70" spans="1:15">
       <c r="A70" s="11"/>
       <c r="B70" s="14"/>
       <c r="C70" s="11"/>
@@ -9728,8 +9875,9 @@
       <c r="L70" s="21"/>
       <c r="M70" s="22"/>
       <c r="N70" s="11"/>
-    </row>
-    <row r="71" spans="1:14">
+      <c r="O70" s="11"/>
+    </row>
+    <row r="71" spans="1:15">
       <c r="A71" s="11"/>
       <c r="B71" s="14"/>
       <c r="C71" s="11"/>
@@ -9744,8 +9892,9 @@
       <c r="L71" s="21"/>
       <c r="M71" s="22"/>
       <c r="N71" s="11"/>
-    </row>
-    <row r="72" spans="1:14">
+      <c r="O71" s="11"/>
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72" s="11"/>
       <c r="B72" s="14"/>
       <c r="C72" s="11"/>
@@ -9760,8 +9909,9 @@
       <c r="L72" s="21"/>
       <c r="M72" s="22"/>
       <c r="N72" s="11"/>
-    </row>
-    <row r="73" spans="1:14">
+      <c r="O72" s="11"/>
+    </row>
+    <row r="73" spans="1:15">
       <c r="A73" s="11"/>
       <c r="B73" s="14"/>
       <c r="C73" s="11"/>
@@ -9776,8 +9926,9 @@
       <c r="L73" s="21"/>
       <c r="M73" s="22"/>
       <c r="N73" s="11"/>
-    </row>
-    <row r="74" spans="1:14">
+      <c r="O73" s="11"/>
+    </row>
+    <row r="74" spans="1:15">
       <c r="A74" s="11"/>
       <c r="B74" s="14"/>
       <c r="C74" s="11"/>
@@ -9792,8 +9943,9 @@
       <c r="L74" s="21"/>
       <c r="M74" s="22"/>
       <c r="N74" s="11"/>
-    </row>
-    <row r="75" spans="1:14">
+      <c r="O74" s="11"/>
+    </row>
+    <row r="75" spans="1:15">
       <c r="A75" s="11"/>
       <c r="B75" s="14"/>
       <c r="C75" s="11"/>
@@ -9808,8 +9960,9 @@
       <c r="L75" s="21"/>
       <c r="M75" s="22"/>
       <c r="N75" s="11"/>
-    </row>
-    <row r="76" spans="1:14">
+      <c r="O75" s="11"/>
+    </row>
+    <row r="76" spans="1:15">
       <c r="A76" s="11"/>
       <c r="B76" s="14"/>
       <c r="C76" s="11"/>
@@ -9824,8 +9977,9 @@
       <c r="L76" s="21"/>
       <c r="M76" s="22"/>
       <c r="N76" s="11"/>
-    </row>
-    <row r="77" spans="1:14">
+      <c r="O76" s="11"/>
+    </row>
+    <row r="77" spans="1:15">
       <c r="A77" s="11"/>
       <c r="B77" s="14"/>
       <c r="C77" s="11"/>
@@ -9840,8 +9994,9 @@
       <c r="L77" s="21"/>
       <c r="M77" s="22"/>
       <c r="N77" s="11"/>
-    </row>
-    <row r="78" spans="1:14">
+      <c r="O77" s="11"/>
+    </row>
+    <row r="78" spans="1:15">
       <c r="A78" s="11"/>
       <c r="B78" s="14"/>
       <c r="C78" s="11"/>
@@ -9856,8 +10011,9 @@
       <c r="L78" s="21"/>
       <c r="M78" s="22"/>
       <c r="N78" s="11"/>
-    </row>
-    <row r="79" spans="1:14">
+      <c r="O78" s="11"/>
+    </row>
+    <row r="79" spans="1:15">
       <c r="A79" s="11"/>
       <c r="B79" s="14"/>
       <c r="C79" s="11"/>
@@ -9872,8 +10028,9 @@
       <c r="L79" s="21"/>
       <c r="M79" s="22"/>
       <c r="N79" s="11"/>
-    </row>
-    <row r="80" spans="1:14">
+      <c r="O79" s="11"/>
+    </row>
+    <row r="80" spans="1:15">
       <c r="A80" s="11"/>
       <c r="B80" s="14"/>
       <c r="C80" s="11"/>
@@ -9888,8 +10045,9 @@
       <c r="L80" s="21"/>
       <c r="M80" s="22"/>
       <c r="N80" s="11"/>
-    </row>
-    <row r="81" spans="1:14">
+      <c r="O80" s="11"/>
+    </row>
+    <row r="81" spans="1:15">
       <c r="A81" s="11"/>
       <c r="B81" s="14"/>
       <c r="C81" s="11"/>
@@ -9904,8 +10062,9 @@
       <c r="L81" s="21"/>
       <c r="M81" s="22"/>
       <c r="N81" s="11"/>
-    </row>
-    <row r="82" spans="1:14">
+      <c r="O81" s="11"/>
+    </row>
+    <row r="82" spans="1:15">
       <c r="A82" s="11"/>
       <c r="B82" s="14"/>
       <c r="C82" s="11"/>
@@ -9920,8 +10079,9 @@
       <c r="L82" s="21"/>
       <c r="M82" s="22"/>
       <c r="N82" s="11"/>
-    </row>
-    <row r="83" spans="1:14">
+      <c r="O82" s="11"/>
+    </row>
+    <row r="83" spans="1:15">
       <c r="A83" s="11"/>
       <c r="B83" s="14"/>
       <c r="C83" s="11"/>
@@ -9936,8 +10096,9 @@
       <c r="L83" s="21"/>
       <c r="M83" s="22"/>
       <c r="N83" s="11"/>
-    </row>
-    <row r="84" spans="1:14">
+      <c r="O83" s="11"/>
+    </row>
+    <row r="84" spans="1:15">
       <c r="A84" s="11"/>
       <c r="B84" s="14"/>
       <c r="C84" s="11"/>
@@ -9952,8 +10113,9 @@
       <c r="L84" s="21"/>
       <c r="M84" s="22"/>
       <c r="N84" s="11"/>
-    </row>
-    <row r="85" spans="1:14">
+      <c r="O84" s="11"/>
+    </row>
+    <row r="85" spans="1:15">
       <c r="A85" s="11"/>
       <c r="B85" s="14"/>
       <c r="C85" s="11"/>
@@ -9968,8 +10130,9 @@
       <c r="L85" s="21"/>
       <c r="M85" s="22"/>
       <c r="N85" s="11"/>
-    </row>
-    <row r="86" spans="1:14">
+      <c r="O85" s="11"/>
+    </row>
+    <row r="86" spans="1:15">
       <c r="A86" s="11"/>
       <c r="B86" s="14"/>
       <c r="C86" s="11"/>
@@ -9984,8 +10147,9 @@
       <c r="L86" s="21"/>
       <c r="M86" s="22"/>
       <c r="N86" s="11"/>
-    </row>
-    <row r="87" spans="1:14">
+      <c r="O86" s="11"/>
+    </row>
+    <row r="87" spans="1:15">
       <c r="A87" s="11"/>
       <c r="B87" s="14"/>
       <c r="C87" s="11"/>
@@ -10000,8 +10164,9 @@
       <c r="L87" s="21"/>
       <c r="M87" s="22"/>
       <c r="N87" s="11"/>
-    </row>
-    <row r="88" spans="1:14">
+      <c r="O87" s="11"/>
+    </row>
+    <row r="88" spans="1:15">
       <c r="A88" s="11"/>
       <c r="B88" s="14"/>
       <c r="C88" s="11"/>
@@ -10016,8 +10181,9 @@
       <c r="L88" s="21"/>
       <c r="M88" s="22"/>
       <c r="N88" s="11"/>
-    </row>
-    <row r="89" spans="1:14">
+      <c r="O88" s="11"/>
+    </row>
+    <row r="89" spans="1:15">
       <c r="A89" s="11"/>
       <c r="B89" s="14"/>
       <c r="C89" s="11"/>
@@ -10032,8 +10198,9 @@
       <c r="L89" s="21"/>
       <c r="M89" s="22"/>
       <c r="N89" s="11"/>
-    </row>
-    <row r="90" spans="1:14">
+      <c r="O89" s="11"/>
+    </row>
+    <row r="90" spans="1:15">
       <c r="A90" s="11"/>
       <c r="B90" s="14"/>
       <c r="C90" s="11"/>
@@ -10048,8 +10215,9 @@
       <c r="L90" s="21"/>
       <c r="M90" s="22"/>
       <c r="N90" s="11"/>
-    </row>
-    <row r="91" spans="1:14">
+      <c r="O90" s="11"/>
+    </row>
+    <row r="91" spans="1:15">
       <c r="A91" s="11"/>
       <c r="B91" s="14"/>
       <c r="C91" s="11"/>
@@ -10064,8 +10232,9 @@
       <c r="L91" s="21"/>
       <c r="M91" s="22"/>
       <c r="N91" s="11"/>
-    </row>
-    <row r="92" spans="1:14">
+      <c r="O91" s="11"/>
+    </row>
+    <row r="92" spans="1:15">
       <c r="A92" s="11"/>
       <c r="B92" s="14"/>
       <c r="C92" s="11"/>
@@ -10080,8 +10249,9 @@
       <c r="L92" s="21"/>
       <c r="M92" s="22"/>
       <c r="N92" s="11"/>
-    </row>
-    <row r="93" spans="1:14">
+      <c r="O92" s="11"/>
+    </row>
+    <row r="93" spans="1:15">
       <c r="A93" s="11"/>
       <c r="B93" s="14"/>
       <c r="C93" s="11"/>
@@ -10096,8 +10266,9 @@
       <c r="L93" s="21"/>
       <c r="M93" s="22"/>
       <c r="N93" s="11"/>
-    </row>
-    <row r="94" spans="1:14">
+      <c r="O93" s="11"/>
+    </row>
+    <row r="94" spans="1:15">
       <c r="A94" s="11"/>
       <c r="B94" s="14"/>
       <c r="C94" s="11"/>
@@ -10112,8 +10283,9 @@
       <c r="L94" s="21"/>
       <c r="M94" s="22"/>
       <c r="N94" s="11"/>
-    </row>
-    <row r="95" spans="1:14">
+      <c r="O94" s="11"/>
+    </row>
+    <row r="95" spans="1:15">
       <c r="A95" s="11"/>
       <c r="B95" s="14"/>
       <c r="C95" s="11"/>
@@ -10128,8 +10300,9 @@
       <c r="L95" s="21"/>
       <c r="M95" s="22"/>
       <c r="N95" s="11"/>
-    </row>
-    <row r="96" spans="1:14">
+      <c r="O95" s="11"/>
+    </row>
+    <row r="96" spans="1:15">
       <c r="A96" s="11"/>
       <c r="B96" s="14"/>
       <c r="C96" s="11"/>
@@ -10144,8 +10317,9 @@
       <c r="L96" s="21"/>
       <c r="M96" s="22"/>
       <c r="N96" s="11"/>
-    </row>
-    <row r="97" spans="1:14">
+      <c r="O96" s="11"/>
+    </row>
+    <row r="97" spans="1:15">
       <c r="A97" s="11"/>
       <c r="B97" s="14"/>
       <c r="C97" s="11"/>
@@ -10160,8 +10334,9 @@
       <c r="L97" s="21"/>
       <c r="M97" s="22"/>
       <c r="N97" s="11"/>
-    </row>
-    <row r="98" spans="1:14">
+      <c r="O97" s="11"/>
+    </row>
+    <row r="98" spans="1:15">
       <c r="A98" s="11"/>
       <c r="B98" s="14"/>
       <c r="C98" s="11"/>
@@ -10176,8 +10351,9 @@
       <c r="L98" s="21"/>
       <c r="M98" s="22"/>
       <c r="N98" s="11"/>
-    </row>
-    <row r="99" spans="1:14">
+      <c r="O98" s="11"/>
+    </row>
+    <row r="99" spans="1:15">
       <c r="A99" s="11"/>
       <c r="B99" s="14"/>
       <c r="C99" s="11"/>
@@ -10192,8 +10368,9 @@
       <c r="L99" s="21"/>
       <c r="M99" s="22"/>
       <c r="N99" s="11"/>
-    </row>
-    <row r="100" spans="1:14">
+      <c r="O99" s="11"/>
+    </row>
+    <row r="100" spans="1:15">
       <c r="A100" s="11"/>
       <c r="B100" s="14"/>
       <c r="C100" s="11"/>
@@ -10208,8 +10385,9 @@
       <c r="L100" s="21"/>
       <c r="M100" s="22"/>
       <c r="N100" s="11"/>
-    </row>
-    <row r="101" spans="1:14">
+      <c r="O100" s="11"/>
+    </row>
+    <row r="101" spans="1:15">
       <c r="A101" s="11"/>
       <c r="B101" s="14"/>
       <c r="C101" s="11"/>
@@ -10224,8 +10402,9 @@
       <c r="L101" s="21"/>
       <c r="M101" s="22"/>
       <c r="N101" s="11"/>
-    </row>
-    <row r="102" spans="1:14">
+      <c r="O101" s="11"/>
+    </row>
+    <row r="102" spans="1:15">
       <c r="A102" s="11"/>
       <c r="B102" s="14"/>
       <c r="C102" s="11"/>
@@ -10240,8 +10419,9 @@
       <c r="L102" s="21"/>
       <c r="M102" s="22"/>
       <c r="N102" s="11"/>
-    </row>
-    <row r="103" spans="1:14">
+      <c r="O102" s="11"/>
+    </row>
+    <row r="103" spans="1:15">
       <c r="A103" s="11"/>
       <c r="B103" s="14"/>
       <c r="C103" s="11"/>
@@ -10256,8 +10436,9 @@
       <c r="L103" s="21"/>
       <c r="M103" s="22"/>
       <c r="N103" s="11"/>
-    </row>
-    <row r="104" spans="1:14">
+      <c r="O103" s="11"/>
+    </row>
+    <row r="104" spans="1:15">
       <c r="A104" s="11"/>
       <c r="B104" s="14"/>
       <c r="C104" s="11"/>
@@ -10272,8 +10453,9 @@
       <c r="L104" s="21"/>
       <c r="M104" s="22"/>
       <c r="N104" s="11"/>
-    </row>
-    <row r="105" spans="1:14">
+      <c r="O104" s="11"/>
+    </row>
+    <row r="105" spans="1:15">
       <c r="A105" s="11"/>
       <c r="B105" s="14"/>
       <c r="C105" s="11"/>
@@ -10288,8 +10470,9 @@
       <c r="L105" s="21"/>
       <c r="M105" s="22"/>
       <c r="N105" s="11"/>
-    </row>
-    <row r="106" spans="1:14">
+      <c r="O105" s="11"/>
+    </row>
+    <row r="106" spans="1:15">
       <c r="A106" s="11"/>
       <c r="B106" s="14"/>
       <c r="C106" s="11"/>
@@ -10304,8 +10487,9 @@
       <c r="L106" s="21"/>
       <c r="M106" s="22"/>
       <c r="N106" s="11"/>
-    </row>
-    <row r="107" spans="1:14">
+      <c r="O106" s="11"/>
+    </row>
+    <row r="107" spans="1:15">
       <c r="A107" s="11"/>
       <c r="B107" s="14"/>
       <c r="C107" s="11"/>
@@ -10320,8 +10504,9 @@
       <c r="L107" s="21"/>
       <c r="M107" s="22"/>
       <c r="N107" s="11"/>
-    </row>
-    <row r="108" spans="1:14">
+      <c r="O107" s="11"/>
+    </row>
+    <row r="108" spans="1:15">
       <c r="A108" s="11"/>
       <c r="B108" s="14"/>
       <c r="C108" s="11"/>
@@ -10336,8 +10521,9 @@
       <c r="L108" s="21"/>
       <c r="M108" s="22"/>
       <c r="N108" s="11"/>
-    </row>
-    <row r="109" spans="1:14">
+      <c r="O108" s="11"/>
+    </row>
+    <row r="109" spans="1:15">
       <c r="A109" s="11"/>
       <c r="B109" s="14"/>
       <c r="C109" s="11"/>
@@ -10352,8 +10538,9 @@
       <c r="L109" s="21"/>
       <c r="M109" s="22"/>
       <c r="N109" s="11"/>
-    </row>
-    <row r="110" spans="1:14">
+      <c r="O109" s="11"/>
+    </row>
+    <row r="110" spans="1:15">
       <c r="A110" s="11"/>
       <c r="B110" s="14"/>
       <c r="C110" s="11"/>
@@ -10368,8 +10555,9 @@
       <c r="L110" s="21"/>
       <c r="M110" s="22"/>
       <c r="N110" s="11"/>
-    </row>
-    <row r="111" spans="1:14">
+      <c r="O110" s="11"/>
+    </row>
+    <row r="111" spans="1:15">
       <c r="A111" s="11"/>
       <c r="B111" s="14"/>
       <c r="C111" s="11"/>
@@ -10384,8 +10572,9 @@
       <c r="L111" s="21"/>
       <c r="M111" s="22"/>
       <c r="N111" s="11"/>
-    </row>
-    <row r="112" spans="1:14">
+      <c r="O111" s="11"/>
+    </row>
+    <row r="112" spans="1:15">
       <c r="A112" s="11"/>
       <c r="B112" s="14"/>
       <c r="C112" s="11"/>
@@ -10400,8 +10589,9 @@
       <c r="L112" s="21"/>
       <c r="M112" s="22"/>
       <c r="N112" s="11"/>
-    </row>
-    <row r="113" spans="1:14">
+      <c r="O112" s="11"/>
+    </row>
+    <row r="113" spans="1:15">
       <c r="A113" s="11"/>
       <c r="B113" s="14"/>
       <c r="C113" s="11"/>
@@ -10416,8 +10606,9 @@
       <c r="L113" s="21"/>
       <c r="M113" s="22"/>
       <c r="N113" s="11"/>
-    </row>
-    <row r="114" spans="1:14">
+      <c r="O113" s="11"/>
+    </row>
+    <row r="114" spans="1:15">
       <c r="A114" s="11"/>
       <c r="B114" s="14"/>
       <c r="C114" s="11"/>
@@ -10432,8 +10623,9 @@
       <c r="L114" s="21"/>
       <c r="M114" s="22"/>
       <c r="N114" s="11"/>
-    </row>
-    <row r="115" spans="1:14">
+      <c r="O114" s="11"/>
+    </row>
+    <row r="115" spans="1:15">
       <c r="A115" s="11"/>
       <c r="B115" s="14"/>
       <c r="C115" s="11"/>
@@ -10448,8 +10640,9 @@
       <c r="L115" s="21"/>
       <c r="M115" s="22"/>
       <c r="N115" s="11"/>
-    </row>
-    <row r="116" spans="1:14">
+      <c r="O115" s="11"/>
+    </row>
+    <row r="116" spans="1:15">
       <c r="A116" s="11"/>
       <c r="B116" s="14"/>
       <c r="C116" s="11"/>
@@ -10464,8 +10657,9 @@
       <c r="L116" s="21"/>
       <c r="M116" s="22"/>
       <c r="N116" s="11"/>
-    </row>
-    <row r="117" spans="1:14">
+      <c r="O116" s="11"/>
+    </row>
+    <row r="117" spans="1:15">
       <c r="A117" s="11"/>
       <c r="B117" s="14"/>
       <c r="C117" s="11"/>
@@ -10480,8 +10674,9 @@
       <c r="L117" s="21"/>
       <c r="M117" s="22"/>
       <c r="N117" s="11"/>
-    </row>
-    <row r="118" spans="1:14">
+      <c r="O117" s="11"/>
+    </row>
+    <row r="118" spans="1:15">
       <c r="A118" s="11"/>
       <c r="B118" s="14"/>
       <c r="C118" s="11"/>
@@ -10496,8 +10691,9 @@
       <c r="L118" s="21"/>
       <c r="M118" s="22"/>
       <c r="N118" s="11"/>
-    </row>
-    <row r="119" spans="1:14">
+      <c r="O118" s="11"/>
+    </row>
+    <row r="119" spans="1:15">
       <c r="A119" s="11"/>
       <c r="B119" s="14"/>
       <c r="C119" s="11"/>
@@ -10512,8 +10708,9 @@
       <c r="L119" s="21"/>
       <c r="M119" s="22"/>
       <c r="N119" s="11"/>
-    </row>
-    <row r="120" spans="1:14">
+      <c r="O119" s="11"/>
+    </row>
+    <row r="120" spans="1:15">
       <c r="A120" s="11"/>
       <c r="B120" s="14"/>
       <c r="C120" s="11"/>
@@ -10528,8 +10725,9 @@
       <c r="L120" s="21"/>
       <c r="M120" s="22"/>
       <c r="N120" s="11"/>
-    </row>
-    <row r="121" spans="1:14">
+      <c r="O120" s="11"/>
+    </row>
+    <row r="121" spans="1:15">
       <c r="A121" s="11"/>
       <c r="B121" s="14"/>
       <c r="C121" s="11"/>
@@ -10544,8 +10742,9 @@
       <c r="L121" s="21"/>
       <c r="M121" s="22"/>
       <c r="N121" s="11"/>
-    </row>
-    <row r="122" spans="1:14">
+      <c r="O121" s="11"/>
+    </row>
+    <row r="122" spans="1:15">
       <c r="A122" s="11"/>
       <c r="B122" s="14"/>
       <c r="C122" s="11"/>
@@ -10560,8 +10759,9 @@
       <c r="L122" s="21"/>
       <c r="M122" s="22"/>
       <c r="N122" s="11"/>
-    </row>
-    <row r="123" spans="1:14">
+      <c r="O122" s="11"/>
+    </row>
+    <row r="123" spans="1:15">
       <c r="A123" s="11"/>
       <c r="B123" s="14"/>
       <c r="C123" s="11"/>
@@ -10576,8 +10776,9 @@
       <c r="L123" s="21"/>
       <c r="M123" s="22"/>
       <c r="N123" s="11"/>
-    </row>
-    <row r="124" spans="1:14">
+      <c r="O123" s="11"/>
+    </row>
+    <row r="124" spans="1:15">
       <c r="A124" s="11"/>
       <c r="B124" s="14"/>
       <c r="C124" s="11"/>
@@ -10592,8 +10793,9 @@
       <c r="L124" s="21"/>
       <c r="M124" s="22"/>
       <c r="N124" s="11"/>
-    </row>
-    <row r="125" spans="1:14">
+      <c r="O124" s="11"/>
+    </row>
+    <row r="125" spans="1:15">
       <c r="A125" s="11"/>
       <c r="B125" s="14"/>
       <c r="C125" s="11"/>
@@ -10608,8 +10810,9 @@
       <c r="L125" s="21"/>
       <c r="M125" s="22"/>
       <c r="N125" s="11"/>
-    </row>
-    <row r="126" spans="1:14">
+      <c r="O125" s="11"/>
+    </row>
+    <row r="126" spans="1:15">
       <c r="A126" s="11"/>
       <c r="B126" s="14"/>
       <c r="C126" s="11"/>
@@ -10624,8 +10827,9 @@
       <c r="L126" s="21"/>
       <c r="M126" s="22"/>
       <c r="N126" s="11"/>
-    </row>
-    <row r="127" spans="1:14">
+      <c r="O126" s="11"/>
+    </row>
+    <row r="127" spans="1:15">
       <c r="A127" s="11"/>
       <c r="B127" s="14"/>
       <c r="C127" s="11"/>
@@ -10640,8 +10844,9 @@
       <c r="L127" s="21"/>
       <c r="M127" s="22"/>
       <c r="N127" s="11"/>
-    </row>
-    <row r="128" spans="1:14">
+      <c r="O127" s="11"/>
+    </row>
+    <row r="128" spans="1:15">
       <c r="A128" s="11"/>
       <c r="B128" s="14"/>
       <c r="C128" s="11"/>
@@ -10656,8 +10861,9 @@
       <c r="L128" s="21"/>
       <c r="M128" s="22"/>
       <c r="N128" s="11"/>
-    </row>
-    <row r="129" spans="1:14">
+      <c r="O128" s="11"/>
+    </row>
+    <row r="129" spans="1:15">
       <c r="A129" s="11"/>
       <c r="B129" s="14"/>
       <c r="C129" s="11"/>
@@ -10672,8 +10878,9 @@
       <c r="L129" s="21"/>
       <c r="M129" s="22"/>
       <c r="N129" s="11"/>
-    </row>
-    <row r="130" spans="1:14">
+      <c r="O129" s="11"/>
+    </row>
+    <row r="130" spans="1:15">
       <c r="A130" s="11"/>
       <c r="B130" s="14"/>
       <c r="C130" s="11"/>
@@ -10688,8 +10895,9 @@
       <c r="L130" s="21"/>
       <c r="M130" s="22"/>
       <c r="N130" s="11"/>
-    </row>
-    <row r="131" spans="1:14">
+      <c r="O130" s="11"/>
+    </row>
+    <row r="131" spans="1:15">
       <c r="A131" s="11"/>
       <c r="B131" s="14"/>
       <c r="C131" s="11"/>
@@ -10704,8 +10912,9 @@
       <c r="L131" s="21"/>
       <c r="M131" s="22"/>
       <c r="N131" s="11"/>
-    </row>
-    <row r="132" spans="1:14">
+      <c r="O131" s="11"/>
+    </row>
+    <row r="132" spans="1:15">
       <c r="A132" s="11"/>
       <c r="B132" s="14"/>
       <c r="C132" s="11"/>
@@ -10720,8 +10929,9 @@
       <c r="L132" s="21"/>
       <c r="M132" s="22"/>
       <c r="N132" s="11"/>
-    </row>
-    <row r="133" spans="1:14">
+      <c r="O132" s="11"/>
+    </row>
+    <row r="133" spans="1:15">
       <c r="A133" s="11"/>
       <c r="B133" s="14"/>
       <c r="C133" s="11"/>
@@ -10736,8 +10946,9 @@
       <c r="L133" s="21"/>
       <c r="M133" s="22"/>
       <c r="N133" s="11"/>
-    </row>
-    <row r="134" spans="1:14">
+      <c r="O133" s="11"/>
+    </row>
+    <row r="134" spans="1:15">
       <c r="A134" s="11"/>
       <c r="B134" s="14"/>
       <c r="C134" s="11"/>
@@ -10752,8 +10963,9 @@
       <c r="L134" s="21"/>
       <c r="M134" s="22"/>
       <c r="N134" s="11"/>
-    </row>
-    <row r="135" spans="1:14">
+      <c r="O134" s="11"/>
+    </row>
+    <row r="135" spans="1:15">
       <c r="A135" s="11"/>
       <c r="B135" s="14"/>
       <c r="C135" s="11"/>
@@ -10768,8 +10980,9 @@
       <c r="L135" s="21"/>
       <c r="M135" s="22"/>
       <c r="N135" s="11"/>
-    </row>
-    <row r="136" spans="1:14">
+      <c r="O135" s="11"/>
+    </row>
+    <row r="136" spans="1:15">
       <c r="A136" s="11"/>
       <c r="B136" s="14"/>
       <c r="C136" s="11"/>
@@ -10784,8 +10997,9 @@
       <c r="L136" s="21"/>
       <c r="M136" s="22"/>
       <c r="N136" s="11"/>
-    </row>
-    <row r="137" spans="1:14">
+      <c r="O136" s="11"/>
+    </row>
+    <row r="137" spans="1:15">
       <c r="A137" s="11"/>
       <c r="B137" s="14"/>
       <c r="C137" s="11"/>
@@ -10800,8 +11014,9 @@
       <c r="L137" s="21"/>
       <c r="M137" s="22"/>
       <c r="N137" s="11"/>
-    </row>
-    <row r="138" spans="1:14">
+      <c r="O137" s="11"/>
+    </row>
+    <row r="138" spans="1:15">
       <c r="A138" s="11"/>
       <c r="B138" s="14"/>
       <c r="C138" s="11"/>
@@ -10816,8 +11031,9 @@
       <c r="L138" s="21"/>
       <c r="M138" s="22"/>
       <c r="N138" s="11"/>
-    </row>
-    <row r="139" spans="1:14">
+      <c r="O138" s="11"/>
+    </row>
+    <row r="139" spans="1:15">
       <c r="A139" s="11"/>
       <c r="B139" s="14"/>
       <c r="C139" s="11"/>
@@ -10832,8 +11048,9 @@
       <c r="L139" s="21"/>
       <c r="M139" s="22"/>
       <c r="N139" s="11"/>
-    </row>
-    <row r="140" spans="1:14">
+      <c r="O139" s="11"/>
+    </row>
+    <row r="140" spans="1:15">
       <c r="A140" s="11"/>
       <c r="B140" s="14"/>
       <c r="C140" s="11"/>
@@ -10848,8 +11065,9 @@
       <c r="L140" s="21"/>
       <c r="M140" s="22"/>
       <c r="N140" s="11"/>
-    </row>
-    <row r="141" spans="1:14">
+      <c r="O140" s="11"/>
+    </row>
+    <row r="141" spans="1:15">
       <c r="A141" s="11"/>
       <c r="B141" s="14"/>
       <c r="C141" s="11"/>
@@ -10864,8 +11082,9 @@
       <c r="L141" s="21"/>
       <c r="M141" s="22"/>
       <c r="N141" s="11"/>
-    </row>
-    <row r="142" spans="1:14">
+      <c r="O141" s="11"/>
+    </row>
+    <row r="142" spans="1:15">
       <c r="A142" s="11"/>
       <c r="B142" s="14"/>
       <c r="C142" s="11"/>
@@ -10880,8 +11099,9 @@
       <c r="L142" s="21"/>
       <c r="M142" s="22"/>
       <c r="N142" s="11"/>
-    </row>
-    <row r="143" spans="1:14">
+      <c r="O142" s="11"/>
+    </row>
+    <row r="143" spans="1:15">
       <c r="A143" s="11"/>
       <c r="B143" s="14"/>
       <c r="C143" s="11"/>
@@ -10896,8 +11116,9 @@
       <c r="L143" s="21"/>
       <c r="M143" s="22"/>
       <c r="N143" s="11"/>
-    </row>
-    <row r="144" spans="1:14">
+      <c r="O143" s="11"/>
+    </row>
+    <row r="144" spans="1:15">
       <c r="A144" s="11"/>
       <c r="B144" s="14"/>
       <c r="C144" s="11"/>
@@ -10912,8 +11133,9 @@
       <c r="L144" s="21"/>
       <c r="M144" s="22"/>
       <c r="N144" s="11"/>
-    </row>
-    <row r="145" spans="1:14">
+      <c r="O144" s="11"/>
+    </row>
+    <row r="145" spans="1:15">
       <c r="A145" s="11"/>
       <c r="B145" s="14"/>
       <c r="C145" s="11"/>
@@ -10928,8 +11150,9 @@
       <c r="L145" s="21"/>
       <c r="M145" s="22"/>
       <c r="N145" s="11"/>
-    </row>
-    <row r="146" spans="1:14">
+      <c r="O145" s="11"/>
+    </row>
+    <row r="146" spans="1:15">
       <c r="A146" s="11"/>
       <c r="B146" s="14"/>
       <c r="C146" s="11"/>
@@ -10944,8 +11167,9 @@
       <c r="L146" s="21"/>
       <c r="M146" s="22"/>
       <c r="N146" s="11"/>
-    </row>
-    <row r="147" spans="1:14">
+      <c r="O146" s="11"/>
+    </row>
+    <row r="147" spans="1:15">
       <c r="A147" s="11"/>
       <c r="B147" s="14"/>
       <c r="C147" s="11"/>
@@ -10960,8 +11184,9 @@
       <c r="L147" s="21"/>
       <c r="M147" s="22"/>
       <c r="N147" s="11"/>
-    </row>
-    <row r="148" spans="1:14">
+      <c r="O147" s="11"/>
+    </row>
+    <row r="148" spans="1:15">
       <c r="A148" s="11"/>
       <c r="B148" s="14"/>
       <c r="C148" s="11"/>
@@ -10976,8 +11201,9 @@
       <c r="L148" s="21"/>
       <c r="M148" s="22"/>
       <c r="N148" s="11"/>
-    </row>
-    <row r="149" spans="1:14">
+      <c r="O148" s="11"/>
+    </row>
+    <row r="149" spans="1:15">
       <c r="A149" s="11"/>
       <c r="B149" s="14"/>
       <c r="C149" s="11"/>
@@ -10992,8 +11218,9 @@
       <c r="L149" s="21"/>
       <c r="M149" s="22"/>
       <c r="N149" s="11"/>
-    </row>
-    <row r="150" spans="1:14">
+      <c r="O149" s="11"/>
+    </row>
+    <row r="150" spans="1:15">
       <c r="A150" s="11"/>
       <c r="B150" s="14"/>
       <c r="C150" s="11"/>
@@ -11008,8 +11235,9 @@
       <c r="L150" s="21"/>
       <c r="M150" s="22"/>
       <c r="N150" s="11"/>
-    </row>
-    <row r="151" spans="1:14">
+      <c r="O150" s="11"/>
+    </row>
+    <row r="151" spans="1:15">
       <c r="A151" s="11"/>
       <c r="B151" s="14"/>
       <c r="C151" s="11"/>
@@ -11024,8 +11252,9 @@
       <c r="L151" s="21"/>
       <c r="M151" s="22"/>
       <c r="N151" s="11"/>
-    </row>
-    <row r="152" spans="1:14">
+      <c r="O151" s="11"/>
+    </row>
+    <row r="152" spans="1:15">
       <c r="A152" s="11"/>
       <c r="B152" s="14"/>
       <c r="C152" s="11"/>
@@ -11040,8 +11269,9 @@
       <c r="L152" s="21"/>
       <c r="M152" s="22"/>
       <c r="N152" s="11"/>
-    </row>
-    <row r="153" spans="1:14">
+      <c r="O152" s="11"/>
+    </row>
+    <row r="153" spans="1:15">
       <c r="A153" s="11"/>
       <c r="B153" s="14"/>
       <c r="C153" s="11"/>
@@ -11056,8 +11286,9 @@
       <c r="L153" s="21"/>
       <c r="M153" s="22"/>
       <c r="N153" s="11"/>
-    </row>
-    <row r="154" spans="1:14">
+      <c r="O153" s="11"/>
+    </row>
+    <row r="154" spans="1:15">
       <c r="A154" s="11"/>
       <c r="B154" s="14"/>
       <c r="C154" s="11"/>
@@ -11072,8 +11303,9 @@
       <c r="L154" s="21"/>
       <c r="M154" s="22"/>
       <c r="N154" s="11"/>
-    </row>
-    <row r="155" spans="1:14">
+      <c r="O154" s="11"/>
+    </row>
+    <row r="155" spans="1:15">
       <c r="A155" s="11"/>
       <c r="B155" s="14"/>
       <c r="C155" s="11"/>
@@ -11088,8 +11320,9 @@
       <c r="L155" s="21"/>
       <c r="M155" s="22"/>
       <c r="N155" s="11"/>
-    </row>
-    <row r="156" spans="1:14">
+      <c r="O155" s="11"/>
+    </row>
+    <row r="156" spans="1:15">
       <c r="A156" s="11"/>
       <c r="B156" s="14"/>
       <c r="C156" s="11"/>
@@ -11104,8 +11337,9 @@
       <c r="L156" s="21"/>
       <c r="M156" s="22"/>
       <c r="N156" s="11"/>
-    </row>
-    <row r="157" spans="1:14">
+      <c r="O156" s="11"/>
+    </row>
+    <row r="157" spans="1:15">
       <c r="A157" s="11"/>
       <c r="B157" s="14"/>
       <c r="C157" s="11"/>
@@ -11120,8 +11354,9 @@
       <c r="L157" s="21"/>
       <c r="M157" s="22"/>
       <c r="N157" s="11"/>
-    </row>
-    <row r="158" spans="1:14">
+      <c r="O157" s="11"/>
+    </row>
+    <row r="158" spans="1:15">
       <c r="A158" s="11"/>
       <c r="B158" s="14"/>
       <c r="C158" s="11"/>
@@ -11136,8 +11371,9 @@
       <c r="L158" s="21"/>
       <c r="M158" s="22"/>
       <c r="N158" s="11"/>
-    </row>
-    <row r="159" spans="1:14">
+      <c r="O158" s="11"/>
+    </row>
+    <row r="159" spans="1:15">
       <c r="A159" s="11"/>
       <c r="B159" s="14"/>
       <c r="C159" s="11"/>
@@ -11152,8 +11388,9 @@
       <c r="L159" s="21"/>
       <c r="M159" s="22"/>
       <c r="N159" s="11"/>
-    </row>
-    <row r="160" spans="1:14">
+      <c r="O159" s="11"/>
+    </row>
+    <row r="160" spans="1:15">
       <c r="A160" s="11"/>
       <c r="B160" s="14"/>
       <c r="C160" s="11"/>
@@ -11168,8 +11405,9 @@
       <c r="L160" s="21"/>
       <c r="M160" s="22"/>
       <c r="N160" s="11"/>
-    </row>
-    <row r="161" spans="1:14">
+      <c r="O160" s="11"/>
+    </row>
+    <row r="161" spans="1:15">
       <c r="A161" s="11"/>
       <c r="B161" s="14"/>
       <c r="C161" s="11"/>
@@ -11184,8 +11422,9 @@
       <c r="L161" s="21"/>
       <c r="M161" s="22"/>
       <c r="N161" s="11"/>
-    </row>
-    <row r="162" spans="1:14">
+      <c r="O161" s="11"/>
+    </row>
+    <row r="162" spans="1:15">
       <c r="A162" s="11"/>
       <c r="B162" s="14"/>
       <c r="C162" s="11"/>
@@ -11200,8 +11439,9 @@
       <c r="L162" s="21"/>
       <c r="M162" s="22"/>
       <c r="N162" s="11"/>
-    </row>
-    <row r="163" spans="1:14">
+      <c r="O162" s="11"/>
+    </row>
+    <row r="163" spans="1:15">
       <c r="A163" s="11"/>
       <c r="B163" s="14"/>
       <c r="C163" s="11"/>
@@ -11216,8 +11456,9 @@
       <c r="L163" s="21"/>
       <c r="M163" s="22"/>
       <c r="N163" s="11"/>
-    </row>
-    <row r="164" spans="1:14">
+      <c r="O163" s="11"/>
+    </row>
+    <row r="164" spans="1:15">
       <c r="A164" s="11"/>
       <c r="B164" s="14"/>
       <c r="C164" s="11"/>
@@ -11232,8 +11473,9 @@
       <c r="L164" s="21"/>
       <c r="M164" s="22"/>
       <c r="N164" s="11"/>
-    </row>
-    <row r="165" spans="1:14">
+      <c r="O164" s="11"/>
+    </row>
+    <row r="165" spans="1:15">
       <c r="A165" s="11"/>
       <c r="B165" s="14"/>
       <c r="C165" s="11"/>
@@ -11248,8 +11490,9 @@
       <c r="L165" s="21"/>
       <c r="M165" s="22"/>
       <c r="N165" s="11"/>
-    </row>
-    <row r="166" spans="1:14">
+      <c r="O165" s="11"/>
+    </row>
+    <row r="166" spans="1:15">
       <c r="A166" s="11"/>
       <c r="B166" s="14"/>
       <c r="C166" s="11"/>
@@ -11264,8 +11507,9 @@
       <c r="L166" s="21"/>
       <c r="M166" s="22"/>
       <c r="N166" s="11"/>
-    </row>
-    <row r="167" spans="1:14">
+      <c r="O166" s="11"/>
+    </row>
+    <row r="167" spans="1:15">
       <c r="A167" s="11"/>
       <c r="B167" s="14"/>
       <c r="C167" s="11"/>
@@ -11280,8 +11524,9 @@
       <c r="L167" s="21"/>
       <c r="M167" s="22"/>
       <c r="N167" s="11"/>
-    </row>
-    <row r="168" spans="1:14">
+      <c r="O167" s="11"/>
+    </row>
+    <row r="168" spans="1:15">
       <c r="A168" s="11"/>
       <c r="B168" s="14"/>
       <c r="C168" s="11"/>
@@ -11296,8 +11541,9 @@
       <c r="L168" s="21"/>
       <c r="M168" s="22"/>
       <c r="N168" s="11"/>
-    </row>
-    <row r="169" spans="1:14">
+      <c r="O168" s="11"/>
+    </row>
+    <row r="169" spans="1:15">
       <c r="A169" s="11"/>
       <c r="B169" s="14"/>
       <c r="C169" s="11"/>
@@ -11312,8 +11558,9 @@
       <c r="L169" s="21"/>
       <c r="M169" s="22"/>
       <c r="N169" s="11"/>
-    </row>
-    <row r="170" spans="1:14">
+      <c r="O169" s="11"/>
+    </row>
+    <row r="170" spans="1:15">
       <c r="A170" s="11"/>
       <c r="B170" s="14"/>
       <c r="C170" s="11"/>
@@ -11328,8 +11575,9 @@
       <c r="L170" s="21"/>
       <c r="M170" s="22"/>
       <c r="N170" s="11"/>
-    </row>
-    <row r="171" spans="1:14">
+      <c r="O170" s="11"/>
+    </row>
+    <row r="171" spans="1:15">
       <c r="A171" s="11"/>
       <c r="B171" s="14"/>
       <c r="C171" s="11"/>
@@ -11344,8 +11592,9 @@
       <c r="L171" s="21"/>
       <c r="M171" s="22"/>
       <c r="N171" s="11"/>
-    </row>
-    <row r="172" spans="1:14">
+      <c r="O171" s="11"/>
+    </row>
+    <row r="172" spans="1:15">
       <c r="A172" s="11"/>
       <c r="B172" s="14"/>
       <c r="C172" s="11"/>
@@ -11360,8 +11609,9 @@
       <c r="L172" s="21"/>
       <c r="M172" s="22"/>
       <c r="N172" s="11"/>
-    </row>
-    <row r="173" spans="1:14">
+      <c r="O172" s="11"/>
+    </row>
+    <row r="173" spans="1:15">
       <c r="A173" s="11"/>
       <c r="B173" s="14"/>
       <c r="C173" s="11"/>
@@ -11376,8 +11626,9 @@
       <c r="L173" s="21"/>
       <c r="M173" s="22"/>
       <c r="N173" s="11"/>
-    </row>
-    <row r="174" spans="1:14">
+      <c r="O173" s="11"/>
+    </row>
+    <row r="174" spans="1:15">
       <c r="A174" s="11"/>
       <c r="B174" s="14"/>
       <c r="C174" s="11"/>
@@ -11392,8 +11643,9 @@
       <c r="L174" s="21"/>
       <c r="M174" s="22"/>
       <c r="N174" s="11"/>
-    </row>
-    <row r="175" spans="1:14">
+      <c r="O174" s="11"/>
+    </row>
+    <row r="175" spans="1:15">
       <c r="A175" s="11"/>
       <c r="B175" s="14"/>
       <c r="C175" s="11"/>
@@ -11408,8 +11660,9 @@
       <c r="L175" s="21"/>
       <c r="M175" s="22"/>
       <c r="N175" s="11"/>
-    </row>
-    <row r="176" spans="1:14">
+      <c r="O175" s="11"/>
+    </row>
+    <row r="176" spans="1:15">
       <c r="A176" s="11"/>
       <c r="B176" s="14"/>
       <c r="C176" s="11"/>
@@ -11424,8 +11677,9 @@
       <c r="L176" s="21"/>
       <c r="M176" s="22"/>
       <c r="N176" s="11"/>
-    </row>
-    <row r="177" spans="1:14">
+      <c r="O176" s="11"/>
+    </row>
+    <row r="177" spans="1:15">
       <c r="A177" s="11"/>
       <c r="B177" s="14"/>
       <c r="C177" s="11"/>
@@ -11440,8 +11694,9 @@
       <c r="L177" s="21"/>
       <c r="M177" s="22"/>
       <c r="N177" s="11"/>
-    </row>
-    <row r="178" spans="1:14">
+      <c r="O177" s="11"/>
+    </row>
+    <row r="178" spans="1:15">
       <c r="A178" s="11"/>
       <c r="B178" s="14"/>
       <c r="C178" s="11"/>
@@ -11456,8 +11711,9 @@
       <c r="L178" s="21"/>
       <c r="M178" s="22"/>
       <c r="N178" s="11"/>
-    </row>
-    <row r="179" spans="1:14">
+      <c r="O178" s="11"/>
+    </row>
+    <row r="179" spans="1:15">
       <c r="A179" s="11"/>
       <c r="B179" s="14"/>
       <c r="C179" s="11"/>
@@ -11472,8 +11728,9 @@
       <c r="L179" s="21"/>
       <c r="M179" s="22"/>
       <c r="N179" s="11"/>
-    </row>
-    <row r="180" spans="1:14">
+      <c r="O179" s="11"/>
+    </row>
+    <row r="180" spans="1:15">
       <c r="A180" s="11"/>
       <c r="B180" s="14"/>
       <c r="C180" s="11"/>
@@ -11488,8 +11745,9 @@
       <c r="L180" s="21"/>
       <c r="M180" s="22"/>
       <c r="N180" s="11"/>
-    </row>
-    <row r="181" spans="1:14">
+      <c r="O180" s="11"/>
+    </row>
+    <row r="181" spans="1:15">
       <c r="A181" s="11"/>
       <c r="B181" s="14"/>
       <c r="C181" s="11"/>
@@ -11504,8 +11762,9 @@
       <c r="L181" s="21"/>
       <c r="M181" s="22"/>
       <c r="N181" s="11"/>
-    </row>
-    <row r="182" spans="1:14">
+      <c r="O181" s="11"/>
+    </row>
+    <row r="182" spans="1:15">
       <c r="A182" s="11"/>
       <c r="B182" s="14"/>
       <c r="C182" s="11"/>
@@ -11520,8 +11779,9 @@
       <c r="L182" s="21"/>
       <c r="M182" s="22"/>
       <c r="N182" s="11"/>
-    </row>
-    <row r="183" spans="1:14">
+      <c r="O182" s="11"/>
+    </row>
+    <row r="183" spans="1:15">
       <c r="A183" s="11"/>
       <c r="B183" s="14"/>
       <c r="C183" s="11"/>
@@ -11536,8 +11796,9 @@
       <c r="L183" s="21"/>
       <c r="M183" s="22"/>
       <c r="N183" s="11"/>
-    </row>
-    <row r="184" spans="1:14">
+      <c r="O183" s="11"/>
+    </row>
+    <row r="184" spans="1:15">
       <c r="A184" s="11"/>
       <c r="B184" s="14"/>
       <c r="C184" s="11"/>
@@ -11552,8 +11813,9 @@
       <c r="L184" s="21"/>
       <c r="M184" s="22"/>
       <c r="N184" s="11"/>
-    </row>
-    <row r="185" spans="1:14">
+      <c r="O184" s="11"/>
+    </row>
+    <row r="185" spans="1:15">
       <c r="A185" s="11"/>
       <c r="B185" s="14"/>
       <c r="C185" s="11"/>
@@ -11568,8 +11830,9 @@
       <c r="L185" s="21"/>
       <c r="M185" s="22"/>
       <c r="N185" s="11"/>
-    </row>
-    <row r="186" spans="1:14">
+      <c r="O185" s="11"/>
+    </row>
+    <row r="186" spans="1:15">
       <c r="A186" s="11"/>
       <c r="B186" s="14"/>
       <c r="C186" s="11"/>
@@ -11584,8 +11847,9 @@
       <c r="L186" s="21"/>
       <c r="M186" s="22"/>
       <c r="N186" s="11"/>
-    </row>
-    <row r="187" spans="1:14">
+      <c r="O186" s="11"/>
+    </row>
+    <row r="187" spans="1:15">
       <c r="A187" s="11"/>
       <c r="B187" s="14"/>
       <c r="C187" s="11"/>
@@ -11600,8 +11864,9 @@
       <c r="L187" s="21"/>
       <c r="M187" s="22"/>
       <c r="N187" s="11"/>
-    </row>
-    <row r="188" spans="1:14">
+      <c r="O187" s="11"/>
+    </row>
+    <row r="188" spans="1:15">
       <c r="A188" s="11"/>
       <c r="B188" s="14"/>
       <c r="C188" s="11"/>
@@ -11616,8 +11881,9 @@
       <c r="L188" s="21"/>
       <c r="M188" s="22"/>
       <c r="N188" s="11"/>
-    </row>
-    <row r="189" spans="1:14">
+      <c r="O188" s="11"/>
+    </row>
+    <row r="189" spans="1:15">
       <c r="A189" s="11"/>
       <c r="B189" s="14"/>
       <c r="C189" s="11"/>
@@ -11632,8 +11898,9 @@
       <c r="L189" s="21"/>
       <c r="M189" s="22"/>
       <c r="N189" s="11"/>
-    </row>
-    <row r="190" spans="1:14">
+      <c r="O189" s="11"/>
+    </row>
+    <row r="190" spans="1:15">
       <c r="A190" s="11"/>
       <c r="B190" s="14"/>
       <c r="C190" s="11"/>
@@ -11648,8 +11915,9 @@
       <c r="L190" s="21"/>
       <c r="M190" s="22"/>
       <c r="N190" s="11"/>
-    </row>
-    <row r="191" spans="1:14">
+      <c r="O190" s="11"/>
+    </row>
+    <row r="191" spans="1:15">
       <c r="A191" s="11"/>
       <c r="B191" s="14"/>
       <c r="C191" s="11"/>
@@ -11664,8 +11932,9 @@
       <c r="L191" s="21"/>
       <c r="M191" s="22"/>
       <c r="N191" s="11"/>
-    </row>
-    <row r="192" spans="1:14">
+      <c r="O191" s="11"/>
+    </row>
+    <row r="192" spans="1:15">
       <c r="A192" s="11"/>
       <c r="B192" s="14"/>
       <c r="C192" s="11"/>
@@ -11680,8 +11949,9 @@
       <c r="L192" s="21"/>
       <c r="M192" s="22"/>
       <c r="N192" s="11"/>
-    </row>
-    <row r="193" spans="1:14">
+      <c r="O192" s="11"/>
+    </row>
+    <row r="193" spans="1:15">
       <c r="A193" s="11"/>
       <c r="B193" s="14"/>
       <c r="C193" s="11"/>
@@ -11696,8 +11966,9 @@
       <c r="L193" s="21"/>
       <c r="M193" s="22"/>
       <c r="N193" s="11"/>
-    </row>
-    <row r="194" spans="1:14">
+      <c r="O193" s="11"/>
+    </row>
+    <row r="194" spans="1:15">
       <c r="A194" s="11"/>
       <c r="B194" s="14"/>
       <c r="C194" s="11"/>
@@ -11712,8 +11983,9 @@
       <c r="L194" s="21"/>
       <c r="M194" s="22"/>
       <c r="N194" s="11"/>
-    </row>
-    <row r="195" spans="1:14">
+      <c r="O194" s="11"/>
+    </row>
+    <row r="195" spans="1:15">
       <c r="A195" s="11"/>
       <c r="B195" s="14"/>
       <c r="C195" s="11"/>
@@ -11728,8 +12000,9 @@
       <c r="L195" s="21"/>
       <c r="M195" s="22"/>
       <c r="N195" s="11"/>
-    </row>
-    <row r="196" spans="1:14">
+      <c r="O195" s="11"/>
+    </row>
+    <row r="196" spans="1:15">
       <c r="A196" s="11"/>
       <c r="B196" s="14"/>
       <c r="C196" s="11"/>
@@ -11744,8 +12017,9 @@
       <c r="L196" s="21"/>
       <c r="M196" s="22"/>
       <c r="N196" s="11"/>
-    </row>
-    <row r="197" spans="1:14">
+      <c r="O196" s="11"/>
+    </row>
+    <row r="197" spans="1:15">
       <c r="A197" s="11"/>
       <c r="B197" s="14"/>
       <c r="C197" s="11"/>
@@ -11760,8 +12034,9 @@
       <c r="L197" s="21"/>
       <c r="M197" s="22"/>
       <c r="N197" s="11"/>
-    </row>
-    <row r="198" spans="1:14">
+      <c r="O197" s="11"/>
+    </row>
+    <row r="198" spans="1:15">
       <c r="A198" s="11"/>
       <c r="B198" s="14"/>
       <c r="C198" s="11"/>
@@ -11776,8 +12051,9 @@
       <c r="L198" s="21"/>
       <c r="M198" s="22"/>
       <c r="N198" s="11"/>
-    </row>
-    <row r="199" spans="1:14">
+      <c r="O198" s="11"/>
+    </row>
+    <row r="199" spans="1:15">
       <c r="A199" s="11"/>
       <c r="B199" s="14"/>
       <c r="C199" s="11"/>
@@ -11792,8 +12068,9 @@
       <c r="L199" s="21"/>
       <c r="M199" s="22"/>
       <c r="N199" s="11"/>
-    </row>
-    <row r="200" spans="1:14">
+      <c r="O199" s="11"/>
+    </row>
+    <row r="200" spans="1:15">
       <c r="A200" s="11"/>
       <c r="B200" s="14"/>
       <c r="C200" s="11"/>
@@ -11808,8 +12085,9 @@
       <c r="L200" s="21"/>
       <c r="M200" s="22"/>
       <c r="N200" s="11"/>
-    </row>
-    <row r="201" spans="1:14">
+      <c r="O200" s="11"/>
+    </row>
+    <row r="201" spans="1:15">
       <c r="A201" s="11"/>
       <c r="B201" s="14"/>
       <c r="C201" s="11"/>
@@ -11824,8 +12102,9 @@
       <c r="L201" s="21"/>
       <c r="M201" s="22"/>
       <c r="N201" s="11"/>
-    </row>
-    <row r="202" spans="1:14">
+      <c r="O201" s="11"/>
+    </row>
+    <row r="202" spans="1:15">
       <c r="A202" s="11"/>
       <c r="B202" s="14"/>
       <c r="C202" s="11"/>
@@ -11840,8 +12119,9 @@
       <c r="L202" s="21"/>
       <c r="M202" s="22"/>
       <c r="N202" s="11"/>
-    </row>
-    <row r="203" spans="1:14">
+      <c r="O202" s="11"/>
+    </row>
+    <row r="203" spans="1:15">
       <c r="A203" s="11"/>
       <c r="B203" s="14"/>
       <c r="C203" s="11"/>
@@ -11856,8 +12136,9 @@
       <c r="L203" s="21"/>
       <c r="M203" s="22"/>
       <c r="N203" s="11"/>
-    </row>
-    <row r="204" spans="1:14">
+      <c r="O203" s="11"/>
+    </row>
+    <row r="204" spans="1:15">
       <c r="A204" s="11"/>
       <c r="B204" s="14"/>
       <c r="C204" s="11"/>
@@ -11872,14 +12153,15 @@
       <c r="L204" s="21"/>
       <c r="M204" s="22"/>
       <c r="N204" s="11"/>
+      <c r="O204" s="11"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C204">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D204">
-      <formula1>"Y,N"</formula1>
+      <formula1>"N,CM,CLIENT"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F204">
       <formula1>"Y,N"</formula1>
@@ -11889,6 +12171,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N5:N204">
       <formula1>"CRR,BCBS"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5:O204">
+      <formula1>"MIXED,SHARED"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -23600,7 +23885,7 @@
     </row>
     <row r="3">
       <c r="A3" s="30" t="str" cm="1">
-        <f t="array" ref="A3">ResultsStatusText(SACCR_RunInputs,NettingSets!$A:$N,Trades!$A:$W,Params!$A:$H)</f>
+        <f t="array" ref="A3">ResultsStatusText(SACCR_RunInputs,NettingSets!$A:$O,Trades!$A:$W,Params!$A:$H)</f>
         <v>No results: press Run SA-CCR.</v>
       </c>
     </row>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="945">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -2903,6 +2903,12 @@
   </si>
   <si>
     <t>Not implemented: declare SHARED under Margin agreements; the netting set is rejected.</t>
+  </si>
+  <si>
+    <t>Unmargined maturity factors; collateral basis per regime (see Results columns Z-AC).</t>
+  </si>
+  <si>
+    <t>ReadMe</t>
   </si>
 </sst>
 </file>
@@ -2925,13 +2931,12 @@
     <numFmt numFmtId="176" formatCode="0.0E+00"/>
     <numFmt numFmtId="177" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2939,7 +2944,6 @@
       <color rgb="FF1F3864"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
@@ -2947,7 +2951,6 @@
       <color rgb="FF595959"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2955,7 +2958,6 @@
       <color rgb="FF1F3864"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2963,14 +2965,12 @@
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2978,14 +2978,12 @@
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
@@ -2993,14 +2991,12 @@
       <color rgb="FF595959"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3008,7 +3004,6 @@
       <color rgb="FFC00000"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
@@ -3016,7 +3011,6 @@
       <color rgb="FF7F6000"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -3030,7 +3024,6 @@
       <color rgb="FF375623"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3038,31 +3031,93 @@
       <color rgb="FF9C0006"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF375623"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3099,8 +3154,23 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -3141,13 +3211,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3315,6 +3401,57 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3629,508 +3766,538 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="shReadme">
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C3:E72"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:X71"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="2.7109375" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="100.7109375" customWidth="1"/>
+    <col min="1" max="2" width="4" style="57" customWidth="1"/>
+    <col min="3" max="3" width="46" style="57" customWidth="1"/>
+    <col min="4" max="4" width="126.85546875" style="57" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" style="57" customWidth="1"/>
+    <col min="6" max="24" width="0" style="57" hidden="1"/>
+    <col min="25" max="16384" width="9.140625" style="57" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="55" customFormat="1"/>
-    <row r="2" ht="26" customHeight="1" s="56" customFormat="1"/>
-    <row r="3" spans="4:5" ht="34" customHeight="1">
-      <c r="D3" s="1" t="s">
+    <row r="1" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="58" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="4:5">
-      <c r="D4" s="2" t="s">
+      <c r="C1" s="60"/>
+      <c r="D1" s="59"/>
+      <c r="S1" s="61"/>
+    </row>
+    <row r="2" spans="2:19" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="62" t="s">
+        <v>944</v>
+      </c>
+      <c r="C2" s="64"/>
+      <c r="D2" s="63"/>
+      <c r="S2" s="61"/>
+    </row>
+    <row r="3" spans="2:19" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="65"/>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C4" s="66" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="4:5">
-      <c r="D7" s="3" t="s">
+    <row r="5" spans="2:19" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="4:5" ht="28" customHeight="1">
-      <c r="D8" s="4" t="s">
+      <c r="D6" s="67"/>
+    </row>
+    <row r="7" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="D7" s="71" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="4:5" ht="28" customHeight="1">
-      <c r="D9" s="4" t="s">
+    <row r="8" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="D8" s="71" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="4:5" ht="28" customHeight="1">
-      <c r="D10" s="4" t="s">
+    <row r="9" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="D9" s="71" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="4:5" ht="16" customHeight="1">
-      <c r="D11" s="4" t="s">
+    <row r="10" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="D10" s="71" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="4:5" ht="28" customHeight="1">
-      <c r="D12" s="4" t="s">
+    <row r="11" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="D11" s="71" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="4:5" ht="28" customHeight="1">
-      <c r="D13" s="4" t="s">
+    <row r="12" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="D12" s="71" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="4:5" ht="28" customHeight="1">
-      <c r="D14" s="4" t="s">
+    <row r="13" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="D13" s="71" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="4:5">
-      <c r="D16" s="3" t="s">
+    <row r="14" spans="2:19" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="70"/>
+      <c r="D14" s="72"/>
+    </row>
+    <row r="15" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="4:5" ht="40" customHeight="1">
-      <c r="D17" s="4" t="s">
+      <c r="D15" s="73"/>
+    </row>
+    <row r="16" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="D16" s="71" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="4:5" ht="40" customHeight="1">
-      <c r="D18" s="4" t="s">
+    <row r="17" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="D17" s="71" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="4:5" ht="40" customHeight="1">
-      <c r="D19" s="4" t="s">
+    <row r="18" spans="3:4" ht="36" x14ac:dyDescent="0.25">
+      <c r="C18" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="D18" s="71" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="20" spans="4:5" ht="28" customHeight="1">
-      <c r="D20" s="4" t="s">
+    <row r="19" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="D19" s="71" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="4:5" ht="40" customHeight="1">
-      <c r="D21" s="4" t="s">
+    <row r="20" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="D20" s="71" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="4:5" ht="28" customHeight="1">
-      <c r="D22" s="4" t="s">
+    <row r="21" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="D21" s="71" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="4:5" ht="40" customHeight="1">
-      <c r="D23" s="4" t="s">
+    <row r="22" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="D22" s="71" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="4:5">
-      <c r="D25" s="3" t="s">
+    <row r="23" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="70"/>
+      <c r="D23" s="72"/>
+    </row>
+    <row r="24" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="4:5" ht="28" customHeight="1">
-      <c r="D26" s="4" t="s">
+      <c r="D24" s="73"/>
+    </row>
+    <row r="25" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="D25" s="71" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="27" spans="4:5">
-      <c r="D27" s="4" t="s">
+    <row r="26" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="D26" s="71" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="4:5">
-      <c r="D28" s="4" t="s">
+    <row r="27" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="D27" s="71" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="4:5" ht="28" customHeight="1">
-      <c r="D29" s="4" t="s">
+    <row r="28" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="D28" s="71" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="4:5">
-      <c r="D30" s="4" t="s">
+    <row r="29" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="D29" s="71" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="4:5" ht="28" customHeight="1">
-      <c r="D31" s="4" t="s">
+    <row r="30" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="D30" s="71" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="32" spans="4:5" ht="28" customHeight="1">
-      <c r="D32" s="4" t="s">
+    <row r="31" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="D31" s="71" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="33" spans="4:5">
-      <c r="D33" s="4" t="s">
+    <row r="32" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="D32" s="71" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="4:5">
-      <c r="D34" s="4" t="s">
+    <row r="33" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="D33" s="71" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="4:5" ht="28" customHeight="1">
-      <c r="D35" s="4" t="s">
+    <row r="34" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="D34" s="71" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="4:5">
-      <c r="D36" s="4" t="s">
+    <row r="35" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="D35" s="71" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="4:5">
-      <c r="D38" s="3" t="s">
+    <row r="36" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="70"/>
+      <c r="D36" s="72"/>
+    </row>
+    <row r="37" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="4:5">
-      <c r="D39" s="4" t="s">
+      <c r="D37" s="73"/>
+    </row>
+    <row r="38" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="D38" s="71" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="4:5">
-      <c r="D40" s="4" t="s">
+    <row r="39" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="D39" s="71" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="4:5">
-      <c r="D41" s="4" t="s">
+    <row r="40" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="D40" s="71" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="4:5">
-      <c r="D42" s="4" t="s">
+    <row r="41" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="D41" s="71" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="4:5">
-      <c r="D43" s="4" t="s">
+    <row r="42" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="D42" s="71" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="4:5">
-      <c r="D44" s="4" t="s">
+    <row r="43" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="D43" s="71" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="4:5">
-      <c r="D45" s="4" t="s">
+    <row r="44" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="D44" s="71" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="4:5">
-      <c r="D46" s="4" t="s">
+    <row r="45" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="D45" s="71" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="4:5">
-      <c r="D47" s="4" t="s">
+    <row r="46" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="D46" s="71" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="4:5">
-      <c r="D48" s="4" t="s">
+    <row r="47" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="D47" s="71" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="49" spans="4:5">
-      <c r="D49" s="4" t="s">
+    <row r="48" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="D48" s="71" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="51" spans="4:5">
-      <c r="D51" s="3" t="s">
+    <row r="49" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="70"/>
+      <c r="D49" s="72"/>
+    </row>
+    <row r="50" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="4:5">
-      <c r="D52" s="4" t="s">
+      <c r="D50" s="73"/>
+    </row>
+    <row r="51" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="D51" s="71" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="53" spans="4:5">
-      <c r="D53" s="4" t="s">
+    <row r="52" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="D52" s="71" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="4:5">
-      <c r="D54" s="4" t="s">
+    <row r="53" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="D53" s="71" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="4:5">
-      <c r="D55" s="4" t="s">
+    <row r="54" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="D54" s="71" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="4:5">
-      <c r="D56" s="4" t="s">
+    <row r="55" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="D55" s="71" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="4:5">
-      <c r="D57" s="4" t="s">
+    <row r="56" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="69" t="s">
         <v>88</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="D56" s="71" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="58" spans="4:5">
-      <c r="D58" s="4" t="s">
+    <row r="57" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="D57" s="71" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="4:5">
-      <c r="D59" s="4" t="s">
+    <row r="58" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C58" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="D58" s="71" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="4:5">
-      <c r="D60" s="4" t="s">
+    <row r="59" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="D59" s="71" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="4:5">
-      <c r="D61" s="4" t="s">
+    <row r="60" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="D60" s="71" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="63" spans="4:5">
-      <c r="D63" s="3" t="s">
+    <row r="61" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="70"/>
+      <c r="D61" s="72"/>
+    </row>
+    <row r="62" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="E63" s="3"/>
-    </row>
-    <row r="64" spans="4:5" ht="28" customHeight="1">
-      <c r="D64" s="4" t="s">
+      <c r="D62" s="73"/>
+    </row>
+    <row r="63" spans="3:4" ht="36" x14ac:dyDescent="0.25">
+      <c r="C63" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="D63" s="71" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="65" spans="4:5" ht="28" customHeight="1">
-      <c r="D65" s="4" t="s">
+    <row r="64" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="69" t="s">
         <v>907</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="D64" s="71" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="66" spans="4:5">
-      <c r="D66" s="4" t="s">
+    <row r="65" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="D65" s="71" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="67" spans="4:5">
-      <c r="D67" s="4" t="s">
+    <row r="66" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="68" spans="4:5">
-      <c r="D68" s="4" t="s">
+      <c r="D66" s="71" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="D67" s="71" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="69" spans="4:5" ht="28" customHeight="1">
-      <c r="D69" s="4" t="s">
+    <row r="68" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="D68" s="71" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="71" spans="4:5">
-      <c r="D71" s="3" t="s">
+    <row r="69" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="70"/>
+      <c r="D69" s="72"/>
+    </row>
+    <row r="70" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="E71" s="3"/>
-    </row>
-    <row r="72" spans="4:5" ht="28" customHeight="1">
-      <c r="D72" s="4" t="s">
+      <c r="D70" s="73"/>
+    </row>
+    <row r="71" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C71" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="D71" s="71" t="s">
         <v>113</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D71:E71"/>
-  </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <legacyDrawing r:id="rId1"/>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -79,7 +79,7 @@
     <t>SA-CCR Calculator</t>
   </si>
   <si>
-    <t>Standardised approach for counterparty credit risk - common Basel CRE52 core with an EU CRR (Art. 274-280f) rules layer. VBA engine v1.1.0.</t>
+    <t>Standardised approach for counterparty credit risk - common Basel CRE52 core with an EU CRR (Art. 274-280f) rules layer. VBA engine v1.0.0.</t>
   </si>
   <si>
     <t>How to use</t>
@@ -2931,7 +2931,7 @@
     <numFmt numFmtId="176" formatCode="0.0E+00"/>
     <numFmt numFmtId="177" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3112,6 +3112,13 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color rgb="FF1F3864"/>
       <name val="Aptos"/>
       <family val="2"/>
@@ -3434,7 +3441,7 @@
     <xf numFmtId="0" fontId="24" fillId="7" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -23,29 +23,31 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Basel_vs_CRR!$C$6:$K$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Trades!$C$6:$Z$71</definedName>
-    <definedName name="Alpha">Params!$E$9</definedName>
-    <definedName name="AsOfDate">Params!$E$7</definedName>
-    <definedName name="BasisFactor">Params!$E$18</definedName>
-    <definedName name="BusinessDaysPerYear">Params!$E$12</definedName>
-    <definedName name="DaysPerYear">Params!$E$11</definedName>
-    <definedName name="FX_Table">Params!$C$58:$E$63</definedName>
-    <definedName name="IRBucketOffset">Params!$E$23</definedName>
-    <definedName name="IRCorrBucket12">Params!$E$20</definedName>
-    <definedName name="IRCorrBucket13">Params!$E$22</definedName>
-    <definedName name="IRCorrBucket23">Params!$E$21</definedName>
-    <definedName name="LambdaThresholdCO">Params!$E$26</definedName>
-    <definedName name="LambdaThresholdIR">Params!$E$25</definedName>
-    <definedName name="MinMaturityBD">Params!$E$13</definedName>
-    <definedName name="MPORFloorBilateral">Params!$E$15</definedName>
-    <definedName name="MPORFloorCleared">Params!$E$16</definedName>
-    <definedName name="MPORFloorLarge">Params!$E$17</definedName>
-    <definedName name="MultiplierFloor">Params!$E$10</definedName>
-    <definedName name="Regime">Params!$E$24</definedName>
-    <definedName name="ReportingCcy">Params!$E$8</definedName>
+    <definedName name="Alpha">Params!$E$8</definedName>
+    <definedName name="AsOfDate">Params!$E$6</definedName>
+    <definedName name="BasisFactor">Params!$E$17</definedName>
+    <definedName name="BusinessDaysPerYear">Params!$E$11</definedName>
+    <definedName name="DaysPerYear">Params!$E$10</definedName>
+    <definedName name="FX_Table">Params!$C$57:$E$62</definedName>
+    <definedName name="IRBucketOffset">Params!$E$22</definedName>
+    <definedName name="IRCorrBucket12">Params!$E$19</definedName>
+    <definedName name="IRCorrBucket13">Params!$E$21</definedName>
+    <definedName name="IRCorrBucket23">Params!$E$20</definedName>
+    <definedName name="LambdaThresholdCO">Params!$E$25</definedName>
+    <definedName name="LambdaThresholdIR">Params!$E$24</definedName>
+    <definedName name="MinMaturityBD">Params!$E$12</definedName>
+    <definedName name="MPORFloorBilateral">Params!$E$14</definedName>
+    <definedName name="MPORFloorCleared">Params!$E$15</definedName>
+    <definedName name="MPORFloorLarge">Params!$E$16</definedName>
+    <definedName name="MultiplierFloor">Params!$E$9</definedName>
+    <definedName name="Params_Code">Params!$C$5</definedName>
+    <definedName name="Params_Value">Params!$E$5</definedName>
+    <definedName name="Regime">Params!$E$23</definedName>
+    <definedName name="ReportingCcy">Params!$E$7</definedName>
     <definedName name="SACCR_RunInputs" hidden="1">""</definedName>
-    <definedName name="SDFloorBD">Params!$E$14</definedName>
-    <definedName name="SF_Table">Params!$C$29:$K$55</definedName>
-    <definedName name="VolatilityFactor">Params!$E$19</definedName>
+    <definedName name="SDFloorBD">Params!$E$13</definedName>
+    <definedName name="SF_Table">Params!$C$28:$K$54</definedName>
+    <definedName name="VolatilityFactor">Params!$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2915,7 +2917,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="0.00##"/>
@@ -2930,8 +2932,9 @@
     <numFmt numFmtId="175" formatCode="#,##0.0#####"/>
     <numFmt numFmtId="176" formatCode="0.0E+00"/>
     <numFmt numFmtId="177" formatCode="0.000000000"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="49">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3123,8 +3126,141 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3176,8 +3312,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -3234,13 +3400,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3457,6 +3683,132 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="6" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="6" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="32" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="32" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="10" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="6" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="10" borderId="6" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="11" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3781,526 +4133,526 @@
   <dimension ref="A1:X71"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4" style="57" customWidth="1"/>
-    <col min="3" max="3" width="46" style="57" customWidth="1"/>
-    <col min="4" max="4" width="126.85546875" style="57" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" style="57" customWidth="1"/>
-    <col min="6" max="24" width="0" style="57" hidden="1"/>
-    <col min="25" max="16384" width="9.140625" style="57" hidden="1"/>
+    <col min="1" max="2" width="4" style="77" customWidth="1"/>
+    <col min="3" max="3" width="46" style="77" customWidth="1"/>
+    <col min="4" max="4" width="126.875" style="77" customWidth="1"/>
+    <col min="5" max="5" width="4.75" style="77" customWidth="1"/>
+    <col min="6" max="24" width="0" style="77" hidden="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.125" style="77" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="59"/>
-      <c r="S1" s="61"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="78"/>
+      <c r="S1" s="80"/>
     </row>
     <row r="2" spans="2:19" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="92" t="s">
         <v>944</v>
       </c>
-      <c r="C2" s="64"/>
-      <c r="D2" s="63"/>
-      <c r="S2" s="61"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="81"/>
+      <c r="S2" s="80"/>
     </row>
     <row r="3" spans="2:19" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="65"/>
+      <c r="C3" s="83"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="84" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="67"/>
+      <c r="D6" s="85"/>
     </row>
     <row r="7" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="89" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="71" t="s">
+      <c r="D8" s="89" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="89" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="71" t="s">
+      <c r="D10" s="89" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="69" t="s">
+      <c r="C11" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="71" t="s">
+      <c r="D11" s="89" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="69" t="s">
+      <c r="C12" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="71" t="s">
+      <c r="D12" s="89" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="71" t="s">
+      <c r="D13" s="89" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="2:19" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="70"/>
-      <c r="D14" s="72"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="90"/>
     </row>
     <row r="15" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="73"/>
+      <c r="D15" s="91"/>
     </row>
     <row r="16" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="71" t="s">
+      <c r="D16" s="89" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="71" t="s">
+      <c r="D17" s="89" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="3:4" ht="36" x14ac:dyDescent="0.25">
-      <c r="C18" s="69" t="s">
+    <row r="18" spans="3:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="C18" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="71" t="s">
+      <c r="D18" s="89" t="s">
         <v>903</v>
       </c>
     </row>
     <row r="19" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="69" t="s">
+      <c r="C19" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="71" t="s">
+      <c r="D19" s="89" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="89" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="21" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="71" t="s">
+      <c r="D21" s="89" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="22" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="69" t="s">
+      <c r="C22" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="71" t="s">
+      <c r="D22" s="89" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="23" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="70"/>
-      <c r="D23" s="72"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="90"/>
     </row>
     <row r="24" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="73"/>
+      <c r="D24" s="91"/>
     </row>
     <row r="25" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="71" t="s">
+      <c r="D25" s="89" t="s">
         <v>917</v>
       </c>
     </row>
     <row r="26" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="69" t="s">
+      <c r="C26" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="D26" s="89" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="27" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="69" t="s">
+      <c r="C27" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="71" t="s">
+      <c r="D27" s="89" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="28" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="69" t="s">
+      <c r="C28" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="71" t="s">
+      <c r="D28" s="89" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="29" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="71" t="s">
+      <c r="D29" s="89" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="30" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="69" t="s">
+      <c r="C30" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="71" t="s">
+      <c r="D30" s="89" t="s">
         <v>918</v>
       </c>
     </row>
     <row r="31" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="69" t="s">
+      <c r="C31" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="71" t="s">
+      <c r="D31" s="89" t="s">
         <v>904</v>
       </c>
     </row>
     <row r="32" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="69" t="s">
+      <c r="C32" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="71" t="s">
+      <c r="D32" s="89" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="33" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="69" t="s">
+      <c r="C33" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="71" t="s">
+      <c r="D33" s="89" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="34" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="69" t="s">
+      <c r="C34" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="71" t="s">
+      <c r="D34" s="89" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="35" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="69" t="s">
+      <c r="C35" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="71" t="s">
+      <c r="D35" s="89" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="36" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="70"/>
-      <c r="D36" s="72"/>
+      <c r="C36" s="88"/>
+      <c r="D36" s="90"/>
     </row>
     <row r="37" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="68" t="s">
+      <c r="C37" s="86" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="73"/>
+      <c r="D37" s="91"/>
     </row>
     <row r="38" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="69" t="s">
+      <c r="C38" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="71" t="s">
+      <c r="D38" s="89" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="39" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="69" t="s">
+      <c r="C39" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="D39" s="71" t="s">
+      <c r="D39" s="89" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="40" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="69" t="s">
+      <c r="C40" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="D40" s="71" t="s">
+      <c r="D40" s="89" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="41" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="69" t="s">
+      <c r="C41" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="D41" s="71" t="s">
+      <c r="D41" s="89" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="42" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="69" t="s">
+      <c r="C42" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="D42" s="71" t="s">
+      <c r="D42" s="89" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="43" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="69" t="s">
+      <c r="C43" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="D43" s="71" t="s">
+      <c r="D43" s="89" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="44" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="69" t="s">
+      <c r="C44" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="D44" s="71" t="s">
+      <c r="D44" s="89" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="45" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="69" t="s">
+      <c r="C45" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="D45" s="71" t="s">
+      <c r="D45" s="89" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="46" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="69" t="s">
+      <c r="C46" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="D46" s="71" t="s">
+      <c r="D46" s="89" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="47" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="69" t="s">
+      <c r="C47" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="D47" s="71" t="s">
+      <c r="D47" s="89" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="48" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C48" s="69" t="s">
+      <c r="C48" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="71" t="s">
+      <c r="D48" s="89" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="49" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="70"/>
-      <c r="D49" s="72"/>
+      <c r="C49" s="88"/>
+      <c r="D49" s="90"/>
     </row>
     <row r="50" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="D50" s="73"/>
+      <c r="D50" s="91"/>
     </row>
     <row r="51" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="69" t="s">
+      <c r="C51" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="D51" s="71" t="s">
+      <c r="D51" s="89" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="52" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="69" t="s">
+      <c r="C52" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="D52" s="71" t="s">
+      <c r="D52" s="89" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="53" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="69" t="s">
+      <c r="C53" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="D53" s="71" t="s">
+      <c r="D53" s="89" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="54" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="69" t="s">
+      <c r="C54" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="D54" s="71" t="s">
+      <c r="D54" s="89" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="55" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="69" t="s">
+      <c r="C55" s="87" t="s">
         <v>86</v>
       </c>
-      <c r="D55" s="71" t="s">
+      <c r="D55" s="89" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="56" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="69" t="s">
+      <c r="C56" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="D56" s="71" t="s">
+      <c r="D56" s="89" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="57" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="69" t="s">
+      <c r="C57" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="D57" s="71" t="s">
+      <c r="D57" s="89" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="58" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="69" t="s">
+      <c r="C58" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="D58" s="71" t="s">
+      <c r="D58" s="89" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="59" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C59" s="69" t="s">
+      <c r="C59" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="D59" s="71" t="s">
+      <c r="D59" s="89" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="60" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C60" s="69" t="s">
+      <c r="C60" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="D60" s="71" t="s">
+      <c r="D60" s="89" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="61" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C61" s="70"/>
-      <c r="D61" s="72"/>
+      <c r="C61" s="88"/>
+      <c r="D61" s="90"/>
     </row>
     <row r="62" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="68" t="s">
+      <c r="C62" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="D62" s="73"/>
+      <c r="D62" s="91"/>
     </row>
     <row r="63" spans="3:4" ht="36" x14ac:dyDescent="0.25">
-      <c r="C63" s="69" t="s">
+      <c r="C63" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="D63" s="71" t="s">
+      <c r="D63" s="89" t="s">
         <v>905</v>
       </c>
     </row>
     <row r="64" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="69" t="s">
+      <c r="C64" s="87" t="s">
         <v>907</v>
       </c>
-      <c r="D64" s="71" t="s">
+      <c r="D64" s="89" t="s">
         <v>906</v>
       </c>
     </row>
     <row r="65" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="69" t="s">
+      <c r="C65" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="D65" s="71" t="s">
+      <c r="D65" s="89" t="s">
         <v>919</v>
       </c>
     </row>
     <row r="66" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="69" t="s">
+      <c r="C66" s="87" t="s">
         <v>105</v>
       </c>
-      <c r="D66" s="71" t="s">
+      <c r="D66" s="89" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="67" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="69" t="s">
+      <c r="C67" s="87" t="s">
         <v>107</v>
       </c>
-      <c r="D67" s="71" t="s">
+      <c r="D67" s="89" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="68" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="69" t="s">
+      <c r="C68" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="D68" s="71" t="s">
+      <c r="D68" s="89" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="69" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="70"/>
-      <c r="D69" s="72"/>
+      <c r="C69" s="88"/>
+      <c r="D69" s="90"/>
     </row>
     <row r="70" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="68" t="s">
+      <c r="C70" s="86" t="s">
         <v>111</v>
       </c>
-      <c r="D70" s="73"/>
+      <c r="D70" s="91"/>
     </row>
     <row r="71" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C71" s="69" t="s">
+      <c r="C71" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="D71" s="71" t="s">
+      <c r="D71" s="89" t="s">
         <v>113</v>
       </c>
     </row>
@@ -7329,1155 +7681,1262 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="shParams">
     <tabColor rgb="FFBF9000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C3:K64"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:X64"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="60.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="16.7109375" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.625" customWidth="1"/>
+    <col min="4" max="4" width="50.625" customWidth="1"/>
+    <col min="5" max="10" width="15.625" customWidth="1"/>
+    <col min="11" max="11" width="40.625" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="25" max="16384" width="9" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="55" customFormat="1"/>
-    <row r="2" ht="26" customHeight="1" s="56" customFormat="1"/>
-    <row r="3" spans="3:11">
-      <c r="C3" s="1" t="s">
+    <row r="1" spans="2:19" s="77" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="79"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="S1" s="80"/>
+    </row>
+    <row r="2" spans="2:19" s="77" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="92" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="4" spans="3:11">
-      <c r="C4" s="2" t="s">
+      <c r="C2" s="82"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="S2" s="80"/>
+    </row>
+    <row r="3" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="74" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="3:11" ht="42" customHeight="1">
-      <c r="C6" s="6" t="s">
+    <row r="4" spans="2:19" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="98" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D5" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E5" s="114" t="s">
         <v>117</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F5" s="99" t="s">
         <v>118</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="3:11">
-      <c r="C7" s="7" t="s">
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+    </row>
+    <row r="6" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="75" t="s">
         <v>119</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D6" s="107" t="s">
         <v>120</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E6" s="108">
         <v>46295</v>
       </c>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="3:11">
-      <c r="C8" s="7" t="s">
+      <c r="F6" s="106"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="107"/>
+    </row>
+    <row r="7" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="75" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D7" s="107" t="s">
         <v>122</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E7" s="105" t="s">
         <v>123</v>
       </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="3:11">
-      <c r="C9" s="7" t="s">
+      <c r="F7" s="106"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+    </row>
+    <row r="8" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="75" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D8" s="107" t="s">
         <v>125</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E8" s="109">
         <v>1.4</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F8" s="106" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="10" spans="3:11">
-      <c r="C10" s="7" t="s">
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="107"/>
+    </row>
+    <row r="9" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="75" t="s">
         <v>127</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D9" s="107" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E9" s="110">
         <v>0.05</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F9" s="106" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="11" spans="3:11">
-      <c r="C11" s="7" t="s">
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="107"/>
+    </row>
+    <row r="10" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="75" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D10" s="107" t="s">
         <v>131</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E10" s="109">
         <v>365</v>
       </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="3:11">
-      <c r="C12" s="7" t="s">
+      <c r="F10" s="106"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="107"/>
+      <c r="I10" s="107"/>
+      <c r="J10" s="107"/>
+    </row>
+    <row r="11" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D11" s="107" t="s">
         <v>133</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E11" s="109">
         <v>250</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F11" s="106" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="13" spans="3:11">
-      <c r="C13" s="7" t="s">
+      <c r="G11" s="107"/>
+      <c r="H11" s="107"/>
+      <c r="I11" s="107"/>
+      <c r="J11" s="107"/>
+    </row>
+    <row r="12" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="75" t="s">
         <v>135</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D12" s="107" t="s">
         <v>136</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E12" s="109">
         <v>10</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F12" s="106" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="14" spans="3:11">
-      <c r="C14" s="7" t="s">
+      <c r="G12" s="107"/>
+      <c r="H12" s="107"/>
+      <c r="I12" s="107"/>
+      <c r="J12" s="107"/>
+    </row>
+    <row r="13" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D13" s="107" t="s">
         <v>139</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E13" s="109">
         <v>10</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F13" s="106" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="15" spans="3:11">
-      <c r="C15" s="7" t="s">
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="107"/>
+    </row>
+    <row r="14" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D14" s="107" t="s">
         <v>142</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E14" s="109">
         <v>10</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F14" s="106" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="16" spans="3:11">
-      <c r="C16" s="7" t="s">
+      <c r="G14" s="107"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="107"/>
+      <c r="J14" s="107"/>
+    </row>
+    <row r="15" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="75" t="s">
         <v>144</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D15" s="107" t="s">
         <v>920</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E15" s="109">
         <v>5</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F15" s="106" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="17" spans="3:11">
-      <c r="C17" s="7" t="s">
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="107"/>
+      <c r="J15" s="107"/>
+    </row>
+    <row r="16" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="75" t="s">
         <v>147</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D16" s="107" t="s">
         <v>148</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E16" s="109">
         <v>20</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F16" s="106" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="18" spans="3:11">
-      <c r="C18" s="7" t="s">
+      <c r="G16" s="107"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="107"/>
+      <c r="J16" s="107"/>
+    </row>
+    <row r="17" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="75" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D17" s="107" t="s">
         <v>150</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E17" s="109">
         <v>0.5</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F17" s="106" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="19" spans="3:11">
-      <c r="C19" s="7" t="s">
+      <c r="G17" s="107"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="107"/>
+    </row>
+    <row r="18" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="75" t="s">
         <v>152</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D18" s="107" t="s">
         <v>153</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E18" s="109">
         <v>5</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F18" s="106" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="20" spans="3:11">
-      <c r="C20" s="7" t="s">
+      <c r="G18" s="107"/>
+      <c r="H18" s="107"/>
+      <c r="I18" s="107"/>
+      <c r="J18" s="107"/>
+    </row>
+    <row r="19" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D19" s="107" t="s">
         <v>156</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E19" s="109">
         <v>0.7</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F19" s="106" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="21" spans="3:11">
-      <c r="C21" s="7" t="s">
+      <c r="G19" s="107"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="107"/>
+    </row>
+    <row r="20" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="75" t="s">
         <v>158</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D20" s="107" t="s">
         <v>159</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E20" s="109">
         <v>0.7</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F20" s="106" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="22" spans="3:11">
-      <c r="C22" s="7" t="s">
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="107"/>
+    </row>
+    <row r="21" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D21" s="107" t="s">
         <v>161</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E21" s="109">
         <v>0.3</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F21" s="106" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="23" spans="3:11">
-      <c r="C23" s="7" t="s">
+      <c r="G21" s="107"/>
+      <c r="H21" s="107"/>
+      <c r="I21" s="107"/>
+      <c r="J21" s="107"/>
+    </row>
+    <row r="22" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D22" s="107" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="14" t="b">
+      <c r="E22" s="111" t="b">
         <v>1</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F22" s="106" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="24" spans="3:11">
-      <c r="C24" s="7" t="s">
+      <c r="G22" s="107"/>
+      <c r="H22" s="107"/>
+      <c r="I22" s="107"/>
+      <c r="J22" s="107"/>
+    </row>
+    <row r="23" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="75" t="s">
         <v>165</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D23" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E23" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F23" s="106" t="s">
         <v>168</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G23" s="107"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="95" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="25" spans="3:11">
-      <c r="C25" s="7" t="s">
+      <c r="J23" s="107"/>
+    </row>
+    <row r="24" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="75" t="s">
         <v>169</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D24" s="107" t="s">
         <v>170</v>
       </c>
-      <c r="E25" s="13">
-        <v>0.001</v>
-      </c>
-      <c r="F25" s="10" t="s">
+      <c r="E24" s="110">
+        <v>1E-3</v>
+      </c>
+      <c r="F24" s="106" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="26" spans="3:11">
-      <c r="C26" s="7" t="s">
+      <c r="G24" s="107"/>
+      <c r="H24" s="107"/>
+      <c r="I24" s="107"/>
+      <c r="J24" s="107"/>
+    </row>
+    <row r="25" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="75" t="s">
         <v>172</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D25" s="107" t="s">
         <v>173</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E25" s="109">
         <v>0.1</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F25" s="106" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="28" spans="3:11">
-      <c r="C28" s="3" t="s">
+      <c r="G25" s="107"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="107"/>
+      <c r="J25" s="107"/>
+    </row>
+    <row r="26" spans="3:11" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="115" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="29" spans="3:11" ht="30" customHeight="1">
-      <c r="C29" s="6" t="s">
+    <row r="28" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="98" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D28" s="100" t="s">
         <v>177</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E28" s="100" t="s">
         <v>178</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F28" s="100" t="s">
         <v>179</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G28" s="100" t="s">
         <v>180</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H28" s="100" t="s">
         <v>181</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I28" s="100" t="s">
         <v>182</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J28" s="100" t="s">
         <v>183</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K28" s="98" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="30" spans="3:11">
-      <c r="C30" s="7" t="s">
+    <row r="29" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D29" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="13">
-        <v>0.005</v>
-      </c>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16">
+      <c r="E29" s="101"/>
+      <c r="F29" s="102">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G29" s="103"/>
+      <c r="H29" s="103">
         <v>0.5</v>
       </c>
-      <c r="I30" s="14"/>
-      <c r="J30" s="11" t="s">
+      <c r="I29" s="104"/>
+      <c r="J29" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K30" s="17" t="s">
+      <c r="K29" s="106" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="31" spans="3:11">
-      <c r="C31" s="7" t="s">
+    <row r="30" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D30" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="13">
+      <c r="E30" s="101"/>
+      <c r="F30" s="102">
         <v>0.04</v>
       </c>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16">
+      <c r="G30" s="103"/>
+      <c r="H30" s="103">
         <v>0.15</v>
       </c>
-      <c r="I31" s="14"/>
-      <c r="J31" s="11" t="s">
+      <c r="I30" s="104"/>
+      <c r="J30" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K31" s="17" t="s">
+      <c r="K30" s="106" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="32" spans="3:11">
-      <c r="C32" s="7" t="s">
+    <row r="31" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="75" t="s">
         <v>187</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D31" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E31" s="101" t="s">
         <v>189</v>
       </c>
-      <c r="F32" s="13">
-        <v>0.0038</v>
-      </c>
-      <c r="G32" s="16">
+      <c r="F31" s="102">
+        <v>3.8E-3</v>
+      </c>
+      <c r="G31" s="103">
         <v>0.5</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H31" s="103">
         <v>1</v>
       </c>
-      <c r="I32" s="14"/>
-      <c r="J32" s="11" t="s">
+      <c r="I31" s="104"/>
+      <c r="J31" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K32" s="17" t="s">
+      <c r="K31" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="3:11">
-      <c r="C33" s="7" t="s">
+    <row r="32" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="75" t="s">
         <v>191</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D32" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E32" s="101" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="13">
-        <v>0.0038</v>
-      </c>
-      <c r="G33" s="16">
+      <c r="F32" s="102">
+        <v>3.8E-3</v>
+      </c>
+      <c r="G32" s="103">
         <v>0.5</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H32" s="103">
         <v>1</v>
       </c>
-      <c r="I33" s="14"/>
-      <c r="J33" s="11" t="s">
+      <c r="I32" s="104"/>
+      <c r="J32" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K33" s="17" t="s">
+      <c r="K32" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="3:11">
-      <c r="C34" s="7" t="s">
+    <row r="33" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="75" t="s">
         <v>193</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D33" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E33" s="101" t="s">
         <v>194</v>
       </c>
-      <c r="F34" s="13">
-        <v>0.0042</v>
-      </c>
-      <c r="G34" s="16">
+      <c r="F33" s="102">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="G33" s="103">
         <v>0.5</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H33" s="103">
         <v>1</v>
       </c>
-      <c r="I34" s="14"/>
-      <c r="J34" s="11" t="s">
+      <c r="I33" s="104"/>
+      <c r="J33" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K34" s="17" t="s">
+      <c r="K33" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="3:11">
-      <c r="C35" s="7" t="s">
+    <row r="34" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="75" t="s">
         <v>195</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D34" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E34" s="101" t="s">
         <v>196</v>
       </c>
-      <c r="F35" s="13">
-        <v>0.0054</v>
-      </c>
-      <c r="G35" s="16">
+      <c r="F34" s="102">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="G34" s="103">
         <v>0.5</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H34" s="103">
         <v>1</v>
       </c>
-      <c r="I35" s="14"/>
-      <c r="J35" s="11" t="s">
+      <c r="I34" s="104"/>
+      <c r="J34" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K35" s="17" t="s">
+      <c r="K34" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="3:11">
-      <c r="C36" s="7" t="s">
+    <row r="35" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="75" t="s">
         <v>197</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D35" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E35" s="101" t="s">
         <v>198</v>
       </c>
-      <c r="F36" s="13">
-        <v>0.0106</v>
-      </c>
-      <c r="G36" s="16">
+      <c r="F35" s="102">
+        <v>1.06E-2</v>
+      </c>
+      <c r="G35" s="103">
         <v>0.5</v>
       </c>
-      <c r="H36" s="16">
+      <c r="H35" s="103">
         <v>1</v>
       </c>
-      <c r="I36" s="14"/>
-      <c r="J36" s="11" t="s">
+      <c r="I35" s="104"/>
+      <c r="J35" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K36" s="17" t="s">
+      <c r="K35" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="3:11">
-      <c r="C37" s="7" t="s">
+    <row r="36" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D36" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E36" s="101" t="s">
         <v>200</v>
       </c>
-      <c r="F37" s="13">
-        <v>0.016</v>
-      </c>
-      <c r="G37" s="16">
+      <c r="F36" s="102">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G36" s="103">
         <v>0.5</v>
       </c>
-      <c r="H37" s="16">
+      <c r="H36" s="103">
         <v>1</v>
       </c>
-      <c r="I37" s="14"/>
-      <c r="J37" s="11" t="s">
+      <c r="I36" s="104"/>
+      <c r="J36" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K37" s="17" t="s">
+      <c r="K36" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="38" spans="3:11">
-      <c r="C38" s="7" t="s">
+    <row r="37" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="75" t="s">
         <v>201</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D37" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E37" s="101" t="s">
         <v>202</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F37" s="102">
         <v>0.06</v>
       </c>
-      <c r="G38" s="16">
+      <c r="G37" s="103">
         <v>0.5</v>
       </c>
-      <c r="H38" s="16">
+      <c r="H37" s="103">
         <v>1</v>
       </c>
-      <c r="I38" s="14"/>
-      <c r="J38" s="11" t="s">
+      <c r="I37" s="104"/>
+      <c r="J37" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K38" s="17" t="s">
+      <c r="K37" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="3:11">
-      <c r="C39" s="7" t="s">
+    <row r="38" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D38" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E38" s="101" t="s">
         <v>204</v>
       </c>
-      <c r="F39" s="13">
-        <v>0.0038</v>
-      </c>
-      <c r="G39" s="16">
+      <c r="F38" s="102">
+        <v>3.8E-3</v>
+      </c>
+      <c r="G38" s="103">
         <v>0.5</v>
       </c>
-      <c r="H39" s="16">
+      <c r="H38" s="103">
         <v>1</v>
       </c>
-      <c r="I39" s="14"/>
-      <c r="J39" s="11" t="s">
+      <c r="I38" s="104"/>
+      <c r="J38" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K39" s="17" t="s">
+      <c r="K38" s="106" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="40" spans="3:11">
-      <c r="C40" s="7" t="s">
+    <row r="39" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="75" t="s">
         <v>206</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D39" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E39" s="101" t="s">
         <v>207</v>
       </c>
-      <c r="F40" s="13">
-        <v>0.0042</v>
-      </c>
-      <c r="G40" s="16">
+      <c r="F39" s="102">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="G39" s="103">
         <v>0.5</v>
       </c>
-      <c r="H40" s="16">
+      <c r="H39" s="103">
         <v>1</v>
       </c>
-      <c r="I40" s="14"/>
-      <c r="J40" s="11" t="s">
+      <c r="I39" s="104"/>
+      <c r="J39" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K40" s="17" t="s">
+      <c r="K39" s="106" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="41" spans="3:11">
-      <c r="C41" s="7" t="s">
+    <row r="40" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="75" t="s">
         <v>208</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D40" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E40" s="101" t="s">
         <v>209</v>
       </c>
-      <c r="F41" s="13">
-        <v>0.0054</v>
-      </c>
-      <c r="G41" s="16">
+      <c r="F40" s="102">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="G40" s="103">
         <v>0.5</v>
       </c>
-      <c r="H41" s="16">
+      <c r="H40" s="103">
         <v>1</v>
       </c>
-      <c r="I41" s="14"/>
-      <c r="J41" s="11" t="s">
+      <c r="I40" s="104"/>
+      <c r="J40" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K41" s="17" t="s">
+      <c r="K40" s="106" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="42" spans="3:11">
-      <c r="C42" s="7" t="s">
+    <row r="41" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="75" t="s">
         <v>210</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D41" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E41" s="101" t="s">
         <v>211</v>
       </c>
-      <c r="F42" s="13">
-        <v>0.0106</v>
-      </c>
-      <c r="G42" s="16">
+      <c r="F41" s="102">
+        <v>1.06E-2</v>
+      </c>
+      <c r="G41" s="103">
         <v>0.5</v>
       </c>
-      <c r="H42" s="16">
+      <c r="H41" s="103">
         <v>1</v>
       </c>
-      <c r="I42" s="14"/>
-      <c r="J42" s="11" t="s">
+      <c r="I41" s="104"/>
+      <c r="J41" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K42" s="17" t="s">
+      <c r="K41" s="106" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="43" spans="3:11">
-      <c r="C43" s="7" t="s">
+    <row r="42" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="75" t="s">
         <v>212</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D42" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E42" s="101" t="s">
         <v>213</v>
       </c>
-      <c r="F43" s="13">
-        <v>0.016</v>
-      </c>
-      <c r="G43" s="16">
+      <c r="F42" s="102">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G42" s="103">
         <v>0.5</v>
       </c>
-      <c r="H43" s="16">
+      <c r="H42" s="103">
         <v>1</v>
       </c>
-      <c r="I43" s="14"/>
-      <c r="J43" s="11" t="s">
+      <c r="I42" s="104"/>
+      <c r="J42" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K43" s="17" t="s">
+      <c r="K42" s="106" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="44" spans="3:11">
-      <c r="C44" s="7" t="s">
+    <row r="43" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="75" t="s">
         <v>214</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D43" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E43" s="101" t="s">
         <v>215</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F43" s="102">
         <v>0.06</v>
       </c>
-      <c r="G44" s="16">
+      <c r="G43" s="103">
         <v>0.5</v>
       </c>
-      <c r="H44" s="16">
+      <c r="H43" s="103">
         <v>1</v>
       </c>
-      <c r="I44" s="14"/>
-      <c r="J44" s="11" t="s">
+      <c r="I43" s="104"/>
+      <c r="J43" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K44" s="17" t="s">
+      <c r="K43" s="106" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="45" spans="3:11">
-      <c r="C45" s="7" t="s">
+    <row r="44" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="75" t="s">
         <v>216</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D44" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E44" s="101" t="s">
         <v>217</v>
       </c>
-      <c r="F45" s="13">
-        <v>0.0038</v>
-      </c>
-      <c r="G45" s="16">
+      <c r="F44" s="102">
+        <v>3.8E-3</v>
+      </c>
+      <c r="G44" s="103">
         <v>0.8</v>
       </c>
-      <c r="H45" s="16">
+      <c r="H44" s="103">
         <v>0.8</v>
       </c>
-      <c r="I45" s="14"/>
-      <c r="J45" s="11" t="s">
+      <c r="I44" s="104"/>
+      <c r="J44" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K45" s="17" t="s">
+      <c r="K44" s="106" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="46" spans="3:11">
-      <c r="C46" s="7" t="s">
+    <row r="45" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="75" t="s">
         <v>219</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D45" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E45" s="101" t="s">
         <v>220</v>
       </c>
-      <c r="F46" s="13">
-        <v>0.0106</v>
-      </c>
-      <c r="G46" s="16">
+      <c r="F45" s="102">
+        <v>1.06E-2</v>
+      </c>
+      <c r="G45" s="103">
         <v>0.8</v>
       </c>
-      <c r="H46" s="16">
+      <c r="H45" s="103">
         <v>0.8</v>
       </c>
-      <c r="I46" s="14"/>
-      <c r="J46" s="11" t="s">
+      <c r="I45" s="104"/>
+      <c r="J45" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K46" s="17" t="s">
+      <c r="K45" s="106" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="47" spans="3:11">
-      <c r="C47" s="7" t="s">
+    <row r="46" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="75" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D46" s="101" t="s">
         <v>222</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E46" s="101" t="s">
         <v>223</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F46" s="102">
         <v>0.32</v>
       </c>
-      <c r="G47" s="16">
+      <c r="G46" s="103">
         <v>0.5</v>
       </c>
-      <c r="H47" s="16">
+      <c r="H46" s="103">
         <v>1.2</v>
       </c>
-      <c r="I47" s="14"/>
-      <c r="J47" s="11" t="s">
+      <c r="I46" s="104"/>
+      <c r="J46" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K47" s="17" t="s">
+      <c r="K46" s="106" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="48" spans="3:11">
-      <c r="C48" s="7" t="s">
+    <row r="47" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="75" t="s">
         <v>225</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D47" s="101" t="s">
         <v>222</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E47" s="101" t="s">
         <v>226</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F47" s="102">
         <v>0.2</v>
       </c>
-      <c r="G48" s="16">
+      <c r="G47" s="103">
         <v>0.8</v>
       </c>
-      <c r="H48" s="16">
+      <c r="H47" s="103">
         <v>0.75</v>
       </c>
-      <c r="I48" s="14"/>
-      <c r="J48" s="11" t="s">
+      <c r="I47" s="104"/>
+      <c r="J47" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K48" s="17" t="s">
+      <c r="K47" s="106" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="49" spans="3:11">
-      <c r="C49" s="7" t="s">
+    <row r="48" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="75" t="s">
         <v>227</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D48" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E48" s="101" t="s">
         <v>228</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F48" s="102">
         <v>0.4</v>
       </c>
-      <c r="G49" s="16">
+      <c r="G48" s="103">
         <v>0.4</v>
       </c>
-      <c r="H49" s="16">
+      <c r="H48" s="103">
         <v>1.5</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I48" s="105" t="s">
         <v>229</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J48" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K49" s="17" t="s">
+      <c r="K48" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="50" spans="3:11">
-      <c r="C50" s="7" t="s">
+    <row r="49" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="75" t="s">
         <v>230</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D49" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E49" s="101" t="s">
         <v>231</v>
       </c>
-      <c r="F50" s="13">
+      <c r="F49" s="102">
         <v>0.18</v>
       </c>
-      <c r="G50" s="16">
+      <c r="G49" s="103">
         <v>0.4</v>
       </c>
-      <c r="H50" s="16">
+      <c r="H49" s="103">
         <v>0.7</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I49" s="105" t="s">
         <v>229</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="J49" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K50" s="17" t="s">
+      <c r="K49" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="51" spans="3:11">
-      <c r="C51" s="7" t="s">
+    <row r="50" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="75" t="s">
         <v>232</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D50" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E50" s="101" t="s">
         <v>233</v>
       </c>
-      <c r="F51" s="13">
+      <c r="F50" s="102">
         <v>0.18</v>
       </c>
-      <c r="G51" s="16">
+      <c r="G50" s="103">
         <v>0.4</v>
       </c>
-      <c r="H51" s="16">
+      <c r="H50" s="103">
         <v>0.7</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I50" s="105" t="s">
         <v>233</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J50" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K51" s="17" t="s">
+      <c r="K50" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="52" spans="3:11">
-      <c r="C52" s="7" t="s">
+    <row r="51" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="75" t="s">
         <v>234</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D51" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E51" s="101" t="s">
         <v>235</v>
       </c>
-      <c r="F52" s="13">
+      <c r="F51" s="102">
         <v>0.18</v>
       </c>
-      <c r="G52" s="16">
+      <c r="G51" s="103">
         <v>0.4</v>
       </c>
-      <c r="H52" s="16">
+      <c r="H51" s="103">
         <v>0.7</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I51" s="105" t="s">
         <v>235</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J51" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K52" s="17" t="s">
+      <c r="K51" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="53" spans="3:11">
-      <c r="C53" s="7" t="s">
+    <row r="52" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="75" t="s">
         <v>236</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D52" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E52" s="101" t="s">
         <v>237</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F52" s="102">
         <v>0.18</v>
       </c>
-      <c r="G53" s="16">
+      <c r="G52" s="103">
         <v>0.4</v>
       </c>
-      <c r="H53" s="16">
+      <c r="H52" s="103">
         <v>0.7</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I52" s="105" t="s">
         <v>237</v>
       </c>
-      <c r="J53" s="11" t="s">
+      <c r="J52" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K53" s="17" t="s">
+      <c r="K52" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="54" spans="3:11">
-      <c r="C54" s="7" t="s">
+    <row r="53" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="75" t="s">
         <v>238</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D53" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E53" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F53" s="102">
         <v>0.18</v>
       </c>
-      <c r="G54" s="16">
+      <c r="G53" s="103">
         <v>0.4</v>
       </c>
-      <c r="H54" s="16">
+      <c r="H53" s="103">
         <v>0.7</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I53" s="105" t="s">
         <v>239</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="J53" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="K54" s="18" t="s">
+      <c r="K53" s="106" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="55" spans="3:11">
-      <c r="C55" s="7" t="s">
+    <row r="54" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="75" t="s">
         <v>241</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D54" s="101" t="s">
         <v>241</v>
       </c>
-      <c r="E55" s="8"/>
-      <c r="F55" s="13">
+      <c r="E54" s="101"/>
+      <c r="F54" s="102">
         <v>0.08</v>
       </c>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16">
+      <c r="G54" s="103"/>
+      <c r="H54" s="103">
         <v>1.5</v>
       </c>
-      <c r="I55" s="14"/>
-      <c r="J55" s="11" t="s">
+      <c r="I54" s="104"/>
+      <c r="J54" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="K55" s="17" t="s">
+      <c r="K54" s="106" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="57" spans="3:11">
-      <c r="C57" s="3" t="s">
+    <row r="55" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="115" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="58" spans="3:11" ht="30" customHeight="1">
-      <c r="C58" s="6" t="s">
+    <row r="57" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="97" t="s">
         <v>244</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D57" s="97" t="s">
         <v>245</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E57" s="96" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="59" spans="3:11">
-      <c r="C59" s="11" t="s">
+    <row r="58" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C58" s="76" t="s">
         <v>123</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D58" s="107" t="s">
         <v>247</v>
       </c>
-      <c r="E59" s="19">
+      <c r="E58" s="112">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="3:11">
-      <c r="C60" s="11" t="s">
+    <row r="59" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="76" t="s">
         <v>248</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D59" s="107" t="s">
         <v>249</v>
       </c>
-      <c r="E60" s="19">
+      <c r="E59" s="112">
         <v>0.86</v>
       </c>
     </row>
-    <row r="61" spans="3:11">
-      <c r="C61" s="11" t="s">
+    <row r="60" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="76" t="s">
         <v>250</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D60" s="107" t="s">
         <v>251</v>
       </c>
-      <c r="E61" s="19">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="62" spans="3:11">
-      <c r="C62" s="11" t="s">
+      <c r="E60" s="112">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="76" t="s">
         <v>252</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D61" s="107" t="s">
         <v>253</v>
       </c>
-      <c r="E62" s="19">
-        <v>0.0058</v>
-      </c>
-    </row>
-    <row r="63" spans="3:11">
-      <c r="C63" s="11" t="s">
+      <c r="E61" s="112">
+        <v>5.7999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="76" t="s">
         <v>254</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D62" s="107" t="s">
         <v>255</v>
       </c>
-      <c r="E63" s="19">
+      <c r="E62" s="112">
         <v>1.07</v>
       </c>
     </row>
-    <row r="64" spans="3:11">
-      <c r="D64" s="15" t="s">
+    <row r="63" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D63" s="113" t="s">
         <v>256</v>
       </c>
     </row>
+    <row r="64" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E23">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E23" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"CRR,BCBS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J30:J55">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J29:J54" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"BOTH,CRR,BCBS"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D29:D55" xr:uid="{92FC5665-A317-49D8-9552-6AF5B626BBD5}">
+      <formula1>"IR, FX,CR,EQ,CO,OT"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -23,29 +23,31 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Basel_vs_CRR!$C$6:$K$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Trades!$C$6:$Z$71</definedName>
-    <definedName name="Alpha">Params!$E$9</definedName>
-    <definedName name="AsOfDate">Params!$E$7</definedName>
-    <definedName name="BasisFactor">Params!$E$18</definedName>
-    <definedName name="BusinessDaysPerYear">Params!$E$12</definedName>
-    <definedName name="DaysPerYear">Params!$E$11</definedName>
-    <definedName name="FX_Table">Params!$C$58:$E$63</definedName>
-    <definedName name="IRBucketOffset">Params!$E$23</definedName>
-    <definedName name="IRCorrBucket12">Params!$E$20</definedName>
-    <definedName name="IRCorrBucket13">Params!$E$22</definedName>
-    <definedName name="IRCorrBucket23">Params!$E$21</definedName>
-    <definedName name="LambdaThresholdCO">Params!$E$26</definedName>
-    <definedName name="LambdaThresholdIR">Params!$E$25</definedName>
-    <definedName name="MinMaturityBD">Params!$E$13</definedName>
-    <definedName name="MPORFloorBilateral">Params!$E$15</definedName>
-    <definedName name="MPORFloorCleared">Params!$E$16</definedName>
-    <definedName name="MPORFloorLarge">Params!$E$17</definedName>
-    <definedName name="MultiplierFloor">Params!$E$10</definedName>
-    <definedName name="Regime">Params!$E$24</definedName>
-    <definedName name="ReportingCcy">Params!$E$8</definedName>
+    <definedName name="Alpha">Params!$E$8</definedName>
+    <definedName name="AsOfDate">Params!$E$6</definedName>
+    <definedName name="BasisFactor">Params!$E$17</definedName>
+    <definedName name="BusinessDaysPerYear">Params!$E$11</definedName>
+    <definedName name="DaysPerYear">Params!$E$10</definedName>
+    <definedName name="FX_Table">Params!$C$57:$E$62</definedName>
+    <definedName name="IRBucketOffset">Params!$E$22</definedName>
+    <definedName name="IRCorrBucket12">Params!$E$19</definedName>
+    <definedName name="IRCorrBucket13">Params!$E$21</definedName>
+    <definedName name="IRCorrBucket23">Params!$E$20</definedName>
+    <definedName name="LambdaThresholdCO">Params!$E$25</definedName>
+    <definedName name="LambdaThresholdIR">Params!$E$24</definedName>
+    <definedName name="MinMaturityBD">Params!$E$12</definedName>
+    <definedName name="MPORFloorBilateral">Params!$E$14</definedName>
+    <definedName name="MPORFloorCleared">Params!$E$15</definedName>
+    <definedName name="MPORFloorLarge">Params!$E$16</definedName>
+    <definedName name="MultiplierFloor">Params!$E$9</definedName>
+    <definedName name="Params_Code">Params!$C$5</definedName>
+    <definedName name="Params_Value">Params!$E$5</definedName>
+    <definedName name="Regime">Params!$E$23</definedName>
+    <definedName name="ReportingCcy">Params!$E$7</definedName>
     <definedName name="SACCR_RunInputs" hidden="1">""</definedName>
-    <definedName name="SDFloorBD">Params!$E$14</definedName>
-    <definedName name="SF_Table">Params!$C$29:$K$55</definedName>
-    <definedName name="VolatilityFactor">Params!$E$19</definedName>
+    <definedName name="SDFloorBD">Params!$E$13</definedName>
+    <definedName name="SF_Table">Params!$C$28:$K$54</definedName>
+    <definedName name="VolatilityFactor">Params!$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -74,12 +76,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="945">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
   <si>
-    <t>Standardised approach for counterparty credit risk - common Basel CRE52 core with an EU CRR (Art. 274-280f) rules layer. VBA engine v1.1.0.</t>
+    <t>Standardised approach for counterparty credit risk - common Basel CRE52 core with an EU CRR (Art. 274-280f) rules layer. VBA engine v1.0.0.</t>
   </si>
   <si>
     <t>How to use</t>
@@ -2903,13 +2905,19 @@
   </si>
   <si>
     <t>Not implemented: declare SHARED under Margin agreements; the netting set is rejected.</t>
+  </si>
+  <si>
+    <t>Unmargined maturity factors; collateral basis per regime (see Results columns Z-AC).</t>
+  </si>
+  <si>
+    <t>ReadMe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="0.00##"/>
@@ -2924,14 +2932,14 @@
     <numFmt numFmtId="175" formatCode="#,##0.0#####"/>
     <numFmt numFmtId="176" formatCode="0.0E+00"/>
     <numFmt numFmtId="177" formatCode="0.000000000"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="49">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2939,7 +2947,6 @@
       <color rgb="FF1F3864"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
@@ -2947,7 +2954,6 @@
       <color rgb="FF595959"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2955,7 +2961,6 @@
       <color rgb="FF1F3864"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2963,14 +2968,12 @@
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2978,14 +2981,12 @@
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
@@ -2993,14 +2994,12 @@
       <color rgb="FF595959"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3008,7 +3007,6 @@
       <color rgb="FFC00000"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
@@ -3016,7 +3014,6 @@
       <color rgb="FF7F6000"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -3030,7 +3027,6 @@
       <color rgb="FF375623"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3038,31 +3034,233 @@
       <color rgb="FF9C0006"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF375623"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F3864"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3099,8 +3297,53 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -3141,13 +3384,89 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3315,6 +3634,183 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="6" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="6" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="32" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="32" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="10" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="6" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="10" borderId="6" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="47" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3629,508 +4125,538 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="shReadme">
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C3:E72"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:X71"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="2.7109375" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="100.7109375" customWidth="1"/>
+    <col min="1" max="2" width="4" style="77" customWidth="1"/>
+    <col min="3" max="3" width="46" style="77" customWidth="1"/>
+    <col min="4" max="4" width="126.875" style="77" customWidth="1"/>
+    <col min="5" max="5" width="4.75" style="77" customWidth="1"/>
+    <col min="6" max="24" width="0" style="77" hidden="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.125" style="77" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="55" customFormat="1"/>
-    <row r="2" ht="26" customHeight="1" s="56" customFormat="1"/>
-    <row r="3" spans="4:5" ht="34" customHeight="1">
-      <c r="D3" s="1" t="s">
+    <row r="1" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="93" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="4:5">
-      <c r="D4" s="2" t="s">
+      <c r="C1" s="79"/>
+      <c r="D1" s="78"/>
+      <c r="S1" s="80"/>
+    </row>
+    <row r="2" spans="2:19" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="92" t="s">
+        <v>944</v>
+      </c>
+      <c r="C2" s="82"/>
+      <c r="D2" s="81"/>
+      <c r="S2" s="80"/>
+    </row>
+    <row r="3" spans="2:19" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="83"/>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C4" s="84" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="4:5">
-      <c r="D7" s="3" t="s">
+    <row r="5" spans="2:19" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="4:5" ht="28" customHeight="1">
-      <c r="D8" s="4" t="s">
+      <c r="D6" s="85"/>
+    </row>
+    <row r="7" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="D7" s="89" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="4:5" ht="28" customHeight="1">
-      <c r="D9" s="4" t="s">
+    <row r="8" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="D8" s="89" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="4:5" ht="28" customHeight="1">
-      <c r="D10" s="4" t="s">
+    <row r="9" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="D9" s="89" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="4:5" ht="16" customHeight="1">
-      <c r="D11" s="4" t="s">
+    <row r="10" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="D10" s="89" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="4:5" ht="28" customHeight="1">
-      <c r="D12" s="4" t="s">
+    <row r="11" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="D11" s="89" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="4:5" ht="28" customHeight="1">
-      <c r="D13" s="4" t="s">
+    <row r="12" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="D12" s="89" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="4:5" ht="28" customHeight="1">
-      <c r="D14" s="4" t="s">
+    <row r="13" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="D13" s="89" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="4:5">
-      <c r="D16" s="3" t="s">
+    <row r="14" spans="2:19" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="88"/>
+      <c r="D14" s="90"/>
+    </row>
+    <row r="15" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="4:5" ht="40" customHeight="1">
-      <c r="D17" s="4" t="s">
+      <c r="D15" s="91"/>
+    </row>
+    <row r="16" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="D16" s="89" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="4:5" ht="40" customHeight="1">
-      <c r="D18" s="4" t="s">
+    <row r="17" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="D17" s="89" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="4:5" ht="40" customHeight="1">
-      <c r="D19" s="4" t="s">
+    <row r="18" spans="3:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="C18" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="D18" s="89" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="20" spans="4:5" ht="28" customHeight="1">
-      <c r="D20" s="4" t="s">
+    <row r="19" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="D19" s="89" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="4:5" ht="40" customHeight="1">
-      <c r="D21" s="4" t="s">
+    <row r="20" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="D20" s="89" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="4:5" ht="28" customHeight="1">
-      <c r="D22" s="4" t="s">
+    <row r="21" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="D21" s="89" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="4:5" ht="40" customHeight="1">
-      <c r="D23" s="4" t="s">
+    <row r="22" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="D22" s="89" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="4:5">
-      <c r="D25" s="3" t="s">
+    <row r="23" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="88"/>
+      <c r="D23" s="90"/>
+    </row>
+    <row r="24" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="4:5" ht="28" customHeight="1">
-      <c r="D26" s="4" t="s">
+      <c r="D24" s="91"/>
+    </row>
+    <row r="25" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="D25" s="89" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="27" spans="4:5">
-      <c r="D27" s="4" t="s">
+    <row r="26" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="D26" s="89" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="4:5">
-      <c r="D28" s="4" t="s">
+    <row r="27" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="D27" s="89" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="4:5" ht="28" customHeight="1">
-      <c r="D29" s="4" t="s">
+    <row r="28" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="D28" s="89" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="4:5">
-      <c r="D30" s="4" t="s">
+    <row r="29" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="D29" s="89" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="4:5" ht="28" customHeight="1">
-      <c r="D31" s="4" t="s">
+    <row r="30" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="D30" s="89" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="32" spans="4:5" ht="28" customHeight="1">
-      <c r="D32" s="4" t="s">
+    <row r="31" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="D31" s="89" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="33" spans="4:5">
-      <c r="D33" s="4" t="s">
+    <row r="32" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="D32" s="89" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="4:5">
-      <c r="D34" s="4" t="s">
+    <row r="33" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="D33" s="89" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="4:5" ht="28" customHeight="1">
-      <c r="D35" s="4" t="s">
+    <row r="34" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="D34" s="89" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="4:5">
-      <c r="D36" s="4" t="s">
+    <row r="35" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="D35" s="89" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="4:5">
-      <c r="D38" s="3" t="s">
+    <row r="36" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="88"/>
+      <c r="D36" s="90"/>
+    </row>
+    <row r="37" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="86" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="4:5">
-      <c r="D39" s="4" t="s">
+      <c r="D37" s="91"/>
+    </row>
+    <row r="38" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="87" t="s">
         <v>56</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="D38" s="89" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="4:5">
-      <c r="D40" s="4" t="s">
+    <row r="39" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="D39" s="89" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="4:5">
-      <c r="D41" s="4" t="s">
+    <row r="40" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="D40" s="89" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="4:5">
-      <c r="D42" s="4" t="s">
+    <row r="41" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="D41" s="89" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="4:5">
-      <c r="D43" s="4" t="s">
+    <row r="42" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="D42" s="89" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="4:5">
-      <c r="D44" s="4" t="s">
+    <row r="43" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="D43" s="89" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="4:5">
-      <c r="D45" s="4" t="s">
+    <row r="44" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="D44" s="89" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="4:5">
-      <c r="D46" s="4" t="s">
+    <row r="45" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="D45" s="89" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="4:5">
-      <c r="D47" s="4" t="s">
+    <row r="46" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="D46" s="89" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="4:5">
-      <c r="D48" s="4" t="s">
+    <row r="47" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="D47" s="89" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="49" spans="4:5">
-      <c r="D49" s="4" t="s">
+    <row r="48" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="D48" s="89" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="51" spans="4:5">
-      <c r="D51" s="3" t="s">
+    <row r="49" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="88"/>
+      <c r="D49" s="90"/>
+    </row>
+    <row r="50" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="4:5">
-      <c r="D52" s="4" t="s">
+      <c r="D50" s="91"/>
+    </row>
+    <row r="51" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="D51" s="89" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="53" spans="4:5">
-      <c r="D53" s="4" t="s">
+    <row r="52" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="D52" s="89" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="4:5">
-      <c r="D54" s="4" t="s">
+    <row r="53" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="D53" s="89" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="4:5">
-      <c r="D55" s="4" t="s">
+    <row r="54" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="D54" s="89" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="4:5">
-      <c r="D56" s="4" t="s">
+    <row r="55" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="87" t="s">
         <v>86</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="D55" s="89" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="4:5">
-      <c r="D57" s="4" t="s">
+    <row r="56" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="D56" s="89" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="58" spans="4:5">
-      <c r="D58" s="4" t="s">
+    <row r="57" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="D57" s="89" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="4:5">
-      <c r="D59" s="4" t="s">
+    <row r="58" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C58" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="D58" s="89" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="4:5">
-      <c r="D60" s="4" t="s">
+    <row r="59" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="D59" s="89" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="4:5">
-      <c r="D61" s="4" t="s">
+    <row r="60" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="D60" s="89" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="63" spans="4:5">
-      <c r="D63" s="3" t="s">
+    <row r="61" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="88"/>
+      <c r="D61" s="90"/>
+    </row>
+    <row r="62" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="E63" s="3"/>
-    </row>
-    <row r="64" spans="4:5" ht="28" customHeight="1">
-      <c r="D64" s="4" t="s">
+      <c r="D62" s="91"/>
+    </row>
+    <row r="63" spans="3:4" ht="36" x14ac:dyDescent="0.25">
+      <c r="C63" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="D63" s="89" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="65" spans="4:5" ht="28" customHeight="1">
-      <c r="D65" s="4" t="s">
+    <row r="64" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="87" t="s">
         <v>907</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="D64" s="89" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="66" spans="4:5">
-      <c r="D66" s="4" t="s">
+    <row r="65" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="D65" s="89" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="67" spans="4:5">
-      <c r="D67" s="4" t="s">
+    <row r="66" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="87" t="s">
         <v>105</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="68" spans="4:5">
-      <c r="D68" s="4" t="s">
+      <c r="D66" s="89" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="87" t="s">
         <v>107</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="D67" s="89" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="69" spans="4:5" ht="28" customHeight="1">
-      <c r="D69" s="4" t="s">
+    <row r="68" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="D68" s="89" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="71" spans="4:5">
-      <c r="D71" s="3" t="s">
+    <row r="69" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="88"/>
+      <c r="D69" s="90"/>
+    </row>
+    <row r="70" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="86" t="s">
         <v>111</v>
       </c>
-      <c r="E71" s="3"/>
-    </row>
-    <row r="72" spans="4:5" ht="28" customHeight="1">
-      <c r="D72" s="4" t="s">
+      <c r="D70" s="91"/>
+    </row>
+    <row r="71" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C71" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="D71" s="89" t="s">
         <v>113</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D71:E71"/>
-  </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <legacyDrawing r:id="rId1"/>
@@ -7155,1155 +7681,1262 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="shParams">
     <tabColor rgb="FFBF9000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C3:K64"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:X64"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="60.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="16.7109375" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.625" customWidth="1"/>
+    <col min="4" max="4" width="50.625" customWidth="1"/>
+    <col min="5" max="10" width="15.625" customWidth="1"/>
+    <col min="11" max="11" width="40.625" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="25" max="16384" width="9" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="55" customFormat="1"/>
-    <row r="2" ht="26" customHeight="1" s="56" customFormat="1"/>
-    <row r="3" spans="3:11">
-      <c r="C3" s="1" t="s">
+    <row r="1" spans="2:19" s="77" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="79"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="S1" s="80"/>
+    </row>
+    <row r="2" spans="2:19" s="77" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="92" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="4" spans="3:11">
-      <c r="C4" s="2" t="s">
+      <c r="C2" s="82"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="S2" s="80"/>
+    </row>
+    <row r="3" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="74" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="3:11" ht="42" customHeight="1">
-      <c r="C6" s="6" t="s">
+    <row r="4" spans="2:19" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="98" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D5" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E5" s="114" t="s">
         <v>117</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F5" s="99" t="s">
         <v>118</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="3:11">
-      <c r="C7" s="7" t="s">
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+    </row>
+    <row r="6" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="75" t="s">
         <v>119</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D6" s="107" t="s">
         <v>120</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E6" s="108">
         <v>46295</v>
       </c>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="3:11">
-      <c r="C8" s="7" t="s">
+      <c r="F6" s="106"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="107"/>
+    </row>
+    <row r="7" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="75" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D7" s="107" t="s">
         <v>122</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E7" s="105" t="s">
         <v>123</v>
       </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="3:11">
-      <c r="C9" s="7" t="s">
+      <c r="F7" s="106"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+    </row>
+    <row r="8" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="75" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D8" s="107" t="s">
         <v>125</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E8" s="109">
         <v>1.4</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F8" s="106" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="10" spans="3:11">
-      <c r="C10" s="7" t="s">
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="107"/>
+    </row>
+    <row r="9" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="75" t="s">
         <v>127</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D9" s="107" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E9" s="110">
         <v>0.05</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F9" s="106" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="11" spans="3:11">
-      <c r="C11" s="7" t="s">
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="107"/>
+    </row>
+    <row r="10" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="75" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D10" s="107" t="s">
         <v>131</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E10" s="109">
         <v>365</v>
       </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="3:11">
-      <c r="C12" s="7" t="s">
+      <c r="F10" s="106"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="107"/>
+      <c r="I10" s="107"/>
+      <c r="J10" s="107"/>
+    </row>
+    <row r="11" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D11" s="107" t="s">
         <v>133</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E11" s="109">
         <v>250</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F11" s="106" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="13" spans="3:11">
-      <c r="C13" s="7" t="s">
+      <c r="G11" s="107"/>
+      <c r="H11" s="107"/>
+      <c r="I11" s="107"/>
+      <c r="J11" s="107"/>
+    </row>
+    <row r="12" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="75" t="s">
         <v>135</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D12" s="107" t="s">
         <v>136</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E12" s="109">
         <v>10</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F12" s="106" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="14" spans="3:11">
-      <c r="C14" s="7" t="s">
+      <c r="G12" s="107"/>
+      <c r="H12" s="107"/>
+      <c r="I12" s="107"/>
+      <c r="J12" s="107"/>
+    </row>
+    <row r="13" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D13" s="107" t="s">
         <v>139</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E13" s="109">
         <v>10</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F13" s="106" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="15" spans="3:11">
-      <c r="C15" s="7" t="s">
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="107"/>
+    </row>
+    <row r="14" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D14" s="107" t="s">
         <v>142</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E14" s="109">
         <v>10</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F14" s="106" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="16" spans="3:11">
-      <c r="C16" s="7" t="s">
+      <c r="G14" s="107"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="107"/>
+      <c r="J14" s="107"/>
+    </row>
+    <row r="15" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="75" t="s">
         <v>144</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D15" s="107" t="s">
         <v>920</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E15" s="109">
         <v>5</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F15" s="106" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="17" spans="3:11">
-      <c r="C17" s="7" t="s">
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="107"/>
+      <c r="J15" s="107"/>
+    </row>
+    <row r="16" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="75" t="s">
         <v>147</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D16" s="107" t="s">
         <v>148</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E16" s="109">
         <v>20</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F16" s="106" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="18" spans="3:11">
-      <c r="C18" s="7" t="s">
+      <c r="G16" s="107"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="107"/>
+      <c r="J16" s="107"/>
+    </row>
+    <row r="17" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="75" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D17" s="107" t="s">
         <v>150</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E17" s="109">
         <v>0.5</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F17" s="106" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="19" spans="3:11">
-      <c r="C19" s="7" t="s">
+      <c r="G17" s="107"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="107"/>
+    </row>
+    <row r="18" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="75" t="s">
         <v>152</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D18" s="107" t="s">
         <v>153</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E18" s="109">
         <v>5</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F18" s="106" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="20" spans="3:11">
-      <c r="C20" s="7" t="s">
+      <c r="G18" s="107"/>
+      <c r="H18" s="107"/>
+      <c r="I18" s="107"/>
+      <c r="J18" s="107"/>
+    </row>
+    <row r="19" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D19" s="107" t="s">
         <v>156</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E19" s="109">
         <v>0.7</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F19" s="106" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="21" spans="3:11">
-      <c r="C21" s="7" t="s">
+      <c r="G19" s="107"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="107"/>
+    </row>
+    <row r="20" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="75" t="s">
         <v>158</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D20" s="107" t="s">
         <v>159</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E20" s="109">
         <v>0.7</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F20" s="106" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="22" spans="3:11">
-      <c r="C22" s="7" t="s">
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="107"/>
+    </row>
+    <row r="21" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D21" s="107" t="s">
         <v>161</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E21" s="109">
         <v>0.3</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F21" s="106" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="23" spans="3:11">
-      <c r="C23" s="7" t="s">
+      <c r="G21" s="107"/>
+      <c r="H21" s="107"/>
+      <c r="I21" s="107"/>
+      <c r="J21" s="107"/>
+    </row>
+    <row r="22" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D22" s="107" t="s">
         <v>163</v>
       </c>
-      <c r="E23" s="14" t="b">
+      <c r="E22" s="111" t="b">
         <v>1</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F22" s="106" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="24" spans="3:11">
-      <c r="C24" s="7" t="s">
+      <c r="G22" s="107"/>
+      <c r="H22" s="107"/>
+      <c r="I22" s="107"/>
+      <c r="J22" s="107"/>
+    </row>
+    <row r="23" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="75" t="s">
         <v>165</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D23" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E23" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F23" s="106" t="s">
         <v>168</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G23" s="107"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="95" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="25" spans="3:11">
-      <c r="C25" s="7" t="s">
+      <c r="J23" s="107"/>
+    </row>
+    <row r="24" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="75" t="s">
         <v>169</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D24" s="107" t="s">
         <v>170</v>
       </c>
-      <c r="E25" s="13">
-        <v>0.001</v>
-      </c>
-      <c r="F25" s="10" t="s">
+      <c r="E24" s="110">
+        <v>1E-3</v>
+      </c>
+      <c r="F24" s="106" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="26" spans="3:11">
-      <c r="C26" s="7" t="s">
+      <c r="G24" s="107"/>
+      <c r="H24" s="107"/>
+      <c r="I24" s="107"/>
+      <c r="J24" s="107"/>
+    </row>
+    <row r="25" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="75" t="s">
         <v>172</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D25" s="107" t="s">
         <v>173</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E25" s="109">
         <v>0.1</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F25" s="106" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="28" spans="3:11">
-      <c r="C28" s="3" t="s">
+      <c r="G25" s="107"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="107"/>
+      <c r="J25" s="107"/>
+    </row>
+    <row r="26" spans="3:11" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="115" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="29" spans="3:11" ht="30" customHeight="1">
-      <c r="C29" s="6" t="s">
+    <row r="28" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="98" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D28" s="100" t="s">
         <v>177</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E28" s="100" t="s">
         <v>178</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F28" s="100" t="s">
         <v>179</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G28" s="100" t="s">
         <v>180</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H28" s="100" t="s">
         <v>181</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I28" s="100" t="s">
         <v>182</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J28" s="100" t="s">
         <v>183</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K28" s="98" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="30" spans="3:11">
-      <c r="C30" s="7" t="s">
+    <row r="29" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D29" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="13">
-        <v>0.005</v>
-      </c>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16">
+      <c r="E29" s="101"/>
+      <c r="F29" s="102">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G29" s="103"/>
+      <c r="H29" s="103">
         <v>0.5</v>
       </c>
-      <c r="I30" s="14"/>
-      <c r="J30" s="11" t="s">
+      <c r="I29" s="104"/>
+      <c r="J29" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K30" s="17" t="s">
+      <c r="K29" s="106" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="31" spans="3:11">
-      <c r="C31" s="7" t="s">
+    <row r="30" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D30" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="13">
+      <c r="E30" s="101"/>
+      <c r="F30" s="102">
         <v>0.04</v>
       </c>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16">
+      <c r="G30" s="103"/>
+      <c r="H30" s="103">
         <v>0.15</v>
       </c>
-      <c r="I31" s="14"/>
-      <c r="J31" s="11" t="s">
+      <c r="I30" s="104"/>
+      <c r="J30" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K31" s="17" t="s">
+      <c r="K30" s="106" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="32" spans="3:11">
-      <c r="C32" s="7" t="s">
+    <row r="31" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="75" t="s">
         <v>187</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D31" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E31" s="101" t="s">
         <v>189</v>
       </c>
-      <c r="F32" s="13">
-        <v>0.0038</v>
-      </c>
-      <c r="G32" s="16">
+      <c r="F31" s="102">
+        <v>3.8E-3</v>
+      </c>
+      <c r="G31" s="103">
         <v>0.5</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H31" s="103">
         <v>1</v>
       </c>
-      <c r="I32" s="14"/>
-      <c r="J32" s="11" t="s">
+      <c r="I31" s="104"/>
+      <c r="J31" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K32" s="17" t="s">
+      <c r="K31" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="3:11">
-      <c r="C33" s="7" t="s">
+    <row r="32" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="75" t="s">
         <v>191</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D32" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E32" s="101" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="13">
-        <v>0.0038</v>
-      </c>
-      <c r="G33" s="16">
+      <c r="F32" s="102">
+        <v>3.8E-3</v>
+      </c>
+      <c r="G32" s="103">
         <v>0.5</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H32" s="103">
         <v>1</v>
       </c>
-      <c r="I33" s="14"/>
-      <c r="J33" s="11" t="s">
+      <c r="I32" s="104"/>
+      <c r="J32" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K33" s="17" t="s">
+      <c r="K32" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="3:11">
-      <c r="C34" s="7" t="s">
+    <row r="33" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="75" t="s">
         <v>193</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D33" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E33" s="101" t="s">
         <v>194</v>
       </c>
-      <c r="F34" s="13">
-        <v>0.0042</v>
-      </c>
-      <c r="G34" s="16">
+      <c r="F33" s="102">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="G33" s="103">
         <v>0.5</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H33" s="103">
         <v>1</v>
       </c>
-      <c r="I34" s="14"/>
-      <c r="J34" s="11" t="s">
+      <c r="I33" s="104"/>
+      <c r="J33" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K34" s="17" t="s">
+      <c r="K33" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="3:11">
-      <c r="C35" s="7" t="s">
+    <row r="34" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="75" t="s">
         <v>195</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D34" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E34" s="101" t="s">
         <v>196</v>
       </c>
-      <c r="F35" s="13">
-        <v>0.0054</v>
-      </c>
-      <c r="G35" s="16">
+      <c r="F34" s="102">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="G34" s="103">
         <v>0.5</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H34" s="103">
         <v>1</v>
       </c>
-      <c r="I35" s="14"/>
-      <c r="J35" s="11" t="s">
+      <c r="I34" s="104"/>
+      <c r="J34" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K35" s="17" t="s">
+      <c r="K34" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="3:11">
-      <c r="C36" s="7" t="s">
+    <row r="35" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="75" t="s">
         <v>197</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D35" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E35" s="101" t="s">
         <v>198</v>
       </c>
-      <c r="F36" s="13">
-        <v>0.0106</v>
-      </c>
-      <c r="G36" s="16">
+      <c r="F35" s="102">
+        <v>1.06E-2</v>
+      </c>
+      <c r="G35" s="103">
         <v>0.5</v>
       </c>
-      <c r="H36" s="16">
+      <c r="H35" s="103">
         <v>1</v>
       </c>
-      <c r="I36" s="14"/>
-      <c r="J36" s="11" t="s">
+      <c r="I35" s="104"/>
+      <c r="J35" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K36" s="17" t="s">
+      <c r="K35" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="3:11">
-      <c r="C37" s="7" t="s">
+    <row r="36" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D36" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E36" s="101" t="s">
         <v>200</v>
       </c>
-      <c r="F37" s="13">
-        <v>0.016</v>
-      </c>
-      <c r="G37" s="16">
+      <c r="F36" s="102">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G36" s="103">
         <v>0.5</v>
       </c>
-      <c r="H37" s="16">
+      <c r="H36" s="103">
         <v>1</v>
       </c>
-      <c r="I37" s="14"/>
-      <c r="J37" s="11" t="s">
+      <c r="I36" s="104"/>
+      <c r="J36" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K37" s="17" t="s">
+      <c r="K36" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="38" spans="3:11">
-      <c r="C38" s="7" t="s">
+    <row r="37" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="75" t="s">
         <v>201</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D37" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E37" s="101" t="s">
         <v>202</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F37" s="102">
         <v>0.06</v>
       </c>
-      <c r="G38" s="16">
+      <c r="G37" s="103">
         <v>0.5</v>
       </c>
-      <c r="H38" s="16">
+      <c r="H37" s="103">
         <v>1</v>
       </c>
-      <c r="I38" s="14"/>
-      <c r="J38" s="11" t="s">
+      <c r="I37" s="104"/>
+      <c r="J37" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K38" s="17" t="s">
+      <c r="K37" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="3:11">
-      <c r="C39" s="7" t="s">
+    <row r="38" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D38" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E38" s="101" t="s">
         <v>204</v>
       </c>
-      <c r="F39" s="13">
-        <v>0.0038</v>
-      </c>
-      <c r="G39" s="16">
+      <c r="F38" s="102">
+        <v>3.8E-3</v>
+      </c>
+      <c r="G38" s="103">
         <v>0.5</v>
       </c>
-      <c r="H39" s="16">
+      <c r="H38" s="103">
         <v>1</v>
       </c>
-      <c r="I39" s="14"/>
-      <c r="J39" s="11" t="s">
+      <c r="I38" s="104"/>
+      <c r="J38" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K39" s="17" t="s">
+      <c r="K38" s="106" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="40" spans="3:11">
-      <c r="C40" s="7" t="s">
+    <row r="39" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="75" t="s">
         <v>206</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D39" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E39" s="101" t="s">
         <v>207</v>
       </c>
-      <c r="F40" s="13">
-        <v>0.0042</v>
-      </c>
-      <c r="G40" s="16">
+      <c r="F39" s="102">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="G39" s="103">
         <v>0.5</v>
       </c>
-      <c r="H40" s="16">
+      <c r="H39" s="103">
         <v>1</v>
       </c>
-      <c r="I40" s="14"/>
-      <c r="J40" s="11" t="s">
+      <c r="I39" s="104"/>
+      <c r="J39" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K40" s="17" t="s">
+      <c r="K39" s="106" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="41" spans="3:11">
-      <c r="C41" s="7" t="s">
+    <row r="40" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="75" t="s">
         <v>208</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D40" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E40" s="101" t="s">
         <v>209</v>
       </c>
-      <c r="F41" s="13">
-        <v>0.0054</v>
-      </c>
-      <c r="G41" s="16">
+      <c r="F40" s="102">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="G40" s="103">
         <v>0.5</v>
       </c>
-      <c r="H41" s="16">
+      <c r="H40" s="103">
         <v>1</v>
       </c>
-      <c r="I41" s="14"/>
-      <c r="J41" s="11" t="s">
+      <c r="I40" s="104"/>
+      <c r="J40" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K41" s="17" t="s">
+      <c r="K40" s="106" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="42" spans="3:11">
-      <c r="C42" s="7" t="s">
+    <row r="41" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="75" t="s">
         <v>210</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D41" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E41" s="101" t="s">
         <v>211</v>
       </c>
-      <c r="F42" s="13">
-        <v>0.0106</v>
-      </c>
-      <c r="G42" s="16">
+      <c r="F41" s="102">
+        <v>1.06E-2</v>
+      </c>
+      <c r="G41" s="103">
         <v>0.5</v>
       </c>
-      <c r="H42" s="16">
+      <c r="H41" s="103">
         <v>1</v>
       </c>
-      <c r="I42" s="14"/>
-      <c r="J42" s="11" t="s">
+      <c r="I41" s="104"/>
+      <c r="J41" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K42" s="17" t="s">
+      <c r="K41" s="106" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="43" spans="3:11">
-      <c r="C43" s="7" t="s">
+    <row r="42" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="75" t="s">
         <v>212</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D42" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E42" s="101" t="s">
         <v>213</v>
       </c>
-      <c r="F43" s="13">
-        <v>0.016</v>
-      </c>
-      <c r="G43" s="16">
+      <c r="F42" s="102">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G42" s="103">
         <v>0.5</v>
       </c>
-      <c r="H43" s="16">
+      <c r="H42" s="103">
         <v>1</v>
       </c>
-      <c r="I43" s="14"/>
-      <c r="J43" s="11" t="s">
+      <c r="I42" s="104"/>
+      <c r="J42" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K43" s="17" t="s">
+      <c r="K42" s="106" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="44" spans="3:11">
-      <c r="C44" s="7" t="s">
+    <row r="43" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="75" t="s">
         <v>214</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D43" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E43" s="101" t="s">
         <v>215</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F43" s="102">
         <v>0.06</v>
       </c>
-      <c r="G44" s="16">
+      <c r="G43" s="103">
         <v>0.5</v>
       </c>
-      <c r="H44" s="16">
+      <c r="H43" s="103">
         <v>1</v>
       </c>
-      <c r="I44" s="14"/>
-      <c r="J44" s="11" t="s">
+      <c r="I43" s="104"/>
+      <c r="J43" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K44" s="17" t="s">
+      <c r="K43" s="106" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="45" spans="3:11">
-      <c r="C45" s="7" t="s">
+    <row r="44" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="75" t="s">
         <v>216</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D44" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E44" s="101" t="s">
         <v>217</v>
       </c>
-      <c r="F45" s="13">
-        <v>0.0038</v>
-      </c>
-      <c r="G45" s="16">
+      <c r="F44" s="102">
+        <v>3.8E-3</v>
+      </c>
+      <c r="G44" s="103">
         <v>0.8</v>
       </c>
-      <c r="H45" s="16">
+      <c r="H44" s="103">
         <v>0.8</v>
       </c>
-      <c r="I45" s="14"/>
-      <c r="J45" s="11" t="s">
+      <c r="I44" s="104"/>
+      <c r="J44" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K45" s="17" t="s">
+      <c r="K44" s="106" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="46" spans="3:11">
-      <c r="C46" s="7" t="s">
+    <row r="45" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="75" t="s">
         <v>219</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D45" s="101" t="s">
         <v>188</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E45" s="101" t="s">
         <v>220</v>
       </c>
-      <c r="F46" s="13">
-        <v>0.0106</v>
-      </c>
-      <c r="G46" s="16">
+      <c r="F45" s="102">
+        <v>1.06E-2</v>
+      </c>
+      <c r="G45" s="103">
         <v>0.8</v>
       </c>
-      <c r="H46" s="16">
+      <c r="H45" s="103">
         <v>0.8</v>
       </c>
-      <c r="I46" s="14"/>
-      <c r="J46" s="11" t="s">
+      <c r="I45" s="104"/>
+      <c r="J45" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K46" s="17" t="s">
+      <c r="K45" s="106" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="47" spans="3:11">
-      <c r="C47" s="7" t="s">
+    <row r="46" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="75" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D46" s="101" t="s">
         <v>222</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E46" s="101" t="s">
         <v>223</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F46" s="102">
         <v>0.32</v>
       </c>
-      <c r="G47" s="16">
+      <c r="G46" s="103">
         <v>0.5</v>
       </c>
-      <c r="H47" s="16">
+      <c r="H46" s="103">
         <v>1.2</v>
       </c>
-      <c r="I47" s="14"/>
-      <c r="J47" s="11" t="s">
+      <c r="I46" s="104"/>
+      <c r="J46" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K47" s="17" t="s">
+      <c r="K46" s="106" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="48" spans="3:11">
-      <c r="C48" s="7" t="s">
+    <row r="47" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="75" t="s">
         <v>225</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D47" s="101" t="s">
         <v>222</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E47" s="101" t="s">
         <v>226</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F47" s="102">
         <v>0.2</v>
       </c>
-      <c r="G48" s="16">
+      <c r="G47" s="103">
         <v>0.8</v>
       </c>
-      <c r="H48" s="16">
+      <c r="H47" s="103">
         <v>0.75</v>
       </c>
-      <c r="I48" s="14"/>
-      <c r="J48" s="11" t="s">
+      <c r="I47" s="104"/>
+      <c r="J47" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K48" s="17" t="s">
+      <c r="K47" s="106" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="49" spans="3:11">
-      <c r="C49" s="7" t="s">
+    <row r="48" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="75" t="s">
         <v>227</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D48" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E48" s="101" t="s">
         <v>228</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F48" s="102">
         <v>0.4</v>
       </c>
-      <c r="G49" s="16">
+      <c r="G48" s="103">
         <v>0.4</v>
       </c>
-      <c r="H49" s="16">
+      <c r="H48" s="103">
         <v>1.5</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I48" s="105" t="s">
         <v>229</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J48" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K49" s="17" t="s">
+      <c r="K48" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="50" spans="3:11">
-      <c r="C50" s="7" t="s">
+    <row r="49" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="75" t="s">
         <v>230</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D49" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E49" s="101" t="s">
         <v>231</v>
       </c>
-      <c r="F50" s="13">
+      <c r="F49" s="102">
         <v>0.18</v>
       </c>
-      <c r="G50" s="16">
+      <c r="G49" s="103">
         <v>0.4</v>
       </c>
-      <c r="H50" s="16">
+      <c r="H49" s="103">
         <v>0.7</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I49" s="105" t="s">
         <v>229</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="J49" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K50" s="17" t="s">
+      <c r="K49" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="51" spans="3:11">
-      <c r="C51" s="7" t="s">
+    <row r="50" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="75" t="s">
         <v>232</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D50" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E50" s="101" t="s">
         <v>233</v>
       </c>
-      <c r="F51" s="13">
+      <c r="F50" s="102">
         <v>0.18</v>
       </c>
-      <c r="G51" s="16">
+      <c r="G50" s="103">
         <v>0.4</v>
       </c>
-      <c r="H51" s="16">
+      <c r="H50" s="103">
         <v>0.7</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I50" s="105" t="s">
         <v>233</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J50" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K51" s="17" t="s">
+      <c r="K50" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="52" spans="3:11">
-      <c r="C52" s="7" t="s">
+    <row r="51" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="75" t="s">
         <v>234</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D51" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E51" s="101" t="s">
         <v>235</v>
       </c>
-      <c r="F52" s="13">
+      <c r="F51" s="102">
         <v>0.18</v>
       </c>
-      <c r="G52" s="16">
+      <c r="G51" s="103">
         <v>0.4</v>
       </c>
-      <c r="H52" s="16">
+      <c r="H51" s="103">
         <v>0.7</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I51" s="105" t="s">
         <v>235</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J51" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K52" s="17" t="s">
+      <c r="K51" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="53" spans="3:11">
-      <c r="C53" s="7" t="s">
+    <row r="52" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="75" t="s">
         <v>236</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D52" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E52" s="101" t="s">
         <v>237</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F52" s="102">
         <v>0.18</v>
       </c>
-      <c r="G53" s="16">
+      <c r="G52" s="103">
         <v>0.4</v>
       </c>
-      <c r="H53" s="16">
+      <c r="H52" s="103">
         <v>0.7</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I52" s="105" t="s">
         <v>237</v>
       </c>
-      <c r="J53" s="11" t="s">
+      <c r="J52" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="K53" s="17" t="s">
+      <c r="K52" s="106" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="54" spans="3:11">
-      <c r="C54" s="7" t="s">
+    <row r="53" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="75" t="s">
         <v>238</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D53" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E53" s="101" t="s">
         <v>239</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F53" s="102">
         <v>0.18</v>
       </c>
-      <c r="G54" s="16">
+      <c r="G53" s="103">
         <v>0.4</v>
       </c>
-      <c r="H54" s="16">
+      <c r="H53" s="103">
         <v>0.7</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I53" s="105" t="s">
         <v>239</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="J53" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="K54" s="18" t="s">
+      <c r="K53" s="106" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="55" spans="3:11">
-      <c r="C55" s="7" t="s">
+    <row r="54" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="75" t="s">
         <v>241</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D54" s="101" t="s">
         <v>241</v>
       </c>
-      <c r="E55" s="8"/>
-      <c r="F55" s="13">
+      <c r="E54" s="101"/>
+      <c r="F54" s="102">
         <v>0.08</v>
       </c>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16">
+      <c r="G54" s="103"/>
+      <c r="H54" s="103">
         <v>1.5</v>
       </c>
-      <c r="I55" s="14"/>
-      <c r="J55" s="11" t="s">
+      <c r="I54" s="104"/>
+      <c r="J54" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="K55" s="17" t="s">
+      <c r="K54" s="106" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="57" spans="3:11">
-      <c r="C57" s="3" t="s">
+    <row r="55" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="115" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="58" spans="3:11" ht="30" customHeight="1">
-      <c r="C58" s="6" t="s">
+    <row r="57" spans="3:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="97" t="s">
         <v>244</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D57" s="97" t="s">
         <v>245</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E57" s="96" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="59" spans="3:11">
-      <c r="C59" s="11" t="s">
+    <row r="58" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C58" s="76" t="s">
         <v>123</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D58" s="107" t="s">
         <v>247</v>
       </c>
-      <c r="E59" s="19">
+      <c r="E58" s="112">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="3:11">
-      <c r="C60" s="11" t="s">
+    <row r="59" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="76" t="s">
         <v>248</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D59" s="107" t="s">
         <v>249</v>
       </c>
-      <c r="E60" s="19">
+      <c r="E59" s="112">
         <v>0.86</v>
       </c>
     </row>
-    <row r="61" spans="3:11">
-      <c r="C61" s="11" t="s">
+    <row r="60" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="76" t="s">
         <v>250</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D60" s="107" t="s">
         <v>251</v>
       </c>
-      <c r="E61" s="19">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="62" spans="3:11">
-      <c r="C62" s="11" t="s">
+      <c r="E60" s="112">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="76" t="s">
         <v>252</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D61" s="107" t="s">
         <v>253</v>
       </c>
-      <c r="E62" s="19">
-        <v>0.0058</v>
-      </c>
-    </row>
-    <row r="63" spans="3:11">
-      <c r="C63" s="11" t="s">
+      <c r="E61" s="112">
+        <v>5.7999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="76" t="s">
         <v>254</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D62" s="107" t="s">
         <v>255</v>
       </c>
-      <c r="E63" s="19">
+      <c r="E62" s="112">
         <v>1.07</v>
       </c>
     </row>
-    <row r="64" spans="3:11">
-      <c r="D64" s="15" t="s">
+    <row r="63" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D63" s="113" t="s">
         <v>256</v>
       </c>
     </row>
+    <row r="64" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E23">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E23" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"CRR,BCBS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J30:J55">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J29:J54" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"BOTH,CRR,BCBS"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D29:D55" xr:uid="{92FC5665-A317-49D8-9552-6AF5B626BBD5}">
+      <formula1>"IR, FX,CR,EQ,CO,OT"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -8925,18 +8925,85 @@
     </row>
     <row r="64" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations count="22">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid reporting date" error="Enter a date between 2000 and 2100." promptTitle="Reporting date" prompt="Date the exposures are calculated for. Maturities and dates are measured from it." sqref="E6">
+      <formula1>36526</formula1>
+      <formula2>73415</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid currency" error="Enter a three-letter ISO currency code, e.g. EUR." promptTitle="Reporting currency" prompt="ISO code, e.g. EUR. Every amount is converted into it with the FX table below." sqref="E7">
+      <formula1>AND(ISTEXT(ReportingCcy),LEN(ReportingCcy)=3)</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid alpha" error="Alpha must be a number greater than zero. Regulatory value: 1.4." promptTitle="Alpha" prompt="Multiplier on RC + PFE. Regulatory value 1.4 (CRE52.1, CRR Art. 274(2))." sqref="E8">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid floor" error="Enter a percentage from 0% to below 100%. Regulatory value: 5%." promptTitle="Multiplier floor" prompt="Floor of the PFE multiplier, as a percentage. Regulatory value 5% (CRE52.23)." sqref="E9">
+      <formula1>0</formula1>
+      <formula2>0.9999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid day count" error="Enter a number from 360 to 366. Normally 365." promptTitle="Days per year" prompt="Calendar days per year for S, E, M and T. Normally 365." sqref="E10">
+      <formula1>360</formula1>
+      <formula2>366</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid business days" error="Enter a whole number from 200 to 366. Regulatory value: 250." promptTitle="Business days per year" prompt="Converts MPOR and the maturity floors into years. Regulatory value 250 (CRE52.48, 52.52)." sqref="E11">
+      <formula1>200</formula1>
+      <formula2>366</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid minimum maturity" error="Enter a whole number of business days from 0 to 250. Regulatory value: 10." promptTitle="Minimum maturity" prompt="Floor on M for the unmargined maturity factor, in business days. Regulatory value 10 (CRE52.48)." sqref="E12">
+      <formula1>0</formula1>
+      <formula2>250</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid duration floor" error="Enter a whole number of business days from 0 to 250 (0 = no floor). Regulatory value: 10." promptTitle="Supervisory duration floor" prompt="Floor on S and E for the supervisory duration, in business days; 0 = no floor. Regulatory value 10 (CRE52.34, CRR Art. 279b)." sqref="E13">
+      <formula1>0</formula1>
+      <formula2>250</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid MPOR floor" error="Enter a whole number of business days from 1 to 250." promptTitle="MPOR floor, bilateral" prompt="Minimum MPOR for a bilateral, daily-margined netting set, in business days. Regulatory value 10 (CRE52.50)." sqref="E14">
+      <formula1>1</formula1>
+      <formula2>250</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid MPOR floor" error="Enter a whole number of business days from 1 to 250." promptTitle="MPOR floor, client clearing" prompt="Minimum MPOR for a cleared netting set, in business days. Regulatory value 5 (CRE54)." sqref="E15">
+      <formula1>1</formula1>
+      <formula2>250</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid MPOR floor" error="Enter a whole number of business days from 1 to 250." promptTitle="MPOR floor, large netting set" prompt="Minimum MPOR when a netting set has more than 5,000 trades or illiquid collateral, in business days. Regulatory value 20 (CRE52.50)." sqref="E16">
+      <formula1>1</formula1>
+      <formula2>250</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid basis factor" error="Enter a number from 0 to 1. Regulatory value: 0.5." promptTitle="Basis factor" prompt="Supervisory factor multiplier for basis transactions. Regulatory value 0.5 (CRE52.46)." sqref="E17">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid volatility factor" error="Enter a number from 0 to 10. Regulatory value: 5." promptTitle="Volatility factor" prompt="Supervisory factor multiplier for volatility transactions. Regulatory value 5 (CRE52.47)." sqref="E18">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid IR correlation" error="Each correlation must be from 0 to 1, and the three together must form a valid correlation matrix." promptTitle="IR correlation 1-2" prompt="Correlation between maturity buckets. Regulatory values: 1-2 and 2-3 = 0.7, 1-3 = 0.3 (CRE52.57)." sqref="E19">
+      <formula1>AND(ISNUMBER(IRCorrBucket12),ISNUMBER(IRCorrBucket23),ISNUMBER(IRCorrBucket13),MIN(IRCorrBucket12,IRCorrBucket23,IRCorrBucket13)&gt;=0,MAX(IRCorrBucket12,IRCorrBucket23,IRCorrBucket13)&lt;=1,1-IRCorrBucket12^2-IRCorrBucket23^2-IRCorrBucket13^2+2*IRCorrBucket12*IRCorrBucket23*IRCorrBucket13&gt;=0)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid IR correlation" error="Each correlation must be from 0 to 1, and the three together must form a valid correlation matrix." promptTitle="IR correlation 2-3" prompt="Correlation between maturity buckets. Regulatory values: 1-2 and 2-3 = 0.7, 1-3 = 0.3 (CRE52.57)." sqref="E20">
+      <formula1>AND(ISNUMBER(IRCorrBucket12),ISNUMBER(IRCorrBucket23),ISNUMBER(IRCorrBucket13),MIN(IRCorrBucket12,IRCorrBucket23,IRCorrBucket13)&gt;=0,MAX(IRCorrBucket12,IRCorrBucket23,IRCorrBucket13)&lt;=1,1-IRCorrBucket12^2-IRCorrBucket23^2-IRCorrBucket13^2+2*IRCorrBucket12*IRCorrBucket23*IRCorrBucket13&gt;=0)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid IR correlation" error="Each correlation must be from 0 to 1, and the three together must form a valid correlation matrix." promptTitle="IR correlation 1-3" prompt="Correlation between maturity buckets. Regulatory values: 1-2 and 2-3 = 0.7, 1-3 = 0.3 (CRE52.57)." sqref="E21">
+      <formula1>AND(ISNUMBER(IRCorrBucket12),ISNUMBER(IRCorrBucket23),ISNUMBER(IRCorrBucket13),MIN(IRCorrBucket12,IRCorrBucket23,IRCorrBucket13)&gt;=0,MAX(IRCorrBucket12,IRCorrBucket23,IRCorrBucket13)&lt;=1,1-IRCorrBucket12^2-IRCorrBucket23^2-IRCorrBucket13^2+2*IRCorrBucket12*IRCorrBucket23*IRCorrBucket13&gt;=0)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="IR bucket offset" prompt="TRUE = bucket formula with offsets. FALSE = sum of absolute bucket values (Basel only). Under CRR only TRUE is allowed (Art. 280a(3))." sqref="E22">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E23" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid regime" error="Choose CRR or BCBS." promptTitle="Default regime" prompt="CRR = EU rules; BCBS = Basel CRE52. Used for every netting set without its own regime. Blank means CRR." sqref="E23">
       <formula1>"CRR,BCBS"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid IR threshold" error="Enter a percentage from 0% to 10%. Value: 0.1%." promptTitle="Lambda threshold, IR" prompt="CRR shift for IR options with negative rates, as a percentage. Value 0.1% (Del. Reg. 2021/931 Art. 5)." sqref="E24">
+      <formula1>0</formula1>
+      <formula2>0.1</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid commodity threshold" error="Enter a number from 0 to 1. Value: 0.10." promptTitle="Lambda threshold, commodity" prompt="CRR shift for commodity options with negative prices. Value 0.10 (Del. Reg. 2021/931 Art. 5)." sqref="E25">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J29:J54" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"BOTH,CRR,BCBS"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D29:D55" xr:uid="{92FC5665-A317-49D8-9552-6AF5B626BBD5}">
-      <formula1>"IR, FX,CR,EQ,CO,OT"</formula1>
+      <formula1>"IR,FX,CR,EQ,CO,OT"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -8925,7 +8925,7 @@
     </row>
     <row r="64" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations count="22">
+  <dataValidations count="29">
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid reporting date" error="Enter a date between 2000 and 2100." promptTitle="Reporting date" prompt="Date the exposures are calculated for. Maturities and dates are measured from it." sqref="E6">
       <formula1>36526</formula1>
       <formula2>73415</formula2>
@@ -8999,11 +8999,35 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J29:J54" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid or duplicate key" error="Enter a text key that is not already used in this table." promptTitle="Supervisory factor key" prompt="Unique key of the row, e.g. CR_BBB. A key listed twice with different values stops the run." sqref="C29:C54">
+      <formula1>AND(ISTEXT(C29),COUNTIF($C$29:$C$54,C29)=1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid asset class" error="Choose IR, FX, CR, EQ, CO or OT." promptTitle="Asset class" prompt="IR, FX, CR (credit), EQ (equity), CO (commodity) or OT (other risks, CRR Art. 280f)." sqref="D29:D55">
+      <formula1>"IR,FX,CR,EQ,CO,OT"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid supervisory factor" error="Enter a percentage from 0% to 100%." promptTitle="Supervisory factor" prompt="Supervisory factor as a percentage (CRE52.72; CRR Art. 280a to 280f)." sqref="F29:F54">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid correlation" error="Enter a percentage from 0% to 100%." promptTitle="Correlation" prompt="Correlation with the systematic factor, for credit, equity and commodity (CRE52.72). Leave blank for IR, FX and OT." sqref="G29:G54">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid volatility" error="Enter a percentage from 0% to 500%." promptTitle="Supervisory option volatility" prompt="Volatility used in the supervisory delta of options (CRE52.72)." sqref="H29:H54">
+      <formula1>0</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid hedging set" error="Choose ENERGY, METALS, AGRICULTURAL, OTHER or CLIMATIC." promptTitle="Commodity hedging set" prompt="Commodity rows only (CRE52.69). CLIMATIC is the CRR climatic-conditions hedging set (Art. 277a(1)(e)). Leave blank for other asset classes." sqref="I29:I54">
+      <formula1>"ENERGY,METALS,AGRICULTURAL,OTHER,CLIMATIC"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid regime" error="Choose BOTH, CRR or BCBS." promptTitle="Regimes" prompt="Regimes in which the row applies: BOTH, CRR only or BCBS only." sqref="J29:J54">
       <formula1>"BOTH,CRR,BCBS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D29:D55" xr:uid="{92FC5665-A317-49D8-9552-6AF5B626BBD5}">
-      <formula1>"IR,FX,CR,EQ,CO,OT"</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid or duplicate currency" error="Enter a three-letter ISO code that is not already in the table." promptTitle="Currency" prompt="ISO code, e.g. USD. Add currencies directly below the last row, with no blank rows." sqref="C58:C77">
+      <formula1>AND(ISTEXT(C58),LEN(C58)=3,COUNTIF($C$58:$C$77,C58)=1)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid FX rate" error="Enter a number greater than zero; the reporting currency's rate must be 1." promptTitle="FX rate" prompt="Units of the reporting currency per 1 unit of this currency. The reporting currency itself is 1." sqref="E58:E77">
+      <formula1>AND(ISNUMBER(E58),E58&gt;0,OR(UPPER(C58)&lt;&gt;UPPER(ReportingCcy),E58=1))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -25056,7 +25056,7 @@
       <formula1>"IR,FX,CR,EQ,CO,OT"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F5002">
-      <formula1>Params!$E$30:$E$55</formula1>
+      <formula1>Params!$E$29:$E$54</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7:H5002">
       <formula1>"Linear,Option,CDO"</formula1>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -9099,6 +9099,16 @@
     </row>
     <row r="64" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <conditionalFormatting sqref="C29:C54">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>AND(C29&lt;&gt;"",COUNTIF($C$29:$C$54,C29)&gt;1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C58:C77">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND(C58&lt;&gt;"",COUNTIF($C$58:$C$77,C58)&gt;1)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="29">
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid reporting date" error="Enter a date between 2000 and 2100." promptTitle="Reporting date" prompt="Date the exposures are calculated for. Maturities and dates are measured from it." sqref="E6">
       <formula1>36526</formula1>
@@ -13376,6 +13386,11 @@
     <row r="433" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="434" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <conditionalFormatting sqref="C7:C206">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>AND(C7&lt;&gt;"",COUNTIF($C$7:$C$206,C7)&gt;1)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="14">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Duplicate ID" error="This netting set ID is already used. Enter a unique ID." promptTitle="Netting set ID" prompt="Unique ID of the legally enforceable netting set. Trades refer to it. A repeated ID makes the set INVALID." sqref="C7:C206">
       <formula1>COUNTIF($C$7:$C$206,C7)=1</formula1>
@@ -25070,7 +25085,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K7:K5002">
       <formula1>"Standard,Basis,Volatility"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D5002">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Netting set not listed" error="This ID is not on NettingSets. Add the netting set there, or the trade will be rejected. Continue anyway?" promptTitle="Netting set" prompt="Choose the ID of a netting set listed on NettingSets. A trade whose netting set is not listed there is rejected." sqref="D7:D5002">
       <formula1>NettingSets!$C$7:$C$206</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -989,7 +989,7 @@
     <t>CRR-CLIMATE</t>
   </si>
   <si>
-    <t>Climatic-conditions hedging set (Art. 277a) - SF to confirm</t>
+    <t>Climatic-conditions hedging set (Art. 277a), factor 18% (Art. 280e(5))</t>
   </si>
   <si>
     <t>NS-ALPHA</t>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Basel_vs_CRR!$C$5:$K$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Trades!$C$4:$Z$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Trades!$C$4:$AB$69</definedName>
     <definedName name="Alpha">Params!$E$8</definedName>
     <definedName name="AsOfDate">Params!$E$6</definedName>
     <definedName name="BasisFactor">Params!$E$17</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="963">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -2528,7 +2528,7 @@
     <t>Classification of hybrids</t>
   </si>
   <si>
-    <t>Not automated: enter one row per risk-category leg, classified per the RTS.</t>
+    <t>Not automated: enter one leg per risk category, classified per the RTS, all with the same Economic trade ID; the MtM leg (Y) carries the trade's MtM and every other leg 0, which the engine enforces (#38).</t>
   </si>
   <si>
     <t>Commodity hedging sets</t>
@@ -2714,7 +2714,7 @@
     <t>Combinations of options</t>
   </si>
   <si>
-    <t>Not specifically addressed in the text reviewed.</t>
+    <t>CRE52.42(4): a payoff that is a combination of European options is treated as separate trades; CRE52.43 and the CRE52 FAQ allow a multiple-payment option as single-payment options; linear products may not be decomposed.</t>
   </si>
   <si>
     <t>Art. 274(6): decompose linear combinations and vanilla digital options.</t>
@@ -2726,7 +2726,7 @@
     <t>Depends on booking</t>
   </si>
   <si>
-    <t>Enter the components as separate trades.</t>
+    <t>Enter each option as a leg of one economic trade: same Economic trade ID, the MtM on the MtM leg (Y) and 0 on the others; legs in one asset class must all be options (#38).</t>
   </si>
   <si>
     <t>VERIFIED (CRR)</t>
@@ -2973,6 +2973,12 @@
   <si>
     <t>Detachment
 D</t>
+  </si>
+  <si>
+    <t>Economic trade ID</t>
+  </si>
+  <si>
+    <t>MtM leg (Y/N)</t>
   </si>
 </sst>
 </file>
@@ -16536,7 +16542,7 @@
     <tabColor rgb="FFBF9000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Z5005"/>
+  <dimension ref="B1:AB5005"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
@@ -16553,10 +16559,12 @@
     <col min="16" max="20" width="10.625" style="184" customWidth="1"/>
     <col min="21" max="23" width="10.625" style="163" customWidth="1"/>
     <col min="24" max="25" width="15.625" style="163" customWidth="1"/>
-    <col min="26" max="26" width="50.75" style="163" customWidth="1"/>
+    <col min="26" max="26" width="15.625" style="163" customWidth="1"/>
+    <col min="27" max="27" width="10.625" style="184" customWidth="1"/>
+    <col min="28" max="28" width="50.75" style="163" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="164" t="s">
         <v>0</v>
       </c>
@@ -16584,8 +16592,10 @@
       <c r="X1" s="167"/>
       <c r="Y1" s="167"/>
       <c r="Z1" s="167"/>
-    </row>
-    <row r="2" spans="2:26" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA1" s="167"/>
+      <c r="AB1" s="167"/>
+    </row>
+    <row r="2" spans="2:28" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="168" t="s">
         <v>60</v>
       </c>
@@ -16613,8 +16623,10 @@
       <c r="X2" s="171"/>
       <c r="Y2" s="171"/>
       <c r="Z2" s="171"/>
-    </row>
-    <row r="3" spans="2:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA2" s="171"/>
+      <c r="AB2" s="171"/>
+    </row>
+    <row r="3" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="173"/>
       <c r="D3"/>
       <c r="E3" s="172"/>
@@ -16638,9 +16650,11 @@
       <c r="W3"/>
       <c r="X3"/>
       <c r="Y3"/>
-      <c r="Z3"/>
-    </row>
-    <row r="4" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z3" s="172"/>
+      <c r="AA3" s="172"/>
+      <c r="AB3"/>
+    </row>
+    <row r="4" spans="2:28" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="175" t="s">
         <v>309</v>
       </c>
@@ -16710,11 +16724,17 @@
       <c r="Y4" s="151" t="s">
         <v>960</v>
       </c>
-      <c r="Z4" s="175" t="s">
+      <c r="Z4" s="151" t="s">
+        <v>961</v>
+      </c>
+      <c r="AA4" s="151" t="s">
+        <v>962</v>
+      </c>
+      <c r="AB4" s="175" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="5" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="158" t="s">
         <v>346</v>
       </c>
@@ -16764,11 +16784,13 @@
       <c r="W5" s="199"/>
       <c r="X5" s="142"/>
       <c r="Y5" s="142"/>
-      <c r="Z5" s="143" t="s">
+      <c r="Z5" s="140"/>
+      <c r="AA5" s="140"/>
+      <c r="AB5" s="143" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="6" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="158" t="s">
         <v>351</v>
       </c>
@@ -16818,11 +16840,13 @@
       <c r="W6" s="199"/>
       <c r="X6" s="142"/>
       <c r="Y6" s="142"/>
-      <c r="Z6" s="143" t="s">
+      <c r="Z6" s="140"/>
+      <c r="AA6" s="140"/>
+      <c r="AB6" s="143" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="7" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="158" t="s">
         <v>354</v>
       </c>
@@ -16882,11 +16906,13 @@
       <c r="W7" s="199"/>
       <c r="X7" s="142"/>
       <c r="Y7" s="142"/>
-      <c r="Z7" s="143" t="s">
+      <c r="Z7" s="140"/>
+      <c r="AA7" s="140"/>
+      <c r="AB7" s="143" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="8" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="158" t="s">
         <v>358</v>
       </c>
@@ -16938,11 +16964,13 @@
       <c r="W8" s="199"/>
       <c r="X8" s="142"/>
       <c r="Y8" s="142"/>
-      <c r="Z8" s="143" t="s">
+      <c r="Z8" s="140"/>
+      <c r="AA8" s="140"/>
+      <c r="AB8" s="143" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="9" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="158" t="s">
         <v>361</v>
       </c>
@@ -16994,11 +17022,13 @@
       <c r="W9" s="199"/>
       <c r="X9" s="142"/>
       <c r="Y9" s="142"/>
-      <c r="Z9" s="143" t="s">
+      <c r="Z9" s="140"/>
+      <c r="AA9" s="140"/>
+      <c r="AB9" s="143" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="10" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="158" t="s">
         <v>364</v>
       </c>
@@ -17050,11 +17080,13 @@
       <c r="W10" s="199"/>
       <c r="X10" s="142"/>
       <c r="Y10" s="142"/>
-      <c r="Z10" s="143" t="s">
+      <c r="Z10" s="140"/>
+      <c r="AA10" s="140"/>
+      <c r="AB10" s="143" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="11" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="158" t="s">
         <v>367</v>
       </c>
@@ -17104,11 +17136,13 @@
       <c r="W11" s="199"/>
       <c r="X11" s="142"/>
       <c r="Y11" s="142"/>
-      <c r="Z11" s="143" t="s">
+      <c r="Z11" s="140"/>
+      <c r="AA11" s="140"/>
+      <c r="AB11" s="143" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="12" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="158" t="s">
         <v>370</v>
       </c>
@@ -17158,11 +17192,13 @@
       <c r="W12" s="199"/>
       <c r="X12" s="142"/>
       <c r="Y12" s="142"/>
-      <c r="Z12" s="143" t="s">
+      <c r="Z12" s="140"/>
+      <c r="AA12" s="140"/>
+      <c r="AB12" s="143" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="13" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="158" t="s">
         <v>372</v>
       </c>
@@ -17212,11 +17248,13 @@
       <c r="W13" s="199"/>
       <c r="X13" s="142"/>
       <c r="Y13" s="142"/>
-      <c r="Z13" s="143" t="s">
+      <c r="Z13" s="140"/>
+      <c r="AA13" s="140"/>
+      <c r="AB13" s="143" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="14" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="158" t="s">
         <v>375</v>
       </c>
@@ -17266,11 +17304,13 @@
       <c r="W14" s="199"/>
       <c r="X14" s="142"/>
       <c r="Y14" s="142"/>
-      <c r="Z14" s="143" t="s">
+      <c r="Z14" s="140"/>
+      <c r="AA14" s="140"/>
+      <c r="AB14" s="143" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="15" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="158" t="s">
         <v>376</v>
       </c>
@@ -17320,11 +17360,13 @@
       <c r="W15" s="199"/>
       <c r="X15" s="142"/>
       <c r="Y15" s="142"/>
-      <c r="Z15" s="143" t="s">
+      <c r="Z15" s="140"/>
+      <c r="AA15" s="140"/>
+      <c r="AB15" s="143" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="16" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="158" t="s">
         <v>377</v>
       </c>
@@ -17384,11 +17426,13 @@
       <c r="W16" s="199"/>
       <c r="X16" s="142"/>
       <c r="Y16" s="142"/>
-      <c r="Z16" s="143" t="s">
+      <c r="Z16" s="140"/>
+      <c r="AA16" s="140"/>
+      <c r="AB16" s="143" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="17" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="158" t="s">
         <v>378</v>
       </c>
@@ -17440,11 +17484,13 @@
       <c r="W17" s="199"/>
       <c r="X17" s="142"/>
       <c r="Y17" s="142"/>
-      <c r="Z17" s="143" t="s">
+      <c r="Z17" s="140"/>
+      <c r="AA17" s="140"/>
+      <c r="AB17" s="143" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="18" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="158" t="s">
         <v>379</v>
       </c>
@@ -17496,11 +17542,13 @@
       <c r="W18" s="199"/>
       <c r="X18" s="142"/>
       <c r="Y18" s="142"/>
-      <c r="Z18" s="143" t="s">
+      <c r="Z18" s="140"/>
+      <c r="AA18" s="140"/>
+      <c r="AB18" s="143" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="19" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="158" t="s">
         <v>380</v>
       </c>
@@ -17552,11 +17600,13 @@
       <c r="W19" s="199"/>
       <c r="X19" s="142"/>
       <c r="Y19" s="142"/>
-      <c r="Z19" s="143" t="s">
+      <c r="Z19" s="140"/>
+      <c r="AA19" s="140"/>
+      <c r="AB19" s="143" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="20" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="158" t="s">
         <v>381</v>
       </c>
@@ -17606,11 +17656,13 @@
       <c r="W20" s="199"/>
       <c r="X20" s="142"/>
       <c r="Y20" s="142"/>
-      <c r="Z20" s="143" t="s">
+      <c r="Z20" s="140"/>
+      <c r="AA20" s="140"/>
+      <c r="AB20" s="143" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="21" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="158" t="s">
         <v>382</v>
       </c>
@@ -17660,11 +17712,13 @@
       <c r="W21" s="199"/>
       <c r="X21" s="142"/>
       <c r="Y21" s="142"/>
-      <c r="Z21" s="143" t="s">
+      <c r="Z21" s="140"/>
+      <c r="AA21" s="140"/>
+      <c r="AB21" s="143" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="22" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="158" t="s">
         <v>383</v>
       </c>
@@ -17724,11 +17778,13 @@
       <c r="W22" s="199"/>
       <c r="X22" s="142"/>
       <c r="Y22" s="142"/>
-      <c r="Z22" s="143" t="s">
+      <c r="Z22" s="140"/>
+      <c r="AA22" s="140"/>
+      <c r="AB22" s="143" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="23" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="158" t="s">
         <v>384</v>
       </c>
@@ -17778,11 +17834,13 @@
       <c r="W23" s="199"/>
       <c r="X23" s="142"/>
       <c r="Y23" s="142"/>
-      <c r="Z23" s="143" t="s">
+      <c r="Z23" s="140"/>
+      <c r="AA23" s="140"/>
+      <c r="AB23" s="143" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="24" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="158" t="s">
         <v>385</v>
       </c>
@@ -17832,11 +17890,13 @@
       <c r="W24" s="199"/>
       <c r="X24" s="142"/>
       <c r="Y24" s="142"/>
-      <c r="Z24" s="143" t="s">
+      <c r="Z24" s="140"/>
+      <c r="AA24" s="140"/>
+      <c r="AB24" s="143" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="25" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="158" t="s">
         <v>386</v>
       </c>
@@ -17886,11 +17946,13 @@
       <c r="W25" s="199"/>
       <c r="X25" s="142"/>
       <c r="Y25" s="142"/>
-      <c r="Z25" s="143" t="s">
+      <c r="Z25" s="140"/>
+      <c r="AA25" s="140"/>
+      <c r="AB25" s="143" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="26" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="158" t="s">
         <v>387</v>
       </c>
@@ -17940,11 +18002,13 @@
       <c r="W26" s="199"/>
       <c r="X26" s="142"/>
       <c r="Y26" s="142"/>
-      <c r="Z26" s="143" t="s">
+      <c r="Z26" s="140"/>
+      <c r="AA26" s="140"/>
+      <c r="AB26" s="143" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="27" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="158" t="s">
         <v>388</v>
       </c>
@@ -17994,11 +18058,13 @@
       <c r="W27" s="199"/>
       <c r="X27" s="142"/>
       <c r="Y27" s="142"/>
-      <c r="Z27" s="143" t="s">
+      <c r="Z27" s="140"/>
+      <c r="AA27" s="140"/>
+      <c r="AB27" s="143" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="28" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="158" t="s">
         <v>389</v>
       </c>
@@ -18058,11 +18124,13 @@
       <c r="W28" s="199"/>
       <c r="X28" s="142"/>
       <c r="Y28" s="142"/>
-      <c r="Z28" s="143" t="s">
+      <c r="Z28" s="140"/>
+      <c r="AA28" s="140"/>
+      <c r="AB28" s="143" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="29" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="158" t="s">
         <v>390</v>
       </c>
@@ -18112,11 +18180,13 @@
       <c r="W29" s="199"/>
       <c r="X29" s="142"/>
       <c r="Y29" s="142"/>
-      <c r="Z29" s="143" t="s">
+      <c r="Z29" s="140"/>
+      <c r="AA29" s="140"/>
+      <c r="AB29" s="143" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="30" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="158" t="s">
         <v>391</v>
       </c>
@@ -18166,11 +18236,13 @@
       <c r="W30" s="199"/>
       <c r="X30" s="142"/>
       <c r="Y30" s="142"/>
-      <c r="Z30" s="143" t="s">
+      <c r="Z30" s="140"/>
+      <c r="AA30" s="140"/>
+      <c r="AB30" s="143" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="31" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="158" t="s">
         <v>392</v>
       </c>
@@ -18220,11 +18292,13 @@
       <c r="W31" s="199"/>
       <c r="X31" s="142"/>
       <c r="Y31" s="142"/>
-      <c r="Z31" s="143" t="s">
+      <c r="Z31" s="140"/>
+      <c r="AA31" s="140"/>
+      <c r="AB31" s="143" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="32" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="158" t="s">
         <v>393</v>
       </c>
@@ -18274,11 +18348,13 @@
       <c r="W32" s="199"/>
       <c r="X32" s="142"/>
       <c r="Y32" s="142"/>
-      <c r="Z32" s="143" t="s">
+      <c r="Z32" s="140"/>
+      <c r="AA32" s="140"/>
+      <c r="AB32" s="143" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="33" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="158" t="s">
         <v>394</v>
       </c>
@@ -18328,11 +18404,13 @@
       <c r="W33" s="199"/>
       <c r="X33" s="142"/>
       <c r="Y33" s="142"/>
-      <c r="Z33" s="143" t="s">
+      <c r="Z33" s="140"/>
+      <c r="AA33" s="140"/>
+      <c r="AB33" s="143" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="34" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="158" t="s">
         <v>395</v>
       </c>
@@ -18392,11 +18470,13 @@
       <c r="W34" s="199"/>
       <c r="X34" s="142"/>
       <c r="Y34" s="142"/>
-      <c r="Z34" s="143" t="s">
+      <c r="Z34" s="140"/>
+      <c r="AA34" s="140"/>
+      <c r="AB34" s="143" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="35" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="158" t="s">
         <v>397</v>
       </c>
@@ -18446,11 +18526,13 @@
       <c r="W35" s="199"/>
       <c r="X35" s="142"/>
       <c r="Y35" s="142"/>
-      <c r="Z35" s="143" t="s">
+      <c r="Z35" s="140"/>
+      <c r="AA35" s="140"/>
+      <c r="AB35" s="143" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="36" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="158" t="s">
         <v>399</v>
       </c>
@@ -18500,11 +18582,13 @@
       <c r="W36" s="199"/>
       <c r="X36" s="142"/>
       <c r="Y36" s="142"/>
-      <c r="Z36" s="143" t="s">
+      <c r="Z36" s="140"/>
+      <c r="AA36" s="140"/>
+      <c r="AB36" s="143" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="37" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="158" t="s">
         <v>400</v>
       </c>
@@ -18564,11 +18648,13 @@
       <c r="W37" s="199"/>
       <c r="X37" s="142"/>
       <c r="Y37" s="142"/>
-      <c r="Z37" s="143" t="s">
+      <c r="Z37" s="140"/>
+      <c r="AA37" s="140"/>
+      <c r="AB37" s="143" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="38" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="158" t="s">
         <v>402</v>
       </c>
@@ -18628,11 +18714,13 @@
       <c r="W38" s="199"/>
       <c r="X38" s="142"/>
       <c r="Y38" s="142"/>
-      <c r="Z38" s="143" t="s">
+      <c r="Z38" s="140"/>
+      <c r="AA38" s="140"/>
+      <c r="AB38" s="143" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="39" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="158" t="s">
         <v>403</v>
       </c>
@@ -18690,11 +18778,13 @@
       <c r="W39" s="199"/>
       <c r="X39" s="142"/>
       <c r="Y39" s="142"/>
-      <c r="Z39" s="143" t="s">
+      <c r="Z39" s="140"/>
+      <c r="AA39" s="140"/>
+      <c r="AB39" s="143" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="40" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="158" t="s">
         <v>407</v>
       </c>
@@ -18742,11 +18832,13 @@
       <c r="W40" s="199"/>
       <c r="X40" s="142"/>
       <c r="Y40" s="142"/>
-      <c r="Z40" s="143" t="s">
+      <c r="Z40" s="140"/>
+      <c r="AA40" s="140"/>
+      <c r="AB40" s="143" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="41" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="158" t="s">
         <v>410</v>
       </c>
@@ -18794,11 +18886,13 @@
       <c r="W41" s="199"/>
       <c r="X41" s="142"/>
       <c r="Y41" s="142"/>
-      <c r="Z41" s="143" t="s">
+      <c r="Z41" s="140"/>
+      <c r="AA41" s="140"/>
+      <c r="AB41" s="143" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="42" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="158" t="s">
         <v>412</v>
       </c>
@@ -18846,11 +18940,13 @@
       <c r="W42" s="199"/>
       <c r="X42" s="142"/>
       <c r="Y42" s="142"/>
-      <c r="Z42" s="143" t="s">
+      <c r="Z42" s="140"/>
+      <c r="AA42" s="140"/>
+      <c r="AB42" s="143" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="43" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="158" t="s">
         <v>415</v>
       </c>
@@ -18898,11 +18994,13 @@
       <c r="W43" s="199"/>
       <c r="X43" s="142"/>
       <c r="Y43" s="142"/>
-      <c r="Z43" s="143" t="s">
+      <c r="Z43" s="140"/>
+      <c r="AA43" s="140"/>
+      <c r="AB43" s="143" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="44" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="158" t="s">
         <v>417</v>
       </c>
@@ -18952,11 +19050,13 @@
       <c r="W44" s="199"/>
       <c r="X44" s="142"/>
       <c r="Y44" s="142"/>
-      <c r="Z44" s="143" t="s">
+      <c r="Z44" s="140"/>
+      <c r="AA44" s="140"/>
+      <c r="AB44" s="143" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="45" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="158" t="s">
         <v>420</v>
       </c>
@@ -19006,11 +19106,13 @@
       <c r="W45" s="199"/>
       <c r="X45" s="142"/>
       <c r="Y45" s="142"/>
-      <c r="Z45" s="143" t="s">
+      <c r="Z45" s="140"/>
+      <c r="AA45" s="140"/>
+      <c r="AB45" s="143" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="46" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="158" t="s">
         <v>422</v>
       </c>
@@ -19060,11 +19162,13 @@
       <c r="W46" s="199"/>
       <c r="X46" s="142"/>
       <c r="Y46" s="142"/>
-      <c r="Z46" s="143" t="s">
+      <c r="Z46" s="140"/>
+      <c r="AA46" s="140"/>
+      <c r="AB46" s="143" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="47" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="158" t="s">
         <v>424</v>
       </c>
@@ -19114,11 +19218,13 @@
       <c r="W47" s="199"/>
       <c r="X47" s="142"/>
       <c r="Y47" s="142"/>
-      <c r="Z47" s="143" t="s">
+      <c r="Z47" s="140"/>
+      <c r="AA47" s="140"/>
+      <c r="AB47" s="143" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="48" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="158" t="s">
         <v>426</v>
       </c>
@@ -19170,11 +19276,13 @@
       <c r="W48" s="199"/>
       <c r="X48" s="142"/>
       <c r="Y48" s="142"/>
-      <c r="Z48" s="143" t="s">
+      <c r="Z48" s="140"/>
+      <c r="AA48" s="140"/>
+      <c r="AB48" s="143" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="49" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="158" t="s">
         <v>430</v>
       </c>
@@ -19234,11 +19342,13 @@
       <c r="W49" s="199"/>
       <c r="X49" s="142"/>
       <c r="Y49" s="142"/>
-      <c r="Z49" s="143" t="s">
+      <c r="Z49" s="140"/>
+      <c r="AA49" s="140"/>
+      <c r="AB49" s="143" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="50" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="158" t="s">
         <v>432</v>
       </c>
@@ -19290,11 +19400,13 @@
       <c r="W50" s="199"/>
       <c r="X50" s="142"/>
       <c r="Y50" s="142"/>
-      <c r="Z50" s="143" t="s">
+      <c r="Z50" s="140"/>
+      <c r="AA50" s="140"/>
+      <c r="AB50" s="143" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="51" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="158" t="s">
         <v>434</v>
       </c>
@@ -19342,11 +19454,13 @@
       <c r="W51" s="199"/>
       <c r="X51" s="142"/>
       <c r="Y51" s="142"/>
-      <c r="Z51" s="143" t="s">
+      <c r="Z51" s="140"/>
+      <c r="AA51" s="140"/>
+      <c r="AB51" s="143" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="52" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="158" t="s">
         <v>437</v>
       </c>
@@ -19402,11 +19516,13 @@
       <c r="W52" s="199"/>
       <c r="X52" s="142"/>
       <c r="Y52" s="142"/>
-      <c r="Z52" s="143" t="s">
+      <c r="Z52" s="140"/>
+      <c r="AA52" s="140"/>
+      <c r="AB52" s="143" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="53" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="158" t="s">
         <v>440</v>
       </c>
@@ -19454,11 +19570,13 @@
       <c r="W53" s="199"/>
       <c r="X53" s="142"/>
       <c r="Y53" s="142"/>
-      <c r="Z53" s="143" t="s">
+      <c r="Z53" s="140"/>
+      <c r="AA53" s="140"/>
+      <c r="AB53" s="143" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="54" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="158" t="s">
         <v>443</v>
       </c>
@@ -19508,11 +19626,13 @@
       <c r="W54" s="199"/>
       <c r="X54" s="142"/>
       <c r="Y54" s="142"/>
-      <c r="Z54" s="143" t="s">
+      <c r="Z54" s="140"/>
+      <c r="AA54" s="140"/>
+      <c r="AB54" s="143" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="55" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="158" t="s">
         <v>445</v>
       </c>
@@ -19562,11 +19682,13 @@
       <c r="W55" s="199"/>
       <c r="X55" s="142"/>
       <c r="Y55" s="142"/>
-      <c r="Z55" s="143" t="s">
+      <c r="Z55" s="140"/>
+      <c r="AA55" s="140"/>
+      <c r="AB55" s="143" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="56" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="158" t="s">
         <v>447</v>
       </c>
@@ -19618,11 +19740,13 @@
       <c r="W56" s="199"/>
       <c r="X56" s="142"/>
       <c r="Y56" s="142"/>
-      <c r="Z56" s="143" t="s">
+      <c r="Z56" s="140"/>
+      <c r="AA56" s="140"/>
+      <c r="AB56" s="143" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="57" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="158" t="s">
         <v>450</v>
       </c>
@@ -19674,11 +19798,13 @@
       <c r="W57" s="199"/>
       <c r="X57" s="142"/>
       <c r="Y57" s="142"/>
-      <c r="Z57" s="143" t="s">
+      <c r="Z57" s="140"/>
+      <c r="AA57" s="140"/>
+      <c r="AB57" s="143" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="58" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="158" t="s">
         <v>452</v>
       </c>
@@ -19730,11 +19856,13 @@
       <c r="W58" s="199"/>
       <c r="X58" s="142"/>
       <c r="Y58" s="142"/>
-      <c r="Z58" s="143" t="s">
+      <c r="Z58" s="140"/>
+      <c r="AA58" s="140"/>
+      <c r="AB58" s="143" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="59" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C59" s="158" t="s">
         <v>455</v>
       </c>
@@ -19786,11 +19914,13 @@
       <c r="W59" s="199"/>
       <c r="X59" s="142"/>
       <c r="Y59" s="142"/>
-      <c r="Z59" s="143" t="s">
+      <c r="Z59" s="140"/>
+      <c r="AA59" s="140"/>
+      <c r="AB59" s="143" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="60" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="158" t="s">
         <v>458</v>
       </c>
@@ -19846,11 +19976,13 @@
       <c r="Y60" s="142">
         <v>0.06</v>
       </c>
-      <c r="Z60" s="143" t="s">
+      <c r="Z60" s="140"/>
+      <c r="AA60" s="140"/>
+      <c r="AB60" s="143" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="61" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="158" t="s">
         <v>461</v>
       </c>
@@ -19900,11 +20032,13 @@
       <c r="W61" s="199"/>
       <c r="X61" s="142"/>
       <c r="Y61" s="142"/>
-      <c r="Z61" s="143" t="s">
+      <c r="Z61" s="140"/>
+      <c r="AA61" s="140"/>
+      <c r="AB61" s="143" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="62" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="158" t="s">
         <v>464</v>
       </c>
@@ -19962,11 +20096,13 @@
       <c r="W62" s="199"/>
       <c r="X62" s="142"/>
       <c r="Y62" s="142"/>
-      <c r="Z62" s="143" t="s">
+      <c r="Z62" s="140"/>
+      <c r="AA62" s="140"/>
+      <c r="AB62" s="143" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="63" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="158" t="s">
         <v>467</v>
       </c>
@@ -20016,11 +20152,13 @@
       <c r="W63" s="199"/>
       <c r="X63" s="142"/>
       <c r="Y63" s="142"/>
-      <c r="Z63" s="143" t="s">
+      <c r="Z63" s="140"/>
+      <c r="AA63" s="140"/>
+      <c r="AB63" s="143" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="64" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="158" t="s">
         <v>470</v>
       </c>
@@ -20072,11 +20210,13 @@
       <c r="W64" s="199"/>
       <c r="X64" s="142"/>
       <c r="Y64" s="142"/>
-      <c r="Z64" s="143" t="s">
+      <c r="Z64" s="140"/>
+      <c r="AA64" s="140"/>
+      <c r="AB64" s="143" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="65" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="158" t="s">
         <v>474</v>
       </c>
@@ -20126,11 +20266,13 @@
       <c r="W65" s="199"/>
       <c r="X65" s="142"/>
       <c r="Y65" s="142"/>
-      <c r="Z65" s="143" t="s">
+      <c r="Z65" s="140"/>
+      <c r="AA65" s="140"/>
+      <c r="AB65" s="143" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="66" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="158" t="s">
         <v>477</v>
       </c>
@@ -20180,11 +20322,13 @@
       <c r="W66" s="199"/>
       <c r="X66" s="142"/>
       <c r="Y66" s="142"/>
-      <c r="Z66" s="143" t="s">
+      <c r="Z66" s="140"/>
+      <c r="AA66" s="140"/>
+      <c r="AB66" s="143" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="67" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="158" t="s">
         <v>479</v>
       </c>
@@ -20234,11 +20378,13 @@
       <c r="W67" s="199"/>
       <c r="X67" s="142"/>
       <c r="Y67" s="142"/>
-      <c r="Z67" s="143" t="s">
+      <c r="Z67" s="140"/>
+      <c r="AA67" s="140"/>
+      <c r="AB67" s="143" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="68" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="158" t="s">
         <v>482</v>
       </c>
@@ -20288,11 +20434,13 @@
       <c r="W68" s="199"/>
       <c r="X68" s="142"/>
       <c r="Y68" s="142"/>
-      <c r="Z68" s="143" t="s">
+      <c r="Z68" s="140"/>
+      <c r="AA68" s="140"/>
+      <c r="AB68" s="143" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="69" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="158" t="s">
         <v>485</v>
       </c>
@@ -20342,11 +20490,13 @@
       <c r="W69" s="199"/>
       <c r="X69" s="142"/>
       <c r="Y69" s="142"/>
-      <c r="Z69" s="143" t="s">
+      <c r="Z69" s="140"/>
+      <c r="AA69" s="140"/>
+      <c r="AB69" s="143" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="70" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="158"/>
       <c r="D70" s="158"/>
       <c r="E70" s="140"/>
@@ -20370,9 +20520,11 @@
       <c r="W70" s="199"/>
       <c r="X70" s="142"/>
       <c r="Y70" s="142"/>
-      <c r="Z70" s="143"/>
-    </row>
-    <row r="71" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z70" s="140"/>
+      <c r="AA70" s="140"/>
+      <c r="AB70" s="143"/>
+    </row>
+    <row r="71" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="158"/>
       <c r="D71" s="158"/>
       <c r="E71" s="140"/>
@@ -20396,9 +20548,11 @@
       <c r="W71" s="199"/>
       <c r="X71" s="142"/>
       <c r="Y71" s="142"/>
-      <c r="Z71" s="143"/>
-    </row>
-    <row r="72" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z71" s="140"/>
+      <c r="AA71" s="140"/>
+      <c r="AB71" s="143"/>
+    </row>
+    <row r="72" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="158"/>
       <c r="D72" s="158"/>
       <c r="E72" s="140"/>
@@ -20422,9 +20576,11 @@
       <c r="W72" s="199"/>
       <c r="X72" s="142"/>
       <c r="Y72" s="142"/>
-      <c r="Z72" s="143"/>
-    </row>
-    <row r="73" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z72" s="140"/>
+      <c r="AA72" s="140"/>
+      <c r="AB72" s="143"/>
+    </row>
+    <row r="73" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="158"/>
       <c r="D73" s="158"/>
       <c r="E73" s="140"/>
@@ -20448,9 +20604,11 @@
       <c r="W73" s="199"/>
       <c r="X73" s="142"/>
       <c r="Y73" s="142"/>
-      <c r="Z73" s="143"/>
-    </row>
-    <row r="74" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z73" s="140"/>
+      <c r="AA73" s="140"/>
+      <c r="AB73" s="143"/>
+    </row>
+    <row r="74" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="158"/>
       <c r="D74" s="158"/>
       <c r="E74" s="140"/>
@@ -20474,9 +20632,11 @@
       <c r="W74" s="199"/>
       <c r="X74" s="142"/>
       <c r="Y74" s="142"/>
-      <c r="Z74" s="143"/>
-    </row>
-    <row r="75" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z74" s="140"/>
+      <c r="AA74" s="140"/>
+      <c r="AB74" s="143"/>
+    </row>
+    <row r="75" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="158"/>
       <c r="D75" s="158"/>
       <c r="E75" s="140"/>
@@ -20500,9 +20660,11 @@
       <c r="W75" s="199"/>
       <c r="X75" s="142"/>
       <c r="Y75" s="142"/>
-      <c r="Z75" s="143"/>
-    </row>
-    <row r="76" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z75" s="140"/>
+      <c r="AA75" s="140"/>
+      <c r="AB75" s="143"/>
+    </row>
+    <row r="76" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C76" s="158"/>
       <c r="D76" s="158"/>
       <c r="E76" s="140"/>
@@ -20526,9 +20688,11 @@
       <c r="W76" s="199"/>
       <c r="X76" s="142"/>
       <c r="Y76" s="142"/>
-      <c r="Z76" s="143"/>
-    </row>
-    <row r="77" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z76" s="140"/>
+      <c r="AA76" s="140"/>
+      <c r="AB76" s="143"/>
+    </row>
+    <row r="77" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C77" s="158"/>
       <c r="D77" s="158"/>
       <c r="E77" s="140"/>
@@ -20552,9 +20716,11 @@
       <c r="W77" s="199"/>
       <c r="X77" s="142"/>
       <c r="Y77" s="142"/>
-      <c r="Z77" s="143"/>
-    </row>
-    <row r="78" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z77" s="140"/>
+      <c r="AA77" s="140"/>
+      <c r="AB77" s="143"/>
+    </row>
+    <row r="78" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="158"/>
       <c r="D78" s="158"/>
       <c r="E78" s="140"/>
@@ -20578,9 +20744,11 @@
       <c r="W78" s="199"/>
       <c r="X78" s="142"/>
       <c r="Y78" s="142"/>
-      <c r="Z78" s="143"/>
-    </row>
-    <row r="79" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z78" s="140"/>
+      <c r="AA78" s="140"/>
+      <c r="AB78" s="143"/>
+    </row>
+    <row r="79" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C79" s="158"/>
       <c r="D79" s="158"/>
       <c r="E79" s="140"/>
@@ -20604,9 +20772,11 @@
       <c r="W79" s="199"/>
       <c r="X79" s="142"/>
       <c r="Y79" s="142"/>
-      <c r="Z79" s="143"/>
-    </row>
-    <row r="80" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z79" s="140"/>
+      <c r="AA79" s="140"/>
+      <c r="AB79" s="143"/>
+    </row>
+    <row r="80" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C80" s="158"/>
       <c r="D80" s="158"/>
       <c r="E80" s="140"/>
@@ -20630,9 +20800,11 @@
       <c r="W80" s="199"/>
       <c r="X80" s="142"/>
       <c r="Y80" s="142"/>
-      <c r="Z80" s="143"/>
-    </row>
-    <row r="81" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z80" s="140"/>
+      <c r="AA80" s="140"/>
+      <c r="AB80" s="143"/>
+    </row>
+    <row r="81" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C81" s="158"/>
       <c r="D81" s="158"/>
       <c r="E81" s="140"/>
@@ -20656,9 +20828,11 @@
       <c r="W81" s="199"/>
       <c r="X81" s="142"/>
       <c r="Y81" s="142"/>
-      <c r="Z81" s="143"/>
-    </row>
-    <row r="82" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z81" s="140"/>
+      <c r="AA81" s="140"/>
+      <c r="AB81" s="143"/>
+    </row>
+    <row r="82" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C82" s="158"/>
       <c r="D82" s="158"/>
       <c r="E82" s="140"/>
@@ -20682,9 +20856,11 @@
       <c r="W82" s="199"/>
       <c r="X82" s="142"/>
       <c r="Y82" s="142"/>
-      <c r="Z82" s="143"/>
-    </row>
-    <row r="83" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z82" s="140"/>
+      <c r="AA82" s="140"/>
+      <c r="AB82" s="143"/>
+    </row>
+    <row r="83" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C83" s="158"/>
       <c r="D83" s="158"/>
       <c r="E83" s="140"/>
@@ -20708,9 +20884,11 @@
       <c r="W83" s="199"/>
       <c r="X83" s="142"/>
       <c r="Y83" s="142"/>
-      <c r="Z83" s="143"/>
-    </row>
-    <row r="84" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z83" s="140"/>
+      <c r="AA83" s="140"/>
+      <c r="AB83" s="143"/>
+    </row>
+    <row r="84" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C84" s="158"/>
       <c r="D84" s="158"/>
       <c r="E84" s="140"/>
@@ -20734,9 +20912,11 @@
       <c r="W84" s="199"/>
       <c r="X84" s="142"/>
       <c r="Y84" s="142"/>
-      <c r="Z84" s="143"/>
-    </row>
-    <row r="85" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z84" s="140"/>
+      <c r="AA84" s="140"/>
+      <c r="AB84" s="143"/>
+    </row>
+    <row r="85" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C85" s="158"/>
       <c r="D85" s="158"/>
       <c r="E85" s="140"/>
@@ -20760,9 +20940,11 @@
       <c r="W85" s="199"/>
       <c r="X85" s="142"/>
       <c r="Y85" s="142"/>
-      <c r="Z85" s="143"/>
-    </row>
-    <row r="86" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z85" s="140"/>
+      <c r="AA85" s="140"/>
+      <c r="AB85" s="143"/>
+    </row>
+    <row r="86" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C86" s="158"/>
       <c r="D86" s="158"/>
       <c r="E86" s="140"/>
@@ -20786,9 +20968,11 @@
       <c r="W86" s="199"/>
       <c r="X86" s="142"/>
       <c r="Y86" s="142"/>
-      <c r="Z86" s="143"/>
-    </row>
-    <row r="87" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z86" s="140"/>
+      <c r="AA86" s="140"/>
+      <c r="AB86" s="143"/>
+    </row>
+    <row r="87" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C87" s="158"/>
       <c r="D87" s="158"/>
       <c r="E87" s="140"/>
@@ -20812,9 +20996,11 @@
       <c r="W87" s="199"/>
       <c r="X87" s="142"/>
       <c r="Y87" s="142"/>
-      <c r="Z87" s="143"/>
-    </row>
-    <row r="88" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z87" s="140"/>
+      <c r="AA87" s="140"/>
+      <c r="AB87" s="143"/>
+    </row>
+    <row r="88" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C88" s="158"/>
       <c r="D88" s="158"/>
       <c r="E88" s="140"/>
@@ -20838,9 +21024,11 @@
       <c r="W88" s="199"/>
       <c r="X88" s="142"/>
       <c r="Y88" s="142"/>
-      <c r="Z88" s="143"/>
-    </row>
-    <row r="89" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z88" s="140"/>
+      <c r="AA88" s="140"/>
+      <c r="AB88" s="143"/>
+    </row>
+    <row r="89" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C89" s="158"/>
       <c r="D89" s="158"/>
       <c r="E89" s="140"/>
@@ -20864,9 +21052,11 @@
       <c r="W89" s="199"/>
       <c r="X89" s="142"/>
       <c r="Y89" s="142"/>
-      <c r="Z89" s="143"/>
-    </row>
-    <row r="90" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z89" s="140"/>
+      <c r="AA89" s="140"/>
+      <c r="AB89" s="143"/>
+    </row>
+    <row r="90" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="158"/>
       <c r="D90" s="158"/>
       <c r="E90" s="140"/>
@@ -20890,9 +21080,11 @@
       <c r="W90" s="199"/>
       <c r="X90" s="142"/>
       <c r="Y90" s="142"/>
-      <c r="Z90" s="143"/>
-    </row>
-    <row r="91" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z90" s="140"/>
+      <c r="AA90" s="140"/>
+      <c r="AB90" s="143"/>
+    </row>
+    <row r="91" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C91" s="158"/>
       <c r="D91" s="158"/>
       <c r="E91" s="140"/>
@@ -20916,9 +21108,11 @@
       <c r="W91" s="199"/>
       <c r="X91" s="142"/>
       <c r="Y91" s="142"/>
-      <c r="Z91" s="143"/>
-    </row>
-    <row r="92" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z91" s="140"/>
+      <c r="AA91" s="140"/>
+      <c r="AB91" s="143"/>
+    </row>
+    <row r="92" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C92" s="158"/>
       <c r="D92" s="158"/>
       <c r="E92" s="140"/>
@@ -20942,9 +21136,11 @@
       <c r="W92" s="199"/>
       <c r="X92" s="142"/>
       <c r="Y92" s="142"/>
-      <c r="Z92" s="143"/>
-    </row>
-    <row r="93" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z92" s="140"/>
+      <c r="AA92" s="140"/>
+      <c r="AB92" s="143"/>
+    </row>
+    <row r="93" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="158"/>
       <c r="D93" s="158"/>
       <c r="E93" s="140"/>
@@ -20968,9 +21164,11 @@
       <c r="W93" s="199"/>
       <c r="X93" s="142"/>
       <c r="Y93" s="142"/>
-      <c r="Z93" s="143"/>
-    </row>
-    <row r="94" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z93" s="140"/>
+      <c r="AA93" s="140"/>
+      <c r="AB93" s="143"/>
+    </row>
+    <row r="94" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C94" s="158"/>
       <c r="D94" s="158"/>
       <c r="E94" s="140"/>
@@ -20994,9 +21192,11 @@
       <c r="W94" s="199"/>
       <c r="X94" s="142"/>
       <c r="Y94" s="142"/>
-      <c r="Z94" s="143"/>
-    </row>
-    <row r="95" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z94" s="140"/>
+      <c r="AA94" s="140"/>
+      <c r="AB94" s="143"/>
+    </row>
+    <row r="95" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C95" s="158"/>
       <c r="D95" s="158"/>
       <c r="E95" s="140"/>
@@ -21020,9 +21220,11 @@
       <c r="W95" s="199"/>
       <c r="X95" s="142"/>
       <c r="Y95" s="142"/>
-      <c r="Z95" s="143"/>
-    </row>
-    <row r="96" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z95" s="140"/>
+      <c r="AA95" s="140"/>
+      <c r="AB95" s="143"/>
+    </row>
+    <row r="96" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C96" s="158"/>
       <c r="D96" s="158"/>
       <c r="E96" s="140"/>
@@ -21046,9 +21248,11 @@
       <c r="W96" s="199"/>
       <c r="X96" s="142"/>
       <c r="Y96" s="142"/>
-      <c r="Z96" s="143"/>
-    </row>
-    <row r="97" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z96" s="140"/>
+      <c r="AA96" s="140"/>
+      <c r="AB96" s="143"/>
+    </row>
+    <row r="97" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C97" s="158"/>
       <c r="D97" s="158"/>
       <c r="E97" s="140"/>
@@ -21072,9 +21276,11 @@
       <c r="W97" s="199"/>
       <c r="X97" s="142"/>
       <c r="Y97" s="142"/>
-      <c r="Z97" s="143"/>
-    </row>
-    <row r="98" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z97" s="140"/>
+      <c r="AA97" s="140"/>
+      <c r="AB97" s="143"/>
+    </row>
+    <row r="98" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C98" s="158"/>
       <c r="D98" s="158"/>
       <c r="E98" s="140"/>
@@ -21098,9 +21304,11 @@
       <c r="W98" s="199"/>
       <c r="X98" s="142"/>
       <c r="Y98" s="142"/>
-      <c r="Z98" s="143"/>
-    </row>
-    <row r="99" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z98" s="140"/>
+      <c r="AA98" s="140"/>
+      <c r="AB98" s="143"/>
+    </row>
+    <row r="99" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C99" s="158"/>
       <c r="D99" s="158"/>
       <c r="E99" s="140"/>
@@ -21124,9 +21332,11 @@
       <c r="W99" s="199"/>
       <c r="X99" s="142"/>
       <c r="Y99" s="142"/>
-      <c r="Z99" s="143"/>
-    </row>
-    <row r="100" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z99" s="140"/>
+      <c r="AA99" s="140"/>
+      <c r="AB99" s="143"/>
+    </row>
+    <row r="100" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C100" s="158"/>
       <c r="D100" s="158"/>
       <c r="E100" s="140"/>
@@ -21150,9 +21360,11 @@
       <c r="W100" s="199"/>
       <c r="X100" s="142"/>
       <c r="Y100" s="142"/>
-      <c r="Z100" s="143"/>
-    </row>
-    <row r="101" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z100" s="140"/>
+      <c r="AA100" s="140"/>
+      <c r="AB100" s="143"/>
+    </row>
+    <row r="101" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C101" s="158"/>
       <c r="D101" s="158"/>
       <c r="E101" s="140"/>
@@ -21176,9 +21388,11 @@
       <c r="W101" s="199"/>
       <c r="X101" s="142"/>
       <c r="Y101" s="142"/>
-      <c r="Z101" s="143"/>
-    </row>
-    <row r="102" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z101" s="140"/>
+      <c r="AA101" s="140"/>
+      <c r="AB101" s="143"/>
+    </row>
+    <row r="102" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C102" s="158"/>
       <c r="D102" s="158"/>
       <c r="E102" s="140"/>
@@ -21202,9 +21416,11 @@
       <c r="W102" s="199"/>
       <c r="X102" s="142"/>
       <c r="Y102" s="142"/>
-      <c r="Z102" s="143"/>
-    </row>
-    <row r="103" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z102" s="140"/>
+      <c r="AA102" s="140"/>
+      <c r="AB102" s="143"/>
+    </row>
+    <row r="103" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C103" s="158"/>
       <c r="D103" s="158"/>
       <c r="E103" s="140"/>
@@ -21228,9 +21444,11 @@
       <c r="W103" s="199"/>
       <c r="X103" s="142"/>
       <c r="Y103" s="142"/>
-      <c r="Z103" s="143"/>
-    </row>
-    <row r="104" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z103" s="140"/>
+      <c r="AA103" s="140"/>
+      <c r="AB103" s="143"/>
+    </row>
+    <row r="104" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C104" s="158"/>
       <c r="D104" s="158"/>
       <c r="E104" s="140"/>
@@ -21254,9 +21472,11 @@
       <c r="W104" s="199"/>
       <c r="X104" s="142"/>
       <c r="Y104" s="142"/>
-      <c r="Z104" s="143"/>
-    </row>
-    <row r="105" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z104" s="140"/>
+      <c r="AA104" s="140"/>
+      <c r="AB104" s="143"/>
+    </row>
+    <row r="105" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C105" s="158"/>
       <c r="D105" s="158"/>
       <c r="E105" s="140"/>
@@ -21280,9 +21500,11 @@
       <c r="W105" s="199"/>
       <c r="X105" s="142"/>
       <c r="Y105" s="142"/>
-      <c r="Z105" s="143"/>
-    </row>
-    <row r="106" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z105" s="140"/>
+      <c r="AA105" s="140"/>
+      <c r="AB105" s="143"/>
+    </row>
+    <row r="106" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C106" s="158"/>
       <c r="D106" s="158"/>
       <c r="E106" s="140"/>
@@ -21306,9 +21528,11 @@
       <c r="W106" s="199"/>
       <c r="X106" s="142"/>
       <c r="Y106" s="142"/>
-      <c r="Z106" s="143"/>
-    </row>
-    <row r="107" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z106" s="140"/>
+      <c r="AA106" s="140"/>
+      <c r="AB106" s="143"/>
+    </row>
+    <row r="107" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C107" s="158"/>
       <c r="D107" s="158"/>
       <c r="E107" s="140"/>
@@ -21332,9 +21556,11 @@
       <c r="W107" s="199"/>
       <c r="X107" s="142"/>
       <c r="Y107" s="142"/>
-      <c r="Z107" s="143"/>
-    </row>
-    <row r="108" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z107" s="140"/>
+      <c r="AA107" s="140"/>
+      <c r="AB107" s="143"/>
+    </row>
+    <row r="108" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C108" s="158"/>
       <c r="D108" s="158"/>
       <c r="E108" s="140"/>
@@ -21358,9 +21584,11 @@
       <c r="W108" s="199"/>
       <c r="X108" s="142"/>
       <c r="Y108" s="142"/>
-      <c r="Z108" s="143"/>
-    </row>
-    <row r="109" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z108" s="140"/>
+      <c r="AA108" s="140"/>
+      <c r="AB108" s="143"/>
+    </row>
+    <row r="109" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C109" s="158"/>
       <c r="D109" s="158"/>
       <c r="E109" s="140"/>
@@ -21384,9 +21612,11 @@
       <c r="W109" s="199"/>
       <c r="X109" s="142"/>
       <c r="Y109" s="142"/>
-      <c r="Z109" s="143"/>
-    </row>
-    <row r="110" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z109" s="140"/>
+      <c r="AA109" s="140"/>
+      <c r="AB109" s="143"/>
+    </row>
+    <row r="110" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C110" s="158"/>
       <c r="D110" s="158"/>
       <c r="E110" s="140"/>
@@ -21410,9 +21640,11 @@
       <c r="W110" s="199"/>
       <c r="X110" s="142"/>
       <c r="Y110" s="142"/>
-      <c r="Z110" s="143"/>
-    </row>
-    <row r="111" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z110" s="140"/>
+      <c r="AA110" s="140"/>
+      <c r="AB110" s="143"/>
+    </row>
+    <row r="111" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C111" s="158"/>
       <c r="D111" s="158"/>
       <c r="E111" s="140"/>
@@ -21436,9 +21668,11 @@
       <c r="W111" s="199"/>
       <c r="X111" s="142"/>
       <c r="Y111" s="142"/>
-      <c r="Z111" s="143"/>
-    </row>
-    <row r="112" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z111" s="140"/>
+      <c r="AA111" s="140"/>
+      <c r="AB111" s="143"/>
+    </row>
+    <row r="112" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C112" s="158"/>
       <c r="D112" s="158"/>
       <c r="E112" s="140"/>
@@ -21462,9 +21696,11 @@
       <c r="W112" s="199"/>
       <c r="X112" s="142"/>
       <c r="Y112" s="142"/>
-      <c r="Z112" s="143"/>
-    </row>
-    <row r="113" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z112" s="140"/>
+      <c r="AA112" s="140"/>
+      <c r="AB112" s="143"/>
+    </row>
+    <row r="113" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C113" s="158"/>
       <c r="D113" s="158"/>
       <c r="E113" s="140"/>
@@ -21488,9 +21724,11 @@
       <c r="W113" s="199"/>
       <c r="X113" s="142"/>
       <c r="Y113" s="142"/>
-      <c r="Z113" s="143"/>
-    </row>
-    <row r="114" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z113" s="140"/>
+      <c r="AA113" s="140"/>
+      <c r="AB113" s="143"/>
+    </row>
+    <row r="114" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C114" s="158"/>
       <c r="D114" s="158"/>
       <c r="E114" s="140"/>
@@ -21514,9 +21752,11 @@
       <c r="W114" s="199"/>
       <c r="X114" s="142"/>
       <c r="Y114" s="142"/>
-      <c r="Z114" s="143"/>
-    </row>
-    <row r="115" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z114" s="140"/>
+      <c r="AA114" s="140"/>
+      <c r="AB114" s="143"/>
+    </row>
+    <row r="115" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C115" s="158"/>
       <c r="D115" s="158"/>
       <c r="E115" s="140"/>
@@ -21540,9 +21780,11 @@
       <c r="W115" s="199"/>
       <c r="X115" s="142"/>
       <c r="Y115" s="142"/>
-      <c r="Z115" s="143"/>
-    </row>
-    <row r="116" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z115" s="140"/>
+      <c r="AA115" s="140"/>
+      <c r="AB115" s="143"/>
+    </row>
+    <row r="116" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C116" s="158"/>
       <c r="D116" s="158"/>
       <c r="E116" s="140"/>
@@ -21566,9 +21808,11 @@
       <c r="W116" s="199"/>
       <c r="X116" s="142"/>
       <c r="Y116" s="142"/>
-      <c r="Z116" s="143"/>
-    </row>
-    <row r="117" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z116" s="140"/>
+      <c r="AA116" s="140"/>
+      <c r="AB116" s="143"/>
+    </row>
+    <row r="117" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C117" s="158"/>
       <c r="D117" s="158"/>
       <c r="E117" s="140"/>
@@ -21592,9 +21836,11 @@
       <c r="W117" s="199"/>
       <c r="X117" s="142"/>
       <c r="Y117" s="142"/>
-      <c r="Z117" s="143"/>
-    </row>
-    <row r="118" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z117" s="140"/>
+      <c r="AA117" s="140"/>
+      <c r="AB117" s="143"/>
+    </row>
+    <row r="118" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C118" s="158"/>
       <c r="D118" s="158"/>
       <c r="E118" s="140"/>
@@ -21618,9 +21864,11 @@
       <c r="W118" s="199"/>
       <c r="X118" s="142"/>
       <c r="Y118" s="142"/>
-      <c r="Z118" s="143"/>
-    </row>
-    <row r="119" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z118" s="140"/>
+      <c r="AA118" s="140"/>
+      <c r="AB118" s="143"/>
+    </row>
+    <row r="119" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C119" s="158"/>
       <c r="D119" s="158"/>
       <c r="E119" s="140"/>
@@ -21644,9 +21892,11 @@
       <c r="W119" s="199"/>
       <c r="X119" s="142"/>
       <c r="Y119" s="142"/>
-      <c r="Z119" s="143"/>
-    </row>
-    <row r="120" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z119" s="140"/>
+      <c r="AA119" s="140"/>
+      <c r="AB119" s="143"/>
+    </row>
+    <row r="120" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C120" s="158"/>
       <c r="D120" s="158"/>
       <c r="E120" s="140"/>
@@ -21670,9 +21920,11 @@
       <c r="W120" s="199"/>
       <c r="X120" s="142"/>
       <c r="Y120" s="142"/>
-      <c r="Z120" s="143"/>
-    </row>
-    <row r="121" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z120" s="140"/>
+      <c r="AA120" s="140"/>
+      <c r="AB120" s="143"/>
+    </row>
+    <row r="121" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C121" s="158"/>
       <c r="D121" s="158"/>
       <c r="E121" s="140"/>
@@ -21696,9 +21948,11 @@
       <c r="W121" s="199"/>
       <c r="X121" s="142"/>
       <c r="Y121" s="142"/>
-      <c r="Z121" s="143"/>
-    </row>
-    <row r="122" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z121" s="140"/>
+      <c r="AA121" s="140"/>
+      <c r="AB121" s="143"/>
+    </row>
+    <row r="122" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C122" s="158"/>
       <c r="D122" s="158"/>
       <c r="E122" s="140"/>
@@ -21722,9 +21976,11 @@
       <c r="W122" s="199"/>
       <c r="X122" s="142"/>
       <c r="Y122" s="142"/>
-      <c r="Z122" s="143"/>
-    </row>
-    <row r="123" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z122" s="140"/>
+      <c r="AA122" s="140"/>
+      <c r="AB122" s="143"/>
+    </row>
+    <row r="123" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C123" s="158"/>
       <c r="D123" s="158"/>
       <c r="E123" s="140"/>
@@ -21748,9 +22004,11 @@
       <c r="W123" s="199"/>
       <c r="X123" s="142"/>
       <c r="Y123" s="142"/>
-      <c r="Z123" s="143"/>
-    </row>
-    <row r="124" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z123" s="140"/>
+      <c r="AA123" s="140"/>
+      <c r="AB123" s="143"/>
+    </row>
+    <row r="124" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C124" s="158"/>
       <c r="D124" s="158"/>
       <c r="E124" s="140"/>
@@ -21774,9 +22032,11 @@
       <c r="W124" s="199"/>
       <c r="X124" s="142"/>
       <c r="Y124" s="142"/>
-      <c r="Z124" s="143"/>
-    </row>
-    <row r="125" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z124" s="140"/>
+      <c r="AA124" s="140"/>
+      <c r="AB124" s="143"/>
+    </row>
+    <row r="125" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C125" s="158"/>
       <c r="D125" s="158"/>
       <c r="E125" s="140"/>
@@ -21800,9 +22060,11 @@
       <c r="W125" s="199"/>
       <c r="X125" s="142"/>
       <c r="Y125" s="142"/>
-      <c r="Z125" s="143"/>
-    </row>
-    <row r="126" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z125" s="140"/>
+      <c r="AA125" s="140"/>
+      <c r="AB125" s="143"/>
+    </row>
+    <row r="126" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C126" s="158"/>
       <c r="D126" s="158"/>
       <c r="E126" s="140"/>
@@ -21826,9 +22088,11 @@
       <c r="W126" s="199"/>
       <c r="X126" s="142"/>
       <c r="Y126" s="142"/>
-      <c r="Z126" s="143"/>
-    </row>
-    <row r="127" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z126" s="140"/>
+      <c r="AA126" s="140"/>
+      <c r="AB126" s="143"/>
+    </row>
+    <row r="127" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C127" s="158"/>
       <c r="D127" s="158"/>
       <c r="E127" s="140"/>
@@ -21852,9 +22116,11 @@
       <c r="W127" s="199"/>
       <c r="X127" s="142"/>
       <c r="Y127" s="142"/>
-      <c r="Z127" s="143"/>
-    </row>
-    <row r="128" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z127" s="140"/>
+      <c r="AA127" s="140"/>
+      <c r="AB127" s="143"/>
+    </row>
+    <row r="128" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C128" s="158"/>
       <c r="D128" s="158"/>
       <c r="E128" s="140"/>
@@ -21878,9 +22144,11 @@
       <c r="W128" s="199"/>
       <c r="X128" s="142"/>
       <c r="Y128" s="142"/>
-      <c r="Z128" s="143"/>
-    </row>
-    <row r="129" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z128" s="140"/>
+      <c r="AA128" s="140"/>
+      <c r="AB128" s="143"/>
+    </row>
+    <row r="129" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C129" s="158"/>
       <c r="D129" s="158"/>
       <c r="E129" s="140"/>
@@ -21904,9 +22172,11 @@
       <c r="W129" s="199"/>
       <c r="X129" s="142"/>
       <c r="Y129" s="142"/>
-      <c r="Z129" s="143"/>
-    </row>
-    <row r="130" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z129" s="140"/>
+      <c r="AA129" s="140"/>
+      <c r="AB129" s="143"/>
+    </row>
+    <row r="130" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C130" s="158"/>
       <c r="D130" s="158"/>
       <c r="E130" s="140"/>
@@ -21930,9 +22200,11 @@
       <c r="W130" s="199"/>
       <c r="X130" s="142"/>
       <c r="Y130" s="142"/>
-      <c r="Z130" s="143"/>
-    </row>
-    <row r="131" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z130" s="140"/>
+      <c r="AA130" s="140"/>
+      <c r="AB130" s="143"/>
+    </row>
+    <row r="131" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C131" s="158"/>
       <c r="D131" s="158"/>
       <c r="E131" s="140"/>
@@ -21956,9 +22228,11 @@
       <c r="W131" s="199"/>
       <c r="X131" s="142"/>
       <c r="Y131" s="142"/>
-      <c r="Z131" s="143"/>
-    </row>
-    <row r="132" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z131" s="140"/>
+      <c r="AA131" s="140"/>
+      <c r="AB131" s="143"/>
+    </row>
+    <row r="132" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C132" s="158"/>
       <c r="D132" s="158"/>
       <c r="E132" s="140"/>
@@ -21982,9 +22256,11 @@
       <c r="W132" s="199"/>
       <c r="X132" s="142"/>
       <c r="Y132" s="142"/>
-      <c r="Z132" s="143"/>
-    </row>
-    <row r="133" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z132" s="140"/>
+      <c r="AA132" s="140"/>
+      <c r="AB132" s="143"/>
+    </row>
+    <row r="133" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C133" s="158"/>
       <c r="D133" s="158"/>
       <c r="E133" s="140"/>
@@ -22008,9 +22284,11 @@
       <c r="W133" s="199"/>
       <c r="X133" s="142"/>
       <c r="Y133" s="142"/>
-      <c r="Z133" s="143"/>
-    </row>
-    <row r="134" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z133" s="140"/>
+      <c r="AA133" s="140"/>
+      <c r="AB133" s="143"/>
+    </row>
+    <row r="134" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C134" s="158"/>
       <c r="D134" s="158"/>
       <c r="E134" s="140"/>
@@ -22034,9 +22312,11 @@
       <c r="W134" s="199"/>
       <c r="X134" s="142"/>
       <c r="Y134" s="142"/>
-      <c r="Z134" s="143"/>
-    </row>
-    <row r="135" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z134" s="140"/>
+      <c r="AA134" s="140"/>
+      <c r="AB134" s="143"/>
+    </row>
+    <row r="135" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C135" s="158"/>
       <c r="D135" s="158"/>
       <c r="E135" s="140"/>
@@ -22060,9 +22340,11 @@
       <c r="W135" s="199"/>
       <c r="X135" s="142"/>
       <c r="Y135" s="142"/>
-      <c r="Z135" s="143"/>
-    </row>
-    <row r="136" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z135" s="140"/>
+      <c r="AA135" s="140"/>
+      <c r="AB135" s="143"/>
+    </row>
+    <row r="136" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C136" s="158"/>
       <c r="D136" s="158"/>
       <c r="E136" s="140"/>
@@ -22086,9 +22368,11 @@
       <c r="W136" s="199"/>
       <c r="X136" s="142"/>
       <c r="Y136" s="142"/>
-      <c r="Z136" s="143"/>
-    </row>
-    <row r="137" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z136" s="140"/>
+      <c r="AA136" s="140"/>
+      <c r="AB136" s="143"/>
+    </row>
+    <row r="137" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="158"/>
       <c r="D137" s="158"/>
       <c r="E137" s="140"/>
@@ -22112,9 +22396,11 @@
       <c r="W137" s="199"/>
       <c r="X137" s="142"/>
       <c r="Y137" s="142"/>
-      <c r="Z137" s="143"/>
-    </row>
-    <row r="138" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z137" s="140"/>
+      <c r="AA137" s="140"/>
+      <c r="AB137" s="143"/>
+    </row>
+    <row r="138" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C138" s="158"/>
       <c r="D138" s="158"/>
       <c r="E138" s="140"/>
@@ -22138,9 +22424,11 @@
       <c r="W138" s="199"/>
       <c r="X138" s="142"/>
       <c r="Y138" s="142"/>
-      <c r="Z138" s="143"/>
-    </row>
-    <row r="139" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z138" s="140"/>
+      <c r="AA138" s="140"/>
+      <c r="AB138" s="143"/>
+    </row>
+    <row r="139" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C139" s="158"/>
       <c r="D139" s="158"/>
       <c r="E139" s="140"/>
@@ -22164,9 +22452,11 @@
       <c r="W139" s="199"/>
       <c r="X139" s="142"/>
       <c r="Y139" s="142"/>
-      <c r="Z139" s="143"/>
-    </row>
-    <row r="140" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z139" s="140"/>
+      <c r="AA139" s="140"/>
+      <c r="AB139" s="143"/>
+    </row>
+    <row r="140" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C140" s="158"/>
       <c r="D140" s="158"/>
       <c r="E140" s="140"/>
@@ -22190,9 +22480,11 @@
       <c r="W140" s="199"/>
       <c r="X140" s="142"/>
       <c r="Y140" s="142"/>
-      <c r="Z140" s="143"/>
-    </row>
-    <row r="141" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z140" s="140"/>
+      <c r="AA140" s="140"/>
+      <c r="AB140" s="143"/>
+    </row>
+    <row r="141" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C141" s="158"/>
       <c r="D141" s="158"/>
       <c r="E141" s="140"/>
@@ -22216,9 +22508,11 @@
       <c r="W141" s="199"/>
       <c r="X141" s="142"/>
       <c r="Y141" s="142"/>
-      <c r="Z141" s="143"/>
-    </row>
-    <row r="142" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z141" s="140"/>
+      <c r="AA141" s="140"/>
+      <c r="AB141" s="143"/>
+    </row>
+    <row r="142" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C142" s="158"/>
       <c r="D142" s="158"/>
       <c r="E142" s="140"/>
@@ -22242,9 +22536,11 @@
       <c r="W142" s="199"/>
       <c r="X142" s="142"/>
       <c r="Y142" s="142"/>
-      <c r="Z142" s="143"/>
-    </row>
-    <row r="143" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z142" s="140"/>
+      <c r="AA142" s="140"/>
+      <c r="AB142" s="143"/>
+    </row>
+    <row r="143" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C143" s="158"/>
       <c r="D143" s="158"/>
       <c r="E143" s="140"/>
@@ -22268,9 +22564,11 @@
       <c r="W143" s="199"/>
       <c r="X143" s="142"/>
       <c r="Y143" s="142"/>
-      <c r="Z143" s="143"/>
-    </row>
-    <row r="144" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z143" s="140"/>
+      <c r="AA143" s="140"/>
+      <c r="AB143" s="143"/>
+    </row>
+    <row r="144" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C144" s="158"/>
       <c r="D144" s="158"/>
       <c r="E144" s="140"/>
@@ -22294,9 +22592,11 @@
       <c r="W144" s="199"/>
       <c r="X144" s="142"/>
       <c r="Y144" s="142"/>
-      <c r="Z144" s="143"/>
-    </row>
-    <row r="145" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z144" s="140"/>
+      <c r="AA144" s="140"/>
+      <c r="AB144" s="143"/>
+    </row>
+    <row r="145" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C145" s="158"/>
       <c r="D145" s="158"/>
       <c r="E145" s="140"/>
@@ -22320,9 +22620,11 @@
       <c r="W145" s="199"/>
       <c r="X145" s="142"/>
       <c r="Y145" s="142"/>
-      <c r="Z145" s="143"/>
-    </row>
-    <row r="146" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z145" s="140"/>
+      <c r="AA145" s="140"/>
+      <c r="AB145" s="143"/>
+    </row>
+    <row r="146" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="158"/>
       <c r="D146" s="158"/>
       <c r="E146" s="140"/>
@@ -22346,9 +22648,11 @@
       <c r="W146" s="199"/>
       <c r="X146" s="142"/>
       <c r="Y146" s="142"/>
-      <c r="Z146" s="143"/>
-    </row>
-    <row r="147" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z146" s="140"/>
+      <c r="AA146" s="140"/>
+      <c r="AB146" s="143"/>
+    </row>
+    <row r="147" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C147" s="158"/>
       <c r="D147" s="158"/>
       <c r="E147" s="140"/>
@@ -22372,9 +22676,11 @@
       <c r="W147" s="199"/>
       <c r="X147" s="142"/>
       <c r="Y147" s="142"/>
-      <c r="Z147" s="143"/>
-    </row>
-    <row r="148" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z147" s="140"/>
+      <c r="AA147" s="140"/>
+      <c r="AB147" s="143"/>
+    </row>
+    <row r="148" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C148" s="158"/>
       <c r="D148" s="158"/>
       <c r="E148" s="140"/>
@@ -22398,9 +22704,11 @@
       <c r="W148" s="199"/>
       <c r="X148" s="142"/>
       <c r="Y148" s="142"/>
-      <c r="Z148" s="143"/>
-    </row>
-    <row r="149" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z148" s="140"/>
+      <c r="AA148" s="140"/>
+      <c r="AB148" s="143"/>
+    </row>
+    <row r="149" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C149" s="158"/>
       <c r="D149" s="158"/>
       <c r="E149" s="140"/>
@@ -22424,9 +22732,11 @@
       <c r="W149" s="199"/>
       <c r="X149" s="142"/>
       <c r="Y149" s="142"/>
-      <c r="Z149" s="143"/>
-    </row>
-    <row r="150" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z149" s="140"/>
+      <c r="AA149" s="140"/>
+      <c r="AB149" s="143"/>
+    </row>
+    <row r="150" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C150" s="158"/>
       <c r="D150" s="158"/>
       <c r="E150" s="140"/>
@@ -22450,9 +22760,11 @@
       <c r="W150" s="199"/>
       <c r="X150" s="142"/>
       <c r="Y150" s="142"/>
-      <c r="Z150" s="143"/>
-    </row>
-    <row r="151" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z150" s="140"/>
+      <c r="AA150" s="140"/>
+      <c r="AB150" s="143"/>
+    </row>
+    <row r="151" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C151" s="158"/>
       <c r="D151" s="158"/>
       <c r="E151" s="140"/>
@@ -22476,9 +22788,11 @@
       <c r="W151" s="199"/>
       <c r="X151" s="142"/>
       <c r="Y151" s="142"/>
-      <c r="Z151" s="143"/>
-    </row>
-    <row r="152" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z151" s="140"/>
+      <c r="AA151" s="140"/>
+      <c r="AB151" s="143"/>
+    </row>
+    <row r="152" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C152" s="158"/>
       <c r="D152" s="158"/>
       <c r="E152" s="140"/>
@@ -22502,9 +22816,11 @@
       <c r="W152" s="199"/>
       <c r="X152" s="142"/>
       <c r="Y152" s="142"/>
-      <c r="Z152" s="143"/>
-    </row>
-    <row r="153" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z152" s="140"/>
+      <c r="AA152" s="140"/>
+      <c r="AB152" s="143"/>
+    </row>
+    <row r="153" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C153" s="158"/>
       <c r="D153" s="158"/>
       <c r="E153" s="140"/>
@@ -22528,9 +22844,11 @@
       <c r="W153" s="199"/>
       <c r="X153" s="142"/>
       <c r="Y153" s="142"/>
-      <c r="Z153" s="143"/>
-    </row>
-    <row r="154" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z153" s="140"/>
+      <c r="AA153" s="140"/>
+      <c r="AB153" s="143"/>
+    </row>
+    <row r="154" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C154" s="158"/>
       <c r="D154" s="158"/>
       <c r="E154" s="140"/>
@@ -22554,9 +22872,11 @@
       <c r="W154" s="199"/>
       <c r="X154" s="142"/>
       <c r="Y154" s="142"/>
-      <c r="Z154" s="143"/>
-    </row>
-    <row r="155" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z154" s="140"/>
+      <c r="AA154" s="140"/>
+      <c r="AB154" s="143"/>
+    </row>
+    <row r="155" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C155" s="158"/>
       <c r="D155" s="158"/>
       <c r="E155" s="140"/>
@@ -22580,9 +22900,11 @@
       <c r="W155" s="199"/>
       <c r="X155" s="142"/>
       <c r="Y155" s="142"/>
-      <c r="Z155" s="143"/>
-    </row>
-    <row r="156" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z155" s="140"/>
+      <c r="AA155" s="140"/>
+      <c r="AB155" s="143"/>
+    </row>
+    <row r="156" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C156" s="158"/>
       <c r="D156" s="158"/>
       <c r="E156" s="140"/>
@@ -22606,9 +22928,11 @@
       <c r="W156" s="199"/>
       <c r="X156" s="142"/>
       <c r="Y156" s="142"/>
-      <c r="Z156" s="143"/>
-    </row>
-    <row r="157" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z156" s="140"/>
+      <c r="AA156" s="140"/>
+      <c r="AB156" s="143"/>
+    </row>
+    <row r="157" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C157" s="158"/>
       <c r="D157" s="158"/>
       <c r="E157" s="140"/>
@@ -22632,9 +22956,11 @@
       <c r="W157" s="199"/>
       <c r="X157" s="142"/>
       <c r="Y157" s="142"/>
-      <c r="Z157" s="143"/>
-    </row>
-    <row r="158" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z157" s="140"/>
+      <c r="AA157" s="140"/>
+      <c r="AB157" s="143"/>
+    </row>
+    <row r="158" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C158" s="158"/>
       <c r="D158" s="158"/>
       <c r="E158" s="140"/>
@@ -22658,9 +22984,11 @@
       <c r="W158" s="199"/>
       <c r="X158" s="142"/>
       <c r="Y158" s="142"/>
-      <c r="Z158" s="143"/>
-    </row>
-    <row r="159" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z158" s="140"/>
+      <c r="AA158" s="140"/>
+      <c r="AB158" s="143"/>
+    </row>
+    <row r="159" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C159" s="158"/>
       <c r="D159" s="158"/>
       <c r="E159" s="140"/>
@@ -22684,9 +23012,11 @@
       <c r="W159" s="199"/>
       <c r="X159" s="142"/>
       <c r="Y159" s="142"/>
-      <c r="Z159" s="143"/>
-    </row>
-    <row r="160" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z159" s="140"/>
+      <c r="AA159" s="140"/>
+      <c r="AB159" s="143"/>
+    </row>
+    <row r="160" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C160" s="158"/>
       <c r="D160" s="158"/>
       <c r="E160" s="140"/>
@@ -22710,9 +23040,11 @@
       <c r="W160" s="199"/>
       <c r="X160" s="142"/>
       <c r="Y160" s="142"/>
-      <c r="Z160" s="143"/>
-    </row>
-    <row r="161" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z160" s="140"/>
+      <c r="AA160" s="140"/>
+      <c r="AB160" s="143"/>
+    </row>
+    <row r="161" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C161" s="158"/>
       <c r="D161" s="158"/>
       <c r="E161" s="140"/>
@@ -22736,9 +23068,11 @@
       <c r="W161" s="199"/>
       <c r="X161" s="142"/>
       <c r="Y161" s="142"/>
-      <c r="Z161" s="143"/>
-    </row>
-    <row r="162" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z161" s="140"/>
+      <c r="AA161" s="140"/>
+      <c r="AB161" s="143"/>
+    </row>
+    <row r="162" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C162" s="158"/>
       <c r="D162" s="158"/>
       <c r="E162" s="140"/>
@@ -22762,9 +23096,11 @@
       <c r="W162" s="199"/>
       <c r="X162" s="142"/>
       <c r="Y162" s="142"/>
-      <c r="Z162" s="143"/>
-    </row>
-    <row r="163" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z162" s="140"/>
+      <c r="AA162" s="140"/>
+      <c r="AB162" s="143"/>
+    </row>
+    <row r="163" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C163" s="158"/>
       <c r="D163" s="158"/>
       <c r="E163" s="140"/>
@@ -22788,9 +23124,11 @@
       <c r="W163" s="199"/>
       <c r="X163" s="142"/>
       <c r="Y163" s="142"/>
-      <c r="Z163" s="143"/>
-    </row>
-    <row r="164" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z163" s="140"/>
+      <c r="AA163" s="140"/>
+      <c r="AB163" s="143"/>
+    </row>
+    <row r="164" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C164" s="158"/>
       <c r="D164" s="158"/>
       <c r="E164" s="140"/>
@@ -22814,9 +23152,11 @@
       <c r="W164" s="199"/>
       <c r="X164" s="142"/>
       <c r="Y164" s="142"/>
-      <c r="Z164" s="143"/>
-    </row>
-    <row r="165" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z164" s="140"/>
+      <c r="AA164" s="140"/>
+      <c r="AB164" s="143"/>
+    </row>
+    <row r="165" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C165" s="158"/>
       <c r="D165" s="158"/>
       <c r="E165" s="140"/>
@@ -22840,9 +23180,11 @@
       <c r="W165" s="199"/>
       <c r="X165" s="142"/>
       <c r="Y165" s="142"/>
-      <c r="Z165" s="143"/>
-    </row>
-    <row r="166" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z165" s="140"/>
+      <c r="AA165" s="140"/>
+      <c r="AB165" s="143"/>
+    </row>
+    <row r="166" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C166" s="158"/>
       <c r="D166" s="158"/>
       <c r="E166" s="140"/>
@@ -22866,9 +23208,11 @@
       <c r="W166" s="199"/>
       <c r="X166" s="142"/>
       <c r="Y166" s="142"/>
-      <c r="Z166" s="143"/>
-    </row>
-    <row r="167" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z166" s="140"/>
+      <c r="AA166" s="140"/>
+      <c r="AB166" s="143"/>
+    </row>
+    <row r="167" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C167" s="158"/>
       <c r="D167" s="158"/>
       <c r="E167" s="140"/>
@@ -22892,9 +23236,11 @@
       <c r="W167" s="199"/>
       <c r="X167" s="142"/>
       <c r="Y167" s="142"/>
-      <c r="Z167" s="143"/>
-    </row>
-    <row r="168" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z167" s="140"/>
+      <c r="AA167" s="140"/>
+      <c r="AB167" s="143"/>
+    </row>
+    <row r="168" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C168" s="158"/>
       <c r="D168" s="158"/>
       <c r="E168" s="140"/>
@@ -22918,9 +23264,11 @@
       <c r="W168" s="199"/>
       <c r="X168" s="142"/>
       <c r="Y168" s="142"/>
-      <c r="Z168" s="143"/>
-    </row>
-    <row r="169" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z168" s="140"/>
+      <c r="AA168" s="140"/>
+      <c r="AB168" s="143"/>
+    </row>
+    <row r="169" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C169" s="158"/>
       <c r="D169" s="158"/>
       <c r="E169" s="140"/>
@@ -22944,9 +23292,11 @@
       <c r="W169" s="199"/>
       <c r="X169" s="142"/>
       <c r="Y169" s="142"/>
-      <c r="Z169" s="143"/>
-    </row>
-    <row r="170" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z169" s="140"/>
+      <c r="AA169" s="140"/>
+      <c r="AB169" s="143"/>
+    </row>
+    <row r="170" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C170" s="158"/>
       <c r="D170" s="158"/>
       <c r="E170" s="140"/>
@@ -22970,9 +23320,11 @@
       <c r="W170" s="199"/>
       <c r="X170" s="142"/>
       <c r="Y170" s="142"/>
-      <c r="Z170" s="143"/>
-    </row>
-    <row r="171" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z170" s="140"/>
+      <c r="AA170" s="140"/>
+      <c r="AB170" s="143"/>
+    </row>
+    <row r="171" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C171" s="158"/>
       <c r="D171" s="158"/>
       <c r="E171" s="140"/>
@@ -22996,9 +23348,11 @@
       <c r="W171" s="199"/>
       <c r="X171" s="142"/>
       <c r="Y171" s="142"/>
-      <c r="Z171" s="143"/>
-    </row>
-    <row r="172" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z171" s="140"/>
+      <c r="AA171" s="140"/>
+      <c r="AB171" s="143"/>
+    </row>
+    <row r="172" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C172" s="158"/>
       <c r="D172" s="158"/>
       <c r="E172" s="140"/>
@@ -23022,9 +23376,11 @@
       <c r="W172" s="199"/>
       <c r="X172" s="142"/>
       <c r="Y172" s="142"/>
-      <c r="Z172" s="143"/>
-    </row>
-    <row r="173" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z172" s="140"/>
+      <c r="AA172" s="140"/>
+      <c r="AB172" s="143"/>
+    </row>
+    <row r="173" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C173" s="158"/>
       <c r="D173" s="158"/>
       <c r="E173" s="140"/>
@@ -23048,9 +23404,11 @@
       <c r="W173" s="199"/>
       <c r="X173" s="142"/>
       <c r="Y173" s="142"/>
-      <c r="Z173" s="143"/>
-    </row>
-    <row r="174" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z173" s="140"/>
+      <c r="AA173" s="140"/>
+      <c r="AB173" s="143"/>
+    </row>
+    <row r="174" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C174" s="158"/>
       <c r="D174" s="158"/>
       <c r="E174" s="140"/>
@@ -23074,9 +23432,11 @@
       <c r="W174" s="199"/>
       <c r="X174" s="142"/>
       <c r="Y174" s="142"/>
-      <c r="Z174" s="143"/>
-    </row>
-    <row r="175" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z174" s="140"/>
+      <c r="AA174" s="140"/>
+      <c r="AB174" s="143"/>
+    </row>
+    <row r="175" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C175" s="158"/>
       <c r="D175" s="158"/>
       <c r="E175" s="140"/>
@@ -23100,9 +23460,11 @@
       <c r="W175" s="199"/>
       <c r="X175" s="142"/>
       <c r="Y175" s="142"/>
-      <c r="Z175" s="143"/>
-    </row>
-    <row r="176" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z175" s="140"/>
+      <c r="AA175" s="140"/>
+      <c r="AB175" s="143"/>
+    </row>
+    <row r="176" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C176" s="158"/>
       <c r="D176" s="158"/>
       <c r="E176" s="140"/>
@@ -23126,9 +23488,11 @@
       <c r="W176" s="199"/>
       <c r="X176" s="142"/>
       <c r="Y176" s="142"/>
-      <c r="Z176" s="143"/>
-    </row>
-    <row r="177" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z176" s="140"/>
+      <c r="AA176" s="140"/>
+      <c r="AB176" s="143"/>
+    </row>
+    <row r="177" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C177" s="158"/>
       <c r="D177" s="158"/>
       <c r="E177" s="140"/>
@@ -23152,9 +23516,11 @@
       <c r="W177" s="199"/>
       <c r="X177" s="142"/>
       <c r="Y177" s="142"/>
-      <c r="Z177" s="143"/>
-    </row>
-    <row r="178" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z177" s="140"/>
+      <c r="AA177" s="140"/>
+      <c r="AB177" s="143"/>
+    </row>
+    <row r="178" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C178" s="158"/>
       <c r="D178" s="158"/>
       <c r="E178" s="140"/>
@@ -23178,9 +23544,11 @@
       <c r="W178" s="199"/>
       <c r="X178" s="142"/>
       <c r="Y178" s="142"/>
-      <c r="Z178" s="143"/>
-    </row>
-    <row r="179" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z178" s="140"/>
+      <c r="AA178" s="140"/>
+      <c r="AB178" s="143"/>
+    </row>
+    <row r="179" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C179" s="158"/>
       <c r="D179" s="158"/>
       <c r="E179" s="140"/>
@@ -23204,9 +23572,11 @@
       <c r="W179" s="199"/>
       <c r="X179" s="142"/>
       <c r="Y179" s="142"/>
-      <c r="Z179" s="143"/>
-    </row>
-    <row r="180" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z179" s="140"/>
+      <c r="AA179" s="140"/>
+      <c r="AB179" s="143"/>
+    </row>
+    <row r="180" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C180" s="158"/>
       <c r="D180" s="158"/>
       <c r="E180" s="140"/>
@@ -23230,9 +23600,11 @@
       <c r="W180" s="199"/>
       <c r="X180" s="142"/>
       <c r="Y180" s="142"/>
-      <c r="Z180" s="143"/>
-    </row>
-    <row r="181" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z180" s="140"/>
+      <c r="AA180" s="140"/>
+      <c r="AB180" s="143"/>
+    </row>
+    <row r="181" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C181" s="158"/>
       <c r="D181" s="158"/>
       <c r="E181" s="140"/>
@@ -23256,9 +23628,11 @@
       <c r="W181" s="199"/>
       <c r="X181" s="142"/>
       <c r="Y181" s="142"/>
-      <c r="Z181" s="143"/>
-    </row>
-    <row r="182" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z181" s="140"/>
+      <c r="AA181" s="140"/>
+      <c r="AB181" s="143"/>
+    </row>
+    <row r="182" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C182" s="158"/>
       <c r="D182" s="158"/>
       <c r="E182" s="140"/>
@@ -23282,9 +23656,11 @@
       <c r="W182" s="199"/>
       <c r="X182" s="142"/>
       <c r="Y182" s="142"/>
-      <c r="Z182" s="143"/>
-    </row>
-    <row r="183" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z182" s="140"/>
+      <c r="AA182" s="140"/>
+      <c r="AB182" s="143"/>
+    </row>
+    <row r="183" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C183" s="158"/>
       <c r="D183" s="158"/>
       <c r="E183" s="140"/>
@@ -23308,9 +23684,11 @@
       <c r="W183" s="199"/>
       <c r="X183" s="142"/>
       <c r="Y183" s="142"/>
-      <c r="Z183" s="143"/>
-    </row>
-    <row r="184" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z183" s="140"/>
+      <c r="AA183" s="140"/>
+      <c r="AB183" s="143"/>
+    </row>
+    <row r="184" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C184" s="158"/>
       <c r="D184" s="158"/>
       <c r="E184" s="140"/>
@@ -23334,9 +23712,11 @@
       <c r="W184" s="199"/>
       <c r="X184" s="142"/>
       <c r="Y184" s="142"/>
-      <c r="Z184" s="143"/>
-    </row>
-    <row r="185" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z184" s="140"/>
+      <c r="AA184" s="140"/>
+      <c r="AB184" s="143"/>
+    </row>
+    <row r="185" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C185" s="158"/>
       <c r="D185" s="158"/>
       <c r="E185" s="140"/>
@@ -23360,9 +23740,11 @@
       <c r="W185" s="199"/>
       <c r="X185" s="142"/>
       <c r="Y185" s="142"/>
-      <c r="Z185" s="143"/>
-    </row>
-    <row r="186" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z185" s="140"/>
+      <c r="AA185" s="140"/>
+      <c r="AB185" s="143"/>
+    </row>
+    <row r="186" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C186" s="158"/>
       <c r="D186" s="158"/>
       <c r="E186" s="140"/>
@@ -23386,9 +23768,11 @@
       <c r="W186" s="199"/>
       <c r="X186" s="142"/>
       <c r="Y186" s="142"/>
-      <c r="Z186" s="143"/>
-    </row>
-    <row r="187" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z186" s="140"/>
+      <c r="AA186" s="140"/>
+      <c r="AB186" s="143"/>
+    </row>
+    <row r="187" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C187" s="158"/>
       <c r="D187" s="158"/>
       <c r="E187" s="140"/>
@@ -23412,9 +23796,11 @@
       <c r="W187" s="199"/>
       <c r="X187" s="142"/>
       <c r="Y187" s="142"/>
-      <c r="Z187" s="143"/>
-    </row>
-    <row r="188" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z187" s="140"/>
+      <c r="AA187" s="140"/>
+      <c r="AB187" s="143"/>
+    </row>
+    <row r="188" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C188" s="158"/>
       <c r="D188" s="158"/>
       <c r="E188" s="140"/>
@@ -23438,9 +23824,11 @@
       <c r="W188" s="199"/>
       <c r="X188" s="142"/>
       <c r="Y188" s="142"/>
-      <c r="Z188" s="143"/>
-    </row>
-    <row r="189" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z188" s="140"/>
+      <c r="AA188" s="140"/>
+      <c r="AB188" s="143"/>
+    </row>
+    <row r="189" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C189" s="158"/>
       <c r="D189" s="158"/>
       <c r="E189" s="140"/>
@@ -23464,9 +23852,11 @@
       <c r="W189" s="199"/>
       <c r="X189" s="142"/>
       <c r="Y189" s="142"/>
-      <c r="Z189" s="143"/>
-    </row>
-    <row r="190" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z189" s="140"/>
+      <c r="AA189" s="140"/>
+      <c r="AB189" s="143"/>
+    </row>
+    <row r="190" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C190" s="158"/>
       <c r="D190" s="158"/>
       <c r="E190" s="140"/>
@@ -23490,9 +23880,11 @@
       <c r="W190" s="199"/>
       <c r="X190" s="142"/>
       <c r="Y190" s="142"/>
-      <c r="Z190" s="143"/>
-    </row>
-    <row r="191" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z190" s="140"/>
+      <c r="AA190" s="140"/>
+      <c r="AB190" s="143"/>
+    </row>
+    <row r="191" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C191" s="158"/>
       <c r="D191" s="158"/>
       <c r="E191" s="140"/>
@@ -23516,9 +23908,11 @@
       <c r="W191" s="199"/>
       <c r="X191" s="142"/>
       <c r="Y191" s="142"/>
-      <c r="Z191" s="143"/>
-    </row>
-    <row r="192" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z191" s="140"/>
+      <c r="AA191" s="140"/>
+      <c r="AB191" s="143"/>
+    </row>
+    <row r="192" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C192" s="158"/>
       <c r="D192" s="158"/>
       <c r="E192" s="140"/>
@@ -23542,9 +23936,11 @@
       <c r="W192" s="199"/>
       <c r="X192" s="142"/>
       <c r="Y192" s="142"/>
-      <c r="Z192" s="143"/>
-    </row>
-    <row r="193" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z192" s="140"/>
+      <c r="AA192" s="140"/>
+      <c r="AB192" s="143"/>
+    </row>
+    <row r="193" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C193" s="158"/>
       <c r="D193" s="158"/>
       <c r="E193" s="140"/>
@@ -23568,9 +23964,11 @@
       <c r="W193" s="199"/>
       <c r="X193" s="142"/>
       <c r="Y193" s="142"/>
-      <c r="Z193" s="143"/>
-    </row>
-    <row r="194" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z193" s="140"/>
+      <c r="AA193" s="140"/>
+      <c r="AB193" s="143"/>
+    </row>
+    <row r="194" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C194" s="158"/>
       <c r="D194" s="158"/>
       <c r="E194" s="140"/>
@@ -23594,9 +23992,11 @@
       <c r="W194" s="199"/>
       <c r="X194" s="142"/>
       <c r="Y194" s="142"/>
-      <c r="Z194" s="143"/>
-    </row>
-    <row r="195" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z194" s="140"/>
+      <c r="AA194" s="140"/>
+      <c r="AB194" s="143"/>
+    </row>
+    <row r="195" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C195" s="158"/>
       <c r="D195" s="158"/>
       <c r="E195" s="140"/>
@@ -23620,9 +24020,11 @@
       <c r="W195" s="199"/>
       <c r="X195" s="142"/>
       <c r="Y195" s="142"/>
-      <c r="Z195" s="143"/>
-    </row>
-    <row r="196" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z195" s="140"/>
+      <c r="AA195" s="140"/>
+      <c r="AB195" s="143"/>
+    </row>
+    <row r="196" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C196" s="158"/>
       <c r="D196" s="158"/>
       <c r="E196" s="140"/>
@@ -23646,9 +24048,11 @@
       <c r="W196" s="199"/>
       <c r="X196" s="142"/>
       <c r="Y196" s="142"/>
-      <c r="Z196" s="143"/>
-    </row>
-    <row r="197" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z196" s="140"/>
+      <c r="AA196" s="140"/>
+      <c r="AB196" s="143"/>
+    </row>
+    <row r="197" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C197" s="158"/>
       <c r="D197" s="158"/>
       <c r="E197" s="140"/>
@@ -23672,9 +24076,11 @@
       <c r="W197" s="199"/>
       <c r="X197" s="142"/>
       <c r="Y197" s="142"/>
-      <c r="Z197" s="143"/>
-    </row>
-    <row r="198" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z197" s="140"/>
+      <c r="AA197" s="140"/>
+      <c r="AB197" s="143"/>
+    </row>
+    <row r="198" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C198" s="158"/>
       <c r="D198" s="158"/>
       <c r="E198" s="140"/>
@@ -23698,9 +24104,11 @@
       <c r="W198" s="199"/>
       <c r="X198" s="142"/>
       <c r="Y198" s="142"/>
-      <c r="Z198" s="143"/>
-    </row>
-    <row r="199" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z198" s="140"/>
+      <c r="AA198" s="140"/>
+      <c r="AB198" s="143"/>
+    </row>
+    <row r="199" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C199" s="158"/>
       <c r="D199" s="158"/>
       <c r="E199" s="140"/>
@@ -23724,9 +24132,11 @@
       <c r="W199" s="199"/>
       <c r="X199" s="142"/>
       <c r="Y199" s="142"/>
-      <c r="Z199" s="143"/>
-    </row>
-    <row r="200" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z199" s="140"/>
+      <c r="AA199" s="140"/>
+      <c r="AB199" s="143"/>
+    </row>
+    <row r="200" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C200" s="158"/>
       <c r="D200" s="158"/>
       <c r="E200" s="140"/>
@@ -23750,9 +24160,11 @@
       <c r="W200" s="199"/>
       <c r="X200" s="142"/>
       <c r="Y200" s="142"/>
-      <c r="Z200" s="143"/>
-    </row>
-    <row r="201" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z200" s="140"/>
+      <c r="AA200" s="140"/>
+      <c r="AB200" s="143"/>
+    </row>
+    <row r="201" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C201" s="158"/>
       <c r="D201" s="158"/>
       <c r="E201" s="140"/>
@@ -23776,9 +24188,11 @@
       <c r="W201" s="199"/>
       <c r="X201" s="142"/>
       <c r="Y201" s="142"/>
-      <c r="Z201" s="143"/>
-    </row>
-    <row r="202" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z201" s="140"/>
+      <c r="AA201" s="140"/>
+      <c r="AB201" s="143"/>
+    </row>
+    <row r="202" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C202" s="158"/>
       <c r="D202" s="158"/>
       <c r="E202" s="140"/>
@@ -23802,9 +24216,11 @@
       <c r="W202" s="199"/>
       <c r="X202" s="142"/>
       <c r="Y202" s="142"/>
-      <c r="Z202" s="143"/>
-    </row>
-    <row r="203" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z202" s="140"/>
+      <c r="AA202" s="140"/>
+      <c r="AB202" s="143"/>
+    </row>
+    <row r="203" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C203" s="158"/>
       <c r="D203" s="158"/>
       <c r="E203" s="140"/>
@@ -23828,9 +24244,11 @@
       <c r="W203" s="199"/>
       <c r="X203" s="142"/>
       <c r="Y203" s="142"/>
-      <c r="Z203" s="143"/>
-    </row>
-    <row r="204" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z203" s="140"/>
+      <c r="AA203" s="140"/>
+      <c r="AB203" s="143"/>
+    </row>
+    <row r="204" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C204" s="158"/>
       <c r="D204" s="158"/>
       <c r="E204" s="140"/>
@@ -23854,9 +24272,11 @@
       <c r="W204" s="199"/>
       <c r="X204" s="142"/>
       <c r="Y204" s="142"/>
-      <c r="Z204" s="143"/>
-    </row>
-    <row r="205" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z204" s="140"/>
+      <c r="AA204" s="140"/>
+      <c r="AB204" s="143"/>
+    </row>
+    <row r="205" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C205" s="158"/>
       <c r="D205" s="158"/>
       <c r="E205" s="140"/>
@@ -23880,9 +24300,11 @@
       <c r="W205" s="199"/>
       <c r="X205" s="142"/>
       <c r="Y205" s="142"/>
-      <c r="Z205" s="143"/>
-    </row>
-    <row r="206" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z205" s="140"/>
+      <c r="AA205" s="140"/>
+      <c r="AB205" s="143"/>
+    </row>
+    <row r="206" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C206" s="158"/>
       <c r="D206" s="158"/>
       <c r="E206" s="140"/>
@@ -23906,9 +24328,11 @@
       <c r="W206" s="199"/>
       <c r="X206" s="142"/>
       <c r="Y206" s="142"/>
-      <c r="Z206" s="143"/>
-    </row>
-    <row r="207" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z206" s="140"/>
+      <c r="AA206" s="140"/>
+      <c r="AB206" s="143"/>
+    </row>
+    <row r="207" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C207" s="158"/>
       <c r="D207" s="158"/>
       <c r="E207" s="140"/>
@@ -23932,9 +24356,11 @@
       <c r="W207" s="199"/>
       <c r="X207" s="142"/>
       <c r="Y207" s="142"/>
-      <c r="Z207" s="143"/>
-    </row>
-    <row r="208" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z207" s="140"/>
+      <c r="AA207" s="140"/>
+      <c r="AB207" s="143"/>
+    </row>
+    <row r="208" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C208" s="158"/>
       <c r="D208" s="158"/>
       <c r="E208" s="140"/>
@@ -23958,9 +24384,11 @@
       <c r="W208" s="199"/>
       <c r="X208" s="142"/>
       <c r="Y208" s="142"/>
-      <c r="Z208" s="143"/>
-    </row>
-    <row r="209" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z208" s="140"/>
+      <c r="AA208" s="140"/>
+      <c r="AB208" s="143"/>
+    </row>
+    <row r="209" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C209" s="158"/>
       <c r="D209" s="158"/>
       <c r="E209" s="140"/>
@@ -23984,9 +24412,11 @@
       <c r="W209" s="199"/>
       <c r="X209" s="142"/>
       <c r="Y209" s="142"/>
-      <c r="Z209" s="143"/>
-    </row>
-    <row r="210" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z209" s="140"/>
+      <c r="AA209" s="140"/>
+      <c r="AB209" s="143"/>
+    </row>
+    <row r="210" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C210" s="158"/>
       <c r="D210" s="158"/>
       <c r="E210" s="140"/>
@@ -24010,9 +24440,11 @@
       <c r="W210" s="199"/>
       <c r="X210" s="142"/>
       <c r="Y210" s="142"/>
-      <c r="Z210" s="143"/>
-    </row>
-    <row r="211" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z210" s="140"/>
+      <c r="AA210" s="140"/>
+      <c r="AB210" s="143"/>
+    </row>
+    <row r="211" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C211" s="158"/>
       <c r="D211" s="158"/>
       <c r="E211" s="140"/>
@@ -24036,9 +24468,11 @@
       <c r="W211" s="199"/>
       <c r="X211" s="142"/>
       <c r="Y211" s="142"/>
-      <c r="Z211" s="143"/>
-    </row>
-    <row r="212" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z211" s="140"/>
+      <c r="AA211" s="140"/>
+      <c r="AB211" s="143"/>
+    </row>
+    <row r="212" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C212" s="158"/>
       <c r="D212" s="158"/>
       <c r="E212" s="140"/>
@@ -24062,9 +24496,11 @@
       <c r="W212" s="199"/>
       <c r="X212" s="142"/>
       <c r="Y212" s="142"/>
-      <c r="Z212" s="143"/>
-    </row>
-    <row r="213" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z212" s="140"/>
+      <c r="AA212" s="140"/>
+      <c r="AB212" s="143"/>
+    </row>
+    <row r="213" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C213" s="158"/>
       <c r="D213" s="158"/>
       <c r="E213" s="140"/>
@@ -24088,9 +24524,11 @@
       <c r="W213" s="199"/>
       <c r="X213" s="142"/>
       <c r="Y213" s="142"/>
-      <c r="Z213" s="143"/>
-    </row>
-    <row r="214" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z213" s="140"/>
+      <c r="AA213" s="140"/>
+      <c r="AB213" s="143"/>
+    </row>
+    <row r="214" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C214" s="158"/>
       <c r="D214" s="158"/>
       <c r="E214" s="140"/>
@@ -24114,9 +24552,11 @@
       <c r="W214" s="199"/>
       <c r="X214" s="142"/>
       <c r="Y214" s="142"/>
-      <c r="Z214" s="143"/>
-    </row>
-    <row r="215" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z214" s="140"/>
+      <c r="AA214" s="140"/>
+      <c r="AB214" s="143"/>
+    </row>
+    <row r="215" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C215" s="158"/>
       <c r="D215" s="158"/>
       <c r="E215" s="140"/>
@@ -24140,9 +24580,11 @@
       <c r="W215" s="199"/>
       <c r="X215" s="142"/>
       <c r="Y215" s="142"/>
-      <c r="Z215" s="143"/>
-    </row>
-    <row r="216" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z215" s="140"/>
+      <c r="AA215" s="140"/>
+      <c r="AB215" s="143"/>
+    </row>
+    <row r="216" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C216" s="158"/>
       <c r="D216" s="158"/>
       <c r="E216" s="140"/>
@@ -24166,9 +24608,11 @@
       <c r="W216" s="199"/>
       <c r="X216" s="142"/>
       <c r="Y216" s="142"/>
-      <c r="Z216" s="143"/>
-    </row>
-    <row r="217" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z216" s="140"/>
+      <c r="AA216" s="140"/>
+      <c r="AB216" s="143"/>
+    </row>
+    <row r="217" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C217" s="158"/>
       <c r="D217" s="158"/>
       <c r="E217" s="140"/>
@@ -24192,9 +24636,11 @@
       <c r="W217" s="199"/>
       <c r="X217" s="142"/>
       <c r="Y217" s="142"/>
-      <c r="Z217" s="143"/>
-    </row>
-    <row r="218" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z217" s="140"/>
+      <c r="AA217" s="140"/>
+      <c r="AB217" s="143"/>
+    </row>
+    <row r="218" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C218" s="158"/>
       <c r="D218" s="158"/>
       <c r="E218" s="140"/>
@@ -24218,9 +24664,11 @@
       <c r="W218" s="199"/>
       <c r="X218" s="142"/>
       <c r="Y218" s="142"/>
-      <c r="Z218" s="143"/>
-    </row>
-    <row r="219" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z218" s="140"/>
+      <c r="AA218" s="140"/>
+      <c r="AB218" s="143"/>
+    </row>
+    <row r="219" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C219" s="158"/>
       <c r="D219" s="158"/>
       <c r="E219" s="140"/>
@@ -24244,9 +24692,11 @@
       <c r="W219" s="199"/>
       <c r="X219" s="142"/>
       <c r="Y219" s="142"/>
-      <c r="Z219" s="143"/>
-    </row>
-    <row r="220" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z219" s="140"/>
+      <c r="AA219" s="140"/>
+      <c r="AB219" s="143"/>
+    </row>
+    <row r="220" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C220" s="158"/>
       <c r="D220" s="158"/>
       <c r="E220" s="140"/>
@@ -24270,9 +24720,11 @@
       <c r="W220" s="199"/>
       <c r="X220" s="142"/>
       <c r="Y220" s="142"/>
-      <c r="Z220" s="143"/>
-    </row>
-    <row r="221" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z220" s="140"/>
+      <c r="AA220" s="140"/>
+      <c r="AB220" s="143"/>
+    </row>
+    <row r="221" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C221" s="158"/>
       <c r="D221" s="158"/>
       <c r="E221" s="140"/>
@@ -24296,9 +24748,11 @@
       <c r="W221" s="199"/>
       <c r="X221" s="142"/>
       <c r="Y221" s="142"/>
-      <c r="Z221" s="143"/>
-    </row>
-    <row r="222" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z221" s="140"/>
+      <c r="AA221" s="140"/>
+      <c r="AB221" s="143"/>
+    </row>
+    <row r="222" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C222" s="158"/>
       <c r="D222" s="158"/>
       <c r="E222" s="140"/>
@@ -24322,9 +24776,11 @@
       <c r="W222" s="199"/>
       <c r="X222" s="142"/>
       <c r="Y222" s="142"/>
-      <c r="Z222" s="143"/>
-    </row>
-    <row r="223" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z222" s="140"/>
+      <c r="AA222" s="140"/>
+      <c r="AB222" s="143"/>
+    </row>
+    <row r="223" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C223" s="158"/>
       <c r="D223" s="158"/>
       <c r="E223" s="140"/>
@@ -24348,9 +24804,11 @@
       <c r="W223" s="199"/>
       <c r="X223" s="142"/>
       <c r="Y223" s="142"/>
-      <c r="Z223" s="143"/>
-    </row>
-    <row r="224" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z223" s="140"/>
+      <c r="AA223" s="140"/>
+      <c r="AB223" s="143"/>
+    </row>
+    <row r="224" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C224" s="158"/>
       <c r="D224" s="158"/>
       <c r="E224" s="140"/>
@@ -24374,9 +24832,11 @@
       <c r="W224" s="199"/>
       <c r="X224" s="142"/>
       <c r="Y224" s="142"/>
-      <c r="Z224" s="143"/>
-    </row>
-    <row r="225" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z224" s="140"/>
+      <c r="AA224" s="140"/>
+      <c r="AB224" s="143"/>
+    </row>
+    <row r="225" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C225" s="158"/>
       <c r="D225" s="158"/>
       <c r="E225" s="140"/>
@@ -24400,9 +24860,11 @@
       <c r="W225" s="199"/>
       <c r="X225" s="142"/>
       <c r="Y225" s="142"/>
-      <c r="Z225" s="143"/>
-    </row>
-    <row r="226" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z225" s="140"/>
+      <c r="AA225" s="140"/>
+      <c r="AB225" s="143"/>
+    </row>
+    <row r="226" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C226" s="158"/>
       <c r="D226" s="158"/>
       <c r="E226" s="140"/>
@@ -24426,9 +24888,11 @@
       <c r="W226" s="199"/>
       <c r="X226" s="142"/>
       <c r="Y226" s="142"/>
-      <c r="Z226" s="143"/>
-    </row>
-    <row r="227" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z226" s="140"/>
+      <c r="AA226" s="140"/>
+      <c r="AB226" s="143"/>
+    </row>
+    <row r="227" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C227" s="158"/>
       <c r="D227" s="158"/>
       <c r="E227" s="140"/>
@@ -24452,9 +24916,11 @@
       <c r="W227" s="199"/>
       <c r="X227" s="142"/>
       <c r="Y227" s="142"/>
-      <c r="Z227" s="143"/>
-    </row>
-    <row r="228" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z227" s="140"/>
+      <c r="AA227" s="140"/>
+      <c r="AB227" s="143"/>
+    </row>
+    <row r="228" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C228" s="158"/>
       <c r="D228" s="158"/>
       <c r="E228" s="140"/>
@@ -24478,9 +24944,11 @@
       <c r="W228" s="199"/>
       <c r="X228" s="142"/>
       <c r="Y228" s="142"/>
-      <c r="Z228" s="143"/>
-    </row>
-    <row r="229" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z228" s="140"/>
+      <c r="AA228" s="140"/>
+      <c r="AB228" s="143"/>
+    </row>
+    <row r="229" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C229" s="158"/>
       <c r="D229" s="158"/>
       <c r="E229" s="140"/>
@@ -24504,9 +24972,11 @@
       <c r="W229" s="199"/>
       <c r="X229" s="142"/>
       <c r="Y229" s="142"/>
-      <c r="Z229" s="143"/>
-    </row>
-    <row r="230" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z229" s="140"/>
+      <c r="AA229" s="140"/>
+      <c r="AB229" s="143"/>
+    </row>
+    <row r="230" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C230" s="158"/>
       <c r="D230" s="158"/>
       <c r="E230" s="140"/>
@@ -24530,9 +25000,11 @@
       <c r="W230" s="199"/>
       <c r="X230" s="142"/>
       <c r="Y230" s="142"/>
-      <c r="Z230" s="143"/>
-    </row>
-    <row r="231" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z230" s="140"/>
+      <c r="AA230" s="140"/>
+      <c r="AB230" s="143"/>
+    </row>
+    <row r="231" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C231" s="158"/>
       <c r="D231" s="158"/>
       <c r="E231" s="140"/>
@@ -24556,9 +25028,11 @@
       <c r="W231" s="199"/>
       <c r="X231" s="142"/>
       <c r="Y231" s="142"/>
-      <c r="Z231" s="143"/>
-    </row>
-    <row r="232" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z231" s="140"/>
+      <c r="AA231" s="140"/>
+      <c r="AB231" s="143"/>
+    </row>
+    <row r="232" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C232" s="158"/>
       <c r="D232" s="158"/>
       <c r="E232" s="140"/>
@@ -24582,9 +25056,11 @@
       <c r="W232" s="199"/>
       <c r="X232" s="142"/>
       <c r="Y232" s="142"/>
-      <c r="Z232" s="143"/>
-    </row>
-    <row r="233" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z232" s="140"/>
+      <c r="AA232" s="140"/>
+      <c r="AB232" s="143"/>
+    </row>
+    <row r="233" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C233" s="158"/>
       <c r="D233" s="158"/>
       <c r="E233" s="140"/>
@@ -24608,9 +25084,11 @@
       <c r="W233" s="199"/>
       <c r="X233" s="142"/>
       <c r="Y233" s="142"/>
-      <c r="Z233" s="143"/>
-    </row>
-    <row r="234" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z233" s="140"/>
+      <c r="AA233" s="140"/>
+      <c r="AB233" s="143"/>
+    </row>
+    <row r="234" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C234" s="158"/>
       <c r="D234" s="158"/>
       <c r="E234" s="140"/>
@@ -24634,9 +25112,11 @@
       <c r="W234" s="199"/>
       <c r="X234" s="142"/>
       <c r="Y234" s="142"/>
-      <c r="Z234" s="143"/>
-    </row>
-    <row r="235" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z234" s="140"/>
+      <c r="AA234" s="140"/>
+      <c r="AB234" s="143"/>
+    </row>
+    <row r="235" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C235" s="158"/>
       <c r="D235" s="158"/>
       <c r="E235" s="140"/>
@@ -24660,9 +25140,11 @@
       <c r="W235" s="199"/>
       <c r="X235" s="142"/>
       <c r="Y235" s="142"/>
-      <c r="Z235" s="143"/>
-    </row>
-    <row r="236" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z235" s="140"/>
+      <c r="AA235" s="140"/>
+      <c r="AB235" s="143"/>
+    </row>
+    <row r="236" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C236" s="158"/>
       <c r="D236" s="158"/>
       <c r="E236" s="140"/>
@@ -24686,9 +25168,11 @@
       <c r="W236" s="199"/>
       <c r="X236" s="142"/>
       <c r="Y236" s="142"/>
-      <c r="Z236" s="143"/>
-    </row>
-    <row r="237" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z236" s="140"/>
+      <c r="AA236" s="140"/>
+      <c r="AB236" s="143"/>
+    </row>
+    <row r="237" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C237" s="158"/>
       <c r="D237" s="158"/>
       <c r="E237" s="140"/>
@@ -24712,9 +25196,11 @@
       <c r="W237" s="199"/>
       <c r="X237" s="142"/>
       <c r="Y237" s="142"/>
-      <c r="Z237" s="143"/>
-    </row>
-    <row r="238" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z237" s="140"/>
+      <c r="AA237" s="140"/>
+      <c r="AB237" s="143"/>
+    </row>
+    <row r="238" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C238" s="158"/>
       <c r="D238" s="158"/>
       <c r="E238" s="140"/>
@@ -24738,9 +25224,11 @@
       <c r="W238" s="199"/>
       <c r="X238" s="142"/>
       <c r="Y238" s="142"/>
-      <c r="Z238" s="143"/>
-    </row>
-    <row r="239" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z238" s="140"/>
+      <c r="AA238" s="140"/>
+      <c r="AB238" s="143"/>
+    </row>
+    <row r="239" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C239" s="158"/>
       <c r="D239" s="158"/>
       <c r="E239" s="140"/>
@@ -24764,9 +25252,11 @@
       <c r="W239" s="199"/>
       <c r="X239" s="142"/>
       <c r="Y239" s="142"/>
-      <c r="Z239" s="143"/>
-    </row>
-    <row r="240" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z239" s="140"/>
+      <c r="AA239" s="140"/>
+      <c r="AB239" s="143"/>
+    </row>
+    <row r="240" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C240" s="158"/>
       <c r="D240" s="158"/>
       <c r="E240" s="140"/>
@@ -24790,9 +25280,11 @@
       <c r="W240" s="199"/>
       <c r="X240" s="142"/>
       <c r="Y240" s="142"/>
-      <c r="Z240" s="143"/>
-    </row>
-    <row r="241" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z240" s="140"/>
+      <c r="AA240" s="140"/>
+      <c r="AB240" s="143"/>
+    </row>
+    <row r="241" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C241" s="158"/>
       <c r="D241" s="158"/>
       <c r="E241" s="140"/>
@@ -24816,9 +25308,11 @@
       <c r="W241" s="199"/>
       <c r="X241" s="142"/>
       <c r="Y241" s="142"/>
-      <c r="Z241" s="143"/>
-    </row>
-    <row r="242" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z241" s="140"/>
+      <c r="AA241" s="140"/>
+      <c r="AB241" s="143"/>
+    </row>
+    <row r="242" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C242" s="158"/>
       <c r="D242" s="158"/>
       <c r="E242" s="140"/>
@@ -24842,9 +25336,11 @@
       <c r="W242" s="199"/>
       <c r="X242" s="142"/>
       <c r="Y242" s="142"/>
-      <c r="Z242" s="143"/>
-    </row>
-    <row r="243" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z242" s="140"/>
+      <c r="AA242" s="140"/>
+      <c r="AB242" s="143"/>
+    </row>
+    <row r="243" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C243" s="158"/>
       <c r="D243" s="158"/>
       <c r="E243" s="140"/>
@@ -24868,9 +25364,11 @@
       <c r="W243" s="199"/>
       <c r="X243" s="142"/>
       <c r="Y243" s="142"/>
-      <c r="Z243" s="143"/>
-    </row>
-    <row r="244" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z243" s="140"/>
+      <c r="AA243" s="140"/>
+      <c r="AB243" s="143"/>
+    </row>
+    <row r="244" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C244" s="158"/>
       <c r="D244" s="158"/>
       <c r="E244" s="140"/>
@@ -24894,9 +25392,11 @@
       <c r="W244" s="199"/>
       <c r="X244" s="142"/>
       <c r="Y244" s="142"/>
-      <c r="Z244" s="143"/>
-    </row>
-    <row r="245" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z244" s="140"/>
+      <c r="AA244" s="140"/>
+      <c r="AB244" s="143"/>
+    </row>
+    <row r="245" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C245" s="158"/>
       <c r="D245" s="158"/>
       <c r="E245" s="140"/>
@@ -24920,9 +25420,11 @@
       <c r="W245" s="199"/>
       <c r="X245" s="142"/>
       <c r="Y245" s="142"/>
-      <c r="Z245" s="143"/>
-    </row>
-    <row r="246" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z245" s="140"/>
+      <c r="AA245" s="140"/>
+      <c r="AB245" s="143"/>
+    </row>
+    <row r="246" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C246" s="158"/>
       <c r="D246" s="158"/>
       <c r="E246" s="140"/>
@@ -24946,9 +25448,11 @@
       <c r="W246" s="199"/>
       <c r="X246" s="142"/>
       <c r="Y246" s="142"/>
-      <c r="Z246" s="143"/>
-    </row>
-    <row r="247" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z246" s="140"/>
+      <c r="AA246" s="140"/>
+      <c r="AB246" s="143"/>
+    </row>
+    <row r="247" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C247" s="158"/>
       <c r="D247" s="158"/>
       <c r="E247" s="140"/>
@@ -24972,9 +25476,11 @@
       <c r="W247" s="199"/>
       <c r="X247" s="142"/>
       <c r="Y247" s="142"/>
-      <c r="Z247" s="143"/>
-    </row>
-    <row r="248" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z247" s="140"/>
+      <c r="AA247" s="140"/>
+      <c r="AB247" s="143"/>
+    </row>
+    <row r="248" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C248" s="158"/>
       <c r="D248" s="158"/>
       <c r="E248" s="140"/>
@@ -24998,9 +25504,11 @@
       <c r="W248" s="199"/>
       <c r="X248" s="142"/>
       <c r="Y248" s="142"/>
-      <c r="Z248" s="143"/>
-    </row>
-    <row r="249" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z248" s="140"/>
+      <c r="AA248" s="140"/>
+      <c r="AB248" s="143"/>
+    </row>
+    <row r="249" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C249" s="158"/>
       <c r="D249" s="158"/>
       <c r="E249" s="140"/>
@@ -25024,9 +25532,11 @@
       <c r="W249" s="199"/>
       <c r="X249" s="142"/>
       <c r="Y249" s="142"/>
-      <c r="Z249" s="143"/>
-    </row>
-    <row r="250" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z249" s="140"/>
+      <c r="AA249" s="140"/>
+      <c r="AB249" s="143"/>
+    </row>
+    <row r="250" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C250" s="158"/>
       <c r="D250" s="158"/>
       <c r="E250" s="140"/>
@@ -25050,9 +25560,11 @@
       <c r="W250" s="199"/>
       <c r="X250" s="142"/>
       <c r="Y250" s="142"/>
-      <c r="Z250" s="143"/>
-    </row>
-    <row r="251" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z250" s="140"/>
+      <c r="AA250" s="140"/>
+      <c r="AB250" s="143"/>
+    </row>
+    <row r="251" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C251" s="158"/>
       <c r="D251" s="158"/>
       <c r="E251" s="140"/>
@@ -25076,9 +25588,11 @@
       <c r="W251" s="199"/>
       <c r="X251" s="142"/>
       <c r="Y251" s="142"/>
-      <c r="Z251" s="143"/>
-    </row>
-    <row r="252" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z251" s="140"/>
+      <c r="AA251" s="140"/>
+      <c r="AB251" s="143"/>
+    </row>
+    <row r="252" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C252" s="158"/>
       <c r="D252" s="158"/>
       <c r="E252" s="140"/>
@@ -25102,9 +25616,11 @@
       <c r="W252" s="199"/>
       <c r="X252" s="142"/>
       <c r="Y252" s="142"/>
-      <c r="Z252" s="143"/>
-    </row>
-    <row r="253" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z252" s="140"/>
+      <c r="AA252" s="140"/>
+      <c r="AB252" s="143"/>
+    </row>
+    <row r="253" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C253" s="158"/>
       <c r="D253" s="158"/>
       <c r="E253" s="140"/>
@@ -25128,9 +25644,11 @@
       <c r="W253" s="199"/>
       <c r="X253" s="142"/>
       <c r="Y253" s="142"/>
-      <c r="Z253" s="143"/>
-    </row>
-    <row r="254" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z253" s="140"/>
+      <c r="AA253" s="140"/>
+      <c r="AB253" s="143"/>
+    </row>
+    <row r="254" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C254" s="158"/>
       <c r="D254" s="158"/>
       <c r="E254" s="140"/>
@@ -25154,9 +25672,11 @@
       <c r="W254" s="199"/>
       <c r="X254" s="142"/>
       <c r="Y254" s="142"/>
-      <c r="Z254" s="143"/>
-    </row>
-    <row r="255" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z254" s="140"/>
+      <c r="AA254" s="140"/>
+      <c r="AB254" s="143"/>
+    </row>
+    <row r="255" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C255" s="158"/>
       <c r="D255" s="158"/>
       <c r="E255" s="140"/>
@@ -25180,9 +25700,11 @@
       <c r="W255" s="199"/>
       <c r="X255" s="142"/>
       <c r="Y255" s="142"/>
-      <c r="Z255" s="143"/>
-    </row>
-    <row r="256" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z255" s="140"/>
+      <c r="AA255" s="140"/>
+      <c r="AB255" s="143"/>
+    </row>
+    <row r="256" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C256" s="158"/>
       <c r="D256" s="158"/>
       <c r="E256" s="140"/>
@@ -25206,9 +25728,11 @@
       <c r="W256" s="199"/>
       <c r="X256" s="142"/>
       <c r="Y256" s="142"/>
-      <c r="Z256" s="143"/>
-    </row>
-    <row r="257" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z256" s="140"/>
+      <c r="AA256" s="140"/>
+      <c r="AB256" s="143"/>
+    </row>
+    <row r="257" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C257" s="158"/>
       <c r="D257" s="158"/>
       <c r="E257" s="140"/>
@@ -25232,9 +25756,11 @@
       <c r="W257" s="199"/>
       <c r="X257" s="142"/>
       <c r="Y257" s="142"/>
-      <c r="Z257" s="143"/>
-    </row>
-    <row r="258" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z257" s="140"/>
+      <c r="AA257" s="140"/>
+      <c r="AB257" s="143"/>
+    </row>
+    <row r="258" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C258" s="158"/>
       <c r="D258" s="158"/>
       <c r="E258" s="140"/>
@@ -25258,9 +25784,11 @@
       <c r="W258" s="199"/>
       <c r="X258" s="142"/>
       <c r="Y258" s="142"/>
-      <c r="Z258" s="143"/>
-    </row>
-    <row r="259" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z258" s="140"/>
+      <c r="AA258" s="140"/>
+      <c r="AB258" s="143"/>
+    </row>
+    <row r="259" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C259" s="158"/>
       <c r="D259" s="158"/>
       <c r="E259" s="140"/>
@@ -25284,9 +25812,11 @@
       <c r="W259" s="199"/>
       <c r="X259" s="142"/>
       <c r="Y259" s="142"/>
-      <c r="Z259" s="143"/>
-    </row>
-    <row r="260" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z259" s="140"/>
+      <c r="AA259" s="140"/>
+      <c r="AB259" s="143"/>
+    </row>
+    <row r="260" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C260" s="158"/>
       <c r="D260" s="158"/>
       <c r="E260" s="140"/>
@@ -25310,9 +25840,11 @@
       <c r="W260" s="199"/>
       <c r="X260" s="142"/>
       <c r="Y260" s="142"/>
-      <c r="Z260" s="143"/>
-    </row>
-    <row r="261" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z260" s="140"/>
+      <c r="AA260" s="140"/>
+      <c r="AB260" s="143"/>
+    </row>
+    <row r="261" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C261" s="158"/>
       <c r="D261" s="158"/>
       <c r="E261" s="140"/>
@@ -25336,9 +25868,11 @@
       <c r="W261" s="199"/>
       <c r="X261" s="142"/>
       <c r="Y261" s="142"/>
-      <c r="Z261" s="143"/>
-    </row>
-    <row r="262" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z261" s="140"/>
+      <c r="AA261" s="140"/>
+      <c r="AB261" s="143"/>
+    </row>
+    <row r="262" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C262" s="158"/>
       <c r="D262" s="158"/>
       <c r="E262" s="140"/>
@@ -25362,9 +25896,11 @@
       <c r="W262" s="199"/>
       <c r="X262" s="142"/>
       <c r="Y262" s="142"/>
-      <c r="Z262" s="143"/>
-    </row>
-    <row r="263" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z262" s="140"/>
+      <c r="AA262" s="140"/>
+      <c r="AB262" s="143"/>
+    </row>
+    <row r="263" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C263" s="158"/>
       <c r="D263" s="158"/>
       <c r="E263" s="140"/>
@@ -25388,9 +25924,11 @@
       <c r="W263" s="199"/>
       <c r="X263" s="142"/>
       <c r="Y263" s="142"/>
-      <c r="Z263" s="143"/>
-    </row>
-    <row r="264" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z263" s="140"/>
+      <c r="AA263" s="140"/>
+      <c r="AB263" s="143"/>
+    </row>
+    <row r="264" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C264" s="158"/>
       <c r="D264" s="158"/>
       <c r="E264" s="140"/>
@@ -25414,9 +25952,11 @@
       <c r="W264" s="199"/>
       <c r="X264" s="142"/>
       <c r="Y264" s="142"/>
-      <c r="Z264" s="143"/>
-    </row>
-    <row r="265" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z264" s="140"/>
+      <c r="AA264" s="140"/>
+      <c r="AB264" s="143"/>
+    </row>
+    <row r="265" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C265" s="158"/>
       <c r="D265" s="158"/>
       <c r="E265" s="140"/>
@@ -25440,9 +25980,11 @@
       <c r="W265" s="199"/>
       <c r="X265" s="142"/>
       <c r="Y265" s="142"/>
-      <c r="Z265" s="143"/>
-    </row>
-    <row r="266" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z265" s="140"/>
+      <c r="AA265" s="140"/>
+      <c r="AB265" s="143"/>
+    </row>
+    <row r="266" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C266" s="158"/>
       <c r="D266" s="158"/>
       <c r="E266" s="140"/>
@@ -25466,9 +26008,11 @@
       <c r="W266" s="199"/>
       <c r="X266" s="142"/>
       <c r="Y266" s="142"/>
-      <c r="Z266" s="143"/>
-    </row>
-    <row r="267" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z266" s="140"/>
+      <c r="AA266" s="140"/>
+      <c r="AB266" s="143"/>
+    </row>
+    <row r="267" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C267" s="158"/>
       <c r="D267" s="158"/>
       <c r="E267" s="140"/>
@@ -25492,9 +26036,11 @@
       <c r="W267" s="199"/>
       <c r="X267" s="142"/>
       <c r="Y267" s="142"/>
-      <c r="Z267" s="143"/>
-    </row>
-    <row r="268" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z267" s="140"/>
+      <c r="AA267" s="140"/>
+      <c r="AB267" s="143"/>
+    </row>
+    <row r="268" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C268" s="158"/>
       <c r="D268" s="158"/>
       <c r="E268" s="140"/>
@@ -25518,9 +26064,11 @@
       <c r="W268" s="199"/>
       <c r="X268" s="142"/>
       <c r="Y268" s="142"/>
-      <c r="Z268" s="143"/>
-    </row>
-    <row r="269" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z268" s="140"/>
+      <c r="AA268" s="140"/>
+      <c r="AB268" s="143"/>
+    </row>
+    <row r="269" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C269" s="158"/>
       <c r="D269" s="158"/>
       <c r="E269" s="140"/>
@@ -25544,9 +26092,11 @@
       <c r="W269" s="199"/>
       <c r="X269" s="142"/>
       <c r="Y269" s="142"/>
-      <c r="Z269" s="143"/>
-    </row>
-    <row r="270" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z269" s="140"/>
+      <c r="AA269" s="140"/>
+      <c r="AB269" s="143"/>
+    </row>
+    <row r="270" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C270" s="158"/>
       <c r="D270" s="158"/>
       <c r="E270" s="140"/>
@@ -25570,9 +26120,11 @@
       <c r="W270" s="199"/>
       <c r="X270" s="142"/>
       <c r="Y270" s="142"/>
-      <c r="Z270" s="143"/>
-    </row>
-    <row r="271" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z270" s="140"/>
+      <c r="AA270" s="140"/>
+      <c r="AB270" s="143"/>
+    </row>
+    <row r="271" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C271" s="158"/>
       <c r="D271" s="158"/>
       <c r="E271" s="140"/>
@@ -25596,9 +26148,11 @@
       <c r="W271" s="199"/>
       <c r="X271" s="142"/>
       <c r="Y271" s="142"/>
-      <c r="Z271" s="143"/>
-    </row>
-    <row r="272" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z271" s="140"/>
+      <c r="AA271" s="140"/>
+      <c r="AB271" s="143"/>
+    </row>
+    <row r="272" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C272" s="158"/>
       <c r="D272" s="158"/>
       <c r="E272" s="140"/>
@@ -25622,9 +26176,11 @@
       <c r="W272" s="199"/>
       <c r="X272" s="142"/>
       <c r="Y272" s="142"/>
-      <c r="Z272" s="143"/>
-    </row>
-    <row r="273" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z272" s="140"/>
+      <c r="AA272" s="140"/>
+      <c r="AB272" s="143"/>
+    </row>
+    <row r="273" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C273" s="158"/>
       <c r="D273" s="158"/>
       <c r="E273" s="140"/>
@@ -25648,9 +26204,11 @@
       <c r="W273" s="199"/>
       <c r="X273" s="142"/>
       <c r="Y273" s="142"/>
-      <c r="Z273" s="143"/>
-    </row>
-    <row r="274" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z273" s="140"/>
+      <c r="AA273" s="140"/>
+      <c r="AB273" s="143"/>
+    </row>
+    <row r="274" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C274" s="158"/>
       <c r="D274" s="158"/>
       <c r="E274" s="140"/>
@@ -25674,9 +26232,11 @@
       <c r="W274" s="199"/>
       <c r="X274" s="142"/>
       <c r="Y274" s="142"/>
-      <c r="Z274" s="143"/>
-    </row>
-    <row r="275" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z274" s="140"/>
+      <c r="AA274" s="140"/>
+      <c r="AB274" s="143"/>
+    </row>
+    <row r="275" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C275" s="158"/>
       <c r="D275" s="158"/>
       <c r="E275" s="140"/>
@@ -25700,9 +26260,11 @@
       <c r="W275" s="199"/>
       <c r="X275" s="142"/>
       <c r="Y275" s="142"/>
-      <c r="Z275" s="143"/>
-    </row>
-    <row r="276" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z275" s="140"/>
+      <c r="AA275" s="140"/>
+      <c r="AB275" s="143"/>
+    </row>
+    <row r="276" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C276" s="158"/>
       <c r="D276" s="158"/>
       <c r="E276" s="140"/>
@@ -25726,9 +26288,11 @@
       <c r="W276" s="199"/>
       <c r="X276" s="142"/>
       <c r="Y276" s="142"/>
-      <c r="Z276" s="143"/>
-    </row>
-    <row r="277" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z276" s="140"/>
+      <c r="AA276" s="140"/>
+      <c r="AB276" s="143"/>
+    </row>
+    <row r="277" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C277" s="158"/>
       <c r="D277" s="158"/>
       <c r="E277" s="140"/>
@@ -25752,9 +26316,11 @@
       <c r="W277" s="199"/>
       <c r="X277" s="142"/>
       <c r="Y277" s="142"/>
-      <c r="Z277" s="143"/>
-    </row>
-    <row r="278" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z277" s="140"/>
+      <c r="AA277" s="140"/>
+      <c r="AB277" s="143"/>
+    </row>
+    <row r="278" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C278" s="158"/>
       <c r="D278" s="158"/>
       <c r="E278" s="140"/>
@@ -25778,9 +26344,11 @@
       <c r="W278" s="199"/>
       <c r="X278" s="142"/>
       <c r="Y278" s="142"/>
-      <c r="Z278" s="143"/>
-    </row>
-    <row r="279" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z278" s="140"/>
+      <c r="AA278" s="140"/>
+      <c r="AB278" s="143"/>
+    </row>
+    <row r="279" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C279" s="158"/>
       <c r="D279" s="158"/>
       <c r="E279" s="140"/>
@@ -25804,9 +26372,11 @@
       <c r="W279" s="199"/>
       <c r="X279" s="142"/>
       <c r="Y279" s="142"/>
-      <c r="Z279" s="143"/>
-    </row>
-    <row r="280" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z279" s="140"/>
+      <c r="AA279" s="140"/>
+      <c r="AB279" s="143"/>
+    </row>
+    <row r="280" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C280" s="158"/>
       <c r="D280" s="158"/>
       <c r="E280" s="140"/>
@@ -25830,9 +26400,11 @@
       <c r="W280" s="199"/>
       <c r="X280" s="142"/>
       <c r="Y280" s="142"/>
-      <c r="Z280" s="143"/>
-    </row>
-    <row r="281" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z280" s="140"/>
+      <c r="AA280" s="140"/>
+      <c r="AB280" s="143"/>
+    </row>
+    <row r="281" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C281" s="158"/>
       <c r="D281" s="158"/>
       <c r="E281" s="140"/>
@@ -25856,9 +26428,11 @@
       <c r="W281" s="199"/>
       <c r="X281" s="142"/>
       <c r="Y281" s="142"/>
-      <c r="Z281" s="143"/>
-    </row>
-    <row r="282" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z281" s="140"/>
+      <c r="AA281" s="140"/>
+      <c r="AB281" s="143"/>
+    </row>
+    <row r="282" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C282" s="158"/>
       <c r="D282" s="158"/>
       <c r="E282" s="140"/>
@@ -25882,9 +26456,11 @@
       <c r="W282" s="199"/>
       <c r="X282" s="142"/>
       <c r="Y282" s="142"/>
-      <c r="Z282" s="143"/>
-    </row>
-    <row r="283" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z282" s="140"/>
+      <c r="AA282" s="140"/>
+      <c r="AB282" s="143"/>
+    </row>
+    <row r="283" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C283" s="158"/>
       <c r="D283" s="158"/>
       <c r="E283" s="140"/>
@@ -25908,9 +26484,11 @@
       <c r="W283" s="199"/>
       <c r="X283" s="142"/>
       <c r="Y283" s="142"/>
-      <c r="Z283" s="143"/>
-    </row>
-    <row r="284" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z283" s="140"/>
+      <c r="AA283" s="140"/>
+      <c r="AB283" s="143"/>
+    </row>
+    <row r="284" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C284" s="158"/>
       <c r="D284" s="158"/>
       <c r="E284" s="140"/>
@@ -25934,9 +26512,11 @@
       <c r="W284" s="199"/>
       <c r="X284" s="142"/>
       <c r="Y284" s="142"/>
-      <c r="Z284" s="143"/>
-    </row>
-    <row r="285" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z284" s="140"/>
+      <c r="AA284" s="140"/>
+      <c r="AB284" s="143"/>
+    </row>
+    <row r="285" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C285" s="158"/>
       <c r="D285" s="158"/>
       <c r="E285" s="140"/>
@@ -25960,9 +26540,11 @@
       <c r="W285" s="199"/>
       <c r="X285" s="142"/>
       <c r="Y285" s="142"/>
-      <c r="Z285" s="143"/>
-    </row>
-    <row r="286" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z285" s="140"/>
+      <c r="AA285" s="140"/>
+      <c r="AB285" s="143"/>
+    </row>
+    <row r="286" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C286" s="158"/>
       <c r="D286" s="158"/>
       <c r="E286" s="140"/>
@@ -25986,9 +26568,11 @@
       <c r="W286" s="199"/>
       <c r="X286" s="142"/>
       <c r="Y286" s="142"/>
-      <c r="Z286" s="143"/>
-    </row>
-    <row r="287" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z286" s="140"/>
+      <c r="AA286" s="140"/>
+      <c r="AB286" s="143"/>
+    </row>
+    <row r="287" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C287" s="158"/>
       <c r="D287" s="158"/>
       <c r="E287" s="140"/>
@@ -26012,9 +26596,11 @@
       <c r="W287" s="199"/>
       <c r="X287" s="142"/>
       <c r="Y287" s="142"/>
-      <c r="Z287" s="143"/>
-    </row>
-    <row r="288" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z287" s="140"/>
+      <c r="AA287" s="140"/>
+      <c r="AB287" s="143"/>
+    </row>
+    <row r="288" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C288" s="158"/>
       <c r="D288" s="158"/>
       <c r="E288" s="140"/>
@@ -26038,9 +26624,11 @@
       <c r="W288" s="199"/>
       <c r="X288" s="142"/>
       <c r="Y288" s="142"/>
-      <c r="Z288" s="143"/>
-    </row>
-    <row r="289" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z288" s="140"/>
+      <c r="AA288" s="140"/>
+      <c r="AB288" s="143"/>
+    </row>
+    <row r="289" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C289" s="158"/>
       <c r="D289" s="158"/>
       <c r="E289" s="140"/>
@@ -26064,9 +26652,11 @@
       <c r="W289" s="199"/>
       <c r="X289" s="142"/>
       <c r="Y289" s="142"/>
-      <c r="Z289" s="143"/>
-    </row>
-    <row r="290" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z289" s="140"/>
+      <c r="AA289" s="140"/>
+      <c r="AB289" s="143"/>
+    </row>
+    <row r="290" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C290" s="158"/>
       <c r="D290" s="158"/>
       <c r="E290" s="140"/>
@@ -26090,9 +26680,11 @@
       <c r="W290" s="199"/>
       <c r="X290" s="142"/>
       <c r="Y290" s="142"/>
-      <c r="Z290" s="143"/>
-    </row>
-    <row r="291" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z290" s="140"/>
+      <c r="AA290" s="140"/>
+      <c r="AB290" s="143"/>
+    </row>
+    <row r="291" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C291" s="158"/>
       <c r="D291" s="158"/>
       <c r="E291" s="140"/>
@@ -26116,9 +26708,11 @@
       <c r="W291" s="199"/>
       <c r="X291" s="142"/>
       <c r="Y291" s="142"/>
-      <c r="Z291" s="143"/>
-    </row>
-    <row r="292" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z291" s="140"/>
+      <c r="AA291" s="140"/>
+      <c r="AB291" s="143"/>
+    </row>
+    <row r="292" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C292" s="158"/>
       <c r="D292" s="158"/>
       <c r="E292" s="140"/>
@@ -26142,9 +26736,11 @@
       <c r="W292" s="199"/>
       <c r="X292" s="142"/>
       <c r="Y292" s="142"/>
-      <c r="Z292" s="143"/>
-    </row>
-    <row r="293" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z292" s="140"/>
+      <c r="AA292" s="140"/>
+      <c r="AB292" s="143"/>
+    </row>
+    <row r="293" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C293" s="158"/>
       <c r="D293" s="158"/>
       <c r="E293" s="140"/>
@@ -26168,9 +26764,11 @@
       <c r="W293" s="199"/>
       <c r="X293" s="142"/>
       <c r="Y293" s="142"/>
-      <c r="Z293" s="143"/>
-    </row>
-    <row r="294" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z293" s="140"/>
+      <c r="AA293" s="140"/>
+      <c r="AB293" s="143"/>
+    </row>
+    <row r="294" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C294" s="158"/>
       <c r="D294" s="158"/>
       <c r="E294" s="140"/>
@@ -26194,9 +26792,11 @@
       <c r="W294" s="199"/>
       <c r="X294" s="142"/>
       <c r="Y294" s="142"/>
-      <c r="Z294" s="143"/>
-    </row>
-    <row r="295" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z294" s="140"/>
+      <c r="AA294" s="140"/>
+      <c r="AB294" s="143"/>
+    </row>
+    <row r="295" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C295" s="158"/>
       <c r="D295" s="158"/>
       <c r="E295" s="140"/>
@@ -26220,9 +26820,11 @@
       <c r="W295" s="199"/>
       <c r="X295" s="142"/>
       <c r="Y295" s="142"/>
-      <c r="Z295" s="143"/>
-    </row>
-    <row r="296" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z295" s="140"/>
+      <c r="AA295" s="140"/>
+      <c r="AB295" s="143"/>
+    </row>
+    <row r="296" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C296" s="158"/>
       <c r="D296" s="158"/>
       <c r="E296" s="140"/>
@@ -26246,9 +26848,11 @@
       <c r="W296" s="199"/>
       <c r="X296" s="142"/>
       <c r="Y296" s="142"/>
-      <c r="Z296" s="143"/>
-    </row>
-    <row r="297" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z296" s="140"/>
+      <c r="AA296" s="140"/>
+      <c r="AB296" s="143"/>
+    </row>
+    <row r="297" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C297" s="158"/>
       <c r="D297" s="158"/>
       <c r="E297" s="140"/>
@@ -26272,9 +26876,11 @@
       <c r="W297" s="199"/>
       <c r="X297" s="142"/>
       <c r="Y297" s="142"/>
-      <c r="Z297" s="143"/>
-    </row>
-    <row r="298" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z297" s="140"/>
+      <c r="AA297" s="140"/>
+      <c r="AB297" s="143"/>
+    </row>
+    <row r="298" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C298" s="158"/>
       <c r="D298" s="158"/>
       <c r="E298" s="140"/>
@@ -26298,9 +26904,11 @@
       <c r="W298" s="199"/>
       <c r="X298" s="142"/>
       <c r="Y298" s="142"/>
-      <c r="Z298" s="143"/>
-    </row>
-    <row r="299" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z298" s="140"/>
+      <c r="AA298" s="140"/>
+      <c r="AB298" s="143"/>
+    </row>
+    <row r="299" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C299" s="158"/>
       <c r="D299" s="158"/>
       <c r="E299" s="140"/>
@@ -26324,9 +26932,11 @@
       <c r="W299" s="199"/>
       <c r="X299" s="142"/>
       <c r="Y299" s="142"/>
-      <c r="Z299" s="143"/>
-    </row>
-    <row r="300" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z299" s="140"/>
+      <c r="AA299" s="140"/>
+      <c r="AB299" s="143"/>
+    </row>
+    <row r="300" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C300" s="158"/>
       <c r="D300" s="158"/>
       <c r="E300" s="140"/>
@@ -26350,9 +26960,11 @@
       <c r="W300" s="199"/>
       <c r="X300" s="142"/>
       <c r="Y300" s="142"/>
-      <c r="Z300" s="143"/>
-    </row>
-    <row r="301" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z300" s="140"/>
+      <c r="AA300" s="140"/>
+      <c r="AB300" s="143"/>
+    </row>
+    <row r="301" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C301" s="158"/>
       <c r="D301" s="158"/>
       <c r="E301" s="140"/>
@@ -26376,9 +26988,11 @@
       <c r="W301" s="199"/>
       <c r="X301" s="142"/>
       <c r="Y301" s="142"/>
-      <c r="Z301" s="143"/>
-    </row>
-    <row r="302" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z301" s="140"/>
+      <c r="AA301" s="140"/>
+      <c r="AB301" s="143"/>
+    </row>
+    <row r="302" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C302" s="158"/>
       <c r="D302" s="158"/>
       <c r="E302" s="140"/>
@@ -26402,9 +27016,11 @@
       <c r="W302" s="199"/>
       <c r="X302" s="142"/>
       <c r="Y302" s="142"/>
-      <c r="Z302" s="143"/>
-    </row>
-    <row r="303" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z302" s="140"/>
+      <c r="AA302" s="140"/>
+      <c r="AB302" s="143"/>
+    </row>
+    <row r="303" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C303" s="158"/>
       <c r="D303" s="158"/>
       <c r="E303" s="140"/>
@@ -26428,9 +27044,11 @@
       <c r="W303" s="199"/>
       <c r="X303" s="142"/>
       <c r="Y303" s="142"/>
-      <c r="Z303" s="143"/>
-    </row>
-    <row r="304" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z303" s="140"/>
+      <c r="AA303" s="140"/>
+      <c r="AB303" s="143"/>
+    </row>
+    <row r="304" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C304" s="158"/>
       <c r="D304" s="158"/>
       <c r="E304" s="140"/>
@@ -26454,9 +27072,11 @@
       <c r="W304" s="199"/>
       <c r="X304" s="142"/>
       <c r="Y304" s="142"/>
-      <c r="Z304" s="143"/>
-    </row>
-    <row r="305" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z304" s="140"/>
+      <c r="AA304" s="140"/>
+      <c r="AB304" s="143"/>
+    </row>
+    <row r="305" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C305" s="158"/>
       <c r="D305" s="158"/>
       <c r="E305" s="140"/>
@@ -26480,9 +27100,11 @@
       <c r="W305" s="199"/>
       <c r="X305" s="142"/>
       <c r="Y305" s="142"/>
-      <c r="Z305" s="143"/>
-    </row>
-    <row r="306" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z305" s="140"/>
+      <c r="AA305" s="140"/>
+      <c r="AB305" s="143"/>
+    </row>
+    <row r="306" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C306" s="158"/>
       <c r="D306" s="158"/>
       <c r="E306" s="140"/>
@@ -26506,9 +27128,11 @@
       <c r="W306" s="199"/>
       <c r="X306" s="142"/>
       <c r="Y306" s="142"/>
-      <c r="Z306" s="143"/>
-    </row>
-    <row r="307" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z306" s="140"/>
+      <c r="AA306" s="140"/>
+      <c r="AB306" s="143"/>
+    </row>
+    <row r="307" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C307" s="158"/>
       <c r="D307" s="158"/>
       <c r="E307" s="140"/>
@@ -26532,9 +27156,11 @@
       <c r="W307" s="199"/>
       <c r="X307" s="142"/>
       <c r="Y307" s="142"/>
-      <c r="Z307" s="143"/>
-    </row>
-    <row r="308" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z307" s="140"/>
+      <c r="AA307" s="140"/>
+      <c r="AB307" s="143"/>
+    </row>
+    <row r="308" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C308" s="158"/>
       <c r="D308" s="158"/>
       <c r="E308" s="140"/>
@@ -26558,9 +27184,11 @@
       <c r="W308" s="199"/>
       <c r="X308" s="142"/>
       <c r="Y308" s="142"/>
-      <c r="Z308" s="143"/>
-    </row>
-    <row r="309" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z308" s="140"/>
+      <c r="AA308" s="140"/>
+      <c r="AB308" s="143"/>
+    </row>
+    <row r="309" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C309" s="158"/>
       <c r="D309" s="158"/>
       <c r="E309" s="140"/>
@@ -26584,9 +27212,11 @@
       <c r="W309" s="199"/>
       <c r="X309" s="142"/>
       <c r="Y309" s="142"/>
-      <c r="Z309" s="143"/>
-    </row>
-    <row r="310" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z309" s="140"/>
+      <c r="AA309" s="140"/>
+      <c r="AB309" s="143"/>
+    </row>
+    <row r="310" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C310" s="158"/>
       <c r="D310" s="158"/>
       <c r="E310" s="140"/>
@@ -26610,9 +27240,11 @@
       <c r="W310" s="199"/>
       <c r="X310" s="142"/>
       <c r="Y310" s="142"/>
-      <c r="Z310" s="143"/>
-    </row>
-    <row r="311" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z310" s="140"/>
+      <c r="AA310" s="140"/>
+      <c r="AB310" s="143"/>
+    </row>
+    <row r="311" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C311" s="158"/>
       <c r="D311" s="158"/>
       <c r="E311" s="140"/>
@@ -26636,9 +27268,11 @@
       <c r="W311" s="199"/>
       <c r="X311" s="142"/>
       <c r="Y311" s="142"/>
-      <c r="Z311" s="143"/>
-    </row>
-    <row r="312" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z311" s="140"/>
+      <c r="AA311" s="140"/>
+      <c r="AB311" s="143"/>
+    </row>
+    <row r="312" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C312" s="158"/>
       <c r="D312" s="158"/>
       <c r="E312" s="140"/>
@@ -26662,9 +27296,11 @@
       <c r="W312" s="199"/>
       <c r="X312" s="142"/>
       <c r="Y312" s="142"/>
-      <c r="Z312" s="143"/>
-    </row>
-    <row r="313" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z312" s="140"/>
+      <c r="AA312" s="140"/>
+      <c r="AB312" s="143"/>
+    </row>
+    <row r="313" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C313" s="158"/>
       <c r="D313" s="158"/>
       <c r="E313" s="140"/>
@@ -26688,9 +27324,11 @@
       <c r="W313" s="199"/>
       <c r="X313" s="142"/>
       <c r="Y313" s="142"/>
-      <c r="Z313" s="143"/>
-    </row>
-    <row r="314" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z313" s="140"/>
+      <c r="AA313" s="140"/>
+      <c r="AB313" s="143"/>
+    </row>
+    <row r="314" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C314" s="158"/>
       <c r="D314" s="158"/>
       <c r="E314" s="140"/>
@@ -26714,9 +27352,11 @@
       <c r="W314" s="199"/>
       <c r="X314" s="142"/>
       <c r="Y314" s="142"/>
-      <c r="Z314" s="143"/>
-    </row>
-    <row r="315" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z314" s="140"/>
+      <c r="AA314" s="140"/>
+      <c r="AB314" s="143"/>
+    </row>
+    <row r="315" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C315" s="158"/>
       <c r="D315" s="158"/>
       <c r="E315" s="140"/>
@@ -26740,9 +27380,11 @@
       <c r="W315" s="199"/>
       <c r="X315" s="142"/>
       <c r="Y315" s="142"/>
-      <c r="Z315" s="143"/>
-    </row>
-    <row r="316" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z315" s="140"/>
+      <c r="AA315" s="140"/>
+      <c r="AB315" s="143"/>
+    </row>
+    <row r="316" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C316" s="158"/>
       <c r="D316" s="158"/>
       <c r="E316" s="140"/>
@@ -26766,9 +27408,11 @@
       <c r="W316" s="199"/>
       <c r="X316" s="142"/>
       <c r="Y316" s="142"/>
-      <c r="Z316" s="143"/>
-    </row>
-    <row r="317" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z316" s="140"/>
+      <c r="AA316" s="140"/>
+      <c r="AB316" s="143"/>
+    </row>
+    <row r="317" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C317" s="158"/>
       <c r="D317" s="158"/>
       <c r="E317" s="140"/>
@@ -26792,9 +27436,11 @@
       <c r="W317" s="199"/>
       <c r="X317" s="142"/>
       <c r="Y317" s="142"/>
-      <c r="Z317" s="143"/>
-    </row>
-    <row r="318" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z317" s="140"/>
+      <c r="AA317" s="140"/>
+      <c r="AB317" s="143"/>
+    </row>
+    <row r="318" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C318" s="158"/>
       <c r="D318" s="158"/>
       <c r="E318" s="140"/>
@@ -26818,9 +27464,11 @@
       <c r="W318" s="199"/>
       <c r="X318" s="142"/>
       <c r="Y318" s="142"/>
-      <c r="Z318" s="143"/>
-    </row>
-    <row r="319" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z318" s="140"/>
+      <c r="AA318" s="140"/>
+      <c r="AB318" s="143"/>
+    </row>
+    <row r="319" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C319" s="158"/>
       <c r="D319" s="158"/>
       <c r="E319" s="140"/>
@@ -26844,9 +27492,11 @@
       <c r="W319" s="199"/>
       <c r="X319" s="142"/>
       <c r="Y319" s="142"/>
-      <c r="Z319" s="143"/>
-    </row>
-    <row r="320" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z319" s="140"/>
+      <c r="AA319" s="140"/>
+      <c r="AB319" s="143"/>
+    </row>
+    <row r="320" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C320" s="158"/>
       <c r="D320" s="158"/>
       <c r="E320" s="140"/>
@@ -26870,9 +27520,11 @@
       <c r="W320" s="199"/>
       <c r="X320" s="142"/>
       <c r="Y320" s="142"/>
-      <c r="Z320" s="143"/>
-    </row>
-    <row r="321" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z320" s="140"/>
+      <c r="AA320" s="140"/>
+      <c r="AB320" s="143"/>
+    </row>
+    <row r="321" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C321" s="158"/>
       <c r="D321" s="158"/>
       <c r="E321" s="140"/>
@@ -26896,9 +27548,11 @@
       <c r="W321" s="199"/>
       <c r="X321" s="142"/>
       <c r="Y321" s="142"/>
-      <c r="Z321" s="143"/>
-    </row>
-    <row r="322" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z321" s="140"/>
+      <c r="AA321" s="140"/>
+      <c r="AB321" s="143"/>
+    </row>
+    <row r="322" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C322" s="158"/>
       <c r="D322" s="158"/>
       <c r="E322" s="140"/>
@@ -26922,9 +27576,11 @@
       <c r="W322" s="199"/>
       <c r="X322" s="142"/>
       <c r="Y322" s="142"/>
-      <c r="Z322" s="143"/>
-    </row>
-    <row r="323" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z322" s="140"/>
+      <c r="AA322" s="140"/>
+      <c r="AB322" s="143"/>
+    </row>
+    <row r="323" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C323" s="158"/>
       <c r="D323" s="158"/>
       <c r="E323" s="140"/>
@@ -26948,9 +27604,11 @@
       <c r="W323" s="199"/>
       <c r="X323" s="142"/>
       <c r="Y323" s="142"/>
-      <c r="Z323" s="143"/>
-    </row>
-    <row r="324" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z323" s="140"/>
+      <c r="AA323" s="140"/>
+      <c r="AB323" s="143"/>
+    </row>
+    <row r="324" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C324" s="158"/>
       <c r="D324" s="158"/>
       <c r="E324" s="140"/>
@@ -26974,9 +27632,11 @@
       <c r="W324" s="199"/>
       <c r="X324" s="142"/>
       <c r="Y324" s="142"/>
-      <c r="Z324" s="143"/>
-    </row>
-    <row r="325" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z324" s="140"/>
+      <c r="AA324" s="140"/>
+      <c r="AB324" s="143"/>
+    </row>
+    <row r="325" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C325" s="158"/>
       <c r="D325" s="158"/>
       <c r="E325" s="140"/>
@@ -27000,9 +27660,11 @@
       <c r="W325" s="199"/>
       <c r="X325" s="142"/>
       <c r="Y325" s="142"/>
-      <c r="Z325" s="143"/>
-    </row>
-    <row r="326" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z325" s="140"/>
+      <c r="AA325" s="140"/>
+      <c r="AB325" s="143"/>
+    </row>
+    <row r="326" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C326" s="158"/>
       <c r="D326" s="158"/>
       <c r="E326" s="140"/>
@@ -27026,9 +27688,11 @@
       <c r="W326" s="199"/>
       <c r="X326" s="142"/>
       <c r="Y326" s="142"/>
-      <c r="Z326" s="143"/>
-    </row>
-    <row r="327" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z326" s="140"/>
+      <c r="AA326" s="140"/>
+      <c r="AB326" s="143"/>
+    </row>
+    <row r="327" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C327" s="158"/>
       <c r="D327" s="158"/>
       <c r="E327" s="140"/>
@@ -27052,9 +27716,11 @@
       <c r="W327" s="199"/>
       <c r="X327" s="142"/>
       <c r="Y327" s="142"/>
-      <c r="Z327" s="143"/>
-    </row>
-    <row r="328" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z327" s="140"/>
+      <c r="AA327" s="140"/>
+      <c r="AB327" s="143"/>
+    </row>
+    <row r="328" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C328" s="158"/>
       <c r="D328" s="158"/>
       <c r="E328" s="140"/>
@@ -27078,9 +27744,11 @@
       <c r="W328" s="199"/>
       <c r="X328" s="142"/>
       <c r="Y328" s="142"/>
-      <c r="Z328" s="143"/>
-    </row>
-    <row r="329" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z328" s="140"/>
+      <c r="AA328" s="140"/>
+      <c r="AB328" s="143"/>
+    </row>
+    <row r="329" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C329" s="158"/>
       <c r="D329" s="158"/>
       <c r="E329" s="140"/>
@@ -27104,9 +27772,11 @@
       <c r="W329" s="199"/>
       <c r="X329" s="142"/>
       <c r="Y329" s="142"/>
-      <c r="Z329" s="143"/>
-    </row>
-    <row r="330" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z329" s="140"/>
+      <c r="AA329" s="140"/>
+      <c r="AB329" s="143"/>
+    </row>
+    <row r="330" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C330" s="158"/>
       <c r="D330" s="158"/>
       <c r="E330" s="140"/>
@@ -27130,9 +27800,11 @@
       <c r="W330" s="199"/>
       <c r="X330" s="142"/>
       <c r="Y330" s="142"/>
-      <c r="Z330" s="143"/>
-    </row>
-    <row r="331" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z330" s="140"/>
+      <c r="AA330" s="140"/>
+      <c r="AB330" s="143"/>
+    </row>
+    <row r="331" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C331" s="158"/>
       <c r="D331" s="158"/>
       <c r="E331" s="140"/>
@@ -27156,9 +27828,11 @@
       <c r="W331" s="199"/>
       <c r="X331" s="142"/>
       <c r="Y331" s="142"/>
-      <c r="Z331" s="143"/>
-    </row>
-    <row r="332" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z331" s="140"/>
+      <c r="AA331" s="140"/>
+      <c r="AB331" s="143"/>
+    </row>
+    <row r="332" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C332" s="158"/>
       <c r="D332" s="158"/>
       <c r="E332" s="140"/>
@@ -27182,9 +27856,11 @@
       <c r="W332" s="199"/>
       <c r="X332" s="142"/>
       <c r="Y332" s="142"/>
-      <c r="Z332" s="143"/>
-    </row>
-    <row r="333" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z332" s="140"/>
+      <c r="AA332" s="140"/>
+      <c r="AB332" s="143"/>
+    </row>
+    <row r="333" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C333" s="158"/>
       <c r="D333" s="158"/>
       <c r="E333" s="140"/>
@@ -27208,9 +27884,11 @@
       <c r="W333" s="199"/>
       <c r="X333" s="142"/>
       <c r="Y333" s="142"/>
-      <c r="Z333" s="143"/>
-    </row>
-    <row r="334" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z333" s="140"/>
+      <c r="AA333" s="140"/>
+      <c r="AB333" s="143"/>
+    </row>
+    <row r="334" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C334" s="158"/>
       <c r="D334" s="158"/>
       <c r="E334" s="140"/>
@@ -27234,9 +27912,11 @@
       <c r="W334" s="199"/>
       <c r="X334" s="142"/>
       <c r="Y334" s="142"/>
-      <c r="Z334" s="143"/>
-    </row>
-    <row r="335" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z334" s="140"/>
+      <c r="AA334" s="140"/>
+      <c r="AB334" s="143"/>
+    </row>
+    <row r="335" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C335" s="158"/>
       <c r="D335" s="158"/>
       <c r="E335" s="140"/>
@@ -27260,9 +27940,11 @@
       <c r="W335" s="199"/>
       <c r="X335" s="142"/>
       <c r="Y335" s="142"/>
-      <c r="Z335" s="143"/>
-    </row>
-    <row r="336" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z335" s="140"/>
+      <c r="AA335" s="140"/>
+      <c r="AB335" s="143"/>
+    </row>
+    <row r="336" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C336" s="158"/>
       <c r="D336" s="158"/>
       <c r="E336" s="140"/>
@@ -27286,9 +27968,11 @@
       <c r="W336" s="199"/>
       <c r="X336" s="142"/>
       <c r="Y336" s="142"/>
-      <c r="Z336" s="143"/>
-    </row>
-    <row r="337" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z336" s="140"/>
+      <c r="AA336" s="140"/>
+      <c r="AB336" s="143"/>
+    </row>
+    <row r="337" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C337" s="158"/>
       <c r="D337" s="158"/>
       <c r="E337" s="140"/>
@@ -27312,9 +27996,11 @@
       <c r="W337" s="199"/>
       <c r="X337" s="142"/>
       <c r="Y337" s="142"/>
-      <c r="Z337" s="143"/>
-    </row>
-    <row r="338" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z337" s="140"/>
+      <c r="AA337" s="140"/>
+      <c r="AB337" s="143"/>
+    </row>
+    <row r="338" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C338" s="158"/>
       <c r="D338" s="158"/>
       <c r="E338" s="140"/>
@@ -27338,9 +28024,11 @@
       <c r="W338" s="199"/>
       <c r="X338" s="142"/>
       <c r="Y338" s="142"/>
-      <c r="Z338" s="143"/>
-    </row>
-    <row r="339" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z338" s="140"/>
+      <c r="AA338" s="140"/>
+      <c r="AB338" s="143"/>
+    </row>
+    <row r="339" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C339" s="158"/>
       <c r="D339" s="158"/>
       <c r="E339" s="140"/>
@@ -27364,9 +28052,11 @@
       <c r="W339" s="199"/>
       <c r="X339" s="142"/>
       <c r="Y339" s="142"/>
-      <c r="Z339" s="143"/>
-    </row>
-    <row r="340" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z339" s="140"/>
+      <c r="AA339" s="140"/>
+      <c r="AB339" s="143"/>
+    </row>
+    <row r="340" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C340" s="158"/>
       <c r="D340" s="158"/>
       <c r="E340" s="140"/>
@@ -27390,9 +28080,11 @@
       <c r="W340" s="199"/>
       <c r="X340" s="142"/>
       <c r="Y340" s="142"/>
-      <c r="Z340" s="143"/>
-    </row>
-    <row r="341" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z340" s="140"/>
+      <c r="AA340" s="140"/>
+      <c r="AB340" s="143"/>
+    </row>
+    <row r="341" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C341" s="158"/>
       <c r="D341" s="158"/>
       <c r="E341" s="140"/>
@@ -27416,9 +28108,11 @@
       <c r="W341" s="199"/>
       <c r="X341" s="142"/>
       <c r="Y341" s="142"/>
-      <c r="Z341" s="143"/>
-    </row>
-    <row r="342" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z341" s="140"/>
+      <c r="AA341" s="140"/>
+      <c r="AB341" s="143"/>
+    </row>
+    <row r="342" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C342" s="158"/>
       <c r="D342" s="158"/>
       <c r="E342" s="140"/>
@@ -27442,9 +28136,11 @@
       <c r="W342" s="199"/>
       <c r="X342" s="142"/>
       <c r="Y342" s="142"/>
-      <c r="Z342" s="143"/>
-    </row>
-    <row r="343" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z342" s="140"/>
+      <c r="AA342" s="140"/>
+      <c r="AB342" s="143"/>
+    </row>
+    <row r="343" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C343" s="158"/>
       <c r="D343" s="158"/>
       <c r="E343" s="140"/>
@@ -27468,9 +28164,11 @@
       <c r="W343" s="199"/>
       <c r="X343" s="142"/>
       <c r="Y343" s="142"/>
-      <c r="Z343" s="143"/>
-    </row>
-    <row r="344" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z343" s="140"/>
+      <c r="AA343" s="140"/>
+      <c r="AB343" s="143"/>
+    </row>
+    <row r="344" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C344" s="158"/>
       <c r="D344" s="158"/>
       <c r="E344" s="140"/>
@@ -27494,9 +28192,11 @@
       <c r="W344" s="199"/>
       <c r="X344" s="142"/>
       <c r="Y344" s="142"/>
-      <c r="Z344" s="143"/>
-    </row>
-    <row r="345" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z344" s="140"/>
+      <c r="AA344" s="140"/>
+      <c r="AB344" s="143"/>
+    </row>
+    <row r="345" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C345" s="158"/>
       <c r="D345" s="158"/>
       <c r="E345" s="140"/>
@@ -27520,9 +28220,11 @@
       <c r="W345" s="199"/>
       <c r="X345" s="142"/>
       <c r="Y345" s="142"/>
-      <c r="Z345" s="143"/>
-    </row>
-    <row r="346" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z345" s="140"/>
+      <c r="AA345" s="140"/>
+      <c r="AB345" s="143"/>
+    </row>
+    <row r="346" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C346" s="158"/>
       <c r="D346" s="158"/>
       <c r="E346" s="140"/>
@@ -27546,9 +28248,11 @@
       <c r="W346" s="199"/>
       <c r="X346" s="142"/>
       <c r="Y346" s="142"/>
-      <c r="Z346" s="143"/>
-    </row>
-    <row r="347" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z346" s="140"/>
+      <c r="AA346" s="140"/>
+      <c r="AB346" s="143"/>
+    </row>
+    <row r="347" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C347" s="158"/>
       <c r="D347" s="158"/>
       <c r="E347" s="140"/>
@@ -27572,9 +28276,11 @@
       <c r="W347" s="199"/>
       <c r="X347" s="142"/>
       <c r="Y347" s="142"/>
-      <c r="Z347" s="143"/>
-    </row>
-    <row r="348" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z347" s="140"/>
+      <c r="AA347" s="140"/>
+      <c r="AB347" s="143"/>
+    </row>
+    <row r="348" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C348" s="158"/>
       <c r="D348" s="158"/>
       <c r="E348" s="140"/>
@@ -27598,9 +28304,11 @@
       <c r="W348" s="199"/>
       <c r="X348" s="142"/>
       <c r="Y348" s="142"/>
-      <c r="Z348" s="143"/>
-    </row>
-    <row r="349" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z348" s="140"/>
+      <c r="AA348" s="140"/>
+      <c r="AB348" s="143"/>
+    </row>
+    <row r="349" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C349" s="158"/>
       <c r="D349" s="158"/>
       <c r="E349" s="140"/>
@@ -27624,9 +28332,11 @@
       <c r="W349" s="199"/>
       <c r="X349" s="142"/>
       <c r="Y349" s="142"/>
-      <c r="Z349" s="143"/>
-    </row>
-    <row r="350" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z349" s="140"/>
+      <c r="AA349" s="140"/>
+      <c r="AB349" s="143"/>
+    </row>
+    <row r="350" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C350" s="158"/>
       <c r="D350" s="158"/>
       <c r="E350" s="140"/>
@@ -27650,9 +28360,11 @@
       <c r="W350" s="199"/>
       <c r="X350" s="142"/>
       <c r="Y350" s="142"/>
-      <c r="Z350" s="143"/>
-    </row>
-    <row r="351" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z350" s="140"/>
+      <c r="AA350" s="140"/>
+      <c r="AB350" s="143"/>
+    </row>
+    <row r="351" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C351" s="158"/>
       <c r="D351" s="158"/>
       <c r="E351" s="140"/>
@@ -27676,9 +28388,11 @@
       <c r="W351" s="199"/>
       <c r="X351" s="142"/>
       <c r="Y351" s="142"/>
-      <c r="Z351" s="143"/>
-    </row>
-    <row r="352" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z351" s="140"/>
+      <c r="AA351" s="140"/>
+      <c r="AB351" s="143"/>
+    </row>
+    <row r="352" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C352" s="158"/>
       <c r="D352" s="158"/>
       <c r="E352" s="140"/>
@@ -27702,9 +28416,11 @@
       <c r="W352" s="199"/>
       <c r="X352" s="142"/>
       <c r="Y352" s="142"/>
-      <c r="Z352" s="143"/>
-    </row>
-    <row r="353" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z352" s="140"/>
+      <c r="AA352" s="140"/>
+      <c r="AB352" s="143"/>
+    </row>
+    <row r="353" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C353" s="158"/>
       <c r="D353" s="158"/>
       <c r="E353" s="140"/>
@@ -27728,9 +28444,11 @@
       <c r="W353" s="199"/>
       <c r="X353" s="142"/>
       <c r="Y353" s="142"/>
-      <c r="Z353" s="143"/>
-    </row>
-    <row r="354" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z353" s="140"/>
+      <c r="AA353" s="140"/>
+      <c r="AB353" s="143"/>
+    </row>
+    <row r="354" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C354" s="158"/>
       <c r="D354" s="158"/>
       <c r="E354" s="140"/>
@@ -27754,9 +28472,11 @@
       <c r="W354" s="199"/>
       <c r="X354" s="142"/>
       <c r="Y354" s="142"/>
-      <c r="Z354" s="143"/>
-    </row>
-    <row r="355" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z354" s="140"/>
+      <c r="AA354" s="140"/>
+      <c r="AB354" s="143"/>
+    </row>
+    <row r="355" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C355" s="158"/>
       <c r="D355" s="158"/>
       <c r="E355" s="140"/>
@@ -27780,9 +28500,11 @@
       <c r="W355" s="199"/>
       <c r="X355" s="142"/>
       <c r="Y355" s="142"/>
-      <c r="Z355" s="143"/>
-    </row>
-    <row r="356" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z355" s="140"/>
+      <c r="AA355" s="140"/>
+      <c r="AB355" s="143"/>
+    </row>
+    <row r="356" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C356" s="158"/>
       <c r="D356" s="158"/>
       <c r="E356" s="140"/>
@@ -27806,9 +28528,11 @@
       <c r="W356" s="199"/>
       <c r="X356" s="142"/>
       <c r="Y356" s="142"/>
-      <c r="Z356" s="143"/>
-    </row>
-    <row r="357" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z356" s="140"/>
+      <c r="AA356" s="140"/>
+      <c r="AB356" s="143"/>
+    </row>
+    <row r="357" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C357" s="158"/>
       <c r="D357" s="158"/>
       <c r="E357" s="140"/>
@@ -27832,9 +28556,11 @@
       <c r="W357" s="199"/>
       <c r="X357" s="142"/>
       <c r="Y357" s="142"/>
-      <c r="Z357" s="143"/>
-    </row>
-    <row r="358" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z357" s="140"/>
+      <c r="AA357" s="140"/>
+      <c r="AB357" s="143"/>
+    </row>
+    <row r="358" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C358" s="158"/>
       <c r="D358" s="158"/>
       <c r="E358" s="140"/>
@@ -27858,9 +28584,11 @@
       <c r="W358" s="199"/>
       <c r="X358" s="142"/>
       <c r="Y358" s="142"/>
-      <c r="Z358" s="143"/>
-    </row>
-    <row r="359" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z358" s="140"/>
+      <c r="AA358" s="140"/>
+      <c r="AB358" s="143"/>
+    </row>
+    <row r="359" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C359" s="158"/>
       <c r="D359" s="158"/>
       <c r="E359" s="140"/>
@@ -27884,9 +28612,11 @@
       <c r="W359" s="199"/>
       <c r="X359" s="142"/>
       <c r="Y359" s="142"/>
-      <c r="Z359" s="143"/>
-    </row>
-    <row r="360" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z359" s="140"/>
+      <c r="AA359" s="140"/>
+      <c r="AB359" s="143"/>
+    </row>
+    <row r="360" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C360" s="158"/>
       <c r="D360" s="158"/>
       <c r="E360" s="140"/>
@@ -27910,9 +28640,11 @@
       <c r="W360" s="199"/>
       <c r="X360" s="142"/>
       <c r="Y360" s="142"/>
-      <c r="Z360" s="143"/>
-    </row>
-    <row r="361" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z360" s="140"/>
+      <c r="AA360" s="140"/>
+      <c r="AB360" s="143"/>
+    </row>
+    <row r="361" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C361" s="158"/>
       <c r="D361" s="158"/>
       <c r="E361" s="140"/>
@@ -27936,9 +28668,11 @@
       <c r="W361" s="199"/>
       <c r="X361" s="142"/>
       <c r="Y361" s="142"/>
-      <c r="Z361" s="143"/>
-    </row>
-    <row r="362" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z361" s="140"/>
+      <c r="AA361" s="140"/>
+      <c r="AB361" s="143"/>
+    </row>
+    <row r="362" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C362" s="158"/>
       <c r="D362" s="158"/>
       <c r="E362" s="140"/>
@@ -27962,9 +28696,11 @@
       <c r="W362" s="199"/>
       <c r="X362" s="142"/>
       <c r="Y362" s="142"/>
-      <c r="Z362" s="143"/>
-    </row>
-    <row r="363" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z362" s="140"/>
+      <c r="AA362" s="140"/>
+      <c r="AB362" s="143"/>
+    </row>
+    <row r="363" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C363" s="158"/>
       <c r="D363" s="158"/>
       <c r="E363" s="140"/>
@@ -27988,9 +28724,11 @@
       <c r="W363" s="199"/>
       <c r="X363" s="142"/>
       <c r="Y363" s="142"/>
-      <c r="Z363" s="143"/>
-    </row>
-    <row r="364" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z363" s="140"/>
+      <c r="AA363" s="140"/>
+      <c r="AB363" s="143"/>
+    </row>
+    <row r="364" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C364" s="158"/>
       <c r="D364" s="158"/>
       <c r="E364" s="140"/>
@@ -28014,9 +28752,11 @@
       <c r="W364" s="199"/>
       <c r="X364" s="142"/>
       <c r="Y364" s="142"/>
-      <c r="Z364" s="143"/>
-    </row>
-    <row r="365" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z364" s="140"/>
+      <c r="AA364" s="140"/>
+      <c r="AB364" s="143"/>
+    </row>
+    <row r="365" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C365" s="158"/>
       <c r="D365" s="158"/>
       <c r="E365" s="140"/>
@@ -28040,9 +28780,11 @@
       <c r="W365" s="199"/>
       <c r="X365" s="142"/>
       <c r="Y365" s="142"/>
-      <c r="Z365" s="143"/>
-    </row>
-    <row r="366" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z365" s="140"/>
+      <c r="AA365" s="140"/>
+      <c r="AB365" s="143"/>
+    </row>
+    <row r="366" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C366" s="158"/>
       <c r="D366" s="158"/>
       <c r="E366" s="140"/>
@@ -28066,9 +28808,11 @@
       <c r="W366" s="199"/>
       <c r="X366" s="142"/>
       <c r="Y366" s="142"/>
-      <c r="Z366" s="143"/>
-    </row>
-    <row r="367" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z366" s="140"/>
+      <c r="AA366" s="140"/>
+      <c r="AB366" s="143"/>
+    </row>
+    <row r="367" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C367" s="158"/>
       <c r="D367" s="158"/>
       <c r="E367" s="140"/>
@@ -28092,9 +28836,11 @@
       <c r="W367" s="199"/>
       <c r="X367" s="142"/>
       <c r="Y367" s="142"/>
-      <c r="Z367" s="143"/>
-    </row>
-    <row r="368" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z367" s="140"/>
+      <c r="AA367" s="140"/>
+      <c r="AB367" s="143"/>
+    </row>
+    <row r="368" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C368" s="158"/>
       <c r="D368" s="158"/>
       <c r="E368" s="140"/>
@@ -28118,9 +28864,11 @@
       <c r="W368" s="199"/>
       <c r="X368" s="142"/>
       <c r="Y368" s="142"/>
-      <c r="Z368" s="143"/>
-    </row>
-    <row r="369" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z368" s="140"/>
+      <c r="AA368" s="140"/>
+      <c r="AB368" s="143"/>
+    </row>
+    <row r="369" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C369" s="158"/>
       <c r="D369" s="158"/>
       <c r="E369" s="140"/>
@@ -28144,65 +28892,67 @@
       <c r="W369" s="199"/>
       <c r="X369" s="142"/>
       <c r="Y369" s="142"/>
-      <c r="Z369" s="143"/>
-    </row>
-    <row r="370" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z369" s="140"/>
+      <c r="AA369" s="140"/>
+      <c r="AB369" s="143"/>
+    </row>
+    <row r="370" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R370" s="200"/>
       <c r="S370" s="200"/>
     </row>
-    <row r="371" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R371" s="200"/>
       <c r="S371" s="200"/>
     </row>
-    <row r="372" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R372" s="200"/>
       <c r="S372" s="200"/>
     </row>
-    <row r="373" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R373" s="200"/>
       <c r="S373" s="200"/>
     </row>
-    <row r="374" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R374" s="200"/>
       <c r="S374" s="200"/>
     </row>
-    <row r="375" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R375" s="200"/>
       <c r="S375" s="200"/>
     </row>
-    <row r="376" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R376" s="200"/>
       <c r="S376" s="200"/>
     </row>
-    <row r="377" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R377" s="200"/>
       <c r="S377" s="200"/>
     </row>
-    <row r="378" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R378" s="200"/>
       <c r="S378" s="200"/>
     </row>
-    <row r="379" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R379" s="200"/>
       <c r="S379" s="200"/>
     </row>
-    <row r="380" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R380" s="200"/>
       <c r="S380" s="200"/>
     </row>
-    <row r="381" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R381" s="200"/>
       <c r="S381" s="200"/>
     </row>
-    <row r="382" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R382" s="200"/>
       <c r="S382" s="200"/>
     </row>
-    <row r="383" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R383" s="200"/>
       <c r="S383" s="200"/>
     </row>
-    <row r="384" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="3:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R384" s="200"/>
       <c r="S384" s="200"/>
     </row>
@@ -46691,13 +47441,13 @@
       <c r="S5005" s="200"/>
     </row>
   </sheetData>
-  <autoFilter ref="C4:Z69" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="C4:AB69" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <conditionalFormatting sqref="C5:C5000">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND(C5&lt;&gt;"",COUNTIF($C$5:$C$5000,C5)&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="24">
+  <dataValidations count="26">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Duplicate Trade ID" error="This Trade ID is already used. Enter a unique ID." promptTitle="Trade ID" prompt="Unique ID of the trade. A row without a Trade ID is ignored; a repeated ID rejects the trade." sqref="C5:C5000">
       <formula1>COUNTIF($C$5:$C$5000,C5)=1</formula1>
     </dataValidation>
@@ -46768,8 +47518,14 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid detachment" error="Enter a decimal above the attachment point and at most 1." promptTitle="Detachment D" prompt="CDO tranches only: detachment point, above the attachment and at most 1 (CRE52.42)." sqref="Y5:Y5000">
       <formula1>AND(ISNUMBER(Y5),Y5&gt;0,Y5&lt;=1,OR(X5="",Y5&gt;X5))</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Comment too long" error="Keep the comment to 500 characters or fewer." promptTitle="Comment" prompt="Free text, not read by the engine." sqref="Z5:Z5000">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Comment too long" error="Keep the comment to 500 characters or fewer." promptTitle="Comment" prompt="Free text, not read by the engine." sqref="AB5:AB5000">
       <formula1>500</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid economic trade ID" error="The ID must not contain | or #." promptTitle="Economic trade ID" prompt="Legs of one economic trade share this ID; blank = the row is a whole trade. Use legs for several risk categories or for an option structure split into options." sqref="Z5:Z5000">
+      <formula1>AND(ISERROR(FIND("|",Z5)),ISERROR(FIND("#",Z5)))</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose Y or N." promptTitle="MtM leg" prompt="Y on the one leg that carries the economic trade's MtM; N on every other leg, whose MtM must be 0. Blank on a whole trade." sqref="AA5:AA5000">
+      <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -46834,7 +47590,7 @@
     </row>
     <row r="5">
       <c r="C5" s="30" t="str" cm="1">
-        <f t="array" ref="C5">ResultsStatusText(SACCR_RunInputs,NettingSets!$C:$Q,Trades!$C:$Y,Params!$C:$J)</f>
+        <f t="array" ref="C5">ResultsStatusText(SACCR_RunInputs,NettingSets!$C:$Q,Trades!$C:$AA,Params!$C:$J)</f>
         <v>No results: press Run SA-CCR.</v>
       </c>
     </row>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -6936,8 +6936,8 @@
       <c r="E8" s="125">
         <v>7.8693868057473324</v>
       </c>
-      <c r="F8" s="125">
-        <f>SACCR_SupervisoryDuration(0,10)</f>
+      <c r="F8" s="125" cm="1">
+        <f t="array" ref="F8">SACCR_SupervisoryDuration(0,10)</f>
         <v>7.8693868057473315</v>
       </c>
       <c r="G8" s="126">
@@ -6959,8 +6959,8 @@
       <c r="E9" s="125">
         <v>7.4855922824045473</v>
       </c>
-      <c r="F9" s="125">
-        <f>SACCR_SupervisoryDuration(1,11)</f>
+      <c r="F9" s="125" cm="1">
+        <f t="array" ref="F9">SACCR_SupervisoryDuration(1,11)</f>
         <v>7.4855922824045473</v>
       </c>
       <c r="G9" s="126">
@@ -6982,8 +6982,8 @@
       <c r="E10" s="125">
         <v>0.04</v>
       </c>
-      <c r="F10" s="125">
-        <f>SACCR_SupervisoryDuration(0,0.01,10/250)</f>
+      <c r="F10" s="125" cm="1">
+        <f t="array" ref="F10">SACCR_SupervisoryDuration(0,0.01,10/250)</f>
         <v>0.04</v>
       </c>
       <c r="G10" s="126">
@@ -7005,8 +7005,8 @@
       <c r="E11" s="125">
         <v>0.8660254037844386</v>
       </c>
-      <c r="F11" s="125">
-        <f>SACCR_MaturityFactor(0.75)</f>
+      <c r="F11" s="125" cm="1">
+        <f t="array" ref="F11">SACCR_MaturityFactor(0.75)</f>
         <v>0.8660254037844386</v>
       </c>
       <c r="G11" s="126">
@@ -7028,8 +7028,8 @@
       <c r="E12" s="125">
         <v>0.2</v>
       </c>
-      <c r="F12" s="125">
-        <f>SACCR_MaturityFactor(3/365)</f>
+      <c r="F12" s="125" cm="1">
+        <f t="array" ref="F12">SACCR_MaturityFactor(3/365)</f>
         <v>0.2</v>
       </c>
       <c r="G12" s="126">
@@ -7051,8 +7051,8 @@
       <c r="E13" s="125">
         <v>0.3</v>
       </c>
-      <c r="F13" s="125">
-        <f>SACCR_MaturityFactor(0,TRUE,10)</f>
+      <c r="F13" s="125" cm="1">
+        <f t="array" ref="F13">SACCR_MaturityFactor(0,TRUE,10)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="G13" s="126">
@@ -7074,8 +7074,8 @@
       <c r="E14" s="125">
         <v>-0.26939521771053271</v>
       </c>
-      <c r="F14" s="125">
-        <f>SACCR_OptionDelta(0.06,0.05,1,0.5,FALSE,TRUE)</f>
+      <c r="F14" s="125" cm="1">
+        <f t="array" ref="F14">SACCR_OptionDelta(0.06,0.05,1,0.5,FALSE,TRUE)</f>
         <v>-0.26939521771053271</v>
       </c>
       <c r="G14" s="126">
@@ -7097,8 +7097,8 @@
       <c r="E15" s="125">
         <v>-0.37901134582780288</v>
       </c>
-      <c r="F15" s="125">
-        <f>SACCR_OptionDelta(100,110,0.5,0.32,TRUE,FALSE)</f>
+      <c r="F15" s="125" cm="1">
+        <f t="array" ref="F15">SACCR_OptionDelta(100,110,0.5,0.32,TRUE,FALSE)</f>
         <v>-0.37901134582780294</v>
       </c>
       <c r="G15" s="126">
@@ -7120,8 +7120,8 @@
       <c r="E16" s="125">
         <v>0.46143935794124907</v>
       </c>
-      <c r="F16" s="125">
-        <f>SACCR_OptionDelta(-0.002,0.001,2,0.5,TRUE,TRUE,0.01)</f>
+      <c r="F16" s="125" cm="1">
+        <f t="array" ref="F16">SACCR_OptionDelta(-0.002,0.001,2,0.5,TRUE,TRUE,0.01)</f>
         <v>0.46143935794124913</v>
       </c>
       <c r="G16" s="126">
@@ -7143,8 +7143,8 @@
       <c r="E17" s="125">
         <v>5.740967544396816</v>
       </c>
-      <c r="F17" s="125">
-        <f>SACCR_CDODelta(0.03,0.06,TRUE)</f>
+      <c r="F17" s="125" cm="1">
+        <f t="array" ref="F17">SACCR_CDODelta(0.03,0.06,TRUE)</f>
         <v>5.740967544396816</v>
       </c>
       <c r="G17" s="126">
@@ -7166,8 +7166,8 @@
       <c r="E18" s="125">
         <v>59269.963463710403</v>
       </c>
-      <c r="F18" s="125">
-        <f>SACCR_IREffectiveNotional(0,-36253.8493844036,78693.8680574733)</f>
+      <c r="F18" s="125" cm="1">
+        <f t="array" ref="F18">SACCR_IREffectiveNotional(0,-36253.8493844036,78693.8680574733)</f>
         <v>59269.963463710395</v>
       </c>
       <c r="G18" s="126">
@@ -7189,8 +7189,8 @@
       <c r="E19" s="125">
         <v>282.1288318596666</v>
       </c>
-      <c r="F19" s="125">
-        <f>SACCR_FactorAggregation({105.861937916956,-279.916321663744,168.111404865732},{0.5,0.5,0.8})</f>
+      <c r="F19" s="125" cm="1">
+        <f t="array" ref="F19">SACCR_FactorAggregation({105.861937916956,-279.916321663744,168.111404865732},{0.5,0.5,0.8})</f>
         <v>282.12883185966604</v>
       </c>
       <c r="G19" s="126">
@@ -7212,8 +7212,8 @@
       <c r="E20" s="125">
         <v>0.96519268118719448</v>
       </c>
-      <c r="F20" s="125">
-        <f>SACCR_Multiplier(-20,282)</f>
+      <c r="F20" s="125" cm="1">
+        <f t="array" ref="F20">SACCR_Multiplier(-20,282)</f>
         <v>0.96519268118719448</v>
       </c>
       <c r="G20" s="126">
@@ -7235,8 +7235,8 @@
       <c r="E21" s="125">
         <v>1</v>
       </c>
-      <c r="F21" s="125">
-        <f>SACCR_Multiplier(10,282)</f>
+      <c r="F21" s="125" cm="1">
+        <f t="array" ref="F21">SACCR_Multiplier(10,282)</f>
         <v>1</v>
       </c>
       <c r="G21" s="126">
@@ -7258,8 +7258,8 @@
       <c r="E22" s="125">
         <v>8</v>
       </c>
-      <c r="F22" s="125">
-        <f>SACCR_ReplacementCost(5,10,TRUE,0,10,2)</f>
+      <c r="F22" s="125" cm="1">
+        <f t="array" ref="F22">SACCR_ReplacementCost(5,10,TRUE,0,10,2)</f>
         <v>8</v>
       </c>
       <c r="G22" s="126">
@@ -7281,8 +7281,8 @@
       <c r="E23" s="125">
         <v>0.97500210485177952</v>
       </c>
-      <c r="F23" s="125">
-        <f>SACCR_NormCDF(1.96)</f>
+      <c r="F23" s="125" cm="1">
+        <f t="array" ref="F23">SACCR_NormCDF(1.96)</f>
         <v>0.97500210485177952</v>
       </c>
       <c r="G23" s="126">
@@ -7304,8 +7304,8 @@
       <c r="E24" s="125">
         <v>6.2209605742718194E-16</v>
       </c>
-      <c r="F24" s="125">
-        <f>SACCR_NormCDF(-8)</f>
+      <c r="F24" s="125" cm="1">
+        <f t="array" ref="F24">SACCR_NormCDF(-8)</f>
         <v>6.2209605201427843E-16</v>
       </c>
       <c r="G24" s="126">
@@ -7327,8 +7327,8 @@
       <c r="E25" s="125">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F25" s="125">
-        <f>SACCR_LambdaCRR(-0.002,0.001,TRUE)</f>
+      <c r="F25" s="125" cm="1">
+        <f t="array" ref="F25">SACCR_LambdaCRR(-0.002,0.001,TRUE)</f>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="G25" s="126">
@@ -7350,8 +7350,8 @@
       <c r="E26" s="125">
         <v>0</v>
       </c>
-      <c r="F26" s="125">
-        <f>SACCR_LambdaCRR(0.02,0.03,TRUE)</f>
+      <c r="F26" s="125" cm="1">
+        <f t="array" ref="F26">SACCR_LambdaCRR(0.02,0.03,TRUE)</f>
         <v>0</v>
       </c>
       <c r="G26" s="126">
@@ -7373,8 +7373,8 @@
       <c r="E27" s="125">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="F27" s="125">
-        <f>SACCR_LambdaCRR(0.0005,0.01,TRUE)</f>
+      <c r="F27" s="125" cm="1">
+        <f t="array" ref="F27">SACCR_LambdaCRR(0.0005,0.01,TRUE)</f>
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="G27" s="126">
@@ -7396,8 +7396,8 @@
       <c r="E28" s="125">
         <v>5.5</v>
       </c>
-      <c r="F28" s="125">
-        <f>SACCR_LambdaCRR(-5,-4,FALSE)</f>
+      <c r="F28" s="125" cm="1">
+        <f t="array" ref="F28">SACCR_LambdaCRR(-5,-4,FALSE)</f>
         <v>5.5</v>
       </c>
       <c r="G28" s="126">
@@ -7419,8 +7419,8 @@
       <c r="E29" s="125">
         <v>0</v>
       </c>
-      <c r="F29" s="125">
-        <f>SACCR_LambdaCRR(40,35,FALSE)</f>
+      <c r="F29" s="125" cm="1">
+        <f t="array" ref="F29">SACCR_LambdaCRR(40,35,FALSE)</f>
         <v>0</v>
       </c>
       <c r="G29" s="126">

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -6930,8 +6930,9 @@
       <c r="C8" s="128" t="s">
         <v>516</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>517</v>
+      <c r="D8" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F8)</f>
+        <v>=SACCR_SupervisoryDuration(0,10)</v>
       </c>
       <c r="E8" s="125">
         <v>7.8693868057473324</v>
@@ -6953,8 +6954,9 @@
       <c r="C9" s="128" t="s">
         <v>518</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>519</v>
+      <c r="D9" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F9)</f>
+        <v>=SACCR_SupervisoryDuration(1,11)</v>
       </c>
       <c r="E9" s="125">
         <v>7.4855922824045473</v>
@@ -6976,8 +6978,9 @@
       <c r="C10" s="128" t="s">
         <v>520</v>
       </c>
-      <c r="D10" s="24" t="s">
-        <v>521</v>
+      <c r="D10" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F10)</f>
+        <v>=SACCR_SupervisoryDuration(0,0.01,10/250)</v>
       </c>
       <c r="E10" s="125">
         <v>0.04</v>
@@ -6999,8 +7002,9 @@
       <c r="C11" s="128" t="s">
         <v>522</v>
       </c>
-      <c r="D11" s="24" t="s">
-        <v>523</v>
+      <c r="D11" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F11)</f>
+        <v>=SACCR_MaturityFactor(0.75)</v>
       </c>
       <c r="E11" s="125">
         <v>0.8660254037844386</v>
@@ -7022,8 +7026,9 @@
       <c r="C12" s="128" t="s">
         <v>524</v>
       </c>
-      <c r="D12" s="24" t="s">
-        <v>525</v>
+      <c r="D12" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F12)</f>
+        <v>=SACCR_MaturityFactor(3/365)</v>
       </c>
       <c r="E12" s="125">
         <v>0.2</v>
@@ -7045,8 +7050,9 @@
       <c r="C13" s="128" t="s">
         <v>526</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>527</v>
+      <c r="D13" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F13)</f>
+        <v>=SACCR_MaturityFactor(0,TRUE,10)</v>
       </c>
       <c r="E13" s="125">
         <v>0.3</v>
@@ -7068,8 +7074,9 @@
       <c r="C14" s="128" t="s">
         <v>528</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>529</v>
+      <c r="D14" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F14)</f>
+        <v>=SACCR_OptionDelta(0.06,0.05,1,0.5,FALSE,TRUE)</v>
       </c>
       <c r="E14" s="125">
         <v>-0.26939521771053271</v>
@@ -7091,8 +7098,9 @@
       <c r="C15" s="128" t="s">
         <v>530</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>531</v>
+      <c r="D15" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F15)</f>
+        <v>=SACCR_OptionDelta(100,110,0.5,0.32,TRUE,FALSE)</v>
       </c>
       <c r="E15" s="125">
         <v>-0.37901134582780288</v>
@@ -7114,8 +7122,9 @@
       <c r="C16" s="128" t="s">
         <v>532</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>533</v>
+      <c r="D16" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F16)</f>
+        <v>=SACCR_OptionDelta(-0.002,0.001,2,0.5,TRUE,TRUE,0.01)</v>
       </c>
       <c r="E16" s="125">
         <v>0.46143935794124907</v>
@@ -7137,8 +7146,9 @@
       <c r="C17" s="128" t="s">
         <v>534</v>
       </c>
-      <c r="D17" s="24" t="s">
-        <v>535</v>
+      <c r="D17" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F17)</f>
+        <v>=SACCR_CDODelta(0.03,0.06,TRUE)</v>
       </c>
       <c r="E17" s="125">
         <v>5.740967544396816</v>
@@ -7160,8 +7170,9 @@
       <c r="C18" s="128" t="s">
         <v>536</v>
       </c>
-      <c r="D18" s="24" t="s">
-        <v>537</v>
+      <c r="D18" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F18)</f>
+        <v>=SACCR_IREffectiveNotional(0,-36253.8493844036,78693.8680574733)</v>
       </c>
       <c r="E18" s="125">
         <v>59269.963463710403</v>
@@ -7183,8 +7194,9 @@
       <c r="C19" s="128" t="s">
         <v>538</v>
       </c>
-      <c r="D19" s="24" t="s">
-        <v>539</v>
+      <c r="D19" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F19)</f>
+        <v>=SACCR_FactorAggregation({105.861937916956,-279.916321663744,168.111404865732},{0.5,0.5,0.8})</v>
       </c>
       <c r="E19" s="125">
         <v>282.1288318596666</v>
@@ -7206,8 +7218,9 @@
       <c r="C20" s="128" t="s">
         <v>540</v>
       </c>
-      <c r="D20" s="24" t="s">
-        <v>541</v>
+      <c r="D20" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F20)</f>
+        <v>=SACCR_Multiplier(-20,282)</v>
       </c>
       <c r="E20" s="125">
         <v>0.96519268118719448</v>
@@ -7229,8 +7242,9 @@
       <c r="C21" s="128" t="s">
         <v>542</v>
       </c>
-      <c r="D21" s="24" t="s">
-        <v>543</v>
+      <c r="D21" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F21)</f>
+        <v>=SACCR_Multiplier(10,282)</v>
       </c>
       <c r="E21" s="125">
         <v>1</v>
@@ -7252,8 +7266,9 @@
       <c r="C22" s="128" t="s">
         <v>544</v>
       </c>
-      <c r="D22" s="24" t="s">
-        <v>545</v>
+      <c r="D22" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F22)</f>
+        <v>=SACCR_ReplacementCost(5,10,TRUE,0,10,2)</v>
       </c>
       <c r="E22" s="125">
         <v>8</v>
@@ -7275,8 +7290,9 @@
       <c r="C23" s="128" t="s">
         <v>546</v>
       </c>
-      <c r="D23" s="24" t="s">
-        <v>547</v>
+      <c r="D23" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F23)</f>
+        <v>=SACCR_NormCDF(1.96)</v>
       </c>
       <c r="E23" s="125">
         <v>0.97500210485177952</v>
@@ -7298,8 +7314,9 @@
       <c r="C24" s="128" t="s">
         <v>548</v>
       </c>
-      <c r="D24" s="24" t="s">
-        <v>549</v>
+      <c r="D24" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F24)</f>
+        <v>=SACCR_NormCDF(-8)</v>
       </c>
       <c r="E24" s="125">
         <v>6.2209605742718194E-16</v>
@@ -7321,8 +7338,9 @@
       <c r="C25" s="128" t="s">
         <v>550</v>
       </c>
-      <c r="D25" s="24" t="s">
-        <v>551</v>
+      <c r="D25" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F25)</f>
+        <v>=SACCR_LambdaCRR(-0.002,0.001,TRUE)</v>
       </c>
       <c r="E25" s="125">
         <v>3.0000000000000001E-3</v>
@@ -7344,8 +7362,9 @@
       <c r="C26" s="128" t="s">
         <v>552</v>
       </c>
-      <c r="D26" s="24" t="s">
-        <v>553</v>
+      <c r="D26" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F26)</f>
+        <v>=SACCR_LambdaCRR(0.02,0.03,TRUE)</v>
       </c>
       <c r="E26" s="125">
         <v>0</v>
@@ -7367,8 +7386,9 @@
       <c r="C27" s="128" t="s">
         <v>554</v>
       </c>
-      <c r="D27" s="24" t="s">
-        <v>555</v>
+      <c r="D27" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F27)</f>
+        <v>=SACCR_LambdaCRR(0.0005,0.01,TRUE)</v>
       </c>
       <c r="E27" s="125">
         <v>5.0000000000000001E-4</v>
@@ -7390,8 +7410,9 @@
       <c r="C28" s="128" t="s">
         <v>556</v>
       </c>
-      <c r="D28" s="24" t="s">
-        <v>557</v>
+      <c r="D28" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F28)</f>
+        <v>=SACCR_LambdaCRR(-5,-4,FALSE)</v>
       </c>
       <c r="E28" s="125">
         <v>5.5</v>
@@ -7413,8 +7434,9 @@
       <c r="C29" s="128" t="s">
         <v>558</v>
       </c>
-      <c r="D29" s="24" t="s">
-        <v>559</v>
+      <c r="D29" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F29)</f>
+        <v>=SACCR_LambdaCRR(40,35,FALSE)</v>
       </c>
       <c r="E29" s="125">
         <v>0</v>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -6930,14 +6930,15 @@
       <c r="C8" s="128" t="s">
         <v>516</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>517</v>
+      <c r="D8" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F8)</f>
+        <v>=SACCR_SupervisoryDuration(0,10)</v>
       </c>
       <c r="E8" s="125">
         <v>7.8693868057473324</v>
       </c>
-      <c r="F8" s="125">
-        <f>SACCR_SupervisoryDuration(0,10)</f>
+      <c r="F8" s="125" cm="1">
+        <f t="array" ref="F8">SACCR_SupervisoryDuration(0,10)</f>
         <v>7.8693868057473315</v>
       </c>
       <c r="G8" s="126">
@@ -6953,14 +6954,15 @@
       <c r="C9" s="128" t="s">
         <v>518</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>519</v>
+      <c r="D9" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F9)</f>
+        <v>=SACCR_SupervisoryDuration(1,11)</v>
       </c>
       <c r="E9" s="125">
         <v>7.4855922824045473</v>
       </c>
-      <c r="F9" s="125">
-        <f>SACCR_SupervisoryDuration(1,11)</f>
+      <c r="F9" s="125" cm="1">
+        <f t="array" ref="F9">SACCR_SupervisoryDuration(1,11)</f>
         <v>7.4855922824045473</v>
       </c>
       <c r="G9" s="126">
@@ -6976,14 +6978,15 @@
       <c r="C10" s="128" t="s">
         <v>520</v>
       </c>
-      <c r="D10" s="24" t="s">
-        <v>521</v>
+      <c r="D10" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F10)</f>
+        <v>=SACCR_SupervisoryDuration(0,0.01,10/250)</v>
       </c>
       <c r="E10" s="125">
         <v>0.04</v>
       </c>
-      <c r="F10" s="125">
-        <f>SACCR_SupervisoryDuration(0,0.01,10/250)</f>
+      <c r="F10" s="125" cm="1">
+        <f t="array" ref="F10">SACCR_SupervisoryDuration(0,0.01,10/250)</f>
         <v>0.04</v>
       </c>
       <c r="G10" s="126">
@@ -6999,14 +7002,15 @@
       <c r="C11" s="128" t="s">
         <v>522</v>
       </c>
-      <c r="D11" s="24" t="s">
-        <v>523</v>
+      <c r="D11" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F11)</f>
+        <v>=SACCR_MaturityFactor(0.75)</v>
       </c>
       <c r="E11" s="125">
         <v>0.8660254037844386</v>
       </c>
-      <c r="F11" s="125">
-        <f>SACCR_MaturityFactor(0.75)</f>
+      <c r="F11" s="125" cm="1">
+        <f t="array" ref="F11">SACCR_MaturityFactor(0.75)</f>
         <v>0.8660254037844386</v>
       </c>
       <c r="G11" s="126">
@@ -7022,14 +7026,15 @@
       <c r="C12" s="128" t="s">
         <v>524</v>
       </c>
-      <c r="D12" s="24" t="s">
-        <v>525</v>
+      <c r="D12" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F12)</f>
+        <v>=SACCR_MaturityFactor(3/365)</v>
       </c>
       <c r="E12" s="125">
         <v>0.2</v>
       </c>
-      <c r="F12" s="125">
-        <f>SACCR_MaturityFactor(3/365)</f>
+      <c r="F12" s="125" cm="1">
+        <f t="array" ref="F12">SACCR_MaturityFactor(3/365)</f>
         <v>0.2</v>
       </c>
       <c r="G12" s="126">
@@ -7045,14 +7050,15 @@
       <c r="C13" s="128" t="s">
         <v>526</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>527</v>
+      <c r="D13" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F13)</f>
+        <v>=SACCR_MaturityFactor(0,TRUE,10)</v>
       </c>
       <c r="E13" s="125">
         <v>0.3</v>
       </c>
-      <c r="F13" s="125">
-        <f>SACCR_MaturityFactor(0,TRUE,10)</f>
+      <c r="F13" s="125" cm="1">
+        <f t="array" ref="F13">SACCR_MaturityFactor(0,TRUE,10)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="G13" s="126">
@@ -7068,14 +7074,15 @@
       <c r="C14" s="128" t="s">
         <v>528</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>529</v>
+      <c r="D14" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F14)</f>
+        <v>=SACCR_OptionDelta(0.06,0.05,1,0.5,FALSE,TRUE)</v>
       </c>
       <c r="E14" s="125">
         <v>-0.26939521771053271</v>
       </c>
-      <c r="F14" s="125">
-        <f>SACCR_OptionDelta(0.06,0.05,1,0.5,FALSE,TRUE)</f>
+      <c r="F14" s="125" cm="1">
+        <f t="array" ref="F14">SACCR_OptionDelta(0.06,0.05,1,0.5,FALSE,TRUE)</f>
         <v>-0.26939521771053271</v>
       </c>
       <c r="G14" s="126">
@@ -7091,14 +7098,15 @@
       <c r="C15" s="128" t="s">
         <v>530</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>531</v>
+      <c r="D15" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F15)</f>
+        <v>=SACCR_OptionDelta(100,110,0.5,0.32,TRUE,FALSE)</v>
       </c>
       <c r="E15" s="125">
         <v>-0.37901134582780288</v>
       </c>
-      <c r="F15" s="125">
-        <f>SACCR_OptionDelta(100,110,0.5,0.32,TRUE,FALSE)</f>
+      <c r="F15" s="125" cm="1">
+        <f t="array" ref="F15">SACCR_OptionDelta(100,110,0.5,0.32,TRUE,FALSE)</f>
         <v>-0.37901134582780294</v>
       </c>
       <c r="G15" s="126">
@@ -7114,14 +7122,15 @@
       <c r="C16" s="128" t="s">
         <v>532</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>533</v>
+      <c r="D16" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F16)</f>
+        <v>=SACCR_OptionDelta(-0.002,0.001,2,0.5,TRUE,TRUE,0.01)</v>
       </c>
       <c r="E16" s="125">
         <v>0.46143935794124907</v>
       </c>
-      <c r="F16" s="125">
-        <f>SACCR_OptionDelta(-0.002,0.001,2,0.5,TRUE,TRUE,0.01)</f>
+      <c r="F16" s="125" cm="1">
+        <f t="array" ref="F16">SACCR_OptionDelta(-0.002,0.001,2,0.5,TRUE,TRUE,0.01)</f>
         <v>0.46143935794124913</v>
       </c>
       <c r="G16" s="126">
@@ -7137,14 +7146,15 @@
       <c r="C17" s="128" t="s">
         <v>534</v>
       </c>
-      <c r="D17" s="24" t="s">
-        <v>535</v>
+      <c r="D17" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F17)</f>
+        <v>=SACCR_CDODelta(0.03,0.06,TRUE)</v>
       </c>
       <c r="E17" s="125">
         <v>5.740967544396816</v>
       </c>
-      <c r="F17" s="125">
-        <f>SACCR_CDODelta(0.03,0.06,TRUE)</f>
+      <c r="F17" s="125" cm="1">
+        <f t="array" ref="F17">SACCR_CDODelta(0.03,0.06,TRUE)</f>
         <v>5.740967544396816</v>
       </c>
       <c r="G17" s="126">
@@ -7160,14 +7170,15 @@
       <c r="C18" s="128" t="s">
         <v>536</v>
       </c>
-      <c r="D18" s="24" t="s">
-        <v>537</v>
+      <c r="D18" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F18)</f>
+        <v>=SACCR_IREffectiveNotional(0,-36253.8493844036,78693.8680574733)</v>
       </c>
       <c r="E18" s="125">
         <v>59269.963463710403</v>
       </c>
-      <c r="F18" s="125">
-        <f>SACCR_IREffectiveNotional(0,-36253.8493844036,78693.8680574733)</f>
+      <c r="F18" s="125" cm="1">
+        <f t="array" ref="F18">SACCR_IREffectiveNotional(0,-36253.8493844036,78693.8680574733)</f>
         <v>59269.963463710395</v>
       </c>
       <c r="G18" s="126">
@@ -7183,14 +7194,15 @@
       <c r="C19" s="128" t="s">
         <v>538</v>
       </c>
-      <c r="D19" s="24" t="s">
-        <v>539</v>
+      <c r="D19" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F19)</f>
+        <v>=SACCR_FactorAggregation({105.861937916956,-279.916321663744,168.111404865732},{0.5,0.5,0.8})</v>
       </c>
       <c r="E19" s="125">
         <v>282.1288318596666</v>
       </c>
-      <c r="F19" s="125">
-        <f>SACCR_FactorAggregation({105.861937916956,-279.916321663744,168.111404865732},{0.5,0.5,0.8})</f>
+      <c r="F19" s="125" cm="1">
+        <f t="array" ref="F19">SACCR_FactorAggregation({105.861937916956,-279.916321663744,168.111404865732},{0.5,0.5,0.8})</f>
         <v>282.12883185966604</v>
       </c>
       <c r="G19" s="126">
@@ -7206,14 +7218,15 @@
       <c r="C20" s="128" t="s">
         <v>540</v>
       </c>
-      <c r="D20" s="24" t="s">
-        <v>541</v>
+      <c r="D20" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F20)</f>
+        <v>=SACCR_Multiplier(-20,282)</v>
       </c>
       <c r="E20" s="125">
         <v>0.96519268118719448</v>
       </c>
-      <c r="F20" s="125">
-        <f>SACCR_Multiplier(-20,282)</f>
+      <c r="F20" s="125" cm="1">
+        <f t="array" ref="F20">SACCR_Multiplier(-20,282)</f>
         <v>0.96519268118719448</v>
       </c>
       <c r="G20" s="126">
@@ -7229,14 +7242,15 @@
       <c r="C21" s="128" t="s">
         <v>542</v>
       </c>
-      <c r="D21" s="24" t="s">
-        <v>543</v>
+      <c r="D21" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F21)</f>
+        <v>=SACCR_Multiplier(10,282)</v>
       </c>
       <c r="E21" s="125">
         <v>1</v>
       </c>
-      <c r="F21" s="125">
-        <f>SACCR_Multiplier(10,282)</f>
+      <c r="F21" s="125" cm="1">
+        <f t="array" ref="F21">SACCR_Multiplier(10,282)</f>
         <v>1</v>
       </c>
       <c r="G21" s="126">
@@ -7252,14 +7266,15 @@
       <c r="C22" s="128" t="s">
         <v>544</v>
       </c>
-      <c r="D22" s="24" t="s">
-        <v>545</v>
+      <c r="D22" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F22)</f>
+        <v>=SACCR_ReplacementCost(5,10,TRUE,0,10,2)</v>
       </c>
       <c r="E22" s="125">
         <v>8</v>
       </c>
-      <c r="F22" s="125">
-        <f>SACCR_ReplacementCost(5,10,TRUE,0,10,2)</f>
+      <c r="F22" s="125" cm="1">
+        <f t="array" ref="F22">SACCR_ReplacementCost(5,10,TRUE,0,10,2)</f>
         <v>8</v>
       </c>
       <c r="G22" s="126">
@@ -7275,14 +7290,15 @@
       <c r="C23" s="128" t="s">
         <v>546</v>
       </c>
-      <c r="D23" s="24" t="s">
-        <v>547</v>
+      <c r="D23" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F23)</f>
+        <v>=SACCR_NormCDF(1.96)</v>
       </c>
       <c r="E23" s="125">
         <v>0.97500210485177952</v>
       </c>
-      <c r="F23" s="125">
-        <f>SACCR_NormCDF(1.96)</f>
+      <c r="F23" s="125" cm="1">
+        <f t="array" ref="F23">SACCR_NormCDF(1.96)</f>
         <v>0.97500210485177952</v>
       </c>
       <c r="G23" s="126">
@@ -7298,14 +7314,15 @@
       <c r="C24" s="128" t="s">
         <v>548</v>
       </c>
-      <c r="D24" s="24" t="s">
-        <v>549</v>
+      <c r="D24" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F24)</f>
+        <v>=SACCR_NormCDF(-8)</v>
       </c>
       <c r="E24" s="125">
         <v>6.2209605742718194E-16</v>
       </c>
-      <c r="F24" s="125">
-        <f>SACCR_NormCDF(-8)</f>
+      <c r="F24" s="125" cm="1">
+        <f t="array" ref="F24">SACCR_NormCDF(-8)</f>
         <v>6.2209605201427843E-16</v>
       </c>
       <c r="G24" s="126">
@@ -7321,14 +7338,15 @@
       <c r="C25" s="128" t="s">
         <v>550</v>
       </c>
-      <c r="D25" s="24" t="s">
-        <v>551</v>
+      <c r="D25" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F25)</f>
+        <v>=SACCR_LambdaCRR(-0.002,0.001,TRUE)</v>
       </c>
       <c r="E25" s="125">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F25" s="125">
-        <f>SACCR_LambdaCRR(-0.002,0.001,TRUE)</f>
+      <c r="F25" s="125" cm="1">
+        <f t="array" ref="F25">SACCR_LambdaCRR(-0.002,0.001,TRUE)</f>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="G25" s="126">
@@ -7344,14 +7362,15 @@
       <c r="C26" s="128" t="s">
         <v>552</v>
       </c>
-      <c r="D26" s="24" t="s">
-        <v>553</v>
+      <c r="D26" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F26)</f>
+        <v>=SACCR_LambdaCRR(0.02,0.03,TRUE)</v>
       </c>
       <c r="E26" s="125">
         <v>0</v>
       </c>
-      <c r="F26" s="125">
-        <f>SACCR_LambdaCRR(0.02,0.03,TRUE)</f>
+      <c r="F26" s="125" cm="1">
+        <f t="array" ref="F26">SACCR_LambdaCRR(0.02,0.03,TRUE)</f>
         <v>0</v>
       </c>
       <c r="G26" s="126">
@@ -7367,14 +7386,15 @@
       <c r="C27" s="128" t="s">
         <v>554</v>
       </c>
-      <c r="D27" s="24" t="s">
-        <v>555</v>
+      <c r="D27" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F27)</f>
+        <v>=SACCR_LambdaCRR(0.0005,0.01,TRUE)</v>
       </c>
       <c r="E27" s="125">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="F27" s="125">
-        <f>SACCR_LambdaCRR(0.0005,0.01,TRUE)</f>
+      <c r="F27" s="125" cm="1">
+        <f t="array" ref="F27">SACCR_LambdaCRR(0.0005,0.01,TRUE)</f>
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="G27" s="126">
@@ -7390,14 +7410,15 @@
       <c r="C28" s="128" t="s">
         <v>556</v>
       </c>
-      <c r="D28" s="24" t="s">
-        <v>557</v>
+      <c r="D28" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F28)</f>
+        <v>=SACCR_LambdaCRR(-5,-4,FALSE)</v>
       </c>
       <c r="E28" s="125">
         <v>5.5</v>
       </c>
-      <c r="F28" s="125">
-        <f>SACCR_LambdaCRR(-5,-4,FALSE)</f>
+      <c r="F28" s="125" cm="1">
+        <f t="array" ref="F28">SACCR_LambdaCRR(-5,-4,FALSE)</f>
         <v>5.5</v>
       </c>
       <c r="G28" s="126">
@@ -7413,14 +7434,15 @@
       <c r="C29" s="128" t="s">
         <v>558</v>
       </c>
-      <c r="D29" s="24" t="s">
-        <v>559</v>
+      <c r="D29" s="24" t="str">
+        <f>_xlfn.FORMULATEXT(F29)</f>
+        <v>=SACCR_LambdaCRR(40,35,FALSE)</v>
       </c>
       <c r="E29" s="125">
         <v>0</v>
       </c>
-      <c r="F29" s="125">
-        <f>SACCR_LambdaCRR(40,35,FALSE)</f>
+      <c r="F29" s="125" cm="1">
+        <f t="array" ref="F29">SACCR_LambdaCRR(40,35,FALSE)</f>
         <v>0</v>
       </c>
       <c r="G29" s="126">

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="895">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -1617,7 +1617,7 @@
     <t>Message</t>
   </si>
   <si>
-    <t>Unit tests call the SACCR_* worksheet functions (macros enabled); portfolio tests are on TestCatalogue.</t>
+    <t>Unit tests call the SACCR_* worksheet functions (macros enabled) on the yellow inputs. Expected computes the same rule with Excel's own functions, so changing an input tests the function on new values. Portfolio tests are on TestCatalogue.</t>
   </si>
   <si>
     <t>Unit tests of the worksheet functions</t>
@@ -2680,6 +2680,114 @@
   </si>
   <si>
     <t>No results yet: build the workbook from the source, then press Run SA-CCR.</t>
+  </si>
+  <si>
+    <t>S, E (years)</t>
+  </si>
+  <si>
+    <t>CRE52.34; CRR Art. 279b(1)(a)</t>
+  </si>
+  <si>
+    <t>S, E, floor (years)</t>
+  </si>
+  <si>
+    <t>M (years)</t>
+  </si>
+  <si>
+    <t>CRE52.48; CRR Art. 279c(1)(a)</t>
+  </si>
+  <si>
+    <t>M (years), margined, MPOR (business days)</t>
+  </si>
+  <si>
+    <t>CRE52.52; CRR Art. 279c(1)(b)</t>
+  </si>
+  <si>
+    <t>P, K, T, volatility, call, bought</t>
+  </si>
+  <si>
+    <t>CRE52.40; CRR Art. 279a(1)(a)</t>
+  </si>
+  <si>
+    <t>P, K, T, volatility, call, bought, lambda</t>
+  </si>
+  <si>
+    <t>CRE52.40 FAQ; CRR-RTS Art. 5(1)</t>
+  </si>
+  <si>
+    <t>A, D, long</t>
+  </si>
+  <si>
+    <t>CRE52.41; CRR Art. 279a(1)(c)</t>
+  </si>
+  <si>
+    <t>D1, D2, D3 (bucket effective notionals)</t>
+  </si>
+  <si>
+    <t>CRE52.57(5); CRR Art. 280a</t>
+  </si>
+  <si>
+    <t>Add-ons A1, A2, A3, correlations 1, 2, 3</t>
+  </si>
+  <si>
+    <t>CRE52.61; CRR Art. 280c</t>
+  </si>
+  <si>
+    <t>V - C, add-on</t>
+  </si>
+  <si>
+    <t>CRE52.23; CRR Art. 278(3)</t>
+  </si>
+  <si>
+    <t>V, C, margined, TH, MTA, NICA</t>
+  </si>
+  <si>
+    <t>CRE52.10, .18; CRR Art. 275(1), (2)</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Standard normal distribution</t>
+  </si>
+  <si>
+    <t>P, K, interest rate</t>
+  </si>
+  <si>
+    <t>CRR-RTS Art. 5(2)</t>
+  </si>
+  <si>
+    <t>Arguments</t>
+  </si>
+  <si>
+    <t>Input 1</t>
+  </si>
+  <si>
+    <t>Input 2</t>
+  </si>
+  <si>
+    <t>Input 3</t>
+  </si>
+  <si>
+    <t>Input 4</t>
+  </si>
+  <si>
+    <t>Input 5</t>
+  </si>
+  <si>
+    <t>Input 6</t>
+  </si>
+  <si>
+    <t>Input 7</t>
+  </si>
+  <si>
+    <t>Expected (Excel)</t>
+  </si>
+  <si>
+    <t>Function (VBA)</t>
+  </si>
+  <si>
+    <t>Rule</t>
   </si>
 </sst>
 </file>
@@ -3106,7 +3214,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3493,6 +3601,12 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6826,11 +6940,14 @@
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
     <col min="3" max="3" width="40.75" customWidth="1"/>
-    <col min="4" max="4" width="89.125" customWidth="1"/>
-    <col min="5" max="12" width="14.75" customWidth="1"/>
+    <col min="4" max="4" width="36.75" customWidth="1"/>
+    <col min="5" max="11" width="11.75" customWidth="1"/>
+    <col min="12" max="13" width="14.75" customWidth="1"/>
+    <col min="14" max="15" width="10.75" customWidth="1"/>
+    <col min="16" max="16" width="30.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
@@ -6861,7 +6978,7 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
     </row>
-    <row r="2" spans="2:28" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
         <v>70</v>
       </c>
@@ -6892,566 +7009,868 @@
       <c r="AA2" s="68"/>
       <c r="AB2" s="68"/>
     </row>
-    <row r="3" spans="2:28" ht="21" x14ac:dyDescent="0.25">
+    <row r="3" ht="21" x14ac:dyDescent="0.25">
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="2" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="5" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="48" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="7" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="54" t="s">
         <v>510</v>
       </c>
       <c r="D7" s="54" t="s">
-        <v>511</v>
+        <v>884</v>
       </c>
       <c r="E7" s="55" t="s">
-        <v>512</v>
+        <v>885</v>
       </c>
       <c r="F7" s="55" t="s">
-        <v>513</v>
+        <v>886</v>
       </c>
       <c r="G7" s="55" t="s">
+        <v>887</v>
+      </c>
+      <c r="H7" s="55" t="s">
+        <v>888</v>
+      </c>
+      <c r="I7" s="55" t="s">
+        <v>889</v>
+      </c>
+      <c r="J7" s="55" t="s">
+        <v>890</v>
+      </c>
+      <c r="K7" s="55" t="s">
+        <v>891</v>
+      </c>
+      <c r="L7" s="55" t="s">
+        <v>892</v>
+      </c>
+      <c r="M7" s="55" t="s">
+        <v>893</v>
+      </c>
+      <c r="N7" s="55" t="s">
         <v>514</v>
       </c>
-      <c r="H7" s="55" t="s">
+      <c r="O7" s="55" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="8" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P7" s="54" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="128" t="s">
         <v>516</v>
       </c>
-      <c r="D8" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F8)</f>
-        <v>=SACCR_SupervisoryDuration(0,10)</v>
-      </c>
-      <c r="E8" s="125">
-        <v>7.8693868057473324</v>
-      </c>
-      <c r="F8" s="125" cm="1">
-        <f t="array" ref="F8">SACCR_SupervisoryDuration(0,10)</f>
+      <c r="D8" s="24" t="s">
+        <v>859</v>
+      </c>
+      <c r="E8" s="129">
+        <v>0</v>
+      </c>
+      <c r="F8" s="129">
+        <v>10</v>
+      </c>
+      <c r="L8" s="125">
+        <f>(EXP(-0.05*$E8)-EXP(-0.05*$F8))/0.05</f>
         <v>7.8693868057473315</v>
       </c>
-      <c r="G8" s="126">
-        <f t="shared" ref="G8:G29" si="0">IFERROR(ABS(F8-E8),"")</f>
-        <v>8.8817841970012523E-16</v>
-      </c>
-      <c r="H8" s="127" t="str">
-        <f t="shared" ref="H8:H29" si="1">IF(ISNUMBER(G8),IF(G8&lt;=0.000000001*MAX(1,ABS(E8)),"PASS","FAIL"),"FAIL")</f>
+      <c r="M8" s="125" cm="1">
+        <f t="array" ref="M8">SACCR_SupervisoryDuration($E8,$F8)</f>
+        <v>7.8693868057473315</v>
+      </c>
+      <c r="N8" s="126">
+        <f>IFERROR(ABS(M8-L8),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="127" t="str">
+        <f>IF(ISNUMBER(N8),IF(N8&lt;=0.000000001*MAX(1,ABS(L8)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="9" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P8" s="130" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="128" t="s">
         <v>518</v>
       </c>
-      <c r="D9" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F9)</f>
-        <v>=SACCR_SupervisoryDuration(1,11)</v>
-      </c>
-      <c r="E9" s="125">
-        <v>7.4855922824045473</v>
-      </c>
-      <c r="F9" s="125" cm="1">
-        <f t="array" ref="F9">SACCR_SupervisoryDuration(1,11)</f>
-        <v>7.4855922824045473</v>
-      </c>
-      <c r="G9" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="D9" s="24" t="s">
+        <v>859</v>
+      </c>
+      <c r="E9" s="129">
+        <v>1</v>
+      </c>
+      <c r="F9" s="129">
+        <v>11</v>
+      </c>
+      <c r="L9" s="125">
+        <f>(EXP(-0.05*$E9)-EXP(-0.05*$F9))/0.05</f>
+        <v>7.485592282404547</v>
+      </c>
+      <c r="M9" s="125" cm="1">
+        <f t="array" ref="M9">SACCR_SupervisoryDuration($E9,$F9)</f>
+        <v>7.485592282404547</v>
+      </c>
+      <c r="N9" s="126">
+        <f>IFERROR(ABS(M9-L9),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="127" t="str">
+        <f>IF(ISNUMBER(N9),IF(N9&lt;=0.000000001*MAX(1,ABS(L9)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="10" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P9" s="130" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="128" t="s">
         <v>520</v>
       </c>
-      <c r="D10" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F10)</f>
-        <v>=SACCR_SupervisoryDuration(0,0.01,10/250)</v>
-      </c>
-      <c r="E10" s="125">
+      <c r="D10" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="E10" s="129">
+        <v>0</v>
+      </c>
+      <c r="F10" s="129">
+        <v>0.01</v>
+      </c>
+      <c r="G10" s="129">
+        <f>10/250</f>
         <v>0.04</v>
       </c>
-      <c r="F10" s="125" cm="1">
-        <f t="array" ref="F10">SACCR_SupervisoryDuration(0,0.01,10/250)</f>
+      <c r="L10" s="125">
+        <f>MAX((EXP(-0.05*$E10)-EXP(-0.05*$F10))/0.05,$G10)</f>
         <v>0.04</v>
       </c>
-      <c r="G10" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M10" s="125" cm="1">
+        <f t="array" ref="M10">SACCR_SupervisoryDuration($E10,$F10,$G10)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N10" s="126">
+        <f>IFERROR(ABS(M10-L10),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="127" t="str">
+        <f>IF(ISNUMBER(N10),IF(N10&lt;=0.000000001*MAX(1,ABS(L10)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="11" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P10" s="130" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="128" t="s">
         <v>522</v>
       </c>
-      <c r="D11" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F11)</f>
-        <v>=SACCR_MaturityFactor(0.75)</v>
-      </c>
-      <c r="E11" s="125">
+      <c r="D11" s="24" t="s">
+        <v>862</v>
+      </c>
+      <c r="E11" s="129">
+        <v>0.75</v>
+      </c>
+      <c r="L11" s="125">
+        <f>SQRT(MIN(MAX($E11,10/250),1))</f>
         <v>0.8660254037844386</v>
       </c>
-      <c r="F11" s="125" cm="1">
-        <f t="array" ref="F11">SACCR_MaturityFactor(0.75)</f>
+      <c r="M11" s="125" cm="1">
+        <f t="array" ref="M11">SACCR_MaturityFactor($E11)</f>
         <v>0.8660254037844386</v>
       </c>
-      <c r="G11" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="N11" s="126">
+        <f>IFERROR(ABS(M11-L11),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="127" t="str">
+        <f>IF(ISNUMBER(N11),IF(N11&lt;=0.000000001*MAX(1,ABS(L11)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="12" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P11" s="130" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="128" t="s">
         <v>524</v>
       </c>
-      <c r="D12" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F12)</f>
-        <v>=SACCR_MaturityFactor(3/365)</v>
-      </c>
-      <c r="E12" s="125">
+      <c r="D12" s="24" t="s">
+        <v>862</v>
+      </c>
+      <c r="E12" s="129">
+        <f>3/365</f>
+        <v>0.00821917808219178</v>
+      </c>
+      <c r="L12" s="125">
+        <f>SQRT(MIN(MAX($E12,10/250),1))</f>
         <v>0.2</v>
       </c>
-      <c r="F12" s="125" cm="1">
-        <f t="array" ref="F12">SACCR_MaturityFactor(3/365)</f>
+      <c r="M12" s="125" cm="1">
+        <f t="array" ref="M12">SACCR_MaturityFactor($E12)</f>
         <v>0.2</v>
       </c>
-      <c r="G12" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="N12" s="126">
+        <f>IFERROR(ABS(M12-L12),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="127" t="str">
+        <f>IF(ISNUMBER(N12),IF(N12&lt;=0.000000001*MAX(1,ABS(L12)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="13" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P12" s="130" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="128" t="s">
         <v>526</v>
       </c>
-      <c r="D13" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F13)</f>
-        <v>=SACCR_MaturityFactor(0,TRUE,10)</v>
-      </c>
-      <c r="E13" s="125">
-        <v>0.3</v>
-      </c>
-      <c r="F13" s="125" cm="1">
-        <f t="array" ref="F13">SACCR_MaturityFactor(0,TRUE,10)</f>
+      <c r="D13" s="24" t="s">
+        <v>864</v>
+      </c>
+      <c r="E13" s="129">
+        <v>0</v>
+      </c>
+      <c r="F13" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="129">
+        <v>10</v>
+      </c>
+      <c r="L13" s="125">
+        <f>IF($F13,1.5*SQRT($G13/250),SQRT(MIN(MAX($E13,10/250),1)))</f>
         <v>0.30000000000000004</v>
       </c>
-      <c r="G13" s="126">
-        <f t="shared" si="0"/>
-        <v>5.5511151231257827E-17</v>
-      </c>
-      <c r="H13" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M13" s="125" cm="1">
+        <f t="array" ref="M13">SACCR_MaturityFactor($E13,$F13,$G13)</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="N13" s="126">
+        <f>IFERROR(ABS(M13-L13),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="127" t="str">
+        <f>IF(ISNUMBER(N13),IF(N13&lt;=0.000000001*MAX(1,ABS(L13)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="14" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P13" s="130" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="128" t="s">
         <v>528</v>
       </c>
-      <c r="D14" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F14)</f>
-        <v>=SACCR_OptionDelta(0.06,0.05,1,0.5,FALSE,TRUE)</v>
-      </c>
-      <c r="E14" s="125">
-        <v>-0.26939521771053271</v>
-      </c>
-      <c r="F14" s="125" cm="1">
-        <f t="array" ref="F14">SACCR_OptionDelta(0.06,0.05,1,0.5,FALSE,TRUE)</f>
-        <v>-0.26939521771053271</v>
-      </c>
-      <c r="G14" s="126">
-        <f t="shared" si="0"/>
+      <c r="D14" s="24" t="s">
+        <v>866</v>
+      </c>
+      <c r="E14" s="129">
+        <v>0.06</v>
+      </c>
+      <c r="F14" s="129">
+        <v>0.05</v>
+      </c>
+      <c r="G14" s="129">
+        <v>1</v>
+      </c>
+      <c r="H14" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="129" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="J14" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="125">
+        <f>IF($I14,_xlfn.NORM.S.DIST((LN(($E14+$K14)/($F14+$K14))+$H14^2*$G14/2)/($H14*SQRT($G14)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E14+$K14)/($F14+$K14))+$H14^2*$G14/2)/($H14*SQRT($G14)),TRUE))*IF($J14,1,-1)</f>
+        <v>-0.2693952177105327</v>
+      </c>
+      <c r="M14" s="125" cm="1">
+        <f t="array" ref="M14">SACCR_OptionDelta($E14,$F14,$G14,$H14,$I14,$J14)</f>
+        <v>-0.2693952177105327</v>
+      </c>
+      <c r="N14" s="126">
+        <f>IFERROR(ABS(M14-L14),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="127" t="str">
+        <f>IF(ISNUMBER(N14),IF(N14&lt;=0.000000001*MAX(1,ABS(L14)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="15" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P14" s="130" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="128" t="s">
         <v>530</v>
       </c>
-      <c r="D15" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F15)</f>
-        <v>=SACCR_OptionDelta(100,110,0.5,0.32,TRUE,FALSE)</v>
-      </c>
-      <c r="E15" s="125">
-        <v>-0.37901134582780288</v>
-      </c>
-      <c r="F15" s="125" cm="1">
-        <f t="array" ref="F15">SACCR_OptionDelta(100,110,0.5,0.32,TRUE,FALSE)</f>
+      <c r="D15" s="24" t="s">
+        <v>866</v>
+      </c>
+      <c r="E15" s="129">
+        <v>100</v>
+      </c>
+      <c r="F15" s="129">
+        <v>110</v>
+      </c>
+      <c r="G15" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="129">
+        <v>0.32</v>
+      </c>
+      <c r="I15" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="129" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="125">
+        <f>IF($I15,_xlfn.NORM.S.DIST((LN(($E15+$K15)/($F15+$K15))+$H15^2*$G15/2)/($H15*SQRT($G15)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E15+$K15)/($F15+$K15))+$H15^2*$G15/2)/($H15*SQRT($G15)),TRUE))*IF($J15,1,-1)</f>
         <v>-0.37901134582780294</v>
       </c>
-      <c r="G15" s="126">
-        <f t="shared" si="0"/>
-        <v>5.5511151231257827E-17</v>
-      </c>
-      <c r="H15" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M15" s="125" cm="1">
+        <f t="array" ref="M15">SACCR_OptionDelta($E15,$F15,$G15,$H15,$I15,$J15)</f>
+        <v>-0.37901134582780294</v>
+      </c>
+      <c r="N15" s="126">
+        <f>IFERROR(ABS(M15-L15),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="127" t="str">
+        <f>IF(ISNUMBER(N15),IF(N15&lt;=0.000000001*MAX(1,ABS(L15)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="16" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P15" s="130" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="128" t="s">
         <v>532</v>
       </c>
-      <c r="D16" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F16)</f>
-        <v>=SACCR_OptionDelta(-0.002,0.001,2,0.5,TRUE,TRUE,0.01)</v>
-      </c>
-      <c r="E16" s="125">
-        <v>0.46143935794124907</v>
-      </c>
-      <c r="F16" s="125" cm="1">
-        <f t="array" ref="F16">SACCR_OptionDelta(-0.002,0.001,2,0.5,TRUE,TRUE,0.01)</f>
+      <c r="D16" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="E16" s="129">
+        <v>-0.002</v>
+      </c>
+      <c r="F16" s="129">
+        <v>0.001</v>
+      </c>
+      <c r="G16" s="129">
+        <v>2</v>
+      </c>
+      <c r="H16" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="I16" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" s="129">
+        <v>0.01</v>
+      </c>
+      <c r="L16" s="125">
+        <f>IF($I16,_xlfn.NORM.S.DIST((LN(($E16+$K16)/($F16+$K16))+$H16^2*$G16/2)/($H16*SQRT($G16)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E16+$K16)/($F16+$K16))+$H16^2*$G16/2)/($H16*SQRT($G16)),TRUE))*IF($J16,1,-1)</f>
         <v>0.46143935794124913</v>
       </c>
-      <c r="G16" s="126">
-        <f t="shared" si="0"/>
-        <v>5.5511151231257827E-17</v>
-      </c>
-      <c r="H16" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M16" s="125" cm="1">
+        <f t="array" ref="M16">SACCR_OptionDelta($E16,$F16,$G16,$H16,$I16,$J16,$K16)</f>
+        <v>0.46143935794124913</v>
+      </c>
+      <c r="N16" s="126">
+        <f>IFERROR(ABS(M16-L16),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="127" t="str">
+        <f>IF(ISNUMBER(N16),IF(N16&lt;=0.000000001*MAX(1,ABS(L16)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="17" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P16" s="130" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="128" t="s">
         <v>534</v>
       </c>
-      <c r="D17" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F17)</f>
-        <v>=SACCR_CDODelta(0.03,0.06,TRUE)</v>
-      </c>
-      <c r="E17" s="125">
+      <c r="D17" s="24" t="s">
+        <v>870</v>
+      </c>
+      <c r="E17" s="129">
+        <v>0.03</v>
+      </c>
+      <c r="F17" s="129">
+        <v>0.06</v>
+      </c>
+      <c r="G17" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="125">
+        <f>15/((1+14*$E17)*(1+14*$F17))*IF($G17,1,-1)</f>
+        <v>5.740967544396817</v>
+      </c>
+      <c r="M17" s="125" cm="1">
+        <f t="array" ref="M17">SACCR_CDODelta($E17,$F17,$G17)</f>
         <v>5.740967544396816</v>
       </c>
-      <c r="F17" s="125" cm="1">
-        <f t="array" ref="F17">SACCR_CDODelta(0.03,0.06,TRUE)</f>
-        <v>5.740967544396816</v>
-      </c>
-      <c r="G17" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="N17" s="126">
+        <f>IFERROR(ABS(M17-L17),"")</f>
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="O17" s="127" t="str">
+        <f>IF(ISNUMBER(N17),IF(N17&lt;=0.000000001*MAX(1,ABS(L17)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="18" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P17" s="130" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="128" t="s">
         <v>536</v>
       </c>
-      <c r="D18" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F18)</f>
-        <v>=SACCR_IREffectiveNotional(0,-36253.8493844036,78693.8680574733)</v>
-      </c>
-      <c r="E18" s="125">
-        <v>59269.963463710403</v>
-      </c>
-      <c r="F18" s="125" cm="1">
-        <f t="array" ref="F18">SACCR_IREffectiveNotional(0,-36253.8493844036,78693.8680574733)</f>
+      <c r="D18" s="24" t="s">
+        <v>872</v>
+      </c>
+      <c r="E18" s="129">
+        <v>0</v>
+      </c>
+      <c r="F18" s="129">
+        <v>-36253.8493844036</v>
+      </c>
+      <c r="G18" s="129">
+        <v>78693.8680574733</v>
+      </c>
+      <c r="L18" s="125">
+        <f>SQRT($E18^2+$F18^2+$G18^2+1.4*$E18*$F18+1.4*$F18*$G18+0.6*$E18*$G18)</f>
         <v>59269.963463710395</v>
       </c>
-      <c r="G18" s="126">
-        <f t="shared" si="0"/>
-        <v>7.2759576141834259E-12</v>
-      </c>
-      <c r="H18" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M18" s="125" cm="1">
+        <f t="array" ref="M18">SACCR_IREffectiveNotional($E18,$F18,$G18)</f>
+        <v>59269.963463710395</v>
+      </c>
+      <c r="N18" s="126">
+        <f>IFERROR(ABS(M18-L18),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="127" t="str">
+        <f>IF(ISNUMBER(N18),IF(N18&lt;=0.000000001*MAX(1,ABS(L18)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="19" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P18" s="130" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="128" t="s">
         <v>538</v>
       </c>
-      <c r="D19" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F19)</f>
-        <v>=SACCR_FactorAggregation({105.861937916956,-279.916321663744,168.111404865732},{0.5,0.5,0.8})</v>
-      </c>
-      <c r="E19" s="125">
-        <v>282.1288318596666</v>
-      </c>
-      <c r="F19" s="125" cm="1">
-        <f t="array" ref="F19">SACCR_FactorAggregation({105.861937916956,-279.916321663744,168.111404865732},{0.5,0.5,0.8})</f>
+      <c r="D19" s="24" t="s">
+        <v>874</v>
+      </c>
+      <c r="E19" s="129">
+        <v>105.861937916956</v>
+      </c>
+      <c r="F19" s="129">
+        <v>-279.916321663744</v>
+      </c>
+      <c r="G19" s="129">
+        <v>168.111404865732</v>
+      </c>
+      <c r="H19" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="J19" s="129">
+        <v>0.8</v>
+      </c>
+      <c r="L19" s="125">
+        <f>SQRT(SUMPRODUCT($E19:$G19,$H19:$J19)^2+SUMPRODUCT((1-$H19:$J19^2)*$E19:$G19^2))</f>
         <v>282.12883185966604</v>
       </c>
-      <c r="G19" s="126">
-        <f t="shared" si="0"/>
-        <v>5.6843418860808015E-13</v>
-      </c>
-      <c r="H19" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M19" s="125" cm="1">
+        <f t="array" ref="M19">SACCR_FactorAggregation($E19:$G19,$H19:$J19)</f>
+        <v>282.12883185966604</v>
+      </c>
+      <c r="N19" s="126">
+        <f>IFERROR(ABS(M19-L19),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="127" t="str">
+        <f>IF(ISNUMBER(N19),IF(N19&lt;=0.000000001*MAX(1,ABS(L19)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="20" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P19" s="130" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="128" t="s">
         <v>540</v>
       </c>
-      <c r="D20" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F20)</f>
-        <v>=SACCR_Multiplier(-20,282)</v>
-      </c>
-      <c r="E20" s="125">
-        <v>0.96519268118719448</v>
-      </c>
-      <c r="F20" s="125" cm="1">
-        <f t="array" ref="F20">SACCR_Multiplier(-20,282)</f>
-        <v>0.96519268118719448</v>
-      </c>
-      <c r="G20" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="D20" s="24" t="s">
+        <v>876</v>
+      </c>
+      <c r="E20" s="129">
+        <v>-20</v>
+      </c>
+      <c r="F20" s="129">
+        <v>282</v>
+      </c>
+      <c r="L20" s="125">
+        <f>MIN(1,0.05+0.95*EXP($E20/(2*0.95*$F20)))</f>
+        <v>0.9651926811871945</v>
+      </c>
+      <c r="M20" s="125" cm="1">
+        <f t="array" ref="M20">SACCR_Multiplier($E20,$F20)</f>
+        <v>0.9651926811871945</v>
+      </c>
+      <c r="N20" s="126">
+        <f>IFERROR(ABS(M20-L20),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="127" t="str">
+        <f>IF(ISNUMBER(N20),IF(N20&lt;=0.000000001*MAX(1,ABS(L20)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="21" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P20" s="130" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="128" t="s">
         <v>542</v>
       </c>
-      <c r="D21" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F21)</f>
-        <v>=SACCR_Multiplier(10,282)</v>
-      </c>
-      <c r="E21" s="125">
+      <c r="D21" s="24" t="s">
+        <v>876</v>
+      </c>
+      <c r="E21" s="129">
+        <v>10</v>
+      </c>
+      <c r="F21" s="129">
+        <v>282</v>
+      </c>
+      <c r="L21" s="125">
+        <f>MIN(1,0.05+0.95*EXP($E21/(2*0.95*$F21)))</f>
         <v>1</v>
       </c>
-      <c r="F21" s="125" cm="1">
-        <f t="array" ref="F21">SACCR_Multiplier(10,282)</f>
-        <v>1</v>
-      </c>
-      <c r="G21" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M21" s="125" cm="1">
+        <f t="array" ref="M21">SACCR_Multiplier($E21,$F21)</f>
+        <v>1.0</v>
+      </c>
+      <c r="N21" s="126">
+        <f>IFERROR(ABS(M21-L21),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="127" t="str">
+        <f>IF(ISNUMBER(N21),IF(N21&lt;=0.000000001*MAX(1,ABS(L21)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="22" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P21" s="130" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="128" t="s">
         <v>544</v>
       </c>
-      <c r="D22" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F22)</f>
-        <v>=SACCR_ReplacementCost(5,10,TRUE,0,10,2)</v>
-      </c>
-      <c r="E22" s="125">
+      <c r="D22" s="24" t="s">
+        <v>878</v>
+      </c>
+      <c r="E22" s="129">
+        <v>5</v>
+      </c>
+      <c r="F22" s="129">
+        <v>10</v>
+      </c>
+      <c r="G22" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="129">
+        <v>0</v>
+      </c>
+      <c r="I22" s="129">
+        <v>10</v>
+      </c>
+      <c r="J22" s="129">
+        <v>2</v>
+      </c>
+      <c r="L22" s="125">
+        <f>IF($G22,MAX($E22-$F22,$H22+$I22-$J22,0),MAX($E22-$F22,0))</f>
         <v>8</v>
       </c>
-      <c r="F22" s="125" cm="1">
-        <f t="array" ref="F22">SACCR_ReplacementCost(5,10,TRUE,0,10,2)</f>
-        <v>8</v>
-      </c>
-      <c r="G22" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M22" s="125" cm="1">
+        <f t="array" ref="M22">SACCR_ReplacementCost($E22,$F22,$G22,$H22,$I22,$J22)</f>
+        <v>8.0</v>
+      </c>
+      <c r="N22" s="126">
+        <f>IFERROR(ABS(M22-L22),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="127" t="str">
+        <f>IF(ISNUMBER(N22),IF(N22&lt;=0.000000001*MAX(1,ABS(L22)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="23" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P22" s="130" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="128" t="s">
         <v>546</v>
       </c>
-      <c r="D23" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F23)</f>
-        <v>=SACCR_NormCDF(1.96)</v>
-      </c>
-      <c r="E23" s="125">
-        <v>0.97500210485177952</v>
-      </c>
-      <c r="F23" s="125" cm="1">
-        <f t="array" ref="F23">SACCR_NormCDF(1.96)</f>
-        <v>0.97500210485177952</v>
-      </c>
-      <c r="G23" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="D23" s="24" t="s">
+        <v>880</v>
+      </c>
+      <c r="E23" s="129">
+        <v>1.96</v>
+      </c>
+      <c r="L23" s="125">
+        <f>_xlfn.NORM.S.DIST($E23,TRUE)</f>
+        <v>0.9750021048517795</v>
+      </c>
+      <c r="M23" s="125" cm="1">
+        <f t="array" ref="M23">SACCR_NormCDF($E23)</f>
+        <v>0.9750021048517795</v>
+      </c>
+      <c r="N23" s="126">
+        <f>IFERROR(ABS(M23-L23),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="127" t="str">
+        <f>IF(ISNUMBER(N23),IF(N23&lt;=0.000000001*MAX(1,ABS(L23)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="24" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P23" s="130" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="128" t="s">
         <v>548</v>
       </c>
-      <c r="D24" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F24)</f>
-        <v>=SACCR_NormCDF(-8)</v>
-      </c>
-      <c r="E24" s="125">
-        <v>6.2209605742718194E-16</v>
-      </c>
-      <c r="F24" s="125" cm="1">
-        <f t="array" ref="F24">SACCR_NormCDF(-8)</f>
-        <v>6.2209605201427843E-16</v>
-      </c>
-      <c r="G24" s="126">
-        <f t="shared" si="0"/>
-        <v>5.4129035033506995E-24</v>
-      </c>
-      <c r="H24" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="D24" s="24" t="s">
+        <v>880</v>
+      </c>
+      <c r="E24" s="129">
+        <v>-8</v>
+      </c>
+      <c r="L24" s="125">
+        <f>_xlfn.NORM.S.DIST($E24,TRUE)</f>
+        <v>6.220960574271819e-16</v>
+      </c>
+      <c r="M24" s="125" cm="1">
+        <f t="array" ref="M24">SACCR_NormCDF($E24)</f>
+        <v>6.220960520142784e-16</v>
+      </c>
+      <c r="N24" s="126">
+        <f>IFERROR(ABS(M24-L24),"")</f>
+        <v>5.4129035033506995e-24</v>
+      </c>
+      <c r="O24" s="127" t="str">
+        <f>IF(ISNUMBER(N24),IF(N24&lt;=0.000000001*MAX(1,ABS(L24)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="25" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="130" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="128" t="s">
         <v>550</v>
       </c>
-      <c r="D25" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F25)</f>
-        <v>=SACCR_LambdaCRR(-0.002,0.001,TRUE)</v>
-      </c>
-      <c r="E25" s="125">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="F25" s="125" cm="1">
-        <f t="array" ref="F25">SACCR_LambdaCRR(-0.002,0.001,TRUE)</f>
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="G25" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="D25" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="E25" s="129">
+        <v>-0.002</v>
+      </c>
+      <c r="F25" s="129">
+        <v>0.001</v>
+      </c>
+      <c r="G25" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="125">
+        <f>IF($G25,MAX(0.001-MIN($E25,$F25),0),MAX(-(1+0.1)*MIN($E25,$F25),0))</f>
+        <v>0.003</v>
+      </c>
+      <c r="M25" s="125" cm="1">
+        <f t="array" ref="M25">SACCR_LambdaCRR($E25,$F25,$G25)</f>
+        <v>0.003</v>
+      </c>
+      <c r="N25" s="126">
+        <f>IFERROR(ABS(M25-L25),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="127" t="str">
+        <f>IF(ISNUMBER(N25),IF(N25&lt;=0.000000001*MAX(1,ABS(L25)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="26" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P25" s="130" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="128" t="s">
         <v>552</v>
       </c>
-      <c r="D26" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F26)</f>
-        <v>=SACCR_LambdaCRR(0.02,0.03,TRUE)</v>
-      </c>
-      <c r="E26" s="125">
+      <c r="D26" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="E26" s="129">
+        <v>0.02</v>
+      </c>
+      <c r="F26" s="129">
+        <v>0.03</v>
+      </c>
+      <c r="G26" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="125">
+        <f>IF($G26,MAX(0.001-MIN($E26,$F26),0),MAX(-(1+0.1)*MIN($E26,$F26),0))</f>
         <v>0</v>
       </c>
-      <c r="F26" s="125" cm="1">
-        <f t="array" ref="F26">SACCR_LambdaCRR(0.02,0.03,TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M26" s="125" cm="1">
+        <f t="array" ref="M26">SACCR_LambdaCRR($E26,$F26,$G26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="126">
+        <f>IFERROR(ABS(M26-L26),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="127" t="str">
+        <f>IF(ISNUMBER(N26),IF(N26&lt;=0.000000001*MAX(1,ABS(L26)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="27" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P26" s="130" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="128" t="s">
         <v>554</v>
       </c>
-      <c r="D27" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F27)</f>
-        <v>=SACCR_LambdaCRR(0.0005,0.01,TRUE)</v>
-      </c>
-      <c r="E27" s="125">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="F27" s="125" cm="1">
-        <f t="array" ref="F27">SACCR_LambdaCRR(0.0005,0.01,TRUE)</f>
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="G27" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="D27" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="E27" s="129">
+        <v>0.0005</v>
+      </c>
+      <c r="F27" s="129">
+        <v>0.01</v>
+      </c>
+      <c r="G27" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="125">
+        <f>IF($G27,MAX(0.001-MIN($E27,$F27),0),MAX(-(1+0.1)*MIN($E27,$F27),0))</f>
+        <v>0.0005</v>
+      </c>
+      <c r="M27" s="125" cm="1">
+        <f t="array" ref="M27">SACCR_LambdaCRR($E27,$F27,$G27)</f>
+        <v>0.0005</v>
+      </c>
+      <c r="N27" s="126">
+        <f>IFERROR(ABS(M27-L27),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="127" t="str">
+        <f>IF(ISNUMBER(N27),IF(N27&lt;=0.000000001*MAX(1,ABS(L27)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="28" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P27" s="130" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="128" t="s">
         <v>556</v>
       </c>
-      <c r="D28" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F28)</f>
-        <v>=SACCR_LambdaCRR(-5,-4,FALSE)</v>
-      </c>
-      <c r="E28" s="125">
+      <c r="D28" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="E28" s="129">
+        <v>-5</v>
+      </c>
+      <c r="F28" s="129">
+        <v>-4</v>
+      </c>
+      <c r="G28" s="129" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="125">
+        <f>IF($G28,MAX(0.001-MIN($E28,$F28),0),MAX(-(1+0.1)*MIN($E28,$F28),0))</f>
         <v>5.5</v>
       </c>
-      <c r="F28" s="125" cm="1">
-        <f t="array" ref="F28">SACCR_LambdaCRR(-5,-4,FALSE)</f>
+      <c r="M28" s="125" cm="1">
+        <f t="array" ref="M28">SACCR_LambdaCRR($E28,$F28,$G28)</f>
         <v>5.5</v>
       </c>
-      <c r="G28" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="N28" s="126">
+        <f>IFERROR(ABS(M28-L28),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="127" t="str">
+        <f>IF(ISNUMBER(N28),IF(N28&lt;=0.000000001*MAX(1,ABS(L28)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="29" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P28" s="130" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="128" t="s">
         <v>558</v>
       </c>
-      <c r="D29" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F29)</f>
-        <v>=SACCR_LambdaCRR(40,35,FALSE)</v>
-      </c>
-      <c r="E29" s="125">
+      <c r="D29" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="E29" s="129">
+        <v>40</v>
+      </c>
+      <c r="F29" s="129">
+        <v>35</v>
+      </c>
+      <c r="G29" s="129" t="b">
         <v>0</v>
       </c>
-      <c r="F29" s="125" cm="1">
-        <f t="array" ref="F29">SACCR_LambdaCRR(40,35,FALSE)</f>
+      <c r="L29" s="125">
+        <f>IF($G29,MAX(0.001-MIN($E29,$F29),0),MAX(-(1+0.1)*MIN($E29,$F29),0))</f>
         <v>0</v>
       </c>
-      <c r="G29" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M29" s="125" cm="1">
+        <f t="array" ref="M29">SACCR_LambdaCRR($E29,$F29,$G29)</f>
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="126">
+        <f>IFERROR(ABS(M29-L29),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="127" t="str">
+        <f>IF(ISNUMBER(N29),IF(N29&lt;=0.000000001*MAX(1,ABS(L29)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
+      </c>
+      <c r="P29" s="130" t="s">
+        <v>883</v>
       </c>
     </row>
   </sheetData>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -48,6 +48,7 @@
     <definedName name="SACCR_RunInputs" hidden="1">""</definedName>
     <definedName name="SDFloorBD">Params!$E$13</definedName>
     <definedName name="SF_Table">Params!$C$28:$K$54</definedName>
+    <definedName name="Tests_Tolerance">Tests!$D$5</definedName>
     <definedName name="Trades_Header">Trades!$C$4</definedName>
     <definedName name="VolatilityFactor">Params!$E$18</definedName>
   </definedNames>
@@ -91,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="896">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -2788,6 +2789,9 @@
   </si>
   <si>
     <t>Rule</t>
+  </si>
+  <si>
+    <t>Tolerance: a test passes when |Function - Expected| &lt;= tolerance x max(1, |Expected|)</t>
   </si>
 </sst>
 </file>
@@ -3214,7 +3218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3607,6 +3611,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7017,7 +7024,14 @@
         <v>508</v>
       </c>
     </row>
-    <row r="5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="128" t="s">
+        <v>895</v>
+      </c>
+      <c r="D5" s="131">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
     <row r="6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="48" t="s">
         <v>509</v>
@@ -7093,7 +7107,7 @@
         <v>0.0</v>
       </c>
       <c r="O8" s="127" t="str">
-        <f>IF(ISNUMBER(N8),IF(N8&lt;=0.000000001*MAX(1,ABS(L8)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N8),IF(N8&lt;=Tests_Tolerance*MAX(1,ABS(L8)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P8" s="130" t="s">
@@ -7126,7 +7140,7 @@
         <v>0.0</v>
       </c>
       <c r="O9" s="127" t="str">
-        <f>IF(ISNUMBER(N9),IF(N9&lt;=0.000000001*MAX(1,ABS(L9)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N9),IF(N9&lt;=Tests_Tolerance*MAX(1,ABS(L9)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P9" s="130" t="s">
@@ -7163,7 +7177,7 @@
         <v>0.0</v>
       </c>
       <c r="O10" s="127" t="str">
-        <f>IF(ISNUMBER(N10),IF(N10&lt;=0.000000001*MAX(1,ABS(L10)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N10),IF(N10&lt;=Tests_Tolerance*MAX(1,ABS(L10)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P10" s="130" t="s">
@@ -7193,7 +7207,7 @@
         <v>0.0</v>
       </c>
       <c r="O11" s="127" t="str">
-        <f>IF(ISNUMBER(N11),IF(N11&lt;=0.000000001*MAX(1,ABS(L11)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N11),IF(N11&lt;=Tests_Tolerance*MAX(1,ABS(L11)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P11" s="130" t="s">
@@ -7224,7 +7238,7 @@
         <v>0.0</v>
       </c>
       <c r="O12" s="127" t="str">
-        <f>IF(ISNUMBER(N12),IF(N12&lt;=0.000000001*MAX(1,ABS(L12)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N12),IF(N12&lt;=Tests_Tolerance*MAX(1,ABS(L12)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P12" s="130" t="s">
@@ -7260,7 +7274,7 @@
         <v>0.0</v>
       </c>
       <c r="O13" s="127" t="str">
-        <f>IF(ISNUMBER(N13),IF(N13&lt;=0.000000001*MAX(1,ABS(L13)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N13),IF(N13&lt;=Tests_Tolerance*MAX(1,ABS(L13)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P13" s="130" t="s">
@@ -7305,7 +7319,7 @@
         <v>0.0</v>
       </c>
       <c r="O14" s="127" t="str">
-        <f>IF(ISNUMBER(N14),IF(N14&lt;=0.000000001*MAX(1,ABS(L14)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N14),IF(N14&lt;=Tests_Tolerance*MAX(1,ABS(L14)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P14" s="130" t="s">
@@ -7350,7 +7364,7 @@
         <v>0.0</v>
       </c>
       <c r="O15" s="127" t="str">
-        <f>IF(ISNUMBER(N15),IF(N15&lt;=0.000000001*MAX(1,ABS(L15)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N15),IF(N15&lt;=Tests_Tolerance*MAX(1,ABS(L15)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P15" s="130" t="s">
@@ -7398,7 +7412,7 @@
         <v>0.0</v>
       </c>
       <c r="O16" s="127" t="str">
-        <f>IF(ISNUMBER(N16),IF(N16&lt;=0.000000001*MAX(1,ABS(L16)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N16),IF(N16&lt;=Tests_Tolerance*MAX(1,ABS(L16)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P16" s="130" t="s">
@@ -7434,7 +7448,7 @@
         <v>8.881784197001252e-16</v>
       </c>
       <c r="O17" s="127" t="str">
-        <f>IF(ISNUMBER(N17),IF(N17&lt;=0.000000001*MAX(1,ABS(L17)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N17),IF(N17&lt;=Tests_Tolerance*MAX(1,ABS(L17)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P17" s="130" t="s">
@@ -7470,7 +7484,7 @@
         <v>0.0</v>
       </c>
       <c r="O18" s="127" t="str">
-        <f>IF(ISNUMBER(N18),IF(N18&lt;=0.000000001*MAX(1,ABS(L18)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N18),IF(N18&lt;=Tests_Tolerance*MAX(1,ABS(L18)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P18" s="130" t="s">
@@ -7515,7 +7529,7 @@
         <v>0.0</v>
       </c>
       <c r="O19" s="127" t="str">
-        <f>IF(ISNUMBER(N19),IF(N19&lt;=0.000000001*MAX(1,ABS(L19)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N19),IF(N19&lt;=Tests_Tolerance*MAX(1,ABS(L19)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P19" s="130" t="s">
@@ -7548,7 +7562,7 @@
         <v>0.0</v>
       </c>
       <c r="O20" s="127" t="str">
-        <f>IF(ISNUMBER(N20),IF(N20&lt;=0.000000001*MAX(1,ABS(L20)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N20),IF(N20&lt;=Tests_Tolerance*MAX(1,ABS(L20)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P20" s="130" t="s">
@@ -7581,7 +7595,7 @@
         <v>0.0</v>
       </c>
       <c r="O21" s="127" t="str">
-        <f>IF(ISNUMBER(N21),IF(N21&lt;=0.000000001*MAX(1,ABS(L21)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N21),IF(N21&lt;=Tests_Tolerance*MAX(1,ABS(L21)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P21" s="130" t="s">
@@ -7626,7 +7640,7 @@
         <v>0.0</v>
       </c>
       <c r="O22" s="127" t="str">
-        <f>IF(ISNUMBER(N22),IF(N22&lt;=0.000000001*MAX(1,ABS(L22)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N22),IF(N22&lt;=Tests_Tolerance*MAX(1,ABS(L22)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P22" s="130" t="s">
@@ -7656,7 +7670,7 @@
         <v>0.0</v>
       </c>
       <c r="O23" s="127" t="str">
-        <f>IF(ISNUMBER(N23),IF(N23&lt;=0.000000001*MAX(1,ABS(L23)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N23),IF(N23&lt;=Tests_Tolerance*MAX(1,ABS(L23)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P23" s="130" t="s">
@@ -7686,7 +7700,7 @@
         <v>5.4129035033506995e-24</v>
       </c>
       <c r="O24" s="127" t="str">
-        <f>IF(ISNUMBER(N24),IF(N24&lt;=0.000000001*MAX(1,ABS(L24)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N24),IF(N24&lt;=Tests_Tolerance*MAX(1,ABS(L24)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P24" s="130" t="s">
@@ -7722,7 +7736,7 @@
         <v>0.0</v>
       </c>
       <c r="O25" s="127" t="str">
-        <f>IF(ISNUMBER(N25),IF(N25&lt;=0.000000001*MAX(1,ABS(L25)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N25),IF(N25&lt;=Tests_Tolerance*MAX(1,ABS(L25)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P25" s="130" t="s">
@@ -7758,7 +7772,7 @@
         <v>0.0</v>
       </c>
       <c r="O26" s="127" t="str">
-        <f>IF(ISNUMBER(N26),IF(N26&lt;=0.000000001*MAX(1,ABS(L26)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N26),IF(N26&lt;=Tests_Tolerance*MAX(1,ABS(L26)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P26" s="130" t="s">
@@ -7794,7 +7808,7 @@
         <v>0.0</v>
       </c>
       <c r="O27" s="127" t="str">
-        <f>IF(ISNUMBER(N27),IF(N27&lt;=0.000000001*MAX(1,ABS(L27)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N27),IF(N27&lt;=Tests_Tolerance*MAX(1,ABS(L27)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P27" s="130" t="s">
@@ -7830,7 +7844,7 @@
         <v>0.0</v>
       </c>
       <c r="O28" s="127" t="str">
-        <f>IF(ISNUMBER(N28),IF(N28&lt;=0.000000001*MAX(1,ABS(L28)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N28),IF(N28&lt;=Tests_Tolerance*MAX(1,ABS(L28)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P28" s="130" t="s">
@@ -7866,7 +7880,7 @@
         <v>0.0</v>
       </c>
       <c r="O29" s="127" t="str">
-        <f>IF(ISNUMBER(N29),IF(N29&lt;=0.000000001*MAX(1,ABS(L29)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N29),IF(N29&lt;=Tests_Tolerance*MAX(1,ABS(L29)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P29" s="130" t="s">
@@ -7874,6 +7888,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%." sqref="D5">
+      <formula1>0.0000000000000001</formula1>
+      <formula2>0.01</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
 </worksheet>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -7095,7 +7095,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="125">
-        <f>(EXP(-0.05*$E8)-EXP(-0.05*$F8))/0.05</f>
+        <f>(EXP(-0.05*MAX($E8,0))-EXP(-0.05*$F8))/0.05</f>
         <v>7.8693868057473315</v>
       </c>
       <c r="M8" s="125" cm="1">
@@ -7128,7 +7128,7 @@
         <v>11</v>
       </c>
       <c r="L9" s="125">
-        <f>(EXP(-0.05*$E9)-EXP(-0.05*$F9))/0.05</f>
+        <f>(EXP(-0.05*MAX($E9,0))-EXP(-0.05*$F9))/0.05</f>
         <v>7.485592282404547</v>
       </c>
       <c r="M9" s="125" cm="1">
@@ -7165,7 +7165,7 @@
         <v>0.04</v>
       </c>
       <c r="L10" s="125">
-        <f>MAX((EXP(-0.05*$E10)-EXP(-0.05*$F10))/0.05,$G10)</f>
+        <f>MAX((EXP(-0.05*MAX($E10,0))-EXP(-0.05*$F10))/0.05,$G10)</f>
         <v>0.04</v>
       </c>
       <c r="M10" s="125" cm="1">
@@ -7472,7 +7472,7 @@
         <v>78693.8680574733</v>
       </c>
       <c r="L18" s="125">
-        <f>SQRT($E18^2+$F18^2+$G18^2+1.4*$E18*$F18+1.4*$F18*$G18+0.6*$E18*$G18)</f>
+        <f>SQRT(MAX($E18^2+$F18^2+$G18^2+1.4*$E18*$F18+1.4*$F18*$G18+0.6*$E18*$G18,0))</f>
         <v>59269.963463710395</v>
       </c>
       <c r="M18" s="125" cm="1">
@@ -7550,7 +7550,7 @@
         <v>282</v>
       </c>
       <c r="L20" s="125">
-        <f>MIN(1,0.05+0.95*EXP($E20/(2*0.95*$F20)))</f>
+        <f>IF($F20&lt;=0,1,MIN(1,0.05+0.95*EXP($E20/(2*0.95*$F20))))</f>
         <v>0.9651926811871945</v>
       </c>
       <c r="M20" s="125" cm="1">
@@ -7583,7 +7583,7 @@
         <v>282</v>
       </c>
       <c r="L21" s="125">
-        <f>MIN(1,0.05+0.95*EXP($E21/(2*0.95*$F21)))</f>
+        <f>IF($F21&lt;=0,1,MIN(1,0.05+0.95*EXP($E21/(2*0.95*$F21))))</f>
         <v>1</v>
       </c>
       <c r="M21" s="125" cm="1">

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -48,6 +48,7 @@
     <definedName name="SACCR_RunInputs" hidden="1">""</definedName>
     <definedName name="SDFloorBD">Params!$E$13</definedName>
     <definedName name="SF_Table">Params!$C$28:$K$54</definedName>
+    <definedName name="Tests_Tolerance">Tests!$D$5</definedName>
     <definedName name="Trades_Header">Trades!$C$4</definedName>
     <definedName name="VolatilityFactor">Params!$E$18</definedName>
   </definedNames>
@@ -91,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="896">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -1617,7 +1618,7 @@
     <t>Message</t>
   </si>
   <si>
-    <t>Unit tests call the SACCR_* worksheet functions (macros enabled); portfolio tests are on TestCatalogue.</t>
+    <t>Unit tests call the SACCR_* worksheet functions (macros enabled) on the yellow inputs. Expected computes the same rule with Excel's own functions, so changing an input tests the function on new values. Portfolio tests are on TestCatalogue.</t>
   </si>
   <si>
     <t>Unit tests of the worksheet functions</t>
@@ -2680,6 +2681,117 @@
   </si>
   <si>
     <t>No results yet: build the workbook from the source, then press Run SA-CCR.</t>
+  </si>
+  <si>
+    <t>S, E (years)</t>
+  </si>
+  <si>
+    <t>CRE52.34; CRR Art. 279b(1)(a)</t>
+  </si>
+  <si>
+    <t>S, E, floor (years)</t>
+  </si>
+  <si>
+    <t>M (years)</t>
+  </si>
+  <si>
+    <t>CRE52.48; CRR Art. 279c(1)(a)</t>
+  </si>
+  <si>
+    <t>M (years), margined, MPOR (business days)</t>
+  </si>
+  <si>
+    <t>CRE52.52; CRR Art. 279c(1)(b)</t>
+  </si>
+  <si>
+    <t>P, K, T, volatility, call, bought</t>
+  </si>
+  <si>
+    <t>CRE52.40; CRR Art. 279a(1)(a)</t>
+  </si>
+  <si>
+    <t>P, K, T, volatility, call, bought, lambda</t>
+  </si>
+  <si>
+    <t>CRE52.40 FAQ; CRR-RTS Art. 5(1)</t>
+  </si>
+  <si>
+    <t>A, D, long</t>
+  </si>
+  <si>
+    <t>CRE52.41; CRR Art. 279a(1)(c)</t>
+  </si>
+  <si>
+    <t>D1, D2, D3 (bucket effective notionals)</t>
+  </si>
+  <si>
+    <t>CRE52.57(5); CRR Art. 280a</t>
+  </si>
+  <si>
+    <t>Add-ons A1, A2, A3, correlations 1, 2, 3</t>
+  </si>
+  <si>
+    <t>CRE52.61; CRR Art. 280c</t>
+  </si>
+  <si>
+    <t>V - C, add-on</t>
+  </si>
+  <si>
+    <t>CRE52.23; CRR Art. 278(3)</t>
+  </si>
+  <si>
+    <t>V, C, margined, TH, MTA, NICA</t>
+  </si>
+  <si>
+    <t>CRE52.10, .18; CRR Art. 275(1), (2)</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Standard normal distribution</t>
+  </si>
+  <si>
+    <t>P, K, interest rate</t>
+  </si>
+  <si>
+    <t>CRR-RTS Art. 5(2)</t>
+  </si>
+  <si>
+    <t>Arguments</t>
+  </si>
+  <si>
+    <t>Input 1</t>
+  </si>
+  <si>
+    <t>Input 2</t>
+  </si>
+  <si>
+    <t>Input 3</t>
+  </si>
+  <si>
+    <t>Input 4</t>
+  </si>
+  <si>
+    <t>Input 5</t>
+  </si>
+  <si>
+    <t>Input 6</t>
+  </si>
+  <si>
+    <t>Input 7</t>
+  </si>
+  <si>
+    <t>Expected (Excel)</t>
+  </si>
+  <si>
+    <t>Function (VBA)</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>Tolerance: a test passes when |Function - Expected| &lt;= tolerance x max(1, |Expected|)</t>
   </si>
 </sst>
 </file>
@@ -3106,7 +3218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3493,6 +3605,15 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6826,11 +6947,14 @@
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
     <col min="3" max="3" width="40.75" customWidth="1"/>
-    <col min="4" max="4" width="89.125" customWidth="1"/>
-    <col min="5" max="12" width="14.75" customWidth="1"/>
+    <col min="4" max="4" width="36.75" customWidth="1"/>
+    <col min="5" max="11" width="11.75" customWidth="1"/>
+    <col min="12" max="13" width="14.75" customWidth="1"/>
+    <col min="14" max="15" width="10.75" customWidth="1"/>
+    <col min="16" max="16" width="30.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
@@ -6861,7 +6985,7 @@
       <c r="AA1" s="66"/>
       <c r="AB1" s="66"/>
     </row>
-    <row r="2" spans="2:28" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
         <v>70</v>
       </c>
@@ -6892,569 +7016,884 @@
       <c r="AA2" s="68"/>
       <c r="AB2" s="68"/>
     </row>
-    <row r="3" spans="2:28" ht="21" x14ac:dyDescent="0.25">
+    <row r="3" ht="21" x14ac:dyDescent="0.25">
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="2" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="5" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="128" t="s">
+        <v>895</v>
+      </c>
+      <c r="D5" s="131">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="48" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="7" spans="2:28" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="54" t="s">
         <v>510</v>
       </c>
       <c r="D7" s="54" t="s">
-        <v>511</v>
+        <v>884</v>
       </c>
       <c r="E7" s="55" t="s">
-        <v>512</v>
+        <v>885</v>
       </c>
       <c r="F7" s="55" t="s">
-        <v>513</v>
+        <v>886</v>
       </c>
       <c r="G7" s="55" t="s">
+        <v>887</v>
+      </c>
+      <c r="H7" s="55" t="s">
+        <v>888</v>
+      </c>
+      <c r="I7" s="55" t="s">
+        <v>889</v>
+      </c>
+      <c r="J7" s="55" t="s">
+        <v>890</v>
+      </c>
+      <c r="K7" s="55" t="s">
+        <v>891</v>
+      </c>
+      <c r="L7" s="55" t="s">
+        <v>892</v>
+      </c>
+      <c r="M7" s="55" t="s">
+        <v>893</v>
+      </c>
+      <c r="N7" s="55" t="s">
         <v>514</v>
       </c>
-      <c r="H7" s="55" t="s">
+      <c r="O7" s="55" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="8" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P7" s="54" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="128" t="s">
         <v>516</v>
       </c>
-      <c r="D8" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F8)</f>
-        <v>=SACCR_SupervisoryDuration(0,10)</v>
-      </c>
-      <c r="E8" s="125">
-        <v>7.8693868057473324</v>
-      </c>
-      <c r="F8" s="125" cm="1">
-        <f t="array" ref="F8">SACCR_SupervisoryDuration(0,10)</f>
+      <c r="D8" s="24" t="s">
+        <v>859</v>
+      </c>
+      <c r="E8" s="129">
+        <v>0</v>
+      </c>
+      <c r="F8" s="129">
+        <v>10</v>
+      </c>
+      <c r="L8" s="125">
+        <f>(EXP(-0.05*MAX($E8,0))-EXP(-0.05*$F8))/0.05</f>
         <v>7.8693868057473315</v>
       </c>
-      <c r="G8" s="126">
-        <f t="shared" ref="G8:G29" si="0">IFERROR(ABS(F8-E8),"")</f>
-        <v>8.8817841970012523E-16</v>
-      </c>
-      <c r="H8" s="127" t="str">
-        <f t="shared" ref="H8:H29" si="1">IF(ISNUMBER(G8),IF(G8&lt;=0.000000001*MAX(1,ABS(E8)),"PASS","FAIL"),"FAIL")</f>
+      <c r="M8" s="125" cm="1">
+        <f t="array" ref="M8">SACCR_SupervisoryDuration($E8,$F8)</f>
+        <v>7.8693868057473315</v>
+      </c>
+      <c r="N8" s="126">
+        <f>IFERROR(ABS(M8-L8),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="127" t="str">
+        <f>IF(ISNUMBER(N8),IF(N8&lt;=Tests_Tolerance*MAX(1,ABS(L8)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="9" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P8" s="130" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="128" t="s">
         <v>518</v>
       </c>
-      <c r="D9" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F9)</f>
-        <v>=SACCR_SupervisoryDuration(1,11)</v>
-      </c>
-      <c r="E9" s="125">
-        <v>7.4855922824045473</v>
-      </c>
-      <c r="F9" s="125" cm="1">
-        <f t="array" ref="F9">SACCR_SupervisoryDuration(1,11)</f>
-        <v>7.4855922824045473</v>
-      </c>
-      <c r="G9" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="D9" s="24" t="s">
+        <v>859</v>
+      </c>
+      <c r="E9" s="129">
+        <v>1</v>
+      </c>
+      <c r="F9" s="129">
+        <v>11</v>
+      </c>
+      <c r="L9" s="125">
+        <f>(EXP(-0.05*MAX($E9,0))-EXP(-0.05*$F9))/0.05</f>
+        <v>7.485592282404547</v>
+      </c>
+      <c r="M9" s="125" cm="1">
+        <f t="array" ref="M9">SACCR_SupervisoryDuration($E9,$F9)</f>
+        <v>7.485592282404547</v>
+      </c>
+      <c r="N9" s="126">
+        <f>IFERROR(ABS(M9-L9),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="127" t="str">
+        <f>IF(ISNUMBER(N9),IF(N9&lt;=Tests_Tolerance*MAX(1,ABS(L9)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="10" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P9" s="130" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="128" t="s">
         <v>520</v>
       </c>
-      <c r="D10" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F10)</f>
-        <v>=SACCR_SupervisoryDuration(0,0.01,10/250)</v>
-      </c>
-      <c r="E10" s="125">
+      <c r="D10" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="E10" s="129">
+        <v>0</v>
+      </c>
+      <c r="F10" s="129">
+        <v>0.01</v>
+      </c>
+      <c r="G10" s="129">
+        <f>10/250</f>
         <v>0.04</v>
       </c>
-      <c r="F10" s="125" cm="1">
-        <f t="array" ref="F10">SACCR_SupervisoryDuration(0,0.01,10/250)</f>
+      <c r="L10" s="125">
+        <f>MAX((EXP(-0.05*MAX($E10,0))-EXP(-0.05*$F10))/0.05,$G10)</f>
         <v>0.04</v>
       </c>
-      <c r="G10" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M10" s="125" cm="1">
+        <f t="array" ref="M10">SACCR_SupervisoryDuration($E10,$F10,$G10)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N10" s="126">
+        <f>IFERROR(ABS(M10-L10),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="127" t="str">
+        <f>IF(ISNUMBER(N10),IF(N10&lt;=Tests_Tolerance*MAX(1,ABS(L10)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="11" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P10" s="130" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="128" t="s">
         <v>522</v>
       </c>
-      <c r="D11" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F11)</f>
-        <v>=SACCR_MaturityFactor(0.75)</v>
-      </c>
-      <c r="E11" s="125">
+      <c r="D11" s="24" t="s">
+        <v>862</v>
+      </c>
+      <c r="E11" s="129">
+        <v>0.75</v>
+      </c>
+      <c r="L11" s="125">
+        <f>SQRT(MIN(MAX($E11,10/250),1))</f>
         <v>0.8660254037844386</v>
       </c>
-      <c r="F11" s="125" cm="1">
-        <f t="array" ref="F11">SACCR_MaturityFactor(0.75)</f>
+      <c r="M11" s="125" cm="1">
+        <f t="array" ref="M11">SACCR_MaturityFactor($E11)</f>
         <v>0.8660254037844386</v>
       </c>
-      <c r="G11" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="N11" s="126">
+        <f>IFERROR(ABS(M11-L11),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="127" t="str">
+        <f>IF(ISNUMBER(N11),IF(N11&lt;=Tests_Tolerance*MAX(1,ABS(L11)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="12" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P11" s="130" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="128" t="s">
         <v>524</v>
       </c>
-      <c r="D12" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F12)</f>
-        <v>=SACCR_MaturityFactor(3/365)</v>
-      </c>
-      <c r="E12" s="125">
+      <c r="D12" s="24" t="s">
+        <v>862</v>
+      </c>
+      <c r="E12" s="129">
+        <f>3/365</f>
+        <v>0.00821917808219178</v>
+      </c>
+      <c r="L12" s="125">
+        <f>SQRT(MIN(MAX($E12,10/250),1))</f>
         <v>0.2</v>
       </c>
-      <c r="F12" s="125" cm="1">
-        <f t="array" ref="F12">SACCR_MaturityFactor(3/365)</f>
+      <c r="M12" s="125" cm="1">
+        <f t="array" ref="M12">SACCR_MaturityFactor($E12)</f>
         <v>0.2</v>
       </c>
-      <c r="G12" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="N12" s="126">
+        <f>IFERROR(ABS(M12-L12),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="127" t="str">
+        <f>IF(ISNUMBER(N12),IF(N12&lt;=Tests_Tolerance*MAX(1,ABS(L12)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="13" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P12" s="130" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="128" t="s">
         <v>526</v>
       </c>
-      <c r="D13" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F13)</f>
-        <v>=SACCR_MaturityFactor(0,TRUE,10)</v>
-      </c>
-      <c r="E13" s="125">
-        <v>0.3</v>
-      </c>
-      <c r="F13" s="125" cm="1">
-        <f t="array" ref="F13">SACCR_MaturityFactor(0,TRUE,10)</f>
+      <c r="D13" s="24" t="s">
+        <v>864</v>
+      </c>
+      <c r="E13" s="129">
+        <v>0</v>
+      </c>
+      <c r="F13" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="129">
+        <v>10</v>
+      </c>
+      <c r="L13" s="125">
+        <f>IF($F13,1.5*SQRT($G13/250),SQRT(MIN(MAX($E13,10/250),1)))</f>
         <v>0.30000000000000004</v>
       </c>
-      <c r="G13" s="126">
-        <f t="shared" si="0"/>
-        <v>5.5511151231257827E-17</v>
-      </c>
-      <c r="H13" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M13" s="125" cm="1">
+        <f t="array" ref="M13">SACCR_MaturityFactor($E13,$F13,$G13)</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="N13" s="126">
+        <f>IFERROR(ABS(M13-L13),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="127" t="str">
+        <f>IF(ISNUMBER(N13),IF(N13&lt;=Tests_Tolerance*MAX(1,ABS(L13)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="14" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P13" s="130" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="128" t="s">
         <v>528</v>
       </c>
-      <c r="D14" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F14)</f>
-        <v>=SACCR_OptionDelta(0.06,0.05,1,0.5,FALSE,TRUE)</v>
-      </c>
-      <c r="E14" s="125">
-        <v>-0.26939521771053271</v>
-      </c>
-      <c r="F14" s="125" cm="1">
-        <f t="array" ref="F14">SACCR_OptionDelta(0.06,0.05,1,0.5,FALSE,TRUE)</f>
-        <v>-0.26939521771053271</v>
-      </c>
-      <c r="G14" s="126">
-        <f t="shared" si="0"/>
+      <c r="D14" s="24" t="s">
+        <v>866</v>
+      </c>
+      <c r="E14" s="129">
+        <v>0.06</v>
+      </c>
+      <c r="F14" s="129">
+        <v>0.05</v>
+      </c>
+      <c r="G14" s="129">
+        <v>1</v>
+      </c>
+      <c r="H14" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="129" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="J14" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="125">
+        <f>IF($I14,_xlfn.NORM.S.DIST((LN(($E14+$K14)/($F14+$K14))+$H14^2*$G14/2)/($H14*SQRT($G14)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E14+$K14)/($F14+$K14))+$H14^2*$G14/2)/($H14*SQRT($G14)),TRUE))*IF($J14,1,-1)</f>
+        <v>-0.2693952177105327</v>
+      </c>
+      <c r="M14" s="125" cm="1">
+        <f t="array" ref="M14">SACCR_OptionDelta($E14,$F14,$G14,$H14,$I14,$J14)</f>
+        <v>-0.2693952177105327</v>
+      </c>
+      <c r="N14" s="126">
+        <f>IFERROR(ABS(M14-L14),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="127" t="str">
+        <f>IF(ISNUMBER(N14),IF(N14&lt;=Tests_Tolerance*MAX(1,ABS(L14)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="15" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P14" s="130" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="128" t="s">
         <v>530</v>
       </c>
-      <c r="D15" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F15)</f>
-        <v>=SACCR_OptionDelta(100,110,0.5,0.32,TRUE,FALSE)</v>
-      </c>
-      <c r="E15" s="125">
-        <v>-0.37901134582780288</v>
-      </c>
-      <c r="F15" s="125" cm="1">
-        <f t="array" ref="F15">SACCR_OptionDelta(100,110,0.5,0.32,TRUE,FALSE)</f>
+      <c r="D15" s="24" t="s">
+        <v>866</v>
+      </c>
+      <c r="E15" s="129">
+        <v>100</v>
+      </c>
+      <c r="F15" s="129">
+        <v>110</v>
+      </c>
+      <c r="G15" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="129">
+        <v>0.32</v>
+      </c>
+      <c r="I15" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="129" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="125">
+        <f>IF($I15,_xlfn.NORM.S.DIST((LN(($E15+$K15)/($F15+$K15))+$H15^2*$G15/2)/($H15*SQRT($G15)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E15+$K15)/($F15+$K15))+$H15^2*$G15/2)/($H15*SQRT($G15)),TRUE))*IF($J15,1,-1)</f>
         <v>-0.37901134582780294</v>
       </c>
-      <c r="G15" s="126">
-        <f t="shared" si="0"/>
-        <v>5.5511151231257827E-17</v>
-      </c>
-      <c r="H15" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M15" s="125" cm="1">
+        <f t="array" ref="M15">SACCR_OptionDelta($E15,$F15,$G15,$H15,$I15,$J15)</f>
+        <v>-0.37901134582780294</v>
+      </c>
+      <c r="N15" s="126">
+        <f>IFERROR(ABS(M15-L15),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="127" t="str">
+        <f>IF(ISNUMBER(N15),IF(N15&lt;=Tests_Tolerance*MAX(1,ABS(L15)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="16" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P15" s="130" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="128" t="s">
         <v>532</v>
       </c>
-      <c r="D16" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F16)</f>
-        <v>=SACCR_OptionDelta(-0.002,0.001,2,0.5,TRUE,TRUE,0.01)</v>
-      </c>
-      <c r="E16" s="125">
-        <v>0.46143935794124907</v>
-      </c>
-      <c r="F16" s="125" cm="1">
-        <f t="array" ref="F16">SACCR_OptionDelta(-0.002,0.001,2,0.5,TRUE,TRUE,0.01)</f>
+      <c r="D16" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="E16" s="129">
+        <v>-0.002</v>
+      </c>
+      <c r="F16" s="129">
+        <v>0.001</v>
+      </c>
+      <c r="G16" s="129">
+        <v>2</v>
+      </c>
+      <c r="H16" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="I16" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" s="129">
+        <v>0.01</v>
+      </c>
+      <c r="L16" s="125">
+        <f>IF($I16,_xlfn.NORM.S.DIST((LN(($E16+$K16)/($F16+$K16))+$H16^2*$G16/2)/($H16*SQRT($G16)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E16+$K16)/($F16+$K16))+$H16^2*$G16/2)/($H16*SQRT($G16)),TRUE))*IF($J16,1,-1)</f>
         <v>0.46143935794124913</v>
       </c>
-      <c r="G16" s="126">
-        <f t="shared" si="0"/>
-        <v>5.5511151231257827E-17</v>
-      </c>
-      <c r="H16" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M16" s="125" cm="1">
+        <f t="array" ref="M16">SACCR_OptionDelta($E16,$F16,$G16,$H16,$I16,$J16,$K16)</f>
+        <v>0.46143935794124913</v>
+      </c>
+      <c r="N16" s="126">
+        <f>IFERROR(ABS(M16-L16),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="127" t="str">
+        <f>IF(ISNUMBER(N16),IF(N16&lt;=Tests_Tolerance*MAX(1,ABS(L16)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="17" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P16" s="130" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="128" t="s">
         <v>534</v>
       </c>
-      <c r="D17" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F17)</f>
-        <v>=SACCR_CDODelta(0.03,0.06,TRUE)</v>
-      </c>
-      <c r="E17" s="125">
+      <c r="D17" s="24" t="s">
+        <v>870</v>
+      </c>
+      <c r="E17" s="129">
+        <v>0.03</v>
+      </c>
+      <c r="F17" s="129">
+        <v>0.06</v>
+      </c>
+      <c r="G17" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="125">
+        <f>15/((1+14*$E17)*(1+14*$F17))*IF($G17,1,-1)</f>
+        <v>5.740967544396817</v>
+      </c>
+      <c r="M17" s="125" cm="1">
+        <f t="array" ref="M17">SACCR_CDODelta($E17,$F17,$G17)</f>
         <v>5.740967544396816</v>
       </c>
-      <c r="F17" s="125" cm="1">
-        <f t="array" ref="F17">SACCR_CDODelta(0.03,0.06,TRUE)</f>
-        <v>5.740967544396816</v>
-      </c>
-      <c r="G17" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="N17" s="126">
+        <f>IFERROR(ABS(M17-L17),"")</f>
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="O17" s="127" t="str">
+        <f>IF(ISNUMBER(N17),IF(N17&lt;=Tests_Tolerance*MAX(1,ABS(L17)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="18" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P17" s="130" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="128" t="s">
         <v>536</v>
       </c>
-      <c r="D18" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F18)</f>
-        <v>=SACCR_IREffectiveNotional(0,-36253.8493844036,78693.8680574733)</v>
-      </c>
-      <c r="E18" s="125">
-        <v>59269.963463710403</v>
-      </c>
-      <c r="F18" s="125" cm="1">
-        <f t="array" ref="F18">SACCR_IREffectiveNotional(0,-36253.8493844036,78693.8680574733)</f>
+      <c r="D18" s="24" t="s">
+        <v>872</v>
+      </c>
+      <c r="E18" s="129">
+        <v>0</v>
+      </c>
+      <c r="F18" s="129">
+        <v>-36253.8493844036</v>
+      </c>
+      <c r="G18" s="129">
+        <v>78693.8680574733</v>
+      </c>
+      <c r="L18" s="125">
+        <f>SQRT(MAX($E18^2+$F18^2+$G18^2+1.4*$E18*$F18+1.4*$F18*$G18+0.6*$E18*$G18,0))</f>
         <v>59269.963463710395</v>
       </c>
-      <c r="G18" s="126">
-        <f t="shared" si="0"/>
-        <v>7.2759576141834259E-12</v>
-      </c>
-      <c r="H18" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M18" s="125" cm="1">
+        <f t="array" ref="M18">SACCR_IREffectiveNotional($E18,$F18,$G18)</f>
+        <v>59269.963463710395</v>
+      </c>
+      <c r="N18" s="126">
+        <f>IFERROR(ABS(M18-L18),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="127" t="str">
+        <f>IF(ISNUMBER(N18),IF(N18&lt;=Tests_Tolerance*MAX(1,ABS(L18)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="19" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P18" s="130" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="128" t="s">
         <v>538</v>
       </c>
-      <c r="D19" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F19)</f>
-        <v>=SACCR_FactorAggregation({105.861937916956,-279.916321663744,168.111404865732},{0.5,0.5,0.8})</v>
-      </c>
-      <c r="E19" s="125">
-        <v>282.1288318596666</v>
-      </c>
-      <c r="F19" s="125" cm="1">
-        <f t="array" ref="F19">SACCR_FactorAggregation({105.861937916956,-279.916321663744,168.111404865732},{0.5,0.5,0.8})</f>
+      <c r="D19" s="24" t="s">
+        <v>874</v>
+      </c>
+      <c r="E19" s="129">
+        <v>105.861937916956</v>
+      </c>
+      <c r="F19" s="129">
+        <v>-279.916321663744</v>
+      </c>
+      <c r="G19" s="129">
+        <v>168.111404865732</v>
+      </c>
+      <c r="H19" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="J19" s="129">
+        <v>0.8</v>
+      </c>
+      <c r="L19" s="125">
+        <f>SQRT(SUMPRODUCT($E19:$G19,$H19:$J19)^2+SUMPRODUCT((1-$H19:$J19^2)*$E19:$G19^2))</f>
         <v>282.12883185966604</v>
       </c>
-      <c r="G19" s="126">
-        <f t="shared" si="0"/>
-        <v>5.6843418860808015E-13</v>
-      </c>
-      <c r="H19" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M19" s="125" cm="1">
+        <f t="array" ref="M19">SACCR_FactorAggregation($E19:$G19,$H19:$J19)</f>
+        <v>282.12883185966604</v>
+      </c>
+      <c r="N19" s="126">
+        <f>IFERROR(ABS(M19-L19),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="127" t="str">
+        <f>IF(ISNUMBER(N19),IF(N19&lt;=Tests_Tolerance*MAX(1,ABS(L19)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="20" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P19" s="130" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="128" t="s">
         <v>540</v>
       </c>
-      <c r="D20" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F20)</f>
-        <v>=SACCR_Multiplier(-20,282)</v>
-      </c>
-      <c r="E20" s="125">
-        <v>0.96519268118719448</v>
-      </c>
-      <c r="F20" s="125" cm="1">
-        <f t="array" ref="F20">SACCR_Multiplier(-20,282)</f>
-        <v>0.96519268118719448</v>
-      </c>
-      <c r="G20" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="D20" s="24" t="s">
+        <v>876</v>
+      </c>
+      <c r="E20" s="129">
+        <v>-20</v>
+      </c>
+      <c r="F20" s="129">
+        <v>282</v>
+      </c>
+      <c r="L20" s="125">
+        <f>IF($F20&lt;=0,1,MIN(1,0.05+0.95*EXP($E20/(2*0.95*$F20))))</f>
+        <v>0.9651926811871945</v>
+      </c>
+      <c r="M20" s="125" cm="1">
+        <f t="array" ref="M20">SACCR_Multiplier($E20,$F20)</f>
+        <v>0.9651926811871945</v>
+      </c>
+      <c r="N20" s="126">
+        <f>IFERROR(ABS(M20-L20),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="127" t="str">
+        <f>IF(ISNUMBER(N20),IF(N20&lt;=Tests_Tolerance*MAX(1,ABS(L20)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="21" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P20" s="130" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="128" t="s">
         <v>542</v>
       </c>
-      <c r="D21" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F21)</f>
-        <v>=SACCR_Multiplier(10,282)</v>
-      </c>
-      <c r="E21" s="125">
+      <c r="D21" s="24" t="s">
+        <v>876</v>
+      </c>
+      <c r="E21" s="129">
+        <v>10</v>
+      </c>
+      <c r="F21" s="129">
+        <v>282</v>
+      </c>
+      <c r="L21" s="125">
+        <f>IF($F21&lt;=0,1,MIN(1,0.05+0.95*EXP($E21/(2*0.95*$F21))))</f>
         <v>1</v>
       </c>
-      <c r="F21" s="125" cm="1">
-        <f t="array" ref="F21">SACCR_Multiplier(10,282)</f>
-        <v>1</v>
-      </c>
-      <c r="G21" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M21" s="125" cm="1">
+        <f t="array" ref="M21">SACCR_Multiplier($E21,$F21)</f>
+        <v>1.0</v>
+      </c>
+      <c r="N21" s="126">
+        <f>IFERROR(ABS(M21-L21),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="127" t="str">
+        <f>IF(ISNUMBER(N21),IF(N21&lt;=Tests_Tolerance*MAX(1,ABS(L21)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="22" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P21" s="130" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="128" t="s">
         <v>544</v>
       </c>
-      <c r="D22" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F22)</f>
-        <v>=SACCR_ReplacementCost(5,10,TRUE,0,10,2)</v>
-      </c>
-      <c r="E22" s="125">
+      <c r="D22" s="24" t="s">
+        <v>878</v>
+      </c>
+      <c r="E22" s="129">
+        <v>5</v>
+      </c>
+      <c r="F22" s="129">
+        <v>10</v>
+      </c>
+      <c r="G22" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="129">
+        <v>0</v>
+      </c>
+      <c r="I22" s="129">
+        <v>10</v>
+      </c>
+      <c r="J22" s="129">
+        <v>2</v>
+      </c>
+      <c r="L22" s="125">
+        <f>IF($G22,MAX($E22-$F22,$H22+$I22-$J22,0),MAX($E22-$F22,0))</f>
         <v>8</v>
       </c>
-      <c r="F22" s="125" cm="1">
-        <f t="array" ref="F22">SACCR_ReplacementCost(5,10,TRUE,0,10,2)</f>
-        <v>8</v>
-      </c>
-      <c r="G22" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M22" s="125" cm="1">
+        <f t="array" ref="M22">SACCR_ReplacementCost($E22,$F22,$G22,$H22,$I22,$J22)</f>
+        <v>8.0</v>
+      </c>
+      <c r="N22" s="126">
+        <f>IFERROR(ABS(M22-L22),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="127" t="str">
+        <f>IF(ISNUMBER(N22),IF(N22&lt;=Tests_Tolerance*MAX(1,ABS(L22)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="23" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P22" s="130" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="128" t="s">
         <v>546</v>
       </c>
-      <c r="D23" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F23)</f>
-        <v>=SACCR_NormCDF(1.96)</v>
-      </c>
-      <c r="E23" s="125">
-        <v>0.97500210485177952</v>
-      </c>
-      <c r="F23" s="125" cm="1">
-        <f t="array" ref="F23">SACCR_NormCDF(1.96)</f>
-        <v>0.97500210485177952</v>
-      </c>
-      <c r="G23" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="D23" s="24" t="s">
+        <v>880</v>
+      </c>
+      <c r="E23" s="129">
+        <v>1.96</v>
+      </c>
+      <c r="L23" s="125">
+        <f>_xlfn.NORM.S.DIST($E23,TRUE)</f>
+        <v>0.9750021048517795</v>
+      </c>
+      <c r="M23" s="125" cm="1">
+        <f t="array" ref="M23">SACCR_NormCDF($E23)</f>
+        <v>0.9750021048517795</v>
+      </c>
+      <c r="N23" s="126">
+        <f>IFERROR(ABS(M23-L23),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="127" t="str">
+        <f>IF(ISNUMBER(N23),IF(N23&lt;=Tests_Tolerance*MAX(1,ABS(L23)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="24" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P23" s="130" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="128" t="s">
         <v>548</v>
       </c>
-      <c r="D24" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F24)</f>
-        <v>=SACCR_NormCDF(-8)</v>
-      </c>
-      <c r="E24" s="125">
-        <v>6.2209605742718194E-16</v>
-      </c>
-      <c r="F24" s="125" cm="1">
-        <f t="array" ref="F24">SACCR_NormCDF(-8)</f>
-        <v>6.2209605201427843E-16</v>
-      </c>
-      <c r="G24" s="126">
-        <f t="shared" si="0"/>
-        <v>5.4129035033506995E-24</v>
-      </c>
-      <c r="H24" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="D24" s="24" t="s">
+        <v>880</v>
+      </c>
+      <c r="E24" s="129">
+        <v>-8</v>
+      </c>
+      <c r="L24" s="125">
+        <f>_xlfn.NORM.S.DIST($E24,TRUE)</f>
+        <v>6.220960574271819e-16</v>
+      </c>
+      <c r="M24" s="125" cm="1">
+        <f t="array" ref="M24">SACCR_NormCDF($E24)</f>
+        <v>6.220960520142784e-16</v>
+      </c>
+      <c r="N24" s="126">
+        <f>IFERROR(ABS(M24-L24),"")</f>
+        <v>5.4129035033506995e-24</v>
+      </c>
+      <c r="O24" s="127" t="str">
+        <f>IF(ISNUMBER(N24),IF(N24&lt;=Tests_Tolerance*MAX(1,ABS(L24)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="25" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="130" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="128" t="s">
         <v>550</v>
       </c>
-      <c r="D25" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F25)</f>
-        <v>=SACCR_LambdaCRR(-0.002,0.001,TRUE)</v>
-      </c>
-      <c r="E25" s="125">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="F25" s="125" cm="1">
-        <f t="array" ref="F25">SACCR_LambdaCRR(-0.002,0.001,TRUE)</f>
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="G25" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="D25" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="E25" s="129">
+        <v>-0.002</v>
+      </c>
+      <c r="F25" s="129">
+        <v>0.001</v>
+      </c>
+      <c r="G25" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="125">
+        <f>IF($G25,MAX(0.001-MIN($E25,$F25),0),MAX(-(1+0.1)*MIN($E25,$F25),0))</f>
+        <v>0.003</v>
+      </c>
+      <c r="M25" s="125" cm="1">
+        <f t="array" ref="M25">SACCR_LambdaCRR($E25,$F25,$G25)</f>
+        <v>0.003</v>
+      </c>
+      <c r="N25" s="126">
+        <f>IFERROR(ABS(M25-L25),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="127" t="str">
+        <f>IF(ISNUMBER(N25),IF(N25&lt;=Tests_Tolerance*MAX(1,ABS(L25)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="26" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P25" s="130" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="128" t="s">
         <v>552</v>
       </c>
-      <c r="D26" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F26)</f>
-        <v>=SACCR_LambdaCRR(0.02,0.03,TRUE)</v>
-      </c>
-      <c r="E26" s="125">
+      <c r="D26" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="E26" s="129">
+        <v>0.02</v>
+      </c>
+      <c r="F26" s="129">
+        <v>0.03</v>
+      </c>
+      <c r="G26" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="125">
+        <f>IF($G26,MAX(0.001-MIN($E26,$F26),0),MAX(-(1+0.1)*MIN($E26,$F26),0))</f>
         <v>0</v>
       </c>
-      <c r="F26" s="125" cm="1">
-        <f t="array" ref="F26">SACCR_LambdaCRR(0.02,0.03,TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M26" s="125" cm="1">
+        <f t="array" ref="M26">SACCR_LambdaCRR($E26,$F26,$G26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="126">
+        <f>IFERROR(ABS(M26-L26),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="127" t="str">
+        <f>IF(ISNUMBER(N26),IF(N26&lt;=Tests_Tolerance*MAX(1,ABS(L26)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="27" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P26" s="130" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="128" t="s">
         <v>554</v>
       </c>
-      <c r="D27" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F27)</f>
-        <v>=SACCR_LambdaCRR(0.0005,0.01,TRUE)</v>
-      </c>
-      <c r="E27" s="125">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="F27" s="125" cm="1">
-        <f t="array" ref="F27">SACCR_LambdaCRR(0.0005,0.01,TRUE)</f>
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="G27" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="D27" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="E27" s="129">
+        <v>0.0005</v>
+      </c>
+      <c r="F27" s="129">
+        <v>0.01</v>
+      </c>
+      <c r="G27" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="125">
+        <f>IF($G27,MAX(0.001-MIN($E27,$F27),0),MAX(-(1+0.1)*MIN($E27,$F27),0))</f>
+        <v>0.0005</v>
+      </c>
+      <c r="M27" s="125" cm="1">
+        <f t="array" ref="M27">SACCR_LambdaCRR($E27,$F27,$G27)</f>
+        <v>0.0005</v>
+      </c>
+      <c r="N27" s="126">
+        <f>IFERROR(ABS(M27-L27),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="127" t="str">
+        <f>IF(ISNUMBER(N27),IF(N27&lt;=Tests_Tolerance*MAX(1,ABS(L27)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="28" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P27" s="130" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="128" t="s">
         <v>556</v>
       </c>
-      <c r="D28" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F28)</f>
-        <v>=SACCR_LambdaCRR(-5,-4,FALSE)</v>
-      </c>
-      <c r="E28" s="125">
+      <c r="D28" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="E28" s="129">
+        <v>-5</v>
+      </c>
+      <c r="F28" s="129">
+        <v>-4</v>
+      </c>
+      <c r="G28" s="129" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="125">
+        <f>IF($G28,MAX(0.001-MIN($E28,$F28),0),MAX(-(1+0.1)*MIN($E28,$F28),0))</f>
         <v>5.5</v>
       </c>
-      <c r="F28" s="125" cm="1">
-        <f t="array" ref="F28">SACCR_LambdaCRR(-5,-4,FALSE)</f>
+      <c r="M28" s="125" cm="1">
+        <f t="array" ref="M28">SACCR_LambdaCRR($E28,$F28,$G28)</f>
         <v>5.5</v>
       </c>
-      <c r="G28" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="N28" s="126">
+        <f>IFERROR(ABS(M28-L28),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="127" t="str">
+        <f>IF(ISNUMBER(N28),IF(N28&lt;=Tests_Tolerance*MAX(1,ABS(L28)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="29" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P28" s="130" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="128" t="s">
         <v>558</v>
       </c>
-      <c r="D29" s="24" t="str">
-        <f>_xlfn.FORMULATEXT(F29)</f>
-        <v>=SACCR_LambdaCRR(40,35,FALSE)</v>
-      </c>
-      <c r="E29" s="125">
+      <c r="D29" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="E29" s="129">
+        <v>40</v>
+      </c>
+      <c r="F29" s="129">
+        <v>35</v>
+      </c>
+      <c r="G29" s="129" t="b">
         <v>0</v>
       </c>
-      <c r="F29" s="125" cm="1">
-        <f t="array" ref="F29">SACCR_LambdaCRR(40,35,FALSE)</f>
+      <c r="L29" s="125">
+        <f>IF($G29,MAX(0.001-MIN($E29,$F29),0),MAX(-(1+0.1)*MIN($E29,$F29),0))</f>
         <v>0</v>
       </c>
-      <c r="G29" s="126">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="127" t="str">
-        <f t="shared" si="1"/>
+      <c r="M29" s="125" cm="1">
+        <f t="array" ref="M29">SACCR_LambdaCRR($E29,$F29,$G29)</f>
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="126">
+        <f>IFERROR(ABS(M29-L29),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="127" t="str">
+        <f>IF(ISNUMBER(N29),IF(N29&lt;=Tests_Tolerance*MAX(1,ABS(L29)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
+      <c r="P29" s="130" t="s">
+        <v>883</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%." sqref="D5">
+      <formula1>0.0000000000000001</formula1>
+      <formula2>0.01</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
 </worksheet>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -17,7 +17,7 @@
     <sheet name="TradeCalc" sheetId="8" r:id="rId8"/>
     <sheet name="Checks" sheetId="9" r:id="rId9"/>
     <sheet name="TestCatalogue" sheetId="10" r:id="rId10"/>
-    <sheet name="Tests" sheetId="11" r:id="rId11"/>
+    <sheet name="FormulaTest" sheetId="11" r:id="rId11"/>
     <sheet name="Basel_vs_CRR" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
@@ -28,6 +28,7 @@
     <definedName name="BasisFactor">Params!$E$17</definedName>
     <definedName name="BusinessDaysPerYear">Params!$E$11</definedName>
     <definedName name="DaysPerYear">Params!$E$10</definedName>
+    <definedName name="FormulaTest_Tolerance">FormulaTest!$D$5</definedName>
     <definedName name="FX_Table">Params!$C$57:$E$62</definedName>
     <definedName name="IRBucketOffset">Params!$E$22</definedName>
     <definedName name="IRCorrBucket12">Params!$E$19</definedName>
@@ -48,7 +49,6 @@
     <definedName name="SACCR_RunInputs" hidden="1">""</definedName>
     <definedName name="SDFloorBD">Params!$E$13</definedName>
     <definedName name="SF_Table">Params!$C$28:$K$54</definedName>
-    <definedName name="Tests_Tolerance">Tests!$D$5</definedName>
     <definedName name="Trades_Header">Trades!$C$4</definedName>
     <definedName name="VolatilityFactor">Params!$E$18</definedName>
   </definedNames>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="898">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -136,7 +136,7 @@
     <t>6. Review</t>
   </si>
   <si>
-    <t>Checks lists every excluded trade and warning. TestCatalogue compares the engine with published / hand-calculated reference values per regime; Tests unit-tests the formula functions.</t>
+    <t>Checks lists every excluded trade and warning. TestCatalogue compares the engine with published / hand-calculated reference values per regime; FormulaTest unit-tests the formula functions.</t>
   </si>
   <si>
     <t>7. Regime</t>
@@ -2338,7 +2338,7 @@
     <t>Common table on Params.</t>
   </si>
   <si>
-    <t>Tests sheet</t>
+    <t>FormulaTest sheet</t>
   </si>
   <si>
     <t>Credit supervisory factors</t>
@@ -2792,6 +2792,12 @@
   </si>
   <si>
     <t>Tolerance: a test passes when |Function - Expected| &lt;= tolerance x max(1, |Expected|)</t>
+  </si>
+  <si>
+    <t>FormulaTest</t>
+  </si>
+  <si>
+    <t>Formula tests</t>
   </si>
 </sst>
 </file>
@@ -5000,7 +5006,7 @@
     </row>
     <row r="46" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="25" t="s">
-        <v>70</v>
+        <v>896</v>
       </c>
       <c r="D46" s="34" t="s">
         <v>71</v>
@@ -6987,7 +6993,7 @@
     </row>
     <row r="2" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
-        <v>70</v>
+        <v>897</v>
       </c>
       <c r="C2" s="31"/>
       <c r="D2" s="32"/>
@@ -7107,7 +7113,7 @@
         <v>0.0</v>
       </c>
       <c r="O8" s="127" t="str">
-        <f>IF(ISNUMBER(N8),IF(N8&lt;=Tests_Tolerance*MAX(1,ABS(L8)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N8),IF(N8&lt;=FormulaTest_Tolerance*MAX(1,ABS(L8)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P8" s="130" t="s">
@@ -7140,7 +7146,7 @@
         <v>0.0</v>
       </c>
       <c r="O9" s="127" t="str">
-        <f>IF(ISNUMBER(N9),IF(N9&lt;=Tests_Tolerance*MAX(1,ABS(L9)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N9),IF(N9&lt;=FormulaTest_Tolerance*MAX(1,ABS(L9)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P9" s="130" t="s">
@@ -7177,7 +7183,7 @@
         <v>0.0</v>
       </c>
       <c r="O10" s="127" t="str">
-        <f>IF(ISNUMBER(N10),IF(N10&lt;=Tests_Tolerance*MAX(1,ABS(L10)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N10),IF(N10&lt;=FormulaTest_Tolerance*MAX(1,ABS(L10)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P10" s="130" t="s">
@@ -7207,7 +7213,7 @@
         <v>0.0</v>
       </c>
       <c r="O11" s="127" t="str">
-        <f>IF(ISNUMBER(N11),IF(N11&lt;=Tests_Tolerance*MAX(1,ABS(L11)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N11),IF(N11&lt;=FormulaTest_Tolerance*MAX(1,ABS(L11)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P11" s="130" t="s">
@@ -7238,7 +7244,7 @@
         <v>0.0</v>
       </c>
       <c r="O12" s="127" t="str">
-        <f>IF(ISNUMBER(N12),IF(N12&lt;=Tests_Tolerance*MAX(1,ABS(L12)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N12),IF(N12&lt;=FormulaTest_Tolerance*MAX(1,ABS(L12)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P12" s="130" t="s">
@@ -7274,7 +7280,7 @@
         <v>0.0</v>
       </c>
       <c r="O13" s="127" t="str">
-        <f>IF(ISNUMBER(N13),IF(N13&lt;=Tests_Tolerance*MAX(1,ABS(L13)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N13),IF(N13&lt;=FormulaTest_Tolerance*MAX(1,ABS(L13)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P13" s="130" t="s">
@@ -7319,7 +7325,7 @@
         <v>0.0</v>
       </c>
       <c r="O14" s="127" t="str">
-        <f>IF(ISNUMBER(N14),IF(N14&lt;=Tests_Tolerance*MAX(1,ABS(L14)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N14),IF(N14&lt;=FormulaTest_Tolerance*MAX(1,ABS(L14)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P14" s="130" t="s">
@@ -7364,7 +7370,7 @@
         <v>0.0</v>
       </c>
       <c r="O15" s="127" t="str">
-        <f>IF(ISNUMBER(N15),IF(N15&lt;=Tests_Tolerance*MAX(1,ABS(L15)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N15),IF(N15&lt;=FormulaTest_Tolerance*MAX(1,ABS(L15)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P15" s="130" t="s">
@@ -7412,7 +7418,7 @@
         <v>0.0</v>
       </c>
       <c r="O16" s="127" t="str">
-        <f>IF(ISNUMBER(N16),IF(N16&lt;=Tests_Tolerance*MAX(1,ABS(L16)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N16),IF(N16&lt;=FormulaTest_Tolerance*MAX(1,ABS(L16)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P16" s="130" t="s">
@@ -7448,7 +7454,7 @@
         <v>8.881784197001252e-16</v>
       </c>
       <c r="O17" s="127" t="str">
-        <f>IF(ISNUMBER(N17),IF(N17&lt;=Tests_Tolerance*MAX(1,ABS(L17)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N17),IF(N17&lt;=FormulaTest_Tolerance*MAX(1,ABS(L17)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P17" s="130" t="s">
@@ -7484,7 +7490,7 @@
         <v>0.0</v>
       </c>
       <c r="O18" s="127" t="str">
-        <f>IF(ISNUMBER(N18),IF(N18&lt;=Tests_Tolerance*MAX(1,ABS(L18)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N18),IF(N18&lt;=FormulaTest_Tolerance*MAX(1,ABS(L18)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P18" s="130" t="s">
@@ -7529,7 +7535,7 @@
         <v>0.0</v>
       </c>
       <c r="O19" s="127" t="str">
-        <f>IF(ISNUMBER(N19),IF(N19&lt;=Tests_Tolerance*MAX(1,ABS(L19)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N19),IF(N19&lt;=FormulaTest_Tolerance*MAX(1,ABS(L19)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P19" s="130" t="s">
@@ -7562,7 +7568,7 @@
         <v>0.0</v>
       </c>
       <c r="O20" s="127" t="str">
-        <f>IF(ISNUMBER(N20),IF(N20&lt;=Tests_Tolerance*MAX(1,ABS(L20)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N20),IF(N20&lt;=FormulaTest_Tolerance*MAX(1,ABS(L20)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P20" s="130" t="s">
@@ -7595,7 +7601,7 @@
         <v>0.0</v>
       </c>
       <c r="O21" s="127" t="str">
-        <f>IF(ISNUMBER(N21),IF(N21&lt;=Tests_Tolerance*MAX(1,ABS(L21)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N21),IF(N21&lt;=FormulaTest_Tolerance*MAX(1,ABS(L21)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P21" s="130" t="s">
@@ -7640,7 +7646,7 @@
         <v>0.0</v>
       </c>
       <c r="O22" s="127" t="str">
-        <f>IF(ISNUMBER(N22),IF(N22&lt;=Tests_Tolerance*MAX(1,ABS(L22)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N22),IF(N22&lt;=FormulaTest_Tolerance*MAX(1,ABS(L22)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P22" s="130" t="s">
@@ -7670,7 +7676,7 @@
         <v>0.0</v>
       </c>
       <c r="O23" s="127" t="str">
-        <f>IF(ISNUMBER(N23),IF(N23&lt;=Tests_Tolerance*MAX(1,ABS(L23)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N23),IF(N23&lt;=FormulaTest_Tolerance*MAX(1,ABS(L23)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P23" s="130" t="s">
@@ -7700,7 +7706,7 @@
         <v>5.4129035033506995e-24</v>
       </c>
       <c r="O24" s="127" t="str">
-        <f>IF(ISNUMBER(N24),IF(N24&lt;=Tests_Tolerance*MAX(1,ABS(L24)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N24),IF(N24&lt;=FormulaTest_Tolerance*MAX(1,ABS(L24)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P24" s="130" t="s">
@@ -7736,7 +7742,7 @@
         <v>0.0</v>
       </c>
       <c r="O25" s="127" t="str">
-        <f>IF(ISNUMBER(N25),IF(N25&lt;=Tests_Tolerance*MAX(1,ABS(L25)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N25),IF(N25&lt;=FormulaTest_Tolerance*MAX(1,ABS(L25)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P25" s="130" t="s">
@@ -7772,7 +7778,7 @@
         <v>0.0</v>
       </c>
       <c r="O26" s="127" t="str">
-        <f>IF(ISNUMBER(N26),IF(N26&lt;=Tests_Tolerance*MAX(1,ABS(L26)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N26),IF(N26&lt;=FormulaTest_Tolerance*MAX(1,ABS(L26)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P26" s="130" t="s">
@@ -7808,7 +7814,7 @@
         <v>0.0</v>
       </c>
       <c r="O27" s="127" t="str">
-        <f>IF(ISNUMBER(N27),IF(N27&lt;=Tests_Tolerance*MAX(1,ABS(L27)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N27),IF(N27&lt;=FormulaTest_Tolerance*MAX(1,ABS(L27)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P27" s="130" t="s">
@@ -7844,7 +7850,7 @@
         <v>0.0</v>
       </c>
       <c r="O28" s="127" t="str">
-        <f>IF(ISNUMBER(N28),IF(N28&lt;=Tests_Tolerance*MAX(1,ABS(L28)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N28),IF(N28&lt;=FormulaTest_Tolerance*MAX(1,ABS(L28)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P28" s="130" t="s">
@@ -7880,7 +7886,7 @@
         <v>0.0</v>
       </c>
       <c r="O29" s="127" t="str">
-        <f>IF(ISNUMBER(N29),IF(N29&lt;=Tests_Tolerance*MAX(1,ABS(L29)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N29),IF(N29&lt;=FormulaTest_Tolerance*MAX(1,ABS(L29)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P29" s="130" t="s">

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -7894,10 +7894,106 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="31">
     <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%." sqref="D5">
       <formula1>0.0000000000000001</formula1>
       <formula2>0.01</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid start date" error="Enter a number of years from -50 to 50." promptTitle="Start date S (years)" prompt="Years from today to the start of the period referenced. Zero or negative means already started and is floored at 0 (CRE52.34; CRR Art. 279b(1)(a))." sqref="E8:E10">
+      <formula1>-50</formula1>
+      <formula2>50</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid end date" error="Enter a number of years after the start date and after 0, at most 50." promptTitle="End date E (years)" prompt="Years from today to the end of the period referenced: after the start date and after today, at most 50 (CRE52.34)." sqref="F8:F10">
+      <formula1>AND(ISNUMBER(F8),F8&gt;MAX(E8,0),F8&lt;=50)</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid floor" error="Enter a number of years from 0 to 1." promptTitle="SD floor (years)" prompt="Floor on the supervisory duration, in years: 10 business days = 10/250 (CRE52.34)." sqref="G10">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid maturity" error="Enter a number of years from 0 to 50." promptTitle="Maturity M (years)" prompt="Remaining maturity in years. The unmargined factor floors it at 10 business days and caps it at 1 year (CRE52.48; CRR Art. 279c(1)(a))." sqref="E11:E13">
+      <formula1>0</formula1>
+      <formula2>50</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Margined" prompt="TRUE = margined factor 1.5 x sqrt(MPOR / 250) (CRE52.52; CRR Art. 279c(1)(b)). FALSE = unmargined factor from M." sqref="F13">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid MPOR" error="Enter a whole number of business days from 1 to 250." promptTitle="MPOR (business days)" prompt="Margin period of risk in business days, used when margined (CRE52.50-52; CRR Art. 285)." sqref="G13">
+      <formula1>1</formula1>
+      <formula2>250</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid price" error="Enter a number; P plus lambda (Input 7) must be above 0." promptTitle="Price P" prompt="Price of the underlying (forward rate for IR options). P plus lambda (Input 7) must be above 0 (CRE52.40)." sqref="E14:E16">
+      <formula1>AND(ISNUMBER(E14),E14+$K14&gt;0)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid strike" error="Enter a number; K plus lambda (Input 7) must be above 0." promptTitle="Strike K" prompt="Strike of the option. K plus lambda (Input 7) must be above 0 (CRE52.40)." sqref="F14:F16">
+      <formula1>AND(ISNUMBER(F14),F14+$K14&gt;0)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid expiry" error="Enter a number of years above 0, at most 100." promptTitle="Expiry T (years)" prompt="Latest contractual exercise date, in years from today, above 0 (CRE52.40; CRR Art. 279a(1)(a))." sqref="G14:G16">
+      <formula1>AND(ISNUMBER(G14),G14&gt;0,G14&lt;=100)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid volatility" error="Enter a decimal above 0, at most 5." promptTitle="Supervisory volatility" prompt="Supervisory option volatility as a decimal (0.5 = 50%), above 0 and at most 5 (CRE52.72; CRR Art. 279a)." sqref="H14:H16">
+      <formula1>AND(ISNUMBER(H14),H14&gt;0,H14&lt;=5)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Call" prompt="TRUE = call option; FALSE = put option (CRE52.40)." sqref="I14:I16">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Bought" prompt="TRUE = bought option (long); FALSE = sold option (short) (CRE52.40)." sqref="J14:J16">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Lambda shift" prompt="Shift added to P and K so that both are above 0 (CRE52.40 FAQ; CRR-RTS Art. 5). 0 or more." sqref="K16">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid attachment" error="Enter a decimal from 0 to below 1, e.g. 0.03 for 3%." promptTitle="Attachment A" prompt="Attachment point of the tranche, from 0 to below 1 (CRE52.41)." sqref="E17">
+      <formula1>0</formula1>
+      <formula2>0.9999</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid detachment" error="Enter a decimal above the attachment point and at most 1." promptTitle="Detachment D" prompt="Detachment point, above the attachment and at most 1 (CRE52.41)." sqref="F17">
+      <formula1>AND(ISNUMBER(F17),F17&gt;E17,F17&lt;=1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Long" prompt="TRUE = long in the tranche (positive delta); FALSE = short (CRE52.41)." sqref="G17">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Bucket effective notional" prompt="Signed effective notional D of maturity bucket 1, 2 or 3 (under 1 year, 1 to 5 years, over 5 years) (CRE52.57)." sqref="E18:G18">
+      <formula1>ISNUMBER(E18)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Entity add-on" prompt="Add-on of entity or commodity type k, signed by direction (CRE52.61; CRR Art. 280c)." sqref="E19:G19">
+      <formula1>ISNUMBER(E19)</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid correlation" error="Enter a decimal from 0 to 1." promptTitle="Correlation" prompt="Correlation of entity k, as a decimal from 0 to 1: credit 0.5 single name, 0.8 index (CRE52.61)." sqref="H19:J19">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="V - C" prompt="Net market value of the netting set less collateral, signed (CRE52.23; CRR Art. 278(3))." sqref="E20:E21">
+      <formula1>ISNUMBER(E20)</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Aggregate add-on" prompt="Aggregate add-on of the netting set, 0 or more; 0 gives a multiplier of 1 (CRE52.23)." sqref="F20:F21">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="V" prompt="Net market value of the trades in the netting set, signed (CRE52.10; CRR Art. 275)." sqref="E22">
+      <formula1>ISNUMBER(E22)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="C" prompt="Net collateral held after haircuts; negative if posted (CRE52.10; CRR Art. 275)." sqref="F22">
+      <formula1>ISNUMBER(F22)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Margined" prompt="TRUE = margined RC max(V - C, TH + MTA - NICA, 0) (CRE52.18); FALSE = max(V - C, 0) (CRE52.10)." sqref="G22">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Threshold TH" prompt="Threshold of the margin agreement, 0 or more (CRE52.18; CRR Art. 275(2))." sqref="H22">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Minimum transfer amount" prompt="Minimum transfer amount MTA, 0 or more (CRE52.18; CRR Art. 275(2))." sqref="I22">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="NICA" prompt="Net independent collateral amount, signed; negative if posted (CRE52.13; CRR Art. 275(2))." sqref="J22">
+      <formula1>ISNUMBER(J22)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="x" prompt="Point at which the standard normal distribution function is evaluated." sqref="E23:E24">
+      <formula1>ISNUMBER(E23)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Price or strike" prompt="Price P (Input 1) or strike K (Input 2) of the option; negative values allowed (CRR-RTS Art. 5(2))." sqref="E25:F29">
+      <formula1>ISNUMBER(E25)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Interest rate" prompt="TRUE = interest-rate option (threshold 0.10%); FALSE = commodity option (threshold 0.1) (CRR-RTS Art. 5(2))." sqref="G25:G29">
+      <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -7895,9 +7895,8 @@
     </row>
   </sheetData>
   <dataValidations count="31">
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%." sqref="D5">
-      <formula1>0.0000000000000001</formula1>
-      <formula2>0.01</formula2>
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%. Below about 0.00000000000001% (1e-16, double precision) only an exact match passes." sqref="D5">
+      <formula1>AND(ISNUMBER(D5),D5&gt;0,D5&lt;=0.01)</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid start date" error="Enter a number of years from -50 to 50." promptTitle="Start date S (years)" prompt="Years from today to the start of the period referenced. Zero or negative means already started and is floored at 0 (CRE52.34; CRR Art. 279b(1)(a))." sqref="E8:E10">
       <formula1>-50</formula1>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -17,7 +17,7 @@
     <sheet name="TradeCalc" sheetId="8" r:id="rId8"/>
     <sheet name="Checks" sheetId="9" r:id="rId9"/>
     <sheet name="TestCatalogue" sheetId="10" r:id="rId10"/>
-    <sheet name="Tests" sheetId="11" r:id="rId11"/>
+    <sheet name="FormulaTest" sheetId="11" r:id="rId11"/>
     <sheet name="Basel_vs_CRR" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
@@ -28,6 +28,7 @@
     <definedName name="BasisFactor">Params!$E$17</definedName>
     <definedName name="BusinessDaysPerYear">Params!$E$11</definedName>
     <definedName name="DaysPerYear">Params!$E$10</definedName>
+    <definedName name="FormulaTest_Tolerance">FormulaTest!$D$5</definedName>
     <definedName name="FX_Table">Params!$C$57:$E$62</definedName>
     <definedName name="IRBucketOffset">Params!$E$22</definedName>
     <definedName name="IRCorrBucket12">Params!$E$19</definedName>
@@ -48,7 +49,6 @@
     <definedName name="SACCR_RunInputs" hidden="1">""</definedName>
     <definedName name="SDFloorBD">Params!$E$13</definedName>
     <definedName name="SF_Table">Params!$C$28:$K$54</definedName>
-    <definedName name="Tests_Tolerance">Tests!$D$5</definedName>
     <definedName name="Trades_Header">Trades!$C$4</definedName>
     <definedName name="VolatilityFactor">Params!$E$18</definedName>
   </definedNames>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="898">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -136,7 +136,7 @@
     <t>6. Review</t>
   </si>
   <si>
-    <t>Checks lists every excluded trade and warning. TestCatalogue compares the engine with published / hand-calculated reference values per regime; Tests unit-tests the formula functions.</t>
+    <t>Checks lists every excluded trade and warning. TestCatalogue compares the engine with published / hand-calculated reference values per regime; FormulaTest unit-tests the formula functions.</t>
   </si>
   <si>
     <t>7. Regime</t>
@@ -2338,7 +2338,7 @@
     <t>Common table on Params.</t>
   </si>
   <si>
-    <t>Tests sheet</t>
+    <t>FormulaTest sheet</t>
   </si>
   <si>
     <t>Credit supervisory factors</t>
@@ -2792,6 +2792,12 @@
   </si>
   <si>
     <t>Tolerance: a test passes when |Function - Expected| &lt;= tolerance x max(1, |Expected|)</t>
+  </si>
+  <si>
+    <t>FormulaTest</t>
+  </si>
+  <si>
+    <t>Formula tests</t>
   </si>
 </sst>
 </file>
@@ -5000,7 +5006,7 @@
     </row>
     <row r="46" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="25" t="s">
-        <v>70</v>
+        <v>896</v>
       </c>
       <c r="D46" s="34" t="s">
         <v>71</v>
@@ -6987,7 +6993,7 @@
     </row>
     <row r="2" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
-        <v>70</v>
+        <v>897</v>
       </c>
       <c r="C2" s="31"/>
       <c r="D2" s="32"/>
@@ -7107,7 +7113,7 @@
         <v>0.0</v>
       </c>
       <c r="O8" s="127" t="str">
-        <f>IF(ISNUMBER(N8),IF(N8&lt;=Tests_Tolerance*MAX(1,ABS(L8)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N8),IF(N8&lt;=FormulaTest_Tolerance*MAX(1,ABS(L8)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P8" s="130" t="s">
@@ -7140,7 +7146,7 @@
         <v>0.0</v>
       </c>
       <c r="O9" s="127" t="str">
-        <f>IF(ISNUMBER(N9),IF(N9&lt;=Tests_Tolerance*MAX(1,ABS(L9)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N9),IF(N9&lt;=FormulaTest_Tolerance*MAX(1,ABS(L9)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P9" s="130" t="s">
@@ -7177,7 +7183,7 @@
         <v>0.0</v>
       </c>
       <c r="O10" s="127" t="str">
-        <f>IF(ISNUMBER(N10),IF(N10&lt;=Tests_Tolerance*MAX(1,ABS(L10)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N10),IF(N10&lt;=FormulaTest_Tolerance*MAX(1,ABS(L10)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P10" s="130" t="s">
@@ -7207,7 +7213,7 @@
         <v>0.0</v>
       </c>
       <c r="O11" s="127" t="str">
-        <f>IF(ISNUMBER(N11),IF(N11&lt;=Tests_Tolerance*MAX(1,ABS(L11)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N11),IF(N11&lt;=FormulaTest_Tolerance*MAX(1,ABS(L11)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P11" s="130" t="s">
@@ -7238,7 +7244,7 @@
         <v>0.0</v>
       </c>
       <c r="O12" s="127" t="str">
-        <f>IF(ISNUMBER(N12),IF(N12&lt;=Tests_Tolerance*MAX(1,ABS(L12)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N12),IF(N12&lt;=FormulaTest_Tolerance*MAX(1,ABS(L12)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P12" s="130" t="s">
@@ -7274,7 +7280,7 @@
         <v>0.0</v>
       </c>
       <c r="O13" s="127" t="str">
-        <f>IF(ISNUMBER(N13),IF(N13&lt;=Tests_Tolerance*MAX(1,ABS(L13)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N13),IF(N13&lt;=FormulaTest_Tolerance*MAX(1,ABS(L13)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P13" s="130" t="s">
@@ -7319,7 +7325,7 @@
         <v>0.0</v>
       </c>
       <c r="O14" s="127" t="str">
-        <f>IF(ISNUMBER(N14),IF(N14&lt;=Tests_Tolerance*MAX(1,ABS(L14)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N14),IF(N14&lt;=FormulaTest_Tolerance*MAX(1,ABS(L14)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P14" s="130" t="s">
@@ -7364,7 +7370,7 @@
         <v>0.0</v>
       </c>
       <c r="O15" s="127" t="str">
-        <f>IF(ISNUMBER(N15),IF(N15&lt;=Tests_Tolerance*MAX(1,ABS(L15)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N15),IF(N15&lt;=FormulaTest_Tolerance*MAX(1,ABS(L15)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P15" s="130" t="s">
@@ -7412,7 +7418,7 @@
         <v>0.0</v>
       </c>
       <c r="O16" s="127" t="str">
-        <f>IF(ISNUMBER(N16),IF(N16&lt;=Tests_Tolerance*MAX(1,ABS(L16)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N16),IF(N16&lt;=FormulaTest_Tolerance*MAX(1,ABS(L16)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P16" s="130" t="s">
@@ -7448,7 +7454,7 @@
         <v>8.881784197001252e-16</v>
       </c>
       <c r="O17" s="127" t="str">
-        <f>IF(ISNUMBER(N17),IF(N17&lt;=Tests_Tolerance*MAX(1,ABS(L17)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N17),IF(N17&lt;=FormulaTest_Tolerance*MAX(1,ABS(L17)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P17" s="130" t="s">
@@ -7484,7 +7490,7 @@
         <v>0.0</v>
       </c>
       <c r="O18" s="127" t="str">
-        <f>IF(ISNUMBER(N18),IF(N18&lt;=Tests_Tolerance*MAX(1,ABS(L18)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N18),IF(N18&lt;=FormulaTest_Tolerance*MAX(1,ABS(L18)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P18" s="130" t="s">
@@ -7529,7 +7535,7 @@
         <v>0.0</v>
       </c>
       <c r="O19" s="127" t="str">
-        <f>IF(ISNUMBER(N19),IF(N19&lt;=Tests_Tolerance*MAX(1,ABS(L19)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N19),IF(N19&lt;=FormulaTest_Tolerance*MAX(1,ABS(L19)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P19" s="130" t="s">
@@ -7562,7 +7568,7 @@
         <v>0.0</v>
       </c>
       <c r="O20" s="127" t="str">
-        <f>IF(ISNUMBER(N20),IF(N20&lt;=Tests_Tolerance*MAX(1,ABS(L20)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N20),IF(N20&lt;=FormulaTest_Tolerance*MAX(1,ABS(L20)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P20" s="130" t="s">
@@ -7595,7 +7601,7 @@
         <v>0.0</v>
       </c>
       <c r="O21" s="127" t="str">
-        <f>IF(ISNUMBER(N21),IF(N21&lt;=Tests_Tolerance*MAX(1,ABS(L21)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N21),IF(N21&lt;=FormulaTest_Tolerance*MAX(1,ABS(L21)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P21" s="130" t="s">
@@ -7640,7 +7646,7 @@
         <v>0.0</v>
       </c>
       <c r="O22" s="127" t="str">
-        <f>IF(ISNUMBER(N22),IF(N22&lt;=Tests_Tolerance*MAX(1,ABS(L22)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N22),IF(N22&lt;=FormulaTest_Tolerance*MAX(1,ABS(L22)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P22" s="130" t="s">
@@ -7670,7 +7676,7 @@
         <v>0.0</v>
       </c>
       <c r="O23" s="127" t="str">
-        <f>IF(ISNUMBER(N23),IF(N23&lt;=Tests_Tolerance*MAX(1,ABS(L23)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N23),IF(N23&lt;=FormulaTest_Tolerance*MAX(1,ABS(L23)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P23" s="130" t="s">
@@ -7700,7 +7706,7 @@
         <v>5.4129035033506995e-24</v>
       </c>
       <c r="O24" s="127" t="str">
-        <f>IF(ISNUMBER(N24),IF(N24&lt;=Tests_Tolerance*MAX(1,ABS(L24)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N24),IF(N24&lt;=FormulaTest_Tolerance*MAX(1,ABS(L24)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P24" s="130" t="s">
@@ -7736,7 +7742,7 @@
         <v>0.0</v>
       </c>
       <c r="O25" s="127" t="str">
-        <f>IF(ISNUMBER(N25),IF(N25&lt;=Tests_Tolerance*MAX(1,ABS(L25)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N25),IF(N25&lt;=FormulaTest_Tolerance*MAX(1,ABS(L25)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P25" s="130" t="s">
@@ -7772,7 +7778,7 @@
         <v>0.0</v>
       </c>
       <c r="O26" s="127" t="str">
-        <f>IF(ISNUMBER(N26),IF(N26&lt;=Tests_Tolerance*MAX(1,ABS(L26)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N26),IF(N26&lt;=FormulaTest_Tolerance*MAX(1,ABS(L26)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P26" s="130" t="s">
@@ -7808,7 +7814,7 @@
         <v>0.0</v>
       </c>
       <c r="O27" s="127" t="str">
-        <f>IF(ISNUMBER(N27),IF(N27&lt;=Tests_Tolerance*MAX(1,ABS(L27)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N27),IF(N27&lt;=FormulaTest_Tolerance*MAX(1,ABS(L27)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P27" s="130" t="s">
@@ -7844,7 +7850,7 @@
         <v>0.0</v>
       </c>
       <c r="O28" s="127" t="str">
-        <f>IF(ISNUMBER(N28),IF(N28&lt;=Tests_Tolerance*MAX(1,ABS(L28)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N28),IF(N28&lt;=FormulaTest_Tolerance*MAX(1,ABS(L28)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P28" s="130" t="s">
@@ -7880,7 +7886,7 @@
         <v>0.0</v>
       </c>
       <c r="O29" s="127" t="str">
-        <f>IF(ISNUMBER(N29),IF(N29&lt;=Tests_Tolerance*MAX(1,ABS(L29)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N29),IF(N29&lt;=FormulaTest_Tolerance*MAX(1,ABS(L29)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P29" s="130" t="s">
@@ -7888,10 +7894,105 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%." sqref="D5">
-      <formula1>0.0000000000000001</formula1>
-      <formula2>0.01</formula2>
+  <dataValidations count="31">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%. Below about 0.00000000000001% (1e-16, double precision) only an exact match passes." sqref="D5">
+      <formula1>AND(ISNUMBER(D5),D5&gt;0,D5&lt;=0.01)</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid start date" error="Enter a number of years from -50 to 50." promptTitle="Start date S (years)" prompt="Years from today to the start of the period referenced. Zero or negative means already started and is floored at 0 (CRE52.34; CRR Art. 279b(1)(a))." sqref="E8:E10">
+      <formula1>-50</formula1>
+      <formula2>50</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid end date" error="Enter a number of years after the start date and after 0, at most 50." promptTitle="End date E (years)" prompt="Years from today to the end of the period referenced: after the start date and after today, at most 50 (CRE52.34)." sqref="F8:F10">
+      <formula1>AND(ISNUMBER(F8),F8&gt;MAX(E8,0),F8&lt;=50)</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid floor" error="Enter a number of years from 0 to 1." promptTitle="SD floor (years)" prompt="Floor on the supervisory duration, in years: 10 business days = 10/250 (CRE52.34)." sqref="G10">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid maturity" error="Enter a number of years from 0 to 50." promptTitle="Maturity M (years)" prompt="Remaining maturity in years. The unmargined factor floors it at 10 business days and caps it at 1 year (CRE52.48; CRR Art. 279c(1)(a))." sqref="E11:E13">
+      <formula1>0</formula1>
+      <formula2>50</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Margined" prompt="TRUE = margined factor 1.5 x sqrt(MPOR / 250) (CRE52.52; CRR Art. 279c(1)(b)). FALSE = unmargined factor from M." sqref="F13">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid MPOR" error="Enter a whole number of business days from 1 to 250." promptTitle="MPOR (business days)" prompt="Margin period of risk in business days, used when margined (CRE52.50-52; CRR Art. 285)." sqref="G13">
+      <formula1>1</formula1>
+      <formula2>250</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid price" error="Enter a number; P plus lambda (Input 7) must be above 0." promptTitle="Price P" prompt="Price of the underlying (forward rate for IR options). P plus lambda (Input 7) must be above 0 (CRE52.40)." sqref="E14:E16">
+      <formula1>AND(ISNUMBER(E14),E14+$K14&gt;0)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid strike" error="Enter a number; K plus lambda (Input 7) must be above 0." promptTitle="Strike K" prompt="Strike of the option. K plus lambda (Input 7) must be above 0 (CRE52.40)." sqref="F14:F16">
+      <formula1>AND(ISNUMBER(F14),F14+$K14&gt;0)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid expiry" error="Enter a number of years above 0, at most 100." promptTitle="Expiry T (years)" prompt="Latest contractual exercise date, in years from today, above 0 (CRE52.40; CRR Art. 279a(1)(a))." sqref="G14:G16">
+      <formula1>AND(ISNUMBER(G14),G14&gt;0,G14&lt;=100)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid volatility" error="Enter a decimal above 0, at most 5." promptTitle="Supervisory volatility" prompt="Supervisory option volatility as a decimal (0.5 = 50%), above 0 and at most 5 (CRE52.72; CRR Art. 279a)." sqref="H14:H16">
+      <formula1>AND(ISNUMBER(H14),H14&gt;0,H14&lt;=5)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Call" prompt="TRUE = call option; FALSE = put option (CRE52.40)." sqref="I14:I16">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Bought" prompt="TRUE = bought option (long); FALSE = sold option (short) (CRE52.40)." sqref="J14:J16">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Lambda shift" prompt="Shift added to P and K so that both are above 0 (CRE52.40 FAQ; CRR-RTS Art. 5). 0 or more." sqref="K16">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid attachment" error="Enter a decimal from 0 to below 1, e.g. 0.03 for 3%." promptTitle="Attachment A" prompt="Attachment point of the tranche, from 0 to below 1 (CRE52.41)." sqref="E17">
+      <formula1>0</formula1>
+      <formula2>0.9999</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid detachment" error="Enter a decimal above the attachment point and at most 1." promptTitle="Detachment D" prompt="Detachment point, above the attachment and at most 1 (CRE52.41)." sqref="F17">
+      <formula1>AND(ISNUMBER(F17),F17&gt;E17,F17&lt;=1)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Long" prompt="TRUE = long in the tranche (positive delta); FALSE = short (CRE52.41)." sqref="G17">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Bucket effective notional" prompt="Signed effective notional D of maturity bucket 1, 2 or 3 (under 1 year, 1 to 5 years, over 5 years) (CRE52.57)." sqref="E18:G18">
+      <formula1>ISNUMBER(E18)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Entity add-on" prompt="Add-on of entity or commodity type k, signed by direction (CRE52.61; CRR Art. 280c)." sqref="E19:G19">
+      <formula1>ISNUMBER(E19)</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid correlation" error="Enter a decimal from 0 to 1." promptTitle="Correlation" prompt="Correlation of entity k, as a decimal from 0 to 1: credit 0.5 single name, 0.8 index (CRE52.61)." sqref="H19:J19">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="V - C" prompt="Net market value of the netting set less collateral, signed (CRE52.23; CRR Art. 278(3))." sqref="E20:E21">
+      <formula1>ISNUMBER(E20)</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Aggregate add-on" prompt="Aggregate add-on of the netting set, 0 or more; 0 gives a multiplier of 1 (CRE52.23)." sqref="F20:F21">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="V" prompt="Net market value of the trades in the netting set, signed (CRE52.10; CRR Art. 275)." sqref="E22">
+      <formula1>ISNUMBER(E22)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="C" prompt="Net collateral held after haircuts; negative if posted (CRE52.10; CRR Art. 275)." sqref="F22">
+      <formula1>ISNUMBER(F22)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Margined" prompt="TRUE = margined RC max(V - C, TH + MTA - NICA, 0) (CRE52.18); FALSE = max(V - C, 0) (CRE52.10)." sqref="G22">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Threshold TH" prompt="Threshold of the margin agreement, 0 or more (CRE52.18; CRR Art. 275(2))." sqref="H22">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Minimum transfer amount" prompt="Minimum transfer amount MTA, 0 or more (CRE52.18; CRR Art. 275(2))." sqref="I22">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="NICA" prompt="Net independent collateral amount, signed; negative if posted (CRE52.13; CRR Art. 275(2))." sqref="J22">
+      <formula1>ISNUMBER(J22)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="x" prompt="Point at which the standard normal distribution function is evaluated." sqref="E23:E24">
+      <formula1>ISNUMBER(E23)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Price or strike" prompt="Price P (Input 1) or strike K (Input 2) of the option; negative values allowed (CRR-RTS Art. 5(2))." sqref="E25:F29">
+      <formula1>ISNUMBER(E25)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Interest rate" prompt="TRUE = interest-rate option (threshold 0.10%); FALSE = commodity option (threshold 0.1) (CRR-RTS Art. 5(2))." sqref="G25:G29">
+      <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -28,7 +28,7 @@
     <definedName name="BasisFactor">Params!$E$17</definedName>
     <definedName name="BusinessDaysPerYear">Params!$E$11</definedName>
     <definedName name="DaysPerYear">Params!$E$10</definedName>
-    <definedName name="FormulaTest_Tolerance">FormulaTest!$D$5</definedName>
+    <definedName name="FormulaTest_Tolerance">FormulaTest!$E$5</definedName>
     <definedName name="FX_Table">Params!$C$57:$E$62</definedName>
     <definedName name="IRBucketOffset">Params!$E$22</definedName>
     <definedName name="IRCorrBucket12">Params!$E$19</definedName>
@@ -7034,7 +7034,7 @@
       <c r="C5" s="128" t="s">
         <v>895</v>
       </c>
-      <c r="D5" s="131">
+      <c r="E5" s="131">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
@@ -7895,8 +7895,8 @@
     </row>
   </sheetData>
   <dataValidations count="31">
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%. Below about 0.00000000000001% (1e-16, double precision) only an exact match passes." sqref="D5">
-      <formula1>AND(ISNUMBER(D5),D5&gt;0,D5&lt;=0.01)</formula1>
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%. Below about 0.00000000000001% (1e-16, double precision) only an exact match passes." sqref="E5">
+      <formula1>AND(ISNUMBER(E5),E5&gt;0,E5&lt;=0.01)</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid start date" error="Enter a number of years from -50 to 50." promptTitle="Start date S (years)" prompt="Years from today to the start of the period referenced. Zero or negative means already started and is floored at 0 (CRE52.34; CRR Art. 279b(1)(a))." sqref="E8:E10">
       <formula1>-50</formula1>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -28,7 +28,7 @@
     <definedName name="BasisFactor">Params!$E$17</definedName>
     <definedName name="BusinessDaysPerYear">Params!$E$11</definedName>
     <definedName name="DaysPerYear">Params!$E$10</definedName>
-    <definedName name="FormulaTest_Tolerance">FormulaTest!$E$5</definedName>
+    <definedName name="FormulaTest_Tolerance">FormulaTest!$E$4</definedName>
     <definedName name="FX_Table">Params!$C$57:$E$62</definedName>
     <definedName name="IRBucketOffset">Params!$E$22</definedName>
     <definedName name="IRCorrBucket12">Params!$E$19</definedName>
@@ -6948,7 +6948,7 @@
     <tabColor rgb="FF548235"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AB29"/>
+  <dimension ref="B1:AB28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
@@ -7022,91 +7022,121 @@
       <c r="AA2" s="68"/>
       <c r="AB2" s="68"/>
     </row>
-    <row r="3" ht="21" x14ac:dyDescent="0.25">
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="2" t="s">
+    <row r="3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="2" t="s">
         <v>508</v>
       </c>
     </row>
+    <row r="4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="128" t="s">
+        <v>895</v>
+      </c>
+      <c r="E4" s="131">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
     <row r="5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="128" t="s">
-        <v>895</v>
-      </c>
-      <c r="E5" s="131">
-        <v>1.0000000000000001E-5</v>
-      </c>
-    </row>
-    <row r="6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="48" t="s">
+      <c r="C5" s="48" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="54" t="s">
+    <row r="6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="54" t="s">
         <v>510</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D6" s="54" t="s">
         <v>884</v>
       </c>
-      <c r="E7" s="55" t="s">
+      <c r="E6" s="55" t="s">
         <v>885</v>
       </c>
-      <c r="F7" s="55" t="s">
+      <c r="F6" s="55" t="s">
         <v>886</v>
       </c>
-      <c r="G7" s="55" t="s">
+      <c r="G6" s="55" t="s">
         <v>887</v>
       </c>
-      <c r="H7" s="55" t="s">
+      <c r="H6" s="55" t="s">
         <v>888</v>
       </c>
-      <c r="I7" s="55" t="s">
+      <c r="I6" s="55" t="s">
         <v>889</v>
       </c>
-      <c r="J7" s="55" t="s">
+      <c r="J6" s="55" t="s">
         <v>890</v>
       </c>
-      <c r="K7" s="55" t="s">
+      <c r="K6" s="55" t="s">
         <v>891</v>
       </c>
-      <c r="L7" s="55" t="s">
+      <c r="L6" s="55" t="s">
         <v>892</v>
       </c>
-      <c r="M7" s="55" t="s">
+      <c r="M6" s="55" t="s">
         <v>893</v>
       </c>
-      <c r="N7" s="55" t="s">
+      <c r="N6" s="55" t="s">
         <v>514</v>
       </c>
-      <c r="O7" s="55" t="s">
+      <c r="O6" s="55" t="s">
         <v>515</v>
       </c>
-      <c r="P7" s="54" t="s">
+      <c r="P6" s="54" t="s">
         <v>894</v>
+      </c>
+    </row>
+    <row r="7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="128" t="s">
+        <v>516</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>859</v>
+      </c>
+      <c r="E7" s="129">
+        <v>0</v>
+      </c>
+      <c r="F7" s="129">
+        <v>10</v>
+      </c>
+      <c r="L7" s="125">
+        <f>(EXP(-0.05*MAX($E7,0))-EXP(-0.05*$F7))/0.05</f>
+        <v>7.8693868057473315</v>
+      </c>
+      <c r="M7" s="125" cm="1">
+        <f t="array" ref="M7">SACCR_SupervisoryDuration($E7,$F7)</f>
+        <v>7.8693868057473315</v>
+      </c>
+      <c r="N7" s="126">
+        <f>IFERROR(ABS(M7-L7),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="127" t="str">
+        <f>IF(ISNUMBER(N7),IF(N7&lt;=FormulaTest_Tolerance*MAX(1,ABS(L7)),"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="P7" s="130" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="128" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>859</v>
       </c>
       <c r="E8" s="129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="129">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L8" s="125">
         <f>(EXP(-0.05*MAX($E8,0))-EXP(-0.05*$F8))/0.05</f>
-        <v>7.8693868057473315</v>
+        <v>7.485592282404547</v>
       </c>
       <c r="M8" s="125" cm="1">
         <f t="array" ref="M8">SACCR_SupervisoryDuration($E8,$F8)</f>
-        <v>7.8693868057473315</v>
+        <v>7.485592282404547</v>
       </c>
       <c r="N8" s="126">
         <f>IFERROR(ABS(M8-L8),"")</f>
@@ -7122,24 +7152,28 @@
     </row>
     <row r="9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="128" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="E9" s="129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="129">
-        <v>11</v>
+        <v>0.01</v>
+      </c>
+      <c r="G9" s="129">
+        <f>10/250</f>
+        <v>0.04</v>
       </c>
       <c r="L9" s="125">
-        <f>(EXP(-0.05*MAX($E9,0))-EXP(-0.05*$F9))/0.05</f>
-        <v>7.485592282404547</v>
+        <f>MAX((EXP(-0.05*MAX($E9,0))-EXP(-0.05*$F9))/0.05,$G9)</f>
+        <v>0.04</v>
       </c>
       <c r="M9" s="125" cm="1">
-        <f t="array" ref="M9">SACCR_SupervisoryDuration($E9,$F9)</f>
-        <v>7.485592282404547</v>
+        <f t="array" ref="M9">SACCR_SupervisoryDuration($E9,$F9,$G9)</f>
+        <v>0.04</v>
       </c>
       <c r="N9" s="126">
         <f>IFERROR(ABS(M9-L9),"")</f>
@@ -7155,28 +7189,21 @@
     </row>
     <row r="10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="128" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E10" s="129">
-        <v>0</v>
-      </c>
-      <c r="F10" s="129">
-        <v>0.01</v>
-      </c>
-      <c r="G10" s="129">
-        <f>10/250</f>
-        <v>0.04</v>
+        <v>0.75</v>
       </c>
       <c r="L10" s="125">
-        <f>MAX((EXP(-0.05*MAX($E10,0))-EXP(-0.05*$F10))/0.05,$G10)</f>
-        <v>0.04</v>
+        <f>SQRT(MIN(MAX($E10,10/250),1))</f>
+        <v>0.8660254037844386</v>
       </c>
       <c r="M10" s="125" cm="1">
-        <f t="array" ref="M10">SACCR_SupervisoryDuration($E10,$F10,$G10)</f>
-        <v>0.04</v>
+        <f t="array" ref="M10">SACCR_MaturityFactor($E10)</f>
+        <v>0.8660254037844386</v>
       </c>
       <c r="N10" s="126">
         <f>IFERROR(ABS(M10-L10),"")</f>
@@ -7187,26 +7214,27 @@
         <v>PASS</v>
       </c>
       <c r="P10" s="130" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="128" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D11" s="24" t="s">
         <v>862</v>
       </c>
       <c r="E11" s="129">
-        <v>0.75</v>
+        <f>3/365</f>
+        <v>0.00821917808219178</v>
       </c>
       <c r="L11" s="125">
         <f>SQRT(MIN(MAX($E11,10/250),1))</f>
-        <v>0.8660254037844386</v>
+        <v>0.2</v>
       </c>
       <c r="M11" s="125" cm="1">
         <f t="array" ref="M11">SACCR_MaturityFactor($E11)</f>
-        <v>0.8660254037844386</v>
+        <v>0.2</v>
       </c>
       <c r="N11" s="126">
         <f>IFERROR(ABS(M11-L11),"")</f>
@@ -7222,22 +7250,27 @@
     </row>
     <row r="12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="128" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="E12" s="129">
-        <f>3/365</f>
-        <v>0.00821917808219178</v>
+        <v>0</v>
+      </c>
+      <c r="F12" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="129">
+        <v>10</v>
       </c>
       <c r="L12" s="125">
-        <f>SQRT(MIN(MAX($E12,10/250),1))</f>
-        <v>0.2</v>
+        <f>IF($F12,1.5*SQRT($G12/250),SQRT(MIN(MAX($E12,10/250),1)))</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="M12" s="125" cm="1">
-        <f t="array" ref="M12">SACCR_MaturityFactor($E12)</f>
-        <v>0.2</v>
+        <f t="array" ref="M12">SACCR_MaturityFactor($E12,$F12,$G12)</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="N12" s="126">
         <f>IFERROR(ABS(M12-L12),"")</f>
@@ -7248,32 +7281,41 @@
         <v>PASS</v>
       </c>
       <c r="P12" s="130" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="128" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="E13" s="129">
+        <v>0.06</v>
+      </c>
+      <c r="F13" s="129">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="129">
+        <v>1</v>
+      </c>
+      <c r="H13" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="129" t="b">
         <v>0</v>
       </c>
-      <c r="F13" s="129" t="b">
+      <c r="J13" s="129" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="129">
-        <v>10</v>
-      </c>
       <c r="L13" s="125">
-        <f>IF($F13,1.5*SQRT($G13/250),SQRT(MIN(MAX($E13,10/250),1)))</f>
-        <v>0.30000000000000004</v>
+        <f>IF($I13,_xlfn.NORM.S.DIST((LN(($E13+$K13)/($F13+$K13))+$H13^2*$G13/2)/($H13*SQRT($G13)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E13+$K13)/($F13+$K13))+$H13^2*$G13/2)/($H13*SQRT($G13)),TRUE))*IF($J13,1,-1)</f>
+        <v>-0.2693952177105327</v>
       </c>
       <c r="M13" s="125" cm="1">
-        <f t="array" ref="M13">SACCR_MaturityFactor($E13,$F13,$G13)</f>
-        <v>0.30000000000000004</v>
+        <f t="array" ref="M13">SACCR_OptionDelta($E13,$F13,$G13,$H13,$I13,$J13)</f>
+        <v>-0.2693952177105327</v>
       </c>
       <c r="N13" s="126">
         <f>IFERROR(ABS(M13-L13),"")</f>
@@ -7284,41 +7326,41 @@
         <v>PASS</v>
       </c>
       <c r="P13" s="130" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="128" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>866</v>
       </c>
       <c r="E14" s="129">
-        <v>0.06</v>
+        <v>100</v>
       </c>
       <c r="F14" s="129">
-        <v>0.05</v>
+        <v>110</v>
       </c>
       <c r="G14" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="129">
+        <v>0.32</v>
+      </c>
+      <c r="I14" s="129" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="129">
-        <v>0.5</v>
-      </c>
-      <c r="I14" s="129" t="b">
+      <c r="J14" s="129" t="b">
         <v>0</v>
-      </c>
-      <c r="J14" s="129" t="b">
-        <v>1</v>
       </c>
       <c r="L14" s="125">
         <f>IF($I14,_xlfn.NORM.S.DIST((LN(($E14+$K14)/($F14+$K14))+$H14^2*$G14/2)/($H14*SQRT($G14)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E14+$K14)/($F14+$K14))+$H14^2*$G14/2)/($H14*SQRT($G14)),TRUE))*IF($J14,1,-1)</f>
-        <v>-0.2693952177105327</v>
+        <v>-0.37901134582780294</v>
       </c>
       <c r="M14" s="125" cm="1">
         <f t="array" ref="M14">SACCR_OptionDelta($E14,$F14,$G14,$H14,$I14,$J14)</f>
-        <v>-0.2693952177105327</v>
+        <v>-0.37901134582780294</v>
       </c>
       <c r="N14" s="126">
         <f>IFERROR(ABS(M14-L14),"")</f>
@@ -7334,36 +7376,39 @@
     </row>
     <row r="15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="128" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="E15" s="129">
-        <v>100</v>
+        <v>-0.002</v>
       </c>
       <c r="F15" s="129">
-        <v>110</v>
+        <v>0.001</v>
       </c>
       <c r="G15" s="129">
+        <v>2</v>
+      </c>
+      <c r="H15" s="129">
         <v>0.5</v>
-      </c>
-      <c r="H15" s="129">
-        <v>0.32</v>
       </c>
       <c r="I15" s="129" t="b">
         <v>1</v>
       </c>
       <c r="J15" s="129" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K15" s="129">
+        <v>0.01</v>
       </c>
       <c r="L15" s="125">
         <f>IF($I15,_xlfn.NORM.S.DIST((LN(($E15+$K15)/($F15+$K15))+$H15^2*$G15/2)/($H15*SQRT($G15)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E15+$K15)/($F15+$K15))+$H15^2*$G15/2)/($H15*SQRT($G15)),TRUE))*IF($J15,1,-1)</f>
-        <v>-0.37901134582780294</v>
+        <v>0.46143935794124913</v>
       </c>
       <c r="M15" s="125" cm="1">
-        <f t="array" ref="M15">SACCR_OptionDelta($E15,$F15,$G15,$H15,$I15,$J15)</f>
-        <v>-0.37901134582780294</v>
+        <f t="array" ref="M15">SACCR_OptionDelta($E15,$F15,$G15,$H15,$I15,$J15,$K15)</f>
+        <v>0.46143935794124913</v>
       </c>
       <c r="N15" s="126">
         <f>IFERROR(ABS(M15-L15),"")</f>
@@ -7374,116 +7419,113 @@
         <v>PASS</v>
       </c>
       <c r="P15" s="130" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="128" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="E16" s="129">
-        <v>-0.002</v>
+        <v>0.03</v>
       </c>
       <c r="F16" s="129">
-        <v>0.001</v>
-      </c>
-      <c r="G16" s="129">
-        <v>2</v>
-      </c>
-      <c r="H16" s="129">
-        <v>0.5</v>
-      </c>
-      <c r="I16" s="129" t="b">
+        <v>0.06</v>
+      </c>
+      <c r="G16" s="129" t="b">
         <v>1</v>
       </c>
-      <c r="J16" s="129" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16" s="129">
-        <v>0.01</v>
-      </c>
       <c r="L16" s="125">
-        <f>IF($I16,_xlfn.NORM.S.DIST((LN(($E16+$K16)/($F16+$K16))+$H16^2*$G16/2)/($H16*SQRT($G16)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E16+$K16)/($F16+$K16))+$H16^2*$G16/2)/($H16*SQRT($G16)),TRUE))*IF($J16,1,-1)</f>
-        <v>0.46143935794124913</v>
+        <f>15/((1+14*$E16)*(1+14*$F16))*IF($G16,1,-1)</f>
+        <v>5.740967544396817</v>
       </c>
       <c r="M16" s="125" cm="1">
-        <f t="array" ref="M16">SACCR_OptionDelta($E16,$F16,$G16,$H16,$I16,$J16,$K16)</f>
-        <v>0.46143935794124913</v>
+        <f t="array" ref="M16">SACCR_CDODelta($E16,$F16,$G16)</f>
+        <v>5.740967544396816</v>
       </c>
       <c r="N16" s="126">
         <f>IFERROR(ABS(M16-L16),"")</f>
-        <v>0.0</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O16" s="127" t="str">
         <f>IF(ISNUMBER(N16),IF(N16&lt;=FormulaTest_Tolerance*MAX(1,ABS(L16)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P16" s="130" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="128" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="E17" s="129">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F17" s="129">
-        <v>0.06</v>
-      </c>
-      <c r="G17" s="129" t="b">
-        <v>1</v>
+        <v>-36253.8493844036</v>
+      </c>
+      <c r="G17" s="129">
+        <v>78693.8680574733</v>
       </c>
       <c r="L17" s="125">
-        <f>15/((1+14*$E17)*(1+14*$F17))*IF($G17,1,-1)</f>
-        <v>5.740967544396817</v>
+        <f>SQRT(MAX($E17^2+$F17^2+$G17^2+1.4*$E17*$F17+1.4*$F17*$G17+0.6*$E17*$G17,0))</f>
+        <v>59269.963463710395</v>
       </c>
       <c r="M17" s="125" cm="1">
-        <f t="array" ref="M17">SACCR_CDODelta($E17,$F17,$G17)</f>
-        <v>5.740967544396816</v>
+        <f t="array" ref="M17">SACCR_IREffectiveNotional($E17,$F17,$G17)</f>
+        <v>59269.963463710395</v>
       </c>
       <c r="N17" s="126">
         <f>IFERROR(ABS(M17-L17),"")</f>
-        <v>8.881784197001252e-16</v>
+        <v>0.0</v>
       </c>
       <c r="O17" s="127" t="str">
         <f>IF(ISNUMBER(N17),IF(N17&lt;=FormulaTest_Tolerance*MAX(1,ABS(L17)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P17" s="130" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="128" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="E18" s="129">
-        <v>0</v>
+        <v>105.861937916956</v>
       </c>
       <c r="F18" s="129">
-        <v>-36253.8493844036</v>
+        <v>-279.916321663744</v>
       </c>
       <c r="G18" s="129">
-        <v>78693.8680574733</v>
+        <v>168.111404865732</v>
+      </c>
+      <c r="H18" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="J18" s="129">
+        <v>0.8</v>
       </c>
       <c r="L18" s="125">
-        <f>SQRT(MAX($E18^2+$F18^2+$G18^2+1.4*$E18*$F18+1.4*$F18*$G18+0.6*$E18*$G18,0))</f>
-        <v>59269.963463710395</v>
+        <f>SQRT(SUMPRODUCT($E18:$G18,$H18:$J18)^2+SUMPRODUCT((1-$H18:$J18^2)*$E18:$G18^2))</f>
+        <v>282.12883185966604</v>
       </c>
       <c r="M18" s="125" cm="1">
-        <f t="array" ref="M18">SACCR_IREffectiveNotional($E18,$F18,$G18)</f>
-        <v>59269.963463710395</v>
+        <f t="array" ref="M18">SACCR_FactorAggregation($E18:$G18,$H18:$J18)</f>
+        <v>282.12883185966604</v>
       </c>
       <c r="N18" s="126">
         <f>IFERROR(ABS(M18-L18),"")</f>
@@ -7494,41 +7536,29 @@
         <v>PASS</v>
       </c>
       <c r="P18" s="130" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="128" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E19" s="129">
-        <v>105.861937916956</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="129">
-        <v>-279.916321663744</v>
-      </c>
-      <c r="G19" s="129">
-        <v>168.111404865732</v>
-      </c>
-      <c r="H19" s="129">
-        <v>0.5</v>
-      </c>
-      <c r="I19" s="129">
-        <v>0.5</v>
-      </c>
-      <c r="J19" s="129">
-        <v>0.8</v>
+        <v>282</v>
       </c>
       <c r="L19" s="125">
-        <f>SQRT(SUMPRODUCT($E19:$G19,$H19:$J19)^2+SUMPRODUCT((1-$H19:$J19^2)*$E19:$G19^2))</f>
-        <v>282.12883185966604</v>
+        <f>IF($F19&lt;=0,1,MIN(1,0.05+0.95*EXP($E19/(2*0.95*$F19))))</f>
+        <v>0.9651926811871945</v>
       </c>
       <c r="M19" s="125" cm="1">
-        <f t="array" ref="M19">SACCR_FactorAggregation($E19:$G19,$H19:$J19)</f>
-        <v>282.12883185966604</v>
+        <f t="array" ref="M19">SACCR_Multiplier($E19,$F19)</f>
+        <v>0.9651926811871945</v>
       </c>
       <c r="N19" s="126">
         <f>IFERROR(ABS(M19-L19),"")</f>
@@ -7539,29 +7569,29 @@
         <v>PASS</v>
       </c>
       <c r="P19" s="130" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="128" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D20" s="24" t="s">
         <v>876</v>
       </c>
       <c r="E20" s="129">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="F20" s="129">
         <v>282</v>
       </c>
       <c r="L20" s="125">
         <f>IF($F20&lt;=0,1,MIN(1,0.05+0.95*EXP($E20/(2*0.95*$F20))))</f>
-        <v>0.9651926811871945</v>
+        <v>1</v>
       </c>
       <c r="M20" s="125" cm="1">
         <f t="array" ref="M20">SACCR_Multiplier($E20,$F20)</f>
-        <v>0.9651926811871945</v>
+        <v>1.0</v>
       </c>
       <c r="N20" s="126">
         <f>IFERROR(ABS(M20-L20),"")</f>
@@ -7577,24 +7607,36 @@
     </row>
     <row r="21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="128" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="E21" s="129">
+        <v>5</v>
+      </c>
+      <c r="F21" s="129">
         <v>10</v>
       </c>
-      <c r="F21" s="129">
-        <v>282</v>
+      <c r="G21" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="129">
+        <v>0</v>
+      </c>
+      <c r="I21" s="129">
+        <v>10</v>
+      </c>
+      <c r="J21" s="129">
+        <v>2</v>
       </c>
       <c r="L21" s="125">
-        <f>IF($F21&lt;=0,1,MIN(1,0.05+0.95*EXP($E21/(2*0.95*$F21))))</f>
-        <v>1</v>
+        <f>IF($G21,MAX($E21-$F21,$H21+$I21-$J21,0),MAX($E21-$F21,0))</f>
+        <v>8</v>
       </c>
       <c r="M21" s="125" cm="1">
-        <f t="array" ref="M21">SACCR_Multiplier($E21,$F21)</f>
-        <v>1.0</v>
+        <f t="array" ref="M21">SACCR_ReplacementCost($E21,$F21,$G21,$H21,$I21,$J21)</f>
+        <v>8.0</v>
       </c>
       <c r="N21" s="126">
         <f>IFERROR(ABS(M21-L21),"")</f>
@@ -7605,41 +7647,26 @@
         <v>PASS</v>
       </c>
       <c r="P21" s="130" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="128" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E22" s="129">
-        <v>5</v>
-      </c>
-      <c r="F22" s="129">
-        <v>10</v>
-      </c>
-      <c r="G22" s="129" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" s="129">
-        <v>0</v>
-      </c>
-      <c r="I22" s="129">
-        <v>10</v>
-      </c>
-      <c r="J22" s="129">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="L22" s="125">
-        <f>IF($G22,MAX($E22-$F22,$H22+$I22-$J22,0),MAX($E22-$F22,0))</f>
-        <v>8</v>
+        <f>_xlfn.NORM.S.DIST($E22,TRUE)</f>
+        <v>0.9750021048517795</v>
       </c>
       <c r="M22" s="125" cm="1">
-        <f t="array" ref="M22">SACCR_ReplacementCost($E22,$F22,$G22,$H22,$I22,$J22)</f>
-        <v>8.0</v>
+        <f t="array" ref="M22">SACCR_NormCDF($E22)</f>
+        <v>0.9750021048517795</v>
       </c>
       <c r="N22" s="126">
         <f>IFERROR(ABS(M22-L22),"")</f>
@@ -7650,30 +7677,30 @@
         <v>PASS</v>
       </c>
       <c r="P22" s="130" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="128" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>880</v>
       </c>
       <c r="E23" s="129">
-        <v>1.96</v>
+        <v>-8</v>
       </c>
       <c r="L23" s="125">
         <f>_xlfn.NORM.S.DIST($E23,TRUE)</f>
-        <v>0.9750021048517795</v>
+        <v>6.220960574271819e-16</v>
       </c>
       <c r="M23" s="125" cm="1">
         <f t="array" ref="M23">SACCR_NormCDF($E23)</f>
-        <v>0.9750021048517795</v>
+        <v>6.220960520142784e-16</v>
       </c>
       <c r="N23" s="126">
         <f>IFERROR(ABS(M23-L23),"")</f>
-        <v>0.0</v>
+        <v>5.4129035033506995e-24</v>
       </c>
       <c r="O23" s="127" t="str">
         <f>IF(ISNUMBER(N23),IF(N23&lt;=FormulaTest_Tolerance*MAX(1,ABS(L23)),"PASS","FAIL"),"FAIL")</f>
@@ -7685,57 +7712,63 @@
     </row>
     <row r="24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="128" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="E24" s="129">
-        <v>-8</v>
+        <v>-0.002</v>
+      </c>
+      <c r="F24" s="129">
+        <v>0.001</v>
+      </c>
+      <c r="G24" s="129" t="b">
+        <v>1</v>
       </c>
       <c r="L24" s="125">
-        <f>_xlfn.NORM.S.DIST($E24,TRUE)</f>
-        <v>6.220960574271819e-16</v>
+        <f>IF($G24,MAX(0.001-MIN($E24,$F24),0),MAX(-(1+0.1)*MIN($E24,$F24),0))</f>
+        <v>0.003</v>
       </c>
       <c r="M24" s="125" cm="1">
-        <f t="array" ref="M24">SACCR_NormCDF($E24)</f>
-        <v>6.220960520142784e-16</v>
+        <f t="array" ref="M24">SACCR_LambdaCRR($E24,$F24,$G24)</f>
+        <v>0.003</v>
       </c>
       <c r="N24" s="126">
         <f>IFERROR(ABS(M24-L24),"")</f>
-        <v>5.4129035033506995e-24</v>
+        <v>0.0</v>
       </c>
       <c r="O24" s="127" t="str">
         <f>IF(ISNUMBER(N24),IF(N24&lt;=FormulaTest_Tolerance*MAX(1,ABS(L24)),"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P24" s="130" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="128" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D25" s="24" t="s">
         <v>882</v>
       </c>
       <c r="E25" s="129">
-        <v>-0.002</v>
+        <v>0.02</v>
       </c>
       <c r="F25" s="129">
-        <v>0.001</v>
+        <v>0.03</v>
       </c>
       <c r="G25" s="129" t="b">
         <v>1</v>
       </c>
       <c r="L25" s="125">
         <f>IF($G25,MAX(0.001-MIN($E25,$F25),0),MAX(-(1+0.1)*MIN($E25,$F25),0))</f>
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="M25" s="125" cm="1">
         <f t="array" ref="M25">SACCR_LambdaCRR($E25,$F25,$G25)</f>
-        <v>0.003</v>
+        <v>0.0</v>
       </c>
       <c r="N25" s="126">
         <f>IFERROR(ABS(M25-L25),"")</f>
@@ -7751,27 +7784,27 @@
     </row>
     <row r="26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="128" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D26" s="24" t="s">
         <v>882</v>
       </c>
       <c r="E26" s="129">
-        <v>0.02</v>
+        <v>0.0005</v>
       </c>
       <c r="F26" s="129">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G26" s="129" t="b">
         <v>1</v>
       </c>
       <c r="L26" s="125">
         <f>IF($G26,MAX(0.001-MIN($E26,$F26),0),MAX(-(1+0.1)*MIN($E26,$F26),0))</f>
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="M26" s="125" cm="1">
         <f t="array" ref="M26">SACCR_LambdaCRR($E26,$F26,$G26)</f>
-        <v>0.0</v>
+        <v>0.0005</v>
       </c>
       <c r="N26" s="126">
         <f>IFERROR(ABS(M26-L26),"")</f>
@@ -7787,27 +7820,27 @@
     </row>
     <row r="27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="128" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D27" s="24" t="s">
         <v>882</v>
       </c>
       <c r="E27" s="129">
-        <v>0.0005</v>
+        <v>-5</v>
       </c>
       <c r="F27" s="129">
-        <v>0.01</v>
+        <v>-4</v>
       </c>
       <c r="G27" s="129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="125">
         <f>IF($G27,MAX(0.001-MIN($E27,$F27),0),MAX(-(1+0.1)*MIN($E27,$F27),0))</f>
-        <v>0.0005</v>
+        <v>5.5</v>
       </c>
       <c r="M27" s="125" cm="1">
         <f t="array" ref="M27">SACCR_LambdaCRR($E27,$F27,$G27)</f>
-        <v>0.0005</v>
+        <v>5.5</v>
       </c>
       <c r="N27" s="126">
         <f>IFERROR(ABS(M27-L27),"")</f>
@@ -7823,27 +7856,27 @@
     </row>
     <row r="28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="128" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D28" s="24" t="s">
         <v>882</v>
       </c>
       <c r="E28" s="129">
-        <v>-5</v>
+        <v>40</v>
       </c>
       <c r="F28" s="129">
-        <v>-4</v>
+        <v>35</v>
       </c>
       <c r="G28" s="129" t="b">
         <v>0</v>
       </c>
       <c r="L28" s="125">
         <f>IF($G28,MAX(0.001-MIN($E28,$F28),0),MAX(-(1+0.1)*MIN($E28,$F28),0))</f>
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M28" s="125" cm="1">
         <f t="array" ref="M28">SACCR_LambdaCRR($E28,$F28,$G28)</f>
-        <v>5.5</v>
+        <v>0.0</v>
       </c>
       <c r="N28" s="126">
         <f>IFERROR(ABS(M28-L28),"")</f>
@@ -7857,141 +7890,105 @@
         <v>883</v>
       </c>
     </row>
-    <row r="29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="128" t="s">
-        <v>558</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>882</v>
-      </c>
-      <c r="E29" s="129">
-        <v>40</v>
-      </c>
-      <c r="F29" s="129">
-        <v>35</v>
-      </c>
-      <c r="G29" s="129" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" s="125">
-        <f>IF($G29,MAX(0.001-MIN($E29,$F29),0),MAX(-(1+0.1)*MIN($E29,$F29),0))</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="125" cm="1">
-        <f t="array" ref="M29">SACCR_LambdaCRR($E29,$F29,$G29)</f>
-        <v>0.0</v>
-      </c>
-      <c r="N29" s="126">
-        <f>IFERROR(ABS(M29-L29),"")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O29" s="127" t="str">
-        <f>IF(ISNUMBER(N29),IF(N29&lt;=FormulaTest_Tolerance*MAX(1,ABS(L29)),"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="P29" s="130" t="s">
-        <v>883</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="31">
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%. Below about 0.00000000000001% (1e-16, double precision) only an exact match passes." sqref="E5">
-      <formula1>AND(ISNUMBER(E5),E5&gt;0,E5&lt;=0.01)</formula1>
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%. Below about 0.00000000000001% (1e-16, double precision) only an exact match passes." sqref="E4">
+      <formula1>AND(ISNUMBER(E4),E4&gt;0,E4&lt;=0.01)</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid start date" error="Enter a number of years from -50 to 50." promptTitle="Start date S (years)" prompt="Years from today to the start of the period referenced. Zero or negative means already started and is floored at 0 (CRE52.34; CRR Art. 279b(1)(a))." sqref="E8:E10">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid start date" error="Enter a number of years from -50 to 50." promptTitle="Start date S (years)" prompt="Years from today to the start of the period referenced. Zero or negative means already started and is floored at 0 (CRE52.34; CRR Art. 279b(1)(a))." sqref="E7:E9">
       <formula1>-50</formula1>
       <formula2>50</formula2>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid end date" error="Enter a number of years after the start date and after 0, at most 50." promptTitle="End date E (years)" prompt="Years from today to the end of the period referenced: after the start date and after today, at most 50 (CRE52.34)." sqref="F8:F10">
-      <formula1>AND(ISNUMBER(F8),F8&gt;MAX(E8,0),F8&lt;=50)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid end date" error="Enter a number of years after the start date and after 0, at most 50." promptTitle="End date E (years)" prompt="Years from today to the end of the period referenced: after the start date and after today, at most 50 (CRE52.34)." sqref="F7:F9">
+      <formula1>AND(ISNUMBER(F7),F7&gt;MAX(E7,0),F7&lt;=50)</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid floor" error="Enter a number of years from 0 to 1." promptTitle="SD floor (years)" prompt="Floor on the supervisory duration, in years: 10 business days = 10/250 (CRE52.34)." sqref="G10">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid floor" error="Enter a number of years from 0 to 1." promptTitle="SD floor (years)" prompt="Floor on the supervisory duration, in years: 10 business days = 10/250 (CRE52.34)." sqref="G9">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid maturity" error="Enter a number of years from 0 to 50." promptTitle="Maturity M (years)" prompt="Remaining maturity in years. The unmargined factor floors it at 10 business days and caps it at 1 year (CRE52.48; CRR Art. 279c(1)(a))." sqref="E11:E13">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid maturity" error="Enter a number of years from 0 to 50." promptTitle="Maturity M (years)" prompt="Remaining maturity in years. The unmargined factor floors it at 10 business days and caps it at 1 year (CRE52.48; CRR Art. 279c(1)(a))." sqref="E10:E12">
       <formula1>0</formula1>
       <formula2>50</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Margined" prompt="TRUE = margined factor 1.5 x sqrt(MPOR / 250) (CRE52.52; CRR Art. 279c(1)(b)). FALSE = unmargined factor from M." sqref="F13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Margined" prompt="TRUE = margined factor 1.5 x sqrt(MPOR / 250) (CRE52.52; CRR Art. 279c(1)(b)). FALSE = unmargined factor from M." sqref="F12">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid MPOR" error="Enter a whole number of business days from 1 to 250." promptTitle="MPOR (business days)" prompt="Margin period of risk in business days, used when margined (CRE52.50-52; CRR Art. 285)." sqref="G13">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid MPOR" error="Enter a whole number of business days from 1 to 250." promptTitle="MPOR (business days)" prompt="Margin period of risk in business days, used when margined (CRE52.50-52; CRR Art. 285)." sqref="G12">
       <formula1>1</formula1>
       <formula2>250</formula2>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid price" error="Enter a number; P plus lambda (Input 7) must be above 0." promptTitle="Price P" prompt="Price of the underlying (forward rate for IR options). P plus lambda (Input 7) must be above 0 (CRE52.40)." sqref="E14:E16">
-      <formula1>AND(ISNUMBER(E14),E14+$K14&gt;0)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid price" error="Enter a number; P plus lambda (Input 7) must be above 0." promptTitle="Price P" prompt="Price of the underlying (forward rate for IR options). P plus lambda (Input 7) must be above 0 (CRE52.40)." sqref="E13:E15">
+      <formula1>AND(ISNUMBER(E13),E13+$K13&gt;0)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid strike" error="Enter a number; K plus lambda (Input 7) must be above 0." promptTitle="Strike K" prompt="Strike of the option. K plus lambda (Input 7) must be above 0 (CRE52.40)." sqref="F14:F16">
-      <formula1>AND(ISNUMBER(F14),F14+$K14&gt;0)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid strike" error="Enter a number; K plus lambda (Input 7) must be above 0." promptTitle="Strike K" prompt="Strike of the option. K plus lambda (Input 7) must be above 0 (CRE52.40)." sqref="F13:F15">
+      <formula1>AND(ISNUMBER(F13),F13+$K13&gt;0)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid expiry" error="Enter a number of years above 0, at most 100." promptTitle="Expiry T (years)" prompt="Latest contractual exercise date, in years from today, above 0 (CRE52.40; CRR Art. 279a(1)(a))." sqref="G14:G16">
-      <formula1>AND(ISNUMBER(G14),G14&gt;0,G14&lt;=100)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid expiry" error="Enter a number of years above 0, at most 100." promptTitle="Expiry T (years)" prompt="Latest contractual exercise date, in years from today, above 0 (CRE52.40; CRR Art. 279a(1)(a))." sqref="G13:G15">
+      <formula1>AND(ISNUMBER(G13),G13&gt;0,G13&lt;=100)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid volatility" error="Enter a decimal above 0, at most 5." promptTitle="Supervisory volatility" prompt="Supervisory option volatility as a decimal (0.5 = 50%), above 0 and at most 5 (CRE52.72; CRR Art. 279a)." sqref="H14:H16">
-      <formula1>AND(ISNUMBER(H14),H14&gt;0,H14&lt;=5)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid volatility" error="Enter a decimal above 0, at most 5." promptTitle="Supervisory volatility" prompt="Supervisory option volatility as a decimal (0.5 = 50%), above 0 and at most 5 (CRE52.72; CRR Art. 279a)." sqref="H13:H15">
+      <formula1>AND(ISNUMBER(H13),H13&gt;0,H13&lt;=5)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Call" prompt="TRUE = call option; FALSE = put option (CRE52.40)." sqref="I14:I16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Call" prompt="TRUE = call option; FALSE = put option (CRE52.40)." sqref="I13:I15">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Bought" prompt="TRUE = bought option (long); FALSE = sold option (short) (CRE52.40)." sqref="J14:J16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Bought" prompt="TRUE = bought option (long); FALSE = sold option (short) (CRE52.40)." sqref="J13:J15">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Lambda shift" prompt="Shift added to P and K so that both are above 0 (CRE52.40 FAQ; CRR-RTS Art. 5). 0 or more." sqref="K16">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Lambda shift" prompt="Shift added to P and K so that both are above 0 (CRE52.40 FAQ; CRR-RTS Art. 5). 0 or more." sqref="K15">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid attachment" error="Enter a decimal from 0 to below 1, e.g. 0.03 for 3%." promptTitle="Attachment A" prompt="Attachment point of the tranche, from 0 to below 1 (CRE52.41)." sqref="E17">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid attachment" error="Enter a decimal from 0 to below 1, e.g. 0.03 for 3%." promptTitle="Attachment A" prompt="Attachment point of the tranche, from 0 to below 1 (CRE52.41)." sqref="E16">
       <formula1>0</formula1>
       <formula2>0.9999</formula2>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid detachment" error="Enter a decimal above the attachment point and at most 1." promptTitle="Detachment D" prompt="Detachment point, above the attachment and at most 1 (CRE52.41)." sqref="F17">
-      <formula1>AND(ISNUMBER(F17),F17&gt;E17,F17&lt;=1)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid detachment" error="Enter a decimal above the attachment point and at most 1." promptTitle="Detachment D" prompt="Detachment point, above the attachment and at most 1 (CRE52.41)." sqref="F16">
+      <formula1>AND(ISNUMBER(F16),F16&gt;E16,F16&lt;=1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Long" prompt="TRUE = long in the tranche (positive delta); FALSE = short (CRE52.41)." sqref="G17">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Long" prompt="TRUE = long in the tranche (positive delta); FALSE = short (CRE52.41)." sqref="G16">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Bucket effective notional" prompt="Signed effective notional D of maturity bucket 1, 2 or 3 (under 1 year, 1 to 5 years, over 5 years) (CRE52.57)." sqref="E18:G18">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Bucket effective notional" prompt="Signed effective notional D of maturity bucket 1, 2 or 3 (under 1 year, 1 to 5 years, over 5 years) (CRE52.57)." sqref="E17:G17">
+      <formula1>ISNUMBER(E17)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Entity add-on" prompt="Add-on of entity or commodity type k, signed by direction (CRE52.61; CRR Art. 280c)." sqref="E18:G18">
       <formula1>ISNUMBER(E18)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Entity add-on" prompt="Add-on of entity or commodity type k, signed by direction (CRE52.61; CRR Art. 280c)." sqref="E19:G19">
-      <formula1>ISNUMBER(E19)</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid correlation" error="Enter a decimal from 0 to 1." promptTitle="Correlation" prompt="Correlation of entity k, as a decimal from 0 to 1: credit 0.5 single name, 0.8 index (CRE52.61)." sqref="H19:J19">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid correlation" error="Enter a decimal from 0 to 1." promptTitle="Correlation" prompt="Correlation of entity k, as a decimal from 0 to 1: credit 0.5 single name, 0.8 index (CRE52.61)." sqref="H18:J18">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="V - C" prompt="Net market value of the netting set less collateral, signed (CRE52.23; CRR Art. 278(3))." sqref="E20:E21">
-      <formula1>ISNUMBER(E20)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="V - C" prompt="Net market value of the netting set less collateral, signed (CRE52.23; CRR Art. 278(3))." sqref="E19:E20">
+      <formula1>ISNUMBER(E19)</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Aggregate add-on" prompt="Aggregate add-on of the netting set, 0 or more; 0 gives a multiplier of 1 (CRE52.23)." sqref="F20:F21">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Aggregate add-on" prompt="Aggregate add-on of the netting set, 0 or more; 0 gives a multiplier of 1 (CRE52.23)." sqref="F19:F20">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="V" prompt="Net market value of the trades in the netting set, signed (CRE52.10; CRR Art. 275)." sqref="E22">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="V" prompt="Net market value of the trades in the netting set, signed (CRE52.10; CRR Art. 275)." sqref="E21">
+      <formula1>ISNUMBER(E21)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="C" prompt="Net collateral held after haircuts; negative if posted (CRE52.10; CRR Art. 275)." sqref="F21">
+      <formula1>ISNUMBER(F21)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Margined" prompt="TRUE = margined RC max(V - C, TH + MTA - NICA, 0) (CRE52.18); FALSE = max(V - C, 0) (CRE52.10)." sqref="G21">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Threshold TH" prompt="Threshold of the margin agreement, 0 or more (CRE52.18; CRR Art. 275(2))." sqref="H21">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Minimum transfer amount" prompt="Minimum transfer amount MTA, 0 or more (CRE52.18; CRR Art. 275(2))." sqref="I21">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="NICA" prompt="Net independent collateral amount, signed; negative if posted (CRE52.13; CRR Art. 275(2))." sqref="J21">
+      <formula1>ISNUMBER(J21)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="x" prompt="Point at which the standard normal distribution function is evaluated." sqref="E22:E23">
       <formula1>ISNUMBER(E22)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="C" prompt="Net collateral held after haircuts; negative if posted (CRE52.10; CRR Art. 275)." sqref="F22">
-      <formula1>ISNUMBER(F22)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Price or strike" prompt="Price P (Input 1) or strike K (Input 2) of the option; negative values allowed (CRR-RTS Art. 5(2))." sqref="E24:F28">
+      <formula1>ISNUMBER(E24)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Margined" prompt="TRUE = margined RC max(V - C, TH + MTA - NICA, 0) (CRE52.18); FALSE = max(V - C, 0) (CRE52.10)." sqref="G22">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Threshold TH" prompt="Threshold of the margin agreement, 0 or more (CRE52.18; CRR Art. 275(2))." sqref="H22">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Minimum transfer amount" prompt="Minimum transfer amount MTA, 0 or more (CRE52.18; CRR Art. 275(2))." sqref="I22">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="NICA" prompt="Net independent collateral amount, signed; negative if posted (CRE52.13; CRR Art. 275(2))." sqref="J22">
-      <formula1>ISNUMBER(J22)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="x" prompt="Point at which the standard normal distribution function is evaluated." sqref="E23:E24">
-      <formula1>ISNUMBER(E23)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Price or strike" prompt="Price P (Input 1) or strike K (Input 2) of the option; negative values allowed (CRR-RTS Art. 5(2))." sqref="E25:F29">
-      <formula1>ISNUMBER(E25)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Interest rate" prompt="TRUE = interest-rate option (threshold 0.10%); FALSE = commodity option (threshold 0.1) (CRR-RTS Art. 5(2))." sqref="G25:G29">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Interest rate" prompt="TRUE = interest-rate option (threshold 0.10%); FALSE = commodity option (threshold 0.1) (CRR-RTS Art. 5(2))." sqref="G24:G28">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -7553,7 +7553,7 @@
         <v>282</v>
       </c>
       <c r="L19" s="125">
-        <f>IF($F19&lt;=0,1,MIN(1,0.05+0.95*EXP($E19/(2*0.95*$F19))))</f>
+        <f>IF(OR($F19&lt;=0,$E19&gt;0),1,MIN(1,0.05+0.95*EXP($E19/(2*0.95*$F19))))</f>
         <v>0.9651926811871945</v>
       </c>
       <c r="M19" s="125" cm="1">
@@ -7586,7 +7586,7 @@
         <v>282</v>
       </c>
       <c r="L20" s="125">
-        <f>IF($F20&lt;=0,1,MIN(1,0.05+0.95*EXP($E20/(2*0.95*$F20))))</f>
+        <f>IF(OR($F20&lt;=0,$E20&gt;0),1,MIN(1,0.05+0.95*EXP($E20/(2*0.95*$F20))))</f>
         <v>1</v>
       </c>
       <c r="M20" s="125" cm="1">

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="899">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -2791,13 +2791,16 @@
     <t>Rule</t>
   </si>
   <si>
-    <t>Tolerance: a test passes when |Function - Expected| &lt;= tolerance x max(1, |Expected|)</t>
+    <t>Tolerance: a test passes when its Rel. diff is at most this value</t>
   </si>
   <si>
     <t>FormulaTest</t>
   </si>
   <si>
     <t>Formula tests</t>
+  </si>
+  <si>
+    <t>Rel. diff</t>
   </si>
 </sst>
 </file>
@@ -3224,7 +3227,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3620,6 +3623,9 @@
     </xf>
     <xf numFmtId="169" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7075,7 +7081,7 @@
         <v>893</v>
       </c>
       <c r="N6" s="55" t="s">
-        <v>514</v>
+        <v>898</v>
       </c>
       <c r="O6" s="55" t="s">
         <v>515</v>
@@ -7105,12 +7111,12 @@
         <f t="array" ref="M7">SACCR_SupervisoryDuration($E7,$F7)</f>
         <v>7.8693868057473315</v>
       </c>
-      <c r="N7" s="126">
-        <f>IFERROR(ABS(M7-L7),"")</f>
+      <c r="N7" s="132">
+        <f>IFERROR(ABS(M7-L7)/MAX(1,ABS(L7)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O7" s="127" t="str">
-        <f>IF(ISNUMBER(N7),IF(N7&lt;=FormulaTest_Tolerance*MAX(1,ABS(L7)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N7),IF(N7&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P7" s="130" t="s">
@@ -7138,12 +7144,12 @@
         <f t="array" ref="M8">SACCR_SupervisoryDuration($E8,$F8)</f>
         <v>7.485592282404547</v>
       </c>
-      <c r="N8" s="126">
-        <f>IFERROR(ABS(M8-L8),"")</f>
+      <c r="N8" s="132">
+        <f>IFERROR(ABS(M8-L8)/MAX(1,ABS(L8)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O8" s="127" t="str">
-        <f>IF(ISNUMBER(N8),IF(N8&lt;=FormulaTest_Tolerance*MAX(1,ABS(L8)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N8),IF(N8&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P8" s="130" t="s">
@@ -7175,12 +7181,12 @@
         <f t="array" ref="M9">SACCR_SupervisoryDuration($E9,$F9,$G9)</f>
         <v>0.04</v>
       </c>
-      <c r="N9" s="126">
-        <f>IFERROR(ABS(M9-L9),"")</f>
+      <c r="N9" s="132">
+        <f>IFERROR(ABS(M9-L9)/MAX(1,ABS(L9)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O9" s="127" t="str">
-        <f>IF(ISNUMBER(N9),IF(N9&lt;=FormulaTest_Tolerance*MAX(1,ABS(L9)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N9),IF(N9&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P9" s="130" t="s">
@@ -7205,12 +7211,12 @@
         <f t="array" ref="M10">SACCR_MaturityFactor($E10)</f>
         <v>0.8660254037844386</v>
       </c>
-      <c r="N10" s="126">
-        <f>IFERROR(ABS(M10-L10),"")</f>
+      <c r="N10" s="132">
+        <f>IFERROR(ABS(M10-L10)/MAX(1,ABS(L10)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O10" s="127" t="str">
-        <f>IF(ISNUMBER(N10),IF(N10&lt;=FormulaTest_Tolerance*MAX(1,ABS(L10)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N10),IF(N10&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P10" s="130" t="s">
@@ -7236,12 +7242,12 @@
         <f t="array" ref="M11">SACCR_MaturityFactor($E11)</f>
         <v>0.2</v>
       </c>
-      <c r="N11" s="126">
-        <f>IFERROR(ABS(M11-L11),"")</f>
+      <c r="N11" s="132">
+        <f>IFERROR(ABS(M11-L11)/MAX(1,ABS(L11)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O11" s="127" t="str">
-        <f>IF(ISNUMBER(N11),IF(N11&lt;=FormulaTest_Tolerance*MAX(1,ABS(L11)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N11),IF(N11&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P11" s="130" t="s">
@@ -7272,12 +7278,12 @@
         <f t="array" ref="M12">SACCR_MaturityFactor($E12,$F12,$G12)</f>
         <v>0.30000000000000004</v>
       </c>
-      <c r="N12" s="126">
-        <f>IFERROR(ABS(M12-L12),"")</f>
+      <c r="N12" s="132">
+        <f>IFERROR(ABS(M12-L12)/MAX(1,ABS(L12)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O12" s="127" t="str">
-        <f>IF(ISNUMBER(N12),IF(N12&lt;=FormulaTest_Tolerance*MAX(1,ABS(L12)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N12),IF(N12&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P12" s="130" t="s">
@@ -7317,12 +7323,12 @@
         <f t="array" ref="M13">SACCR_OptionDelta($E13,$F13,$G13,$H13,$I13,$J13)</f>
         <v>-0.2693952177105327</v>
       </c>
-      <c r="N13" s="126">
-        <f>IFERROR(ABS(M13-L13),"")</f>
+      <c r="N13" s="132">
+        <f>IFERROR(ABS(M13-L13)/MAX(1,ABS(L13)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O13" s="127" t="str">
-        <f>IF(ISNUMBER(N13),IF(N13&lt;=FormulaTest_Tolerance*MAX(1,ABS(L13)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N13),IF(N13&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P13" s="130" t="s">
@@ -7362,12 +7368,12 @@
         <f t="array" ref="M14">SACCR_OptionDelta($E14,$F14,$G14,$H14,$I14,$J14)</f>
         <v>-0.37901134582780294</v>
       </c>
-      <c r="N14" s="126">
-        <f>IFERROR(ABS(M14-L14),"")</f>
+      <c r="N14" s="132">
+        <f>IFERROR(ABS(M14-L14)/MAX(1,ABS(L14)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O14" s="127" t="str">
-        <f>IF(ISNUMBER(N14),IF(N14&lt;=FormulaTest_Tolerance*MAX(1,ABS(L14)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N14),IF(N14&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P14" s="130" t="s">
@@ -7410,12 +7416,12 @@
         <f t="array" ref="M15">SACCR_OptionDelta($E15,$F15,$G15,$H15,$I15,$J15,$K15)</f>
         <v>0.46143935794124913</v>
       </c>
-      <c r="N15" s="126">
-        <f>IFERROR(ABS(M15-L15),"")</f>
+      <c r="N15" s="132">
+        <f>IFERROR(ABS(M15-L15)/MAX(1,ABS(L15)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O15" s="127" t="str">
-        <f>IF(ISNUMBER(N15),IF(N15&lt;=FormulaTest_Tolerance*MAX(1,ABS(L15)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N15),IF(N15&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P15" s="130" t="s">
@@ -7446,12 +7452,12 @@
         <f t="array" ref="M16">SACCR_CDODelta($E16,$F16,$G16)</f>
         <v>5.740967544396816</v>
       </c>
-      <c r="N16" s="126">
-        <f>IFERROR(ABS(M16-L16),"")</f>
-        <v>8.881784197001252e-16</v>
+      <c r="N16" s="132">
+        <f>IFERROR(ABS(M16-L16)/MAX(1,ABS(L16)),"")</f>
+        <v>1.5470883833283245e-16</v>
       </c>
       <c r="O16" s="127" t="str">
-        <f>IF(ISNUMBER(N16),IF(N16&lt;=FormulaTest_Tolerance*MAX(1,ABS(L16)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N16),IF(N16&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P16" s="130" t="s">
@@ -7482,12 +7488,12 @@
         <f t="array" ref="M17">SACCR_IREffectiveNotional($E17,$F17,$G17)</f>
         <v>59269.963463710395</v>
       </c>
-      <c r="N17" s="126">
-        <f>IFERROR(ABS(M17-L17),"")</f>
+      <c r="N17" s="132">
+        <f>IFERROR(ABS(M17-L17)/MAX(1,ABS(L17)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O17" s="127" t="str">
-        <f>IF(ISNUMBER(N17),IF(N17&lt;=FormulaTest_Tolerance*MAX(1,ABS(L17)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N17),IF(N17&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P17" s="130" t="s">
@@ -7527,12 +7533,12 @@
         <f t="array" ref="M18">SACCR_FactorAggregation($E18:$G18,$H18:$J18)</f>
         <v>282.12883185966604</v>
       </c>
-      <c r="N18" s="126">
-        <f>IFERROR(ABS(M18-L18),"")</f>
+      <c r="N18" s="132">
+        <f>IFERROR(ABS(M18-L18)/MAX(1,ABS(L18)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O18" s="127" t="str">
-        <f>IF(ISNUMBER(N18),IF(N18&lt;=FormulaTest_Tolerance*MAX(1,ABS(L18)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N18),IF(N18&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P18" s="130" t="s">
@@ -7560,12 +7566,12 @@
         <f t="array" ref="M19">SACCR_Multiplier($E19,$F19)</f>
         <v>0.9651926811871945</v>
       </c>
-      <c r="N19" s="126">
-        <f>IFERROR(ABS(M19-L19),"")</f>
+      <c r="N19" s="132">
+        <f>IFERROR(ABS(M19-L19)/MAX(1,ABS(L19)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O19" s="127" t="str">
-        <f>IF(ISNUMBER(N19),IF(N19&lt;=FormulaTest_Tolerance*MAX(1,ABS(L19)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N19),IF(N19&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P19" s="130" t="s">
@@ -7593,12 +7599,12 @@
         <f t="array" ref="M20">SACCR_Multiplier($E20,$F20)</f>
         <v>1.0</v>
       </c>
-      <c r="N20" s="126">
-        <f>IFERROR(ABS(M20-L20),"")</f>
+      <c r="N20" s="132">
+        <f>IFERROR(ABS(M20-L20)/MAX(1,ABS(L20)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O20" s="127" t="str">
-        <f>IF(ISNUMBER(N20),IF(N20&lt;=FormulaTest_Tolerance*MAX(1,ABS(L20)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N20),IF(N20&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P20" s="130" t="s">
@@ -7638,12 +7644,12 @@
         <f t="array" ref="M21">SACCR_ReplacementCost($E21,$F21,$G21,$H21,$I21,$J21)</f>
         <v>8.0</v>
       </c>
-      <c r="N21" s="126">
-        <f>IFERROR(ABS(M21-L21),"")</f>
+      <c r="N21" s="132">
+        <f>IFERROR(ABS(M21-L21)/MAX(1,ABS(L21)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O21" s="127" t="str">
-        <f>IF(ISNUMBER(N21),IF(N21&lt;=FormulaTest_Tolerance*MAX(1,ABS(L21)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N21),IF(N21&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P21" s="130" t="s">
@@ -7668,12 +7674,12 @@
         <f t="array" ref="M22">SACCR_NormCDF($E22)</f>
         <v>0.9750021048517795</v>
       </c>
-      <c r="N22" s="126">
-        <f>IFERROR(ABS(M22-L22),"")</f>
+      <c r="N22" s="132">
+        <f>IFERROR(ABS(M22-L22)/MAX(1,ABS(L22)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O22" s="127" t="str">
-        <f>IF(ISNUMBER(N22),IF(N22&lt;=FormulaTest_Tolerance*MAX(1,ABS(L22)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N22),IF(N22&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P22" s="130" t="s">
@@ -7698,12 +7704,12 @@
         <f t="array" ref="M23">SACCR_NormCDF($E23)</f>
         <v>6.220960520142784e-16</v>
       </c>
-      <c r="N23" s="126">
-        <f>IFERROR(ABS(M23-L23),"")</f>
+      <c r="N23" s="132">
+        <f>IFERROR(ABS(M23-L23)/MAX(1,ABS(L23)),"")</f>
         <v>5.4129035033506995e-24</v>
       </c>
       <c r="O23" s="127" t="str">
-        <f>IF(ISNUMBER(N23),IF(N23&lt;=FormulaTest_Tolerance*MAX(1,ABS(L23)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N23),IF(N23&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P23" s="130" t="s">
@@ -7734,12 +7740,12 @@
         <f t="array" ref="M24">SACCR_LambdaCRR($E24,$F24,$G24)</f>
         <v>0.003</v>
       </c>
-      <c r="N24" s="126">
-        <f>IFERROR(ABS(M24-L24),"")</f>
+      <c r="N24" s="132">
+        <f>IFERROR(ABS(M24-L24)/MAX(1,ABS(L24)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O24" s="127" t="str">
-        <f>IF(ISNUMBER(N24),IF(N24&lt;=FormulaTest_Tolerance*MAX(1,ABS(L24)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N24),IF(N24&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P24" s="130" t="s">
@@ -7770,12 +7776,12 @@
         <f t="array" ref="M25">SACCR_LambdaCRR($E25,$F25,$G25)</f>
         <v>0.0</v>
       </c>
-      <c r="N25" s="126">
-        <f>IFERROR(ABS(M25-L25),"")</f>
+      <c r="N25" s="132">
+        <f>IFERROR(ABS(M25-L25)/MAX(1,ABS(L25)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O25" s="127" t="str">
-        <f>IF(ISNUMBER(N25),IF(N25&lt;=FormulaTest_Tolerance*MAX(1,ABS(L25)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N25),IF(N25&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P25" s="130" t="s">
@@ -7806,12 +7812,12 @@
         <f t="array" ref="M26">SACCR_LambdaCRR($E26,$F26,$G26)</f>
         <v>0.0005</v>
       </c>
-      <c r="N26" s="126">
-        <f>IFERROR(ABS(M26-L26),"")</f>
+      <c r="N26" s="132">
+        <f>IFERROR(ABS(M26-L26)/MAX(1,ABS(L26)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O26" s="127" t="str">
-        <f>IF(ISNUMBER(N26),IF(N26&lt;=FormulaTest_Tolerance*MAX(1,ABS(L26)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N26),IF(N26&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P26" s="130" t="s">
@@ -7842,12 +7848,12 @@
         <f t="array" ref="M27">SACCR_LambdaCRR($E27,$F27,$G27)</f>
         <v>5.5</v>
       </c>
-      <c r="N27" s="126">
-        <f>IFERROR(ABS(M27-L27),"")</f>
+      <c r="N27" s="132">
+        <f>IFERROR(ABS(M27-L27)/MAX(1,ABS(L27)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O27" s="127" t="str">
-        <f>IF(ISNUMBER(N27),IF(N27&lt;=FormulaTest_Tolerance*MAX(1,ABS(L27)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N27),IF(N27&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P27" s="130" t="s">
@@ -7878,12 +7884,12 @@
         <f t="array" ref="M28">SACCR_LambdaCRR($E28,$F28,$G28)</f>
         <v>0.0</v>
       </c>
-      <c r="N28" s="126">
-        <f>IFERROR(ABS(M28-L28),"")</f>
+      <c r="N28" s="132">
+        <f>IFERROR(ABS(M28-L28)/MAX(1,ABS(L28)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O28" s="127" t="str">
-        <f>IF(ISNUMBER(N28),IF(N28&lt;=FormulaTest_Tolerance*MAX(1,ABS(L28)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N28),IF(N28&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P28" s="130" t="s">
@@ -7892,7 +7898,7 @@
     </row>
   </sheetData>
   <dataValidations count="31">
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%. Below about 0.00000000000001% (1e-16, double precision) only an exact match passes." sqref="E4">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test: a row passes when its Rel. diff, |Function - Expected| / max(1, |Expected|), is at most this value. Default 0.001%. Below about 1e-16 (double precision) only an exact match passes." sqref="E4">
       <formula1>AND(ISNUMBER(E4),E4&gt;0,E4&lt;=0.01)</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid start date" error="Enter a number of years from -50 to 50." promptTitle="Start date S (years)" prompt="Years from today to the start of the period referenced. Zero or negative means already started and is floored at 0 (CRE52.34; CRR Art. 279b(1)(a))." sqref="E7:E9">

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -1738,7 +1738,7 @@
     <t>=SACCR_NormCDF(1.96)</t>
   </si>
   <si>
-    <t>Normal CDF(-8)</t>
+    <t>Normal CDF(-4)</t>
   </si>
   <si>
     <t>=SACCR_NormCDF(-8)</t>
@@ -7694,19 +7694,19 @@
         <v>880</v>
       </c>
       <c r="E23" s="129">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="L23" s="125">
         <f>_xlfn.NORM.S.DIST($E23,TRUE)</f>
-        <v>6.220960574271819e-16</v>
+        <v>3.1671241833119965e-05</v>
       </c>
       <c r="M23" s="125" cm="1">
         <f t="array" ref="M23">SACCR_NormCDF($E23)</f>
-        <v>6.220960520142784e-16</v>
+        <v>3.167124183311601e-05</v>
       </c>
       <c r="N23" s="132">
         <f>IFERROR(ABS(M23-L23)/MAX(1,ABS(L23)),"")</f>
-        <v>5.4129035033506995e-24</v>
+        <v>3.957337929572091e-18</v>
       </c>
       <c r="O23" s="127" t="str">
         <f>IF(ISNUMBER(N23),IF(N23&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -28,7 +28,7 @@
     <definedName name="BasisFactor">Params!$E$17</definedName>
     <definedName name="BusinessDaysPerYear">Params!$E$11</definedName>
     <definedName name="DaysPerYear">Params!$E$10</definedName>
-    <definedName name="FormulaTest_Tolerance">FormulaTest!$D$5</definedName>
+    <definedName name="FormulaTest_Tolerance">FormulaTest!$E$4</definedName>
     <definedName name="FX_Table">Params!$C$57:$E$62</definedName>
     <definedName name="IRBucketOffset">Params!$E$22</definedName>
     <definedName name="IRCorrBucket12">Params!$E$19</definedName>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="899">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -1738,7 +1738,7 @@
     <t>=SACCR_NormCDF(1.96)</t>
   </si>
   <si>
-    <t>Normal CDF(-8)</t>
+    <t>Normal CDF(-4)</t>
   </si>
   <si>
     <t>=SACCR_NormCDF(-8)</t>
@@ -2791,13 +2791,16 @@
     <t>Rule</t>
   </si>
   <si>
-    <t>Tolerance: a test passes when |Function - Expected| &lt;= tolerance x max(1, |Expected|)</t>
+    <t>Tolerance: a test passes when its Rel. diff is at most this value</t>
   </si>
   <si>
     <t>FormulaTest</t>
   </si>
   <si>
     <t>Formula tests</t>
+  </si>
+  <si>
+    <t>Rel. diff</t>
   </si>
 </sst>
 </file>
@@ -3224,7 +3227,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3620,6 +3623,9 @@
     </xf>
     <xf numFmtId="169" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6948,7 +6954,7 @@
     <tabColor rgb="FF548235"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AB29"/>
+  <dimension ref="B1:AB28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
@@ -7022,98 +7028,128 @@
       <c r="AA2" s="68"/>
       <c r="AB2" s="68"/>
     </row>
-    <row r="3" ht="21" x14ac:dyDescent="0.25">
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="2" t="s">
+    <row r="3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="2" t="s">
         <v>508</v>
       </c>
     </row>
+    <row r="4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="128" t="s">
+        <v>895</v>
+      </c>
+      <c r="E4" s="131">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
     <row r="5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="128" t="s">
-        <v>895</v>
-      </c>
-      <c r="D5" s="131">
-        <v>1.0000000000000001E-5</v>
-      </c>
-    </row>
-    <row r="6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="48" t="s">
+      <c r="C5" s="48" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="54" t="s">
+    <row r="6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="54" t="s">
         <v>510</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D6" s="54" t="s">
         <v>884</v>
       </c>
-      <c r="E7" s="55" t="s">
+      <c r="E6" s="55" t="s">
         <v>885</v>
       </c>
-      <c r="F7" s="55" t="s">
+      <c r="F6" s="55" t="s">
         <v>886</v>
       </c>
-      <c r="G7" s="55" t="s">
+      <c r="G6" s="55" t="s">
         <v>887</v>
       </c>
-      <c r="H7" s="55" t="s">
+      <c r="H6" s="55" t="s">
         <v>888</v>
       </c>
-      <c r="I7" s="55" t="s">
+      <c r="I6" s="55" t="s">
         <v>889</v>
       </c>
-      <c r="J7" s="55" t="s">
+      <c r="J6" s="55" t="s">
         <v>890</v>
       </c>
-      <c r="K7" s="55" t="s">
+      <c r="K6" s="55" t="s">
         <v>891</v>
       </c>
-      <c r="L7" s="55" t="s">
+      <c r="L6" s="55" t="s">
         <v>892</v>
       </c>
-      <c r="M7" s="55" t="s">
+      <c r="M6" s="55" t="s">
         <v>893</v>
       </c>
-      <c r="N7" s="55" t="s">
-        <v>514</v>
-      </c>
-      <c r="O7" s="55" t="s">
+      <c r="N6" s="55" t="s">
+        <v>898</v>
+      </c>
+      <c r="O6" s="55" t="s">
         <v>515</v>
       </c>
-      <c r="P7" s="54" t="s">
+      <c r="P6" s="54" t="s">
         <v>894</v>
+      </c>
+    </row>
+    <row r="7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="128" t="s">
+        <v>516</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>859</v>
+      </c>
+      <c r="E7" s="129">
+        <v>0</v>
+      </c>
+      <c r="F7" s="129">
+        <v>10</v>
+      </c>
+      <c r="L7" s="125">
+        <f>(EXP(-0.05*MAX($E7,0))-EXP(-0.05*$F7))/0.05</f>
+        <v>7.8693868057473315</v>
+      </c>
+      <c r="M7" s="125" cm="1">
+        <f t="array" ref="M7">SACCR_SupervisoryDuration($E7,$F7)</f>
+        <v>7.8693868057473315</v>
+      </c>
+      <c r="N7" s="132">
+        <f>IFERROR(ABS(M7-L7)/MAX(1,ABS(L7)),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="127" t="str">
+        <f>IF(ISNUMBER(N7),IF(N7&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="P7" s="130" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="128" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>859</v>
       </c>
       <c r="E8" s="129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="129">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L8" s="125">
         <f>(EXP(-0.05*MAX($E8,0))-EXP(-0.05*$F8))/0.05</f>
-        <v>7.8693868057473315</v>
+        <v>7.485592282404547</v>
       </c>
       <c r="M8" s="125" cm="1">
         <f t="array" ref="M8">SACCR_SupervisoryDuration($E8,$F8)</f>
-        <v>7.8693868057473315</v>
-      </c>
-      <c r="N8" s="126">
-        <f>IFERROR(ABS(M8-L8),"")</f>
+        <v>7.485592282404547</v>
+      </c>
+      <c r="N8" s="132">
+        <f>IFERROR(ABS(M8-L8)/MAX(1,ABS(L8)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O8" s="127" t="str">
-        <f>IF(ISNUMBER(N8),IF(N8&lt;=FormulaTest_Tolerance*MAX(1,ABS(L8)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N8),IF(N8&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P8" s="130" t="s">
@@ -7122,31 +7158,35 @@
     </row>
     <row r="9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="128" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="E9" s="129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="129">
-        <v>11</v>
+        <v>0.01</v>
+      </c>
+      <c r="G9" s="129">
+        <f>10/250</f>
+        <v>0.04</v>
       </c>
       <c r="L9" s="125">
-        <f>(EXP(-0.05*MAX($E9,0))-EXP(-0.05*$F9))/0.05</f>
-        <v>7.485592282404547</v>
+        <f>MAX((EXP(-0.05*MAX($E9,0))-EXP(-0.05*$F9))/0.05,$G9)</f>
+        <v>0.04</v>
       </c>
       <c r="M9" s="125" cm="1">
-        <f t="array" ref="M9">SACCR_SupervisoryDuration($E9,$F9)</f>
-        <v>7.485592282404547</v>
-      </c>
-      <c r="N9" s="126">
-        <f>IFERROR(ABS(M9-L9),"")</f>
+        <f t="array" ref="M9">SACCR_SupervisoryDuration($E9,$F9,$G9)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N9" s="132">
+        <f>IFERROR(ABS(M9-L9)/MAX(1,ABS(L9)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O9" s="127" t="str">
-        <f>IF(ISNUMBER(N9),IF(N9&lt;=FormulaTest_Tolerance*MAX(1,ABS(L9)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N9),IF(N9&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P9" s="130" t="s">
@@ -7155,65 +7195,59 @@
     </row>
     <row r="10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="128" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E10" s="129">
-        <v>0</v>
-      </c>
-      <c r="F10" s="129">
-        <v>0.01</v>
-      </c>
-      <c r="G10" s="129">
-        <f>10/250</f>
-        <v>0.04</v>
+        <v>0.75</v>
       </c>
       <c r="L10" s="125">
-        <f>MAX((EXP(-0.05*MAX($E10,0))-EXP(-0.05*$F10))/0.05,$G10)</f>
-        <v>0.04</v>
+        <f>SQRT(MIN(MAX($E10,10/250),1))</f>
+        <v>0.8660254037844386</v>
       </c>
       <c r="M10" s="125" cm="1">
-        <f t="array" ref="M10">SACCR_SupervisoryDuration($E10,$F10,$G10)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N10" s="126">
-        <f>IFERROR(ABS(M10-L10),"")</f>
+        <f t="array" ref="M10">SACCR_MaturityFactor($E10)</f>
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="N10" s="132">
+        <f>IFERROR(ABS(M10-L10)/MAX(1,ABS(L10)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O10" s="127" t="str">
-        <f>IF(ISNUMBER(N10),IF(N10&lt;=FormulaTest_Tolerance*MAX(1,ABS(L10)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N10),IF(N10&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P10" s="130" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="128" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D11" s="24" t="s">
         <v>862</v>
       </c>
       <c r="E11" s="129">
-        <v>0.75</v>
+        <f>3/365</f>
+        <v>0.00821917808219178</v>
       </c>
       <c r="L11" s="125">
         <f>SQRT(MIN(MAX($E11,10/250),1))</f>
-        <v>0.8660254037844386</v>
+        <v>0.2</v>
       </c>
       <c r="M11" s="125" cm="1">
         <f t="array" ref="M11">SACCR_MaturityFactor($E11)</f>
-        <v>0.8660254037844386</v>
-      </c>
-      <c r="N11" s="126">
-        <f>IFERROR(ABS(M11-L11),"")</f>
+        <v>0.2</v>
+      </c>
+      <c r="N11" s="132">
+        <f>IFERROR(ABS(M11-L11)/MAX(1,ABS(L11)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O11" s="127" t="str">
-        <f>IF(ISNUMBER(N11),IF(N11&lt;=FormulaTest_Tolerance*MAX(1,ABS(L11)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N11),IF(N11&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P11" s="130" t="s">
@@ -7222,110 +7256,124 @@
     </row>
     <row r="12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="128" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="E12" s="129">
-        <f>3/365</f>
-        <v>0.00821917808219178</v>
+        <v>0</v>
+      </c>
+      <c r="F12" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="129">
+        <v>10</v>
       </c>
       <c r="L12" s="125">
-        <f>SQRT(MIN(MAX($E12,10/250),1))</f>
-        <v>0.2</v>
+        <f>IF($F12,1.5*SQRT($G12/250),SQRT(MIN(MAX($E12,10/250),1)))</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="M12" s="125" cm="1">
-        <f t="array" ref="M12">SACCR_MaturityFactor($E12)</f>
-        <v>0.2</v>
-      </c>
-      <c r="N12" s="126">
-        <f>IFERROR(ABS(M12-L12),"")</f>
+        <f t="array" ref="M12">SACCR_MaturityFactor($E12,$F12,$G12)</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="N12" s="132">
+        <f>IFERROR(ABS(M12-L12)/MAX(1,ABS(L12)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O12" s="127" t="str">
-        <f>IF(ISNUMBER(N12),IF(N12&lt;=FormulaTest_Tolerance*MAX(1,ABS(L12)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N12),IF(N12&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P12" s="130" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="128" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="E13" s="129">
+        <v>0.06</v>
+      </c>
+      <c r="F13" s="129">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="129">
+        <v>1</v>
+      </c>
+      <c r="H13" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="129" t="b">
         <v>0</v>
       </c>
-      <c r="F13" s="129" t="b">
+      <c r="J13" s="129" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="129">
-        <v>10</v>
-      </c>
       <c r="L13" s="125">
-        <f>IF($F13,1.5*SQRT($G13/250),SQRT(MIN(MAX($E13,10/250),1)))</f>
-        <v>0.30000000000000004</v>
+        <f>IF($I13,_xlfn.NORM.S.DIST((LN(($E13+$K13)/($F13+$K13))+$H13^2*$G13/2)/($H13*SQRT($G13)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E13+$K13)/($F13+$K13))+$H13^2*$G13/2)/($H13*SQRT($G13)),TRUE))*IF($J13,1,-1)</f>
+        <v>-0.2693952177105327</v>
       </c>
       <c r="M13" s="125" cm="1">
-        <f t="array" ref="M13">SACCR_MaturityFactor($E13,$F13,$G13)</f>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="N13" s="126">
-        <f>IFERROR(ABS(M13-L13),"")</f>
+        <f t="array" ref="M13">SACCR_OptionDelta($E13,$F13,$G13,$H13,$I13,$J13)</f>
+        <v>-0.2693952177105327</v>
+      </c>
+      <c r="N13" s="132">
+        <f>IFERROR(ABS(M13-L13)/MAX(1,ABS(L13)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O13" s="127" t="str">
-        <f>IF(ISNUMBER(N13),IF(N13&lt;=FormulaTest_Tolerance*MAX(1,ABS(L13)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N13),IF(N13&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P13" s="130" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="128" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>866</v>
       </c>
       <c r="E14" s="129">
-        <v>0.06</v>
+        <v>100</v>
       </c>
       <c r="F14" s="129">
-        <v>0.05</v>
+        <v>110</v>
       </c>
       <c r="G14" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="129">
+        <v>0.32</v>
+      </c>
+      <c r="I14" s="129" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="129">
-        <v>0.5</v>
-      </c>
-      <c r="I14" s="129" t="b">
+      <c r="J14" s="129" t="b">
         <v>0</v>
-      </c>
-      <c r="J14" s="129" t="b">
-        <v>1</v>
       </c>
       <c r="L14" s="125">
         <f>IF($I14,_xlfn.NORM.S.DIST((LN(($E14+$K14)/($F14+$K14))+$H14^2*$G14/2)/($H14*SQRT($G14)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E14+$K14)/($F14+$K14))+$H14^2*$G14/2)/($H14*SQRT($G14)),TRUE))*IF($J14,1,-1)</f>
-        <v>-0.2693952177105327</v>
+        <v>-0.37901134582780294</v>
       </c>
       <c r="M14" s="125" cm="1">
         <f t="array" ref="M14">SACCR_OptionDelta($E14,$F14,$G14,$H14,$I14,$J14)</f>
-        <v>-0.2693952177105327</v>
-      </c>
-      <c r="N14" s="126">
-        <f>IFERROR(ABS(M14-L14),"")</f>
+        <v>-0.37901134582780294</v>
+      </c>
+      <c r="N14" s="132">
+        <f>IFERROR(ABS(M14-L14)/MAX(1,ABS(L14)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O14" s="127" t="str">
-        <f>IF(ISNUMBER(N14),IF(N14&lt;=FormulaTest_Tolerance*MAX(1,ABS(L14)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N14),IF(N14&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P14" s="130" t="s">
@@ -7334,241 +7382,229 @@
     </row>
     <row r="15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="128" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="E15" s="129">
-        <v>100</v>
+        <v>-0.002</v>
       </c>
       <c r="F15" s="129">
-        <v>110</v>
+        <v>0.001</v>
       </c>
       <c r="G15" s="129">
+        <v>2</v>
+      </c>
+      <c r="H15" s="129">
         <v>0.5</v>
-      </c>
-      <c r="H15" s="129">
-        <v>0.32</v>
       </c>
       <c r="I15" s="129" t="b">
         <v>1</v>
       </c>
       <c r="J15" s="129" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K15" s="129">
+        <v>0.01</v>
       </c>
       <c r="L15" s="125">
         <f>IF($I15,_xlfn.NORM.S.DIST((LN(($E15+$K15)/($F15+$K15))+$H15^2*$G15/2)/($H15*SQRT($G15)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E15+$K15)/($F15+$K15))+$H15^2*$G15/2)/($H15*SQRT($G15)),TRUE))*IF($J15,1,-1)</f>
-        <v>-0.37901134582780294</v>
+        <v>0.46143935794124913</v>
       </c>
       <c r="M15" s="125" cm="1">
-        <f t="array" ref="M15">SACCR_OptionDelta($E15,$F15,$G15,$H15,$I15,$J15)</f>
-        <v>-0.37901134582780294</v>
-      </c>
-      <c r="N15" s="126">
-        <f>IFERROR(ABS(M15-L15),"")</f>
+        <f t="array" ref="M15">SACCR_OptionDelta($E15,$F15,$G15,$H15,$I15,$J15,$K15)</f>
+        <v>0.46143935794124913</v>
+      </c>
+      <c r="N15" s="132">
+        <f>IFERROR(ABS(M15-L15)/MAX(1,ABS(L15)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O15" s="127" t="str">
-        <f>IF(ISNUMBER(N15),IF(N15&lt;=FormulaTest_Tolerance*MAX(1,ABS(L15)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N15),IF(N15&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P15" s="130" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="128" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="E16" s="129">
-        <v>-0.002</v>
+        <v>0.03</v>
       </c>
       <c r="F16" s="129">
-        <v>0.001</v>
-      </c>
-      <c r="G16" s="129">
-        <v>2</v>
-      </c>
-      <c r="H16" s="129">
-        <v>0.5</v>
-      </c>
-      <c r="I16" s="129" t="b">
+        <v>0.06</v>
+      </c>
+      <c r="G16" s="129" t="b">
         <v>1</v>
       </c>
-      <c r="J16" s="129" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16" s="129">
-        <v>0.01</v>
-      </c>
       <c r="L16" s="125">
-        <f>IF($I16,_xlfn.NORM.S.DIST((LN(($E16+$K16)/($F16+$K16))+$H16^2*$G16/2)/($H16*SQRT($G16)),TRUE),-_xlfn.NORM.S.DIST(-(LN(($E16+$K16)/($F16+$K16))+$H16^2*$G16/2)/($H16*SQRT($G16)),TRUE))*IF($J16,1,-1)</f>
-        <v>0.46143935794124913</v>
+        <f>15/((1+14*$E16)*(1+14*$F16))*IF($G16,1,-1)</f>
+        <v>5.740967544396817</v>
       </c>
       <c r="M16" s="125" cm="1">
-        <f t="array" ref="M16">SACCR_OptionDelta($E16,$F16,$G16,$H16,$I16,$J16,$K16)</f>
-        <v>0.46143935794124913</v>
-      </c>
-      <c r="N16" s="126">
-        <f>IFERROR(ABS(M16-L16),"")</f>
-        <v>0.0</v>
+        <f t="array" ref="M16">SACCR_CDODelta($E16,$F16,$G16)</f>
+        <v>5.740967544396816</v>
+      </c>
+      <c r="N16" s="132">
+        <f>IFERROR(ABS(M16-L16)/MAX(1,ABS(L16)),"")</f>
+        <v>1.5470883833283245e-16</v>
       </c>
       <c r="O16" s="127" t="str">
-        <f>IF(ISNUMBER(N16),IF(N16&lt;=FormulaTest_Tolerance*MAX(1,ABS(L16)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N16),IF(N16&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P16" s="130" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="128" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="E17" s="129">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F17" s="129">
-        <v>0.06</v>
-      </c>
-      <c r="G17" s="129" t="b">
-        <v>1</v>
+        <v>-36253.8493844036</v>
+      </c>
+      <c r="G17" s="129">
+        <v>78693.8680574733</v>
       </c>
       <c r="L17" s="125">
-        <f>15/((1+14*$E17)*(1+14*$F17))*IF($G17,1,-1)</f>
-        <v>5.740967544396817</v>
+        <f>SQRT(MAX($E17^2+$F17^2+$G17^2+1.4*$E17*$F17+1.4*$F17*$G17+0.6*$E17*$G17,0))</f>
+        <v>59269.963463710395</v>
       </c>
       <c r="M17" s="125" cm="1">
-        <f t="array" ref="M17">SACCR_CDODelta($E17,$F17,$G17)</f>
-        <v>5.740967544396816</v>
-      </c>
-      <c r="N17" s="126">
-        <f>IFERROR(ABS(M17-L17),"")</f>
-        <v>8.881784197001252e-16</v>
+        <f t="array" ref="M17">SACCR_IREffectiveNotional($E17,$F17,$G17)</f>
+        <v>59269.963463710395</v>
+      </c>
+      <c r="N17" s="132">
+        <f>IFERROR(ABS(M17-L17)/MAX(1,ABS(L17)),"")</f>
+        <v>0.0</v>
       </c>
       <c r="O17" s="127" t="str">
-        <f>IF(ISNUMBER(N17),IF(N17&lt;=FormulaTest_Tolerance*MAX(1,ABS(L17)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N17),IF(N17&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P17" s="130" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="128" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="E18" s="129">
-        <v>0</v>
+        <v>105.861937916956</v>
       </c>
       <c r="F18" s="129">
-        <v>-36253.8493844036</v>
+        <v>-279.916321663744</v>
       </c>
       <c r="G18" s="129">
-        <v>78693.8680574733</v>
+        <v>168.111404865732</v>
+      </c>
+      <c r="H18" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="129">
+        <v>0.5</v>
+      </c>
+      <c r="J18" s="129">
+        <v>0.8</v>
       </c>
       <c r="L18" s="125">
-        <f>SQRT(MAX($E18^2+$F18^2+$G18^2+1.4*$E18*$F18+1.4*$F18*$G18+0.6*$E18*$G18,0))</f>
-        <v>59269.963463710395</v>
+        <f>SQRT(SUMPRODUCT($E18:$G18,$H18:$J18)^2+SUMPRODUCT((1-$H18:$J18^2)*$E18:$G18^2))</f>
+        <v>282.12883185966604</v>
       </c>
       <c r="M18" s="125" cm="1">
-        <f t="array" ref="M18">SACCR_IREffectiveNotional($E18,$F18,$G18)</f>
-        <v>59269.963463710395</v>
-      </c>
-      <c r="N18" s="126">
-        <f>IFERROR(ABS(M18-L18),"")</f>
+        <f t="array" ref="M18">SACCR_FactorAggregation($E18:$G18,$H18:$J18)</f>
+        <v>282.12883185966604</v>
+      </c>
+      <c r="N18" s="132">
+        <f>IFERROR(ABS(M18-L18)/MAX(1,ABS(L18)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O18" s="127" t="str">
-        <f>IF(ISNUMBER(N18),IF(N18&lt;=FormulaTest_Tolerance*MAX(1,ABS(L18)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N18),IF(N18&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P18" s="130" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="128" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E19" s="129">
-        <v>105.861937916956</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="129">
-        <v>-279.916321663744</v>
-      </c>
-      <c r="G19" s="129">
-        <v>168.111404865732</v>
-      </c>
-      <c r="H19" s="129">
-        <v>0.5</v>
-      </c>
-      <c r="I19" s="129">
-        <v>0.5</v>
-      </c>
-      <c r="J19" s="129">
-        <v>0.8</v>
+        <v>282</v>
       </c>
       <c r="L19" s="125">
-        <f>SQRT(SUMPRODUCT($E19:$G19,$H19:$J19)^2+SUMPRODUCT((1-$H19:$J19^2)*$E19:$G19^2))</f>
-        <v>282.12883185966604</v>
+        <f>IF(OR($F19&lt;=0,$E19&gt;0),1,MIN(1,0.05+0.95*EXP($E19/(2*0.95*$F19))))</f>
+        <v>0.9651926811871945</v>
       </c>
       <c r="M19" s="125" cm="1">
-        <f t="array" ref="M19">SACCR_FactorAggregation($E19:$G19,$H19:$J19)</f>
-        <v>282.12883185966604</v>
-      </c>
-      <c r="N19" s="126">
-        <f>IFERROR(ABS(M19-L19),"")</f>
+        <f t="array" ref="M19">SACCR_Multiplier($E19,$F19)</f>
+        <v>0.9651926811871945</v>
+      </c>
+      <c r="N19" s="132">
+        <f>IFERROR(ABS(M19-L19)/MAX(1,ABS(L19)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O19" s="127" t="str">
-        <f>IF(ISNUMBER(N19),IF(N19&lt;=FormulaTest_Tolerance*MAX(1,ABS(L19)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N19),IF(N19&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P19" s="130" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="128" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D20" s="24" t="s">
         <v>876</v>
       </c>
       <c r="E20" s="129">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="F20" s="129">
         <v>282</v>
       </c>
       <c r="L20" s="125">
-        <f>IF($F20&lt;=0,1,MIN(1,0.05+0.95*EXP($E20/(2*0.95*$F20))))</f>
-        <v>0.9651926811871945</v>
+        <f>IF(OR($F20&lt;=0,$E20&gt;0),1,MIN(1,0.05+0.95*EXP($E20/(2*0.95*$F20))))</f>
+        <v>1</v>
       </c>
       <c r="M20" s="125" cm="1">
         <f t="array" ref="M20">SACCR_Multiplier($E20,$F20)</f>
-        <v>0.9651926811871945</v>
-      </c>
-      <c r="N20" s="126">
-        <f>IFERROR(ABS(M20-L20),"")</f>
+        <v>1.0</v>
+      </c>
+      <c r="N20" s="132">
+        <f>IFERROR(ABS(M20-L20)/MAX(1,ABS(L20)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O20" s="127" t="str">
-        <f>IF(ISNUMBER(N20),IF(N20&lt;=FormulaTest_Tolerance*MAX(1,ABS(L20)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N20),IF(N20&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P20" s="130" t="s">
@@ -7577,106 +7613,103 @@
     </row>
     <row r="21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="128" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="E21" s="129">
+        <v>5</v>
+      </c>
+      <c r="F21" s="129">
         <v>10</v>
       </c>
-      <c r="F21" s="129">
-        <v>282</v>
+      <c r="G21" s="129" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="129">
+        <v>0</v>
+      </c>
+      <c r="I21" s="129">
+        <v>10</v>
+      </c>
+      <c r="J21" s="129">
+        <v>2</v>
       </c>
       <c r="L21" s="125">
-        <f>IF($F21&lt;=0,1,MIN(1,0.05+0.95*EXP($E21/(2*0.95*$F21))))</f>
-        <v>1</v>
+        <f>IF($G21,MAX($E21-$F21,$H21+$I21-$J21,0),MAX($E21-$F21,0))</f>
+        <v>8</v>
       </c>
       <c r="M21" s="125" cm="1">
-        <f t="array" ref="M21">SACCR_Multiplier($E21,$F21)</f>
-        <v>1.0</v>
-      </c>
-      <c r="N21" s="126">
-        <f>IFERROR(ABS(M21-L21),"")</f>
+        <f t="array" ref="M21">SACCR_ReplacementCost($E21,$F21,$G21,$H21,$I21,$J21)</f>
+        <v>8.0</v>
+      </c>
+      <c r="N21" s="132">
+        <f>IFERROR(ABS(M21-L21)/MAX(1,ABS(L21)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O21" s="127" t="str">
-        <f>IF(ISNUMBER(N21),IF(N21&lt;=FormulaTest_Tolerance*MAX(1,ABS(L21)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N21),IF(N21&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P21" s="130" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="128" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E22" s="129">
-        <v>5</v>
-      </c>
-      <c r="F22" s="129">
-        <v>10</v>
-      </c>
-      <c r="G22" s="129" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" s="129">
-        <v>0</v>
-      </c>
-      <c r="I22" s="129">
-        <v>10</v>
-      </c>
-      <c r="J22" s="129">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="L22" s="125">
-        <f>IF($G22,MAX($E22-$F22,$H22+$I22-$J22,0),MAX($E22-$F22,0))</f>
-        <v>8</v>
+        <f>_xlfn.NORM.S.DIST($E22,TRUE)</f>
+        <v>0.9750021048517795</v>
       </c>
       <c r="M22" s="125" cm="1">
-        <f t="array" ref="M22">SACCR_ReplacementCost($E22,$F22,$G22,$H22,$I22,$J22)</f>
-        <v>8.0</v>
-      </c>
-      <c r="N22" s="126">
-        <f>IFERROR(ABS(M22-L22),"")</f>
+        <f t="array" ref="M22">SACCR_NormCDF($E22)</f>
+        <v>0.9750021048517795</v>
+      </c>
+      <c r="N22" s="132">
+        <f>IFERROR(ABS(M22-L22)/MAX(1,ABS(L22)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O22" s="127" t="str">
-        <f>IF(ISNUMBER(N22),IF(N22&lt;=FormulaTest_Tolerance*MAX(1,ABS(L22)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N22),IF(N22&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P22" s="130" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="128" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>880</v>
       </c>
       <c r="E23" s="129">
-        <v>1.96</v>
+        <v>-4</v>
       </c>
       <c r="L23" s="125">
         <f>_xlfn.NORM.S.DIST($E23,TRUE)</f>
-        <v>0.9750021048517795</v>
+        <v>3.1671241833119965e-05</v>
       </c>
       <c r="M23" s="125" cm="1">
         <f t="array" ref="M23">SACCR_NormCDF($E23)</f>
-        <v>0.9750021048517795</v>
-      </c>
-      <c r="N23" s="126">
-        <f>IFERROR(ABS(M23-L23),"")</f>
-        <v>0.0</v>
+        <v>3.167124183311601e-05</v>
+      </c>
+      <c r="N23" s="132">
+        <f>IFERROR(ABS(M23-L23)/MAX(1,ABS(L23)),"")</f>
+        <v>3.957337929572091e-18</v>
       </c>
       <c r="O23" s="127" t="str">
-        <f>IF(ISNUMBER(N23),IF(N23&lt;=FormulaTest_Tolerance*MAX(1,ABS(L23)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N23),IF(N23&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P23" s="130" t="s">
@@ -7685,64 +7718,70 @@
     </row>
     <row r="24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="128" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="E24" s="129">
-        <v>-8</v>
+        <v>-0.002</v>
+      </c>
+      <c r="F24" s="129">
+        <v>0.001</v>
+      </c>
+      <c r="G24" s="129" t="b">
+        <v>1</v>
       </c>
       <c r="L24" s="125">
-        <f>_xlfn.NORM.S.DIST($E24,TRUE)</f>
-        <v>6.220960574271819e-16</v>
+        <f>IF($G24,MAX(0.001-MIN($E24,$F24),0),MAX(-(1+0.1)*MIN($E24,$F24),0))</f>
+        <v>0.003</v>
       </c>
       <c r="M24" s="125" cm="1">
-        <f t="array" ref="M24">SACCR_NormCDF($E24)</f>
-        <v>6.220960520142784e-16</v>
-      </c>
-      <c r="N24" s="126">
-        <f>IFERROR(ABS(M24-L24),"")</f>
-        <v>5.4129035033506995e-24</v>
+        <f t="array" ref="M24">SACCR_LambdaCRR($E24,$F24,$G24)</f>
+        <v>0.003</v>
+      </c>
+      <c r="N24" s="132">
+        <f>IFERROR(ABS(M24-L24)/MAX(1,ABS(L24)),"")</f>
+        <v>0.0</v>
       </c>
       <c r="O24" s="127" t="str">
-        <f>IF(ISNUMBER(N24),IF(N24&lt;=FormulaTest_Tolerance*MAX(1,ABS(L24)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N24),IF(N24&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P24" s="130" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="128" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D25" s="24" t="s">
         <v>882</v>
       </c>
       <c r="E25" s="129">
-        <v>-0.002</v>
+        <v>0.02</v>
       </c>
       <c r="F25" s="129">
-        <v>0.001</v>
+        <v>0.03</v>
       </c>
       <c r="G25" s="129" t="b">
         <v>1</v>
       </c>
       <c r="L25" s="125">
         <f>IF($G25,MAX(0.001-MIN($E25,$F25),0),MAX(-(1+0.1)*MIN($E25,$F25),0))</f>
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="M25" s="125" cm="1">
         <f t="array" ref="M25">SACCR_LambdaCRR($E25,$F25,$G25)</f>
-        <v>0.003</v>
-      </c>
-      <c r="N25" s="126">
-        <f>IFERROR(ABS(M25-L25),"")</f>
         <v>0.0</v>
       </c>
+      <c r="N25" s="132">
+        <f>IFERROR(ABS(M25-L25)/MAX(1,ABS(L25)),"")</f>
+        <v>0.0</v>
+      </c>
       <c r="O25" s="127" t="str">
-        <f>IF(ISNUMBER(N25),IF(N25&lt;=FormulaTest_Tolerance*MAX(1,ABS(L25)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N25),IF(N25&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P25" s="130" t="s">
@@ -7751,34 +7790,34 @@
     </row>
     <row r="26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="128" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D26" s="24" t="s">
         <v>882</v>
       </c>
       <c r="E26" s="129">
-        <v>0.02</v>
+        <v>0.0005</v>
       </c>
       <c r="F26" s="129">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G26" s="129" t="b">
         <v>1</v>
       </c>
       <c r="L26" s="125">
         <f>IF($G26,MAX(0.001-MIN($E26,$F26),0),MAX(-(1+0.1)*MIN($E26,$F26),0))</f>
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="M26" s="125" cm="1">
         <f t="array" ref="M26">SACCR_LambdaCRR($E26,$F26,$G26)</f>
+        <v>0.0005</v>
+      </c>
+      <c r="N26" s="132">
+        <f>IFERROR(ABS(M26-L26)/MAX(1,ABS(L26)),"")</f>
         <v>0.0</v>
       </c>
-      <c r="N26" s="126">
-        <f>IFERROR(ABS(M26-L26),"")</f>
-        <v>0.0</v>
-      </c>
       <c r="O26" s="127" t="str">
-        <f>IF(ISNUMBER(N26),IF(N26&lt;=FormulaTest_Tolerance*MAX(1,ABS(L26)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N26),IF(N26&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P26" s="130" t="s">
@@ -7787,34 +7826,34 @@
     </row>
     <row r="27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="128" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D27" s="24" t="s">
         <v>882</v>
       </c>
       <c r="E27" s="129">
-        <v>0.0005</v>
+        <v>-5</v>
       </c>
       <c r="F27" s="129">
-        <v>0.01</v>
+        <v>-4</v>
       </c>
       <c r="G27" s="129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="125">
         <f>IF($G27,MAX(0.001-MIN($E27,$F27),0),MAX(-(1+0.1)*MIN($E27,$F27),0))</f>
-        <v>0.0005</v>
+        <v>5.5</v>
       </c>
       <c r="M27" s="125" cm="1">
         <f t="array" ref="M27">SACCR_LambdaCRR($E27,$F27,$G27)</f>
-        <v>0.0005</v>
-      </c>
-      <c r="N27" s="126">
-        <f>IFERROR(ABS(M27-L27),"")</f>
+        <v>5.5</v>
+      </c>
+      <c r="N27" s="132">
+        <f>IFERROR(ABS(M27-L27)/MAX(1,ABS(L27)),"")</f>
         <v>0.0</v>
       </c>
       <c r="O27" s="127" t="str">
-        <f>IF(ISNUMBER(N27),IF(N27&lt;=FormulaTest_Tolerance*MAX(1,ABS(L27)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N27),IF(N27&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P27" s="130" t="s">
@@ -7823,175 +7862,139 @@
     </row>
     <row r="28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="128" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D28" s="24" t="s">
         <v>882</v>
       </c>
       <c r="E28" s="129">
-        <v>-5</v>
+        <v>40</v>
       </c>
       <c r="F28" s="129">
-        <v>-4</v>
+        <v>35</v>
       </c>
       <c r="G28" s="129" t="b">
         <v>0</v>
       </c>
       <c r="L28" s="125">
         <f>IF($G28,MAX(0.001-MIN($E28,$F28),0),MAX(-(1+0.1)*MIN($E28,$F28),0))</f>
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M28" s="125" cm="1">
         <f t="array" ref="M28">SACCR_LambdaCRR($E28,$F28,$G28)</f>
-        <v>5.5</v>
-      </c>
-      <c r="N28" s="126">
-        <f>IFERROR(ABS(M28-L28),"")</f>
         <v>0.0</v>
       </c>
+      <c r="N28" s="132">
+        <f>IFERROR(ABS(M28-L28)/MAX(1,ABS(L28)),"")</f>
+        <v>0.0</v>
+      </c>
       <c r="O28" s="127" t="str">
-        <f>IF(ISNUMBER(N28),IF(N28&lt;=FormulaTest_Tolerance*MAX(1,ABS(L28)),"PASS","FAIL"),"FAIL")</f>
+        <f>IF(ISNUMBER(N28),IF(N28&lt;=FormulaTest_Tolerance,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="P28" s="130" t="s">
         <v>883</v>
       </c>
     </row>
-    <row r="29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="128" t="s">
-        <v>558</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>882</v>
-      </c>
-      <c r="E29" s="129">
-        <v>40</v>
-      </c>
-      <c r="F29" s="129">
-        <v>35</v>
-      </c>
-      <c r="G29" s="129" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" s="125">
-        <f>IF($G29,MAX(0.001-MIN($E29,$F29),0),MAX(-(1+0.1)*MIN($E29,$F29),0))</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="125" cm="1">
-        <f t="array" ref="M29">SACCR_LambdaCRR($E29,$F29,$G29)</f>
-        <v>0.0</v>
-      </c>
-      <c r="N29" s="126">
-        <f>IFERROR(ABS(M29-L29),"")</f>
-        <v>0.0</v>
-      </c>
-      <c r="O29" s="127" t="str">
-        <f>IF(ISNUMBER(N29),IF(N29&lt;=FormulaTest_Tolerance*MAX(1,ABS(L29)),"PASS","FAIL"),"FAIL")</f>
-        <v>PASS</v>
-      </c>
-      <c r="P29" s="130" t="s">
-        <v>883</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="31">
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test, applied to max(1, |Expected|). Default 0.001%. Below about 0.00000000000001% (1e-16, double precision) only an exact match passes." sqref="D5">
-      <formula1>AND(ISNUMBER(D5),D5&gt;0,D5&lt;=0.01)</formula1>
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a percentage above 0% and at most 1%." promptTitle="Tolerance" prompt="Relative tolerance of every unit test: a row passes when its Rel. diff, |Function - Expected| / max(1, |Expected|), is at most this value. Default 0.001%. Below about 1e-16 (double precision) only an exact match passes." sqref="E4">
+      <formula1>AND(ISNUMBER(E4),E4&gt;0,E4&lt;=0.01)</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid start date" error="Enter a number of years from -50 to 50." promptTitle="Start date S (years)" prompt="Years from today to the start of the period referenced. Zero or negative means already started and is floored at 0 (CRE52.34; CRR Art. 279b(1)(a))." sqref="E8:E10">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid start date" error="Enter a number of years from -50 to 50." promptTitle="Start date S (years)" prompt="Years from today to the start of the period referenced. Zero or negative means already started and is floored at 0 (CRE52.34; CRR Art. 279b(1)(a))." sqref="E7:E9">
       <formula1>-50</formula1>
       <formula2>50</formula2>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid end date" error="Enter a number of years after the start date and after 0, at most 50." promptTitle="End date E (years)" prompt="Years from today to the end of the period referenced: after the start date and after today, at most 50 (CRE52.34)." sqref="F8:F10">
-      <formula1>AND(ISNUMBER(F8),F8&gt;MAX(E8,0),F8&lt;=50)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid end date" error="Enter a number of years after the start date and after 0, at most 50." promptTitle="End date E (years)" prompt="Years from today to the end of the period referenced: after the start date and after today, at most 50 (CRE52.34)." sqref="F7:F9">
+      <formula1>AND(ISNUMBER(F7),F7&gt;MAX(E7,0),F7&lt;=50)</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid floor" error="Enter a number of years from 0 to 1." promptTitle="SD floor (years)" prompt="Floor on the supervisory duration, in years: 10 business days = 10/250 (CRE52.34)." sqref="G10">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid floor" error="Enter a number of years from 0 to 1." promptTitle="SD floor (years)" prompt="Floor on the supervisory duration, in years: 10 business days = 10/250 (CRE52.34)." sqref="G9">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid maturity" error="Enter a number of years from 0 to 50." promptTitle="Maturity M (years)" prompt="Remaining maturity in years. The unmargined factor floors it at 10 business days and caps it at 1 year (CRE52.48; CRR Art. 279c(1)(a))." sqref="E11:E13">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid maturity" error="Enter a number of years from 0 to 50." promptTitle="Maturity M (years)" prompt="Remaining maturity in years. The unmargined factor floors it at 10 business days and caps it at 1 year (CRE52.48; CRR Art. 279c(1)(a))." sqref="E10:E12">
       <formula1>0</formula1>
       <formula2>50</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Margined" prompt="TRUE = margined factor 1.5 x sqrt(MPOR / 250) (CRE52.52; CRR Art. 279c(1)(b)). FALSE = unmargined factor from M." sqref="F13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Margined" prompt="TRUE = margined factor 1.5 x sqrt(MPOR / 250) (CRE52.52; CRR Art. 279c(1)(b)). FALSE = unmargined factor from M." sqref="F12">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid MPOR" error="Enter a whole number of business days from 1 to 250." promptTitle="MPOR (business days)" prompt="Margin period of risk in business days, used when margined (CRE52.50-52; CRR Art. 285)." sqref="G13">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid MPOR" error="Enter a whole number of business days from 1 to 250." promptTitle="MPOR (business days)" prompt="Margin period of risk in business days, used when margined (CRE52.50-52; CRR Art. 285)." sqref="G12">
       <formula1>1</formula1>
       <formula2>250</formula2>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid price" error="Enter a number; P plus lambda (Input 7) must be above 0." promptTitle="Price P" prompt="Price of the underlying (forward rate for IR options). P plus lambda (Input 7) must be above 0 (CRE52.40)." sqref="E14:E16">
-      <formula1>AND(ISNUMBER(E14),E14+$K14&gt;0)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid price" error="Enter a number; P plus lambda (Input 7) must be above 0." promptTitle="Price P" prompt="Price of the underlying (forward rate for IR options). P plus lambda (Input 7) must be above 0 (CRE52.40)." sqref="E13:E15">
+      <formula1>AND(ISNUMBER(E13),E13+$K13&gt;0)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid strike" error="Enter a number; K plus lambda (Input 7) must be above 0." promptTitle="Strike K" prompt="Strike of the option. K plus lambda (Input 7) must be above 0 (CRE52.40)." sqref="F14:F16">
-      <formula1>AND(ISNUMBER(F14),F14+$K14&gt;0)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid strike" error="Enter a number; K plus lambda (Input 7) must be above 0." promptTitle="Strike K" prompt="Strike of the option. K plus lambda (Input 7) must be above 0 (CRE52.40)." sqref="F13:F15">
+      <formula1>AND(ISNUMBER(F13),F13+$K13&gt;0)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid expiry" error="Enter a number of years above 0, at most 100." promptTitle="Expiry T (years)" prompt="Latest contractual exercise date, in years from today, above 0 (CRE52.40; CRR Art. 279a(1)(a))." sqref="G14:G16">
-      <formula1>AND(ISNUMBER(G14),G14&gt;0,G14&lt;=100)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid expiry" error="Enter a number of years above 0, at most 100." promptTitle="Expiry T (years)" prompt="Latest contractual exercise date, in years from today, above 0 (CRE52.40; CRR Art. 279a(1)(a))." sqref="G13:G15">
+      <formula1>AND(ISNUMBER(G13),G13&gt;0,G13&lt;=100)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid volatility" error="Enter a decimal above 0, at most 5." promptTitle="Supervisory volatility" prompt="Supervisory option volatility as a decimal (0.5 = 50%), above 0 and at most 5 (CRE52.72; CRR Art. 279a)." sqref="H14:H16">
-      <formula1>AND(ISNUMBER(H14),H14&gt;0,H14&lt;=5)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid volatility" error="Enter a decimal above 0, at most 5." promptTitle="Supervisory volatility" prompt="Supervisory option volatility as a decimal (0.5 = 50%), above 0 and at most 5 (CRE52.72; CRR Art. 279a)." sqref="H13:H15">
+      <formula1>AND(ISNUMBER(H13),H13&gt;0,H13&lt;=5)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Call" prompt="TRUE = call option; FALSE = put option (CRE52.40)." sqref="I14:I16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Call" prompt="TRUE = call option; FALSE = put option (CRE52.40)." sqref="I13:I15">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Bought" prompt="TRUE = bought option (long); FALSE = sold option (short) (CRE52.40)." sqref="J14:J16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Bought" prompt="TRUE = bought option (long); FALSE = sold option (short) (CRE52.40)." sqref="J13:J15">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Lambda shift" prompt="Shift added to P and K so that both are above 0 (CRE52.40 FAQ; CRR-RTS Art. 5). 0 or more." sqref="K16">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Lambda shift" prompt="Shift added to P and K so that both are above 0 (CRE52.40 FAQ; CRR-RTS Art. 5). 0 or more." sqref="K15">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid attachment" error="Enter a decimal from 0 to below 1, e.g. 0.03 for 3%." promptTitle="Attachment A" prompt="Attachment point of the tranche, from 0 to below 1 (CRE52.41)." sqref="E17">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid attachment" error="Enter a decimal from 0 to below 1, e.g. 0.03 for 3%." promptTitle="Attachment A" prompt="Attachment point of the tranche, from 0 to below 1 (CRE52.41)." sqref="E16">
       <formula1>0</formula1>
       <formula2>0.9999</formula2>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid detachment" error="Enter a decimal above the attachment point and at most 1." promptTitle="Detachment D" prompt="Detachment point, above the attachment and at most 1 (CRE52.41)." sqref="F17">
-      <formula1>AND(ISNUMBER(F17),F17&gt;E17,F17&lt;=1)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid detachment" error="Enter a decimal above the attachment point and at most 1." promptTitle="Detachment D" prompt="Detachment point, above the attachment and at most 1 (CRE52.41)." sqref="F16">
+      <formula1>AND(ISNUMBER(F16),F16&gt;E16,F16&lt;=1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Long" prompt="TRUE = long in the tranche (positive delta); FALSE = short (CRE52.41)." sqref="G17">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Long" prompt="TRUE = long in the tranche (positive delta); FALSE = short (CRE52.41)." sqref="G16">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Bucket effective notional" prompt="Signed effective notional D of maturity bucket 1, 2 or 3 (under 1 year, 1 to 5 years, over 5 years) (CRE52.57)." sqref="E18:G18">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Bucket effective notional" prompt="Signed effective notional D of maturity bucket 1, 2 or 3 (under 1 year, 1 to 5 years, over 5 years) (CRE52.57)." sqref="E17:G17">
+      <formula1>ISNUMBER(E17)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Entity add-on" prompt="Add-on of entity or commodity type k, signed by direction (CRE52.61; CRR Art. 280c)." sqref="E18:G18">
       <formula1>ISNUMBER(E18)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Entity add-on" prompt="Add-on of entity or commodity type k, signed by direction (CRE52.61; CRR Art. 280c)." sqref="E19:G19">
-      <formula1>ISNUMBER(E19)</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid correlation" error="Enter a decimal from 0 to 1." promptTitle="Correlation" prompt="Correlation of entity k, as a decimal from 0 to 1: credit 0.5 single name, 0.8 index (CRE52.61)." sqref="H19:J19">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid correlation" error="Enter a decimal from 0 to 1." promptTitle="Correlation" prompt="Correlation of entity k, as a decimal from 0 to 1: credit 0.5 single name, 0.8 index (CRE52.61)." sqref="H18:J18">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="V - C" prompt="Net market value of the netting set less collateral, signed (CRE52.23; CRR Art. 278(3))." sqref="E20:E21">
-      <formula1>ISNUMBER(E20)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="V - C" prompt="Net market value of the netting set less collateral, signed (CRE52.23; CRR Art. 278(3))." sqref="E19:E20">
+      <formula1>ISNUMBER(E19)</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Aggregate add-on" prompt="Aggregate add-on of the netting set, 0 or more; 0 gives a multiplier of 1 (CRE52.23)." sqref="F20:F21">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Aggregate add-on" prompt="Aggregate add-on of the netting set, 0 or more; 0 gives a multiplier of 1 (CRE52.23)." sqref="F19:F20">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="V" prompt="Net market value of the trades in the netting set, signed (CRE52.10; CRR Art. 275)." sqref="E22">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="V" prompt="Net market value of the trades in the netting set, signed (CRE52.10; CRR Art. 275)." sqref="E21">
+      <formula1>ISNUMBER(E21)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="C" prompt="Net collateral held after haircuts; negative if posted (CRE52.10; CRR Art. 275)." sqref="F21">
+      <formula1>ISNUMBER(F21)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Margined" prompt="TRUE = margined RC max(V - C, TH + MTA - NICA, 0) (CRE52.18); FALSE = max(V - C, 0) (CRE52.10)." sqref="G21">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Threshold TH" prompt="Threshold of the margin agreement, 0 or more (CRE52.18; CRR Art. 275(2))." sqref="H21">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Minimum transfer amount" prompt="Minimum transfer amount MTA, 0 or more (CRE52.18; CRR Art. 275(2))." sqref="I21">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="NICA" prompt="Net independent collateral amount, signed; negative if posted (CRE52.13; CRR Art. 275(2))." sqref="J21">
+      <formula1>ISNUMBER(J21)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="x" prompt="Point at which the standard normal distribution function is evaluated." sqref="E22:E23">
       <formula1>ISNUMBER(E22)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="C" prompt="Net collateral held after haircuts; negative if posted (CRE52.10; CRR Art. 275)." sqref="F22">
-      <formula1>ISNUMBER(F22)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Price or strike" prompt="Price P (Input 1) or strike K (Input 2) of the option; negative values allowed (CRR-RTS Art. 5(2))." sqref="E24:F28">
+      <formula1>ISNUMBER(E24)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Margined" prompt="TRUE = margined RC max(V - C, TH + MTA - NICA, 0) (CRE52.18); FALSE = max(V - C, 0) (CRE52.10)." sqref="G22">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Threshold TH" prompt="Threshold of the margin agreement, 0 or more (CRE52.18; CRR Art. 275(2))." sqref="H22">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Enter a number of 0 or more." promptTitle="Minimum transfer amount" prompt="Minimum transfer amount MTA, 0 or more (CRE52.18; CRR Art. 275(2))." sqref="I22">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="NICA" prompt="Net independent collateral amount, signed; negative if posted (CRE52.13; CRR Art. 275(2))." sqref="J22">
-      <formula1>ISNUMBER(J22)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="x" prompt="Point at which the standard normal distribution function is evaluated." sqref="E23:E24">
-      <formula1>ISNUMBER(E23)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid number" error="Enter a number." promptTitle="Price or strike" prompt="Price P (Input 1) or strike K (Input 2) of the option; negative values allowed (CRR-RTS Art. 5(2))." sqref="E25:F29">
-      <formula1>ISNUMBER(E25)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Interest rate" prompt="TRUE = interest-rate option (threshold 0.10%); FALSE = commodity option (threshold 0.1) (CRR-RTS Art. 5(2))." sqref="G25:G29">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose TRUE or FALSE." promptTitle="Interest rate" prompt="TRUE = interest-rate option (threshold 0.10%); FALSE = commodity option (threshold 0.1) (CRR-RTS Art. 5(2))." sqref="G24:G28">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -12759,8 +12759,8 @@
       <formula1>36526</formula1>
       <formula2>73415</formula2>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid currency" error="Enter a three-letter ISO currency code, e.g. EUR." promptTitle="Reporting currency" prompt="ISO code, e.g. EUR. Every amount is converted into it with the FX table below." sqref="E7" xr:uid="{00000000-0002-0000-0100-000001000000}">
-      <formula1>AND(ISTEXT(ReportingCcy),LEN(ReportingCcy)=3)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid currency" error="Enter three letters A to Z, e.g. EUR." promptTitle="Reporting currency" prompt="Three-letter currency code, e.g. EUR: letters A to Z only; case and surrounding spaces are ignored. The format is checked, not ISO membership. Every amount is converted into it with the FX table below." sqref="E7" xr:uid="{00000000-0002-0000-0100-000001000000}">
+      <formula1>AND(ISTEXT(ReportingCcy),LEN(TRIM(ReportingCcy))=3,ABS(CODE(MID(UPPER(TRIM(ReportingCcy)),1,1))-77.5)&lt;13,ABS(CODE(MID(UPPER(TRIM(ReportingCcy)),2,1))-77.5)&lt;13,ABS(CODE(MID(UPPER(TRIM(ReportingCcy)),3,1))-77.5)&lt;13)</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid alpha" error="Alpha must be a number greater than zero. Regulatory value: 1.4." promptTitle="Alpha" prompt="Multiplier on RC + PFE. Regulatory value 1.4 (CRE52.1, CRR Art. 274(2))." sqref="E8" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>0</formula1>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -48280,7 +48280,7 @@
     </row>
     <row r="5" spans="2:30" x14ac:dyDescent="0.25">
       <c r="C5" s="14" t="str" cm="1">
-        <f t="array" ref="C5">ResultsStatusText(SACCR_RunInputs,NettingSets!$C:$Q,Trades!$C:$AA,Params!$C:$J)</f>
+        <f t="array" ref="C5">ResultsStatusText(SACCR_RunInputs,NettingSets!$C:$Q,Trades!$C:$AA,Params!$1:$1048576)</f>
         <v>No results: press Run SA-CCR.</v>
       </c>
     </row>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -172,7 +172,7 @@
     <t>Dates</t>
   </si>
   <si>
-    <t>Start (S, IR/CR only, blank = already started), End (E, IR/CR, also defines the IR maturity bucket), Maturity (M, maturity factor; defaults to End, then Expiry), Option expiry (T, options). Year fractions = days / DaysPerYear.</t>
+    <t>Start (S, IR/CR only; blank = already started, except for IR/CR options, which need the start of the underlying: a swaption's exercise date, the earliest one if Bermudan, or a cap's or floor's first period; CRE52.31, CRE52.42), End (E, IR/CR, also defines the IR maturity bucket), Maturity (M, maturity factor; defaults to End, then Expiry), Option expiry (T, options). Year fractions = days / DaysPerYear.</t>
   </si>
   <si>
     <t>Nature</t>
@@ -48027,7 +48027,7 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid MtM" error="Enter a number (0 if the trade has no value)." promptTitle="MtM" prompt="Mark-to-market value, signed: positive is an asset. Enter 0 if the trade has no value." sqref="O5:O5000" xr:uid="{00000000-0002-0000-0300-00000C000000}">
       <formula1>ISNUMBER(O5)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a date between 1950 and 2200." promptTitle="Start date (S)" prompt="IR and credit: start of the time period referenced; blank = already started (CRE52.31)." sqref="Q5:Q5000" xr:uid="{00000000-0002-0000-0300-00000E000000}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid date" error="Enter a date between 1950 and 2200." promptTitle="Start date (S)" prompt="IR and credit: start of the time period referenced; blank = already started (CRE52.31). Required for IR/credit options: a swaption's exercise date, the earliest if Bermudan." sqref="Q5:Q5000" xr:uid="{00000000-0002-0000-0300-00000E000000}">
       <formula1>AND(ISNUMBER(Q5),Q5&gt;=DATE(1950,1,1),Q5&lt;=DATE(2200,12,31))</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid end date" error="Enter a date between 1950 and 2200, after the start date." promptTitle="End date (E)" prompt="IR and credit: end of the time period referenced (CRE52.31)." sqref="R5:R5000" xr:uid="{00000000-0002-0000-0300-00000F000000}">

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -2497,7 +2497,7 @@
     <t>Collateral is an input after haircuts.</t>
   </si>
   <si>
-    <t>IR: currency (hedging set); inflation as the currency followed by -INFL, e.g. EUR-INFL, in its own hedging set [Art. 277(4)(a), 277a(1)]. FX: currency pair, e.g. EUR/USD (order is normalised and the sign adjusted). CR / EQ: reference entity or index name. CO: commodity type (trades with the same text are netted as one type). OT (CRR other risks): primary risk driver.</t>
+    <t>IR: currency (hedging set); inflation as the currency followed by -INFL, e.g. EUR-INFL, in its own hedging set [Art. 277(4)(a), 277a(1)]. FX: currency pair, e.g. EUR/USD (order is normalised and the sign adjusted); an FX option must be entered in market quote order, base first in EUR, GBP, AUD, NZD, USD, CAD, CHF, JPY (e.g. USD/JPY), with price and strike in that quote (CRE52.59 FAQ1). CR / EQ: reference entity or index name. CO: commodity type (trades with the same text are netted as one type). OT (CRR other risks): primary risk driver.</t>
   </si>
   <si>
     <t>Hedging set per currency; buckets &lt;1y, 1-5y, &gt;5y on E; EN = sqrt(D1^2+D2^2+D3^2+1.4D1D2+1.4D2D3+0.6D1D3); AddOn = 0.5% x EN [CRE52.57, Art. 280a]. BCBS only: IRBucketOffset = FALSE uses the sum of absolute bucket values [CRE52.57(5)]; a CRR netting set with IR trades is then INVALID.</t>
@@ -48003,7 +48003,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid asset class" error="Choose IR, FX, CR, EQ, CO or OT." promptTitle="Asset class" prompt="IR, FX, CR (credit), EQ (equity), CO (commodity) or OT (other risks, CRR only, Art. 280f)." sqref="E5:E5000" xr:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>"IR,FX,CR,EQ,CO,OT"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid reference" error="The reference must not contain | or #." promptTitle="Risk factor / reference" prompt="IR: currency (EUR). FX: pair (EUR/USD). CR, EQ: issuer or index. CO: commodity. Trades with the same reference are aggregated together." sqref="G5:G5000" xr:uid="{00000000-0002-0000-0300-000004000000}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid reference" error="The reference must not contain | or #." promptTitle="Risk factor / reference" prompt="IR: currency (EUR). FX: pair (EUR/USD); options in market order (USD/JPY, not JPY/USD). CR, EQ: issuer or index. CO: commodity. Same reference = aggregated together." sqref="G5:G5000" xr:uid="{00000000-0002-0000-0300-000004000000}">
       <formula1>AND(ISERROR(FIND("|",G5)),ISERROR(FIND("#",G5)))</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid instrument" error="Choose Linear, Option or CDO." promptTitle="Instrument" prompt="Linear, Option, or CDO (credit tranche: needs attachment and detachment)." sqref="H5:H5000" xr:uid="{00000000-0002-0000-0300-000005000000}">

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -2818,7 +2818,7 @@
     <numFmt numFmtId="171" formatCode="0.0E+00"/>
     <numFmt numFmtId="172" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2996,6 +2996,13 @@
       <b/>
       <sz val="9"/>
       <color rgb="FF375623"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF0563C1"/>
       <name val="Aptos"/>
       <family val="2"/>
     </font>
@@ -3227,7 +3234,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3626,6 +3633,9 @@
     </xf>
     <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4838,7 +4848,10 @@
       <c r="C23" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="37"/>
+      <c r="D23" s="133" t="str">
+        <f>HYPERLINK("https://github.com/danielep71/VBA-SACCR-Toolkit/blob/main/docs/assets/SACCR_EAD_reference.svg","One-page reference card: all formulas and parameters (opens on GitHub)")</f>
+        <v>One-page reference card: all formulas and parameters (opens on GitHub)</v>
+      </c>
     </row>
     <row r="24" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="25" t="s">

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -3057,7 +3057,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -3228,13 +3228,133 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3636,6 +3756,30 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4683,7 +4827,7 @@
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
     <col min="4" max="4" width="126.875" customWidth="1"/>
     <col min="5" max="5" width="4.75" customWidth="1"/>
     <col min="6" max="24" width="0" hidden="1" customWidth="1"/>
@@ -4719,58 +4863,58 @@
       <c r="D5" s="3"/>
     </row>
     <row r="6" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="134" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="138" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="139" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="139" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="139" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="139" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="135" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="139" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="140" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4785,58 +4929,58 @@
       <c r="D14" s="37"/>
     </row>
     <row r="15" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="138" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="135" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="D16" s="139" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="3:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="D17" s="139" t="s">
         <v>801</v>
       </c>
     </row>
     <row r="18" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="34" t="s">
+      <c r="D18" s="139" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="139" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="20" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="135" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="139" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="21" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="136" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="140" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4854,90 +4998,90 @@
       </c>
     </row>
     <row r="24" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="34" t="s">
+      <c r="D24" s="138" t="s">
         <v>815</v>
       </c>
     </row>
     <row r="25" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="135" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="34" t="s">
+      <c r="D25" s="139" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="26" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="135" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="34" t="s">
+      <c r="D26" s="139" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="27" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="135" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="34" t="s">
+      <c r="D27" s="139" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="28" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="135" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="34" t="s">
+      <c r="D28" s="139" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="29" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="34" t="s">
+      <c r="D29" s="139" t="s">
         <v>816</v>
       </c>
     </row>
     <row r="30" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="25" t="s">
+      <c r="C30" s="135" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="34" t="s">
+      <c r="D30" s="139" t="s">
         <v>802</v>
       </c>
     </row>
     <row r="31" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="135" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="34" t="s">
+      <c r="D31" s="139" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="32" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="25" t="s">
+      <c r="C32" s="135" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="34" t="s">
+      <c r="D32" s="139" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="33" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="135" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="34" t="s">
+      <c r="D33" s="139" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="34" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="34" t="s">
+      <c r="D34" s="140" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4952,90 +5096,90 @@
       <c r="D36" s="37"/>
     </row>
     <row r="37" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="25" t="s">
+      <c r="C37" s="134" t="s">
         <v>52</v>
       </c>
-      <c r="D37" s="34" t="s">
+      <c r="D37" s="138" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="38" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="135" t="s">
         <v>54</v>
       </c>
-      <c r="D38" s="34" t="s">
+      <c r="D38" s="139" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="39" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="25" t="s">
+      <c r="C39" s="135" t="s">
         <v>56</v>
       </c>
-      <c r="D39" s="34" t="s">
+      <c r="D39" s="139" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="40" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="25" t="s">
+      <c r="C40" s="135" t="s">
         <v>58</v>
       </c>
-      <c r="D40" s="34" t="s">
+      <c r="D40" s="139" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="41" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="135" t="s">
         <v>60</v>
       </c>
-      <c r="D41" s="34" t="s">
+      <c r="D41" s="139" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="42" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="135" t="s">
         <v>62</v>
       </c>
-      <c r="D42" s="34" t="s">
+      <c r="D42" s="139" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="43" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="25" t="s">
+      <c r="C43" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="D43" s="34" t="s">
+      <c r="D43" s="139" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="44" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="25" t="s">
+      <c r="C44" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="D44" s="34" t="s">
+      <c r="D44" s="139" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="45" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="34" t="s">
+      <c r="D45" s="139" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="46" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="135" t="s">
         <v>896</v>
       </c>
-      <c r="D46" s="34" t="s">
+      <c r="D46" s="139" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="47" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="136" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="34" t="s">
+      <c r="D47" s="140" t="s">
         <v>73</v>
       </c>
     </row>
@@ -5050,82 +5194,82 @@
       <c r="D49" s="37"/>
     </row>
     <row r="50" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="25" t="s">
+      <c r="C50" s="134" t="s">
         <v>75</v>
       </c>
-      <c r="D50" s="34" t="s">
+      <c r="D50" s="138" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="51" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="25" t="s">
+      <c r="C51" s="135" t="s">
         <v>77</v>
       </c>
-      <c r="D51" s="34" t="s">
+      <c r="D51" s="139" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="52" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="25" t="s">
+      <c r="C52" s="135" t="s">
         <v>78</v>
       </c>
-      <c r="D52" s="34" t="s">
+      <c r="D52" s="139" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="53" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="25" t="s">
+      <c r="C53" s="135" t="s">
         <v>80</v>
       </c>
-      <c r="D53" s="34" t="s">
+      <c r="D53" s="139" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="54" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="135" t="s">
         <v>82</v>
       </c>
-      <c r="D54" s="34" t="s">
+      <c r="D54" s="139" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="55" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="25" t="s">
+      <c r="C55" s="135" t="s">
         <v>84</v>
       </c>
-      <c r="D55" s="34" t="s">
+      <c r="D55" s="139" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="56" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="25" t="s">
+      <c r="C56" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="D56" s="34" t="s">
+      <c r="D56" s="139" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="57" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="25" t="s">
+      <c r="C57" s="135" t="s">
         <v>88</v>
       </c>
-      <c r="D57" s="34" t="s">
+      <c r="D57" s="139" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="58" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="25" t="s">
+      <c r="C58" s="135" t="s">
         <v>90</v>
       </c>
-      <c r="D58" s="34" t="s">
+      <c r="D58" s="139" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="59" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C59" s="25" t="s">
+      <c r="C59" s="136" t="s">
         <v>92</v>
       </c>
-      <c r="D59" s="34" t="s">
+      <c r="D59" s="140" t="s">
         <v>93</v>
       </c>
     </row>
@@ -5140,50 +5284,50 @@
       <c r="D61" s="37"/>
     </row>
     <row r="62" spans="3:4" ht="36" x14ac:dyDescent="0.25">
-      <c r="C62" s="25" t="s">
+      <c r="C62" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="D62" s="34" t="s">
+      <c r="D62" s="138" t="s">
         <v>803</v>
       </c>
     </row>
     <row r="63" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="25" t="s">
+      <c r="C63" s="135" t="s">
         <v>805</v>
       </c>
-      <c r="D63" s="34" t="s">
+      <c r="D63" s="139" t="s">
         <v>804</v>
       </c>
     </row>
     <row r="64" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="25" t="s">
+      <c r="C64" s="135" t="s">
         <v>96</v>
       </c>
-      <c r="D64" s="34" t="s">
+      <c r="D64" s="139" t="s">
         <v>817</v>
       </c>
     </row>
     <row r="65" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="25" t="s">
+      <c r="C65" s="135" t="s">
         <v>97</v>
       </c>
-      <c r="D65" s="34" t="s">
+      <c r="D65" s="139" t="s">
         <v>838</v>
       </c>
     </row>
     <row r="66" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="25" t="s">
+      <c r="C66" s="135" t="s">
         <v>98</v>
       </c>
-      <c r="D66" s="34" t="s">
+      <c r="D66" s="139" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="67" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="25" t="s">
+      <c r="C67" s="136" t="s">
         <v>100</v>
       </c>
-      <c r="D67" s="34" t="s">
+      <c r="D67" s="140" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5198,10 +5342,10 @@
       <c r="D69" s="37"/>
     </row>
     <row r="70" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="25" t="s">
+      <c r="C70" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="D70" s="34" t="s">
+      <c r="D70" s="141" t="s">
         <v>104</v>
       </c>
     </row>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="916">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -2801,6 +2801,57 @@
   </si>
   <si>
     <t>Rel. diff</t>
+  </si>
+  <si>
+    <t>NettingSets: one row per netting set - margin flag, client-clearing role, MPOR drivers, collateral (net VM held (+) / posted (-), NICA), threshold, MTA, optional Alpha and Regime overrides, and the margin-agreement structure. Collateral is entered after haircuts, in reporting currency.</t>
+  </si>
+  <si>
+    <t>Trades: one row per derivative leg. Dropdowns guide the classification. Amounts can be in any currency of the FX table. Legs of one economic trade share an Economic trade ID; exactly one of them (MtM leg = Y) carries the MtM.</t>
+  </si>
+  <si>
+    <t>Click "Run SA-CCR" (macro RunSACCR). Results, HedgingSets, Buckets, TradeCalc and Checks are rebuilt. "Validate inputs" only runs the checks; "Clear outputs" empties the output sheets.</t>
+  </si>
+  <si>
+    <t>Positive amount; the sign comes from Direction. IR / CR: trade notional. FX: the notional of one leg, in that leg's currency (one of the pair): the foreign-currency leg or, when both legs are foreign, the larger one in reporting currency. EQ / CO: market price x units.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unmargined: max(V - C, 0), C = NICA, plus the posted VM under a BCBS one-way agreement [CRE52.10]   Margined: max(V - C, TH + MTA - NICA, 0), C = VM + NICA [CRE52.18]</t>
+  </si>
+  <si>
+    <t>Floor 10 BD bilateral; 5 BD (configurable) for client clearing: the clearing member in both regimes, the client under CRR only [CRE54.12; Art. 279c(1)]; 20 BD when the netting set is flagged large or illiquid (more than 5,000 trades in the previous quarter, illiquid collateral or a hard-to-replace derivative; a current count above 5,000 with the flag N only gives a warning) [CRE52.51; Art. 285(3)]; + (N - 1) for remargining every N days; the result doubled for disputes [CRE52.50-52.52; Art. 285]</t>
+  </si>
+  <si>
+    <t>Hedging set per currency (inflation in its own set per currency); buckets on E: CRR E &lt;= 1y, 1y &lt; E &lt;= 5y, E &gt; 5y [Art. 280a]; BCBS E &lt; 1y, 1-5y, &gt; 5y [CRE52.57]; EN = sqrt(D1^2+D2^2+D3^2+1.4D1D2+1.4D2D3+0.6D1D3); AddOn = 0.5% x EN. BCBS only: IRBucketOffset = FALSE uses the sum of absolute bucket values [CRE52.57(5)]; a CRR netting set with IR trades is then INVALID.</t>
+  </si>
+  <si>
+    <t>Other risks: per hedging set AddOn = 8% x |sum effective notional| [Art. 280f]. Under BCBS an OT trade is rejected and its netting set's EAD withheld.</t>
+  </si>
+  <si>
+    <t>Output - EAD per netting set, and TOTAL CRR / TOTAL BCBS rows over the VALID netting sets of each regime</t>
+  </si>
+  <si>
+    <t>SACCR_SupervisoryDuration(S, E, [FloorYears])</t>
+  </si>
+  <si>
+    <t>SACCR_MaturityFactor(M, [Margined], [MPOR_BD], [MinBD], [BDPerYear])</t>
+  </si>
+  <si>
+    <t>SACCR_IREffectiveNotional(D1, D2, D3, [Rho12], [Rho23], [Rho13])</t>
+  </si>
+  <si>
+    <t>SACCR_Multiplier(VminusC, AddOn, [FloorPct])</t>
+  </si>
+  <si>
+    <t>Simplified SA-CCR and OEM (CRR Art. 281-282), CCP exposures, SFTs, CVA and RWA; collateral haircuts (enter C after haircuts); several margin agreements in one netting set, or one agreement over several netting sets; automatic risk-driver mapping (RTS 2021/931); digital options (option legs are calculated as an ordinary option combination, without the CRR collar or the BCBS cap). The optional reductions for sold options and sold credit protection (Art. 274(5), (7)) are not applied, which gives a higher EAD.</t>
+  </si>
+  <si>
+    <t>The cap recalculates a margined netting set as unmargined: unmargined maturity factors and C = NICA in both regimes (Results columns Z-AC).</t>
+  </si>
+  <si>
+    <t>Illustrative counterparties (NS-ALPHA, NS-GAMMA) and FX rates. BCBS-EX1..5 reproduce CRE99 / BCBS 279 Annex 4 (amounts in thousands); the other CRR-* and BCBS-* netting sets feed the TestCatalogue; DEMO-REJECTED shows how rejected trades withhold a netting set's EAD.</t>
+  </si>
+  <si>
+    <t>M_Main (macros), CORE_Engine (calculation), SACCR_Formulas (public SACCR_* functions), CORE_Config (layout constants), CORE_Util (helpers). No external references: no Scripting.Dictionary, no WorksheetFunction. Supported on Windows Excel 64-bit; 32-bit is kept compiling but not certified; Mac and Excel for the web are not supported.</t>
   </si>
 </sst>
 </file>
@@ -4821,10 +4872,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="shReadme">
     <tabColor rgb="FF1F3864"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X70"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
@@ -4862,7 +4914,7 @@
       </c>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C6" s="134" t="s">
         <v>3</v>
       </c>
@@ -4870,7 +4922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C7" s="135" t="s">
         <v>5</v>
       </c>
@@ -4878,31 +4930,31 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:19" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C8" s="135" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C9" s="135" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="139" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C10" s="135" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="139" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C11" s="135" t="s">
         <v>13</v>
       </c>
@@ -4910,7 +4962,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C12" s="136" t="s">
         <v>15</v>
       </c>
@@ -4928,7 +4980,7 @@
       </c>
       <c r="D14" s="37"/>
     </row>
-    <row r="15" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C15" s="134" t="s">
         <v>18</v>
       </c>
@@ -4936,7 +4988,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C16" s="135" t="s">
         <v>20</v>
       </c>
@@ -4944,7 +4996,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="3:4" ht="24" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:4" ht="24" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C17" s="135" t="s">
         <v>22</v>
       </c>
@@ -4952,15 +5004,15 @@
         <v>801</v>
       </c>
     </row>
-    <row r="18" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C18" s="135" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="139" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C19" s="135" t="s">
         <v>25</v>
       </c>
@@ -4968,7 +5020,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C20" s="135" t="s">
         <v>27</v>
       </c>
@@ -4976,7 +5028,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C21" s="136" t="s">
         <v>29</v>
       </c>
@@ -4997,7 +5049,7 @@
         <v>One-page reference card: all formulas and parameters (opens on GitHub)</v>
       </c>
     </row>
-    <row r="24" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C24" s="134" t="s">
         <v>32</v>
       </c>
@@ -5005,15 +5057,15 @@
         <v>815</v>
       </c>
     </row>
-    <row r="25" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C25" s="135" t="s">
         <v>33</v>
       </c>
       <c r="D25" s="139" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C26" s="135" t="s">
         <v>35</v>
       </c>
@@ -5021,7 +5073,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C27" s="135" t="s">
         <v>37</v>
       </c>
@@ -5029,7 +5081,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C28" s="135" t="s">
         <v>39</v>
       </c>
@@ -5037,23 +5089,23 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:4" ht="46" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C29" s="135" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="139" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="30" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C30" s="135" t="s">
         <v>42</v>
       </c>
       <c r="D30" s="139" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="31" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C31" s="135" t="s">
         <v>43</v>
       </c>
@@ -5061,7 +5113,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C32" s="135" t="s">
         <v>45</v>
       </c>
@@ -5069,7 +5121,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C33" s="135" t="s">
         <v>47</v>
       </c>
@@ -5077,12 +5129,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C34" s="136" t="s">
         <v>49</v>
       </c>
       <c r="D34" s="140" t="s">
-        <v>50</v>
+        <v>906</v>
       </c>
     </row>
     <row r="35" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
@@ -5095,7 +5147,7 @@
       </c>
       <c r="D36" s="37"/>
     </row>
-    <row r="37" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C37" s="134" t="s">
         <v>52</v>
       </c>
@@ -5103,7 +5155,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C38" s="135" t="s">
         <v>54</v>
       </c>
@@ -5111,7 +5163,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C39" s="135" t="s">
         <v>56</v>
       </c>
@@ -5119,15 +5171,15 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C40" s="135" t="s">
         <v>58</v>
       </c>
       <c r="D40" s="139" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C41" s="135" t="s">
         <v>60</v>
       </c>
@@ -5135,7 +5187,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C42" s="135" t="s">
         <v>62</v>
       </c>
@@ -5143,7 +5195,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C43" s="135" t="s">
         <v>64</v>
       </c>
@@ -5151,7 +5203,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C44" s="135" t="s">
         <v>66</v>
       </c>
@@ -5159,7 +5211,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C45" s="135" t="s">
         <v>68</v>
       </c>
@@ -5167,7 +5219,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C46" s="135" t="s">
         <v>896</v>
       </c>
@@ -5175,7 +5227,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C47" s="136" t="s">
         <v>72</v>
       </c>
@@ -5193,23 +5245,23 @@
       </c>
       <c r="D49" s="37"/>
     </row>
-    <row r="50" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C50" s="134" t="s">
-        <v>75</v>
+        <v>908</v>
       </c>
       <c r="D50" s="138" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C51" s="135" t="s">
-        <v>77</v>
+        <v>909</v>
       </c>
       <c r="D51" s="139" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C52" s="135" t="s">
         <v>78</v>
       </c>
@@ -5217,7 +5269,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C53" s="135" t="s">
         <v>80</v>
       </c>
@@ -5225,7 +5277,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="54" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C54" s="135" t="s">
         <v>82</v>
       </c>
@@ -5233,15 +5285,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C55" s="135" t="s">
-        <v>84</v>
+        <v>910</v>
       </c>
       <c r="D55" s="139" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C56" s="135" t="s">
         <v>86</v>
       </c>
@@ -5249,15 +5301,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C57" s="135" t="s">
-        <v>88</v>
+        <v>911</v>
       </c>
       <c r="D57" s="139" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="58" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C58" s="135" t="s">
         <v>90</v>
       </c>
@@ -5265,7 +5317,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C59" s="136" t="s">
         <v>92</v>
       </c>
@@ -5283,15 +5335,15 @@
       </c>
       <c r="D61" s="37"/>
     </row>
-    <row r="62" spans="3:4" ht="36" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:4" ht="46" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C62" s="134" t="s">
         <v>95</v>
       </c>
       <c r="D62" s="138" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="63" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C63" s="135" t="s">
         <v>805</v>
       </c>
@@ -5299,7 +5351,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="64" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C64" s="135" t="s">
         <v>96</v>
       </c>
@@ -5307,15 +5359,15 @@
         <v>817</v>
       </c>
     </row>
-    <row r="65" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C65" s="135" t="s">
         <v>97</v>
       </c>
       <c r="D65" s="139" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="66" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C66" s="135" t="s">
         <v>98</v>
       </c>
@@ -5323,12 +5375,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="67" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C67" s="136" t="s">
         <v>100</v>
       </c>
       <c r="D67" s="140" t="s">
-        <v>101</v>
+        <v>914</v>
       </c>
     </row>
     <row r="68" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
@@ -5341,12 +5393,12 @@
       </c>
       <c r="D69" s="37"/>
     </row>
-    <row r="70" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C70" s="137" t="s">
         <v>103</v>
       </c>
       <c r="D70" s="141" t="s">
-        <v>104</v>
+        <v>915</v>
       </c>
     </row>
   </sheetData>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="916">
   <si>
     <t>SA-CCR Calculator</t>
   </si>
@@ -2801,6 +2801,57 @@
   </si>
   <si>
     <t>Rel. diff</t>
+  </si>
+  <si>
+    <t>NettingSets: one row per netting set - margin flag, client-clearing role, MPOR drivers, collateral (net VM held (+) / posted (-), NICA), threshold, MTA, optional Alpha and Regime overrides, and the margin-agreement structure. Collateral is entered after haircuts, in reporting currency.</t>
+  </si>
+  <si>
+    <t>Trades: one row per derivative leg. Dropdowns guide the classification. Amounts can be in any currency of the FX table. Legs of one economic trade share an Economic trade ID; exactly one of them (MtM leg = Y) carries the MtM.</t>
+  </si>
+  <si>
+    <t>Click "Run SA-CCR" (macro RunSACCR). Results, HedgingSets, Buckets, TradeCalc and Checks are rebuilt. "Validate inputs" only runs the checks; "Clear outputs" empties the output sheets.</t>
+  </si>
+  <si>
+    <t>Positive amount; the sign comes from Direction. IR / CR: trade notional. FX: the notional of one leg, in that leg's currency (one of the pair): the foreign-currency leg or, when both legs are foreign, the larger one in reporting currency. EQ / CO: market price x units.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unmargined: max(V - C, 0), C = NICA, plus the posted VM under a BCBS one-way agreement [CRE52.10]   Margined: max(V - C, TH + MTA - NICA, 0), C = VM + NICA [CRE52.18]</t>
+  </si>
+  <si>
+    <t>Floor 10 BD bilateral; 5 BD (configurable) for client clearing: the clearing member in both regimes, the client under CRR only [CRE54.12; Art. 279c(1)]; 20 BD when the netting set is flagged large or illiquid (more than 5,000 trades in the previous quarter, illiquid collateral or a hard-to-replace derivative; a current count above 5,000 with the flag N only gives a warning) [CRE52.51; Art. 285(3)]; + (N - 1) for remargining every N days; the result doubled for disputes [CRE52.50-52.52; Art. 285]</t>
+  </si>
+  <si>
+    <t>Hedging set per currency (inflation in its own set per currency); buckets on E: CRR E &lt;= 1y, 1y &lt; E &lt;= 5y, E &gt; 5y [Art. 280a]; BCBS E &lt; 1y, 1-5y, &gt; 5y [CRE52.57]; EN = sqrt(D1^2+D2^2+D3^2+1.4D1D2+1.4D2D3+0.6D1D3); AddOn = 0.5% x EN. BCBS only: IRBucketOffset = FALSE uses the sum of absolute bucket values [CRE52.57(5)]; a CRR netting set with IR trades is then INVALID.</t>
+  </si>
+  <si>
+    <t>Other risks: per hedging set AddOn = 8% x |sum effective notional| [Art. 280f]. Under BCBS an OT trade is rejected and its netting set's EAD withheld.</t>
+  </si>
+  <si>
+    <t>Output - EAD per netting set, and TOTAL CRR / TOTAL BCBS rows over the VALID netting sets of each regime</t>
+  </si>
+  <si>
+    <t>SACCR_SupervisoryDuration(S, E, [FloorYears])</t>
+  </si>
+  <si>
+    <t>SACCR_MaturityFactor(M, [Margined], [MPOR_BD], [MinBD], [BDPerYear])</t>
+  </si>
+  <si>
+    <t>SACCR_IREffectiveNotional(D1, D2, D3, [Rho12], [Rho23], [Rho13])</t>
+  </si>
+  <si>
+    <t>SACCR_Multiplier(VminusC, AddOn, [FloorPct])</t>
+  </si>
+  <si>
+    <t>Simplified SA-CCR and OEM (CRR Art. 281-282), CCP exposures, SFTs, CVA and RWA; collateral haircuts (enter C after haircuts); several margin agreements in one netting set, or one agreement over several netting sets; automatic risk-driver mapping (RTS 2021/931); digital options (option legs are calculated as an ordinary option combination, without the CRR collar or the BCBS cap). The optional reductions for sold options and sold credit protection (Art. 274(5), (7)) are not applied, which gives a higher EAD.</t>
+  </si>
+  <si>
+    <t>The cap recalculates a margined netting set as unmargined: unmargined maturity factors and C = NICA in both regimes (Results columns Z-AC).</t>
+  </si>
+  <si>
+    <t>Illustrative counterparties (NS-ALPHA, NS-GAMMA) and FX rates. BCBS-EX1..5 reproduce CRE99 / BCBS 279 Annex 4 (amounts in thousands); the other CRR-* and BCBS-* netting sets feed the TestCatalogue; DEMO-REJECTED shows how rejected trades withhold a netting set's EAD.</t>
+  </si>
+  <si>
+    <t>M_Main (macros), CORE_Engine (calculation), SACCR_Formulas (public SACCR_* functions), CORE_Config (layout constants), CORE_Util (helpers). No external references: no Scripting.Dictionary, no WorksheetFunction. Supported on Windows Excel 64-bit; 32-bit is kept compiling but not certified; Mac and Excel for the web are not supported.</t>
   </si>
 </sst>
 </file>
@@ -3057,7 +3108,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -3228,13 +3279,133 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3636,6 +3807,30 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4677,13 +4872,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="shReadme">
     <tabColor rgb="FF1F3864"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X70"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
     <col min="4" max="4" width="126.875" customWidth="1"/>
     <col min="5" max="5" width="4.75" customWidth="1"/>
     <col min="6" max="24" width="0" hidden="1" customWidth="1"/>
@@ -4718,59 +4914,59 @@
       </c>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="25" t="s">
+    <row r="6" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C6" s="134" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="138" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="25" t="s">
+    <row r="7" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C7" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="139" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="25" t="s">
+    <row r="8" spans="2:19" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C8" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="25" t="s">
+      <c r="D8" s="139" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C9" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="25" t="s">
+      <c r="D9" s="139" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C10" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="34" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="25" t="s">
+      <c r="D10" s="139" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C11" s="135" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="139" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="25" t="s">
+    <row r="12" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C12" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="140" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4784,59 +4980,59 @@
       </c>
       <c r="D14" s="37"/>
     </row>
-    <row r="15" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="25" t="s">
+    <row r="15" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C15" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="138" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="25" t="s">
+    <row r="16" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C16" s="135" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="D16" s="139" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="3:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="C17" s="25" t="s">
+    <row r="17" spans="3:4" ht="24" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C17" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="D17" s="139" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="18" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="25" t="s">
+    <row r="18" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C18" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="34" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="25" t="s">
+      <c r="D18" s="139" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C19" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="139" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="25" t="s">
+    <row r="20" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C20" s="135" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="139" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="25" t="s">
+    <row r="21" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C21" s="136" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="140" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4853,92 +5049,92 @@
         <v>One-page reference card: all formulas and parameters (opens on GitHub)</v>
       </c>
     </row>
-    <row r="24" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="25" t="s">
+    <row r="24" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C24" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="34" t="s">
+      <c r="D24" s="138" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="25" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="25" t="s">
+    <row r="25" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C25" s="135" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="34" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="25" t="s">
+      <c r="D25" s="139" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C26" s="135" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="34" t="s">
+      <c r="D26" s="139" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="25" t="s">
+    <row r="27" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C27" s="135" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="34" t="s">
+      <c r="D27" s="139" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="25" t="s">
+    <row r="28" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C28" s="135" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="34" t="s">
+      <c r="D28" s="139" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="25" t="s">
+    <row r="29" spans="3:4" ht="46" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C29" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="34" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="30" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="25" t="s">
+      <c r="D29" s="139" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C30" s="135" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="34" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="31" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="25" t="s">
+      <c r="D30" s="139" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C31" s="135" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="34" t="s">
+      <c r="D31" s="139" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="25" t="s">
+    <row r="32" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C32" s="135" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="34" t="s">
+      <c r="D32" s="139" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="25" t="s">
+    <row r="33" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C33" s="135" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="34" t="s">
+      <c r="D33" s="139" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="25" t="s">
+    <row r="34" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C34" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="34" t="s">
-        <v>50</v>
+      <c r="D34" s="140" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="35" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
@@ -4951,91 +5147,91 @@
       </c>
       <c r="D36" s="37"/>
     </row>
-    <row r="37" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="25" t="s">
+    <row r="37" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C37" s="134" t="s">
         <v>52</v>
       </c>
-      <c r="D37" s="34" t="s">
+      <c r="D37" s="138" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="25" t="s">
+    <row r="38" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C38" s="135" t="s">
         <v>54</v>
       </c>
-      <c r="D38" s="34" t="s">
+      <c r="D38" s="139" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="25" t="s">
+    <row r="39" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C39" s="135" t="s">
         <v>56</v>
       </c>
-      <c r="D39" s="34" t="s">
+      <c r="D39" s="139" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="25" t="s">
+    <row r="40" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C40" s="135" t="s">
         <v>58</v>
       </c>
-      <c r="D40" s="34" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="25" t="s">
+      <c r="D40" s="139" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C41" s="135" t="s">
         <v>60</v>
       </c>
-      <c r="D41" s="34" t="s">
+      <c r="D41" s="139" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="25" t="s">
+    <row r="42" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C42" s="135" t="s">
         <v>62</v>
       </c>
-      <c r="D42" s="34" t="s">
+      <c r="D42" s="139" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="25" t="s">
+    <row r="43" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C43" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="D43" s="34" t="s">
+      <c r="D43" s="139" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="25" t="s">
+    <row r="44" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C44" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="D44" s="34" t="s">
+      <c r="D44" s="139" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="25" t="s">
+    <row r="45" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C45" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="34" t="s">
+      <c r="D45" s="139" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="25" t="s">
+    <row r="46" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C46" s="135" t="s">
         <v>896</v>
       </c>
-      <c r="D46" s="34" t="s">
+      <c r="D46" s="139" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="25" t="s">
+    <row r="47" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C47" s="136" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="34" t="s">
+      <c r="D47" s="140" t="s">
         <v>73</v>
       </c>
     </row>
@@ -5049,83 +5245,83 @@
       </c>
       <c r="D49" s="37"/>
     </row>
-    <row r="50" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D50" s="34" t="s">
+    <row r="50" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C50" s="134" t="s">
+        <v>908</v>
+      </c>
+      <c r="D50" s="138" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="D51" s="34" t="s">
+    <row r="51" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C51" s="135" t="s">
+        <v>909</v>
+      </c>
+      <c r="D51" s="139" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="25" t="s">
+    <row r="52" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C52" s="135" t="s">
         <v>78</v>
       </c>
-      <c r="D52" s="34" t="s">
+      <c r="D52" s="139" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="53" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="25" t="s">
+    <row r="53" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C53" s="135" t="s">
         <v>80</v>
       </c>
-      <c r="D53" s="34" t="s">
+      <c r="D53" s="139" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="54" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="25" t="s">
+    <row r="54" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C54" s="135" t="s">
         <v>82</v>
       </c>
-      <c r="D54" s="34" t="s">
+      <c r="D54" s="139" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D55" s="34" t="s">
+    <row r="55" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C55" s="135" t="s">
+        <v>910</v>
+      </c>
+      <c r="D55" s="139" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="25" t="s">
+    <row r="56" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C56" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="D56" s="34" t="s">
+      <c r="D56" s="139" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D57" s="34" t="s">
+    <row r="57" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C57" s="135" t="s">
+        <v>911</v>
+      </c>
+      <c r="D57" s="139" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="58" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="25" t="s">
+    <row r="58" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C58" s="135" t="s">
         <v>90</v>
       </c>
-      <c r="D58" s="34" t="s">
+      <c r="D58" s="139" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C59" s="25" t="s">
+    <row r="59" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C59" s="136" t="s">
         <v>92</v>
       </c>
-      <c r="D59" s="34" t="s">
+      <c r="D59" s="140" t="s">
         <v>93</v>
       </c>
     </row>
@@ -5139,52 +5335,52 @@
       </c>
       <c r="D61" s="37"/>
     </row>
-    <row r="62" spans="3:4" ht="36" x14ac:dyDescent="0.25">
-      <c r="C62" s="25" t="s">
+    <row r="62" spans="3:4" ht="46" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C62" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="D62" s="34" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="63" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="25" t="s">
+      <c r="D62" s="138" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C63" s="135" t="s">
         <v>805</v>
       </c>
-      <c r="D63" s="34" t="s">
+      <c r="D63" s="139" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="64" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="25" t="s">
+    <row r="64" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C64" s="135" t="s">
         <v>96</v>
       </c>
-      <c r="D64" s="34" t="s">
+      <c r="D64" s="139" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="65" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="25" t="s">
+    <row r="65" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C65" s="135" t="s">
         <v>97</v>
       </c>
-      <c r="D65" s="34" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="66" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="25" t="s">
+      <c r="D65" s="139" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C66" s="135" t="s">
         <v>98</v>
       </c>
-      <c r="D66" s="34" t="s">
+      <c r="D66" s="139" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="67" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="25" t="s">
+    <row r="67" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C67" s="136" t="s">
         <v>100</v>
       </c>
-      <c r="D67" s="34" t="s">
-        <v>101</v>
+      <c r="D67" s="140" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="68" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
@@ -5197,12 +5393,12 @@
       </c>
       <c r="D69" s="37"/>
     </row>
-    <row r="70" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="25" t="s">
+    <row r="70" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C70" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="D70" s="34" t="s">
-        <v>104</v>
+      <c r="D70" s="141" t="s">
+        <v>915</v>
       </c>
     </row>
   </sheetData>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -94,7 +94,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="916">
   <si>
-    <t>SA-CCR Calculator</t>
+    <t>K-SACCR</t>
   </si>
   <si>
     <t>Standardised approach for counterparty credit risk - common Basel CRE52 core with an EU CRR (Art. 274-280f) rules layer. VBA engine v1.0.0.</t>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -16,15 +16,21 @@
     <sheet name="Buckets" sheetId="7" r:id="rId7"/>
     <sheet name="TradeCalc" sheetId="8" r:id="rId8"/>
     <sheet name="Checks" sheetId="9" r:id="rId9"/>
+    <sheet name="BankNettingSets" sheetId="13" r:id="rId17"/>
+    <sheet name="Reconciliation" sheetId="14" r:id="rId18"/>
     <sheet name="TestCatalogue" sheetId="10" r:id="rId10"/>
     <sheet name="FormulaTest" sheetId="11" r:id="rId11"/>
     <sheet name="Basel_vs_CRR" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Basel_vs_CRR!$C$5:$K$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">Basel_vs_CRR!$C$5:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Trades!$C$4:$AB$69</definedName>
     <definedName name="Alpha">Params!$E$8</definedName>
     <definedName name="AsOfDate">Params!$E$6</definedName>
+    <definedName name="BankNettingSets_Header">BankNettingSets!$C$8</definedName>
+    <definedName name="BankNS_AbsTol">BankNettingSets!$D$5</definedName>
+    <definedName name="BankNS_RelTol">BankNettingSets!$D$6</definedName>
+    <definedName name="BankNS_Scale">BankNettingSets!$D$4</definedName>
     <definedName name="BasisFactor">Params!$E$17</definedName>
     <definedName name="BusinessDaysPerYear">Params!$E$11</definedName>
     <definedName name="DaysPerYear">Params!$E$10</definedName>
@@ -46,6 +52,7 @@
     <definedName name="Params_Value">Params!$E$5</definedName>
     <definedName name="Regime">Params!$E$23</definedName>
     <definedName name="ReportingCcy">Params!$E$7</definedName>
+    <definedName name="SACCR_ReconInputs" hidden="1">""</definedName>
     <definedName name="SACCR_RunInputs" hidden="1">""</definedName>
     <definedName name="SDFloorBD">Params!$E$13</definedName>
     <definedName name="SF_Table">Params!$C$28:$K$54</definedName>
@@ -92,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="939">
   <si>
     <t>K-SACCR</t>
   </si>
@@ -136,7 +143,7 @@
     <t>6. Review</t>
   </si>
   <si>
-    <t>Checks lists every excluded trade and warning. TestCatalogue compares the engine with published / hand-calculated reference values per regime; FormulaTest unit-tests the formula functions.</t>
+    <t>Checks lists every excluded trade and warning. Reconciliation shows MATCH or DIFFERENCE for each bank figure and every netting set that could not be compared. TestCatalogue compares the engine with published / hand-calculated reference values per regime; FormulaTest unit-tests the formula functions.</t>
   </si>
   <si>
     <t>7. Regime</t>
@@ -2809,7 +2816,7 @@
     <t>Trades: one row per derivative leg. Dropdowns guide the classification. Amounts can be in any currency of the FX table. Legs of one economic trade share an Economic trade ID; exactly one of them (MtM leg = Y) carries the MtM.</t>
   </si>
   <si>
-    <t>Click "Run SA-CCR" (macro RunSACCR). Results, HedgingSets, Buckets, TradeCalc and Checks are rebuilt. "Validate inputs" only runs the checks; "Clear outputs" empties the output sheets.</t>
+    <t>Click "Run SA-CCR" (macro RunSACCR). Results, HedgingSets, Buckets, TradeCalc and Checks are rebuilt, and Reconciliation compares the figures entered on BankNettingSets with Results. "Validate inputs" only runs the checks; "Clear outputs" empties the output sheets.</t>
   </si>
   <si>
     <t>Positive amount; the sign comes from Direction. IR / CR: trade notional. FX: the notional of one leg, in that leg's currency (one of the pair): the foreign-currency leg or, when both legs are foreign, the larger one in reporting currency. EQ / CO: market price x units.</t>
@@ -2851,7 +2858,76 @@
     <t>Illustrative counterparties (NS-ALPHA, NS-GAMMA) and FX rates. BCBS-EX1..5 reproduce CRE99 / BCBS 279 Annex 4 (amounts in thousands); the other CRR-* and BCBS-* netting sets feed the TestCatalogue; DEMO-REJECTED shows how rejected trades withhold a netting set's EAD.</t>
   </si>
   <si>
-    <t>M_Main (macros), CORE_Engine (calculation), SACCR_Formulas (public SACCR_* functions), CORE_Config (layout constants), CORE_Util (helpers). No external references: no Scripting.Dictionary, no WorksheetFunction. Supported on Windows Excel 64-bit; 32-bit is kept compiling but not certified; Mac and Excel for the web are not supported.</t>
+    <t>M_Main (macros), CORE_Engine (calculation), CORE_Reconcile (comparison with bank figures), SACCR_Formulas (public SACCR_* functions), CORE_Config (layout constants), CORE_Util (helpers). No external references: no Scripting.Dictionary, no WorksheetFunction. Supported on Windows Excel 64-bit; 32-bit is kept compiling but not certified; Mac and Excel for the web are not supported.</t>
+  </si>
+  <si>
+    <t>Bank netting-set results</t>
+  </si>
+  <si>
+    <t>Enter the bank's own figures per netting set. Run SA-CCR compares them with Results on the Reconciliation sheet. A blank figure is not compared.</t>
+  </si>
+  <si>
+    <t>Amount scale</t>
+  </si>
+  <si>
+    <t>Units of the reporting currency per bank amount: 1, 1000 (thousands) or 1000000 (millions). The multiplier is not scaled.</t>
+  </si>
+  <si>
+    <t>Absolute tolerance</t>
+  </si>
+  <si>
+    <t>In units of the reporting currency. Not used for the multiplier.</t>
+  </si>
+  <si>
+    <t>Relative tolerance</t>
+  </si>
+  <si>
+    <t>Of the bank figure. A figure matches when its difference is within either tolerance.</t>
+  </si>
+  <si>
+    <t>Regime (BCBS / CRR)</t>
+  </si>
+  <si>
+    <t>Reconciliation</t>
+  </si>
+  <si>
+    <t>No reconciliation yet: enter bank figures on BankNettingSets and press Run SA-CCR.</t>
+  </si>
+  <si>
+    <t>Bank row</t>
+  </si>
+  <si>
+    <t>Bank regime</t>
+  </si>
+  <si>
+    <t>Calculator regime</t>
+  </si>
+  <si>
+    <t>Calculator status</t>
+  </si>
+  <si>
+    <t>Measure</t>
+  </si>
+  <si>
+    <t>Bank figure (units)</t>
+  </si>
+  <si>
+    <t>Calculator figure</t>
+  </si>
+  <si>
+    <t>Difference (calculator - bank)</t>
+  </si>
+  <si>
+    <t>Relative difference</t>
+  </si>
+  <si>
+    <t>BankNettingSets</t>
+  </si>
+  <si>
+    <t>Inputs - the bank's own figures per netting set, to reconcile with Results; amount scale and tolerances at the top</t>
+  </si>
+  <si>
+    <t>Output - each bank figure against Results: MATCH, DIFFERENCE, and every netting set not compared, with the reason</t>
   </si>
 </sst>
 </file>
@@ -4875,7 +4951,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X70"/>
+  <dimension ref="A1:X72"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
@@ -5213,191 +5289,207 @@
     </row>
     <row r="45" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C45" s="135" t="s">
-        <v>68</v>
+        <v>936</v>
       </c>
       <c r="D45" s="139" t="s">
-        <v>69</v>
+        <v>937</v>
       </c>
     </row>
     <row r="46" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C46" s="135" t="s">
+        <v>925</v>
+      </c>
+      <c r="D46" s="139" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C47" s="135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" s="139" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C48" s="135" t="s">
         <v>896</v>
       </c>
-      <c r="D46" s="139" t="s">
+      <c r="D48" s="139" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C47" s="136" t="s">
+    <row r="49" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C49" s="136" t="s">
         <v>72</v>
       </c>
-      <c r="D47" s="140" t="s">
+      <c r="D49" s="140" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C48" s="35"/>
-      <c r="D48" s="36"/>
-    </row>
-    <row r="49" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="33" t="s">
+    <row r="50" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="35"/>
+      <c r="D50" s="36"/>
+    </row>
+    <row r="51" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="D49" s="37"/>
-    </row>
-    <row r="50" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C50" s="134" t="s">
+      <c r="D51" s="37"/>
+    </row>
+    <row r="52" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C52" s="134" t="s">
         <v>908</v>
       </c>
-      <c r="D50" s="138" t="s">
+      <c r="D52" s="138" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="51" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C51" s="135" t="s">
-        <v>909</v>
-      </c>
-      <c r="D51" s="139" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="52" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C52" s="135" t="s">
-        <v>78</v>
-      </c>
-      <c r="D52" s="139" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="53" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C53" s="135" t="s">
-        <v>80</v>
+        <v>909</v>
       </c>
       <c r="D53" s="139" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C54" s="135" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D54" s="139" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C55" s="135" t="s">
-        <v>910</v>
+        <v>80</v>
       </c>
       <c r="D55" s="139" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C56" s="135" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D56" s="139" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C57" s="135" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D57" s="139" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C58" s="135" t="s">
+        <v>86</v>
+      </c>
+      <c r="D58" s="139" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C59" s="135" t="s">
+        <v>911</v>
+      </c>
+      <c r="D59" s="139" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C60" s="135" t="s">
         <v>90</v>
       </c>
-      <c r="D58" s="139" t="s">
+      <c r="D60" s="139" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C59" s="136" t="s">
+    <row r="61" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C61" s="136" t="s">
         <v>92</v>
       </c>
-      <c r="D59" s="140" t="s">
+      <c r="D61" s="140" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C60" s="35"/>
-      <c r="D60" s="36"/>
-    </row>
-    <row r="61" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C61" s="33" t="s">
+    <row r="62" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="35"/>
+      <c r="D62" s="36"/>
+    </row>
+    <row r="63" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C63" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="D61" s="37"/>
-    </row>
-    <row r="62" spans="3:4" ht="46" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C62" s="134" t="s">
+      <c r="D63" s="37"/>
+    </row>
+    <row r="64" spans="3:4" ht="46" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C64" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="D62" s="138" t="s">
+      <c r="D64" s="138" t="s">
         <v>912</v>
-      </c>
-    </row>
-    <row r="63" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C63" s="135" t="s">
-        <v>805</v>
-      </c>
-      <c r="D63" s="139" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="64" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C64" s="135" t="s">
-        <v>96</v>
-      </c>
-      <c r="D64" s="139" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="65" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C65" s="135" t="s">
-        <v>97</v>
+        <v>805</v>
       </c>
       <c r="D65" s="139" t="s">
-        <v>913</v>
+        <v>804</v>
       </c>
     </row>
     <row r="66" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C66" s="135" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66" s="139" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C67" s="135" t="s">
+        <v>97</v>
+      </c>
+      <c r="D67" s="139" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C68" s="135" t="s">
         <v>98</v>
       </c>
-      <c r="D66" s="139" t="s">
+      <c r="D68" s="139" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="67" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C67" s="136" t="s">
+    <row r="69" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C69" s="136" t="s">
         <v>100</v>
       </c>
-      <c r="D67" s="140" t="s">
+      <c r="D69" s="140" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="68" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="35"/>
-      <c r="D68" s="36"/>
-    </row>
-    <row r="69" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="33" t="s">
+    <row r="70" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="35"/>
+      <c r="D70" s="36"/>
+    </row>
+    <row r="71" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C71" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="D69" s="37"/>
-    </row>
-    <row r="70" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C70" s="137" t="s">
+      <c r="D71" s="37"/>
+    </row>
+    <row r="72" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C72" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="D70" s="141" t="s">
+      <c r="D72" s="141" t="s">
         <v>915</v>
       </c>
     </row>
@@ -11702,6 +11794,3506 @@
     </row>
   </sheetData>
   <autoFilter ref="C5:K30" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <sheetPr codeName="shBankNettingSets">
+    <tabColor rgb="FFBF9000"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:P208"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="4" customWidth="1"/>
+    <col min="3" max="3" width="20.625" style="36" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="36" customWidth="1"/>
+    <col min="5" max="14" width="15.625" style="36" customWidth="1"/>
+    <col min="15" max="15" width="11.625" style="36" customWidth="1"/>
+    <col min="16" max="16" width="40.625" style="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+    </row>
+    <row r="2" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="30" t="s">
+        <v>916</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+    </row>
+    <row r="3" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="43" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="36" t="s">
+        <v>918</v>
+      </c>
+      <c r="D4" s="61">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="36" t="s">
+        <v>920</v>
+      </c>
+      <c r="D5" s="63">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="36" t="s">
+        <v>922</v>
+      </c>
+      <c r="D6" s="131">
+        <v>0.0001</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" s="36" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="58" t="s">
+        <v>246</v>
+      </c>
+      <c r="D8" s="58" t="s">
+        <v>924</v>
+      </c>
+      <c r="E8" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="59" t="s">
+        <v>454</v>
+      </c>
+      <c r="I8" s="59" t="s">
+        <v>448</v>
+      </c>
+      <c r="J8" s="59" t="s">
+        <v>449</v>
+      </c>
+      <c r="K8" s="59" t="s">
+        <v>450</v>
+      </c>
+      <c r="L8" s="59" t="s">
+        <v>451</v>
+      </c>
+      <c r="M8" s="59" t="s">
+        <v>452</v>
+      </c>
+      <c r="N8" s="59" t="s">
+        <v>453</v>
+      </c>
+      <c r="O8" s="59" t="s">
+        <v>455</v>
+      </c>
+      <c r="P8" s="59" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="60"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="74"/>
+      <c r="P9" s="47"/>
+    </row>
+    <row r="10" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="60"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
+      <c r="N10" s="63"/>
+      <c r="O10" s="74"/>
+      <c r="P10" s="47"/>
+    </row>
+    <row r="11" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="60"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="63"/>
+      <c r="O11" s="74"/>
+      <c r="P11" s="47"/>
+    </row>
+    <row r="12" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="60"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="63"/>
+      <c r="O12" s="74"/>
+      <c r="P12" s="47"/>
+    </row>
+    <row r="13" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="60"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="47"/>
+    </row>
+    <row r="14" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="60"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="47"/>
+    </row>
+    <row r="15" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="60"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="74"/>
+      <c r="P15" s="47"/>
+    </row>
+    <row r="16" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="60"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="63"/>
+      <c r="L16" s="63"/>
+      <c r="M16" s="63"/>
+      <c r="N16" s="63"/>
+      <c r="O16" s="74"/>
+      <c r="P16" s="47"/>
+    </row>
+    <row r="17" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="60"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
+      <c r="L17" s="63"/>
+      <c r="M17" s="63"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="74"/>
+      <c r="P17" s="47"/>
+    </row>
+    <row r="18" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="60"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="74"/>
+      <c r="P18" s="47"/>
+    </row>
+    <row r="19" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="60"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="74"/>
+      <c r="P19" s="47"/>
+    </row>
+    <row r="20" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="60"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="63"/>
+      <c r="L20" s="63"/>
+      <c r="M20" s="63"/>
+      <c r="N20" s="63"/>
+      <c r="O20" s="74"/>
+      <c r="P20" s="47"/>
+    </row>
+    <row r="21" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="60"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="63"/>
+      <c r="M21" s="63"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="74"/>
+      <c r="P21" s="47"/>
+    </row>
+    <row r="22" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="60"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="63"/>
+      <c r="K22" s="63"/>
+      <c r="L22" s="63"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="74"/>
+      <c r="P22" s="47"/>
+    </row>
+    <row r="23" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="60"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="63"/>
+      <c r="K23" s="63"/>
+      <c r="L23" s="63"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="74"/>
+      <c r="P23" s="47"/>
+    </row>
+    <row r="24" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="60"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="63"/>
+      <c r="K24" s="63"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="74"/>
+      <c r="P24" s="47"/>
+    </row>
+    <row r="25" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="60"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="63"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="63"/>
+      <c r="K25" s="63"/>
+      <c r="L25" s="63"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="74"/>
+      <c r="P25" s="47"/>
+    </row>
+    <row r="26" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="60"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="63"/>
+      <c r="L26" s="63"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="47"/>
+    </row>
+    <row r="27" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="60"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="63"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="74"/>
+      <c r="P27" s="47"/>
+    </row>
+    <row r="28" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="60"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="63"/>
+      <c r="M28" s="63"/>
+      <c r="N28" s="63"/>
+      <c r="O28" s="74"/>
+      <c r="P28" s="47"/>
+    </row>
+    <row r="29" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="60"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="63"/>
+      <c r="L29" s="63"/>
+      <c r="M29" s="63"/>
+      <c r="N29" s="63"/>
+      <c r="O29" s="74"/>
+      <c r="P29" s="47"/>
+    </row>
+    <row r="30" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="60"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="63"/>
+      <c r="L30" s="63"/>
+      <c r="M30" s="63"/>
+      <c r="N30" s="63"/>
+      <c r="O30" s="74"/>
+      <c r="P30" s="47"/>
+    </row>
+    <row r="31" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="60"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="63"/>
+      <c r="K31" s="63"/>
+      <c r="L31" s="63"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="74"/>
+      <c r="P31" s="47"/>
+    </row>
+    <row r="32" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="60"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="63"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="63"/>
+      <c r="N32" s="63"/>
+      <c r="O32" s="74"/>
+      <c r="P32" s="47"/>
+    </row>
+    <row r="33" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="60"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="63"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="63"/>
+      <c r="K33" s="63"/>
+      <c r="L33" s="63"/>
+      <c r="M33" s="63"/>
+      <c r="N33" s="63"/>
+      <c r="O33" s="74"/>
+      <c r="P33" s="47"/>
+    </row>
+    <row r="34" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="60"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="63"/>
+      <c r="J34" s="63"/>
+      <c r="K34" s="63"/>
+      <c r="L34" s="63"/>
+      <c r="M34" s="63"/>
+      <c r="N34" s="63"/>
+      <c r="O34" s="74"/>
+      <c r="P34" s="47"/>
+    </row>
+    <row r="35" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="60"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="74"/>
+      <c r="P35" s="47"/>
+    </row>
+    <row r="36" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="60"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="63"/>
+      <c r="K36" s="63"/>
+      <c r="L36" s="63"/>
+      <c r="M36" s="63"/>
+      <c r="N36" s="63"/>
+      <c r="O36" s="74"/>
+      <c r="P36" s="47"/>
+    </row>
+    <row r="37" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="60"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="63"/>
+      <c r="K37" s="63"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="63"/>
+      <c r="O37" s="74"/>
+      <c r="P37" s="47"/>
+    </row>
+    <row r="38" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="60"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="63"/>
+      <c r="J38" s="63"/>
+      <c r="K38" s="63"/>
+      <c r="L38" s="63"/>
+      <c r="M38" s="63"/>
+      <c r="N38" s="63"/>
+      <c r="O38" s="74"/>
+      <c r="P38" s="47"/>
+    </row>
+    <row r="39" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="60"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="63"/>
+      <c r="J39" s="63"/>
+      <c r="K39" s="63"/>
+      <c r="L39" s="63"/>
+      <c r="M39" s="63"/>
+      <c r="N39" s="63"/>
+      <c r="O39" s="74"/>
+      <c r="P39" s="47"/>
+    </row>
+    <row r="40" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="60"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="63"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="63"/>
+      <c r="K40" s="63"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="63"/>
+      <c r="O40" s="74"/>
+      <c r="P40" s="47"/>
+    </row>
+    <row r="41" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="60"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
+      <c r="I41" s="63"/>
+      <c r="J41" s="63"/>
+      <c r="K41" s="63"/>
+      <c r="L41" s="63"/>
+      <c r="M41" s="63"/>
+      <c r="N41" s="63"/>
+      <c r="O41" s="74"/>
+      <c r="P41" s="47"/>
+    </row>
+    <row r="42" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="60"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
+      <c r="K42" s="63"/>
+      <c r="L42" s="63"/>
+      <c r="M42" s="63"/>
+      <c r="N42" s="63"/>
+      <c r="O42" s="74"/>
+      <c r="P42" s="47"/>
+    </row>
+    <row r="43" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="60"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="63"/>
+      <c r="F43" s="63"/>
+      <c r="G43" s="63"/>
+      <c r="H43" s="63"/>
+      <c r="I43" s="63"/>
+      <c r="J43" s="63"/>
+      <c r="K43" s="63"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="63"/>
+      <c r="N43" s="63"/>
+      <c r="O43" s="74"/>
+      <c r="P43" s="47"/>
+    </row>
+    <row r="44" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="60"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="63"/>
+      <c r="K44" s="63"/>
+      <c r="L44" s="63"/>
+      <c r="M44" s="63"/>
+      <c r="N44" s="63"/>
+      <c r="O44" s="74"/>
+      <c r="P44" s="47"/>
+    </row>
+    <row r="45" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="60"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="63"/>
+      <c r="I45" s="63"/>
+      <c r="J45" s="63"/>
+      <c r="K45" s="63"/>
+      <c r="L45" s="63"/>
+      <c r="M45" s="63"/>
+      <c r="N45" s="63"/>
+      <c r="O45" s="74"/>
+      <c r="P45" s="47"/>
+    </row>
+    <row r="46" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="60"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="63"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="63"/>
+      <c r="J46" s="63"/>
+      <c r="K46" s="63"/>
+      <c r="L46" s="63"/>
+      <c r="M46" s="63"/>
+      <c r="N46" s="63"/>
+      <c r="O46" s="74"/>
+      <c r="P46" s="47"/>
+    </row>
+    <row r="47" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="60"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="63"/>
+      <c r="I47" s="63"/>
+      <c r="J47" s="63"/>
+      <c r="K47" s="63"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="63"/>
+      <c r="O47" s="74"/>
+      <c r="P47" s="47"/>
+    </row>
+    <row r="48" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="60"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="63"/>
+      <c r="J48" s="63"/>
+      <c r="K48" s="63"/>
+      <c r="L48" s="63"/>
+      <c r="M48" s="63"/>
+      <c r="N48" s="63"/>
+      <c r="O48" s="74"/>
+      <c r="P48" s="47"/>
+    </row>
+    <row r="49" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="60"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="63"/>
+      <c r="G49" s="63"/>
+      <c r="H49" s="63"/>
+      <c r="I49" s="63"/>
+      <c r="J49" s="63"/>
+      <c r="K49" s="63"/>
+      <c r="L49" s="63"/>
+      <c r="M49" s="63"/>
+      <c r="N49" s="63"/>
+      <c r="O49" s="74"/>
+      <c r="P49" s="47"/>
+    </row>
+    <row r="50" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="60"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="63"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="63"/>
+      <c r="J50" s="63"/>
+      <c r="K50" s="63"/>
+      <c r="L50" s="63"/>
+      <c r="M50" s="63"/>
+      <c r="N50" s="63"/>
+      <c r="O50" s="74"/>
+      <c r="P50" s="47"/>
+    </row>
+    <row r="51" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="60"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="63"/>
+      <c r="J51" s="63"/>
+      <c r="K51" s="63"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="63"/>
+      <c r="O51" s="74"/>
+      <c r="P51" s="47"/>
+    </row>
+    <row r="52" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="60"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="63"/>
+      <c r="J52" s="63"/>
+      <c r="K52" s="63"/>
+      <c r="L52" s="63"/>
+      <c r="M52" s="63"/>
+      <c r="N52" s="63"/>
+      <c r="O52" s="74"/>
+      <c r="P52" s="47"/>
+    </row>
+    <row r="53" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="60"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="63"/>
+      <c r="F53" s="63"/>
+      <c r="G53" s="63"/>
+      <c r="H53" s="63"/>
+      <c r="I53" s="63"/>
+      <c r="J53" s="63"/>
+      <c r="K53" s="63"/>
+      <c r="L53" s="63"/>
+      <c r="M53" s="63"/>
+      <c r="N53" s="63"/>
+      <c r="O53" s="74"/>
+      <c r="P53" s="47"/>
+    </row>
+    <row r="54" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="60"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="63"/>
+      <c r="F54" s="63"/>
+      <c r="G54" s="63"/>
+      <c r="H54" s="63"/>
+      <c r="I54" s="63"/>
+      <c r="J54" s="63"/>
+      <c r="K54" s="63"/>
+      <c r="L54" s="63"/>
+      <c r="M54" s="63"/>
+      <c r="N54" s="63"/>
+      <c r="O54" s="74"/>
+      <c r="P54" s="47"/>
+    </row>
+    <row r="55" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="60"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
+      <c r="I55" s="63"/>
+      <c r="J55" s="63"/>
+      <c r="K55" s="63"/>
+      <c r="L55" s="63"/>
+      <c r="M55" s="63"/>
+      <c r="N55" s="63"/>
+      <c r="O55" s="74"/>
+      <c r="P55" s="47"/>
+    </row>
+    <row r="56" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="60"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="63"/>
+      <c r="G56" s="63"/>
+      <c r="H56" s="63"/>
+      <c r="I56" s="63"/>
+      <c r="J56" s="63"/>
+      <c r="K56" s="63"/>
+      <c r="L56" s="63"/>
+      <c r="M56" s="63"/>
+      <c r="N56" s="63"/>
+      <c r="O56" s="74"/>
+      <c r="P56" s="47"/>
+    </row>
+    <row r="57" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="60"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="63"/>
+      <c r="G57" s="63"/>
+      <c r="H57" s="63"/>
+      <c r="I57" s="63"/>
+      <c r="J57" s="63"/>
+      <c r="K57" s="63"/>
+      <c r="L57" s="63"/>
+      <c r="M57" s="63"/>
+      <c r="N57" s="63"/>
+      <c r="O57" s="74"/>
+      <c r="P57" s="47"/>
+    </row>
+    <row r="58" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C58" s="60"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="63"/>
+      <c r="F58" s="63"/>
+      <c r="G58" s="63"/>
+      <c r="H58" s="63"/>
+      <c r="I58" s="63"/>
+      <c r="J58" s="63"/>
+      <c r="K58" s="63"/>
+      <c r="L58" s="63"/>
+      <c r="M58" s="63"/>
+      <c r="N58" s="63"/>
+      <c r="O58" s="74"/>
+      <c r="P58" s="47"/>
+    </row>
+    <row r="59" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="60"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="63"/>
+      <c r="F59" s="63"/>
+      <c r="G59" s="63"/>
+      <c r="H59" s="63"/>
+      <c r="I59" s="63"/>
+      <c r="J59" s="63"/>
+      <c r="K59" s="63"/>
+      <c r="L59" s="63"/>
+      <c r="M59" s="63"/>
+      <c r="N59" s="63"/>
+      <c r="O59" s="74"/>
+      <c r="P59" s="47"/>
+    </row>
+    <row r="60" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="60"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="63"/>
+      <c r="F60" s="63"/>
+      <c r="G60" s="63"/>
+      <c r="H60" s="63"/>
+      <c r="I60" s="63"/>
+      <c r="J60" s="63"/>
+      <c r="K60" s="63"/>
+      <c r="L60" s="63"/>
+      <c r="M60" s="63"/>
+      <c r="N60" s="63"/>
+      <c r="O60" s="74"/>
+      <c r="P60" s="47"/>
+    </row>
+    <row r="61" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="60"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="63"/>
+      <c r="F61" s="63"/>
+      <c r="G61" s="63"/>
+      <c r="H61" s="63"/>
+      <c r="I61" s="63"/>
+      <c r="J61" s="63"/>
+      <c r="K61" s="63"/>
+      <c r="L61" s="63"/>
+      <c r="M61" s="63"/>
+      <c r="N61" s="63"/>
+      <c r="O61" s="74"/>
+      <c r="P61" s="47"/>
+    </row>
+    <row r="62" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="60"/>
+      <c r="D62" s="44"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
+      <c r="H62" s="63"/>
+      <c r="I62" s="63"/>
+      <c r="J62" s="63"/>
+      <c r="K62" s="63"/>
+      <c r="L62" s="63"/>
+      <c r="M62" s="63"/>
+      <c r="N62" s="63"/>
+      <c r="O62" s="74"/>
+      <c r="P62" s="47"/>
+    </row>
+    <row r="63" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C63" s="60"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="63"/>
+      <c r="F63" s="63"/>
+      <c r="G63" s="63"/>
+      <c r="H63" s="63"/>
+      <c r="I63" s="63"/>
+      <c r="J63" s="63"/>
+      <c r="K63" s="63"/>
+      <c r="L63" s="63"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="63"/>
+      <c r="O63" s="74"/>
+      <c r="P63" s="47"/>
+    </row>
+    <row r="64" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="60"/>
+      <c r="D64" s="44"/>
+      <c r="E64" s="63"/>
+      <c r="F64" s="63"/>
+      <c r="G64" s="63"/>
+      <c r="H64" s="63"/>
+      <c r="I64" s="63"/>
+      <c r="J64" s="63"/>
+      <c r="K64" s="63"/>
+      <c r="L64" s="63"/>
+      <c r="M64" s="63"/>
+      <c r="N64" s="63"/>
+      <c r="O64" s="74"/>
+      <c r="P64" s="47"/>
+    </row>
+    <row r="65" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="60"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="63"/>
+      <c r="F65" s="63"/>
+      <c r="G65" s="63"/>
+      <c r="H65" s="63"/>
+      <c r="I65" s="63"/>
+      <c r="J65" s="63"/>
+      <c r="K65" s="63"/>
+      <c r="L65" s="63"/>
+      <c r="M65" s="63"/>
+      <c r="N65" s="63"/>
+      <c r="O65" s="74"/>
+      <c r="P65" s="47"/>
+    </row>
+    <row r="66" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="60"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="63"/>
+      <c r="F66" s="63"/>
+      <c r="G66" s="63"/>
+      <c r="H66" s="63"/>
+      <c r="I66" s="63"/>
+      <c r="J66" s="63"/>
+      <c r="K66" s="63"/>
+      <c r="L66" s="63"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="63"/>
+      <c r="O66" s="74"/>
+      <c r="P66" s="47"/>
+    </row>
+    <row r="67" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="60"/>
+      <c r="D67" s="44"/>
+      <c r="E67" s="63"/>
+      <c r="F67" s="63"/>
+      <c r="G67" s="63"/>
+      <c r="H67" s="63"/>
+      <c r="I67" s="63"/>
+      <c r="J67" s="63"/>
+      <c r="K67" s="63"/>
+      <c r="L67" s="63"/>
+      <c r="M67" s="63"/>
+      <c r="N67" s="63"/>
+      <c r="O67" s="74"/>
+      <c r="P67" s="47"/>
+    </row>
+    <row r="68" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="60"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="63"/>
+      <c r="F68" s="63"/>
+      <c r="G68" s="63"/>
+      <c r="H68" s="63"/>
+      <c r="I68" s="63"/>
+      <c r="J68" s="63"/>
+      <c r="K68" s="63"/>
+      <c r="L68" s="63"/>
+      <c r="M68" s="63"/>
+      <c r="N68" s="63"/>
+      <c r="O68" s="74"/>
+      <c r="P68" s="47"/>
+    </row>
+    <row r="69" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="60"/>
+      <c r="D69" s="44"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
+      <c r="I69" s="63"/>
+      <c r="J69" s="63"/>
+      <c r="K69" s="63"/>
+      <c r="L69" s="63"/>
+      <c r="M69" s="63"/>
+      <c r="N69" s="63"/>
+      <c r="O69" s="74"/>
+      <c r="P69" s="47"/>
+    </row>
+    <row r="70" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="60"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="63"/>
+      <c r="G70" s="63"/>
+      <c r="H70" s="63"/>
+      <c r="I70" s="63"/>
+      <c r="J70" s="63"/>
+      <c r="K70" s="63"/>
+      <c r="L70" s="63"/>
+      <c r="M70" s="63"/>
+      <c r="N70" s="63"/>
+      <c r="O70" s="74"/>
+      <c r="P70" s="47"/>
+    </row>
+    <row r="71" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C71" s="60"/>
+      <c r="D71" s="44"/>
+      <c r="E71" s="63"/>
+      <c r="F71" s="63"/>
+      <c r="G71" s="63"/>
+      <c r="H71" s="63"/>
+      <c r="I71" s="63"/>
+      <c r="J71" s="63"/>
+      <c r="K71" s="63"/>
+      <c r="L71" s="63"/>
+      <c r="M71" s="63"/>
+      <c r="N71" s="63"/>
+      <c r="O71" s="74"/>
+      <c r="P71" s="47"/>
+    </row>
+    <row r="72" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C72" s="60"/>
+      <c r="D72" s="44"/>
+      <c r="E72" s="63"/>
+      <c r="F72" s="63"/>
+      <c r="G72" s="63"/>
+      <c r="H72" s="63"/>
+      <c r="I72" s="63"/>
+      <c r="J72" s="63"/>
+      <c r="K72" s="63"/>
+      <c r="L72" s="63"/>
+      <c r="M72" s="63"/>
+      <c r="N72" s="63"/>
+      <c r="O72" s="74"/>
+      <c r="P72" s="47"/>
+    </row>
+    <row r="73" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C73" s="60"/>
+      <c r="D73" s="44"/>
+      <c r="E73" s="63"/>
+      <c r="F73" s="63"/>
+      <c r="G73" s="63"/>
+      <c r="H73" s="63"/>
+      <c r="I73" s="63"/>
+      <c r="J73" s="63"/>
+      <c r="K73" s="63"/>
+      <c r="L73" s="63"/>
+      <c r="M73" s="63"/>
+      <c r="N73" s="63"/>
+      <c r="O73" s="74"/>
+      <c r="P73" s="47"/>
+    </row>
+    <row r="74" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C74" s="60"/>
+      <c r="D74" s="44"/>
+      <c r="E74" s="63"/>
+      <c r="F74" s="63"/>
+      <c r="G74" s="63"/>
+      <c r="H74" s="63"/>
+      <c r="I74" s="63"/>
+      <c r="J74" s="63"/>
+      <c r="K74" s="63"/>
+      <c r="L74" s="63"/>
+      <c r="M74" s="63"/>
+      <c r="N74" s="63"/>
+      <c r="O74" s="74"/>
+      <c r="P74" s="47"/>
+    </row>
+    <row r="75" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C75" s="60"/>
+      <c r="D75" s="44"/>
+      <c r="E75" s="63"/>
+      <c r="F75" s="63"/>
+      <c r="G75" s="63"/>
+      <c r="H75" s="63"/>
+      <c r="I75" s="63"/>
+      <c r="J75" s="63"/>
+      <c r="K75" s="63"/>
+      <c r="L75" s="63"/>
+      <c r="M75" s="63"/>
+      <c r="N75" s="63"/>
+      <c r="O75" s="74"/>
+      <c r="P75" s="47"/>
+    </row>
+    <row r="76" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C76" s="60"/>
+      <c r="D76" s="44"/>
+      <c r="E76" s="63"/>
+      <c r="F76" s="63"/>
+      <c r="G76" s="63"/>
+      <c r="H76" s="63"/>
+      <c r="I76" s="63"/>
+      <c r="J76" s="63"/>
+      <c r="K76" s="63"/>
+      <c r="L76" s="63"/>
+      <c r="M76" s="63"/>
+      <c r="N76" s="63"/>
+      <c r="O76" s="74"/>
+      <c r="P76" s="47"/>
+    </row>
+    <row r="77" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C77" s="60"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="63"/>
+      <c r="F77" s="63"/>
+      <c r="G77" s="63"/>
+      <c r="H77" s="63"/>
+      <c r="I77" s="63"/>
+      <c r="J77" s="63"/>
+      <c r="K77" s="63"/>
+      <c r="L77" s="63"/>
+      <c r="M77" s="63"/>
+      <c r="N77" s="63"/>
+      <c r="O77" s="74"/>
+      <c r="P77" s="47"/>
+    </row>
+    <row r="78" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C78" s="60"/>
+      <c r="D78" s="44"/>
+      <c r="E78" s="63"/>
+      <c r="F78" s="63"/>
+      <c r="G78" s="63"/>
+      <c r="H78" s="63"/>
+      <c r="I78" s="63"/>
+      <c r="J78" s="63"/>
+      <c r="K78" s="63"/>
+      <c r="L78" s="63"/>
+      <c r="M78" s="63"/>
+      <c r="N78" s="63"/>
+      <c r="O78" s="74"/>
+      <c r="P78" s="47"/>
+    </row>
+    <row r="79" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C79" s="60"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="63"/>
+      <c r="F79" s="63"/>
+      <c r="G79" s="63"/>
+      <c r="H79" s="63"/>
+      <c r="I79" s="63"/>
+      <c r="J79" s="63"/>
+      <c r="K79" s="63"/>
+      <c r="L79" s="63"/>
+      <c r="M79" s="63"/>
+      <c r="N79" s="63"/>
+      <c r="O79" s="74"/>
+      <c r="P79" s="47"/>
+    </row>
+    <row r="80" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C80" s="60"/>
+      <c r="D80" s="44"/>
+      <c r="E80" s="63"/>
+      <c r="F80" s="63"/>
+      <c r="G80" s="63"/>
+      <c r="H80" s="63"/>
+      <c r="I80" s="63"/>
+      <c r="J80" s="63"/>
+      <c r="K80" s="63"/>
+      <c r="L80" s="63"/>
+      <c r="M80" s="63"/>
+      <c r="N80" s="63"/>
+      <c r="O80" s="74"/>
+      <c r="P80" s="47"/>
+    </row>
+    <row r="81" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C81" s="60"/>
+      <c r="D81" s="44"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="63"/>
+      <c r="I81" s="63"/>
+      <c r="J81" s="63"/>
+      <c r="K81" s="63"/>
+      <c r="L81" s="63"/>
+      <c r="M81" s="63"/>
+      <c r="N81" s="63"/>
+      <c r="O81" s="74"/>
+      <c r="P81" s="47"/>
+    </row>
+    <row r="82" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C82" s="60"/>
+      <c r="D82" s="44"/>
+      <c r="E82" s="63"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="63"/>
+      <c r="I82" s="63"/>
+      <c r="J82" s="63"/>
+      <c r="K82" s="63"/>
+      <c r="L82" s="63"/>
+      <c r="M82" s="63"/>
+      <c r="N82" s="63"/>
+      <c r="O82" s="74"/>
+      <c r="P82" s="47"/>
+    </row>
+    <row r="83" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C83" s="60"/>
+      <c r="D83" s="44"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="63"/>
+      <c r="I83" s="63"/>
+      <c r="J83" s="63"/>
+      <c r="K83" s="63"/>
+      <c r="L83" s="63"/>
+      <c r="M83" s="63"/>
+      <c r="N83" s="63"/>
+      <c r="O83" s="74"/>
+      <c r="P83" s="47"/>
+    </row>
+    <row r="84" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C84" s="60"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="63"/>
+      <c r="F84" s="63"/>
+      <c r="G84" s="63"/>
+      <c r="H84" s="63"/>
+      <c r="I84" s="63"/>
+      <c r="J84" s="63"/>
+      <c r="K84" s="63"/>
+      <c r="L84" s="63"/>
+      <c r="M84" s="63"/>
+      <c r="N84" s="63"/>
+      <c r="O84" s="74"/>
+      <c r="P84" s="47"/>
+    </row>
+    <row r="85" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C85" s="60"/>
+      <c r="D85" s="44"/>
+      <c r="E85" s="63"/>
+      <c r="F85" s="63"/>
+      <c r="G85" s="63"/>
+      <c r="H85" s="63"/>
+      <c r="I85" s="63"/>
+      <c r="J85" s="63"/>
+      <c r="K85" s="63"/>
+      <c r="L85" s="63"/>
+      <c r="M85" s="63"/>
+      <c r="N85" s="63"/>
+      <c r="O85" s="74"/>
+      <c r="P85" s="47"/>
+    </row>
+    <row r="86" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C86" s="60"/>
+      <c r="D86" s="44"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="63"/>
+      <c r="G86" s="63"/>
+      <c r="H86" s="63"/>
+      <c r="I86" s="63"/>
+      <c r="J86" s="63"/>
+      <c r="K86" s="63"/>
+      <c r="L86" s="63"/>
+      <c r="M86" s="63"/>
+      <c r="N86" s="63"/>
+      <c r="O86" s="74"/>
+      <c r="P86" s="47"/>
+    </row>
+    <row r="87" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C87" s="60"/>
+      <c r="D87" s="44"/>
+      <c r="E87" s="63"/>
+      <c r="F87" s="63"/>
+      <c r="G87" s="63"/>
+      <c r="H87" s="63"/>
+      <c r="I87" s="63"/>
+      <c r="J87" s="63"/>
+      <c r="K87" s="63"/>
+      <c r="L87" s="63"/>
+      <c r="M87" s="63"/>
+      <c r="N87" s="63"/>
+      <c r="O87" s="74"/>
+      <c r="P87" s="47"/>
+    </row>
+    <row r="88" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C88" s="60"/>
+      <c r="D88" s="44"/>
+      <c r="E88" s="63"/>
+      <c r="F88" s="63"/>
+      <c r="G88" s="63"/>
+      <c r="H88" s="63"/>
+      <c r="I88" s="63"/>
+      <c r="J88" s="63"/>
+      <c r="K88" s="63"/>
+      <c r="L88" s="63"/>
+      <c r="M88" s="63"/>
+      <c r="N88" s="63"/>
+      <c r="O88" s="74"/>
+      <c r="P88" s="47"/>
+    </row>
+    <row r="89" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C89" s="60"/>
+      <c r="D89" s="44"/>
+      <c r="E89" s="63"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="63"/>
+      <c r="H89" s="63"/>
+      <c r="I89" s="63"/>
+      <c r="J89" s="63"/>
+      <c r="K89" s="63"/>
+      <c r="L89" s="63"/>
+      <c r="M89" s="63"/>
+      <c r="N89" s="63"/>
+      <c r="O89" s="74"/>
+      <c r="P89" s="47"/>
+    </row>
+    <row r="90" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C90" s="60"/>
+      <c r="D90" s="44"/>
+      <c r="E90" s="63"/>
+      <c r="F90" s="63"/>
+      <c r="G90" s="63"/>
+      <c r="H90" s="63"/>
+      <c r="I90" s="63"/>
+      <c r="J90" s="63"/>
+      <c r="K90" s="63"/>
+      <c r="L90" s="63"/>
+      <c r="M90" s="63"/>
+      <c r="N90" s="63"/>
+      <c r="O90" s="74"/>
+      <c r="P90" s="47"/>
+    </row>
+    <row r="91" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C91" s="60"/>
+      <c r="D91" s="44"/>
+      <c r="E91" s="63"/>
+      <c r="F91" s="63"/>
+      <c r="G91" s="63"/>
+      <c r="H91" s="63"/>
+      <c r="I91" s="63"/>
+      <c r="J91" s="63"/>
+      <c r="K91" s="63"/>
+      <c r="L91" s="63"/>
+      <c r="M91" s="63"/>
+      <c r="N91" s="63"/>
+      <c r="O91" s="74"/>
+      <c r="P91" s="47"/>
+    </row>
+    <row r="92" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C92" s="60"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="63"/>
+      <c r="F92" s="63"/>
+      <c r="G92" s="63"/>
+      <c r="H92" s="63"/>
+      <c r="I92" s="63"/>
+      <c r="J92" s="63"/>
+      <c r="K92" s="63"/>
+      <c r="L92" s="63"/>
+      <c r="M92" s="63"/>
+      <c r="N92" s="63"/>
+      <c r="O92" s="74"/>
+      <c r="P92" s="47"/>
+    </row>
+    <row r="93" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C93" s="60"/>
+      <c r="D93" s="44"/>
+      <c r="E93" s="63"/>
+      <c r="F93" s="63"/>
+      <c r="G93" s="63"/>
+      <c r="H93" s="63"/>
+      <c r="I93" s="63"/>
+      <c r="J93" s="63"/>
+      <c r="K93" s="63"/>
+      <c r="L93" s="63"/>
+      <c r="M93" s="63"/>
+      <c r="N93" s="63"/>
+      <c r="O93" s="74"/>
+      <c r="P93" s="47"/>
+    </row>
+    <row r="94" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C94" s="60"/>
+      <c r="D94" s="44"/>
+      <c r="E94" s="63"/>
+      <c r="F94" s="63"/>
+      <c r="G94" s="63"/>
+      <c r="H94" s="63"/>
+      <c r="I94" s="63"/>
+      <c r="J94" s="63"/>
+      <c r="K94" s="63"/>
+      <c r="L94" s="63"/>
+      <c r="M94" s="63"/>
+      <c r="N94" s="63"/>
+      <c r="O94" s="74"/>
+      <c r="P94" s="47"/>
+    </row>
+    <row r="95" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C95" s="60"/>
+      <c r="D95" s="44"/>
+      <c r="E95" s="63"/>
+      <c r="F95" s="63"/>
+      <c r="G95" s="63"/>
+      <c r="H95" s="63"/>
+      <c r="I95" s="63"/>
+      <c r="J95" s="63"/>
+      <c r="K95" s="63"/>
+      <c r="L95" s="63"/>
+      <c r="M95" s="63"/>
+      <c r="N95" s="63"/>
+      <c r="O95" s="74"/>
+      <c r="P95" s="47"/>
+    </row>
+    <row r="96" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C96" s="60"/>
+      <c r="D96" s="44"/>
+      <c r="E96" s="63"/>
+      <c r="F96" s="63"/>
+      <c r="G96" s="63"/>
+      <c r="H96" s="63"/>
+      <c r="I96" s="63"/>
+      <c r="J96" s="63"/>
+      <c r="K96" s="63"/>
+      <c r="L96" s="63"/>
+      <c r="M96" s="63"/>
+      <c r="N96" s="63"/>
+      <c r="O96" s="74"/>
+      <c r="P96" s="47"/>
+    </row>
+    <row r="97" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C97" s="60"/>
+      <c r="D97" s="44"/>
+      <c r="E97" s="63"/>
+      <c r="F97" s="63"/>
+      <c r="G97" s="63"/>
+      <c r="H97" s="63"/>
+      <c r="I97" s="63"/>
+      <c r="J97" s="63"/>
+      <c r="K97" s="63"/>
+      <c r="L97" s="63"/>
+      <c r="M97" s="63"/>
+      <c r="N97" s="63"/>
+      <c r="O97" s="74"/>
+      <c r="P97" s="47"/>
+    </row>
+    <row r="98" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C98" s="60"/>
+      <c r="D98" s="44"/>
+      <c r="E98" s="63"/>
+      <c r="F98" s="63"/>
+      <c r="G98" s="63"/>
+      <c r="H98" s="63"/>
+      <c r="I98" s="63"/>
+      <c r="J98" s="63"/>
+      <c r="K98" s="63"/>
+      <c r="L98" s="63"/>
+      <c r="M98" s="63"/>
+      <c r="N98" s="63"/>
+      <c r="O98" s="74"/>
+      <c r="P98" s="47"/>
+    </row>
+    <row r="99" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C99" s="60"/>
+      <c r="D99" s="44"/>
+      <c r="E99" s="63"/>
+      <c r="F99" s="63"/>
+      <c r="G99" s="63"/>
+      <c r="H99" s="63"/>
+      <c r="I99" s="63"/>
+      <c r="J99" s="63"/>
+      <c r="K99" s="63"/>
+      <c r="L99" s="63"/>
+      <c r="M99" s="63"/>
+      <c r="N99" s="63"/>
+      <c r="O99" s="74"/>
+      <c r="P99" s="47"/>
+    </row>
+    <row r="100" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C100" s="60"/>
+      <c r="D100" s="44"/>
+      <c r="E100" s="63"/>
+      <c r="F100" s="63"/>
+      <c r="G100" s="63"/>
+      <c r="H100" s="63"/>
+      <c r="I100" s="63"/>
+      <c r="J100" s="63"/>
+      <c r="K100" s="63"/>
+      <c r="L100" s="63"/>
+      <c r="M100" s="63"/>
+      <c r="N100" s="63"/>
+      <c r="O100" s="74"/>
+      <c r="P100" s="47"/>
+    </row>
+    <row r="101" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C101" s="60"/>
+      <c r="D101" s="44"/>
+      <c r="E101" s="63"/>
+      <c r="F101" s="63"/>
+      <c r="G101" s="63"/>
+      <c r="H101" s="63"/>
+      <c r="I101" s="63"/>
+      <c r="J101" s="63"/>
+      <c r="K101" s="63"/>
+      <c r="L101" s="63"/>
+      <c r="M101" s="63"/>
+      <c r="N101" s="63"/>
+      <c r="O101" s="74"/>
+      <c r="P101" s="47"/>
+    </row>
+    <row r="102" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C102" s="60"/>
+      <c r="D102" s="44"/>
+      <c r="E102" s="63"/>
+      <c r="F102" s="63"/>
+      <c r="G102" s="63"/>
+      <c r="H102" s="63"/>
+      <c r="I102" s="63"/>
+      <c r="J102" s="63"/>
+      <c r="K102" s="63"/>
+      <c r="L102" s="63"/>
+      <c r="M102" s="63"/>
+      <c r="N102" s="63"/>
+      <c r="O102" s="74"/>
+      <c r="P102" s="47"/>
+    </row>
+    <row r="103" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="60"/>
+      <c r="D103" s="44"/>
+      <c r="E103" s="63"/>
+      <c r="F103" s="63"/>
+      <c r="G103" s="63"/>
+      <c r="H103" s="63"/>
+      <c r="I103" s="63"/>
+      <c r="J103" s="63"/>
+      <c r="K103" s="63"/>
+      <c r="L103" s="63"/>
+      <c r="M103" s="63"/>
+      <c r="N103" s="63"/>
+      <c r="O103" s="74"/>
+      <c r="P103" s="47"/>
+    </row>
+    <row r="104" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C104" s="60"/>
+      <c r="D104" s="44"/>
+      <c r="E104" s="63"/>
+      <c r="F104" s="63"/>
+      <c r="G104" s="63"/>
+      <c r="H104" s="63"/>
+      <c r="I104" s="63"/>
+      <c r="J104" s="63"/>
+      <c r="K104" s="63"/>
+      <c r="L104" s="63"/>
+      <c r="M104" s="63"/>
+      <c r="N104" s="63"/>
+      <c r="O104" s="74"/>
+      <c r="P104" s="47"/>
+    </row>
+    <row r="105" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C105" s="60"/>
+      <c r="D105" s="44"/>
+      <c r="E105" s="63"/>
+      <c r="F105" s="63"/>
+      <c r="G105" s="63"/>
+      <c r="H105" s="63"/>
+      <c r="I105" s="63"/>
+      <c r="J105" s="63"/>
+      <c r="K105" s="63"/>
+      <c r="L105" s="63"/>
+      <c r="M105" s="63"/>
+      <c r="N105" s="63"/>
+      <c r="O105" s="74"/>
+      <c r="P105" s="47"/>
+    </row>
+    <row r="106" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C106" s="60"/>
+      <c r="D106" s="44"/>
+      <c r="E106" s="63"/>
+      <c r="F106" s="63"/>
+      <c r="G106" s="63"/>
+      <c r="H106" s="63"/>
+      <c r="I106" s="63"/>
+      <c r="J106" s="63"/>
+      <c r="K106" s="63"/>
+      <c r="L106" s="63"/>
+      <c r="M106" s="63"/>
+      <c r="N106" s="63"/>
+      <c r="O106" s="74"/>
+      <c r="P106" s="47"/>
+    </row>
+    <row r="107" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C107" s="60"/>
+      <c r="D107" s="44"/>
+      <c r="E107" s="63"/>
+      <c r="F107" s="63"/>
+      <c r="G107" s="63"/>
+      <c r="H107" s="63"/>
+      <c r="I107" s="63"/>
+      <c r="J107" s="63"/>
+      <c r="K107" s="63"/>
+      <c r="L107" s="63"/>
+      <c r="M107" s="63"/>
+      <c r="N107" s="63"/>
+      <c r="O107" s="74"/>
+      <c r="P107" s="47"/>
+    </row>
+    <row r="108" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C108" s="60"/>
+      <c r="D108" s="44"/>
+      <c r="E108" s="63"/>
+      <c r="F108" s="63"/>
+      <c r="G108" s="63"/>
+      <c r="H108" s="63"/>
+      <c r="I108" s="63"/>
+      <c r="J108" s="63"/>
+      <c r="K108" s="63"/>
+      <c r="L108" s="63"/>
+      <c r="M108" s="63"/>
+      <c r="N108" s="63"/>
+      <c r="O108" s="74"/>
+      <c r="P108" s="47"/>
+    </row>
+    <row r="109" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C109" s="60"/>
+      <c r="D109" s="44"/>
+      <c r="E109" s="63"/>
+      <c r="F109" s="63"/>
+      <c r="G109" s="63"/>
+      <c r="H109" s="63"/>
+      <c r="I109" s="63"/>
+      <c r="J109" s="63"/>
+      <c r="K109" s="63"/>
+      <c r="L109" s="63"/>
+      <c r="M109" s="63"/>
+      <c r="N109" s="63"/>
+      <c r="O109" s="74"/>
+      <c r="P109" s="47"/>
+    </row>
+    <row r="110" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C110" s="60"/>
+      <c r="D110" s="44"/>
+      <c r="E110" s="63"/>
+      <c r="F110" s="63"/>
+      <c r="G110" s="63"/>
+      <c r="H110" s="63"/>
+      <c r="I110" s="63"/>
+      <c r="J110" s="63"/>
+      <c r="K110" s="63"/>
+      <c r="L110" s="63"/>
+      <c r="M110" s="63"/>
+      <c r="N110" s="63"/>
+      <c r="O110" s="74"/>
+      <c r="P110" s="47"/>
+    </row>
+    <row r="111" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C111" s="60"/>
+      <c r="D111" s="44"/>
+      <c r="E111" s="63"/>
+      <c r="F111" s="63"/>
+      <c r="G111" s="63"/>
+      <c r="H111" s="63"/>
+      <c r="I111" s="63"/>
+      <c r="J111" s="63"/>
+      <c r="K111" s="63"/>
+      <c r="L111" s="63"/>
+      <c r="M111" s="63"/>
+      <c r="N111" s="63"/>
+      <c r="O111" s="74"/>
+      <c r="P111" s="47"/>
+    </row>
+    <row r="112" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C112" s="60"/>
+      <c r="D112" s="44"/>
+      <c r="E112" s="63"/>
+      <c r="F112" s="63"/>
+      <c r="G112" s="63"/>
+      <c r="H112" s="63"/>
+      <c r="I112" s="63"/>
+      <c r="J112" s="63"/>
+      <c r="K112" s="63"/>
+      <c r="L112" s="63"/>
+      <c r="M112" s="63"/>
+      <c r="N112" s="63"/>
+      <c r="O112" s="74"/>
+      <c r="P112" s="47"/>
+    </row>
+    <row r="113" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C113" s="60"/>
+      <c r="D113" s="44"/>
+      <c r="E113" s="63"/>
+      <c r="F113" s="63"/>
+      <c r="G113" s="63"/>
+      <c r="H113" s="63"/>
+      <c r="I113" s="63"/>
+      <c r="J113" s="63"/>
+      <c r="K113" s="63"/>
+      <c r="L113" s="63"/>
+      <c r="M113" s="63"/>
+      <c r="N113" s="63"/>
+      <c r="O113" s="74"/>
+      <c r="P113" s="47"/>
+    </row>
+    <row r="114" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C114" s="60"/>
+      <c r="D114" s="44"/>
+      <c r="E114" s="63"/>
+      <c r="F114" s="63"/>
+      <c r="G114" s="63"/>
+      <c r="H114" s="63"/>
+      <c r="I114" s="63"/>
+      <c r="J114" s="63"/>
+      <c r="K114" s="63"/>
+      <c r="L114" s="63"/>
+      <c r="M114" s="63"/>
+      <c r="N114" s="63"/>
+      <c r="O114" s="74"/>
+      <c r="P114" s="47"/>
+    </row>
+    <row r="115" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C115" s="60"/>
+      <c r="D115" s="44"/>
+      <c r="E115" s="63"/>
+      <c r="F115" s="63"/>
+      <c r="G115" s="63"/>
+      <c r="H115" s="63"/>
+      <c r="I115" s="63"/>
+      <c r="J115" s="63"/>
+      <c r="K115" s="63"/>
+      <c r="L115" s="63"/>
+      <c r="M115" s="63"/>
+      <c r="N115" s="63"/>
+      <c r="O115" s="74"/>
+      <c r="P115" s="47"/>
+    </row>
+    <row r="116" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C116" s="60"/>
+      <c r="D116" s="44"/>
+      <c r="E116" s="63"/>
+      <c r="F116" s="63"/>
+      <c r="G116" s="63"/>
+      <c r="H116" s="63"/>
+      <c r="I116" s="63"/>
+      <c r="J116" s="63"/>
+      <c r="K116" s="63"/>
+      <c r="L116" s="63"/>
+      <c r="M116" s="63"/>
+      <c r="N116" s="63"/>
+      <c r="O116" s="74"/>
+      <c r="P116" s="47"/>
+    </row>
+    <row r="117" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C117" s="60"/>
+      <c r="D117" s="44"/>
+      <c r="E117" s="63"/>
+      <c r="F117" s="63"/>
+      <c r="G117" s="63"/>
+      <c r="H117" s="63"/>
+      <c r="I117" s="63"/>
+      <c r="J117" s="63"/>
+      <c r="K117" s="63"/>
+      <c r="L117" s="63"/>
+      <c r="M117" s="63"/>
+      <c r="N117" s="63"/>
+      <c r="O117" s="74"/>
+      <c r="P117" s="47"/>
+    </row>
+    <row r="118" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C118" s="60"/>
+      <c r="D118" s="44"/>
+      <c r="E118" s="63"/>
+      <c r="F118" s="63"/>
+      <c r="G118" s="63"/>
+      <c r="H118" s="63"/>
+      <c r="I118" s="63"/>
+      <c r="J118" s="63"/>
+      <c r="K118" s="63"/>
+      <c r="L118" s="63"/>
+      <c r="M118" s="63"/>
+      <c r="N118" s="63"/>
+      <c r="O118" s="74"/>
+      <c r="P118" s="47"/>
+    </row>
+    <row r="119" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C119" s="60"/>
+      <c r="D119" s="44"/>
+      <c r="E119" s="63"/>
+      <c r="F119" s="63"/>
+      <c r="G119" s="63"/>
+      <c r="H119" s="63"/>
+      <c r="I119" s="63"/>
+      <c r="J119" s="63"/>
+      <c r="K119" s="63"/>
+      <c r="L119" s="63"/>
+      <c r="M119" s="63"/>
+      <c r="N119" s="63"/>
+      <c r="O119" s="74"/>
+      <c r="P119" s="47"/>
+    </row>
+    <row r="120" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C120" s="60"/>
+      <c r="D120" s="44"/>
+      <c r="E120" s="63"/>
+      <c r="F120" s="63"/>
+      <c r="G120" s="63"/>
+      <c r="H120" s="63"/>
+      <c r="I120" s="63"/>
+      <c r="J120" s="63"/>
+      <c r="K120" s="63"/>
+      <c r="L120" s="63"/>
+      <c r="M120" s="63"/>
+      <c r="N120" s="63"/>
+      <c r="O120" s="74"/>
+      <c r="P120" s="47"/>
+    </row>
+    <row r="121" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C121" s="60"/>
+      <c r="D121" s="44"/>
+      <c r="E121" s="63"/>
+      <c r="F121" s="63"/>
+      <c r="G121" s="63"/>
+      <c r="H121" s="63"/>
+      <c r="I121" s="63"/>
+      <c r="J121" s="63"/>
+      <c r="K121" s="63"/>
+      <c r="L121" s="63"/>
+      <c r="M121" s="63"/>
+      <c r="N121" s="63"/>
+      <c r="O121" s="74"/>
+      <c r="P121" s="47"/>
+    </row>
+    <row r="122" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C122" s="60"/>
+      <c r="D122" s="44"/>
+      <c r="E122" s="63"/>
+      <c r="F122" s="63"/>
+      <c r="G122" s="63"/>
+      <c r="H122" s="63"/>
+      <c r="I122" s="63"/>
+      <c r="J122" s="63"/>
+      <c r="K122" s="63"/>
+      <c r="L122" s="63"/>
+      <c r="M122" s="63"/>
+      <c r="N122" s="63"/>
+      <c r="O122" s="74"/>
+      <c r="P122" s="47"/>
+    </row>
+    <row r="123" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C123" s="60"/>
+      <c r="D123" s="44"/>
+      <c r="E123" s="63"/>
+      <c r="F123" s="63"/>
+      <c r="G123" s="63"/>
+      <c r="H123" s="63"/>
+      <c r="I123" s="63"/>
+      <c r="J123" s="63"/>
+      <c r="K123" s="63"/>
+      <c r="L123" s="63"/>
+      <c r="M123" s="63"/>
+      <c r="N123" s="63"/>
+      <c r="O123" s="74"/>
+      <c r="P123" s="47"/>
+    </row>
+    <row r="124" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C124" s="60"/>
+      <c r="D124" s="44"/>
+      <c r="E124" s="63"/>
+      <c r="F124" s="63"/>
+      <c r="G124" s="63"/>
+      <c r="H124" s="63"/>
+      <c r="I124" s="63"/>
+      <c r="J124" s="63"/>
+      <c r="K124" s="63"/>
+      <c r="L124" s="63"/>
+      <c r="M124" s="63"/>
+      <c r="N124" s="63"/>
+      <c r="O124" s="74"/>
+      <c r="P124" s="47"/>
+    </row>
+    <row r="125" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C125" s="60"/>
+      <c r="D125" s="44"/>
+      <c r="E125" s="63"/>
+      <c r="F125" s="63"/>
+      <c r="G125" s="63"/>
+      <c r="H125" s="63"/>
+      <c r="I125" s="63"/>
+      <c r="J125" s="63"/>
+      <c r="K125" s="63"/>
+      <c r="L125" s="63"/>
+      <c r="M125" s="63"/>
+      <c r="N125" s="63"/>
+      <c r="O125" s="74"/>
+      <c r="P125" s="47"/>
+    </row>
+    <row r="126" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C126" s="60"/>
+      <c r="D126" s="44"/>
+      <c r="E126" s="63"/>
+      <c r="F126" s="63"/>
+      <c r="G126" s="63"/>
+      <c r="H126" s="63"/>
+      <c r="I126" s="63"/>
+      <c r="J126" s="63"/>
+      <c r="K126" s="63"/>
+      <c r="L126" s="63"/>
+      <c r="M126" s="63"/>
+      <c r="N126" s="63"/>
+      <c r="O126" s="74"/>
+      <c r="P126" s="47"/>
+    </row>
+    <row r="127" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C127" s="60"/>
+      <c r="D127" s="44"/>
+      <c r="E127" s="63"/>
+      <c r="F127" s="63"/>
+      <c r="G127" s="63"/>
+      <c r="H127" s="63"/>
+      <c r="I127" s="63"/>
+      <c r="J127" s="63"/>
+      <c r="K127" s="63"/>
+      <c r="L127" s="63"/>
+      <c r="M127" s="63"/>
+      <c r="N127" s="63"/>
+      <c r="O127" s="74"/>
+      <c r="P127" s="47"/>
+    </row>
+    <row r="128" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C128" s="60"/>
+      <c r="D128" s="44"/>
+      <c r="E128" s="63"/>
+      <c r="F128" s="63"/>
+      <c r="G128" s="63"/>
+      <c r="H128" s="63"/>
+      <c r="I128" s="63"/>
+      <c r="J128" s="63"/>
+      <c r="K128" s="63"/>
+      <c r="L128" s="63"/>
+      <c r="M128" s="63"/>
+      <c r="N128" s="63"/>
+      <c r="O128" s="74"/>
+      <c r="P128" s="47"/>
+    </row>
+    <row r="129" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C129" s="60"/>
+      <c r="D129" s="44"/>
+      <c r="E129" s="63"/>
+      <c r="F129" s="63"/>
+      <c r="G129" s="63"/>
+      <c r="H129" s="63"/>
+      <c r="I129" s="63"/>
+      <c r="J129" s="63"/>
+      <c r="K129" s="63"/>
+      <c r="L129" s="63"/>
+      <c r="M129" s="63"/>
+      <c r="N129" s="63"/>
+      <c r="O129" s="74"/>
+      <c r="P129" s="47"/>
+    </row>
+    <row r="130" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C130" s="60"/>
+      <c r="D130" s="44"/>
+      <c r="E130" s="63"/>
+      <c r="F130" s="63"/>
+      <c r="G130" s="63"/>
+      <c r="H130" s="63"/>
+      <c r="I130" s="63"/>
+      <c r="J130" s="63"/>
+      <c r="K130" s="63"/>
+      <c r="L130" s="63"/>
+      <c r="M130" s="63"/>
+      <c r="N130" s="63"/>
+      <c r="O130" s="74"/>
+      <c r="P130" s="47"/>
+    </row>
+    <row r="131" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C131" s="60"/>
+      <c r="D131" s="44"/>
+      <c r="E131" s="63"/>
+      <c r="F131" s="63"/>
+      <c r="G131" s="63"/>
+      <c r="H131" s="63"/>
+      <c r="I131" s="63"/>
+      <c r="J131" s="63"/>
+      <c r="K131" s="63"/>
+      <c r="L131" s="63"/>
+      <c r="M131" s="63"/>
+      <c r="N131" s="63"/>
+      <c r="O131" s="74"/>
+      <c r="P131" s="47"/>
+    </row>
+    <row r="132" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C132" s="60"/>
+      <c r="D132" s="44"/>
+      <c r="E132" s="63"/>
+      <c r="F132" s="63"/>
+      <c r="G132" s="63"/>
+      <c r="H132" s="63"/>
+      <c r="I132" s="63"/>
+      <c r="J132" s="63"/>
+      <c r="K132" s="63"/>
+      <c r="L132" s="63"/>
+      <c r="M132" s="63"/>
+      <c r="N132" s="63"/>
+      <c r="O132" s="74"/>
+      <c r="P132" s="47"/>
+    </row>
+    <row r="133" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C133" s="60"/>
+      <c r="D133" s="44"/>
+      <c r="E133" s="63"/>
+      <c r="F133" s="63"/>
+      <c r="G133" s="63"/>
+      <c r="H133" s="63"/>
+      <c r="I133" s="63"/>
+      <c r="J133" s="63"/>
+      <c r="K133" s="63"/>
+      <c r="L133" s="63"/>
+      <c r="M133" s="63"/>
+      <c r="N133" s="63"/>
+      <c r="O133" s="74"/>
+      <c r="P133" s="47"/>
+    </row>
+    <row r="134" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C134" s="60"/>
+      <c r="D134" s="44"/>
+      <c r="E134" s="63"/>
+      <c r="F134" s="63"/>
+      <c r="G134" s="63"/>
+      <c r="H134" s="63"/>
+      <c r="I134" s="63"/>
+      <c r="J134" s="63"/>
+      <c r="K134" s="63"/>
+      <c r="L134" s="63"/>
+      <c r="M134" s="63"/>
+      <c r="N134" s="63"/>
+      <c r="O134" s="74"/>
+      <c r="P134" s="47"/>
+    </row>
+    <row r="135" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C135" s="60"/>
+      <c r="D135" s="44"/>
+      <c r="E135" s="63"/>
+      <c r="F135" s="63"/>
+      <c r="G135" s="63"/>
+      <c r="H135" s="63"/>
+      <c r="I135" s="63"/>
+      <c r="J135" s="63"/>
+      <c r="K135" s="63"/>
+      <c r="L135" s="63"/>
+      <c r="M135" s="63"/>
+      <c r="N135" s="63"/>
+      <c r="O135" s="74"/>
+      <c r="P135" s="47"/>
+    </row>
+    <row r="136" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C136" s="60"/>
+      <c r="D136" s="44"/>
+      <c r="E136" s="63"/>
+      <c r="F136" s="63"/>
+      <c r="G136" s="63"/>
+      <c r="H136" s="63"/>
+      <c r="I136" s="63"/>
+      <c r="J136" s="63"/>
+      <c r="K136" s="63"/>
+      <c r="L136" s="63"/>
+      <c r="M136" s="63"/>
+      <c r="N136" s="63"/>
+      <c r="O136" s="74"/>
+      <c r="P136" s="47"/>
+    </row>
+    <row r="137" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C137" s="60"/>
+      <c r="D137" s="44"/>
+      <c r="E137" s="63"/>
+      <c r="F137" s="63"/>
+      <c r="G137" s="63"/>
+      <c r="H137" s="63"/>
+      <c r="I137" s="63"/>
+      <c r="J137" s="63"/>
+      <c r="K137" s="63"/>
+      <c r="L137" s="63"/>
+      <c r="M137" s="63"/>
+      <c r="N137" s="63"/>
+      <c r="O137" s="74"/>
+      <c r="P137" s="47"/>
+    </row>
+    <row r="138" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C138" s="60"/>
+      <c r="D138" s="44"/>
+      <c r="E138" s="63"/>
+      <c r="F138" s="63"/>
+      <c r="G138" s="63"/>
+      <c r="H138" s="63"/>
+      <c r="I138" s="63"/>
+      <c r="J138" s="63"/>
+      <c r="K138" s="63"/>
+      <c r="L138" s="63"/>
+      <c r="M138" s="63"/>
+      <c r="N138" s="63"/>
+      <c r="O138" s="74"/>
+      <c r="P138" s="47"/>
+    </row>
+    <row r="139" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C139" s="60"/>
+      <c r="D139" s="44"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="63"/>
+      <c r="G139" s="63"/>
+      <c r="H139" s="63"/>
+      <c r="I139" s="63"/>
+      <c r="J139" s="63"/>
+      <c r="K139" s="63"/>
+      <c r="L139" s="63"/>
+      <c r="M139" s="63"/>
+      <c r="N139" s="63"/>
+      <c r="O139" s="74"/>
+      <c r="P139" s="47"/>
+    </row>
+    <row r="140" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C140" s="60"/>
+      <c r="D140" s="44"/>
+      <c r="E140" s="63"/>
+      <c r="F140" s="63"/>
+      <c r="G140" s="63"/>
+      <c r="H140" s="63"/>
+      <c r="I140" s="63"/>
+      <c r="J140" s="63"/>
+      <c r="K140" s="63"/>
+      <c r="L140" s="63"/>
+      <c r="M140" s="63"/>
+      <c r="N140" s="63"/>
+      <c r="O140" s="74"/>
+      <c r="P140" s="47"/>
+    </row>
+    <row r="141" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C141" s="60"/>
+      <c r="D141" s="44"/>
+      <c r="E141" s="63"/>
+      <c r="F141" s="63"/>
+      <c r="G141" s="63"/>
+      <c r="H141" s="63"/>
+      <c r="I141" s="63"/>
+      <c r="J141" s="63"/>
+      <c r="K141" s="63"/>
+      <c r="L141" s="63"/>
+      <c r="M141" s="63"/>
+      <c r="N141" s="63"/>
+      <c r="O141" s="74"/>
+      <c r="P141" s="47"/>
+    </row>
+    <row r="142" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C142" s="60"/>
+      <c r="D142" s="44"/>
+      <c r="E142" s="63"/>
+      <c r="F142" s="63"/>
+      <c r="G142" s="63"/>
+      <c r="H142" s="63"/>
+      <c r="I142" s="63"/>
+      <c r="J142" s="63"/>
+      <c r="K142" s="63"/>
+      <c r="L142" s="63"/>
+      <c r="M142" s="63"/>
+      <c r="N142" s="63"/>
+      <c r="O142" s="74"/>
+      <c r="P142" s="47"/>
+    </row>
+    <row r="143" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C143" s="60"/>
+      <c r="D143" s="44"/>
+      <c r="E143" s="63"/>
+      <c r="F143" s="63"/>
+      <c r="G143" s="63"/>
+      <c r="H143" s="63"/>
+      <c r="I143" s="63"/>
+      <c r="J143" s="63"/>
+      <c r="K143" s="63"/>
+      <c r="L143" s="63"/>
+      <c r="M143" s="63"/>
+      <c r="N143" s="63"/>
+      <c r="O143" s="74"/>
+      <c r="P143" s="47"/>
+    </row>
+    <row r="144" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C144" s="60"/>
+      <c r="D144" s="44"/>
+      <c r="E144" s="63"/>
+      <c r="F144" s="63"/>
+      <c r="G144" s="63"/>
+      <c r="H144" s="63"/>
+      <c r="I144" s="63"/>
+      <c r="J144" s="63"/>
+      <c r="K144" s="63"/>
+      <c r="L144" s="63"/>
+      <c r="M144" s="63"/>
+      <c r="N144" s="63"/>
+      <c r="O144" s="74"/>
+      <c r="P144" s="47"/>
+    </row>
+    <row r="145" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C145" s="60"/>
+      <c r="D145" s="44"/>
+      <c r="E145" s="63"/>
+      <c r="F145" s="63"/>
+      <c r="G145" s="63"/>
+      <c r="H145" s="63"/>
+      <c r="I145" s="63"/>
+      <c r="J145" s="63"/>
+      <c r="K145" s="63"/>
+      <c r="L145" s="63"/>
+      <c r="M145" s="63"/>
+      <c r="N145" s="63"/>
+      <c r="O145" s="74"/>
+      <c r="P145" s="47"/>
+    </row>
+    <row r="146" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C146" s="60"/>
+      <c r="D146" s="44"/>
+      <c r="E146" s="63"/>
+      <c r="F146" s="63"/>
+      <c r="G146" s="63"/>
+      <c r="H146" s="63"/>
+      <c r="I146" s="63"/>
+      <c r="J146" s="63"/>
+      <c r="K146" s="63"/>
+      <c r="L146" s="63"/>
+      <c r="M146" s="63"/>
+      <c r="N146" s="63"/>
+      <c r="O146" s="74"/>
+      <c r="P146" s="47"/>
+    </row>
+    <row r="147" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C147" s="60"/>
+      <c r="D147" s="44"/>
+      <c r="E147" s="63"/>
+      <c r="F147" s="63"/>
+      <c r="G147" s="63"/>
+      <c r="H147" s="63"/>
+      <c r="I147" s="63"/>
+      <c r="J147" s="63"/>
+      <c r="K147" s="63"/>
+      <c r="L147" s="63"/>
+      <c r="M147" s="63"/>
+      <c r="N147" s="63"/>
+      <c r="O147" s="74"/>
+      <c r="P147" s="47"/>
+    </row>
+    <row r="148" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C148" s="60"/>
+      <c r="D148" s="44"/>
+      <c r="E148" s="63"/>
+      <c r="F148" s="63"/>
+      <c r="G148" s="63"/>
+      <c r="H148" s="63"/>
+      <c r="I148" s="63"/>
+      <c r="J148" s="63"/>
+      <c r="K148" s="63"/>
+      <c r="L148" s="63"/>
+      <c r="M148" s="63"/>
+      <c r="N148" s="63"/>
+      <c r="O148" s="74"/>
+      <c r="P148" s="47"/>
+    </row>
+    <row r="149" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C149" s="60"/>
+      <c r="D149" s="44"/>
+      <c r="E149" s="63"/>
+      <c r="F149" s="63"/>
+      <c r="G149" s="63"/>
+      <c r="H149" s="63"/>
+      <c r="I149" s="63"/>
+      <c r="J149" s="63"/>
+      <c r="K149" s="63"/>
+      <c r="L149" s="63"/>
+      <c r="M149" s="63"/>
+      <c r="N149" s="63"/>
+      <c r="O149" s="74"/>
+      <c r="P149" s="47"/>
+    </row>
+    <row r="150" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C150" s="60"/>
+      <c r="D150" s="44"/>
+      <c r="E150" s="63"/>
+      <c r="F150" s="63"/>
+      <c r="G150" s="63"/>
+      <c r="H150" s="63"/>
+      <c r="I150" s="63"/>
+      <c r="J150" s="63"/>
+      <c r="K150" s="63"/>
+      <c r="L150" s="63"/>
+      <c r="M150" s="63"/>
+      <c r="N150" s="63"/>
+      <c r="O150" s="74"/>
+      <c r="P150" s="47"/>
+    </row>
+    <row r="151" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C151" s="60"/>
+      <c r="D151" s="44"/>
+      <c r="E151" s="63"/>
+      <c r="F151" s="63"/>
+      <c r="G151" s="63"/>
+      <c r="H151" s="63"/>
+      <c r="I151" s="63"/>
+      <c r="J151" s="63"/>
+      <c r="K151" s="63"/>
+      <c r="L151" s="63"/>
+      <c r="M151" s="63"/>
+      <c r="N151" s="63"/>
+      <c r="O151" s="74"/>
+      <c r="P151" s="47"/>
+    </row>
+    <row r="152" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C152" s="60"/>
+      <c r="D152" s="44"/>
+      <c r="E152" s="63"/>
+      <c r="F152" s="63"/>
+      <c r="G152" s="63"/>
+      <c r="H152" s="63"/>
+      <c r="I152" s="63"/>
+      <c r="J152" s="63"/>
+      <c r="K152" s="63"/>
+      <c r="L152" s="63"/>
+      <c r="M152" s="63"/>
+      <c r="N152" s="63"/>
+      <c r="O152" s="74"/>
+      <c r="P152" s="47"/>
+    </row>
+    <row r="153" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C153" s="60"/>
+      <c r="D153" s="44"/>
+      <c r="E153" s="63"/>
+      <c r="F153" s="63"/>
+      <c r="G153" s="63"/>
+      <c r="H153" s="63"/>
+      <c r="I153" s="63"/>
+      <c r="J153" s="63"/>
+      <c r="K153" s="63"/>
+      <c r="L153" s="63"/>
+      <c r="M153" s="63"/>
+      <c r="N153" s="63"/>
+      <c r="O153" s="74"/>
+      <c r="P153" s="47"/>
+    </row>
+    <row r="154" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C154" s="60"/>
+      <c r="D154" s="44"/>
+      <c r="E154" s="63"/>
+      <c r="F154" s="63"/>
+      <c r="G154" s="63"/>
+      <c r="H154" s="63"/>
+      <c r="I154" s="63"/>
+      <c r="J154" s="63"/>
+      <c r="K154" s="63"/>
+      <c r="L154" s="63"/>
+      <c r="M154" s="63"/>
+      <c r="N154" s="63"/>
+      <c r="O154" s="74"/>
+      <c r="P154" s="47"/>
+    </row>
+    <row r="155" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C155" s="60"/>
+      <c r="D155" s="44"/>
+      <c r="E155" s="63"/>
+      <c r="F155" s="63"/>
+      <c r="G155" s="63"/>
+      <c r="H155" s="63"/>
+      <c r="I155" s="63"/>
+      <c r="J155" s="63"/>
+      <c r="K155" s="63"/>
+      <c r="L155" s="63"/>
+      <c r="M155" s="63"/>
+      <c r="N155" s="63"/>
+      <c r="O155" s="74"/>
+      <c r="P155" s="47"/>
+    </row>
+    <row r="156" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C156" s="60"/>
+      <c r="D156" s="44"/>
+      <c r="E156" s="63"/>
+      <c r="F156" s="63"/>
+      <c r="G156" s="63"/>
+      <c r="H156" s="63"/>
+      <c r="I156" s="63"/>
+      <c r="J156" s="63"/>
+      <c r="K156" s="63"/>
+      <c r="L156" s="63"/>
+      <c r="M156" s="63"/>
+      <c r="N156" s="63"/>
+      <c r="O156" s="74"/>
+      <c r="P156" s="47"/>
+    </row>
+    <row r="157" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C157" s="60"/>
+      <c r="D157" s="44"/>
+      <c r="E157" s="63"/>
+      <c r="F157" s="63"/>
+      <c r="G157" s="63"/>
+      <c r="H157" s="63"/>
+      <c r="I157" s="63"/>
+      <c r="J157" s="63"/>
+      <c r="K157" s="63"/>
+      <c r="L157" s="63"/>
+      <c r="M157" s="63"/>
+      <c r="N157" s="63"/>
+      <c r="O157" s="74"/>
+      <c r="P157" s="47"/>
+    </row>
+    <row r="158" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C158" s="60"/>
+      <c r="D158" s="44"/>
+      <c r="E158" s="63"/>
+      <c r="F158" s="63"/>
+      <c r="G158" s="63"/>
+      <c r="H158" s="63"/>
+      <c r="I158" s="63"/>
+      <c r="J158" s="63"/>
+      <c r="K158" s="63"/>
+      <c r="L158" s="63"/>
+      <c r="M158" s="63"/>
+      <c r="N158" s="63"/>
+      <c r="O158" s="74"/>
+      <c r="P158" s="47"/>
+    </row>
+    <row r="159" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C159" s="60"/>
+      <c r="D159" s="44"/>
+      <c r="E159" s="63"/>
+      <c r="F159" s="63"/>
+      <c r="G159" s="63"/>
+      <c r="H159" s="63"/>
+      <c r="I159" s="63"/>
+      <c r="J159" s="63"/>
+      <c r="K159" s="63"/>
+      <c r="L159" s="63"/>
+      <c r="M159" s="63"/>
+      <c r="N159" s="63"/>
+      <c r="O159" s="74"/>
+      <c r="P159" s="47"/>
+    </row>
+    <row r="160" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C160" s="60"/>
+      <c r="D160" s="44"/>
+      <c r="E160" s="63"/>
+      <c r="F160" s="63"/>
+      <c r="G160" s="63"/>
+      <c r="H160" s="63"/>
+      <c r="I160" s="63"/>
+      <c r="J160" s="63"/>
+      <c r="K160" s="63"/>
+      <c r="L160" s="63"/>
+      <c r="M160" s="63"/>
+      <c r="N160" s="63"/>
+      <c r="O160" s="74"/>
+      <c r="P160" s="47"/>
+    </row>
+    <row r="161" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C161" s="60"/>
+      <c r="D161" s="44"/>
+      <c r="E161" s="63"/>
+      <c r="F161" s="63"/>
+      <c r="G161" s="63"/>
+      <c r="H161" s="63"/>
+      <c r="I161" s="63"/>
+      <c r="J161" s="63"/>
+      <c r="K161" s="63"/>
+      <c r="L161" s="63"/>
+      <c r="M161" s="63"/>
+      <c r="N161" s="63"/>
+      <c r="O161" s="74"/>
+      <c r="P161" s="47"/>
+    </row>
+    <row r="162" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C162" s="60"/>
+      <c r="D162" s="44"/>
+      <c r="E162" s="63"/>
+      <c r="F162" s="63"/>
+      <c r="G162" s="63"/>
+      <c r="H162" s="63"/>
+      <c r="I162" s="63"/>
+      <c r="J162" s="63"/>
+      <c r="K162" s="63"/>
+      <c r="L162" s="63"/>
+      <c r="M162" s="63"/>
+      <c r="N162" s="63"/>
+      <c r="O162" s="74"/>
+      <c r="P162" s="47"/>
+    </row>
+    <row r="163" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C163" s="60"/>
+      <c r="D163" s="44"/>
+      <c r="E163" s="63"/>
+      <c r="F163" s="63"/>
+      <c r="G163" s="63"/>
+      <c r="H163" s="63"/>
+      <c r="I163" s="63"/>
+      <c r="J163" s="63"/>
+      <c r="K163" s="63"/>
+      <c r="L163" s="63"/>
+      <c r="M163" s="63"/>
+      <c r="N163" s="63"/>
+      <c r="O163" s="74"/>
+      <c r="P163" s="47"/>
+    </row>
+    <row r="164" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C164" s="60"/>
+      <c r="D164" s="44"/>
+      <c r="E164" s="63"/>
+      <c r="F164" s="63"/>
+      <c r="G164" s="63"/>
+      <c r="H164" s="63"/>
+      <c r="I164" s="63"/>
+      <c r="J164" s="63"/>
+      <c r="K164" s="63"/>
+      <c r="L164" s="63"/>
+      <c r="M164" s="63"/>
+      <c r="N164" s="63"/>
+      <c r="O164" s="74"/>
+      <c r="P164" s="47"/>
+    </row>
+    <row r="165" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C165" s="60"/>
+      <c r="D165" s="44"/>
+      <c r="E165" s="63"/>
+      <c r="F165" s="63"/>
+      <c r="G165" s="63"/>
+      <c r="H165" s="63"/>
+      <c r="I165" s="63"/>
+      <c r="J165" s="63"/>
+      <c r="K165" s="63"/>
+      <c r="L165" s="63"/>
+      <c r="M165" s="63"/>
+      <c r="N165" s="63"/>
+      <c r="O165" s="74"/>
+      <c r="P165" s="47"/>
+    </row>
+    <row r="166" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C166" s="60"/>
+      <c r="D166" s="44"/>
+      <c r="E166" s="63"/>
+      <c r="F166" s="63"/>
+      <c r="G166" s="63"/>
+      <c r="H166" s="63"/>
+      <c r="I166" s="63"/>
+      <c r="J166" s="63"/>
+      <c r="K166" s="63"/>
+      <c r="L166" s="63"/>
+      <c r="M166" s="63"/>
+      <c r="N166" s="63"/>
+      <c r="O166" s="74"/>
+      <c r="P166" s="47"/>
+    </row>
+    <row r="167" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C167" s="60"/>
+      <c r="D167" s="44"/>
+      <c r="E167" s="63"/>
+      <c r="F167" s="63"/>
+      <c r="G167" s="63"/>
+      <c r="H167" s="63"/>
+      <c r="I167" s="63"/>
+      <c r="J167" s="63"/>
+      <c r="K167" s="63"/>
+      <c r="L167" s="63"/>
+      <c r="M167" s="63"/>
+      <c r="N167" s="63"/>
+      <c r="O167" s="74"/>
+      <c r="P167" s="47"/>
+    </row>
+    <row r="168" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C168" s="60"/>
+      <c r="D168" s="44"/>
+      <c r="E168" s="63"/>
+      <c r="F168" s="63"/>
+      <c r="G168" s="63"/>
+      <c r="H168" s="63"/>
+      <c r="I168" s="63"/>
+      <c r="J168" s="63"/>
+      <c r="K168" s="63"/>
+      <c r="L168" s="63"/>
+      <c r="M168" s="63"/>
+      <c r="N168" s="63"/>
+      <c r="O168" s="74"/>
+      <c r="P168" s="47"/>
+    </row>
+    <row r="169" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C169" s="60"/>
+      <c r="D169" s="44"/>
+      <c r="E169" s="63"/>
+      <c r="F169" s="63"/>
+      <c r="G169" s="63"/>
+      <c r="H169" s="63"/>
+      <c r="I169" s="63"/>
+      <c r="J169" s="63"/>
+      <c r="K169" s="63"/>
+      <c r="L169" s="63"/>
+      <c r="M169" s="63"/>
+      <c r="N169" s="63"/>
+      <c r="O169" s="74"/>
+      <c r="P169" s="47"/>
+    </row>
+    <row r="170" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C170" s="60"/>
+      <c r="D170" s="44"/>
+      <c r="E170" s="63"/>
+      <c r="F170" s="63"/>
+      <c r="G170" s="63"/>
+      <c r="H170" s="63"/>
+      <c r="I170" s="63"/>
+      <c r="J170" s="63"/>
+      <c r="K170" s="63"/>
+      <c r="L170" s="63"/>
+      <c r="M170" s="63"/>
+      <c r="N170" s="63"/>
+      <c r="O170" s="74"/>
+      <c r="P170" s="47"/>
+    </row>
+    <row r="171" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C171" s="60"/>
+      <c r="D171" s="44"/>
+      <c r="E171" s="63"/>
+      <c r="F171" s="63"/>
+      <c r="G171" s="63"/>
+      <c r="H171" s="63"/>
+      <c r="I171" s="63"/>
+      <c r="J171" s="63"/>
+      <c r="K171" s="63"/>
+      <c r="L171" s="63"/>
+      <c r="M171" s="63"/>
+      <c r="N171" s="63"/>
+      <c r="O171" s="74"/>
+      <c r="P171" s="47"/>
+    </row>
+    <row r="172" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C172" s="60"/>
+      <c r="D172" s="44"/>
+      <c r="E172" s="63"/>
+      <c r="F172" s="63"/>
+      <c r="G172" s="63"/>
+      <c r="H172" s="63"/>
+      <c r="I172" s="63"/>
+      <c r="J172" s="63"/>
+      <c r="K172" s="63"/>
+      <c r="L172" s="63"/>
+      <c r="M172" s="63"/>
+      <c r="N172" s="63"/>
+      <c r="O172" s="74"/>
+      <c r="P172" s="47"/>
+    </row>
+    <row r="173" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C173" s="60"/>
+      <c r="D173" s="44"/>
+      <c r="E173" s="63"/>
+      <c r="F173" s="63"/>
+      <c r="G173" s="63"/>
+      <c r="H173" s="63"/>
+      <c r="I173" s="63"/>
+      <c r="J173" s="63"/>
+      <c r="K173" s="63"/>
+      <c r="L173" s="63"/>
+      <c r="M173" s="63"/>
+      <c r="N173" s="63"/>
+      <c r="O173" s="74"/>
+      <c r="P173" s="47"/>
+    </row>
+    <row r="174" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C174" s="60"/>
+      <c r="D174" s="44"/>
+      <c r="E174" s="63"/>
+      <c r="F174" s="63"/>
+      <c r="G174" s="63"/>
+      <c r="H174" s="63"/>
+      <c r="I174" s="63"/>
+      <c r="J174" s="63"/>
+      <c r="K174" s="63"/>
+      <c r="L174" s="63"/>
+      <c r="M174" s="63"/>
+      <c r="N174" s="63"/>
+      <c r="O174" s="74"/>
+      <c r="P174" s="47"/>
+    </row>
+    <row r="175" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C175" s="60"/>
+      <c r="D175" s="44"/>
+      <c r="E175" s="63"/>
+      <c r="F175" s="63"/>
+      <c r="G175" s="63"/>
+      <c r="H175" s="63"/>
+      <c r="I175" s="63"/>
+      <c r="J175" s="63"/>
+      <c r="K175" s="63"/>
+      <c r="L175" s="63"/>
+      <c r="M175" s="63"/>
+      <c r="N175" s="63"/>
+      <c r="O175" s="74"/>
+      <c r="P175" s="47"/>
+    </row>
+    <row r="176" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C176" s="60"/>
+      <c r="D176" s="44"/>
+      <c r="E176" s="63"/>
+      <c r="F176" s="63"/>
+      <c r="G176" s="63"/>
+      <c r="H176" s="63"/>
+      <c r="I176" s="63"/>
+      <c r="J176" s="63"/>
+      <c r="K176" s="63"/>
+      <c r="L176" s="63"/>
+      <c r="M176" s="63"/>
+      <c r="N176" s="63"/>
+      <c r="O176" s="74"/>
+      <c r="P176" s="47"/>
+    </row>
+    <row r="177" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C177" s="60"/>
+      <c r="D177" s="44"/>
+      <c r="E177" s="63"/>
+      <c r="F177" s="63"/>
+      <c r="G177" s="63"/>
+      <c r="H177" s="63"/>
+      <c r="I177" s="63"/>
+      <c r="J177" s="63"/>
+      <c r="K177" s="63"/>
+      <c r="L177" s="63"/>
+      <c r="M177" s="63"/>
+      <c r="N177" s="63"/>
+      <c r="O177" s="74"/>
+      <c r="P177" s="47"/>
+    </row>
+    <row r="178" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C178" s="60"/>
+      <c r="D178" s="44"/>
+      <c r="E178" s="63"/>
+      <c r="F178" s="63"/>
+      <c r="G178" s="63"/>
+      <c r="H178" s="63"/>
+      <c r="I178" s="63"/>
+      <c r="J178" s="63"/>
+      <c r="K178" s="63"/>
+      <c r="L178" s="63"/>
+      <c r="M178" s="63"/>
+      <c r="N178" s="63"/>
+      <c r="O178" s="74"/>
+      <c r="P178" s="47"/>
+    </row>
+    <row r="179" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C179" s="60"/>
+      <c r="D179" s="44"/>
+      <c r="E179" s="63"/>
+      <c r="F179" s="63"/>
+      <c r="G179" s="63"/>
+      <c r="H179" s="63"/>
+      <c r="I179" s="63"/>
+      <c r="J179" s="63"/>
+      <c r="K179" s="63"/>
+      <c r="L179" s="63"/>
+      <c r="M179" s="63"/>
+      <c r="N179" s="63"/>
+      <c r="O179" s="74"/>
+      <c r="P179" s="47"/>
+    </row>
+    <row r="180" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C180" s="60"/>
+      <c r="D180" s="44"/>
+      <c r="E180" s="63"/>
+      <c r="F180" s="63"/>
+      <c r="G180" s="63"/>
+      <c r="H180" s="63"/>
+      <c r="I180" s="63"/>
+      <c r="J180" s="63"/>
+      <c r="K180" s="63"/>
+      <c r="L180" s="63"/>
+      <c r="M180" s="63"/>
+      <c r="N180" s="63"/>
+      <c r="O180" s="74"/>
+      <c r="P180" s="47"/>
+    </row>
+    <row r="181" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C181" s="60"/>
+      <c r="D181" s="44"/>
+      <c r="E181" s="63"/>
+      <c r="F181" s="63"/>
+      <c r="G181" s="63"/>
+      <c r="H181" s="63"/>
+      <c r="I181" s="63"/>
+      <c r="J181" s="63"/>
+      <c r="K181" s="63"/>
+      <c r="L181" s="63"/>
+      <c r="M181" s="63"/>
+      <c r="N181" s="63"/>
+      <c r="O181" s="74"/>
+      <c r="P181" s="47"/>
+    </row>
+    <row r="182" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C182" s="60"/>
+      <c r="D182" s="44"/>
+      <c r="E182" s="63"/>
+      <c r="F182" s="63"/>
+      <c r="G182" s="63"/>
+      <c r="H182" s="63"/>
+      <c r="I182" s="63"/>
+      <c r="J182" s="63"/>
+      <c r="K182" s="63"/>
+      <c r="L182" s="63"/>
+      <c r="M182" s="63"/>
+      <c r="N182" s="63"/>
+      <c r="O182" s="74"/>
+      <c r="P182" s="47"/>
+    </row>
+    <row r="183" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C183" s="60"/>
+      <c r="D183" s="44"/>
+      <c r="E183" s="63"/>
+      <c r="F183" s="63"/>
+      <c r="G183" s="63"/>
+      <c r="H183" s="63"/>
+      <c r="I183" s="63"/>
+      <c r="J183" s="63"/>
+      <c r="K183" s="63"/>
+      <c r="L183" s="63"/>
+      <c r="M183" s="63"/>
+      <c r="N183" s="63"/>
+      <c r="O183" s="74"/>
+      <c r="P183" s="47"/>
+    </row>
+    <row r="184" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C184" s="60"/>
+      <c r="D184" s="44"/>
+      <c r="E184" s="63"/>
+      <c r="F184" s="63"/>
+      <c r="G184" s="63"/>
+      <c r="H184" s="63"/>
+      <c r="I184" s="63"/>
+      <c r="J184" s="63"/>
+      <c r="K184" s="63"/>
+      <c r="L184" s="63"/>
+      <c r="M184" s="63"/>
+      <c r="N184" s="63"/>
+      <c r="O184" s="74"/>
+      <c r="P184" s="47"/>
+    </row>
+    <row r="185" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C185" s="60"/>
+      <c r="D185" s="44"/>
+      <c r="E185" s="63"/>
+      <c r="F185" s="63"/>
+      <c r="G185" s="63"/>
+      <c r="H185" s="63"/>
+      <c r="I185" s="63"/>
+      <c r="J185" s="63"/>
+      <c r="K185" s="63"/>
+      <c r="L185" s="63"/>
+      <c r="M185" s="63"/>
+      <c r="N185" s="63"/>
+      <c r="O185" s="74"/>
+      <c r="P185" s="47"/>
+    </row>
+    <row r="186" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C186" s="60"/>
+      <c r="D186" s="44"/>
+      <c r="E186" s="63"/>
+      <c r="F186" s="63"/>
+      <c r="G186" s="63"/>
+      <c r="H186" s="63"/>
+      <c r="I186" s="63"/>
+      <c r="J186" s="63"/>
+      <c r="K186" s="63"/>
+      <c r="L186" s="63"/>
+      <c r="M186" s="63"/>
+      <c r="N186" s="63"/>
+      <c r="O186" s="74"/>
+      <c r="P186" s="47"/>
+    </row>
+    <row r="187" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C187" s="60"/>
+      <c r="D187" s="44"/>
+      <c r="E187" s="63"/>
+      <c r="F187" s="63"/>
+      <c r="G187" s="63"/>
+      <c r="H187" s="63"/>
+      <c r="I187" s="63"/>
+      <c r="J187" s="63"/>
+      <c r="K187" s="63"/>
+      <c r="L187" s="63"/>
+      <c r="M187" s="63"/>
+      <c r="N187" s="63"/>
+      <c r="O187" s="74"/>
+      <c r="P187" s="47"/>
+    </row>
+    <row r="188" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C188" s="60"/>
+      <c r="D188" s="44"/>
+      <c r="E188" s="63"/>
+      <c r="F188" s="63"/>
+      <c r="G188" s="63"/>
+      <c r="H188" s="63"/>
+      <c r="I188" s="63"/>
+      <c r="J188" s="63"/>
+      <c r="K188" s="63"/>
+      <c r="L188" s="63"/>
+      <c r="M188" s="63"/>
+      <c r="N188" s="63"/>
+      <c r="O188" s="74"/>
+      <c r="P188" s="47"/>
+    </row>
+    <row r="189" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C189" s="60"/>
+      <c r="D189" s="44"/>
+      <c r="E189" s="63"/>
+      <c r="F189" s="63"/>
+      <c r="G189" s="63"/>
+      <c r="H189" s="63"/>
+      <c r="I189" s="63"/>
+      <c r="J189" s="63"/>
+      <c r="K189" s="63"/>
+      <c r="L189" s="63"/>
+      <c r="M189" s="63"/>
+      <c r="N189" s="63"/>
+      <c r="O189" s="74"/>
+      <c r="P189" s="47"/>
+    </row>
+    <row r="190" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C190" s="60"/>
+      <c r="D190" s="44"/>
+      <c r="E190" s="63"/>
+      <c r="F190" s="63"/>
+      <c r="G190" s="63"/>
+      <c r="H190" s="63"/>
+      <c r="I190" s="63"/>
+      <c r="J190" s="63"/>
+      <c r="K190" s="63"/>
+      <c r="L190" s="63"/>
+      <c r="M190" s="63"/>
+      <c r="N190" s="63"/>
+      <c r="O190" s="74"/>
+      <c r="P190" s="47"/>
+    </row>
+    <row r="191" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C191" s="60"/>
+      <c r="D191" s="44"/>
+      <c r="E191" s="63"/>
+      <c r="F191" s="63"/>
+      <c r="G191" s="63"/>
+      <c r="H191" s="63"/>
+      <c r="I191" s="63"/>
+      <c r="J191" s="63"/>
+      <c r="K191" s="63"/>
+      <c r="L191" s="63"/>
+      <c r="M191" s="63"/>
+      <c r="N191" s="63"/>
+      <c r="O191" s="74"/>
+      <c r="P191" s="47"/>
+    </row>
+    <row r="192" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C192" s="60"/>
+      <c r="D192" s="44"/>
+      <c r="E192" s="63"/>
+      <c r="F192" s="63"/>
+      <c r="G192" s="63"/>
+      <c r="H192" s="63"/>
+      <c r="I192" s="63"/>
+      <c r="J192" s="63"/>
+      <c r="K192" s="63"/>
+      <c r="L192" s="63"/>
+      <c r="M192" s="63"/>
+      <c r="N192" s="63"/>
+      <c r="O192" s="74"/>
+      <c r="P192" s="47"/>
+    </row>
+    <row r="193" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C193" s="60"/>
+      <c r="D193" s="44"/>
+      <c r="E193" s="63"/>
+      <c r="F193" s="63"/>
+      <c r="G193" s="63"/>
+      <c r="H193" s="63"/>
+      <c r="I193" s="63"/>
+      <c r="J193" s="63"/>
+      <c r="K193" s="63"/>
+      <c r="L193" s="63"/>
+      <c r="M193" s="63"/>
+      <c r="N193" s="63"/>
+      <c r="O193" s="74"/>
+      <c r="P193" s="47"/>
+    </row>
+    <row r="194" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C194" s="60"/>
+      <c r="D194" s="44"/>
+      <c r="E194" s="63"/>
+      <c r="F194" s="63"/>
+      <c r="G194" s="63"/>
+      <c r="H194" s="63"/>
+      <c r="I194" s="63"/>
+      <c r="J194" s="63"/>
+      <c r="K194" s="63"/>
+      <c r="L194" s="63"/>
+      <c r="M194" s="63"/>
+      <c r="N194" s="63"/>
+      <c r="O194" s="74"/>
+      <c r="P194" s="47"/>
+    </row>
+    <row r="195" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C195" s="60"/>
+      <c r="D195" s="44"/>
+      <c r="E195" s="63"/>
+      <c r="F195" s="63"/>
+      <c r="G195" s="63"/>
+      <c r="H195" s="63"/>
+      <c r="I195" s="63"/>
+      <c r="J195" s="63"/>
+      <c r="K195" s="63"/>
+      <c r="L195" s="63"/>
+      <c r="M195" s="63"/>
+      <c r="N195" s="63"/>
+      <c r="O195" s="74"/>
+      <c r="P195" s="47"/>
+    </row>
+    <row r="196" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C196" s="60"/>
+      <c r="D196" s="44"/>
+      <c r="E196" s="63"/>
+      <c r="F196" s="63"/>
+      <c r="G196" s="63"/>
+      <c r="H196" s="63"/>
+      <c r="I196" s="63"/>
+      <c r="J196" s="63"/>
+      <c r="K196" s="63"/>
+      <c r="L196" s="63"/>
+      <c r="M196" s="63"/>
+      <c r="N196" s="63"/>
+      <c r="O196" s="74"/>
+      <c r="P196" s="47"/>
+    </row>
+    <row r="197" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C197" s="60"/>
+      <c r="D197" s="44"/>
+      <c r="E197" s="63"/>
+      <c r="F197" s="63"/>
+      <c r="G197" s="63"/>
+      <c r="H197" s="63"/>
+      <c r="I197" s="63"/>
+      <c r="J197" s="63"/>
+      <c r="K197" s="63"/>
+      <c r="L197" s="63"/>
+      <c r="M197" s="63"/>
+      <c r="N197" s="63"/>
+      <c r="O197" s="74"/>
+      <c r="P197" s="47"/>
+    </row>
+    <row r="198" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C198" s="60"/>
+      <c r="D198" s="44"/>
+      <c r="E198" s="63"/>
+      <c r="F198" s="63"/>
+      <c r="G198" s="63"/>
+      <c r="H198" s="63"/>
+      <c r="I198" s="63"/>
+      <c r="J198" s="63"/>
+      <c r="K198" s="63"/>
+      <c r="L198" s="63"/>
+      <c r="M198" s="63"/>
+      <c r="N198" s="63"/>
+      <c r="O198" s="74"/>
+      <c r="P198" s="47"/>
+    </row>
+    <row r="199" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C199" s="60"/>
+      <c r="D199" s="44"/>
+      <c r="E199" s="63"/>
+      <c r="F199" s="63"/>
+      <c r="G199" s="63"/>
+      <c r="H199" s="63"/>
+      <c r="I199" s="63"/>
+      <c r="J199" s="63"/>
+      <c r="K199" s="63"/>
+      <c r="L199" s="63"/>
+      <c r="M199" s="63"/>
+      <c r="N199" s="63"/>
+      <c r="O199" s="74"/>
+      <c r="P199" s="47"/>
+    </row>
+    <row r="200" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C200" s="60"/>
+      <c r="D200" s="44"/>
+      <c r="E200" s="63"/>
+      <c r="F200" s="63"/>
+      <c r="G200" s="63"/>
+      <c r="H200" s="63"/>
+      <c r="I200" s="63"/>
+      <c r="J200" s="63"/>
+      <c r="K200" s="63"/>
+      <c r="L200" s="63"/>
+      <c r="M200" s="63"/>
+      <c r="N200" s="63"/>
+      <c r="O200" s="74"/>
+      <c r="P200" s="47"/>
+    </row>
+    <row r="201" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C201" s="60"/>
+      <c r="D201" s="44"/>
+      <c r="E201" s="63"/>
+      <c r="F201" s="63"/>
+      <c r="G201" s="63"/>
+      <c r="H201" s="63"/>
+      <c r="I201" s="63"/>
+      <c r="J201" s="63"/>
+      <c r="K201" s="63"/>
+      <c r="L201" s="63"/>
+      <c r="M201" s="63"/>
+      <c r="N201" s="63"/>
+      <c r="O201" s="74"/>
+      <c r="P201" s="47"/>
+    </row>
+    <row r="202" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C202" s="60"/>
+      <c r="D202" s="44"/>
+      <c r="E202" s="63"/>
+      <c r="F202" s="63"/>
+      <c r="G202" s="63"/>
+      <c r="H202" s="63"/>
+      <c r="I202" s="63"/>
+      <c r="J202" s="63"/>
+      <c r="K202" s="63"/>
+      <c r="L202" s="63"/>
+      <c r="M202" s="63"/>
+      <c r="N202" s="63"/>
+      <c r="O202" s="74"/>
+      <c r="P202" s="47"/>
+    </row>
+    <row r="203" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C203" s="60"/>
+      <c r="D203" s="44"/>
+      <c r="E203" s="63"/>
+      <c r="F203" s="63"/>
+      <c r="G203" s="63"/>
+      <c r="H203" s="63"/>
+      <c r="I203" s="63"/>
+      <c r="J203" s="63"/>
+      <c r="K203" s="63"/>
+      <c r="L203" s="63"/>
+      <c r="M203" s="63"/>
+      <c r="N203" s="63"/>
+      <c r="O203" s="74"/>
+      <c r="P203" s="47"/>
+    </row>
+    <row r="204" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C204" s="60"/>
+      <c r="D204" s="44"/>
+      <c r="E204" s="63"/>
+      <c r="F204" s="63"/>
+      <c r="G204" s="63"/>
+      <c r="H204" s="63"/>
+      <c r="I204" s="63"/>
+      <c r="J204" s="63"/>
+      <c r="K204" s="63"/>
+      <c r="L204" s="63"/>
+      <c r="M204" s="63"/>
+      <c r="N204" s="63"/>
+      <c r="O204" s="74"/>
+      <c r="P204" s="47"/>
+    </row>
+    <row r="205" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C205" s="60"/>
+      <c r="D205" s="44"/>
+      <c r="E205" s="63"/>
+      <c r="F205" s="63"/>
+      <c r="G205" s="63"/>
+      <c r="H205" s="63"/>
+      <c r="I205" s="63"/>
+      <c r="J205" s="63"/>
+      <c r="K205" s="63"/>
+      <c r="L205" s="63"/>
+      <c r="M205" s="63"/>
+      <c r="N205" s="63"/>
+      <c r="O205" s="74"/>
+      <c r="P205" s="47"/>
+    </row>
+    <row r="206" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C206" s="60"/>
+      <c r="D206" s="44"/>
+      <c r="E206" s="63"/>
+      <c r="F206" s="63"/>
+      <c r="G206" s="63"/>
+      <c r="H206" s="63"/>
+      <c r="I206" s="63"/>
+      <c r="J206" s="63"/>
+      <c r="K206" s="63"/>
+      <c r="L206" s="63"/>
+      <c r="M206" s="63"/>
+      <c r="N206" s="63"/>
+      <c r="O206" s="74"/>
+      <c r="P206" s="47"/>
+    </row>
+    <row r="207" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C207" s="60"/>
+      <c r="D207" s="44"/>
+      <c r="E207" s="63"/>
+      <c r="F207" s="63"/>
+      <c r="G207" s="63"/>
+      <c r="H207" s="63"/>
+      <c r="I207" s="63"/>
+      <c r="J207" s="63"/>
+      <c r="K207" s="63"/>
+      <c r="L207" s="63"/>
+      <c r="M207" s="63"/>
+      <c r="N207" s="63"/>
+      <c r="O207" s="74"/>
+      <c r="P207" s="47"/>
+    </row>
+    <row r="208" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C208" s="60"/>
+      <c r="D208" s="44"/>
+      <c r="E208" s="63"/>
+      <c r="F208" s="63"/>
+      <c r="G208" s="63"/>
+      <c r="H208" s="63"/>
+      <c r="I208" s="63"/>
+      <c r="J208" s="63"/>
+      <c r="K208" s="63"/>
+      <c r="L208" s="63"/>
+      <c r="M208" s="63"/>
+      <c r="N208" s="63"/>
+      <c r="O208" s="74"/>
+      <c r="P208" s="47"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C9:C208">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>AND(C9&lt;&gt;"",COUNTIF($C$9:$C$208,C9)&gt;1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="7">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Unusual scale" error="The usual scales are 1, 1000 and 1000000. Keep this value?" promptTitle="Amount scale" prompt="1 = units, 1000 = thousands, 1000000 = millions of the reporting currency." sqref="D4">
+      <formula1>"1,1000,1000000"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter an amount of zero or more." promptTitle="Absolute tolerance" prompt="Largest difference, in reporting-currency units, that still matches." sqref="D5">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a number of zero or more." promptTitle="Relative tolerance" prompt="Largest difference as a share of the bank figure that still matches, for example 0.01% (0.0001)." sqref="D6">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Duplicate ID" error="This netting set ID is already listed. Keep it? It will not be compared." promptTitle="Netting set ID" prompt="The bank's ID of the netting set, as on NettingSets. A repeated ID is reported as DUPLICATE and not compared." sqref="C9:C208">
+      <formula1>COUNTIF($C$9:$C$208,C9)=1</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid regime" error="Choose BCBS or CRR." promptTitle="Regime" prompt="BCBS or CRR: the regime of the bank's figures. Figures of another regime than Results are not compared." sqref="D9:D208">
+      <formula1>"BCBS,CRR"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid amount" error="Enter a number, or leave the cell blank." promptTitle="Bank figure" prompt="The bank's figure in the amount scale above; blank = not compared." sqref="E9:N208">
+      <formula1>ISNUMBER(E9)</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid multiplier" error="Enter a number greater than zero." promptTitle="Multiplier" prompt="The bank's PFE multiplier, between 0 and 1; not scaled." sqref="O9:O208">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <sheetPr codeName="shReconciliation">
+    <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="4" customWidth="1"/>
+    <col min="3" max="3" width="14.75" style="7" customWidth="1"/>
+    <col min="4" max="4" width="7.75" style="10" customWidth="1"/>
+    <col min="5" max="5" width="9.75" style="9" customWidth="1"/>
+    <col min="6" max="6" width="10.75" style="9" customWidth="1"/>
+    <col min="7" max="7" width="26.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.75" style="7" customWidth="1"/>
+    <col min="9" max="9" width="16.75" style="11" customWidth="1"/>
+    <col min="10" max="10" width="16.75" style="11" customWidth="1"/>
+    <col min="11" max="11" width="16.75" style="11" customWidth="1"/>
+    <col min="12" max="12" width="12.75" style="16" customWidth="1"/>
+    <col min="13" max="13" width="22.75" style="7" customWidth="1"/>
+    <col min="14" max="14" width="80.75" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+    </row>
+    <row r="2" spans="2:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="30" t="s">
+        <v>925</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+    </row>
+    <row r="3" spans="2:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C4" s="14" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C5" s="14" t="str" cm="1">
+        <f t="array" ref="C5">ReconciliationStatusText(SACCR_ReconInputs,SACCR_RunInputs,BankNettingSets!$1:$1048576,NettingSets!$C:$Q,Trades!$C:$AA,Params!$1:$1048576)</f>
+        <v>No reconciliation: enter bank figures on BankNettingSets and press Run SA-CCR.</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>927</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>928</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>929</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>930</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>931</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>932</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>933</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>935</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>515</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>570</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C5">
+    <cfRule type="beginsWith" dxfId="2" priority="3" operator="beginsWith" text="OUT OF DATE">
+      <formula>LEFT(C5,LEN("OUT OF DATE"))="OUT OF DATE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M100000">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"MATCH"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>AND(M7&lt;&gt;"",M7&lt;&gt;"MATCH")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
 </worksheet>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -18,12 +18,14 @@
     <sheet name="Checks" sheetId="9" r:id="rId9"/>
     <sheet name="BankNettingSets" sheetId="13" r:id="rId17"/>
     <sheet name="Reconciliation" sheetId="14" r:id="rId18"/>
+    <sheet name="BankTrades" sheetId="15" r:id="rId19"/>
+    <sheet name="TradeReconciliation" sheetId="16" r:id="rId20"/>
     <sheet name="TestCatalogue" sheetId="10" r:id="rId10"/>
     <sheet name="FormulaTest" sheetId="11" r:id="rId11"/>
     <sheet name="Basel_vs_CRR" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">Basel_vs_CRR!$C$5:$K$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">Basel_vs_CRR!$C$5:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Trades!$C$4:$AB$69</definedName>
     <definedName name="Alpha">Params!$E$8</definedName>
     <definedName name="AsOfDate">Params!$E$6</definedName>
@@ -31,6 +33,10 @@
     <definedName name="BankNS_AbsTol">BankNettingSets!$D$5</definedName>
     <definedName name="BankNS_RelTol">BankNettingSets!$D$6</definedName>
     <definedName name="BankNS_Scale">BankNettingSets!$D$4</definedName>
+    <definedName name="BankTR_AbsTol">BankTrades!$D$5</definedName>
+    <definedName name="BankTR_RelTol">BankTrades!$D$6</definedName>
+    <definedName name="BankTR_Scale">BankTrades!$D$4</definedName>
+    <definedName name="BankTrades_Header">BankTrades!$C$8</definedName>
     <definedName name="BasisFactor">Params!$E$17</definedName>
     <definedName name="BusinessDaysPerYear">Params!$E$11</definedName>
     <definedName name="DaysPerYear">Params!$E$10</definedName>
@@ -54,6 +60,7 @@
     <definedName name="ReportingCcy">Params!$E$7</definedName>
     <definedName name="SACCR_ReconInputs" hidden="1">""</definedName>
     <definedName name="SACCR_RunInputs" hidden="1">""</definedName>
+    <definedName name="SACCR_TradeReconInputs" hidden="1">""</definedName>
     <definedName name="SDFloorBD">Params!$E$13</definedName>
     <definedName name="SF_Table">Params!$C$28:$K$54</definedName>
     <definedName name="Trades_Header">Trades!$C$4</definedName>
@@ -99,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="949">
   <si>
     <t>K-SACCR</t>
   </si>
@@ -143,7 +150,7 @@
     <t>6. Review</t>
   </si>
   <si>
-    <t>Checks lists every excluded trade and warning. Reconciliation shows MATCH or DIFFERENCE for each bank figure and every netting set that could not be compared. TestCatalogue compares the engine with published / hand-calculated reference values per regime; FormulaTest unit-tests the formula functions.</t>
+    <t>Checks lists every excluded trade and warning. Reconciliation and TradeReconciliation show MATCH or DIFFERENCE for each bank figure and every netting set or trade leg that could not be compared. TestCatalogue compares the engine with published / hand-calculated reference values per regime; FormulaTest unit-tests the formula functions.</t>
   </si>
   <si>
     <t>7. Regime</t>
@@ -2816,7 +2823,7 @@
     <t>Trades: one row per derivative leg. Dropdowns guide the classification. Amounts can be in any currency of the FX table. Legs of one economic trade share an Economic trade ID; exactly one of them (MtM leg = Y) carries the MtM.</t>
   </si>
   <si>
-    <t>Click "Run SA-CCR" (macro RunSACCR). Results, HedgingSets, Buckets, TradeCalc and Checks are rebuilt, and Reconciliation compares the figures entered on BankNettingSets with Results. "Validate inputs" only runs the checks; "Clear outputs" empties the output sheets.</t>
+    <t>Click "Run SA-CCR" (macro RunSACCR). Results, HedgingSets, Buckets, TradeCalc and Checks are rebuilt; Reconciliation and TradeReconciliation compare the figures entered on BankNettingSets and BankTrades with Results and TradeCalc. "Validate inputs" only runs the checks; "Clear outputs" empties the output sheets.</t>
   </si>
   <si>
     <t>Positive amount; the sign comes from Direction. IR / CR: trade notional. FX: the notional of one leg, in that leg's currency (one of the pair): the foreign-currency leg or, when both legs are foreign, the larger one in reporting currency. EQ / CO: market price x units.</t>
@@ -2928,6 +2935,36 @@
   </si>
   <si>
     <t>Output - each bank figure against Results: MATCH, DIFFERENCE, and every netting set not compared, with the reason</t>
+  </si>
+  <si>
+    <t>Bank trade-leg results</t>
+  </si>
+  <si>
+    <t>Enter the bank's own figures per trade leg, by Trade ID as on Trades. Run SA-CCR compares them with TradeCalc on the TradeReconciliation sheet. A blank figure is not compared.</t>
+  </si>
+  <si>
+    <t>Units of the reporting currency per bank amount: 1, 1000 (thousands) or 1000000 (millions). M, the supervisory duration, the delta and the maturity factors are not scaled.</t>
+  </si>
+  <si>
+    <t>In units of the reporting currency. Used for amounts only.</t>
+  </si>
+  <si>
+    <t>Trade reconciliation</t>
+  </si>
+  <si>
+    <t>No reconciliation yet: enter bank figures on BankTrades and press Run SA-CCR.</t>
+  </si>
+  <si>
+    <t>BankTrades</t>
+  </si>
+  <si>
+    <t>Inputs - the bank's own figures per trade leg, to reconcile with TradeCalc; amount scale and tolerances at the top</t>
+  </si>
+  <si>
+    <t>TradeReconciliation</t>
+  </si>
+  <si>
+    <t>Output - each bank trade-leg figure against TradeCalc: MATCH, DIFFERENCE, and every leg not compared, with the reason</t>
   </si>
 </sst>
 </file>
@@ -4951,7 +4988,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X72"/>
+  <dimension ref="A1:X74"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
@@ -5305,191 +5342,207 @@
     </row>
     <row r="47" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C47" s="135" t="s">
-        <v>68</v>
+        <v>945</v>
       </c>
       <c r="D47" s="139" t="s">
-        <v>69</v>
+        <v>946</v>
       </c>
     </row>
     <row r="48" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C48" s="135" t="s">
+        <v>947</v>
+      </c>
+      <c r="D48" s="139" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C49" s="135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" s="139" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C50" s="135" t="s">
         <v>896</v>
       </c>
-      <c r="D48" s="139" t="s">
+      <c r="D50" s="139" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C49" s="136" t="s">
+    <row r="51" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C51" s="136" t="s">
         <v>72</v>
       </c>
-      <c r="D49" s="140" t="s">
+      <c r="D51" s="140" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="35"/>
-      <c r="D50" s="36"/>
-    </row>
-    <row r="51" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="33" t="s">
+    <row r="52" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="35"/>
+      <c r="D52" s="36"/>
+    </row>
+    <row r="53" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="D51" s="37"/>
-    </row>
-    <row r="52" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C52" s="134" t="s">
+      <c r="D53" s="37"/>
+    </row>
+    <row r="54" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C54" s="134" t="s">
         <v>908</v>
       </c>
-      <c r="D52" s="138" t="s">
+      <c r="D54" s="138" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="53" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C53" s="135" t="s">
-        <v>909</v>
-      </c>
-      <c r="D53" s="139" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C54" s="135" t="s">
-        <v>78</v>
-      </c>
-      <c r="D54" s="139" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="55" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C55" s="135" t="s">
-        <v>80</v>
+        <v>909</v>
       </c>
       <c r="D55" s="139" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C56" s="135" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D56" s="139" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C57" s="135" t="s">
-        <v>910</v>
+        <v>80</v>
       </c>
       <c r="D57" s="139" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C58" s="135" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D58" s="139" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C59" s="135" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D59" s="139" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C60" s="135" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" s="139" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C61" s="135" t="s">
+        <v>911</v>
+      </c>
+      <c r="D61" s="139" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="62" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C62" s="135" t="s">
         <v>90</v>
       </c>
-      <c r="D60" s="139" t="s">
+      <c r="D62" s="139" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="61" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C61" s="136" t="s">
+    <row r="63" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C63" s="136" t="s">
         <v>92</v>
       </c>
-      <c r="D61" s="140" t="s">
+      <c r="D63" s="140" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="62" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="35"/>
-      <c r="D62" s="36"/>
-    </row>
-    <row r="63" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="33" t="s">
+    <row r="64" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="35"/>
+      <c r="D64" s="36"/>
+    </row>
+    <row r="65" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="D63" s="37"/>
-    </row>
-    <row r="64" spans="3:4" ht="46" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C64" s="134" t="s">
+      <c r="D65" s="37"/>
+    </row>
+    <row r="66" spans="3:4" ht="46" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C66" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="D64" s="138" t="s">
+      <c r="D66" s="138" t="s">
         <v>912</v>
-      </c>
-    </row>
-    <row r="65" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C65" s="135" t="s">
-        <v>805</v>
-      </c>
-      <c r="D65" s="139" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="66" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C66" s="135" t="s">
-        <v>96</v>
-      </c>
-      <c r="D66" s="139" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="67" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C67" s="135" t="s">
-        <v>97</v>
+        <v>805</v>
       </c>
       <c r="D67" s="139" t="s">
-        <v>913</v>
+        <v>804</v>
       </c>
     </row>
     <row r="68" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
       <c r="C68" s="135" t="s">
+        <v>96</v>
+      </c>
+      <c r="D68" s="139" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C69" s="135" t="s">
+        <v>97</v>
+      </c>
+      <c r="D69" s="139" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C70" s="135" t="s">
         <v>98</v>
       </c>
-      <c r="D68" s="139" t="s">
+      <c r="D70" s="139" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="69" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C69" s="136" t="s">
+    <row r="71" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C71" s="136" t="s">
         <v>100</v>
       </c>
-      <c r="D69" s="140" t="s">
+      <c r="D71" s="140" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="70" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="35"/>
-      <c r="D70" s="36"/>
-    </row>
-    <row r="71" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C71" s="33" t="s">
+    <row r="72" spans="3:4" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C72" s="35"/>
+      <c r="D72" s="36"/>
+    </row>
+    <row r="73" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C73" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="D71" s="37"/>
-    </row>
-    <row r="72" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
-      <c r="C72" s="137" t="s">
+      <c r="D73" s="37"/>
+    </row>
+    <row r="74" spans="3:4" ht="34" customHeight="1" x14ac:dyDescent="0.25" outlineLevel="1">
+      <c r="C74" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="D72" s="141" t="s">
+      <c r="D74" s="141" t="s">
         <v>915</v>
       </c>
     </row>
@@ -15254,6 +15307,7793 @@
       </c>
       <c r="F6" s="15" t="s">
         <v>929</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>930</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>931</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>932</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>933</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>935</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>515</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>570</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C5">
+    <cfRule type="beginsWith" dxfId="2" priority="3" operator="beginsWith" text="OUT OF DATE">
+      <formula>LEFT(C5,LEN("OUT OF DATE"))="OUT OF DATE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M100000">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"MATCH"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>AND(M7&lt;&gt;"",M7&lt;&gt;"MATCH")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <sheetPr codeName="shBankTrades">
+    <tabColor rgb="FFBF9000"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O508"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="4" customWidth="1"/>
+    <col min="3" max="3" width="20.625" style="36" customWidth="1"/>
+    <col min="4" max="14" width="14.625" style="36" customWidth="1"/>
+    <col min="15" max="15" width="40.625" style="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+    </row>
+    <row r="2" spans="2:15" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="30" t="s">
+        <v>939</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+    </row>
+    <row r="3" spans="2:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="43" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="36" t="s">
+        <v>918</v>
+      </c>
+      <c r="D4" s="61">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="36" t="s">
+        <v>920</v>
+      </c>
+      <c r="D5" s="63">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="36" t="s">
+        <v>922</v>
+      </c>
+      <c r="D6" s="131">
+        <v>0.0001</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" s="36" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="58" t="s">
+        <v>294</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>488</v>
+      </c>
+      <c r="E8" s="59" t="s">
+        <v>489</v>
+      </c>
+      <c r="F8" s="59" t="s">
+        <v>862</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="59" t="s">
+        <v>494</v>
+      </c>
+      <c r="I8" s="59" t="s">
+        <v>495</v>
+      </c>
+      <c r="J8" s="59" t="s">
+        <v>496</v>
+      </c>
+      <c r="K8" s="59" t="s">
+        <v>497</v>
+      </c>
+      <c r="L8" s="59" t="s">
+        <v>480</v>
+      </c>
+      <c r="M8" s="59" t="s">
+        <v>481</v>
+      </c>
+      <c r="N8" s="59" t="s">
+        <v>499</v>
+      </c>
+      <c r="O8" s="59" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="60"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="74"/>
+      <c r="J9" s="74"/>
+      <c r="K9" s="74"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="47"/>
+    </row>
+    <row r="10" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="60"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
+      <c r="N10" s="63"/>
+      <c r="O10" s="47"/>
+    </row>
+    <row r="11" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="60"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="74"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="63"/>
+      <c r="O11" s="47"/>
+    </row>
+    <row r="12" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="60"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="63"/>
+      <c r="O12" s="47"/>
+    </row>
+    <row r="13" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="60"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="74"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="47"/>
+    </row>
+    <row r="14" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="60"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="74"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="47"/>
+    </row>
+    <row r="15" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="60"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="74"/>
+      <c r="K15" s="74"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="47"/>
+    </row>
+    <row r="16" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="60"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="74"/>
+      <c r="K16" s="74"/>
+      <c r="L16" s="63"/>
+      <c r="M16" s="63"/>
+      <c r="N16" s="63"/>
+      <c r="O16" s="47"/>
+    </row>
+    <row r="17" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="60"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="74"/>
+      <c r="K17" s="74"/>
+      <c r="L17" s="63"/>
+      <c r="M17" s="63"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="47"/>
+    </row>
+    <row r="18" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="60"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="74"/>
+      <c r="K18" s="74"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="47"/>
+    </row>
+    <row r="19" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="60"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="74"/>
+      <c r="K19" s="74"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="47"/>
+    </row>
+    <row r="20" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="60"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="74"/>
+      <c r="L20" s="63"/>
+      <c r="M20" s="63"/>
+      <c r="N20" s="63"/>
+      <c r="O20" s="47"/>
+    </row>
+    <row r="21" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="60"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="74"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="63"/>
+      <c r="M21" s="63"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="47"/>
+    </row>
+    <row r="22" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="60"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="63"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="47"/>
+    </row>
+    <row r="23" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="60"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="74"/>
+      <c r="J23" s="74"/>
+      <c r="K23" s="74"/>
+      <c r="L23" s="63"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="47"/>
+    </row>
+    <row r="24" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="60"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="74"/>
+      <c r="K24" s="74"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="47"/>
+    </row>
+    <row r="25" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="60"/>
+      <c r="D25" s="63"/>
+      <c r="E25" s="63"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="74"/>
+      <c r="K25" s="74"/>
+      <c r="L25" s="63"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="47"/>
+    </row>
+    <row r="26" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="60"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="63"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="47"/>
+    </row>
+    <row r="27" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="60"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="63"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="47"/>
+    </row>
+    <row r="28" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="60"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="74"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="63"/>
+      <c r="M28" s="63"/>
+      <c r="N28" s="63"/>
+      <c r="O28" s="47"/>
+    </row>
+    <row r="29" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="60"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="74"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="63"/>
+      <c r="M29" s="63"/>
+      <c r="N29" s="63"/>
+      <c r="O29" s="47"/>
+    </row>
+    <row r="30" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="60"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="63"/>
+      <c r="M30" s="63"/>
+      <c r="N30" s="63"/>
+      <c r="O30" s="47"/>
+    </row>
+    <row r="31" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="60"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="74"/>
+      <c r="L31" s="63"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="47"/>
+    </row>
+    <row r="32" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="60"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="74"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="74"/>
+      <c r="J32" s="74"/>
+      <c r="K32" s="74"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="63"/>
+      <c r="N32" s="63"/>
+      <c r="O32" s="47"/>
+    </row>
+    <row r="33" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="60"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="74"/>
+      <c r="H33" s="63"/>
+      <c r="I33" s="74"/>
+      <c r="J33" s="74"/>
+      <c r="K33" s="74"/>
+      <c r="L33" s="63"/>
+      <c r="M33" s="63"/>
+      <c r="N33" s="63"/>
+      <c r="O33" s="47"/>
+    </row>
+    <row r="34" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="60"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="74"/>
+      <c r="J34" s="74"/>
+      <c r="K34" s="74"/>
+      <c r="L34" s="63"/>
+      <c r="M34" s="63"/>
+      <c r="N34" s="63"/>
+      <c r="O34" s="47"/>
+    </row>
+    <row r="35" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="60"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="74"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="74"/>
+      <c r="J35" s="74"/>
+      <c r="K35" s="74"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="47"/>
+    </row>
+    <row r="36" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="60"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="74"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="74"/>
+      <c r="J36" s="74"/>
+      <c r="K36" s="74"/>
+      <c r="L36" s="63"/>
+      <c r="M36" s="63"/>
+      <c r="N36" s="63"/>
+      <c r="O36" s="47"/>
+    </row>
+    <row r="37" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="60"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="74"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="74"/>
+      <c r="J37" s="74"/>
+      <c r="K37" s="74"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="63"/>
+      <c r="O37" s="47"/>
+    </row>
+    <row r="38" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="60"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="74"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="74"/>
+      <c r="J38" s="74"/>
+      <c r="K38" s="74"/>
+      <c r="L38" s="63"/>
+      <c r="M38" s="63"/>
+      <c r="N38" s="63"/>
+      <c r="O38" s="47"/>
+    </row>
+    <row r="39" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="60"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="74"/>
+      <c r="G39" s="74"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="74"/>
+      <c r="J39" s="74"/>
+      <c r="K39" s="74"/>
+      <c r="L39" s="63"/>
+      <c r="M39" s="63"/>
+      <c r="N39" s="63"/>
+      <c r="O39" s="47"/>
+    </row>
+    <row r="40" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="60"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="74"/>
+      <c r="G40" s="74"/>
+      <c r="H40" s="63"/>
+      <c r="I40" s="74"/>
+      <c r="J40" s="74"/>
+      <c r="K40" s="74"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="63"/>
+      <c r="O40" s="47"/>
+    </row>
+    <row r="41" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="60"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="74"/>
+      <c r="G41" s="74"/>
+      <c r="H41" s="63"/>
+      <c r="I41" s="74"/>
+      <c r="J41" s="74"/>
+      <c r="K41" s="74"/>
+      <c r="L41" s="63"/>
+      <c r="M41" s="63"/>
+      <c r="N41" s="63"/>
+      <c r="O41" s="47"/>
+    </row>
+    <row r="42" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="60"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="74"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="74"/>
+      <c r="L42" s="63"/>
+      <c r="M42" s="63"/>
+      <c r="N42" s="63"/>
+      <c r="O42" s="47"/>
+    </row>
+    <row r="43" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="60"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63"/>
+      <c r="F43" s="74"/>
+      <c r="G43" s="74"/>
+      <c r="H43" s="63"/>
+      <c r="I43" s="74"/>
+      <c r="J43" s="74"/>
+      <c r="K43" s="74"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="63"/>
+      <c r="N43" s="63"/>
+      <c r="O43" s="47"/>
+    </row>
+    <row r="44" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="60"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="74"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="74"/>
+      <c r="J44" s="74"/>
+      <c r="K44" s="74"/>
+      <c r="L44" s="63"/>
+      <c r="M44" s="63"/>
+      <c r="N44" s="63"/>
+      <c r="O44" s="47"/>
+    </row>
+    <row r="45" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="60"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="74"/>
+      <c r="G45" s="74"/>
+      <c r="H45" s="63"/>
+      <c r="I45" s="74"/>
+      <c r="J45" s="74"/>
+      <c r="K45" s="74"/>
+      <c r="L45" s="63"/>
+      <c r="M45" s="63"/>
+      <c r="N45" s="63"/>
+      <c r="O45" s="47"/>
+    </row>
+    <row r="46" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="60"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="74"/>
+      <c r="G46" s="74"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="74"/>
+      <c r="J46" s="74"/>
+      <c r="K46" s="74"/>
+      <c r="L46" s="63"/>
+      <c r="M46" s="63"/>
+      <c r="N46" s="63"/>
+      <c r="O46" s="47"/>
+    </row>
+    <row r="47" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="60"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="74"/>
+      <c r="H47" s="63"/>
+      <c r="I47" s="74"/>
+      <c r="J47" s="74"/>
+      <c r="K47" s="74"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="63"/>
+      <c r="N47" s="63"/>
+      <c r="O47" s="47"/>
+    </row>
+    <row r="48" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="60"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="74"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="74"/>
+      <c r="J48" s="74"/>
+      <c r="K48" s="74"/>
+      <c r="L48" s="63"/>
+      <c r="M48" s="63"/>
+      <c r="N48" s="63"/>
+      <c r="O48" s="47"/>
+    </row>
+    <row r="49" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="60"/>
+      <c r="D49" s="63"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="74"/>
+      <c r="H49" s="63"/>
+      <c r="I49" s="74"/>
+      <c r="J49" s="74"/>
+      <c r="K49" s="74"/>
+      <c r="L49" s="63"/>
+      <c r="M49" s="63"/>
+      <c r="N49" s="63"/>
+      <c r="O49" s="47"/>
+    </row>
+    <row r="50" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="60"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="74"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="74"/>
+      <c r="J50" s="74"/>
+      <c r="K50" s="74"/>
+      <c r="L50" s="63"/>
+      <c r="M50" s="63"/>
+      <c r="N50" s="63"/>
+      <c r="O50" s="47"/>
+    </row>
+    <row r="51" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="60"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="74"/>
+      <c r="G51" s="74"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="74"/>
+      <c r="J51" s="74"/>
+      <c r="K51" s="74"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="63"/>
+      <c r="O51" s="47"/>
+    </row>
+    <row r="52" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="60"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="74"/>
+      <c r="G52" s="74"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="74"/>
+      <c r="J52" s="74"/>
+      <c r="K52" s="74"/>
+      <c r="L52" s="63"/>
+      <c r="M52" s="63"/>
+      <c r="N52" s="63"/>
+      <c r="O52" s="47"/>
+    </row>
+    <row r="53" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="60"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="63"/>
+      <c r="F53" s="74"/>
+      <c r="G53" s="74"/>
+      <c r="H53" s="63"/>
+      <c r="I53" s="74"/>
+      <c r="J53" s="74"/>
+      <c r="K53" s="74"/>
+      <c r="L53" s="63"/>
+      <c r="M53" s="63"/>
+      <c r="N53" s="63"/>
+      <c r="O53" s="47"/>
+    </row>
+    <row r="54" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="60"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="63"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="63"/>
+      <c r="I54" s="74"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="74"/>
+      <c r="L54" s="63"/>
+      <c r="M54" s="63"/>
+      <c r="N54" s="63"/>
+      <c r="O54" s="47"/>
+    </row>
+    <row r="55" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="60"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="74"/>
+      <c r="G55" s="74"/>
+      <c r="H55" s="63"/>
+      <c r="I55" s="74"/>
+      <c r="J55" s="74"/>
+      <c r="K55" s="74"/>
+      <c r="L55" s="63"/>
+      <c r="M55" s="63"/>
+      <c r="N55" s="63"/>
+      <c r="O55" s="47"/>
+    </row>
+    <row r="56" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="60"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="74"/>
+      <c r="G56" s="74"/>
+      <c r="H56" s="63"/>
+      <c r="I56" s="74"/>
+      <c r="J56" s="74"/>
+      <c r="K56" s="74"/>
+      <c r="L56" s="63"/>
+      <c r="M56" s="63"/>
+      <c r="N56" s="63"/>
+      <c r="O56" s="47"/>
+    </row>
+    <row r="57" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="60"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="74"/>
+      <c r="G57" s="74"/>
+      <c r="H57" s="63"/>
+      <c r="I57" s="74"/>
+      <c r="J57" s="74"/>
+      <c r="K57" s="74"/>
+      <c r="L57" s="63"/>
+      <c r="M57" s="63"/>
+      <c r="N57" s="63"/>
+      <c r="O57" s="47"/>
+    </row>
+    <row r="58" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C58" s="60"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
+      <c r="F58" s="74"/>
+      <c r="G58" s="74"/>
+      <c r="H58" s="63"/>
+      <c r="I58" s="74"/>
+      <c r="J58" s="74"/>
+      <c r="K58" s="74"/>
+      <c r="L58" s="63"/>
+      <c r="M58" s="63"/>
+      <c r="N58" s="63"/>
+      <c r="O58" s="47"/>
+    </row>
+    <row r="59" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="60"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="63"/>
+      <c r="F59" s="74"/>
+      <c r="G59" s="74"/>
+      <c r="H59" s="63"/>
+      <c r="I59" s="74"/>
+      <c r="J59" s="74"/>
+      <c r="K59" s="74"/>
+      <c r="L59" s="63"/>
+      <c r="M59" s="63"/>
+      <c r="N59" s="63"/>
+      <c r="O59" s="47"/>
+    </row>
+    <row r="60" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="60"/>
+      <c r="D60" s="63"/>
+      <c r="E60" s="63"/>
+      <c r="F60" s="74"/>
+      <c r="G60" s="74"/>
+      <c r="H60" s="63"/>
+      <c r="I60" s="74"/>
+      <c r="J60" s="74"/>
+      <c r="K60" s="74"/>
+      <c r="L60" s="63"/>
+      <c r="M60" s="63"/>
+      <c r="N60" s="63"/>
+      <c r="O60" s="47"/>
+    </row>
+    <row r="61" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="60"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="63"/>
+      <c r="F61" s="74"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="63"/>
+      <c r="I61" s="74"/>
+      <c r="J61" s="74"/>
+      <c r="K61" s="74"/>
+      <c r="L61" s="63"/>
+      <c r="M61" s="63"/>
+      <c r="N61" s="63"/>
+      <c r="O61" s="47"/>
+    </row>
+    <row r="62" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="60"/>
+      <c r="D62" s="63"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="74"/>
+      <c r="G62" s="74"/>
+      <c r="H62" s="63"/>
+      <c r="I62" s="74"/>
+      <c r="J62" s="74"/>
+      <c r="K62" s="74"/>
+      <c r="L62" s="63"/>
+      <c r="M62" s="63"/>
+      <c r="N62" s="63"/>
+      <c r="O62" s="47"/>
+    </row>
+    <row r="63" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C63" s="60"/>
+      <c r="D63" s="63"/>
+      <c r="E63" s="63"/>
+      <c r="F63" s="74"/>
+      <c r="G63" s="74"/>
+      <c r="H63" s="63"/>
+      <c r="I63" s="74"/>
+      <c r="J63" s="74"/>
+      <c r="K63" s="74"/>
+      <c r="L63" s="63"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="63"/>
+      <c r="O63" s="47"/>
+    </row>
+    <row r="64" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="60"/>
+      <c r="D64" s="63"/>
+      <c r="E64" s="63"/>
+      <c r="F64" s="74"/>
+      <c r="G64" s="74"/>
+      <c r="H64" s="63"/>
+      <c r="I64" s="74"/>
+      <c r="J64" s="74"/>
+      <c r="K64" s="74"/>
+      <c r="L64" s="63"/>
+      <c r="M64" s="63"/>
+      <c r="N64" s="63"/>
+      <c r="O64" s="47"/>
+    </row>
+    <row r="65" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="60"/>
+      <c r="D65" s="63"/>
+      <c r="E65" s="63"/>
+      <c r="F65" s="74"/>
+      <c r="G65" s="74"/>
+      <c r="H65" s="63"/>
+      <c r="I65" s="74"/>
+      <c r="J65" s="74"/>
+      <c r="K65" s="74"/>
+      <c r="L65" s="63"/>
+      <c r="M65" s="63"/>
+      <c r="N65" s="63"/>
+      <c r="O65" s="47"/>
+    </row>
+    <row r="66" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="60"/>
+      <c r="D66" s="63"/>
+      <c r="E66" s="63"/>
+      <c r="F66" s="74"/>
+      <c r="G66" s="74"/>
+      <c r="H66" s="63"/>
+      <c r="I66" s="74"/>
+      <c r="J66" s="74"/>
+      <c r="K66" s="74"/>
+      <c r="L66" s="63"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="63"/>
+      <c r="O66" s="47"/>
+    </row>
+    <row r="67" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="60"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="63"/>
+      <c r="F67" s="74"/>
+      <c r="G67" s="74"/>
+      <c r="H67" s="63"/>
+      <c r="I67" s="74"/>
+      <c r="J67" s="74"/>
+      <c r="K67" s="74"/>
+      <c r="L67" s="63"/>
+      <c r="M67" s="63"/>
+      <c r="N67" s="63"/>
+      <c r="O67" s="47"/>
+    </row>
+    <row r="68" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="60"/>
+      <c r="D68" s="63"/>
+      <c r="E68" s="63"/>
+      <c r="F68" s="74"/>
+      <c r="G68" s="74"/>
+      <c r="H68" s="63"/>
+      <c r="I68" s="74"/>
+      <c r="J68" s="74"/>
+      <c r="K68" s="74"/>
+      <c r="L68" s="63"/>
+      <c r="M68" s="63"/>
+      <c r="N68" s="63"/>
+      <c r="O68" s="47"/>
+    </row>
+    <row r="69" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="60"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="74"/>
+      <c r="G69" s="74"/>
+      <c r="H69" s="63"/>
+      <c r="I69" s="74"/>
+      <c r="J69" s="74"/>
+      <c r="K69" s="74"/>
+      <c r="L69" s="63"/>
+      <c r="M69" s="63"/>
+      <c r="N69" s="63"/>
+      <c r="O69" s="47"/>
+    </row>
+    <row r="70" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="60"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="74"/>
+      <c r="G70" s="74"/>
+      <c r="H70" s="63"/>
+      <c r="I70" s="74"/>
+      <c r="J70" s="74"/>
+      <c r="K70" s="74"/>
+      <c r="L70" s="63"/>
+      <c r="M70" s="63"/>
+      <c r="N70" s="63"/>
+      <c r="O70" s="47"/>
+    </row>
+    <row r="71" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C71" s="60"/>
+      <c r="D71" s="63"/>
+      <c r="E71" s="63"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="74"/>
+      <c r="H71" s="63"/>
+      <c r="I71" s="74"/>
+      <c r="J71" s="74"/>
+      <c r="K71" s="74"/>
+      <c r="L71" s="63"/>
+      <c r="M71" s="63"/>
+      <c r="N71" s="63"/>
+      <c r="O71" s="47"/>
+    </row>
+    <row r="72" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C72" s="60"/>
+      <c r="D72" s="63"/>
+      <c r="E72" s="63"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="74"/>
+      <c r="H72" s="63"/>
+      <c r="I72" s="74"/>
+      <c r="J72" s="74"/>
+      <c r="K72" s="74"/>
+      <c r="L72" s="63"/>
+      <c r="M72" s="63"/>
+      <c r="N72" s="63"/>
+      <c r="O72" s="47"/>
+    </row>
+    <row r="73" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C73" s="60"/>
+      <c r="D73" s="63"/>
+      <c r="E73" s="63"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="74"/>
+      <c r="H73" s="63"/>
+      <c r="I73" s="74"/>
+      <c r="J73" s="74"/>
+      <c r="K73" s="74"/>
+      <c r="L73" s="63"/>
+      <c r="M73" s="63"/>
+      <c r="N73" s="63"/>
+      <c r="O73" s="47"/>
+    </row>
+    <row r="74" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C74" s="60"/>
+      <c r="D74" s="63"/>
+      <c r="E74" s="63"/>
+      <c r="F74" s="74"/>
+      <c r="G74" s="74"/>
+      <c r="H74" s="63"/>
+      <c r="I74" s="74"/>
+      <c r="J74" s="74"/>
+      <c r="K74" s="74"/>
+      <c r="L74" s="63"/>
+      <c r="M74" s="63"/>
+      <c r="N74" s="63"/>
+      <c r="O74" s="47"/>
+    </row>
+    <row r="75" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C75" s="60"/>
+      <c r="D75" s="63"/>
+      <c r="E75" s="63"/>
+      <c r="F75" s="74"/>
+      <c r="G75" s="74"/>
+      <c r="H75" s="63"/>
+      <c r="I75" s="74"/>
+      <c r="J75" s="74"/>
+      <c r="K75" s="74"/>
+      <c r="L75" s="63"/>
+      <c r="M75" s="63"/>
+      <c r="N75" s="63"/>
+      <c r="O75" s="47"/>
+    </row>
+    <row r="76" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C76" s="60"/>
+      <c r="D76" s="63"/>
+      <c r="E76" s="63"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="74"/>
+      <c r="H76" s="63"/>
+      <c r="I76" s="74"/>
+      <c r="J76" s="74"/>
+      <c r="K76" s="74"/>
+      <c r="L76" s="63"/>
+      <c r="M76" s="63"/>
+      <c r="N76" s="63"/>
+      <c r="O76" s="47"/>
+    </row>
+    <row r="77" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C77" s="60"/>
+      <c r="D77" s="63"/>
+      <c r="E77" s="63"/>
+      <c r="F77" s="74"/>
+      <c r="G77" s="74"/>
+      <c r="H77" s="63"/>
+      <c r="I77" s="74"/>
+      <c r="J77" s="74"/>
+      <c r="K77" s="74"/>
+      <c r="L77" s="63"/>
+      <c r="M77" s="63"/>
+      <c r="N77" s="63"/>
+      <c r="O77" s="47"/>
+    </row>
+    <row r="78" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C78" s="60"/>
+      <c r="D78" s="63"/>
+      <c r="E78" s="63"/>
+      <c r="F78" s="74"/>
+      <c r="G78" s="74"/>
+      <c r="H78" s="63"/>
+      <c r="I78" s="74"/>
+      <c r="J78" s="74"/>
+      <c r="K78" s="74"/>
+      <c r="L78" s="63"/>
+      <c r="M78" s="63"/>
+      <c r="N78" s="63"/>
+      <c r="O78" s="47"/>
+    </row>
+    <row r="79" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C79" s="60"/>
+      <c r="D79" s="63"/>
+      <c r="E79" s="63"/>
+      <c r="F79" s="74"/>
+      <c r="G79" s="74"/>
+      <c r="H79" s="63"/>
+      <c r="I79" s="74"/>
+      <c r="J79" s="74"/>
+      <c r="K79" s="74"/>
+      <c r="L79" s="63"/>
+      <c r="M79" s="63"/>
+      <c r="N79" s="63"/>
+      <c r="O79" s="47"/>
+    </row>
+    <row r="80" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C80" s="60"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="63"/>
+      <c r="F80" s="74"/>
+      <c r="G80" s="74"/>
+      <c r="H80" s="63"/>
+      <c r="I80" s="74"/>
+      <c r="J80" s="74"/>
+      <c r="K80" s="74"/>
+      <c r="L80" s="63"/>
+      <c r="M80" s="63"/>
+      <c r="N80" s="63"/>
+      <c r="O80" s="47"/>
+    </row>
+    <row r="81" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C81" s="60"/>
+      <c r="D81" s="63"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="74"/>
+      <c r="G81" s="74"/>
+      <c r="H81" s="63"/>
+      <c r="I81" s="74"/>
+      <c r="J81" s="74"/>
+      <c r="K81" s="74"/>
+      <c r="L81" s="63"/>
+      <c r="M81" s="63"/>
+      <c r="N81" s="63"/>
+      <c r="O81" s="47"/>
+    </row>
+    <row r="82" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C82" s="60"/>
+      <c r="D82" s="63"/>
+      <c r="E82" s="63"/>
+      <c r="F82" s="74"/>
+      <c r="G82" s="74"/>
+      <c r="H82" s="63"/>
+      <c r="I82" s="74"/>
+      <c r="J82" s="74"/>
+      <c r="K82" s="74"/>
+      <c r="L82" s="63"/>
+      <c r="M82" s="63"/>
+      <c r="N82" s="63"/>
+      <c r="O82" s="47"/>
+    </row>
+    <row r="83" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C83" s="60"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="74"/>
+      <c r="G83" s="74"/>
+      <c r="H83" s="63"/>
+      <c r="I83" s="74"/>
+      <c r="J83" s="74"/>
+      <c r="K83" s="74"/>
+      <c r="L83" s="63"/>
+      <c r="M83" s="63"/>
+      <c r="N83" s="63"/>
+      <c r="O83" s="47"/>
+    </row>
+    <row r="84" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C84" s="60"/>
+      <c r="D84" s="63"/>
+      <c r="E84" s="63"/>
+      <c r="F84" s="74"/>
+      <c r="G84" s="74"/>
+      <c r="H84" s="63"/>
+      <c r="I84" s="74"/>
+      <c r="J84" s="74"/>
+      <c r="K84" s="74"/>
+      <c r="L84" s="63"/>
+      <c r="M84" s="63"/>
+      <c r="N84" s="63"/>
+      <c r="O84" s="47"/>
+    </row>
+    <row r="85" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C85" s="60"/>
+      <c r="D85" s="63"/>
+      <c r="E85" s="63"/>
+      <c r="F85" s="74"/>
+      <c r="G85" s="74"/>
+      <c r="H85" s="63"/>
+      <c r="I85" s="74"/>
+      <c r="J85" s="74"/>
+      <c r="K85" s="74"/>
+      <c r="L85" s="63"/>
+      <c r="M85" s="63"/>
+      <c r="N85" s="63"/>
+      <c r="O85" s="47"/>
+    </row>
+    <row r="86" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C86" s="60"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="74"/>
+      <c r="G86" s="74"/>
+      <c r="H86" s="63"/>
+      <c r="I86" s="74"/>
+      <c r="J86" s="74"/>
+      <c r="K86" s="74"/>
+      <c r="L86" s="63"/>
+      <c r="M86" s="63"/>
+      <c r="N86" s="63"/>
+      <c r="O86" s="47"/>
+    </row>
+    <row r="87" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C87" s="60"/>
+      <c r="D87" s="63"/>
+      <c r="E87" s="63"/>
+      <c r="F87" s="74"/>
+      <c r="G87" s="74"/>
+      <c r="H87" s="63"/>
+      <c r="I87" s="74"/>
+      <c r="J87" s="74"/>
+      <c r="K87" s="74"/>
+      <c r="L87" s="63"/>
+      <c r="M87" s="63"/>
+      <c r="N87" s="63"/>
+      <c r="O87" s="47"/>
+    </row>
+    <row r="88" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C88" s="60"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="63"/>
+      <c r="F88" s="74"/>
+      <c r="G88" s="74"/>
+      <c r="H88" s="63"/>
+      <c r="I88" s="74"/>
+      <c r="J88" s="74"/>
+      <c r="K88" s="74"/>
+      <c r="L88" s="63"/>
+      <c r="M88" s="63"/>
+      <c r="N88" s="63"/>
+      <c r="O88" s="47"/>
+    </row>
+    <row r="89" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C89" s="60"/>
+      <c r="D89" s="63"/>
+      <c r="E89" s="63"/>
+      <c r="F89" s="74"/>
+      <c r="G89" s="74"/>
+      <c r="H89" s="63"/>
+      <c r="I89" s="74"/>
+      <c r="J89" s="74"/>
+      <c r="K89" s="74"/>
+      <c r="L89" s="63"/>
+      <c r="M89" s="63"/>
+      <c r="N89" s="63"/>
+      <c r="O89" s="47"/>
+    </row>
+    <row r="90" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C90" s="60"/>
+      <c r="D90" s="63"/>
+      <c r="E90" s="63"/>
+      <c r="F90" s="74"/>
+      <c r="G90" s="74"/>
+      <c r="H90" s="63"/>
+      <c r="I90" s="74"/>
+      <c r="J90" s="74"/>
+      <c r="K90" s="74"/>
+      <c r="L90" s="63"/>
+      <c r="M90" s="63"/>
+      <c r="N90" s="63"/>
+      <c r="O90" s="47"/>
+    </row>
+    <row r="91" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C91" s="60"/>
+      <c r="D91" s="63"/>
+      <c r="E91" s="63"/>
+      <c r="F91" s="74"/>
+      <c r="G91" s="74"/>
+      <c r="H91" s="63"/>
+      <c r="I91" s="74"/>
+      <c r="J91" s="74"/>
+      <c r="K91" s="74"/>
+      <c r="L91" s="63"/>
+      <c r="M91" s="63"/>
+      <c r="N91" s="63"/>
+      <c r="O91" s="47"/>
+    </row>
+    <row r="92" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C92" s="60"/>
+      <c r="D92" s="63"/>
+      <c r="E92" s="63"/>
+      <c r="F92" s="74"/>
+      <c r="G92" s="74"/>
+      <c r="H92" s="63"/>
+      <c r="I92" s="74"/>
+      <c r="J92" s="74"/>
+      <c r="K92" s="74"/>
+      <c r="L92" s="63"/>
+      <c r="M92" s="63"/>
+      <c r="N92" s="63"/>
+      <c r="O92" s="47"/>
+    </row>
+    <row r="93" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C93" s="60"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="63"/>
+      <c r="F93" s="74"/>
+      <c r="G93" s="74"/>
+      <c r="H93" s="63"/>
+      <c r="I93" s="74"/>
+      <c r="J93" s="74"/>
+      <c r="K93" s="74"/>
+      <c r="L93" s="63"/>
+      <c r="M93" s="63"/>
+      <c r="N93" s="63"/>
+      <c r="O93" s="47"/>
+    </row>
+    <row r="94" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C94" s="60"/>
+      <c r="D94" s="63"/>
+      <c r="E94" s="63"/>
+      <c r="F94" s="74"/>
+      <c r="G94" s="74"/>
+      <c r="H94" s="63"/>
+      <c r="I94" s="74"/>
+      <c r="J94" s="74"/>
+      <c r="K94" s="74"/>
+      <c r="L94" s="63"/>
+      <c r="M94" s="63"/>
+      <c r="N94" s="63"/>
+      <c r="O94" s="47"/>
+    </row>
+    <row r="95" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C95" s="60"/>
+      <c r="D95" s="63"/>
+      <c r="E95" s="63"/>
+      <c r="F95" s="74"/>
+      <c r="G95" s="74"/>
+      <c r="H95" s="63"/>
+      <c r="I95" s="74"/>
+      <c r="J95" s="74"/>
+      <c r="K95" s="74"/>
+      <c r="L95" s="63"/>
+      <c r="M95" s="63"/>
+      <c r="N95" s="63"/>
+      <c r="O95" s="47"/>
+    </row>
+    <row r="96" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C96" s="60"/>
+      <c r="D96" s="63"/>
+      <c r="E96" s="63"/>
+      <c r="F96" s="74"/>
+      <c r="G96" s="74"/>
+      <c r="H96" s="63"/>
+      <c r="I96" s="74"/>
+      <c r="J96" s="74"/>
+      <c r="K96" s="74"/>
+      <c r="L96" s="63"/>
+      <c r="M96" s="63"/>
+      <c r="N96" s="63"/>
+      <c r="O96" s="47"/>
+    </row>
+    <row r="97" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C97" s="60"/>
+      <c r="D97" s="63"/>
+      <c r="E97" s="63"/>
+      <c r="F97" s="74"/>
+      <c r="G97" s="74"/>
+      <c r="H97" s="63"/>
+      <c r="I97" s="74"/>
+      <c r="J97" s="74"/>
+      <c r="K97" s="74"/>
+      <c r="L97" s="63"/>
+      <c r="M97" s="63"/>
+      <c r="N97" s="63"/>
+      <c r="O97" s="47"/>
+    </row>
+    <row r="98" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C98" s="60"/>
+      <c r="D98" s="63"/>
+      <c r="E98" s="63"/>
+      <c r="F98" s="74"/>
+      <c r="G98" s="74"/>
+      <c r="H98" s="63"/>
+      <c r="I98" s="74"/>
+      <c r="J98" s="74"/>
+      <c r="K98" s="74"/>
+      <c r="L98" s="63"/>
+      <c r="M98" s="63"/>
+      <c r="N98" s="63"/>
+      <c r="O98" s="47"/>
+    </row>
+    <row r="99" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C99" s="60"/>
+      <c r="D99" s="63"/>
+      <c r="E99" s="63"/>
+      <c r="F99" s="74"/>
+      <c r="G99" s="74"/>
+      <c r="H99" s="63"/>
+      <c r="I99" s="74"/>
+      <c r="J99" s="74"/>
+      <c r="K99" s="74"/>
+      <c r="L99" s="63"/>
+      <c r="M99" s="63"/>
+      <c r="N99" s="63"/>
+      <c r="O99" s="47"/>
+    </row>
+    <row r="100" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C100" s="60"/>
+      <c r="D100" s="63"/>
+      <c r="E100" s="63"/>
+      <c r="F100" s="74"/>
+      <c r="G100" s="74"/>
+      <c r="H100" s="63"/>
+      <c r="I100" s="74"/>
+      <c r="J100" s="74"/>
+      <c r="K100" s="74"/>
+      <c r="L100" s="63"/>
+      <c r="M100" s="63"/>
+      <c r="N100" s="63"/>
+      <c r="O100" s="47"/>
+    </row>
+    <row r="101" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C101" s="60"/>
+      <c r="D101" s="63"/>
+      <c r="E101" s="63"/>
+      <c r="F101" s="74"/>
+      <c r="G101" s="74"/>
+      <c r="H101" s="63"/>
+      <c r="I101" s="74"/>
+      <c r="J101" s="74"/>
+      <c r="K101" s="74"/>
+      <c r="L101" s="63"/>
+      <c r="M101" s="63"/>
+      <c r="N101" s="63"/>
+      <c r="O101" s="47"/>
+    </row>
+    <row r="102" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C102" s="60"/>
+      <c r="D102" s="63"/>
+      <c r="E102" s="63"/>
+      <c r="F102" s="74"/>
+      <c r="G102" s="74"/>
+      <c r="H102" s="63"/>
+      <c r="I102" s="74"/>
+      <c r="J102" s="74"/>
+      <c r="K102" s="74"/>
+      <c r="L102" s="63"/>
+      <c r="M102" s="63"/>
+      <c r="N102" s="63"/>
+      <c r="O102" s="47"/>
+    </row>
+    <row r="103" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="60"/>
+      <c r="D103" s="63"/>
+      <c r="E103" s="63"/>
+      <c r="F103" s="74"/>
+      <c r="G103" s="74"/>
+      <c r="H103" s="63"/>
+      <c r="I103" s="74"/>
+      <c r="J103" s="74"/>
+      <c r="K103" s="74"/>
+      <c r="L103" s="63"/>
+      <c r="M103" s="63"/>
+      <c r="N103" s="63"/>
+      <c r="O103" s="47"/>
+    </row>
+    <row r="104" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C104" s="60"/>
+      <c r="D104" s="63"/>
+      <c r="E104" s="63"/>
+      <c r="F104" s="74"/>
+      <c r="G104" s="74"/>
+      <c r="H104" s="63"/>
+      <c r="I104" s="74"/>
+      <c r="J104" s="74"/>
+      <c r="K104" s="74"/>
+      <c r="L104" s="63"/>
+      <c r="M104" s="63"/>
+      <c r="N104" s="63"/>
+      <c r="O104" s="47"/>
+    </row>
+    <row r="105" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C105" s="60"/>
+      <c r="D105" s="63"/>
+      <c r="E105" s="63"/>
+      <c r="F105" s="74"/>
+      <c r="G105" s="74"/>
+      <c r="H105" s="63"/>
+      <c r="I105" s="74"/>
+      <c r="J105" s="74"/>
+      <c r="K105" s="74"/>
+      <c r="L105" s="63"/>
+      <c r="M105" s="63"/>
+      <c r="N105" s="63"/>
+      <c r="O105" s="47"/>
+    </row>
+    <row r="106" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C106" s="60"/>
+      <c r="D106" s="63"/>
+      <c r="E106" s="63"/>
+      <c r="F106" s="74"/>
+      <c r="G106" s="74"/>
+      <c r="H106" s="63"/>
+      <c r="I106" s="74"/>
+      <c r="J106" s="74"/>
+      <c r="K106" s="74"/>
+      <c r="L106" s="63"/>
+      <c r="M106" s="63"/>
+      <c r="N106" s="63"/>
+      <c r="O106" s="47"/>
+    </row>
+    <row r="107" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C107" s="60"/>
+      <c r="D107" s="63"/>
+      <c r="E107" s="63"/>
+      <c r="F107" s="74"/>
+      <c r="G107" s="74"/>
+      <c r="H107" s="63"/>
+      <c r="I107" s="74"/>
+      <c r="J107" s="74"/>
+      <c r="K107" s="74"/>
+      <c r="L107" s="63"/>
+      <c r="M107" s="63"/>
+      <c r="N107" s="63"/>
+      <c r="O107" s="47"/>
+    </row>
+    <row r="108" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C108" s="60"/>
+      <c r="D108" s="63"/>
+      <c r="E108" s="63"/>
+      <c r="F108" s="74"/>
+      <c r="G108" s="74"/>
+      <c r="H108" s="63"/>
+      <c r="I108" s="74"/>
+      <c r="J108" s="74"/>
+      <c r="K108" s="74"/>
+      <c r="L108" s="63"/>
+      <c r="M108" s="63"/>
+      <c r="N108" s="63"/>
+      <c r="O108" s="47"/>
+    </row>
+    <row r="109" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C109" s="60"/>
+      <c r="D109" s="63"/>
+      <c r="E109" s="63"/>
+      <c r="F109" s="74"/>
+      <c r="G109" s="74"/>
+      <c r="H109" s="63"/>
+      <c r="I109" s="74"/>
+      <c r="J109" s="74"/>
+      <c r="K109" s="74"/>
+      <c r="L109" s="63"/>
+      <c r="M109" s="63"/>
+      <c r="N109" s="63"/>
+      <c r="O109" s="47"/>
+    </row>
+    <row r="110" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C110" s="60"/>
+      <c r="D110" s="63"/>
+      <c r="E110" s="63"/>
+      <c r="F110" s="74"/>
+      <c r="G110" s="74"/>
+      <c r="H110" s="63"/>
+      <c r="I110" s="74"/>
+      <c r="J110" s="74"/>
+      <c r="K110" s="74"/>
+      <c r="L110" s="63"/>
+      <c r="M110" s="63"/>
+      <c r="N110" s="63"/>
+      <c r="O110" s="47"/>
+    </row>
+    <row r="111" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C111" s="60"/>
+      <c r="D111" s="63"/>
+      <c r="E111" s="63"/>
+      <c r="F111" s="74"/>
+      <c r="G111" s="74"/>
+      <c r="H111" s="63"/>
+      <c r="I111" s="74"/>
+      <c r="J111" s="74"/>
+      <c r="K111" s="74"/>
+      <c r="L111" s="63"/>
+      <c r="M111" s="63"/>
+      <c r="N111" s="63"/>
+      <c r="O111" s="47"/>
+    </row>
+    <row r="112" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C112" s="60"/>
+      <c r="D112" s="63"/>
+      <c r="E112" s="63"/>
+      <c r="F112" s="74"/>
+      <c r="G112" s="74"/>
+      <c r="H112" s="63"/>
+      <c r="I112" s="74"/>
+      <c r="J112" s="74"/>
+      <c r="K112" s="74"/>
+      <c r="L112" s="63"/>
+      <c r="M112" s="63"/>
+      <c r="N112" s="63"/>
+      <c r="O112" s="47"/>
+    </row>
+    <row r="113" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C113" s="60"/>
+      <c r="D113" s="63"/>
+      <c r="E113" s="63"/>
+      <c r="F113" s="74"/>
+      <c r="G113" s="74"/>
+      <c r="H113" s="63"/>
+      <c r="I113" s="74"/>
+      <c r="J113" s="74"/>
+      <c r="K113" s="74"/>
+      <c r="L113" s="63"/>
+      <c r="M113" s="63"/>
+      <c r="N113" s="63"/>
+      <c r="O113" s="47"/>
+    </row>
+    <row r="114" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C114" s="60"/>
+      <c r="D114" s="63"/>
+      <c r="E114" s="63"/>
+      <c r="F114" s="74"/>
+      <c r="G114" s="74"/>
+      <c r="H114" s="63"/>
+      <c r="I114" s="74"/>
+      <c r="J114" s="74"/>
+      <c r="K114" s="74"/>
+      <c r="L114" s="63"/>
+      <c r="M114" s="63"/>
+      <c r="N114" s="63"/>
+      <c r="O114" s="47"/>
+    </row>
+    <row r="115" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C115" s="60"/>
+      <c r="D115" s="63"/>
+      <c r="E115" s="63"/>
+      <c r="F115" s="74"/>
+      <c r="G115" s="74"/>
+      <c r="H115" s="63"/>
+      <c r="I115" s="74"/>
+      <c r="J115" s="74"/>
+      <c r="K115" s="74"/>
+      <c r="L115" s="63"/>
+      <c r="M115" s="63"/>
+      <c r="N115" s="63"/>
+      <c r="O115" s="47"/>
+    </row>
+    <row r="116" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C116" s="60"/>
+      <c r="D116" s="63"/>
+      <c r="E116" s="63"/>
+      <c r="F116" s="74"/>
+      <c r="G116" s="74"/>
+      <c r="H116" s="63"/>
+      <c r="I116" s="74"/>
+      <c r="J116" s="74"/>
+      <c r="K116" s="74"/>
+      <c r="L116" s="63"/>
+      <c r="M116" s="63"/>
+      <c r="N116" s="63"/>
+      <c r="O116" s="47"/>
+    </row>
+    <row r="117" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C117" s="60"/>
+      <c r="D117" s="63"/>
+      <c r="E117" s="63"/>
+      <c r="F117" s="74"/>
+      <c r="G117" s="74"/>
+      <c r="H117" s="63"/>
+      <c r="I117" s="74"/>
+      <c r="J117" s="74"/>
+      <c r="K117" s="74"/>
+      <c r="L117" s="63"/>
+      <c r="M117" s="63"/>
+      <c r="N117" s="63"/>
+      <c r="O117" s="47"/>
+    </row>
+    <row r="118" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C118" s="60"/>
+      <c r="D118" s="63"/>
+      <c r="E118" s="63"/>
+      <c r="F118" s="74"/>
+      <c r="G118" s="74"/>
+      <c r="H118" s="63"/>
+      <c r="I118" s="74"/>
+      <c r="J118" s="74"/>
+      <c r="K118" s="74"/>
+      <c r="L118" s="63"/>
+      <c r="M118" s="63"/>
+      <c r="N118" s="63"/>
+      <c r="O118" s="47"/>
+    </row>
+    <row r="119" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C119" s="60"/>
+      <c r="D119" s="63"/>
+      <c r="E119" s="63"/>
+      <c r="F119" s="74"/>
+      <c r="G119" s="74"/>
+      <c r="H119" s="63"/>
+      <c r="I119" s="74"/>
+      <c r="J119" s="74"/>
+      <c r="K119" s="74"/>
+      <c r="L119" s="63"/>
+      <c r="M119" s="63"/>
+      <c r="N119" s="63"/>
+      <c r="O119" s="47"/>
+    </row>
+    <row r="120" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C120" s="60"/>
+      <c r="D120" s="63"/>
+      <c r="E120" s="63"/>
+      <c r="F120" s="74"/>
+      <c r="G120" s="74"/>
+      <c r="H120" s="63"/>
+      <c r="I120" s="74"/>
+      <c r="J120" s="74"/>
+      <c r="K120" s="74"/>
+      <c r="L120" s="63"/>
+      <c r="M120" s="63"/>
+      <c r="N120" s="63"/>
+      <c r="O120" s="47"/>
+    </row>
+    <row r="121" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C121" s="60"/>
+      <c r="D121" s="63"/>
+      <c r="E121" s="63"/>
+      <c r="F121" s="74"/>
+      <c r="G121" s="74"/>
+      <c r="H121" s="63"/>
+      <c r="I121" s="74"/>
+      <c r="J121" s="74"/>
+      <c r="K121" s="74"/>
+      <c r="L121" s="63"/>
+      <c r="M121" s="63"/>
+      <c r="N121" s="63"/>
+      <c r="O121" s="47"/>
+    </row>
+    <row r="122" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C122" s="60"/>
+      <c r="D122" s="63"/>
+      <c r="E122" s="63"/>
+      <c r="F122" s="74"/>
+      <c r="G122" s="74"/>
+      <c r="H122" s="63"/>
+      <c r="I122" s="74"/>
+      <c r="J122" s="74"/>
+      <c r="K122" s="74"/>
+      <c r="L122" s="63"/>
+      <c r="M122" s="63"/>
+      <c r="N122" s="63"/>
+      <c r="O122" s="47"/>
+    </row>
+    <row r="123" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C123" s="60"/>
+      <c r="D123" s="63"/>
+      <c r="E123" s="63"/>
+      <c r="F123" s="74"/>
+      <c r="G123" s="74"/>
+      <c r="H123" s="63"/>
+      <c r="I123" s="74"/>
+      <c r="J123" s="74"/>
+      <c r="K123" s="74"/>
+      <c r="L123" s="63"/>
+      <c r="M123" s="63"/>
+      <c r="N123" s="63"/>
+      <c r="O123" s="47"/>
+    </row>
+    <row r="124" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C124" s="60"/>
+      <c r="D124" s="63"/>
+      <c r="E124" s="63"/>
+      <c r="F124" s="74"/>
+      <c r="G124" s="74"/>
+      <c r="H124" s="63"/>
+      <c r="I124" s="74"/>
+      <c r="J124" s="74"/>
+      <c r="K124" s="74"/>
+      <c r="L124" s="63"/>
+      <c r="M124" s="63"/>
+      <c r="N124" s="63"/>
+      <c r="O124" s="47"/>
+    </row>
+    <row r="125" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C125" s="60"/>
+      <c r="D125" s="63"/>
+      <c r="E125" s="63"/>
+      <c r="F125" s="74"/>
+      <c r="G125" s="74"/>
+      <c r="H125" s="63"/>
+      <c r="I125" s="74"/>
+      <c r="J125" s="74"/>
+      <c r="K125" s="74"/>
+      <c r="L125" s="63"/>
+      <c r="M125" s="63"/>
+      <c r="N125" s="63"/>
+      <c r="O125" s="47"/>
+    </row>
+    <row r="126" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C126" s="60"/>
+      <c r="D126" s="63"/>
+      <c r="E126" s="63"/>
+      <c r="F126" s="74"/>
+      <c r="G126" s="74"/>
+      <c r="H126" s="63"/>
+      <c r="I126" s="74"/>
+      <c r="J126" s="74"/>
+      <c r="K126" s="74"/>
+      <c r="L126" s="63"/>
+      <c r="M126" s="63"/>
+      <c r="N126" s="63"/>
+      <c r="O126" s="47"/>
+    </row>
+    <row r="127" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C127" s="60"/>
+      <c r="D127" s="63"/>
+      <c r="E127" s="63"/>
+      <c r="F127" s="74"/>
+      <c r="G127" s="74"/>
+      <c r="H127" s="63"/>
+      <c r="I127" s="74"/>
+      <c r="J127" s="74"/>
+      <c r="K127" s="74"/>
+      <c r="L127" s="63"/>
+      <c r="M127" s="63"/>
+      <c r="N127" s="63"/>
+      <c r="O127" s="47"/>
+    </row>
+    <row r="128" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C128" s="60"/>
+      <c r="D128" s="63"/>
+      <c r="E128" s="63"/>
+      <c r="F128" s="74"/>
+      <c r="G128" s="74"/>
+      <c r="H128" s="63"/>
+      <c r="I128" s="74"/>
+      <c r="J128" s="74"/>
+      <c r="K128" s="74"/>
+      <c r="L128" s="63"/>
+      <c r="M128" s="63"/>
+      <c r="N128" s="63"/>
+      <c r="O128" s="47"/>
+    </row>
+    <row r="129" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C129" s="60"/>
+      <c r="D129" s="63"/>
+      <c r="E129" s="63"/>
+      <c r="F129" s="74"/>
+      <c r="G129" s="74"/>
+      <c r="H129" s="63"/>
+      <c r="I129" s="74"/>
+      <c r="J129" s="74"/>
+      <c r="K129" s="74"/>
+      <c r="L129" s="63"/>
+      <c r="M129" s="63"/>
+      <c r="N129" s="63"/>
+      <c r="O129" s="47"/>
+    </row>
+    <row r="130" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C130" s="60"/>
+      <c r="D130" s="63"/>
+      <c r="E130" s="63"/>
+      <c r="F130" s="74"/>
+      <c r="G130" s="74"/>
+      <c r="H130" s="63"/>
+      <c r="I130" s="74"/>
+      <c r="J130" s="74"/>
+      <c r="K130" s="74"/>
+      <c r="L130" s="63"/>
+      <c r="M130" s="63"/>
+      <c r="N130" s="63"/>
+      <c r="O130" s="47"/>
+    </row>
+    <row r="131" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C131" s="60"/>
+      <c r="D131" s="63"/>
+      <c r="E131" s="63"/>
+      <c r="F131" s="74"/>
+      <c r="G131" s="74"/>
+      <c r="H131" s="63"/>
+      <c r="I131" s="74"/>
+      <c r="J131" s="74"/>
+      <c r="K131" s="74"/>
+      <c r="L131" s="63"/>
+      <c r="M131" s="63"/>
+      <c r="N131" s="63"/>
+      <c r="O131" s="47"/>
+    </row>
+    <row r="132" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C132" s="60"/>
+      <c r="D132" s="63"/>
+      <c r="E132" s="63"/>
+      <c r="F132" s="74"/>
+      <c r="G132" s="74"/>
+      <c r="H132" s="63"/>
+      <c r="I132" s="74"/>
+      <c r="J132" s="74"/>
+      <c r="K132" s="74"/>
+      <c r="L132" s="63"/>
+      <c r="M132" s="63"/>
+      <c r="N132" s="63"/>
+      <c r="O132" s="47"/>
+    </row>
+    <row r="133" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C133" s="60"/>
+      <c r="D133" s="63"/>
+      <c r="E133" s="63"/>
+      <c r="F133" s="74"/>
+      <c r="G133" s="74"/>
+      <c r="H133" s="63"/>
+      <c r="I133" s="74"/>
+      <c r="J133" s="74"/>
+      <c r="K133" s="74"/>
+      <c r="L133" s="63"/>
+      <c r="M133" s="63"/>
+      <c r="N133" s="63"/>
+      <c r="O133" s="47"/>
+    </row>
+    <row r="134" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C134" s="60"/>
+      <c r="D134" s="63"/>
+      <c r="E134" s="63"/>
+      <c r="F134" s="74"/>
+      <c r="G134" s="74"/>
+      <c r="H134" s="63"/>
+      <c r="I134" s="74"/>
+      <c r="J134" s="74"/>
+      <c r="K134" s="74"/>
+      <c r="L134" s="63"/>
+      <c r="M134" s="63"/>
+      <c r="N134" s="63"/>
+      <c r="O134" s="47"/>
+    </row>
+    <row r="135" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C135" s="60"/>
+      <c r="D135" s="63"/>
+      <c r="E135" s="63"/>
+      <c r="F135" s="74"/>
+      <c r="G135" s="74"/>
+      <c r="H135" s="63"/>
+      <c r="I135" s="74"/>
+      <c r="J135" s="74"/>
+      <c r="K135" s="74"/>
+      <c r="L135" s="63"/>
+      <c r="M135" s="63"/>
+      <c r="N135" s="63"/>
+      <c r="O135" s="47"/>
+    </row>
+    <row r="136" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C136" s="60"/>
+      <c r="D136" s="63"/>
+      <c r="E136" s="63"/>
+      <c r="F136" s="74"/>
+      <c r="G136" s="74"/>
+      <c r="H136" s="63"/>
+      <c r="I136" s="74"/>
+      <c r="J136" s="74"/>
+      <c r="K136" s="74"/>
+      <c r="L136" s="63"/>
+      <c r="M136" s="63"/>
+      <c r="N136" s="63"/>
+      <c r="O136" s="47"/>
+    </row>
+    <row r="137" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C137" s="60"/>
+      <c r="D137" s="63"/>
+      <c r="E137" s="63"/>
+      <c r="F137" s="74"/>
+      <c r="G137" s="74"/>
+      <c r="H137" s="63"/>
+      <c r="I137" s="74"/>
+      <c r="J137" s="74"/>
+      <c r="K137" s="74"/>
+      <c r="L137" s="63"/>
+      <c r="M137" s="63"/>
+      <c r="N137" s="63"/>
+      <c r="O137" s="47"/>
+    </row>
+    <row r="138" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C138" s="60"/>
+      <c r="D138" s="63"/>
+      <c r="E138" s="63"/>
+      <c r="F138" s="74"/>
+      <c r="G138" s="74"/>
+      <c r="H138" s="63"/>
+      <c r="I138" s="74"/>
+      <c r="J138" s="74"/>
+      <c r="K138" s="74"/>
+      <c r="L138" s="63"/>
+      <c r="M138" s="63"/>
+      <c r="N138" s="63"/>
+      <c r="O138" s="47"/>
+    </row>
+    <row r="139" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C139" s="60"/>
+      <c r="D139" s="63"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="74"/>
+      <c r="G139" s="74"/>
+      <c r="H139" s="63"/>
+      <c r="I139" s="74"/>
+      <c r="J139" s="74"/>
+      <c r="K139" s="74"/>
+      <c r="L139" s="63"/>
+      <c r="M139" s="63"/>
+      <c r="N139" s="63"/>
+      <c r="O139" s="47"/>
+    </row>
+    <row r="140" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C140" s="60"/>
+      <c r="D140" s="63"/>
+      <c r="E140" s="63"/>
+      <c r="F140" s="74"/>
+      <c r="G140" s="74"/>
+      <c r="H140" s="63"/>
+      <c r="I140" s="74"/>
+      <c r="J140" s="74"/>
+      <c r="K140" s="74"/>
+      <c r="L140" s="63"/>
+      <c r="M140" s="63"/>
+      <c r="N140" s="63"/>
+      <c r="O140" s="47"/>
+    </row>
+    <row r="141" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C141" s="60"/>
+      <c r="D141" s="63"/>
+      <c r="E141" s="63"/>
+      <c r="F141" s="74"/>
+      <c r="G141" s="74"/>
+      <c r="H141" s="63"/>
+      <c r="I141" s="74"/>
+      <c r="J141" s="74"/>
+      <c r="K141" s="74"/>
+      <c r="L141" s="63"/>
+      <c r="M141" s="63"/>
+      <c r="N141" s="63"/>
+      <c r="O141" s="47"/>
+    </row>
+    <row r="142" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C142" s="60"/>
+      <c r="D142" s="63"/>
+      <c r="E142" s="63"/>
+      <c r="F142" s="74"/>
+      <c r="G142" s="74"/>
+      <c r="H142" s="63"/>
+      <c r="I142" s="74"/>
+      <c r="J142" s="74"/>
+      <c r="K142" s="74"/>
+      <c r="L142" s="63"/>
+      <c r="M142" s="63"/>
+      <c r="N142" s="63"/>
+      <c r="O142" s="47"/>
+    </row>
+    <row r="143" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C143" s="60"/>
+      <c r="D143" s="63"/>
+      <c r="E143" s="63"/>
+      <c r="F143" s="74"/>
+      <c r="G143" s="74"/>
+      <c r="H143" s="63"/>
+      <c r="I143" s="74"/>
+      <c r="J143" s="74"/>
+      <c r="K143" s="74"/>
+      <c r="L143" s="63"/>
+      <c r="M143" s="63"/>
+      <c r="N143" s="63"/>
+      <c r="O143" s="47"/>
+    </row>
+    <row r="144" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C144" s="60"/>
+      <c r="D144" s="63"/>
+      <c r="E144" s="63"/>
+      <c r="F144" s="74"/>
+      <c r="G144" s="74"/>
+      <c r="H144" s="63"/>
+      <c r="I144" s="74"/>
+      <c r="J144" s="74"/>
+      <c r="K144" s="74"/>
+      <c r="L144" s="63"/>
+      <c r="M144" s="63"/>
+      <c r="N144" s="63"/>
+      <c r="O144" s="47"/>
+    </row>
+    <row r="145" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C145" s="60"/>
+      <c r="D145" s="63"/>
+      <c r="E145" s="63"/>
+      <c r="F145" s="74"/>
+      <c r="G145" s="74"/>
+      <c r="H145" s="63"/>
+      <c r="I145" s="74"/>
+      <c r="J145" s="74"/>
+      <c r="K145" s="74"/>
+      <c r="L145" s="63"/>
+      <c r="M145" s="63"/>
+      <c r="N145" s="63"/>
+      <c r="O145" s="47"/>
+    </row>
+    <row r="146" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C146" s="60"/>
+      <c r="D146" s="63"/>
+      <c r="E146" s="63"/>
+      <c r="F146" s="74"/>
+      <c r="G146" s="74"/>
+      <c r="H146" s="63"/>
+      <c r="I146" s="74"/>
+      <c r="J146" s="74"/>
+      <c r="K146" s="74"/>
+      <c r="L146" s="63"/>
+      <c r="M146" s="63"/>
+      <c r="N146" s="63"/>
+      <c r="O146" s="47"/>
+    </row>
+    <row r="147" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C147" s="60"/>
+      <c r="D147" s="63"/>
+      <c r="E147" s="63"/>
+      <c r="F147" s="74"/>
+      <c r="G147" s="74"/>
+      <c r="H147" s="63"/>
+      <c r="I147" s="74"/>
+      <c r="J147" s="74"/>
+      <c r="K147" s="74"/>
+      <c r="L147" s="63"/>
+      <c r="M147" s="63"/>
+      <c r="N147" s="63"/>
+      <c r="O147" s="47"/>
+    </row>
+    <row r="148" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C148" s="60"/>
+      <c r="D148" s="63"/>
+      <c r="E148" s="63"/>
+      <c r="F148" s="74"/>
+      <c r="G148" s="74"/>
+      <c r="H148" s="63"/>
+      <c r="I148" s="74"/>
+      <c r="J148" s="74"/>
+      <c r="K148" s="74"/>
+      <c r="L148" s="63"/>
+      <c r="M148" s="63"/>
+      <c r="N148" s="63"/>
+      <c r="O148" s="47"/>
+    </row>
+    <row r="149" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C149" s="60"/>
+      <c r="D149" s="63"/>
+      <c r="E149" s="63"/>
+      <c r="F149" s="74"/>
+      <c r="G149" s="74"/>
+      <c r="H149" s="63"/>
+      <c r="I149" s="74"/>
+      <c r="J149" s="74"/>
+      <c r="K149" s="74"/>
+      <c r="L149" s="63"/>
+      <c r="M149" s="63"/>
+      <c r="N149" s="63"/>
+      <c r="O149" s="47"/>
+    </row>
+    <row r="150" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C150" s="60"/>
+      <c r="D150" s="63"/>
+      <c r="E150" s="63"/>
+      <c r="F150" s="74"/>
+      <c r="G150" s="74"/>
+      <c r="H150" s="63"/>
+      <c r="I150" s="74"/>
+      <c r="J150" s="74"/>
+      <c r="K150" s="74"/>
+      <c r="L150" s="63"/>
+      <c r="M150" s="63"/>
+      <c r="N150" s="63"/>
+      <c r="O150" s="47"/>
+    </row>
+    <row r="151" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C151" s="60"/>
+      <c r="D151" s="63"/>
+      <c r="E151" s="63"/>
+      <c r="F151" s="74"/>
+      <c r="G151" s="74"/>
+      <c r="H151" s="63"/>
+      <c r="I151" s="74"/>
+      <c r="J151" s="74"/>
+      <c r="K151" s="74"/>
+      <c r="L151" s="63"/>
+      <c r="M151" s="63"/>
+      <c r="N151" s="63"/>
+      <c r="O151" s="47"/>
+    </row>
+    <row r="152" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C152" s="60"/>
+      <c r="D152" s="63"/>
+      <c r="E152" s="63"/>
+      <c r="F152" s="74"/>
+      <c r="G152" s="74"/>
+      <c r="H152" s="63"/>
+      <c r="I152" s="74"/>
+      <c r="J152" s="74"/>
+      <c r="K152" s="74"/>
+      <c r="L152" s="63"/>
+      <c r="M152" s="63"/>
+      <c r="N152" s="63"/>
+      <c r="O152" s="47"/>
+    </row>
+    <row r="153" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C153" s="60"/>
+      <c r="D153" s="63"/>
+      <c r="E153" s="63"/>
+      <c r="F153" s="74"/>
+      <c r="G153" s="74"/>
+      <c r="H153" s="63"/>
+      <c r="I153" s="74"/>
+      <c r="J153" s="74"/>
+      <c r="K153" s="74"/>
+      <c r="L153" s="63"/>
+      <c r="M153" s="63"/>
+      <c r="N153" s="63"/>
+      <c r="O153" s="47"/>
+    </row>
+    <row r="154" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C154" s="60"/>
+      <c r="D154" s="63"/>
+      <c r="E154" s="63"/>
+      <c r="F154" s="74"/>
+      <c r="G154" s="74"/>
+      <c r="H154" s="63"/>
+      <c r="I154" s="74"/>
+      <c r="J154" s="74"/>
+      <c r="K154" s="74"/>
+      <c r="L154" s="63"/>
+      <c r="M154" s="63"/>
+      <c r="N154" s="63"/>
+      <c r="O154" s="47"/>
+    </row>
+    <row r="155" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C155" s="60"/>
+      <c r="D155" s="63"/>
+      <c r="E155" s="63"/>
+      <c r="F155" s="74"/>
+      <c r="G155" s="74"/>
+      <c r="H155" s="63"/>
+      <c r="I155" s="74"/>
+      <c r="J155" s="74"/>
+      <c r="K155" s="74"/>
+      <c r="L155" s="63"/>
+      <c r="M155" s="63"/>
+      <c r="N155" s="63"/>
+      <c r="O155" s="47"/>
+    </row>
+    <row r="156" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C156" s="60"/>
+      <c r="D156" s="63"/>
+      <c r="E156" s="63"/>
+      <c r="F156" s="74"/>
+      <c r="G156" s="74"/>
+      <c r="H156" s="63"/>
+      <c r="I156" s="74"/>
+      <c r="J156" s="74"/>
+      <c r="K156" s="74"/>
+      <c r="L156" s="63"/>
+      <c r="M156" s="63"/>
+      <c r="N156" s="63"/>
+      <c r="O156" s="47"/>
+    </row>
+    <row r="157" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C157" s="60"/>
+      <c r="D157" s="63"/>
+      <c r="E157" s="63"/>
+      <c r="F157" s="74"/>
+      <c r="G157" s="74"/>
+      <c r="H157" s="63"/>
+      <c r="I157" s="74"/>
+      <c r="J157" s="74"/>
+      <c r="K157" s="74"/>
+      <c r="L157" s="63"/>
+      <c r="M157" s="63"/>
+      <c r="N157" s="63"/>
+      <c r="O157" s="47"/>
+    </row>
+    <row r="158" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C158" s="60"/>
+      <c r="D158" s="63"/>
+      <c r="E158" s="63"/>
+      <c r="F158" s="74"/>
+      <c r="G158" s="74"/>
+      <c r="H158" s="63"/>
+      <c r="I158" s="74"/>
+      <c r="J158" s="74"/>
+      <c r="K158" s="74"/>
+      <c r="L158" s="63"/>
+      <c r="M158" s="63"/>
+      <c r="N158" s="63"/>
+      <c r="O158" s="47"/>
+    </row>
+    <row r="159" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C159" s="60"/>
+      <c r="D159" s="63"/>
+      <c r="E159" s="63"/>
+      <c r="F159" s="74"/>
+      <c r="G159" s="74"/>
+      <c r="H159" s="63"/>
+      <c r="I159" s="74"/>
+      <c r="J159" s="74"/>
+      <c r="K159" s="74"/>
+      <c r="L159" s="63"/>
+      <c r="M159" s="63"/>
+      <c r="N159" s="63"/>
+      <c r="O159" s="47"/>
+    </row>
+    <row r="160" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C160" s="60"/>
+      <c r="D160" s="63"/>
+      <c r="E160" s="63"/>
+      <c r="F160" s="74"/>
+      <c r="G160" s="74"/>
+      <c r="H160" s="63"/>
+      <c r="I160" s="74"/>
+      <c r="J160" s="74"/>
+      <c r="K160" s="74"/>
+      <c r="L160" s="63"/>
+      <c r="M160" s="63"/>
+      <c r="N160" s="63"/>
+      <c r="O160" s="47"/>
+    </row>
+    <row r="161" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C161" s="60"/>
+      <c r="D161" s="63"/>
+      <c r="E161" s="63"/>
+      <c r="F161" s="74"/>
+      <c r="G161" s="74"/>
+      <c r="H161" s="63"/>
+      <c r="I161" s="74"/>
+      <c r="J161" s="74"/>
+      <c r="K161" s="74"/>
+      <c r="L161" s="63"/>
+      <c r="M161" s="63"/>
+      <c r="N161" s="63"/>
+      <c r="O161" s="47"/>
+    </row>
+    <row r="162" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C162" s="60"/>
+      <c r="D162" s="63"/>
+      <c r="E162" s="63"/>
+      <c r="F162" s="74"/>
+      <c r="G162" s="74"/>
+      <c r="H162" s="63"/>
+      <c r="I162" s="74"/>
+      <c r="J162" s="74"/>
+      <c r="K162" s="74"/>
+      <c r="L162" s="63"/>
+      <c r="M162" s="63"/>
+      <c r="N162" s="63"/>
+      <c r="O162" s="47"/>
+    </row>
+    <row r="163" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C163" s="60"/>
+      <c r="D163" s="63"/>
+      <c r="E163" s="63"/>
+      <c r="F163" s="74"/>
+      <c r="G163" s="74"/>
+      <c r="H163" s="63"/>
+      <c r="I163" s="74"/>
+      <c r="J163" s="74"/>
+      <c r="K163" s="74"/>
+      <c r="L163" s="63"/>
+      <c r="M163" s="63"/>
+      <c r="N163" s="63"/>
+      <c r="O163" s="47"/>
+    </row>
+    <row r="164" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C164" s="60"/>
+      <c r="D164" s="63"/>
+      <c r="E164" s="63"/>
+      <c r="F164" s="74"/>
+      <c r="G164" s="74"/>
+      <c r="H164" s="63"/>
+      <c r="I164" s="74"/>
+      <c r="J164" s="74"/>
+      <c r="K164" s="74"/>
+      <c r="L164" s="63"/>
+      <c r="M164" s="63"/>
+      <c r="N164" s="63"/>
+      <c r="O164" s="47"/>
+    </row>
+    <row r="165" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C165" s="60"/>
+      <c r="D165" s="63"/>
+      <c r="E165" s="63"/>
+      <c r="F165" s="74"/>
+      <c r="G165" s="74"/>
+      <c r="H165" s="63"/>
+      <c r="I165" s="74"/>
+      <c r="J165" s="74"/>
+      <c r="K165" s="74"/>
+      <c r="L165" s="63"/>
+      <c r="M165" s="63"/>
+      <c r="N165" s="63"/>
+      <c r="O165" s="47"/>
+    </row>
+    <row r="166" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C166" s="60"/>
+      <c r="D166" s="63"/>
+      <c r="E166" s="63"/>
+      <c r="F166" s="74"/>
+      <c r="G166" s="74"/>
+      <c r="H166" s="63"/>
+      <c r="I166" s="74"/>
+      <c r="J166" s="74"/>
+      <c r="K166" s="74"/>
+      <c r="L166" s="63"/>
+      <c r="M166" s="63"/>
+      <c r="N166" s="63"/>
+      <c r="O166" s="47"/>
+    </row>
+    <row r="167" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C167" s="60"/>
+      <c r="D167" s="63"/>
+      <c r="E167" s="63"/>
+      <c r="F167" s="74"/>
+      <c r="G167" s="74"/>
+      <c r="H167" s="63"/>
+      <c r="I167" s="74"/>
+      <c r="J167" s="74"/>
+      <c r="K167" s="74"/>
+      <c r="L167" s="63"/>
+      <c r="M167" s="63"/>
+      <c r="N167" s="63"/>
+      <c r="O167" s="47"/>
+    </row>
+    <row r="168" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C168" s="60"/>
+      <c r="D168" s="63"/>
+      <c r="E168" s="63"/>
+      <c r="F168" s="74"/>
+      <c r="G168" s="74"/>
+      <c r="H168" s="63"/>
+      <c r="I168" s="74"/>
+      <c r="J168" s="74"/>
+      <c r="K168" s="74"/>
+      <c r="L168" s="63"/>
+      <c r="M168" s="63"/>
+      <c r="N168" s="63"/>
+      <c r="O168" s="47"/>
+    </row>
+    <row r="169" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C169" s="60"/>
+      <c r="D169" s="63"/>
+      <c r="E169" s="63"/>
+      <c r="F169" s="74"/>
+      <c r="G169" s="74"/>
+      <c r="H169" s="63"/>
+      <c r="I169" s="74"/>
+      <c r="J169" s="74"/>
+      <c r="K169" s="74"/>
+      <c r="L169" s="63"/>
+      <c r="M169" s="63"/>
+      <c r="N169" s="63"/>
+      <c r="O169" s="47"/>
+    </row>
+    <row r="170" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C170" s="60"/>
+      <c r="D170" s="63"/>
+      <c r="E170" s="63"/>
+      <c r="F170" s="74"/>
+      <c r="G170" s="74"/>
+      <c r="H170" s="63"/>
+      <c r="I170" s="74"/>
+      <c r="J170" s="74"/>
+      <c r="K170" s="74"/>
+      <c r="L170" s="63"/>
+      <c r="M170" s="63"/>
+      <c r="N170" s="63"/>
+      <c r="O170" s="47"/>
+    </row>
+    <row r="171" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C171" s="60"/>
+      <c r="D171" s="63"/>
+      <c r="E171" s="63"/>
+      <c r="F171" s="74"/>
+      <c r="G171" s="74"/>
+      <c r="H171" s="63"/>
+      <c r="I171" s="74"/>
+      <c r="J171" s="74"/>
+      <c r="K171" s="74"/>
+      <c r="L171" s="63"/>
+      <c r="M171" s="63"/>
+      <c r="N171" s="63"/>
+      <c r="O171" s="47"/>
+    </row>
+    <row r="172" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C172" s="60"/>
+      <c r="D172" s="63"/>
+      <c r="E172" s="63"/>
+      <c r="F172" s="74"/>
+      <c r="G172" s="74"/>
+      <c r="H172" s="63"/>
+      <c r="I172" s="74"/>
+      <c r="J172" s="74"/>
+      <c r="K172" s="74"/>
+      <c r="L172" s="63"/>
+      <c r="M172" s="63"/>
+      <c r="N172" s="63"/>
+      <c r="O172" s="47"/>
+    </row>
+    <row r="173" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C173" s="60"/>
+      <c r="D173" s="63"/>
+      <c r="E173" s="63"/>
+      <c r="F173" s="74"/>
+      <c r="G173" s="74"/>
+      <c r="H173" s="63"/>
+      <c r="I173" s="74"/>
+      <c r="J173" s="74"/>
+      <c r="K173" s="74"/>
+      <c r="L173" s="63"/>
+      <c r="M173" s="63"/>
+      <c r="N173" s="63"/>
+      <c r="O173" s="47"/>
+    </row>
+    <row r="174" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C174" s="60"/>
+      <c r="D174" s="63"/>
+      <c r="E174" s="63"/>
+      <c r="F174" s="74"/>
+      <c r="G174" s="74"/>
+      <c r="H174" s="63"/>
+      <c r="I174" s="74"/>
+      <c r="J174" s="74"/>
+      <c r="K174" s="74"/>
+      <c r="L174" s="63"/>
+      <c r="M174" s="63"/>
+      <c r="N174" s="63"/>
+      <c r="O174" s="47"/>
+    </row>
+    <row r="175" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C175" s="60"/>
+      <c r="D175" s="63"/>
+      <c r="E175" s="63"/>
+      <c r="F175" s="74"/>
+      <c r="G175" s="74"/>
+      <c r="H175" s="63"/>
+      <c r="I175" s="74"/>
+      <c r="J175" s="74"/>
+      <c r="K175" s="74"/>
+      <c r="L175" s="63"/>
+      <c r="M175" s="63"/>
+      <c r="N175" s="63"/>
+      <c r="O175" s="47"/>
+    </row>
+    <row r="176" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C176" s="60"/>
+      <c r="D176" s="63"/>
+      <c r="E176" s="63"/>
+      <c r="F176" s="74"/>
+      <c r="G176" s="74"/>
+      <c r="H176" s="63"/>
+      <c r="I176" s="74"/>
+      <c r="J176" s="74"/>
+      <c r="K176" s="74"/>
+      <c r="L176" s="63"/>
+      <c r="M176" s="63"/>
+      <c r="N176" s="63"/>
+      <c r="O176" s="47"/>
+    </row>
+    <row r="177" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C177" s="60"/>
+      <c r="D177" s="63"/>
+      <c r="E177" s="63"/>
+      <c r="F177" s="74"/>
+      <c r="G177" s="74"/>
+      <c r="H177" s="63"/>
+      <c r="I177" s="74"/>
+      <c r="J177" s="74"/>
+      <c r="K177" s="74"/>
+      <c r="L177" s="63"/>
+      <c r="M177" s="63"/>
+      <c r="N177" s="63"/>
+      <c r="O177" s="47"/>
+    </row>
+    <row r="178" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C178" s="60"/>
+      <c r="D178" s="63"/>
+      <c r="E178" s="63"/>
+      <c r="F178" s="74"/>
+      <c r="G178" s="74"/>
+      <c r="H178" s="63"/>
+      <c r="I178" s="74"/>
+      <c r="J178" s="74"/>
+      <c r="K178" s="74"/>
+      <c r="L178" s="63"/>
+      <c r="M178" s="63"/>
+      <c r="N178" s="63"/>
+      <c r="O178" s="47"/>
+    </row>
+    <row r="179" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C179" s="60"/>
+      <c r="D179" s="63"/>
+      <c r="E179" s="63"/>
+      <c r="F179" s="74"/>
+      <c r="G179" s="74"/>
+      <c r="H179" s="63"/>
+      <c r="I179" s="74"/>
+      <c r="J179" s="74"/>
+      <c r="K179" s="74"/>
+      <c r="L179" s="63"/>
+      <c r="M179" s="63"/>
+      <c r="N179" s="63"/>
+      <c r="O179" s="47"/>
+    </row>
+    <row r="180" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C180" s="60"/>
+      <c r="D180" s="63"/>
+      <c r="E180" s="63"/>
+      <c r="F180" s="74"/>
+      <c r="G180" s="74"/>
+      <c r="H180" s="63"/>
+      <c r="I180" s="74"/>
+      <c r="J180" s="74"/>
+      <c r="K180" s="74"/>
+      <c r="L180" s="63"/>
+      <c r="M180" s="63"/>
+      <c r="N180" s="63"/>
+      <c r="O180" s="47"/>
+    </row>
+    <row r="181" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C181" s="60"/>
+      <c r="D181" s="63"/>
+      <c r="E181" s="63"/>
+      <c r="F181" s="74"/>
+      <c r="G181" s="74"/>
+      <c r="H181" s="63"/>
+      <c r="I181" s="74"/>
+      <c r="J181" s="74"/>
+      <c r="K181" s="74"/>
+      <c r="L181" s="63"/>
+      <c r="M181" s="63"/>
+      <c r="N181" s="63"/>
+      <c r="O181" s="47"/>
+    </row>
+    <row r="182" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C182" s="60"/>
+      <c r="D182" s="63"/>
+      <c r="E182" s="63"/>
+      <c r="F182" s="74"/>
+      <c r="G182" s="74"/>
+      <c r="H182" s="63"/>
+      <c r="I182" s="74"/>
+      <c r="J182" s="74"/>
+      <c r="K182" s="74"/>
+      <c r="L182" s="63"/>
+      <c r="M182" s="63"/>
+      <c r="N182" s="63"/>
+      <c r="O182" s="47"/>
+    </row>
+    <row r="183" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C183" s="60"/>
+      <c r="D183" s="63"/>
+      <c r="E183" s="63"/>
+      <c r="F183" s="74"/>
+      <c r="G183" s="74"/>
+      <c r="H183" s="63"/>
+      <c r="I183" s="74"/>
+      <c r="J183" s="74"/>
+      <c r="K183" s="74"/>
+      <c r="L183" s="63"/>
+      <c r="M183" s="63"/>
+      <c r="N183" s="63"/>
+      <c r="O183" s="47"/>
+    </row>
+    <row r="184" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C184" s="60"/>
+      <c r="D184" s="63"/>
+      <c r="E184" s="63"/>
+      <c r="F184" s="74"/>
+      <c r="G184" s="74"/>
+      <c r="H184" s="63"/>
+      <c r="I184" s="74"/>
+      <c r="J184" s="74"/>
+      <c r="K184" s="74"/>
+      <c r="L184" s="63"/>
+      <c r="M184" s="63"/>
+      <c r="N184" s="63"/>
+      <c r="O184" s="47"/>
+    </row>
+    <row r="185" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C185" s="60"/>
+      <c r="D185" s="63"/>
+      <c r="E185" s="63"/>
+      <c r="F185" s="74"/>
+      <c r="G185" s="74"/>
+      <c r="H185" s="63"/>
+      <c r="I185" s="74"/>
+      <c r="J185" s="74"/>
+      <c r="K185" s="74"/>
+      <c r="L185" s="63"/>
+      <c r="M185" s="63"/>
+      <c r="N185" s="63"/>
+      <c r="O185" s="47"/>
+    </row>
+    <row r="186" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C186" s="60"/>
+      <c r="D186" s="63"/>
+      <c r="E186" s="63"/>
+      <c r="F186" s="74"/>
+      <c r="G186" s="74"/>
+      <c r="H186" s="63"/>
+      <c r="I186" s="74"/>
+      <c r="J186" s="74"/>
+      <c r="K186" s="74"/>
+      <c r="L186" s="63"/>
+      <c r="M186" s="63"/>
+      <c r="N186" s="63"/>
+      <c r="O186" s="47"/>
+    </row>
+    <row r="187" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C187" s="60"/>
+      <c r="D187" s="63"/>
+      <c r="E187" s="63"/>
+      <c r="F187" s="74"/>
+      <c r="G187" s="74"/>
+      <c r="H187" s="63"/>
+      <c r="I187" s="74"/>
+      <c r="J187" s="74"/>
+      <c r="K187" s="74"/>
+      <c r="L187" s="63"/>
+      <c r="M187" s="63"/>
+      <c r="N187" s="63"/>
+      <c r="O187" s="47"/>
+    </row>
+    <row r="188" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C188" s="60"/>
+      <c r="D188" s="63"/>
+      <c r="E188" s="63"/>
+      <c r="F188" s="74"/>
+      <c r="G188" s="74"/>
+      <c r="H188" s="63"/>
+      <c r="I188" s="74"/>
+      <c r="J188" s="74"/>
+      <c r="K188" s="74"/>
+      <c r="L188" s="63"/>
+      <c r="M188" s="63"/>
+      <c r="N188" s="63"/>
+      <c r="O188" s="47"/>
+    </row>
+    <row r="189" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C189" s="60"/>
+      <c r="D189" s="63"/>
+      <c r="E189" s="63"/>
+      <c r="F189" s="74"/>
+      <c r="G189" s="74"/>
+      <c r="H189" s="63"/>
+      <c r="I189" s="74"/>
+      <c r="J189" s="74"/>
+      <c r="K189" s="74"/>
+      <c r="L189" s="63"/>
+      <c r="M189" s="63"/>
+      <c r="N189" s="63"/>
+      <c r="O189" s="47"/>
+    </row>
+    <row r="190" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C190" s="60"/>
+      <c r="D190" s="63"/>
+      <c r="E190" s="63"/>
+      <c r="F190" s="74"/>
+      <c r="G190" s="74"/>
+      <c r="H190" s="63"/>
+      <c r="I190" s="74"/>
+      <c r="J190" s="74"/>
+      <c r="K190" s="74"/>
+      <c r="L190" s="63"/>
+      <c r="M190" s="63"/>
+      <c r="N190" s="63"/>
+      <c r="O190" s="47"/>
+    </row>
+    <row r="191" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C191" s="60"/>
+      <c r="D191" s="63"/>
+      <c r="E191" s="63"/>
+      <c r="F191" s="74"/>
+      <c r="G191" s="74"/>
+      <c r="H191" s="63"/>
+      <c r="I191" s="74"/>
+      <c r="J191" s="74"/>
+      <c r="K191" s="74"/>
+      <c r="L191" s="63"/>
+      <c r="M191" s="63"/>
+      <c r="N191" s="63"/>
+      <c r="O191" s="47"/>
+    </row>
+    <row r="192" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C192" s="60"/>
+      <c r="D192" s="63"/>
+      <c r="E192" s="63"/>
+      <c r="F192" s="74"/>
+      <c r="G192" s="74"/>
+      <c r="H192" s="63"/>
+      <c r="I192" s="74"/>
+      <c r="J192" s="74"/>
+      <c r="K192" s="74"/>
+      <c r="L192" s="63"/>
+      <c r="M192" s="63"/>
+      <c r="N192" s="63"/>
+      <c r="O192" s="47"/>
+    </row>
+    <row r="193" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C193" s="60"/>
+      <c r="D193" s="63"/>
+      <c r="E193" s="63"/>
+      <c r="F193" s="74"/>
+      <c r="G193" s="74"/>
+      <c r="H193" s="63"/>
+      <c r="I193" s="74"/>
+      <c r="J193" s="74"/>
+      <c r="K193" s="74"/>
+      <c r="L193" s="63"/>
+      <c r="M193" s="63"/>
+      <c r="N193" s="63"/>
+      <c r="O193" s="47"/>
+    </row>
+    <row r="194" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C194" s="60"/>
+      <c r="D194" s="63"/>
+      <c r="E194" s="63"/>
+      <c r="F194" s="74"/>
+      <c r="G194" s="74"/>
+      <c r="H194" s="63"/>
+      <c r="I194" s="74"/>
+      <c r="J194" s="74"/>
+      <c r="K194" s="74"/>
+      <c r="L194" s="63"/>
+      <c r="M194" s="63"/>
+      <c r="N194" s="63"/>
+      <c r="O194" s="47"/>
+    </row>
+    <row r="195" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C195" s="60"/>
+      <c r="D195" s="63"/>
+      <c r="E195" s="63"/>
+      <c r="F195" s="74"/>
+      <c r="G195" s="74"/>
+      <c r="H195" s="63"/>
+      <c r="I195" s="74"/>
+      <c r="J195" s="74"/>
+      <c r="K195" s="74"/>
+      <c r="L195" s="63"/>
+      <c r="M195" s="63"/>
+      <c r="N195" s="63"/>
+      <c r="O195" s="47"/>
+    </row>
+    <row r="196" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C196" s="60"/>
+      <c r="D196" s="63"/>
+      <c r="E196" s="63"/>
+      <c r="F196" s="74"/>
+      <c r="G196" s="74"/>
+      <c r="H196" s="63"/>
+      <c r="I196" s="74"/>
+      <c r="J196" s="74"/>
+      <c r="K196" s="74"/>
+      <c r="L196" s="63"/>
+      <c r="M196" s="63"/>
+      <c r="N196" s="63"/>
+      <c r="O196" s="47"/>
+    </row>
+    <row r="197" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C197" s="60"/>
+      <c r="D197" s="63"/>
+      <c r="E197" s="63"/>
+      <c r="F197" s="74"/>
+      <c r="G197" s="74"/>
+      <c r="H197" s="63"/>
+      <c r="I197" s="74"/>
+      <c r="J197" s="74"/>
+      <c r="K197" s="74"/>
+      <c r="L197" s="63"/>
+      <c r="M197" s="63"/>
+      <c r="N197" s="63"/>
+      <c r="O197" s="47"/>
+    </row>
+    <row r="198" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C198" s="60"/>
+      <c r="D198" s="63"/>
+      <c r="E198" s="63"/>
+      <c r="F198" s="74"/>
+      <c r="G198" s="74"/>
+      <c r="H198" s="63"/>
+      <c r="I198" s="74"/>
+      <c r="J198" s="74"/>
+      <c r="K198" s="74"/>
+      <c r="L198" s="63"/>
+      <c r="M198" s="63"/>
+      <c r="N198" s="63"/>
+      <c r="O198" s="47"/>
+    </row>
+    <row r="199" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C199" s="60"/>
+      <c r="D199" s="63"/>
+      <c r="E199" s="63"/>
+      <c r="F199" s="74"/>
+      <c r="G199" s="74"/>
+      <c r="H199" s="63"/>
+      <c r="I199" s="74"/>
+      <c r="J199" s="74"/>
+      <c r="K199" s="74"/>
+      <c r="L199" s="63"/>
+      <c r="M199" s="63"/>
+      <c r="N199" s="63"/>
+      <c r="O199" s="47"/>
+    </row>
+    <row r="200" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C200" s="60"/>
+      <c r="D200" s="63"/>
+      <c r="E200" s="63"/>
+      <c r="F200" s="74"/>
+      <c r="G200" s="74"/>
+      <c r="H200" s="63"/>
+      <c r="I200" s="74"/>
+      <c r="J200" s="74"/>
+      <c r="K200" s="74"/>
+      <c r="L200" s="63"/>
+      <c r="M200" s="63"/>
+      <c r="N200" s="63"/>
+      <c r="O200" s="47"/>
+    </row>
+    <row r="201" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C201" s="60"/>
+      <c r="D201" s="63"/>
+      <c r="E201" s="63"/>
+      <c r="F201" s="74"/>
+      <c r="G201" s="74"/>
+      <c r="H201" s="63"/>
+      <c r="I201" s="74"/>
+      <c r="J201" s="74"/>
+      <c r="K201" s="74"/>
+      <c r="L201" s="63"/>
+      <c r="M201" s="63"/>
+      <c r="N201" s="63"/>
+      <c r="O201" s="47"/>
+    </row>
+    <row r="202" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C202" s="60"/>
+      <c r="D202" s="63"/>
+      <c r="E202" s="63"/>
+      <c r="F202" s="74"/>
+      <c r="G202" s="74"/>
+      <c r="H202" s="63"/>
+      <c r="I202" s="74"/>
+      <c r="J202" s="74"/>
+      <c r="K202" s="74"/>
+      <c r="L202" s="63"/>
+      <c r="M202" s="63"/>
+      <c r="N202" s="63"/>
+      <c r="O202" s="47"/>
+    </row>
+    <row r="203" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C203" s="60"/>
+      <c r="D203" s="63"/>
+      <c r="E203" s="63"/>
+      <c r="F203" s="74"/>
+      <c r="G203" s="74"/>
+      <c r="H203" s="63"/>
+      <c r="I203" s="74"/>
+      <c r="J203" s="74"/>
+      <c r="K203" s="74"/>
+      <c r="L203" s="63"/>
+      <c r="M203" s="63"/>
+      <c r="N203" s="63"/>
+      <c r="O203" s="47"/>
+    </row>
+    <row r="204" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C204" s="60"/>
+      <c r="D204" s="63"/>
+      <c r="E204" s="63"/>
+      <c r="F204" s="74"/>
+      <c r="G204" s="74"/>
+      <c r="H204" s="63"/>
+      <c r="I204" s="74"/>
+      <c r="J204" s="74"/>
+      <c r="K204" s="74"/>
+      <c r="L204" s="63"/>
+      <c r="M204" s="63"/>
+      <c r="N204" s="63"/>
+      <c r="O204" s="47"/>
+    </row>
+    <row r="205" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C205" s="60"/>
+      <c r="D205" s="63"/>
+      <c r="E205" s="63"/>
+      <c r="F205" s="74"/>
+      <c r="G205" s="74"/>
+      <c r="H205" s="63"/>
+      <c r="I205" s="74"/>
+      <c r="J205" s="74"/>
+      <c r="K205" s="74"/>
+      <c r="L205" s="63"/>
+      <c r="M205" s="63"/>
+      <c r="N205" s="63"/>
+      <c r="O205" s="47"/>
+    </row>
+    <row r="206" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C206" s="60"/>
+      <c r="D206" s="63"/>
+      <c r="E206" s="63"/>
+      <c r="F206" s="74"/>
+      <c r="G206" s="74"/>
+      <c r="H206" s="63"/>
+      <c r="I206" s="74"/>
+      <c r="J206" s="74"/>
+      <c r="K206" s="74"/>
+      <c r="L206" s="63"/>
+      <c r="M206" s="63"/>
+      <c r="N206" s="63"/>
+      <c r="O206" s="47"/>
+    </row>
+    <row r="207" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C207" s="60"/>
+      <c r="D207" s="63"/>
+      <c r="E207" s="63"/>
+      <c r="F207" s="74"/>
+      <c r="G207" s="74"/>
+      <c r="H207" s="63"/>
+      <c r="I207" s="74"/>
+      <c r="J207" s="74"/>
+      <c r="K207" s="74"/>
+      <c r="L207" s="63"/>
+      <c r="M207" s="63"/>
+      <c r="N207" s="63"/>
+      <c r="O207" s="47"/>
+    </row>
+    <row r="208" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C208" s="60"/>
+      <c r="D208" s="63"/>
+      <c r="E208" s="63"/>
+      <c r="F208" s="74"/>
+      <c r="G208" s="74"/>
+      <c r="H208" s="63"/>
+      <c r="I208" s="74"/>
+      <c r="J208" s="74"/>
+      <c r="K208" s="74"/>
+      <c r="L208" s="63"/>
+      <c r="M208" s="63"/>
+      <c r="N208" s="63"/>
+      <c r="O208" s="47"/>
+    </row>
+    <row r="209" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C209" s="60"/>
+      <c r="D209" s="63"/>
+      <c r="E209" s="63"/>
+      <c r="F209" s="74"/>
+      <c r="G209" s="74"/>
+      <c r="H209" s="63"/>
+      <c r="I209" s="74"/>
+      <c r="J209" s="74"/>
+      <c r="K209" s="74"/>
+      <c r="L209" s="63"/>
+      <c r="M209" s="63"/>
+      <c r="N209" s="63"/>
+      <c r="O209" s="47"/>
+    </row>
+    <row r="210" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C210" s="60"/>
+      <c r="D210" s="63"/>
+      <c r="E210" s="63"/>
+      <c r="F210" s="74"/>
+      <c r="G210" s="74"/>
+      <c r="H210" s="63"/>
+      <c r="I210" s="74"/>
+      <c r="J210" s="74"/>
+      <c r="K210" s="74"/>
+      <c r="L210" s="63"/>
+      <c r="M210" s="63"/>
+      <c r="N210" s="63"/>
+      <c r="O210" s="47"/>
+    </row>
+    <row r="211" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C211" s="60"/>
+      <c r="D211" s="63"/>
+      <c r="E211" s="63"/>
+      <c r="F211" s="74"/>
+      <c r="G211" s="74"/>
+      <c r="H211" s="63"/>
+      <c r="I211" s="74"/>
+      <c r="J211" s="74"/>
+      <c r="K211" s="74"/>
+      <c r="L211" s="63"/>
+      <c r="M211" s="63"/>
+      <c r="N211" s="63"/>
+      <c r="O211" s="47"/>
+    </row>
+    <row r="212" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C212" s="60"/>
+      <c r="D212" s="63"/>
+      <c r="E212" s="63"/>
+      <c r="F212" s="74"/>
+      <c r="G212" s="74"/>
+      <c r="H212" s="63"/>
+      <c r="I212" s="74"/>
+      <c r="J212" s="74"/>
+      <c r="K212" s="74"/>
+      <c r="L212" s="63"/>
+      <c r="M212" s="63"/>
+      <c r="N212" s="63"/>
+      <c r="O212" s="47"/>
+    </row>
+    <row r="213" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C213" s="60"/>
+      <c r="D213" s="63"/>
+      <c r="E213" s="63"/>
+      <c r="F213" s="74"/>
+      <c r="G213" s="74"/>
+      <c r="H213" s="63"/>
+      <c r="I213" s="74"/>
+      <c r="J213" s="74"/>
+      <c r="K213" s="74"/>
+      <c r="L213" s="63"/>
+      <c r="M213" s="63"/>
+      <c r="N213" s="63"/>
+      <c r="O213" s="47"/>
+    </row>
+    <row r="214" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C214" s="60"/>
+      <c r="D214" s="63"/>
+      <c r="E214" s="63"/>
+      <c r="F214" s="74"/>
+      <c r="G214" s="74"/>
+      <c r="H214" s="63"/>
+      <c r="I214" s="74"/>
+      <c r="J214" s="74"/>
+      <c r="K214" s="74"/>
+      <c r="L214" s="63"/>
+      <c r="M214" s="63"/>
+      <c r="N214" s="63"/>
+      <c r="O214" s="47"/>
+    </row>
+    <row r="215" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C215" s="60"/>
+      <c r="D215" s="63"/>
+      <c r="E215" s="63"/>
+      <c r="F215" s="74"/>
+      <c r="G215" s="74"/>
+      <c r="H215" s="63"/>
+      <c r="I215" s="74"/>
+      <c r="J215" s="74"/>
+      <c r="K215" s="74"/>
+      <c r="L215" s="63"/>
+      <c r="M215" s="63"/>
+      <c r="N215" s="63"/>
+      <c r="O215" s="47"/>
+    </row>
+    <row r="216" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C216" s="60"/>
+      <c r="D216" s="63"/>
+      <c r="E216" s="63"/>
+      <c r="F216" s="74"/>
+      <c r="G216" s="74"/>
+      <c r="H216" s="63"/>
+      <c r="I216" s="74"/>
+      <c r="J216" s="74"/>
+      <c r="K216" s="74"/>
+      <c r="L216" s="63"/>
+      <c r="M216" s="63"/>
+      <c r="N216" s="63"/>
+      <c r="O216" s="47"/>
+    </row>
+    <row r="217" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C217" s="60"/>
+      <c r="D217" s="63"/>
+      <c r="E217" s="63"/>
+      <c r="F217" s="74"/>
+      <c r="G217" s="74"/>
+      <c r="H217" s="63"/>
+      <c r="I217" s="74"/>
+      <c r="J217" s="74"/>
+      <c r="K217" s="74"/>
+      <c r="L217" s="63"/>
+      <c r="M217" s="63"/>
+      <c r="N217" s="63"/>
+      <c r="O217" s="47"/>
+    </row>
+    <row r="218" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C218" s="60"/>
+      <c r="D218" s="63"/>
+      <c r="E218" s="63"/>
+      <c r="F218" s="74"/>
+      <c r="G218" s="74"/>
+      <c r="H218" s="63"/>
+      <c r="I218" s="74"/>
+      <c r="J218" s="74"/>
+      <c r="K218" s="74"/>
+      <c r="L218" s="63"/>
+      <c r="M218" s="63"/>
+      <c r="N218" s="63"/>
+      <c r="O218" s="47"/>
+    </row>
+    <row r="219" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C219" s="60"/>
+      <c r="D219" s="63"/>
+      <c r="E219" s="63"/>
+      <c r="F219" s="74"/>
+      <c r="G219" s="74"/>
+      <c r="H219" s="63"/>
+      <c r="I219" s="74"/>
+      <c r="J219" s="74"/>
+      <c r="K219" s="74"/>
+      <c r="L219" s="63"/>
+      <c r="M219" s="63"/>
+      <c r="N219" s="63"/>
+      <c r="O219" s="47"/>
+    </row>
+    <row r="220" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C220" s="60"/>
+      <c r="D220" s="63"/>
+      <c r="E220" s="63"/>
+      <c r="F220" s="74"/>
+      <c r="G220" s="74"/>
+      <c r="H220" s="63"/>
+      <c r="I220" s="74"/>
+      <c r="J220" s="74"/>
+      <c r="K220" s="74"/>
+      <c r="L220" s="63"/>
+      <c r="M220" s="63"/>
+      <c r="N220" s="63"/>
+      <c r="O220" s="47"/>
+    </row>
+    <row r="221" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C221" s="60"/>
+      <c r="D221" s="63"/>
+      <c r="E221" s="63"/>
+      <c r="F221" s="74"/>
+      <c r="G221" s="74"/>
+      <c r="H221" s="63"/>
+      <c r="I221" s="74"/>
+      <c r="J221" s="74"/>
+      <c r="K221" s="74"/>
+      <c r="L221" s="63"/>
+      <c r="M221" s="63"/>
+      <c r="N221" s="63"/>
+      <c r="O221" s="47"/>
+    </row>
+    <row r="222" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C222" s="60"/>
+      <c r="D222" s="63"/>
+      <c r="E222" s="63"/>
+      <c r="F222" s="74"/>
+      <c r="G222" s="74"/>
+      <c r="H222" s="63"/>
+      <c r="I222" s="74"/>
+      <c r="J222" s="74"/>
+      <c r="K222" s="74"/>
+      <c r="L222" s="63"/>
+      <c r="M222" s="63"/>
+      <c r="N222" s="63"/>
+      <c r="O222" s="47"/>
+    </row>
+    <row r="223" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C223" s="60"/>
+      <c r="D223" s="63"/>
+      <c r="E223" s="63"/>
+      <c r="F223" s="74"/>
+      <c r="G223" s="74"/>
+      <c r="H223" s="63"/>
+      <c r="I223" s="74"/>
+      <c r="J223" s="74"/>
+      <c r="K223" s="74"/>
+      <c r="L223" s="63"/>
+      <c r="M223" s="63"/>
+      <c r="N223" s="63"/>
+      <c r="O223" s="47"/>
+    </row>
+    <row r="224" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C224" s="60"/>
+      <c r="D224" s="63"/>
+      <c r="E224" s="63"/>
+      <c r="F224" s="74"/>
+      <c r="G224" s="74"/>
+      <c r="H224" s="63"/>
+      <c r="I224" s="74"/>
+      <c r="J224" s="74"/>
+      <c r="K224" s="74"/>
+      <c r="L224" s="63"/>
+      <c r="M224" s="63"/>
+      <c r="N224" s="63"/>
+      <c r="O224" s="47"/>
+    </row>
+    <row r="225" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C225" s="60"/>
+      <c r="D225" s="63"/>
+      <c r="E225" s="63"/>
+      <c r="F225" s="74"/>
+      <c r="G225" s="74"/>
+      <c r="H225" s="63"/>
+      <c r="I225" s="74"/>
+      <c r="J225" s="74"/>
+      <c r="K225" s="74"/>
+      <c r="L225" s="63"/>
+      <c r="M225" s="63"/>
+      <c r="N225" s="63"/>
+      <c r="O225" s="47"/>
+    </row>
+    <row r="226" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C226" s="60"/>
+      <c r="D226" s="63"/>
+      <c r="E226" s="63"/>
+      <c r="F226" s="74"/>
+      <c r="G226" s="74"/>
+      <c r="H226" s="63"/>
+      <c r="I226" s="74"/>
+      <c r="J226" s="74"/>
+      <c r="K226" s="74"/>
+      <c r="L226" s="63"/>
+      <c r="M226" s="63"/>
+      <c r="N226" s="63"/>
+      <c r="O226" s="47"/>
+    </row>
+    <row r="227" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C227" s="60"/>
+      <c r="D227" s="63"/>
+      <c r="E227" s="63"/>
+      <c r="F227" s="74"/>
+      <c r="G227" s="74"/>
+      <c r="H227" s="63"/>
+      <c r="I227" s="74"/>
+      <c r="J227" s="74"/>
+      <c r="K227" s="74"/>
+      <c r="L227" s="63"/>
+      <c r="M227" s="63"/>
+      <c r="N227" s="63"/>
+      <c r="O227" s="47"/>
+    </row>
+    <row r="228" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C228" s="60"/>
+      <c r="D228" s="63"/>
+      <c r="E228" s="63"/>
+      <c r="F228" s="74"/>
+      <c r="G228" s="74"/>
+      <c r="H228" s="63"/>
+      <c r="I228" s="74"/>
+      <c r="J228" s="74"/>
+      <c r="K228" s="74"/>
+      <c r="L228" s="63"/>
+      <c r="M228" s="63"/>
+      <c r="N228" s="63"/>
+      <c r="O228" s="47"/>
+    </row>
+    <row r="229" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C229" s="60"/>
+      <c r="D229" s="63"/>
+      <c r="E229" s="63"/>
+      <c r="F229" s="74"/>
+      <c r="G229" s="74"/>
+      <c r="H229" s="63"/>
+      <c r="I229" s="74"/>
+      <c r="J229" s="74"/>
+      <c r="K229" s="74"/>
+      <c r="L229" s="63"/>
+      <c r="M229" s="63"/>
+      <c r="N229" s="63"/>
+      <c r="O229" s="47"/>
+    </row>
+    <row r="230" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C230" s="60"/>
+      <c r="D230" s="63"/>
+      <c r="E230" s="63"/>
+      <c r="F230" s="74"/>
+      <c r="G230" s="74"/>
+      <c r="H230" s="63"/>
+      <c r="I230" s="74"/>
+      <c r="J230" s="74"/>
+      <c r="K230" s="74"/>
+      <c r="L230" s="63"/>
+      <c r="M230" s="63"/>
+      <c r="N230" s="63"/>
+      <c r="O230" s="47"/>
+    </row>
+    <row r="231" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C231" s="60"/>
+      <c r="D231" s="63"/>
+      <c r="E231" s="63"/>
+      <c r="F231" s="74"/>
+      <c r="G231" s="74"/>
+      <c r="H231" s="63"/>
+      <c r="I231" s="74"/>
+      <c r="J231" s="74"/>
+      <c r="K231" s="74"/>
+      <c r="L231" s="63"/>
+      <c r="M231" s="63"/>
+      <c r="N231" s="63"/>
+      <c r="O231" s="47"/>
+    </row>
+    <row r="232" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C232" s="60"/>
+      <c r="D232" s="63"/>
+      <c r="E232" s="63"/>
+      <c r="F232" s="74"/>
+      <c r="G232" s="74"/>
+      <c r="H232" s="63"/>
+      <c r="I232" s="74"/>
+      <c r="J232" s="74"/>
+      <c r="K232" s="74"/>
+      <c r="L232" s="63"/>
+      <c r="M232" s="63"/>
+      <c r="N232" s="63"/>
+      <c r="O232" s="47"/>
+    </row>
+    <row r="233" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C233" s="60"/>
+      <c r="D233" s="63"/>
+      <c r="E233" s="63"/>
+      <c r="F233" s="74"/>
+      <c r="G233" s="74"/>
+      <c r="H233" s="63"/>
+      <c r="I233" s="74"/>
+      <c r="J233" s="74"/>
+      <c r="K233" s="74"/>
+      <c r="L233" s="63"/>
+      <c r="M233" s="63"/>
+      <c r="N233" s="63"/>
+      <c r="O233" s="47"/>
+    </row>
+    <row r="234" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C234" s="60"/>
+      <c r="D234" s="63"/>
+      <c r="E234" s="63"/>
+      <c r="F234" s="74"/>
+      <c r="G234" s="74"/>
+      <c r="H234" s="63"/>
+      <c r="I234" s="74"/>
+      <c r="J234" s="74"/>
+      <c r="K234" s="74"/>
+      <c r="L234" s="63"/>
+      <c r="M234" s="63"/>
+      <c r="N234" s="63"/>
+      <c r="O234" s="47"/>
+    </row>
+    <row r="235" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C235" s="60"/>
+      <c r="D235" s="63"/>
+      <c r="E235" s="63"/>
+      <c r="F235" s="74"/>
+      <c r="G235" s="74"/>
+      <c r="H235" s="63"/>
+      <c r="I235" s="74"/>
+      <c r="J235" s="74"/>
+      <c r="K235" s="74"/>
+      <c r="L235" s="63"/>
+      <c r="M235" s="63"/>
+      <c r="N235" s="63"/>
+      <c r="O235" s="47"/>
+    </row>
+    <row r="236" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C236" s="60"/>
+      <c r="D236" s="63"/>
+      <c r="E236" s="63"/>
+      <c r="F236" s="74"/>
+      <c r="G236" s="74"/>
+      <c r="H236" s="63"/>
+      <c r="I236" s="74"/>
+      <c r="J236" s="74"/>
+      <c r="K236" s="74"/>
+      <c r="L236" s="63"/>
+      <c r="M236" s="63"/>
+      <c r="N236" s="63"/>
+      <c r="O236" s="47"/>
+    </row>
+    <row r="237" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C237" s="60"/>
+      <c r="D237" s="63"/>
+      <c r="E237" s="63"/>
+      <c r="F237" s="74"/>
+      <c r="G237" s="74"/>
+      <c r="H237" s="63"/>
+      <c r="I237" s="74"/>
+      <c r="J237" s="74"/>
+      <c r="K237" s="74"/>
+      <c r="L237" s="63"/>
+      <c r="M237" s="63"/>
+      <c r="N237" s="63"/>
+      <c r="O237" s="47"/>
+    </row>
+    <row r="238" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C238" s="60"/>
+      <c r="D238" s="63"/>
+      <c r="E238" s="63"/>
+      <c r="F238" s="74"/>
+      <c r="G238" s="74"/>
+      <c r="H238" s="63"/>
+      <c r="I238" s="74"/>
+      <c r="J238" s="74"/>
+      <c r="K238" s="74"/>
+      <c r="L238" s="63"/>
+      <c r="M238" s="63"/>
+      <c r="N238" s="63"/>
+      <c r="O238" s="47"/>
+    </row>
+    <row r="239" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C239" s="60"/>
+      <c r="D239" s="63"/>
+      <c r="E239" s="63"/>
+      <c r="F239" s="74"/>
+      <c r="G239" s="74"/>
+      <c r="H239" s="63"/>
+      <c r="I239" s="74"/>
+      <c r="J239" s="74"/>
+      <c r="K239" s="74"/>
+      <c r="L239" s="63"/>
+      <c r="M239" s="63"/>
+      <c r="N239" s="63"/>
+      <c r="O239" s="47"/>
+    </row>
+    <row r="240" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C240" s="60"/>
+      <c r="D240" s="63"/>
+      <c r="E240" s="63"/>
+      <c r="F240" s="74"/>
+      <c r="G240" s="74"/>
+      <c r="H240" s="63"/>
+      <c r="I240" s="74"/>
+      <c r="J240" s="74"/>
+      <c r="K240" s="74"/>
+      <c r="L240" s="63"/>
+      <c r="M240" s="63"/>
+      <c r="N240" s="63"/>
+      <c r="O240" s="47"/>
+    </row>
+    <row r="241" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C241" s="60"/>
+      <c r="D241" s="63"/>
+      <c r="E241" s="63"/>
+      <c r="F241" s="74"/>
+      <c r="G241" s="74"/>
+      <c r="H241" s="63"/>
+      <c r="I241" s="74"/>
+      <c r="J241" s="74"/>
+      <c r="K241" s="74"/>
+      <c r="L241" s="63"/>
+      <c r="M241" s="63"/>
+      <c r="N241" s="63"/>
+      <c r="O241" s="47"/>
+    </row>
+    <row r="242" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C242" s="60"/>
+      <c r="D242" s="63"/>
+      <c r="E242" s="63"/>
+      <c r="F242" s="74"/>
+      <c r="G242" s="74"/>
+      <c r="H242" s="63"/>
+      <c r="I242" s="74"/>
+      <c r="J242" s="74"/>
+      <c r="K242" s="74"/>
+      <c r="L242" s="63"/>
+      <c r="M242" s="63"/>
+      <c r="N242" s="63"/>
+      <c r="O242" s="47"/>
+    </row>
+    <row r="243" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C243" s="60"/>
+      <c r="D243" s="63"/>
+      <c r="E243" s="63"/>
+      <c r="F243" s="74"/>
+      <c r="G243" s="74"/>
+      <c r="H243" s="63"/>
+      <c r="I243" s="74"/>
+      <c r="J243" s="74"/>
+      <c r="K243" s="74"/>
+      <c r="L243" s="63"/>
+      <c r="M243" s="63"/>
+      <c r="N243" s="63"/>
+      <c r="O243" s="47"/>
+    </row>
+    <row r="244" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C244" s="60"/>
+      <c r="D244" s="63"/>
+      <c r="E244" s="63"/>
+      <c r="F244" s="74"/>
+      <c r="G244" s="74"/>
+      <c r="H244" s="63"/>
+      <c r="I244" s="74"/>
+      <c r="J244" s="74"/>
+      <c r="K244" s="74"/>
+      <c r="L244" s="63"/>
+      <c r="M244" s="63"/>
+      <c r="N244" s="63"/>
+      <c r="O244" s="47"/>
+    </row>
+    <row r="245" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C245" s="60"/>
+      <c r="D245" s="63"/>
+      <c r="E245" s="63"/>
+      <c r="F245" s="74"/>
+      <c r="G245" s="74"/>
+      <c r="H245" s="63"/>
+      <c r="I245" s="74"/>
+      <c r="J245" s="74"/>
+      <c r="K245" s="74"/>
+      <c r="L245" s="63"/>
+      <c r="M245" s="63"/>
+      <c r="N245" s="63"/>
+      <c r="O245" s="47"/>
+    </row>
+    <row r="246" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C246" s="60"/>
+      <c r="D246" s="63"/>
+      <c r="E246" s="63"/>
+      <c r="F246" s="74"/>
+      <c r="G246" s="74"/>
+      <c r="H246" s="63"/>
+      <c r="I246" s="74"/>
+      <c r="J246" s="74"/>
+      <c r="K246" s="74"/>
+      <c r="L246" s="63"/>
+      <c r="M246" s="63"/>
+      <c r="N246" s="63"/>
+      <c r="O246" s="47"/>
+    </row>
+    <row r="247" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C247" s="60"/>
+      <c r="D247" s="63"/>
+      <c r="E247" s="63"/>
+      <c r="F247" s="74"/>
+      <c r="G247" s="74"/>
+      <c r="H247" s="63"/>
+      <c r="I247" s="74"/>
+      <c r="J247" s="74"/>
+      <c r="K247" s="74"/>
+      <c r="L247" s="63"/>
+      <c r="M247" s="63"/>
+      <c r="N247" s="63"/>
+      <c r="O247" s="47"/>
+    </row>
+    <row r="248" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C248" s="60"/>
+      <c r="D248" s="63"/>
+      <c r="E248" s="63"/>
+      <c r="F248" s="74"/>
+      <c r="G248" s="74"/>
+      <c r="H248" s="63"/>
+      <c r="I248" s="74"/>
+      <c r="J248" s="74"/>
+      <c r="K248" s="74"/>
+      <c r="L248" s="63"/>
+      <c r="M248" s="63"/>
+      <c r="N248" s="63"/>
+      <c r="O248" s="47"/>
+    </row>
+    <row r="249" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C249" s="60"/>
+      <c r="D249" s="63"/>
+      <c r="E249" s="63"/>
+      <c r="F249" s="74"/>
+      <c r="G249" s="74"/>
+      <c r="H249" s="63"/>
+      <c r="I249" s="74"/>
+      <c r="J249" s="74"/>
+      <c r="K249" s="74"/>
+      <c r="L249" s="63"/>
+      <c r="M249" s="63"/>
+      <c r="N249" s="63"/>
+      <c r="O249" s="47"/>
+    </row>
+    <row r="250" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C250" s="60"/>
+      <c r="D250" s="63"/>
+      <c r="E250" s="63"/>
+      <c r="F250" s="74"/>
+      <c r="G250" s="74"/>
+      <c r="H250" s="63"/>
+      <c r="I250" s="74"/>
+      <c r="J250" s="74"/>
+      <c r="K250" s="74"/>
+      <c r="L250" s="63"/>
+      <c r="M250" s="63"/>
+      <c r="N250" s="63"/>
+      <c r="O250" s="47"/>
+    </row>
+    <row r="251" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C251" s="60"/>
+      <c r="D251" s="63"/>
+      <c r="E251" s="63"/>
+      <c r="F251" s="74"/>
+      <c r="G251" s="74"/>
+      <c r="H251" s="63"/>
+      <c r="I251" s="74"/>
+      <c r="J251" s="74"/>
+      <c r="K251" s="74"/>
+      <c r="L251" s="63"/>
+      <c r="M251" s="63"/>
+      <c r="N251" s="63"/>
+      <c r="O251" s="47"/>
+    </row>
+    <row r="252" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C252" s="60"/>
+      <c r="D252" s="63"/>
+      <c r="E252" s="63"/>
+      <c r="F252" s="74"/>
+      <c r="G252" s="74"/>
+      <c r="H252" s="63"/>
+      <c r="I252" s="74"/>
+      <c r="J252" s="74"/>
+      <c r="K252" s="74"/>
+      <c r="L252" s="63"/>
+      <c r="M252" s="63"/>
+      <c r="N252" s="63"/>
+      <c r="O252" s="47"/>
+    </row>
+    <row r="253" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C253" s="60"/>
+      <c r="D253" s="63"/>
+      <c r="E253" s="63"/>
+      <c r="F253" s="74"/>
+      <c r="G253" s="74"/>
+      <c r="H253" s="63"/>
+      <c r="I253" s="74"/>
+      <c r="J253" s="74"/>
+      <c r="K253" s="74"/>
+      <c r="L253" s="63"/>
+      <c r="M253" s="63"/>
+      <c r="N253" s="63"/>
+      <c r="O253" s="47"/>
+    </row>
+    <row r="254" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C254" s="60"/>
+      <c r="D254" s="63"/>
+      <c r="E254" s="63"/>
+      <c r="F254" s="74"/>
+      <c r="G254" s="74"/>
+      <c r="H254" s="63"/>
+      <c r="I254" s="74"/>
+      <c r="J254" s="74"/>
+      <c r="K254" s="74"/>
+      <c r="L254" s="63"/>
+      <c r="M254" s="63"/>
+      <c r="N254" s="63"/>
+      <c r="O254" s="47"/>
+    </row>
+    <row r="255" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C255" s="60"/>
+      <c r="D255" s="63"/>
+      <c r="E255" s="63"/>
+      <c r="F255" s="74"/>
+      <c r="G255" s="74"/>
+      <c r="H255" s="63"/>
+      <c r="I255" s="74"/>
+      <c r="J255" s="74"/>
+      <c r="K255" s="74"/>
+      <c r="L255" s="63"/>
+      <c r="M255" s="63"/>
+      <c r="N255" s="63"/>
+      <c r="O255" s="47"/>
+    </row>
+    <row r="256" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C256" s="60"/>
+      <c r="D256" s="63"/>
+      <c r="E256" s="63"/>
+      <c r="F256" s="74"/>
+      <c r="G256" s="74"/>
+      <c r="H256" s="63"/>
+      <c r="I256" s="74"/>
+      <c r="J256" s="74"/>
+      <c r="K256" s="74"/>
+      <c r="L256" s="63"/>
+      <c r="M256" s="63"/>
+      <c r="N256" s="63"/>
+      <c r="O256" s="47"/>
+    </row>
+    <row r="257" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C257" s="60"/>
+      <c r="D257" s="63"/>
+      <c r="E257" s="63"/>
+      <c r="F257" s="74"/>
+      <c r="G257" s="74"/>
+      <c r="H257" s="63"/>
+      <c r="I257" s="74"/>
+      <c r="J257" s="74"/>
+      <c r="K257" s="74"/>
+      <c r="L257" s="63"/>
+      <c r="M257" s="63"/>
+      <c r="N257" s="63"/>
+      <c r="O257" s="47"/>
+    </row>
+    <row r="258" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C258" s="60"/>
+      <c r="D258" s="63"/>
+      <c r="E258" s="63"/>
+      <c r="F258" s="74"/>
+      <c r="G258" s="74"/>
+      <c r="H258" s="63"/>
+      <c r="I258" s="74"/>
+      <c r="J258" s="74"/>
+      <c r="K258" s="74"/>
+      <c r="L258" s="63"/>
+      <c r="M258" s="63"/>
+      <c r="N258" s="63"/>
+      <c r="O258" s="47"/>
+    </row>
+    <row r="259" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C259" s="60"/>
+      <c r="D259" s="63"/>
+      <c r="E259" s="63"/>
+      <c r="F259" s="74"/>
+      <c r="G259" s="74"/>
+      <c r="H259" s="63"/>
+      <c r="I259" s="74"/>
+      <c r="J259" s="74"/>
+      <c r="K259" s="74"/>
+      <c r="L259" s="63"/>
+      <c r="M259" s="63"/>
+      <c r="N259" s="63"/>
+      <c r="O259" s="47"/>
+    </row>
+    <row r="260" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C260" s="60"/>
+      <c r="D260" s="63"/>
+      <c r="E260" s="63"/>
+      <c r="F260" s="74"/>
+      <c r="G260" s="74"/>
+      <c r="H260" s="63"/>
+      <c r="I260" s="74"/>
+      <c r="J260" s="74"/>
+      <c r="K260" s="74"/>
+      <c r="L260" s="63"/>
+      <c r="M260" s="63"/>
+      <c r="N260" s="63"/>
+      <c r="O260" s="47"/>
+    </row>
+    <row r="261" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C261" s="60"/>
+      <c r="D261" s="63"/>
+      <c r="E261" s="63"/>
+      <c r="F261" s="74"/>
+      <c r="G261" s="74"/>
+      <c r="H261" s="63"/>
+      <c r="I261" s="74"/>
+      <c r="J261" s="74"/>
+      <c r="K261" s="74"/>
+      <c r="L261" s="63"/>
+      <c r="M261" s="63"/>
+      <c r="N261" s="63"/>
+      <c r="O261" s="47"/>
+    </row>
+    <row r="262" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C262" s="60"/>
+      <c r="D262" s="63"/>
+      <c r="E262" s="63"/>
+      <c r="F262" s="74"/>
+      <c r="G262" s="74"/>
+      <c r="H262" s="63"/>
+      <c r="I262" s="74"/>
+      <c r="J262" s="74"/>
+      <c r="K262" s="74"/>
+      <c r="L262" s="63"/>
+      <c r="M262" s="63"/>
+      <c r="N262" s="63"/>
+      <c r="O262" s="47"/>
+    </row>
+    <row r="263" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C263" s="60"/>
+      <c r="D263" s="63"/>
+      <c r="E263" s="63"/>
+      <c r="F263" s="74"/>
+      <c r="G263" s="74"/>
+      <c r="H263" s="63"/>
+      <c r="I263" s="74"/>
+      <c r="J263" s="74"/>
+      <c r="K263" s="74"/>
+      <c r="L263" s="63"/>
+      <c r="M263" s="63"/>
+      <c r="N263" s="63"/>
+      <c r="O263" s="47"/>
+    </row>
+    <row r="264" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C264" s="60"/>
+      <c r="D264" s="63"/>
+      <c r="E264" s="63"/>
+      <c r="F264" s="74"/>
+      <c r="G264" s="74"/>
+      <c r="H264" s="63"/>
+      <c r="I264" s="74"/>
+      <c r="J264" s="74"/>
+      <c r="K264" s="74"/>
+      <c r="L264" s="63"/>
+      <c r="M264" s="63"/>
+      <c r="N264" s="63"/>
+      <c r="O264" s="47"/>
+    </row>
+    <row r="265" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C265" s="60"/>
+      <c r="D265" s="63"/>
+      <c r="E265" s="63"/>
+      <c r="F265" s="74"/>
+      <c r="G265" s="74"/>
+      <c r="H265" s="63"/>
+      <c r="I265" s="74"/>
+      <c r="J265" s="74"/>
+      <c r="K265" s="74"/>
+      <c r="L265" s="63"/>
+      <c r="M265" s="63"/>
+      <c r="N265" s="63"/>
+      <c r="O265" s="47"/>
+    </row>
+    <row r="266" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C266" s="60"/>
+      <c r="D266" s="63"/>
+      <c r="E266" s="63"/>
+      <c r="F266" s="74"/>
+      <c r="G266" s="74"/>
+      <c r="H266" s="63"/>
+      <c r="I266" s="74"/>
+      <c r="J266" s="74"/>
+      <c r="K266" s="74"/>
+      <c r="L266" s="63"/>
+      <c r="M266" s="63"/>
+      <c r="N266" s="63"/>
+      <c r="O266" s="47"/>
+    </row>
+    <row r="267" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C267" s="60"/>
+      <c r="D267" s="63"/>
+      <c r="E267" s="63"/>
+      <c r="F267" s="74"/>
+      <c r="G267" s="74"/>
+      <c r="H267" s="63"/>
+      <c r="I267" s="74"/>
+      <c r="J267" s="74"/>
+      <c r="K267" s="74"/>
+      <c r="L267" s="63"/>
+      <c r="M267" s="63"/>
+      <c r="N267" s="63"/>
+      <c r="O267" s="47"/>
+    </row>
+    <row r="268" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C268" s="60"/>
+      <c r="D268" s="63"/>
+      <c r="E268" s="63"/>
+      <c r="F268" s="74"/>
+      <c r="G268" s="74"/>
+      <c r="H268" s="63"/>
+      <c r="I268" s="74"/>
+      <c r="J268" s="74"/>
+      <c r="K268" s="74"/>
+      <c r="L268" s="63"/>
+      <c r="M268" s="63"/>
+      <c r="N268" s="63"/>
+      <c r="O268" s="47"/>
+    </row>
+    <row r="269" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C269" s="60"/>
+      <c r="D269" s="63"/>
+      <c r="E269" s="63"/>
+      <c r="F269" s="74"/>
+      <c r="G269" s="74"/>
+      <c r="H269" s="63"/>
+      <c r="I269" s="74"/>
+      <c r="J269" s="74"/>
+      <c r="K269" s="74"/>
+      <c r="L269" s="63"/>
+      <c r="M269" s="63"/>
+      <c r="N269" s="63"/>
+      <c r="O269" s="47"/>
+    </row>
+    <row r="270" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C270" s="60"/>
+      <c r="D270" s="63"/>
+      <c r="E270" s="63"/>
+      <c r="F270" s="74"/>
+      <c r="G270" s="74"/>
+      <c r="H270" s="63"/>
+      <c r="I270" s="74"/>
+      <c r="J270" s="74"/>
+      <c r="K270" s="74"/>
+      <c r="L270" s="63"/>
+      <c r="M270" s="63"/>
+      <c r="N270" s="63"/>
+      <c r="O270" s="47"/>
+    </row>
+    <row r="271" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C271" s="60"/>
+      <c r="D271" s="63"/>
+      <c r="E271" s="63"/>
+      <c r="F271" s="74"/>
+      <c r="G271" s="74"/>
+      <c r="H271" s="63"/>
+      <c r="I271" s="74"/>
+      <c r="J271" s="74"/>
+      <c r="K271" s="74"/>
+      <c r="L271" s="63"/>
+      <c r="M271" s="63"/>
+      <c r="N271" s="63"/>
+      <c r="O271" s="47"/>
+    </row>
+    <row r="272" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C272" s="60"/>
+      <c r="D272" s="63"/>
+      <c r="E272" s="63"/>
+      <c r="F272" s="74"/>
+      <c r="G272" s="74"/>
+      <c r="H272" s="63"/>
+      <c r="I272" s="74"/>
+      <c r="J272" s="74"/>
+      <c r="K272" s="74"/>
+      <c r="L272" s="63"/>
+      <c r="M272" s="63"/>
+      <c r="N272" s="63"/>
+      <c r="O272" s="47"/>
+    </row>
+    <row r="273" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C273" s="60"/>
+      <c r="D273" s="63"/>
+      <c r="E273" s="63"/>
+      <c r="F273" s="74"/>
+      <c r="G273" s="74"/>
+      <c r="H273" s="63"/>
+      <c r="I273" s="74"/>
+      <c r="J273" s="74"/>
+      <c r="K273" s="74"/>
+      <c r="L273" s="63"/>
+      <c r="M273" s="63"/>
+      <c r="N273" s="63"/>
+      <c r="O273" s="47"/>
+    </row>
+    <row r="274" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C274" s="60"/>
+      <c r="D274" s="63"/>
+      <c r="E274" s="63"/>
+      <c r="F274" s="74"/>
+      <c r="G274" s="74"/>
+      <c r="H274" s="63"/>
+      <c r="I274" s="74"/>
+      <c r="J274" s="74"/>
+      <c r="K274" s="74"/>
+      <c r="L274" s="63"/>
+      <c r="M274" s="63"/>
+      <c r="N274" s="63"/>
+      <c r="O274" s="47"/>
+    </row>
+    <row r="275" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C275" s="60"/>
+      <c r="D275" s="63"/>
+      <c r="E275" s="63"/>
+      <c r="F275" s="74"/>
+      <c r="G275" s="74"/>
+      <c r="H275" s="63"/>
+      <c r="I275" s="74"/>
+      <c r="J275" s="74"/>
+      <c r="K275" s="74"/>
+      <c r="L275" s="63"/>
+      <c r="M275" s="63"/>
+      <c r="N275" s="63"/>
+      <c r="O275" s="47"/>
+    </row>
+    <row r="276" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C276" s="60"/>
+      <c r="D276" s="63"/>
+      <c r="E276" s="63"/>
+      <c r="F276" s="74"/>
+      <c r="G276" s="74"/>
+      <c r="H276" s="63"/>
+      <c r="I276" s="74"/>
+      <c r="J276" s="74"/>
+      <c r="K276" s="74"/>
+      <c r="L276" s="63"/>
+      <c r="M276" s="63"/>
+      <c r="N276" s="63"/>
+      <c r="O276" s="47"/>
+    </row>
+    <row r="277" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C277" s="60"/>
+      <c r="D277" s="63"/>
+      <c r="E277" s="63"/>
+      <c r="F277" s="74"/>
+      <c r="G277" s="74"/>
+      <c r="H277" s="63"/>
+      <c r="I277" s="74"/>
+      <c r="J277" s="74"/>
+      <c r="K277" s="74"/>
+      <c r="L277" s="63"/>
+      <c r="M277" s="63"/>
+      <c r="N277" s="63"/>
+      <c r="O277" s="47"/>
+    </row>
+    <row r="278" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C278" s="60"/>
+      <c r="D278" s="63"/>
+      <c r="E278" s="63"/>
+      <c r="F278" s="74"/>
+      <c r="G278" s="74"/>
+      <c r="H278" s="63"/>
+      <c r="I278" s="74"/>
+      <c r="J278" s="74"/>
+      <c r="K278" s="74"/>
+      <c r="L278" s="63"/>
+      <c r="M278" s="63"/>
+      <c r="N278" s="63"/>
+      <c r="O278" s="47"/>
+    </row>
+    <row r="279" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C279" s="60"/>
+      <c r="D279" s="63"/>
+      <c r="E279" s="63"/>
+      <c r="F279" s="74"/>
+      <c r="G279" s="74"/>
+      <c r="H279" s="63"/>
+      <c r="I279" s="74"/>
+      <c r="J279" s="74"/>
+      <c r="K279" s="74"/>
+      <c r="L279" s="63"/>
+      <c r="M279" s="63"/>
+      <c r="N279" s="63"/>
+      <c r="O279" s="47"/>
+    </row>
+    <row r="280" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C280" s="60"/>
+      <c r="D280" s="63"/>
+      <c r="E280" s="63"/>
+      <c r="F280" s="74"/>
+      <c r="G280" s="74"/>
+      <c r="H280" s="63"/>
+      <c r="I280" s="74"/>
+      <c r="J280" s="74"/>
+      <c r="K280" s="74"/>
+      <c r="L280" s="63"/>
+      <c r="M280" s="63"/>
+      <c r="N280" s="63"/>
+      <c r="O280" s="47"/>
+    </row>
+    <row r="281" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C281" s="60"/>
+      <c r="D281" s="63"/>
+      <c r="E281" s="63"/>
+      <c r="F281" s="74"/>
+      <c r="G281" s="74"/>
+      <c r="H281" s="63"/>
+      <c r="I281" s="74"/>
+      <c r="J281" s="74"/>
+      <c r="K281" s="74"/>
+      <c r="L281" s="63"/>
+      <c r="M281" s="63"/>
+      <c r="N281" s="63"/>
+      <c r="O281" s="47"/>
+    </row>
+    <row r="282" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C282" s="60"/>
+      <c r="D282" s="63"/>
+      <c r="E282" s="63"/>
+      <c r="F282" s="74"/>
+      <c r="G282" s="74"/>
+      <c r="H282" s="63"/>
+      <c r="I282" s="74"/>
+      <c r="J282" s="74"/>
+      <c r="K282" s="74"/>
+      <c r="L282" s="63"/>
+      <c r="M282" s="63"/>
+      <c r="N282" s="63"/>
+      <c r="O282" s="47"/>
+    </row>
+    <row r="283" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C283" s="60"/>
+      <c r="D283" s="63"/>
+      <c r="E283" s="63"/>
+      <c r="F283" s="74"/>
+      <c r="G283" s="74"/>
+      <c r="H283" s="63"/>
+      <c r="I283" s="74"/>
+      <c r="J283" s="74"/>
+      <c r="K283" s="74"/>
+      <c r="L283" s="63"/>
+      <c r="M283" s="63"/>
+      <c r="N283" s="63"/>
+      <c r="O283" s="47"/>
+    </row>
+    <row r="284" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C284" s="60"/>
+      <c r="D284" s="63"/>
+      <c r="E284" s="63"/>
+      <c r="F284" s="74"/>
+      <c r="G284" s="74"/>
+      <c r="H284" s="63"/>
+      <c r="I284" s="74"/>
+      <c r="J284" s="74"/>
+      <c r="K284" s="74"/>
+      <c r="L284" s="63"/>
+      <c r="M284" s="63"/>
+      <c r="N284" s="63"/>
+      <c r="O284" s="47"/>
+    </row>
+    <row r="285" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C285" s="60"/>
+      <c r="D285" s="63"/>
+      <c r="E285" s="63"/>
+      <c r="F285" s="74"/>
+      <c r="G285" s="74"/>
+      <c r="H285" s="63"/>
+      <c r="I285" s="74"/>
+      <c r="J285" s="74"/>
+      <c r="K285" s="74"/>
+      <c r="L285" s="63"/>
+      <c r="M285" s="63"/>
+      <c r="N285" s="63"/>
+      <c r="O285" s="47"/>
+    </row>
+    <row r="286" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C286" s="60"/>
+      <c r="D286" s="63"/>
+      <c r="E286" s="63"/>
+      <c r="F286" s="74"/>
+      <c r="G286" s="74"/>
+      <c r="H286" s="63"/>
+      <c r="I286" s="74"/>
+      <c r="J286" s="74"/>
+      <c r="K286" s="74"/>
+      <c r="L286" s="63"/>
+      <c r="M286" s="63"/>
+      <c r="N286" s="63"/>
+      <c r="O286" s="47"/>
+    </row>
+    <row r="287" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C287" s="60"/>
+      <c r="D287" s="63"/>
+      <c r="E287" s="63"/>
+      <c r="F287" s="74"/>
+      <c r="G287" s="74"/>
+      <c r="H287" s="63"/>
+      <c r="I287" s="74"/>
+      <c r="J287" s="74"/>
+      <c r="K287" s="74"/>
+      <c r="L287" s="63"/>
+      <c r="M287" s="63"/>
+      <c r="N287" s="63"/>
+      <c r="O287" s="47"/>
+    </row>
+    <row r="288" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C288" s="60"/>
+      <c r="D288" s="63"/>
+      <c r="E288" s="63"/>
+      <c r="F288" s="74"/>
+      <c r="G288" s="74"/>
+      <c r="H288" s="63"/>
+      <c r="I288" s="74"/>
+      <c r="J288" s="74"/>
+      <c r="K288" s="74"/>
+      <c r="L288" s="63"/>
+      <c r="M288" s="63"/>
+      <c r="N288" s="63"/>
+      <c r="O288" s="47"/>
+    </row>
+    <row r="289" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C289" s="60"/>
+      <c r="D289" s="63"/>
+      <c r="E289" s="63"/>
+      <c r="F289" s="74"/>
+      <c r="G289" s="74"/>
+      <c r="H289" s="63"/>
+      <c r="I289" s="74"/>
+      <c r="J289" s="74"/>
+      <c r="K289" s="74"/>
+      <c r="L289" s="63"/>
+      <c r="M289" s="63"/>
+      <c r="N289" s="63"/>
+      <c r="O289" s="47"/>
+    </row>
+    <row r="290" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C290" s="60"/>
+      <c r="D290" s="63"/>
+      <c r="E290" s="63"/>
+      <c r="F290" s="74"/>
+      <c r="G290" s="74"/>
+      <c r="H290" s="63"/>
+      <c r="I290" s="74"/>
+      <c r="J290" s="74"/>
+      <c r="K290" s="74"/>
+      <c r="L290" s="63"/>
+      <c r="M290" s="63"/>
+      <c r="N290" s="63"/>
+      <c r="O290" s="47"/>
+    </row>
+    <row r="291" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C291" s="60"/>
+      <c r="D291" s="63"/>
+      <c r="E291" s="63"/>
+      <c r="F291" s="74"/>
+      <c r="G291" s="74"/>
+      <c r="H291" s="63"/>
+      <c r="I291" s="74"/>
+      <c r="J291" s="74"/>
+      <c r="K291" s="74"/>
+      <c r="L291" s="63"/>
+      <c r="M291" s="63"/>
+      <c r="N291" s="63"/>
+      <c r="O291" s="47"/>
+    </row>
+    <row r="292" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C292" s="60"/>
+      <c r="D292" s="63"/>
+      <c r="E292" s="63"/>
+      <c r="F292" s="74"/>
+      <c r="G292" s="74"/>
+      <c r="H292" s="63"/>
+      <c r="I292" s="74"/>
+      <c r="J292" s="74"/>
+      <c r="K292" s="74"/>
+      <c r="L292" s="63"/>
+      <c r="M292" s="63"/>
+      <c r="N292" s="63"/>
+      <c r="O292" s="47"/>
+    </row>
+    <row r="293" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C293" s="60"/>
+      <c r="D293" s="63"/>
+      <c r="E293" s="63"/>
+      <c r="F293" s="74"/>
+      <c r="G293" s="74"/>
+      <c r="H293" s="63"/>
+      <c r="I293" s="74"/>
+      <c r="J293" s="74"/>
+      <c r="K293" s="74"/>
+      <c r="L293" s="63"/>
+      <c r="M293" s="63"/>
+      <c r="N293" s="63"/>
+      <c r="O293" s="47"/>
+    </row>
+    <row r="294" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C294" s="60"/>
+      <c r="D294" s="63"/>
+      <c r="E294" s="63"/>
+      <c r="F294" s="74"/>
+      <c r="G294" s="74"/>
+      <c r="H294" s="63"/>
+      <c r="I294" s="74"/>
+      <c r="J294" s="74"/>
+      <c r="K294" s="74"/>
+      <c r="L294" s="63"/>
+      <c r="M294" s="63"/>
+      <c r="N294" s="63"/>
+      <c r="O294" s="47"/>
+    </row>
+    <row r="295" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C295" s="60"/>
+      <c r="D295" s="63"/>
+      <c r="E295" s="63"/>
+      <c r="F295" s="74"/>
+      <c r="G295" s="74"/>
+      <c r="H295" s="63"/>
+      <c r="I295" s="74"/>
+      <c r="J295" s="74"/>
+      <c r="K295" s="74"/>
+      <c r="L295" s="63"/>
+      <c r="M295" s="63"/>
+      <c r="N295" s="63"/>
+      <c r="O295" s="47"/>
+    </row>
+    <row r="296" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C296" s="60"/>
+      <c r="D296" s="63"/>
+      <c r="E296" s="63"/>
+      <c r="F296" s="74"/>
+      <c r="G296" s="74"/>
+      <c r="H296" s="63"/>
+      <c r="I296" s="74"/>
+      <c r="J296" s="74"/>
+      <c r="K296" s="74"/>
+      <c r="L296" s="63"/>
+      <c r="M296" s="63"/>
+      <c r="N296" s="63"/>
+      <c r="O296" s="47"/>
+    </row>
+    <row r="297" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C297" s="60"/>
+      <c r="D297" s="63"/>
+      <c r="E297" s="63"/>
+      <c r="F297" s="74"/>
+      <c r="G297" s="74"/>
+      <c r="H297" s="63"/>
+      <c r="I297" s="74"/>
+      <c r="J297" s="74"/>
+      <c r="K297" s="74"/>
+      <c r="L297" s="63"/>
+      <c r="M297" s="63"/>
+      <c r="N297" s="63"/>
+      <c r="O297" s="47"/>
+    </row>
+    <row r="298" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C298" s="60"/>
+      <c r="D298" s="63"/>
+      <c r="E298" s="63"/>
+      <c r="F298" s="74"/>
+      <c r="G298" s="74"/>
+      <c r="H298" s="63"/>
+      <c r="I298" s="74"/>
+      <c r="J298" s="74"/>
+      <c r="K298" s="74"/>
+      <c r="L298" s="63"/>
+      <c r="M298" s="63"/>
+      <c r="N298" s="63"/>
+      <c r="O298" s="47"/>
+    </row>
+    <row r="299" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C299" s="60"/>
+      <c r="D299" s="63"/>
+      <c r="E299" s="63"/>
+      <c r="F299" s="74"/>
+      <c r="G299" s="74"/>
+      <c r="H299" s="63"/>
+      <c r="I299" s="74"/>
+      <c r="J299" s="74"/>
+      <c r="K299" s="74"/>
+      <c r="L299" s="63"/>
+      <c r="M299" s="63"/>
+      <c r="N299" s="63"/>
+      <c r="O299" s="47"/>
+    </row>
+    <row r="300" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C300" s="60"/>
+      <c r="D300" s="63"/>
+      <c r="E300" s="63"/>
+      <c r="F300" s="74"/>
+      <c r="G300" s="74"/>
+      <c r="H300" s="63"/>
+      <c r="I300" s="74"/>
+      <c r="J300" s="74"/>
+      <c r="K300" s="74"/>
+      <c r="L300" s="63"/>
+      <c r="M300" s="63"/>
+      <c r="N300" s="63"/>
+      <c r="O300" s="47"/>
+    </row>
+    <row r="301" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C301" s="60"/>
+      <c r="D301" s="63"/>
+      <c r="E301" s="63"/>
+      <c r="F301" s="74"/>
+      <c r="G301" s="74"/>
+      <c r="H301" s="63"/>
+      <c r="I301" s="74"/>
+      <c r="J301" s="74"/>
+      <c r="K301" s="74"/>
+      <c r="L301" s="63"/>
+      <c r="M301" s="63"/>
+      <c r="N301" s="63"/>
+      <c r="O301" s="47"/>
+    </row>
+    <row r="302" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C302" s="60"/>
+      <c r="D302" s="63"/>
+      <c r="E302" s="63"/>
+      <c r="F302" s="74"/>
+      <c r="G302" s="74"/>
+      <c r="H302" s="63"/>
+      <c r="I302" s="74"/>
+      <c r="J302" s="74"/>
+      <c r="K302" s="74"/>
+      <c r="L302" s="63"/>
+      <c r="M302" s="63"/>
+      <c r="N302" s="63"/>
+      <c r="O302" s="47"/>
+    </row>
+    <row r="303" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C303" s="60"/>
+      <c r="D303" s="63"/>
+      <c r="E303" s="63"/>
+      <c r="F303" s="74"/>
+      <c r="G303" s="74"/>
+      <c r="H303" s="63"/>
+      <c r="I303" s="74"/>
+      <c r="J303" s="74"/>
+      <c r="K303" s="74"/>
+      <c r="L303" s="63"/>
+      <c r="M303" s="63"/>
+      <c r="N303" s="63"/>
+      <c r="O303" s="47"/>
+    </row>
+    <row r="304" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C304" s="60"/>
+      <c r="D304" s="63"/>
+      <c r="E304" s="63"/>
+      <c r="F304" s="74"/>
+      <c r="G304" s="74"/>
+      <c r="H304" s="63"/>
+      <c r="I304" s="74"/>
+      <c r="J304" s="74"/>
+      <c r="K304" s="74"/>
+      <c r="L304" s="63"/>
+      <c r="M304" s="63"/>
+      <c r="N304" s="63"/>
+      <c r="O304" s="47"/>
+    </row>
+    <row r="305" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C305" s="60"/>
+      <c r="D305" s="63"/>
+      <c r="E305" s="63"/>
+      <c r="F305" s="74"/>
+      <c r="G305" s="74"/>
+      <c r="H305" s="63"/>
+      <c r="I305" s="74"/>
+      <c r="J305" s="74"/>
+      <c r="K305" s="74"/>
+      <c r="L305" s="63"/>
+      <c r="M305" s="63"/>
+      <c r="N305" s="63"/>
+      <c r="O305" s="47"/>
+    </row>
+    <row r="306" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C306" s="60"/>
+      <c r="D306" s="63"/>
+      <c r="E306" s="63"/>
+      <c r="F306" s="74"/>
+      <c r="G306" s="74"/>
+      <c r="H306" s="63"/>
+      <c r="I306" s="74"/>
+      <c r="J306" s="74"/>
+      <c r="K306" s="74"/>
+      <c r="L306" s="63"/>
+      <c r="M306" s="63"/>
+      <c r="N306" s="63"/>
+      <c r="O306" s="47"/>
+    </row>
+    <row r="307" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C307" s="60"/>
+      <c r="D307" s="63"/>
+      <c r="E307" s="63"/>
+      <c r="F307" s="74"/>
+      <c r="G307" s="74"/>
+      <c r="H307" s="63"/>
+      <c r="I307" s="74"/>
+      <c r="J307" s="74"/>
+      <c r="K307" s="74"/>
+      <c r="L307" s="63"/>
+      <c r="M307" s="63"/>
+      <c r="N307" s="63"/>
+      <c r="O307" s="47"/>
+    </row>
+    <row r="308" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C308" s="60"/>
+      <c r="D308" s="63"/>
+      <c r="E308" s="63"/>
+      <c r="F308" s="74"/>
+      <c r="G308" s="74"/>
+      <c r="H308" s="63"/>
+      <c r="I308" s="74"/>
+      <c r="J308" s="74"/>
+      <c r="K308" s="74"/>
+      <c r="L308" s="63"/>
+      <c r="M308" s="63"/>
+      <c r="N308" s="63"/>
+      <c r="O308" s="47"/>
+    </row>
+    <row r="309" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C309" s="60"/>
+      <c r="D309" s="63"/>
+      <c r="E309" s="63"/>
+      <c r="F309" s="74"/>
+      <c r="G309" s="74"/>
+      <c r="H309" s="63"/>
+      <c r="I309" s="74"/>
+      <c r="J309" s="74"/>
+      <c r="K309" s="74"/>
+      <c r="L309" s="63"/>
+      <c r="M309" s="63"/>
+      <c r="N309" s="63"/>
+      <c r="O309" s="47"/>
+    </row>
+    <row r="310" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C310" s="60"/>
+      <c r="D310" s="63"/>
+      <c r="E310" s="63"/>
+      <c r="F310" s="74"/>
+      <c r="G310" s="74"/>
+      <c r="H310" s="63"/>
+      <c r="I310" s="74"/>
+      <c r="J310" s="74"/>
+      <c r="K310" s="74"/>
+      <c r="L310" s="63"/>
+      <c r="M310" s="63"/>
+      <c r="N310" s="63"/>
+      <c r="O310" s="47"/>
+    </row>
+    <row r="311" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C311" s="60"/>
+      <c r="D311" s="63"/>
+      <c r="E311" s="63"/>
+      <c r="F311" s="74"/>
+      <c r="G311" s="74"/>
+      <c r="H311" s="63"/>
+      <c r="I311" s="74"/>
+      <c r="J311" s="74"/>
+      <c r="K311" s="74"/>
+      <c r="L311" s="63"/>
+      <c r="M311" s="63"/>
+      <c r="N311" s="63"/>
+      <c r="O311" s="47"/>
+    </row>
+    <row r="312" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C312" s="60"/>
+      <c r="D312" s="63"/>
+      <c r="E312" s="63"/>
+      <c r="F312" s="74"/>
+      <c r="G312" s="74"/>
+      <c r="H312" s="63"/>
+      <c r="I312" s="74"/>
+      <c r="J312" s="74"/>
+      <c r="K312" s="74"/>
+      <c r="L312" s="63"/>
+      <c r="M312" s="63"/>
+      <c r="N312" s="63"/>
+      <c r="O312" s="47"/>
+    </row>
+    <row r="313" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C313" s="60"/>
+      <c r="D313" s="63"/>
+      <c r="E313" s="63"/>
+      <c r="F313" s="74"/>
+      <c r="G313" s="74"/>
+      <c r="H313" s="63"/>
+      <c r="I313" s="74"/>
+      <c r="J313" s="74"/>
+      <c r="K313" s="74"/>
+      <c r="L313" s="63"/>
+      <c r="M313" s="63"/>
+      <c r="N313" s="63"/>
+      <c r="O313" s="47"/>
+    </row>
+    <row r="314" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C314" s="60"/>
+      <c r="D314" s="63"/>
+      <c r="E314" s="63"/>
+      <c r="F314" s="74"/>
+      <c r="G314" s="74"/>
+      <c r="H314" s="63"/>
+      <c r="I314" s="74"/>
+      <c r="J314" s="74"/>
+      <c r="K314" s="74"/>
+      <c r="L314" s="63"/>
+      <c r="M314" s="63"/>
+      <c r="N314" s="63"/>
+      <c r="O314" s="47"/>
+    </row>
+    <row r="315" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C315" s="60"/>
+      <c r="D315" s="63"/>
+      <c r="E315" s="63"/>
+      <c r="F315" s="74"/>
+      <c r="G315" s="74"/>
+      <c r="H315" s="63"/>
+      <c r="I315" s="74"/>
+      <c r="J315" s="74"/>
+      <c r="K315" s="74"/>
+      <c r="L315" s="63"/>
+      <c r="M315" s="63"/>
+      <c r="N315" s="63"/>
+      <c r="O315" s="47"/>
+    </row>
+    <row r="316" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C316" s="60"/>
+      <c r="D316" s="63"/>
+      <c r="E316" s="63"/>
+      <c r="F316" s="74"/>
+      <c r="G316" s="74"/>
+      <c r="H316" s="63"/>
+      <c r="I316" s="74"/>
+      <c r="J316" s="74"/>
+      <c r="K316" s="74"/>
+      <c r="L316" s="63"/>
+      <c r="M316" s="63"/>
+      <c r="N316" s="63"/>
+      <c r="O316" s="47"/>
+    </row>
+    <row r="317" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C317" s="60"/>
+      <c r="D317" s="63"/>
+      <c r="E317" s="63"/>
+      <c r="F317" s="74"/>
+      <c r="G317" s="74"/>
+      <c r="H317" s="63"/>
+      <c r="I317" s="74"/>
+      <c r="J317" s="74"/>
+      <c r="K317" s="74"/>
+      <c r="L317" s="63"/>
+      <c r="M317" s="63"/>
+      <c r="N317" s="63"/>
+      <c r="O317" s="47"/>
+    </row>
+    <row r="318" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C318" s="60"/>
+      <c r="D318" s="63"/>
+      <c r="E318" s="63"/>
+      <c r="F318" s="74"/>
+      <c r="G318" s="74"/>
+      <c r="H318" s="63"/>
+      <c r="I318" s="74"/>
+      <c r="J318" s="74"/>
+      <c r="K318" s="74"/>
+      <c r="L318" s="63"/>
+      <c r="M318" s="63"/>
+      <c r="N318" s="63"/>
+      <c r="O318" s="47"/>
+    </row>
+    <row r="319" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C319" s="60"/>
+      <c r="D319" s="63"/>
+      <c r="E319" s="63"/>
+      <c r="F319" s="74"/>
+      <c r="G319" s="74"/>
+      <c r="H319" s="63"/>
+      <c r="I319" s="74"/>
+      <c r="J319" s="74"/>
+      <c r="K319" s="74"/>
+      <c r="L319" s="63"/>
+      <c r="M319" s="63"/>
+      <c r="N319" s="63"/>
+      <c r="O319" s="47"/>
+    </row>
+    <row r="320" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C320" s="60"/>
+      <c r="D320" s="63"/>
+      <c r="E320" s="63"/>
+      <c r="F320" s="74"/>
+      <c r="G320" s="74"/>
+      <c r="H320" s="63"/>
+      <c r="I320" s="74"/>
+      <c r="J320" s="74"/>
+      <c r="K320" s="74"/>
+      <c r="L320" s="63"/>
+      <c r="M320" s="63"/>
+      <c r="N320" s="63"/>
+      <c r="O320" s="47"/>
+    </row>
+    <row r="321" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C321" s="60"/>
+      <c r="D321" s="63"/>
+      <c r="E321" s="63"/>
+      <c r="F321" s="74"/>
+      <c r="G321" s="74"/>
+      <c r="H321" s="63"/>
+      <c r="I321" s="74"/>
+      <c r="J321" s="74"/>
+      <c r="K321" s="74"/>
+      <c r="L321" s="63"/>
+      <c r="M321" s="63"/>
+      <c r="N321" s="63"/>
+      <c r="O321" s="47"/>
+    </row>
+    <row r="322" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C322" s="60"/>
+      <c r="D322" s="63"/>
+      <c r="E322" s="63"/>
+      <c r="F322" s="74"/>
+      <c r="G322" s="74"/>
+      <c r="H322" s="63"/>
+      <c r="I322" s="74"/>
+      <c r="J322" s="74"/>
+      <c r="K322" s="74"/>
+      <c r="L322" s="63"/>
+      <c r="M322" s="63"/>
+      <c r="N322" s="63"/>
+      <c r="O322" s="47"/>
+    </row>
+    <row r="323" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C323" s="60"/>
+      <c r="D323" s="63"/>
+      <c r="E323" s="63"/>
+      <c r="F323" s="74"/>
+      <c r="G323" s="74"/>
+      <c r="H323" s="63"/>
+      <c r="I323" s="74"/>
+      <c r="J323" s="74"/>
+      <c r="K323" s="74"/>
+      <c r="L323" s="63"/>
+      <c r="M323" s="63"/>
+      <c r="N323" s="63"/>
+      <c r="O323" s="47"/>
+    </row>
+    <row r="324" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C324" s="60"/>
+      <c r="D324" s="63"/>
+      <c r="E324" s="63"/>
+      <c r="F324" s="74"/>
+      <c r="G324" s="74"/>
+      <c r="H324" s="63"/>
+      <c r="I324" s="74"/>
+      <c r="J324" s="74"/>
+      <c r="K324" s="74"/>
+      <c r="L324" s="63"/>
+      <c r="M324" s="63"/>
+      <c r="N324" s="63"/>
+      <c r="O324" s="47"/>
+    </row>
+    <row r="325" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C325" s="60"/>
+      <c r="D325" s="63"/>
+      <c r="E325" s="63"/>
+      <c r="F325" s="74"/>
+      <c r="G325" s="74"/>
+      <c r="H325" s="63"/>
+      <c r="I325" s="74"/>
+      <c r="J325" s="74"/>
+      <c r="K325" s="74"/>
+      <c r="L325" s="63"/>
+      <c r="M325" s="63"/>
+      <c r="N325" s="63"/>
+      <c r="O325" s="47"/>
+    </row>
+    <row r="326" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C326" s="60"/>
+      <c r="D326" s="63"/>
+      <c r="E326" s="63"/>
+      <c r="F326" s="74"/>
+      <c r="G326" s="74"/>
+      <c r="H326" s="63"/>
+      <c r="I326" s="74"/>
+      <c r="J326" s="74"/>
+      <c r="K326" s="74"/>
+      <c r="L326" s="63"/>
+      <c r="M326" s="63"/>
+      <c r="N326" s="63"/>
+      <c r="O326" s="47"/>
+    </row>
+    <row r="327" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C327" s="60"/>
+      <c r="D327" s="63"/>
+      <c r="E327" s="63"/>
+      <c r="F327" s="74"/>
+      <c r="G327" s="74"/>
+      <c r="H327" s="63"/>
+      <c r="I327" s="74"/>
+      <c r="J327" s="74"/>
+      <c r="K327" s="74"/>
+      <c r="L327" s="63"/>
+      <c r="M327" s="63"/>
+      <c r="N327" s="63"/>
+      <c r="O327" s="47"/>
+    </row>
+    <row r="328" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C328" s="60"/>
+      <c r="D328" s="63"/>
+      <c r="E328" s="63"/>
+      <c r="F328" s="74"/>
+      <c r="G328" s="74"/>
+      <c r="H328" s="63"/>
+      <c r="I328" s="74"/>
+      <c r="J328" s="74"/>
+      <c r="K328" s="74"/>
+      <c r="L328" s="63"/>
+      <c r="M328" s="63"/>
+      <c r="N328" s="63"/>
+      <c r="O328" s="47"/>
+    </row>
+    <row r="329" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C329" s="60"/>
+      <c r="D329" s="63"/>
+      <c r="E329" s="63"/>
+      <c r="F329" s="74"/>
+      <c r="G329" s="74"/>
+      <c r="H329" s="63"/>
+      <c r="I329" s="74"/>
+      <c r="J329" s="74"/>
+      <c r="K329" s="74"/>
+      <c r="L329" s="63"/>
+      <c r="M329" s="63"/>
+      <c r="N329" s="63"/>
+      <c r="O329" s="47"/>
+    </row>
+    <row r="330" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C330" s="60"/>
+      <c r="D330" s="63"/>
+      <c r="E330" s="63"/>
+      <c r="F330" s="74"/>
+      <c r="G330" s="74"/>
+      <c r="H330" s="63"/>
+      <c r="I330" s="74"/>
+      <c r="J330" s="74"/>
+      <c r="K330" s="74"/>
+      <c r="L330" s="63"/>
+      <c r="M330" s="63"/>
+      <c r="N330" s="63"/>
+      <c r="O330" s="47"/>
+    </row>
+    <row r="331" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C331" s="60"/>
+      <c r="D331" s="63"/>
+      <c r="E331" s="63"/>
+      <c r="F331" s="74"/>
+      <c r="G331" s="74"/>
+      <c r="H331" s="63"/>
+      <c r="I331" s="74"/>
+      <c r="J331" s="74"/>
+      <c r="K331" s="74"/>
+      <c r="L331" s="63"/>
+      <c r="M331" s="63"/>
+      <c r="N331" s="63"/>
+      <c r="O331" s="47"/>
+    </row>
+    <row r="332" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C332" s="60"/>
+      <c r="D332" s="63"/>
+      <c r="E332" s="63"/>
+      <c r="F332" s="74"/>
+      <c r="G332" s="74"/>
+      <c r="H332" s="63"/>
+      <c r="I332" s="74"/>
+      <c r="J332" s="74"/>
+      <c r="K332" s="74"/>
+      <c r="L332" s="63"/>
+      <c r="M332" s="63"/>
+      <c r="N332" s="63"/>
+      <c r="O332" s="47"/>
+    </row>
+    <row r="333" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C333" s="60"/>
+      <c r="D333" s="63"/>
+      <c r="E333" s="63"/>
+      <c r="F333" s="74"/>
+      <c r="G333" s="74"/>
+      <c r="H333" s="63"/>
+      <c r="I333" s="74"/>
+      <c r="J333" s="74"/>
+      <c r="K333" s="74"/>
+      <c r="L333" s="63"/>
+      <c r="M333" s="63"/>
+      <c r="N333" s="63"/>
+      <c r="O333" s="47"/>
+    </row>
+    <row r="334" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C334" s="60"/>
+      <c r="D334" s="63"/>
+      <c r="E334" s="63"/>
+      <c r="F334" s="74"/>
+      <c r="G334" s="74"/>
+      <c r="H334" s="63"/>
+      <c r="I334" s="74"/>
+      <c r="J334" s="74"/>
+      <c r="K334" s="74"/>
+      <c r="L334" s="63"/>
+      <c r="M334" s="63"/>
+      <c r="N334" s="63"/>
+      <c r="O334" s="47"/>
+    </row>
+    <row r="335" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C335" s="60"/>
+      <c r="D335" s="63"/>
+      <c r="E335" s="63"/>
+      <c r="F335" s="74"/>
+      <c r="G335" s="74"/>
+      <c r="H335" s="63"/>
+      <c r="I335" s="74"/>
+      <c r="J335" s="74"/>
+      <c r="K335" s="74"/>
+      <c r="L335" s="63"/>
+      <c r="M335" s="63"/>
+      <c r="N335" s="63"/>
+      <c r="O335" s="47"/>
+    </row>
+    <row r="336" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C336" s="60"/>
+      <c r="D336" s="63"/>
+      <c r="E336" s="63"/>
+      <c r="F336" s="74"/>
+      <c r="G336" s="74"/>
+      <c r="H336" s="63"/>
+      <c r="I336" s="74"/>
+      <c r="J336" s="74"/>
+      <c r="K336" s="74"/>
+      <c r="L336" s="63"/>
+      <c r="M336" s="63"/>
+      <c r="N336" s="63"/>
+      <c r="O336" s="47"/>
+    </row>
+    <row r="337" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C337" s="60"/>
+      <c r="D337" s="63"/>
+      <c r="E337" s="63"/>
+      <c r="F337" s="74"/>
+      <c r="G337" s="74"/>
+      <c r="H337" s="63"/>
+      <c r="I337" s="74"/>
+      <c r="J337" s="74"/>
+      <c r="K337" s="74"/>
+      <c r="L337" s="63"/>
+      <c r="M337" s="63"/>
+      <c r="N337" s="63"/>
+      <c r="O337" s="47"/>
+    </row>
+    <row r="338" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C338" s="60"/>
+      <c r="D338" s="63"/>
+      <c r="E338" s="63"/>
+      <c r="F338" s="74"/>
+      <c r="G338" s="74"/>
+      <c r="H338" s="63"/>
+      <c r="I338" s="74"/>
+      <c r="J338" s="74"/>
+      <c r="K338" s="74"/>
+      <c r="L338" s="63"/>
+      <c r="M338" s="63"/>
+      <c r="N338" s="63"/>
+      <c r="O338" s="47"/>
+    </row>
+    <row r="339" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C339" s="60"/>
+      <c r="D339" s="63"/>
+      <c r="E339" s="63"/>
+      <c r="F339" s="74"/>
+      <c r="G339" s="74"/>
+      <c r="H339" s="63"/>
+      <c r="I339" s="74"/>
+      <c r="J339" s="74"/>
+      <c r="K339" s="74"/>
+      <c r="L339" s="63"/>
+      <c r="M339" s="63"/>
+      <c r="N339" s="63"/>
+      <c r="O339" s="47"/>
+    </row>
+    <row r="340" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C340" s="60"/>
+      <c r="D340" s="63"/>
+      <c r="E340" s="63"/>
+      <c r="F340" s="74"/>
+      <c r="G340" s="74"/>
+      <c r="H340" s="63"/>
+      <c r="I340" s="74"/>
+      <c r="J340" s="74"/>
+      <c r="K340" s="74"/>
+      <c r="L340" s="63"/>
+      <c r="M340" s="63"/>
+      <c r="N340" s="63"/>
+      <c r="O340" s="47"/>
+    </row>
+    <row r="341" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C341" s="60"/>
+      <c r="D341" s="63"/>
+      <c r="E341" s="63"/>
+      <c r="F341" s="74"/>
+      <c r="G341" s="74"/>
+      <c r="H341" s="63"/>
+      <c r="I341" s="74"/>
+      <c r="J341" s="74"/>
+      <c r="K341" s="74"/>
+      <c r="L341" s="63"/>
+      <c r="M341" s="63"/>
+      <c r="N341" s="63"/>
+      <c r="O341" s="47"/>
+    </row>
+    <row r="342" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C342" s="60"/>
+      <c r="D342" s="63"/>
+      <c r="E342" s="63"/>
+      <c r="F342" s="74"/>
+      <c r="G342" s="74"/>
+      <c r="H342" s="63"/>
+      <c r="I342" s="74"/>
+      <c r="J342" s="74"/>
+      <c r="K342" s="74"/>
+      <c r="L342" s="63"/>
+      <c r="M342" s="63"/>
+      <c r="N342" s="63"/>
+      <c r="O342" s="47"/>
+    </row>
+    <row r="343" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C343" s="60"/>
+      <c r="D343" s="63"/>
+      <c r="E343" s="63"/>
+      <c r="F343" s="74"/>
+      <c r="G343" s="74"/>
+      <c r="H343" s="63"/>
+      <c r="I343" s="74"/>
+      <c r="J343" s="74"/>
+      <c r="K343" s="74"/>
+      <c r="L343" s="63"/>
+      <c r="M343" s="63"/>
+      <c r="N343" s="63"/>
+      <c r="O343" s="47"/>
+    </row>
+    <row r="344" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C344" s="60"/>
+      <c r="D344" s="63"/>
+      <c r="E344" s="63"/>
+      <c r="F344" s="74"/>
+      <c r="G344" s="74"/>
+      <c r="H344" s="63"/>
+      <c r="I344" s="74"/>
+      <c r="J344" s="74"/>
+      <c r="K344" s="74"/>
+      <c r="L344" s="63"/>
+      <c r="M344" s="63"/>
+      <c r="N344" s="63"/>
+      <c r="O344" s="47"/>
+    </row>
+    <row r="345" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C345" s="60"/>
+      <c r="D345" s="63"/>
+      <c r="E345" s="63"/>
+      <c r="F345" s="74"/>
+      <c r="G345" s="74"/>
+      <c r="H345" s="63"/>
+      <c r="I345" s="74"/>
+      <c r="J345" s="74"/>
+      <c r="K345" s="74"/>
+      <c r="L345" s="63"/>
+      <c r="M345" s="63"/>
+      <c r="N345" s="63"/>
+      <c r="O345" s="47"/>
+    </row>
+    <row r="346" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C346" s="60"/>
+      <c r="D346" s="63"/>
+      <c r="E346" s="63"/>
+      <c r="F346" s="74"/>
+      <c r="G346" s="74"/>
+      <c r="H346" s="63"/>
+      <c r="I346" s="74"/>
+      <c r="J346" s="74"/>
+      <c r="K346" s="74"/>
+      <c r="L346" s="63"/>
+      <c r="M346" s="63"/>
+      <c r="N346" s="63"/>
+      <c r="O346" s="47"/>
+    </row>
+    <row r="347" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C347" s="60"/>
+      <c r="D347" s="63"/>
+      <c r="E347" s="63"/>
+      <c r="F347" s="74"/>
+      <c r="G347" s="74"/>
+      <c r="H347" s="63"/>
+      <c r="I347" s="74"/>
+      <c r="J347" s="74"/>
+      <c r="K347" s="74"/>
+      <c r="L347" s="63"/>
+      <c r="M347" s="63"/>
+      <c r="N347" s="63"/>
+      <c r="O347" s="47"/>
+    </row>
+    <row r="348" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C348" s="60"/>
+      <c r="D348" s="63"/>
+      <c r="E348" s="63"/>
+      <c r="F348" s="74"/>
+      <c r="G348" s="74"/>
+      <c r="H348" s="63"/>
+      <c r="I348" s="74"/>
+      <c r="J348" s="74"/>
+      <c r="K348" s="74"/>
+      <c r="L348" s="63"/>
+      <c r="M348" s="63"/>
+      <c r="N348" s="63"/>
+      <c r="O348" s="47"/>
+    </row>
+    <row r="349" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C349" s="60"/>
+      <c r="D349" s="63"/>
+      <c r="E349" s="63"/>
+      <c r="F349" s="74"/>
+      <c r="G349" s="74"/>
+      <c r="H349" s="63"/>
+      <c r="I349" s="74"/>
+      <c r="J349" s="74"/>
+      <c r="K349" s="74"/>
+      <c r="L349" s="63"/>
+      <c r="M349" s="63"/>
+      <c r="N349" s="63"/>
+      <c r="O349" s="47"/>
+    </row>
+    <row r="350" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C350" s="60"/>
+      <c r="D350" s="63"/>
+      <c r="E350" s="63"/>
+      <c r="F350" s="74"/>
+      <c r="G350" s="74"/>
+      <c r="H350" s="63"/>
+      <c r="I350" s="74"/>
+      <c r="J350" s="74"/>
+      <c r="K350" s="74"/>
+      <c r="L350" s="63"/>
+      <c r="M350" s="63"/>
+      <c r="N350" s="63"/>
+      <c r="O350" s="47"/>
+    </row>
+    <row r="351" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C351" s="60"/>
+      <c r="D351" s="63"/>
+      <c r="E351" s="63"/>
+      <c r="F351" s="74"/>
+      <c r="G351" s="74"/>
+      <c r="H351" s="63"/>
+      <c r="I351" s="74"/>
+      <c r="J351" s="74"/>
+      <c r="K351" s="74"/>
+      <c r="L351" s="63"/>
+      <c r="M351" s="63"/>
+      <c r="N351" s="63"/>
+      <c r="O351" s="47"/>
+    </row>
+    <row r="352" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C352" s="60"/>
+      <c r="D352" s="63"/>
+      <c r="E352" s="63"/>
+      <c r="F352" s="74"/>
+      <c r="G352" s="74"/>
+      <c r="H352" s="63"/>
+      <c r="I352" s="74"/>
+      <c r="J352" s="74"/>
+      <c r="K352" s="74"/>
+      <c r="L352" s="63"/>
+      <c r="M352" s="63"/>
+      <c r="N352" s="63"/>
+      <c r="O352" s="47"/>
+    </row>
+    <row r="353" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C353" s="60"/>
+      <c r="D353" s="63"/>
+      <c r="E353" s="63"/>
+      <c r="F353" s="74"/>
+      <c r="G353" s="74"/>
+      <c r="H353" s="63"/>
+      <c r="I353" s="74"/>
+      <c r="J353" s="74"/>
+      <c r="K353" s="74"/>
+      <c r="L353" s="63"/>
+      <c r="M353" s="63"/>
+      <c r="N353" s="63"/>
+      <c r="O353" s="47"/>
+    </row>
+    <row r="354" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C354" s="60"/>
+      <c r="D354" s="63"/>
+      <c r="E354" s="63"/>
+      <c r="F354" s="74"/>
+      <c r="G354" s="74"/>
+      <c r="H354" s="63"/>
+      <c r="I354" s="74"/>
+      <c r="J354" s="74"/>
+      <c r="K354" s="74"/>
+      <c r="L354" s="63"/>
+      <c r="M354" s="63"/>
+      <c r="N354" s="63"/>
+      <c r="O354" s="47"/>
+    </row>
+    <row r="355" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C355" s="60"/>
+      <c r="D355" s="63"/>
+      <c r="E355" s="63"/>
+      <c r="F355" s="74"/>
+      <c r="G355" s="74"/>
+      <c r="H355" s="63"/>
+      <c r="I355" s="74"/>
+      <c r="J355" s="74"/>
+      <c r="K355" s="74"/>
+      <c r="L355" s="63"/>
+      <c r="M355" s="63"/>
+      <c r="N355" s="63"/>
+      <c r="O355" s="47"/>
+    </row>
+    <row r="356" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C356" s="60"/>
+      <c r="D356" s="63"/>
+      <c r="E356" s="63"/>
+      <c r="F356" s="74"/>
+      <c r="G356" s="74"/>
+      <c r="H356" s="63"/>
+      <c r="I356" s="74"/>
+      <c r="J356" s="74"/>
+      <c r="K356" s="74"/>
+      <c r="L356" s="63"/>
+      <c r="M356" s="63"/>
+      <c r="N356" s="63"/>
+      <c r="O356" s="47"/>
+    </row>
+    <row r="357" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C357" s="60"/>
+      <c r="D357" s="63"/>
+      <c r="E357" s="63"/>
+      <c r="F357" s="74"/>
+      <c r="G357" s="74"/>
+      <c r="H357" s="63"/>
+      <c r="I357" s="74"/>
+      <c r="J357" s="74"/>
+      <c r="K357" s="74"/>
+      <c r="L357" s="63"/>
+      <c r="M357" s="63"/>
+      <c r="N357" s="63"/>
+      <c r="O357" s="47"/>
+    </row>
+    <row r="358" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C358" s="60"/>
+      <c r="D358" s="63"/>
+      <c r="E358" s="63"/>
+      <c r="F358" s="74"/>
+      <c r="G358" s="74"/>
+      <c r="H358" s="63"/>
+      <c r="I358" s="74"/>
+      <c r="J358" s="74"/>
+      <c r="K358" s="74"/>
+      <c r="L358" s="63"/>
+      <c r="M358" s="63"/>
+      <c r="N358" s="63"/>
+      <c r="O358" s="47"/>
+    </row>
+    <row r="359" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C359" s="60"/>
+      <c r="D359" s="63"/>
+      <c r="E359" s="63"/>
+      <c r="F359" s="74"/>
+      <c r="G359" s="74"/>
+      <c r="H359" s="63"/>
+      <c r="I359" s="74"/>
+      <c r="J359" s="74"/>
+      <c r="K359" s="74"/>
+      <c r="L359" s="63"/>
+      <c r="M359" s="63"/>
+      <c r="N359" s="63"/>
+      <c r="O359" s="47"/>
+    </row>
+    <row r="360" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C360" s="60"/>
+      <c r="D360" s="63"/>
+      <c r="E360" s="63"/>
+      <c r="F360" s="74"/>
+      <c r="G360" s="74"/>
+      <c r="H360" s="63"/>
+      <c r="I360" s="74"/>
+      <c r="J360" s="74"/>
+      <c r="K360" s="74"/>
+      <c r="L360" s="63"/>
+      <c r="M360" s="63"/>
+      <c r="N360" s="63"/>
+      <c r="O360" s="47"/>
+    </row>
+    <row r="361" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C361" s="60"/>
+      <c r="D361" s="63"/>
+      <c r="E361" s="63"/>
+      <c r="F361" s="74"/>
+      <c r="G361" s="74"/>
+      <c r="H361" s="63"/>
+      <c r="I361" s="74"/>
+      <c r="J361" s="74"/>
+      <c r="K361" s="74"/>
+      <c r="L361" s="63"/>
+      <c r="M361" s="63"/>
+      <c r="N361" s="63"/>
+      <c r="O361" s="47"/>
+    </row>
+    <row r="362" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C362" s="60"/>
+      <c r="D362" s="63"/>
+      <c r="E362" s="63"/>
+      <c r="F362" s="74"/>
+      <c r="G362" s="74"/>
+      <c r="H362" s="63"/>
+      <c r="I362" s="74"/>
+      <c r="J362" s="74"/>
+      <c r="K362" s="74"/>
+      <c r="L362" s="63"/>
+      <c r="M362" s="63"/>
+      <c r="N362" s="63"/>
+      <c r="O362" s="47"/>
+    </row>
+    <row r="363" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C363" s="60"/>
+      <c r="D363" s="63"/>
+      <c r="E363" s="63"/>
+      <c r="F363" s="74"/>
+      <c r="G363" s="74"/>
+      <c r="H363" s="63"/>
+      <c r="I363" s="74"/>
+      <c r="J363" s="74"/>
+      <c r="K363" s="74"/>
+      <c r="L363" s="63"/>
+      <c r="M363" s="63"/>
+      <c r="N363" s="63"/>
+      <c r="O363" s="47"/>
+    </row>
+    <row r="364" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C364" s="60"/>
+      <c r="D364" s="63"/>
+      <c r="E364" s="63"/>
+      <c r="F364" s="74"/>
+      <c r="G364" s="74"/>
+      <c r="H364" s="63"/>
+      <c r="I364" s="74"/>
+      <c r="J364" s="74"/>
+      <c r="K364" s="74"/>
+      <c r="L364" s="63"/>
+      <c r="M364" s="63"/>
+      <c r="N364" s="63"/>
+      <c r="O364" s="47"/>
+    </row>
+    <row r="365" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C365" s="60"/>
+      <c r="D365" s="63"/>
+      <c r="E365" s="63"/>
+      <c r="F365" s="74"/>
+      <c r="G365" s="74"/>
+      <c r="H365" s="63"/>
+      <c r="I365" s="74"/>
+      <c r="J365" s="74"/>
+      <c r="K365" s="74"/>
+      <c r="L365" s="63"/>
+      <c r="M365" s="63"/>
+      <c r="N365" s="63"/>
+      <c r="O365" s="47"/>
+    </row>
+    <row r="366" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C366" s="60"/>
+      <c r="D366" s="63"/>
+      <c r="E366" s="63"/>
+      <c r="F366" s="74"/>
+      <c r="G366" s="74"/>
+      <c r="H366" s="63"/>
+      <c r="I366" s="74"/>
+      <c r="J366" s="74"/>
+      <c r="K366" s="74"/>
+      <c r="L366" s="63"/>
+      <c r="M366" s="63"/>
+      <c r="N366" s="63"/>
+      <c r="O366" s="47"/>
+    </row>
+    <row r="367" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C367" s="60"/>
+      <c r="D367" s="63"/>
+      <c r="E367" s="63"/>
+      <c r="F367" s="74"/>
+      <c r="G367" s="74"/>
+      <c r="H367" s="63"/>
+      <c r="I367" s="74"/>
+      <c r="J367" s="74"/>
+      <c r="K367" s="74"/>
+      <c r="L367" s="63"/>
+      <c r="M367" s="63"/>
+      <c r="N367" s="63"/>
+      <c r="O367" s="47"/>
+    </row>
+    <row r="368" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C368" s="60"/>
+      <c r="D368" s="63"/>
+      <c r="E368" s="63"/>
+      <c r="F368" s="74"/>
+      <c r="G368" s="74"/>
+      <c r="H368" s="63"/>
+      <c r="I368" s="74"/>
+      <c r="J368" s="74"/>
+      <c r="K368" s="74"/>
+      <c r="L368" s="63"/>
+      <c r="M368" s="63"/>
+      <c r="N368" s="63"/>
+      <c r="O368" s="47"/>
+    </row>
+    <row r="369" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C369" s="60"/>
+      <c r="D369" s="63"/>
+      <c r="E369" s="63"/>
+      <c r="F369" s="74"/>
+      <c r="G369" s="74"/>
+      <c r="H369" s="63"/>
+      <c r="I369" s="74"/>
+      <c r="J369" s="74"/>
+      <c r="K369" s="74"/>
+      <c r="L369" s="63"/>
+      <c r="M369" s="63"/>
+      <c r="N369" s="63"/>
+      <c r="O369" s="47"/>
+    </row>
+    <row r="370" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C370" s="60"/>
+      <c r="D370" s="63"/>
+      <c r="E370" s="63"/>
+      <c r="F370" s="74"/>
+      <c r="G370" s="74"/>
+      <c r="H370" s="63"/>
+      <c r="I370" s="74"/>
+      <c r="J370" s="74"/>
+      <c r="K370" s="74"/>
+      <c r="L370" s="63"/>
+      <c r="M370" s="63"/>
+      <c r="N370" s="63"/>
+      <c r="O370" s="47"/>
+    </row>
+    <row r="371" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C371" s="60"/>
+      <c r="D371" s="63"/>
+      <c r="E371" s="63"/>
+      <c r="F371" s="74"/>
+      <c r="G371" s="74"/>
+      <c r="H371" s="63"/>
+      <c r="I371" s="74"/>
+      <c r="J371" s="74"/>
+      <c r="K371" s="74"/>
+      <c r="L371" s="63"/>
+      <c r="M371" s="63"/>
+      <c r="N371" s="63"/>
+      <c r="O371" s="47"/>
+    </row>
+    <row r="372" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C372" s="60"/>
+      <c r="D372" s="63"/>
+      <c r="E372" s="63"/>
+      <c r="F372" s="74"/>
+      <c r="G372" s="74"/>
+      <c r="H372" s="63"/>
+      <c r="I372" s="74"/>
+      <c r="J372" s="74"/>
+      <c r="K372" s="74"/>
+      <c r="L372" s="63"/>
+      <c r="M372" s="63"/>
+      <c r="N372" s="63"/>
+      <c r="O372" s="47"/>
+    </row>
+    <row r="373" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C373" s="60"/>
+      <c r="D373" s="63"/>
+      <c r="E373" s="63"/>
+      <c r="F373" s="74"/>
+      <c r="G373" s="74"/>
+      <c r="H373" s="63"/>
+      <c r="I373" s="74"/>
+      <c r="J373" s="74"/>
+      <c r="K373" s="74"/>
+      <c r="L373" s="63"/>
+      <c r="M373" s="63"/>
+      <c r="N373" s="63"/>
+      <c r="O373" s="47"/>
+    </row>
+    <row r="374" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C374" s="60"/>
+      <c r="D374" s="63"/>
+      <c r="E374" s="63"/>
+      <c r="F374" s="74"/>
+      <c r="G374" s="74"/>
+      <c r="H374" s="63"/>
+      <c r="I374" s="74"/>
+      <c r="J374" s="74"/>
+      <c r="K374" s="74"/>
+      <c r="L374" s="63"/>
+      <c r="M374" s="63"/>
+      <c r="N374" s="63"/>
+      <c r="O374" s="47"/>
+    </row>
+    <row r="375" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C375" s="60"/>
+      <c r="D375" s="63"/>
+      <c r="E375" s="63"/>
+      <c r="F375" s="74"/>
+      <c r="G375" s="74"/>
+      <c r="H375" s="63"/>
+      <c r="I375" s="74"/>
+      <c r="J375" s="74"/>
+      <c r="K375" s="74"/>
+      <c r="L375" s="63"/>
+      <c r="M375" s="63"/>
+      <c r="N375" s="63"/>
+      <c r="O375" s="47"/>
+    </row>
+    <row r="376" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C376" s="60"/>
+      <c r="D376" s="63"/>
+      <c r="E376" s="63"/>
+      <c r="F376" s="74"/>
+      <c r="G376" s="74"/>
+      <c r="H376" s="63"/>
+      <c r="I376" s="74"/>
+      <c r="J376" s="74"/>
+      <c r="K376" s="74"/>
+      <c r="L376" s="63"/>
+      <c r="M376" s="63"/>
+      <c r="N376" s="63"/>
+      <c r="O376" s="47"/>
+    </row>
+    <row r="377" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C377" s="60"/>
+      <c r="D377" s="63"/>
+      <c r="E377" s="63"/>
+      <c r="F377" s="74"/>
+      <c r="G377" s="74"/>
+      <c r="H377" s="63"/>
+      <c r="I377" s="74"/>
+      <c r="J377" s="74"/>
+      <c r="K377" s="74"/>
+      <c r="L377" s="63"/>
+      <c r="M377" s="63"/>
+      <c r="N377" s="63"/>
+      <c r="O377" s="47"/>
+    </row>
+    <row r="378" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C378" s="60"/>
+      <c r="D378" s="63"/>
+      <c r="E378" s="63"/>
+      <c r="F378" s="74"/>
+      <c r="G378" s="74"/>
+      <c r="H378" s="63"/>
+      <c r="I378" s="74"/>
+      <c r="J378" s="74"/>
+      <c r="K378" s="74"/>
+      <c r="L378" s="63"/>
+      <c r="M378" s="63"/>
+      <c r="N378" s="63"/>
+      <c r="O378" s="47"/>
+    </row>
+    <row r="379" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C379" s="60"/>
+      <c r="D379" s="63"/>
+      <c r="E379" s="63"/>
+      <c r="F379" s="74"/>
+      <c r="G379" s="74"/>
+      <c r="H379" s="63"/>
+      <c r="I379" s="74"/>
+      <c r="J379" s="74"/>
+      <c r="K379" s="74"/>
+      <c r="L379" s="63"/>
+      <c r="M379" s="63"/>
+      <c r="N379" s="63"/>
+      <c r="O379" s="47"/>
+    </row>
+    <row r="380" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C380" s="60"/>
+      <c r="D380" s="63"/>
+      <c r="E380" s="63"/>
+      <c r="F380" s="74"/>
+      <c r="G380" s="74"/>
+      <c r="H380" s="63"/>
+      <c r="I380" s="74"/>
+      <c r="J380" s="74"/>
+      <c r="K380" s="74"/>
+      <c r="L380" s="63"/>
+      <c r="M380" s="63"/>
+      <c r="N380" s="63"/>
+      <c r="O380" s="47"/>
+    </row>
+    <row r="381" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C381" s="60"/>
+      <c r="D381" s="63"/>
+      <c r="E381" s="63"/>
+      <c r="F381" s="74"/>
+      <c r="G381" s="74"/>
+      <c r="H381" s="63"/>
+      <c r="I381" s="74"/>
+      <c r="J381" s="74"/>
+      <c r="K381" s="74"/>
+      <c r="L381" s="63"/>
+      <c r="M381" s="63"/>
+      <c r="N381" s="63"/>
+      <c r="O381" s="47"/>
+    </row>
+    <row r="382" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C382" s="60"/>
+      <c r="D382" s="63"/>
+      <c r="E382" s="63"/>
+      <c r="F382" s="74"/>
+      <c r="G382" s="74"/>
+      <c r="H382" s="63"/>
+      <c r="I382" s="74"/>
+      <c r="J382" s="74"/>
+      <c r="K382" s="74"/>
+      <c r="L382" s="63"/>
+      <c r="M382" s="63"/>
+      <c r="N382" s="63"/>
+      <c r="O382" s="47"/>
+    </row>
+    <row r="383" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C383" s="60"/>
+      <c r="D383" s="63"/>
+      <c r="E383" s="63"/>
+      <c r="F383" s="74"/>
+      <c r="G383" s="74"/>
+      <c r="H383" s="63"/>
+      <c r="I383" s="74"/>
+      <c r="J383" s="74"/>
+      <c r="K383" s="74"/>
+      <c r="L383" s="63"/>
+      <c r="M383" s="63"/>
+      <c r="N383" s="63"/>
+      <c r="O383" s="47"/>
+    </row>
+    <row r="384" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C384" s="60"/>
+      <c r="D384" s="63"/>
+      <c r="E384" s="63"/>
+      <c r="F384" s="74"/>
+      <c r="G384" s="74"/>
+      <c r="H384" s="63"/>
+      <c r="I384" s="74"/>
+      <c r="J384" s="74"/>
+      <c r="K384" s="74"/>
+      <c r="L384" s="63"/>
+      <c r="M384" s="63"/>
+      <c r="N384" s="63"/>
+      <c r="O384" s="47"/>
+    </row>
+    <row r="385" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C385" s="60"/>
+      <c r="D385" s="63"/>
+      <c r="E385" s="63"/>
+      <c r="F385" s="74"/>
+      <c r="G385" s="74"/>
+      <c r="H385" s="63"/>
+      <c r="I385" s="74"/>
+      <c r="J385" s="74"/>
+      <c r="K385" s="74"/>
+      <c r="L385" s="63"/>
+      <c r="M385" s="63"/>
+      <c r="N385" s="63"/>
+      <c r="O385" s="47"/>
+    </row>
+    <row r="386" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C386" s="60"/>
+      <c r="D386" s="63"/>
+      <c r="E386" s="63"/>
+      <c r="F386" s="74"/>
+      <c r="G386" s="74"/>
+      <c r="H386" s="63"/>
+      <c r="I386" s="74"/>
+      <c r="J386" s="74"/>
+      <c r="K386" s="74"/>
+      <c r="L386" s="63"/>
+      <c r="M386" s="63"/>
+      <c r="N386" s="63"/>
+      <c r="O386" s="47"/>
+    </row>
+    <row r="387" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C387" s="60"/>
+      <c r="D387" s="63"/>
+      <c r="E387" s="63"/>
+      <c r="F387" s="74"/>
+      <c r="G387" s="74"/>
+      <c r="H387" s="63"/>
+      <c r="I387" s="74"/>
+      <c r="J387" s="74"/>
+      <c r="K387" s="74"/>
+      <c r="L387" s="63"/>
+      <c r="M387" s="63"/>
+      <c r="N387" s="63"/>
+      <c r="O387" s="47"/>
+    </row>
+    <row r="388" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C388" s="60"/>
+      <c r="D388" s="63"/>
+      <c r="E388" s="63"/>
+      <c r="F388" s="74"/>
+      <c r="G388" s="74"/>
+      <c r="H388" s="63"/>
+      <c r="I388" s="74"/>
+      <c r="J388" s="74"/>
+      <c r="K388" s="74"/>
+      <c r="L388" s="63"/>
+      <c r="M388" s="63"/>
+      <c r="N388" s="63"/>
+      <c r="O388" s="47"/>
+    </row>
+    <row r="389" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C389" s="60"/>
+      <c r="D389" s="63"/>
+      <c r="E389" s="63"/>
+      <c r="F389" s="74"/>
+      <c r="G389" s="74"/>
+      <c r="H389" s="63"/>
+      <c r="I389" s="74"/>
+      <c r="J389" s="74"/>
+      <c r="K389" s="74"/>
+      <c r="L389" s="63"/>
+      <c r="M389" s="63"/>
+      <c r="N389" s="63"/>
+      <c r="O389" s="47"/>
+    </row>
+    <row r="390" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C390" s="60"/>
+      <c r="D390" s="63"/>
+      <c r="E390" s="63"/>
+      <c r="F390" s="74"/>
+      <c r="G390" s="74"/>
+      <c r="H390" s="63"/>
+      <c r="I390" s="74"/>
+      <c r="J390" s="74"/>
+      <c r="K390" s="74"/>
+      <c r="L390" s="63"/>
+      <c r="M390" s="63"/>
+      <c r="N390" s="63"/>
+      <c r="O390" s="47"/>
+    </row>
+    <row r="391" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C391" s="60"/>
+      <c r="D391" s="63"/>
+      <c r="E391" s="63"/>
+      <c r="F391" s="74"/>
+      <c r="G391" s="74"/>
+      <c r="H391" s="63"/>
+      <c r="I391" s="74"/>
+      <c r="J391" s="74"/>
+      <c r="K391" s="74"/>
+      <c r="L391" s="63"/>
+      <c r="M391" s="63"/>
+      <c r="N391" s="63"/>
+      <c r="O391" s="47"/>
+    </row>
+    <row r="392" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C392" s="60"/>
+      <c r="D392" s="63"/>
+      <c r="E392" s="63"/>
+      <c r="F392" s="74"/>
+      <c r="G392" s="74"/>
+      <c r="H392" s="63"/>
+      <c r="I392" s="74"/>
+      <c r="J392" s="74"/>
+      <c r="K392" s="74"/>
+      <c r="L392" s="63"/>
+      <c r="M392" s="63"/>
+      <c r="N392" s="63"/>
+      <c r="O392" s="47"/>
+    </row>
+    <row r="393" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C393" s="60"/>
+      <c r="D393" s="63"/>
+      <c r="E393" s="63"/>
+      <c r="F393" s="74"/>
+      <c r="G393" s="74"/>
+      <c r="H393" s="63"/>
+      <c r="I393" s="74"/>
+      <c r="J393" s="74"/>
+      <c r="K393" s="74"/>
+      <c r="L393" s="63"/>
+      <c r="M393" s="63"/>
+      <c r="N393" s="63"/>
+      <c r="O393" s="47"/>
+    </row>
+    <row r="394" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C394" s="60"/>
+      <c r="D394" s="63"/>
+      <c r="E394" s="63"/>
+      <c r="F394" s="74"/>
+      <c r="G394" s="74"/>
+      <c r="H394" s="63"/>
+      <c r="I394" s="74"/>
+      <c r="J394" s="74"/>
+      <c r="K394" s="74"/>
+      <c r="L394" s="63"/>
+      <c r="M394" s="63"/>
+      <c r="N394" s="63"/>
+      <c r="O394" s="47"/>
+    </row>
+    <row r="395" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C395" s="60"/>
+      <c r="D395" s="63"/>
+      <c r="E395" s="63"/>
+      <c r="F395" s="74"/>
+      <c r="G395" s="74"/>
+      <c r="H395" s="63"/>
+      <c r="I395" s="74"/>
+      <c r="J395" s="74"/>
+      <c r="K395" s="74"/>
+      <c r="L395" s="63"/>
+      <c r="M395" s="63"/>
+      <c r="N395" s="63"/>
+      <c r="O395" s="47"/>
+    </row>
+    <row r="396" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C396" s="60"/>
+      <c r="D396" s="63"/>
+      <c r="E396" s="63"/>
+      <c r="F396" s="74"/>
+      <c r="G396" s="74"/>
+      <c r="H396" s="63"/>
+      <c r="I396" s="74"/>
+      <c r="J396" s="74"/>
+      <c r="K396" s="74"/>
+      <c r="L396" s="63"/>
+      <c r="M396" s="63"/>
+      <c r="N396" s="63"/>
+      <c r="O396" s="47"/>
+    </row>
+    <row r="397" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C397" s="60"/>
+      <c r="D397" s="63"/>
+      <c r="E397" s="63"/>
+      <c r="F397" s="74"/>
+      <c r="G397" s="74"/>
+      <c r="H397" s="63"/>
+      <c r="I397" s="74"/>
+      <c r="J397" s="74"/>
+      <c r="K397" s="74"/>
+      <c r="L397" s="63"/>
+      <c r="M397" s="63"/>
+      <c r="N397" s="63"/>
+      <c r="O397" s="47"/>
+    </row>
+    <row r="398" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C398" s="60"/>
+      <c r="D398" s="63"/>
+      <c r="E398" s="63"/>
+      <c r="F398" s="74"/>
+      <c r="G398" s="74"/>
+      <c r="H398" s="63"/>
+      <c r="I398" s="74"/>
+      <c r="J398" s="74"/>
+      <c r="K398" s="74"/>
+      <c r="L398" s="63"/>
+      <c r="M398" s="63"/>
+      <c r="N398" s="63"/>
+      <c r="O398" s="47"/>
+    </row>
+    <row r="399" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C399" s="60"/>
+      <c r="D399" s="63"/>
+      <c r="E399" s="63"/>
+      <c r="F399" s="74"/>
+      <c r="G399" s="74"/>
+      <c r="H399" s="63"/>
+      <c r="I399" s="74"/>
+      <c r="J399" s="74"/>
+      <c r="K399" s="74"/>
+      <c r="L399" s="63"/>
+      <c r="M399" s="63"/>
+      <c r="N399" s="63"/>
+      <c r="O399" s="47"/>
+    </row>
+    <row r="400" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C400" s="60"/>
+      <c r="D400" s="63"/>
+      <c r="E400" s="63"/>
+      <c r="F400" s="74"/>
+      <c r="G400" s="74"/>
+      <c r="H400" s="63"/>
+      <c r="I400" s="74"/>
+      <c r="J400" s="74"/>
+      <c r="K400" s="74"/>
+      <c r="L400" s="63"/>
+      <c r="M400" s="63"/>
+      <c r="N400" s="63"/>
+      <c r="O400" s="47"/>
+    </row>
+    <row r="401" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C401" s="60"/>
+      <c r="D401" s="63"/>
+      <c r="E401" s="63"/>
+      <c r="F401" s="74"/>
+      <c r="G401" s="74"/>
+      <c r="H401" s="63"/>
+      <c r="I401" s="74"/>
+      <c r="J401" s="74"/>
+      <c r="K401" s="74"/>
+      <c r="L401" s="63"/>
+      <c r="M401" s="63"/>
+      <c r="N401" s="63"/>
+      <c r="O401" s="47"/>
+    </row>
+    <row r="402" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C402" s="60"/>
+      <c r="D402" s="63"/>
+      <c r="E402" s="63"/>
+      <c r="F402" s="74"/>
+      <c r="G402" s="74"/>
+      <c r="H402" s="63"/>
+      <c r="I402" s="74"/>
+      <c r="J402" s="74"/>
+      <c r="K402" s="74"/>
+      <c r="L402" s="63"/>
+      <c r="M402" s="63"/>
+      <c r="N402" s="63"/>
+      <c r="O402" s="47"/>
+    </row>
+    <row r="403" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C403" s="60"/>
+      <c r="D403" s="63"/>
+      <c r="E403" s="63"/>
+      <c r="F403" s="74"/>
+      <c r="G403" s="74"/>
+      <c r="H403" s="63"/>
+      <c r="I403" s="74"/>
+      <c r="J403" s="74"/>
+      <c r="K403" s="74"/>
+      <c r="L403" s="63"/>
+      <c r="M403" s="63"/>
+      <c r="N403" s="63"/>
+      <c r="O403" s="47"/>
+    </row>
+    <row r="404" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C404" s="60"/>
+      <c r="D404" s="63"/>
+      <c r="E404" s="63"/>
+      <c r="F404" s="74"/>
+      <c r="G404" s="74"/>
+      <c r="H404" s="63"/>
+      <c r="I404" s="74"/>
+      <c r="J404" s="74"/>
+      <c r="K404" s="74"/>
+      <c r="L404" s="63"/>
+      <c r="M404" s="63"/>
+      <c r="N404" s="63"/>
+      <c r="O404" s="47"/>
+    </row>
+    <row r="405" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C405" s="60"/>
+      <c r="D405" s="63"/>
+      <c r="E405" s="63"/>
+      <c r="F405" s="74"/>
+      <c r="G405" s="74"/>
+      <c r="H405" s="63"/>
+      <c r="I405" s="74"/>
+      <c r="J405" s="74"/>
+      <c r="K405" s="74"/>
+      <c r="L405" s="63"/>
+      <c r="M405" s="63"/>
+      <c r="N405" s="63"/>
+      <c r="O405" s="47"/>
+    </row>
+    <row r="406" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C406" s="60"/>
+      <c r="D406" s="63"/>
+      <c r="E406" s="63"/>
+      <c r="F406" s="74"/>
+      <c r="G406" s="74"/>
+      <c r="H406" s="63"/>
+      <c r="I406" s="74"/>
+      <c r="J406" s="74"/>
+      <c r="K406" s="74"/>
+      <c r="L406" s="63"/>
+      <c r="M406" s="63"/>
+      <c r="N406" s="63"/>
+      <c r="O406" s="47"/>
+    </row>
+    <row r="407" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C407" s="60"/>
+      <c r="D407" s="63"/>
+      <c r="E407" s="63"/>
+      <c r="F407" s="74"/>
+      <c r="G407" s="74"/>
+      <c r="H407" s="63"/>
+      <c r="I407" s="74"/>
+      <c r="J407" s="74"/>
+      <c r="K407" s="74"/>
+      <c r="L407" s="63"/>
+      <c r="M407" s="63"/>
+      <c r="N407" s="63"/>
+      <c r="O407" s="47"/>
+    </row>
+    <row r="408" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C408" s="60"/>
+      <c r="D408" s="63"/>
+      <c r="E408" s="63"/>
+      <c r="F408" s="74"/>
+      <c r="G408" s="74"/>
+      <c r="H408" s="63"/>
+      <c r="I408" s="74"/>
+      <c r="J408" s="74"/>
+      <c r="K408" s="74"/>
+      <c r="L408" s="63"/>
+      <c r="M408" s="63"/>
+      <c r="N408" s="63"/>
+      <c r="O408" s="47"/>
+    </row>
+    <row r="409" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C409" s="60"/>
+      <c r="D409" s="63"/>
+      <c r="E409" s="63"/>
+      <c r="F409" s="74"/>
+      <c r="G409" s="74"/>
+      <c r="H409" s="63"/>
+      <c r="I409" s="74"/>
+      <c r="J409" s="74"/>
+      <c r="K409" s="74"/>
+      <c r="L409" s="63"/>
+      <c r="M409" s="63"/>
+      <c r="N409" s="63"/>
+      <c r="O409" s="47"/>
+    </row>
+    <row r="410" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C410" s="60"/>
+      <c r="D410" s="63"/>
+      <c r="E410" s="63"/>
+      <c r="F410" s="74"/>
+      <c r="G410" s="74"/>
+      <c r="H410" s="63"/>
+      <c r="I410" s="74"/>
+      <c r="J410" s="74"/>
+      <c r="K410" s="74"/>
+      <c r="L410" s="63"/>
+      <c r="M410" s="63"/>
+      <c r="N410" s="63"/>
+      <c r="O410" s="47"/>
+    </row>
+    <row r="411" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C411" s="60"/>
+      <c r="D411" s="63"/>
+      <c r="E411" s="63"/>
+      <c r="F411" s="74"/>
+      <c r="G411" s="74"/>
+      <c r="H411" s="63"/>
+      <c r="I411" s="74"/>
+      <c r="J411" s="74"/>
+      <c r="K411" s="74"/>
+      <c r="L411" s="63"/>
+      <c r="M411" s="63"/>
+      <c r="N411" s="63"/>
+      <c r="O411" s="47"/>
+    </row>
+    <row r="412" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C412" s="60"/>
+      <c r="D412" s="63"/>
+      <c r="E412" s="63"/>
+      <c r="F412" s="74"/>
+      <c r="G412" s="74"/>
+      <c r="H412" s="63"/>
+      <c r="I412" s="74"/>
+      <c r="J412" s="74"/>
+      <c r="K412" s="74"/>
+      <c r="L412" s="63"/>
+      <c r="M412" s="63"/>
+      <c r="N412" s="63"/>
+      <c r="O412" s="47"/>
+    </row>
+    <row r="413" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C413" s="60"/>
+      <c r="D413" s="63"/>
+      <c r="E413" s="63"/>
+      <c r="F413" s="74"/>
+      <c r="G413" s="74"/>
+      <c r="H413" s="63"/>
+      <c r="I413" s="74"/>
+      <c r="J413" s="74"/>
+      <c r="K413" s="74"/>
+      <c r="L413" s="63"/>
+      <c r="M413" s="63"/>
+      <c r="N413" s="63"/>
+      <c r="O413" s="47"/>
+    </row>
+    <row r="414" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C414" s="60"/>
+      <c r="D414" s="63"/>
+      <c r="E414" s="63"/>
+      <c r="F414" s="74"/>
+      <c r="G414" s="74"/>
+      <c r="H414" s="63"/>
+      <c r="I414" s="74"/>
+      <c r="J414" s="74"/>
+      <c r="K414" s="74"/>
+      <c r="L414" s="63"/>
+      <c r="M414" s="63"/>
+      <c r="N414" s="63"/>
+      <c r="O414" s="47"/>
+    </row>
+    <row r="415" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C415" s="60"/>
+      <c r="D415" s="63"/>
+      <c r="E415" s="63"/>
+      <c r="F415" s="74"/>
+      <c r="G415" s="74"/>
+      <c r="H415" s="63"/>
+      <c r="I415" s="74"/>
+      <c r="J415" s="74"/>
+      <c r="K415" s="74"/>
+      <c r="L415" s="63"/>
+      <c r="M415" s="63"/>
+      <c r="N415" s="63"/>
+      <c r="O415" s="47"/>
+    </row>
+    <row r="416" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C416" s="60"/>
+      <c r="D416" s="63"/>
+      <c r="E416" s="63"/>
+      <c r="F416" s="74"/>
+      <c r="G416" s="74"/>
+      <c r="H416" s="63"/>
+      <c r="I416" s="74"/>
+      <c r="J416" s="74"/>
+      <c r="K416" s="74"/>
+      <c r="L416" s="63"/>
+      <c r="M416" s="63"/>
+      <c r="N416" s="63"/>
+      <c r="O416" s="47"/>
+    </row>
+    <row r="417" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C417" s="60"/>
+      <c r="D417" s="63"/>
+      <c r="E417" s="63"/>
+      <c r="F417" s="74"/>
+      <c r="G417" s="74"/>
+      <c r="H417" s="63"/>
+      <c r="I417" s="74"/>
+      <c r="J417" s="74"/>
+      <c r="K417" s="74"/>
+      <c r="L417" s="63"/>
+      <c r="M417" s="63"/>
+      <c r="N417" s="63"/>
+      <c r="O417" s="47"/>
+    </row>
+    <row r="418" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C418" s="60"/>
+      <c r="D418" s="63"/>
+      <c r="E418" s="63"/>
+      <c r="F418" s="74"/>
+      <c r="G418" s="74"/>
+      <c r="H418" s="63"/>
+      <c r="I418" s="74"/>
+      <c r="J418" s="74"/>
+      <c r="K418" s="74"/>
+      <c r="L418" s="63"/>
+      <c r="M418" s="63"/>
+      <c r="N418" s="63"/>
+      <c r="O418" s="47"/>
+    </row>
+    <row r="419" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C419" s="60"/>
+      <c r="D419" s="63"/>
+      <c r="E419" s="63"/>
+      <c r="F419" s="74"/>
+      <c r="G419" s="74"/>
+      <c r="H419" s="63"/>
+      <c r="I419" s="74"/>
+      <c r="J419" s="74"/>
+      <c r="K419" s="74"/>
+      <c r="L419" s="63"/>
+      <c r="M419" s="63"/>
+      <c r="N419" s="63"/>
+      <c r="O419" s="47"/>
+    </row>
+    <row r="420" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C420" s="60"/>
+      <c r="D420" s="63"/>
+      <c r="E420" s="63"/>
+      <c r="F420" s="74"/>
+      <c r="G420" s="74"/>
+      <c r="H420" s="63"/>
+      <c r="I420" s="74"/>
+      <c r="J420" s="74"/>
+      <c r="K420" s="74"/>
+      <c r="L420" s="63"/>
+      <c r="M420" s="63"/>
+      <c r="N420" s="63"/>
+      <c r="O420" s="47"/>
+    </row>
+    <row r="421" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C421" s="60"/>
+      <c r="D421" s="63"/>
+      <c r="E421" s="63"/>
+      <c r="F421" s="74"/>
+      <c r="G421" s="74"/>
+      <c r="H421" s="63"/>
+      <c r="I421" s="74"/>
+      <c r="J421" s="74"/>
+      <c r="K421" s="74"/>
+      <c r="L421" s="63"/>
+      <c r="M421" s="63"/>
+      <c r="N421" s="63"/>
+      <c r="O421" s="47"/>
+    </row>
+    <row r="422" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C422" s="60"/>
+      <c r="D422" s="63"/>
+      <c r="E422" s="63"/>
+      <c r="F422" s="74"/>
+      <c r="G422" s="74"/>
+      <c r="H422" s="63"/>
+      <c r="I422" s="74"/>
+      <c r="J422" s="74"/>
+      <c r="K422" s="74"/>
+      <c r="L422" s="63"/>
+      <c r="M422" s="63"/>
+      <c r="N422" s="63"/>
+      <c r="O422" s="47"/>
+    </row>
+    <row r="423" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C423" s="60"/>
+      <c r="D423" s="63"/>
+      <c r="E423" s="63"/>
+      <c r="F423" s="74"/>
+      <c r="G423" s="74"/>
+      <c r="H423" s="63"/>
+      <c r="I423" s="74"/>
+      <c r="J423" s="74"/>
+      <c r="K423" s="74"/>
+      <c r="L423" s="63"/>
+      <c r="M423" s="63"/>
+      <c r="N423" s="63"/>
+      <c r="O423" s="47"/>
+    </row>
+    <row r="424" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C424" s="60"/>
+      <c r="D424" s="63"/>
+      <c r="E424" s="63"/>
+      <c r="F424" s="74"/>
+      <c r="G424" s="74"/>
+      <c r="H424" s="63"/>
+      <c r="I424" s="74"/>
+      <c r="J424" s="74"/>
+      <c r="K424" s="74"/>
+      <c r="L424" s="63"/>
+      <c r="M424" s="63"/>
+      <c r="N424" s="63"/>
+      <c r="O424" s="47"/>
+    </row>
+    <row r="425" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C425" s="60"/>
+      <c r="D425" s="63"/>
+      <c r="E425" s="63"/>
+      <c r="F425" s="74"/>
+      <c r="G425" s="74"/>
+      <c r="H425" s="63"/>
+      <c r="I425" s="74"/>
+      <c r="J425" s="74"/>
+      <c r="K425" s="74"/>
+      <c r="L425" s="63"/>
+      <c r="M425" s="63"/>
+      <c r="N425" s="63"/>
+      <c r="O425" s="47"/>
+    </row>
+    <row r="426" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C426" s="60"/>
+      <c r="D426" s="63"/>
+      <c r="E426" s="63"/>
+      <c r="F426" s="74"/>
+      <c r="G426" s="74"/>
+      <c r="H426" s="63"/>
+      <c r="I426" s="74"/>
+      <c r="J426" s="74"/>
+      <c r="K426" s="74"/>
+      <c r="L426" s="63"/>
+      <c r="M426" s="63"/>
+      <c r="N426" s="63"/>
+      <c r="O426" s="47"/>
+    </row>
+    <row r="427" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C427" s="60"/>
+      <c r="D427" s="63"/>
+      <c r="E427" s="63"/>
+      <c r="F427" s="74"/>
+      <c r="G427" s="74"/>
+      <c r="H427" s="63"/>
+      <c r="I427" s="74"/>
+      <c r="J427" s="74"/>
+      <c r="K427" s="74"/>
+      <c r="L427" s="63"/>
+      <c r="M427" s="63"/>
+      <c r="N427" s="63"/>
+      <c r="O427" s="47"/>
+    </row>
+    <row r="428" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C428" s="60"/>
+      <c r="D428" s="63"/>
+      <c r="E428" s="63"/>
+      <c r="F428" s="74"/>
+      <c r="G428" s="74"/>
+      <c r="H428" s="63"/>
+      <c r="I428" s="74"/>
+      <c r="J428" s="74"/>
+      <c r="K428" s="74"/>
+      <c r="L428" s="63"/>
+      <c r="M428" s="63"/>
+      <c r="N428" s="63"/>
+      <c r="O428" s="47"/>
+    </row>
+    <row r="429" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C429" s="60"/>
+      <c r="D429" s="63"/>
+      <c r="E429" s="63"/>
+      <c r="F429" s="74"/>
+      <c r="G429" s="74"/>
+      <c r="H429" s="63"/>
+      <c r="I429" s="74"/>
+      <c r="J429" s="74"/>
+      <c r="K429" s="74"/>
+      <c r="L429" s="63"/>
+      <c r="M429" s="63"/>
+      <c r="N429" s="63"/>
+      <c r="O429" s="47"/>
+    </row>
+    <row r="430" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C430" s="60"/>
+      <c r="D430" s="63"/>
+      <c r="E430" s="63"/>
+      <c r="F430" s="74"/>
+      <c r="G430" s="74"/>
+      <c r="H430" s="63"/>
+      <c r="I430" s="74"/>
+      <c r="J430" s="74"/>
+      <c r="K430" s="74"/>
+      <c r="L430" s="63"/>
+      <c r="M430" s="63"/>
+      <c r="N430" s="63"/>
+      <c r="O430" s="47"/>
+    </row>
+    <row r="431" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C431" s="60"/>
+      <c r="D431" s="63"/>
+      <c r="E431" s="63"/>
+      <c r="F431" s="74"/>
+      <c r="G431" s="74"/>
+      <c r="H431" s="63"/>
+      <c r="I431" s="74"/>
+      <c r="J431" s="74"/>
+      <c r="K431" s="74"/>
+      <c r="L431" s="63"/>
+      <c r="M431" s="63"/>
+      <c r="N431" s="63"/>
+      <c r="O431" s="47"/>
+    </row>
+    <row r="432" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C432" s="60"/>
+      <c r="D432" s="63"/>
+      <c r="E432" s="63"/>
+      <c r="F432" s="74"/>
+      <c r="G432" s="74"/>
+      <c r="H432" s="63"/>
+      <c r="I432" s="74"/>
+      <c r="J432" s="74"/>
+      <c r="K432" s="74"/>
+      <c r="L432" s="63"/>
+      <c r="M432" s="63"/>
+      <c r="N432" s="63"/>
+      <c r="O432" s="47"/>
+    </row>
+    <row r="433" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C433" s="60"/>
+      <c r="D433" s="63"/>
+      <c r="E433" s="63"/>
+      <c r="F433" s="74"/>
+      <c r="G433" s="74"/>
+      <c r="H433" s="63"/>
+      <c r="I433" s="74"/>
+      <c r="J433" s="74"/>
+      <c r="K433" s="74"/>
+      <c r="L433" s="63"/>
+      <c r="M433" s="63"/>
+      <c r="N433" s="63"/>
+      <c r="O433" s="47"/>
+    </row>
+    <row r="434" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C434" s="60"/>
+      <c r="D434" s="63"/>
+      <c r="E434" s="63"/>
+      <c r="F434" s="74"/>
+      <c r="G434" s="74"/>
+      <c r="H434" s="63"/>
+      <c r="I434" s="74"/>
+      <c r="J434" s="74"/>
+      <c r="K434" s="74"/>
+      <c r="L434" s="63"/>
+      <c r="M434" s="63"/>
+      <c r="N434" s="63"/>
+      <c r="O434" s="47"/>
+    </row>
+    <row r="435" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C435" s="60"/>
+      <c r="D435" s="63"/>
+      <c r="E435" s="63"/>
+      <c r="F435" s="74"/>
+      <c r="G435" s="74"/>
+      <c r="H435" s="63"/>
+      <c r="I435" s="74"/>
+      <c r="J435" s="74"/>
+      <c r="K435" s="74"/>
+      <c r="L435" s="63"/>
+      <c r="M435" s="63"/>
+      <c r="N435" s="63"/>
+      <c r="O435" s="47"/>
+    </row>
+    <row r="436" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C436" s="60"/>
+      <c r="D436" s="63"/>
+      <c r="E436" s="63"/>
+      <c r="F436" s="74"/>
+      <c r="G436" s="74"/>
+      <c r="H436" s="63"/>
+      <c r="I436" s="74"/>
+      <c r="J436" s="74"/>
+      <c r="K436" s="74"/>
+      <c r="L436" s="63"/>
+      <c r="M436" s="63"/>
+      <c r="N436" s="63"/>
+      <c r="O436" s="47"/>
+    </row>
+    <row r="437" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C437" s="60"/>
+      <c r="D437" s="63"/>
+      <c r="E437" s="63"/>
+      <c r="F437" s="74"/>
+      <c r="G437" s="74"/>
+      <c r="H437" s="63"/>
+      <c r="I437" s="74"/>
+      <c r="J437" s="74"/>
+      <c r="K437" s="74"/>
+      <c r="L437" s="63"/>
+      <c r="M437" s="63"/>
+      <c r="N437" s="63"/>
+      <c r="O437" s="47"/>
+    </row>
+    <row r="438" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C438" s="60"/>
+      <c r="D438" s="63"/>
+      <c r="E438" s="63"/>
+      <c r="F438" s="74"/>
+      <c r="G438" s="74"/>
+      <c r="H438" s="63"/>
+      <c r="I438" s="74"/>
+      <c r="J438" s="74"/>
+      <c r="K438" s="74"/>
+      <c r="L438" s="63"/>
+      <c r="M438" s="63"/>
+      <c r="N438" s="63"/>
+      <c r="O438" s="47"/>
+    </row>
+    <row r="439" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C439" s="60"/>
+      <c r="D439" s="63"/>
+      <c r="E439" s="63"/>
+      <c r="F439" s="74"/>
+      <c r="G439" s="74"/>
+      <c r="H439" s="63"/>
+      <c r="I439" s="74"/>
+      <c r="J439" s="74"/>
+      <c r="K439" s="74"/>
+      <c r="L439" s="63"/>
+      <c r="M439" s="63"/>
+      <c r="N439" s="63"/>
+      <c r="O439" s="47"/>
+    </row>
+    <row r="440" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C440" s="60"/>
+      <c r="D440" s="63"/>
+      <c r="E440" s="63"/>
+      <c r="F440" s="74"/>
+      <c r="G440" s="74"/>
+      <c r="H440" s="63"/>
+      <c r="I440" s="74"/>
+      <c r="J440" s="74"/>
+      <c r="K440" s="74"/>
+      <c r="L440" s="63"/>
+      <c r="M440" s="63"/>
+      <c r="N440" s="63"/>
+      <c r="O440" s="47"/>
+    </row>
+    <row r="441" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C441" s="60"/>
+      <c r="D441" s="63"/>
+      <c r="E441" s="63"/>
+      <c r="F441" s="74"/>
+      <c r="G441" s="74"/>
+      <c r="H441" s="63"/>
+      <c r="I441" s="74"/>
+      <c r="J441" s="74"/>
+      <c r="K441" s="74"/>
+      <c r="L441" s="63"/>
+      <c r="M441" s="63"/>
+      <c r="N441" s="63"/>
+      <c r="O441" s="47"/>
+    </row>
+    <row r="442" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C442" s="60"/>
+      <c r="D442" s="63"/>
+      <c r="E442" s="63"/>
+      <c r="F442" s="74"/>
+      <c r="G442" s="74"/>
+      <c r="H442" s="63"/>
+      <c r="I442" s="74"/>
+      <c r="J442" s="74"/>
+      <c r="K442" s="74"/>
+      <c r="L442" s="63"/>
+      <c r="M442" s="63"/>
+      <c r="N442" s="63"/>
+      <c r="O442" s="47"/>
+    </row>
+    <row r="443" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C443" s="60"/>
+      <c r="D443" s="63"/>
+      <c r="E443" s="63"/>
+      <c r="F443" s="74"/>
+      <c r="G443" s="74"/>
+      <c r="H443" s="63"/>
+      <c r="I443" s="74"/>
+      <c r="J443" s="74"/>
+      <c r="K443" s="74"/>
+      <c r="L443" s="63"/>
+      <c r="M443" s="63"/>
+      <c r="N443" s="63"/>
+      <c r="O443" s="47"/>
+    </row>
+    <row r="444" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C444" s="60"/>
+      <c r="D444" s="63"/>
+      <c r="E444" s="63"/>
+      <c r="F444" s="74"/>
+      <c r="G444" s="74"/>
+      <c r="H444" s="63"/>
+      <c r="I444" s="74"/>
+      <c r="J444" s="74"/>
+      <c r="K444" s="74"/>
+      <c r="L444" s="63"/>
+      <c r="M444" s="63"/>
+      <c r="N444" s="63"/>
+      <c r="O444" s="47"/>
+    </row>
+    <row r="445" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C445" s="60"/>
+      <c r="D445" s="63"/>
+      <c r="E445" s="63"/>
+      <c r="F445" s="74"/>
+      <c r="G445" s="74"/>
+      <c r="H445" s="63"/>
+      <c r="I445" s="74"/>
+      <c r="J445" s="74"/>
+      <c r="K445" s="74"/>
+      <c r="L445" s="63"/>
+      <c r="M445" s="63"/>
+      <c r="N445" s="63"/>
+      <c r="O445" s="47"/>
+    </row>
+    <row r="446" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C446" s="60"/>
+      <c r="D446" s="63"/>
+      <c r="E446" s="63"/>
+      <c r="F446" s="74"/>
+      <c r="G446" s="74"/>
+      <c r="H446" s="63"/>
+      <c r="I446" s="74"/>
+      <c r="J446" s="74"/>
+      <c r="K446" s="74"/>
+      <c r="L446" s="63"/>
+      <c r="M446" s="63"/>
+      <c r="N446" s="63"/>
+      <c r="O446" s="47"/>
+    </row>
+    <row r="447" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C447" s="60"/>
+      <c r="D447" s="63"/>
+      <c r="E447" s="63"/>
+      <c r="F447" s="74"/>
+      <c r="G447" s="74"/>
+      <c r="H447" s="63"/>
+      <c r="I447" s="74"/>
+      <c r="J447" s="74"/>
+      <c r="K447" s="74"/>
+      <c r="L447" s="63"/>
+      <c r="M447" s="63"/>
+      <c r="N447" s="63"/>
+      <c r="O447" s="47"/>
+    </row>
+    <row r="448" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C448" s="60"/>
+      <c r="D448" s="63"/>
+      <c r="E448" s="63"/>
+      <c r="F448" s="74"/>
+      <c r="G448" s="74"/>
+      <c r="H448" s="63"/>
+      <c r="I448" s="74"/>
+      <c r="J448" s="74"/>
+      <c r="K448" s="74"/>
+      <c r="L448" s="63"/>
+      <c r="M448" s="63"/>
+      <c r="N448" s="63"/>
+      <c r="O448" s="47"/>
+    </row>
+    <row r="449" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C449" s="60"/>
+      <c r="D449" s="63"/>
+      <c r="E449" s="63"/>
+      <c r="F449" s="74"/>
+      <c r="G449" s="74"/>
+      <c r="H449" s="63"/>
+      <c r="I449" s="74"/>
+      <c r="J449" s="74"/>
+      <c r="K449" s="74"/>
+      <c r="L449" s="63"/>
+      <c r="M449" s="63"/>
+      <c r="N449" s="63"/>
+      <c r="O449" s="47"/>
+    </row>
+    <row r="450" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C450" s="60"/>
+      <c r="D450" s="63"/>
+      <c r="E450" s="63"/>
+      <c r="F450" s="74"/>
+      <c r="G450" s="74"/>
+      <c r="H450" s="63"/>
+      <c r="I450" s="74"/>
+      <c r="J450" s="74"/>
+      <c r="K450" s="74"/>
+      <c r="L450" s="63"/>
+      <c r="M450" s="63"/>
+      <c r="N450" s="63"/>
+      <c r="O450" s="47"/>
+    </row>
+    <row r="451" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C451" s="60"/>
+      <c r="D451" s="63"/>
+      <c r="E451" s="63"/>
+      <c r="F451" s="74"/>
+      <c r="G451" s="74"/>
+      <c r="H451" s="63"/>
+      <c r="I451" s="74"/>
+      <c r="J451" s="74"/>
+      <c r="K451" s="74"/>
+      <c r="L451" s="63"/>
+      <c r="M451" s="63"/>
+      <c r="N451" s="63"/>
+      <c r="O451" s="47"/>
+    </row>
+    <row r="452" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C452" s="60"/>
+      <c r="D452" s="63"/>
+      <c r="E452" s="63"/>
+      <c r="F452" s="74"/>
+      <c r="G452" s="74"/>
+      <c r="H452" s="63"/>
+      <c r="I452" s="74"/>
+      <c r="J452" s="74"/>
+      <c r="K452" s="74"/>
+      <c r="L452" s="63"/>
+      <c r="M452" s="63"/>
+      <c r="N452" s="63"/>
+      <c r="O452" s="47"/>
+    </row>
+    <row r="453" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C453" s="60"/>
+      <c r="D453" s="63"/>
+      <c r="E453" s="63"/>
+      <c r="F453" s="74"/>
+      <c r="G453" s="74"/>
+      <c r="H453" s="63"/>
+      <c r="I453" s="74"/>
+      <c r="J453" s="74"/>
+      <c r="K453" s="74"/>
+      <c r="L453" s="63"/>
+      <c r="M453" s="63"/>
+      <c r="N453" s="63"/>
+      <c r="O453" s="47"/>
+    </row>
+    <row r="454" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C454" s="60"/>
+      <c r="D454" s="63"/>
+      <c r="E454" s="63"/>
+      <c r="F454" s="74"/>
+      <c r="G454" s="74"/>
+      <c r="H454" s="63"/>
+      <c r="I454" s="74"/>
+      <c r="J454" s="74"/>
+      <c r="K454" s="74"/>
+      <c r="L454" s="63"/>
+      <c r="M454" s="63"/>
+      <c r="N454" s="63"/>
+      <c r="O454" s="47"/>
+    </row>
+    <row r="455" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C455" s="60"/>
+      <c r="D455" s="63"/>
+      <c r="E455" s="63"/>
+      <c r="F455" s="74"/>
+      <c r="G455" s="74"/>
+      <c r="H455" s="63"/>
+      <c r="I455" s="74"/>
+      <c r="J455" s="74"/>
+      <c r="K455" s="74"/>
+      <c r="L455" s="63"/>
+      <c r="M455" s="63"/>
+      <c r="N455" s="63"/>
+      <c r="O455" s="47"/>
+    </row>
+    <row r="456" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C456" s="60"/>
+      <c r="D456" s="63"/>
+      <c r="E456" s="63"/>
+      <c r="F456" s="74"/>
+      <c r="G456" s="74"/>
+      <c r="H456" s="63"/>
+      <c r="I456" s="74"/>
+      <c r="J456" s="74"/>
+      <c r="K456" s="74"/>
+      <c r="L456" s="63"/>
+      <c r="M456" s="63"/>
+      <c r="N456" s="63"/>
+      <c r="O456" s="47"/>
+    </row>
+    <row r="457" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C457" s="60"/>
+      <c r="D457" s="63"/>
+      <c r="E457" s="63"/>
+      <c r="F457" s="74"/>
+      <c r="G457" s="74"/>
+      <c r="H457" s="63"/>
+      <c r="I457" s="74"/>
+      <c r="J457" s="74"/>
+      <c r="K457" s="74"/>
+      <c r="L457" s="63"/>
+      <c r="M457" s="63"/>
+      <c r="N457" s="63"/>
+      <c r="O457" s="47"/>
+    </row>
+    <row r="458" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C458" s="60"/>
+      <c r="D458" s="63"/>
+      <c r="E458" s="63"/>
+      <c r="F458" s="74"/>
+      <c r="G458" s="74"/>
+      <c r="H458" s="63"/>
+      <c r="I458" s="74"/>
+      <c r="J458" s="74"/>
+      <c r="K458" s="74"/>
+      <c r="L458" s="63"/>
+      <c r="M458" s="63"/>
+      <c r="N458" s="63"/>
+      <c r="O458" s="47"/>
+    </row>
+    <row r="459" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C459" s="60"/>
+      <c r="D459" s="63"/>
+      <c r="E459" s="63"/>
+      <c r="F459" s="74"/>
+      <c r="G459" s="74"/>
+      <c r="H459" s="63"/>
+      <c r="I459" s="74"/>
+      <c r="J459" s="74"/>
+      <c r="K459" s="74"/>
+      <c r="L459" s="63"/>
+      <c r="M459" s="63"/>
+      <c r="N459" s="63"/>
+      <c r="O459" s="47"/>
+    </row>
+    <row r="460" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C460" s="60"/>
+      <c r="D460" s="63"/>
+      <c r="E460" s="63"/>
+      <c r="F460" s="74"/>
+      <c r="G460" s="74"/>
+      <c r="H460" s="63"/>
+      <c r="I460" s="74"/>
+      <c r="J460" s="74"/>
+      <c r="K460" s="74"/>
+      <c r="L460" s="63"/>
+      <c r="M460" s="63"/>
+      <c r="N460" s="63"/>
+      <c r="O460" s="47"/>
+    </row>
+    <row r="461" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C461" s="60"/>
+      <c r="D461" s="63"/>
+      <c r="E461" s="63"/>
+      <c r="F461" s="74"/>
+      <c r="G461" s="74"/>
+      <c r="H461" s="63"/>
+      <c r="I461" s="74"/>
+      <c r="J461" s="74"/>
+      <c r="K461" s="74"/>
+      <c r="L461" s="63"/>
+      <c r="M461" s="63"/>
+      <c r="N461" s="63"/>
+      <c r="O461" s="47"/>
+    </row>
+    <row r="462" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C462" s="60"/>
+      <c r="D462" s="63"/>
+      <c r="E462" s="63"/>
+      <c r="F462" s="74"/>
+      <c r="G462" s="74"/>
+      <c r="H462" s="63"/>
+      <c r="I462" s="74"/>
+      <c r="J462" s="74"/>
+      <c r="K462" s="74"/>
+      <c r="L462" s="63"/>
+      <c r="M462" s="63"/>
+      <c r="N462" s="63"/>
+      <c r="O462" s="47"/>
+    </row>
+    <row r="463" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C463" s="60"/>
+      <c r="D463" s="63"/>
+      <c r="E463" s="63"/>
+      <c r="F463" s="74"/>
+      <c r="G463" s="74"/>
+      <c r="H463" s="63"/>
+      <c r="I463" s="74"/>
+      <c r="J463" s="74"/>
+      <c r="K463" s="74"/>
+      <c r="L463" s="63"/>
+      <c r="M463" s="63"/>
+      <c r="N463" s="63"/>
+      <c r="O463" s="47"/>
+    </row>
+    <row r="464" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C464" s="60"/>
+      <c r="D464" s="63"/>
+      <c r="E464" s="63"/>
+      <c r="F464" s="74"/>
+      <c r="G464" s="74"/>
+      <c r="H464" s="63"/>
+      <c r="I464" s="74"/>
+      <c r="J464" s="74"/>
+      <c r="K464" s="74"/>
+      <c r="L464" s="63"/>
+      <c r="M464" s="63"/>
+      <c r="N464" s="63"/>
+      <c r="O464" s="47"/>
+    </row>
+    <row r="465" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C465" s="60"/>
+      <c r="D465" s="63"/>
+      <c r="E465" s="63"/>
+      <c r="F465" s="74"/>
+      <c r="G465" s="74"/>
+      <c r="H465" s="63"/>
+      <c r="I465" s="74"/>
+      <c r="J465" s="74"/>
+      <c r="K465" s="74"/>
+      <c r="L465" s="63"/>
+      <c r="M465" s="63"/>
+      <c r="N465" s="63"/>
+      <c r="O465" s="47"/>
+    </row>
+    <row r="466" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C466" s="60"/>
+      <c r="D466" s="63"/>
+      <c r="E466" s="63"/>
+      <c r="F466" s="74"/>
+      <c r="G466" s="74"/>
+      <c r="H466" s="63"/>
+      <c r="I466" s="74"/>
+      <c r="J466" s="74"/>
+      <c r="K466" s="74"/>
+      <c r="L466" s="63"/>
+      <c r="M466" s="63"/>
+      <c r="N466" s="63"/>
+      <c r="O466" s="47"/>
+    </row>
+    <row r="467" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C467" s="60"/>
+      <c r="D467" s="63"/>
+      <c r="E467" s="63"/>
+      <c r="F467" s="74"/>
+      <c r="G467" s="74"/>
+      <c r="H467" s="63"/>
+      <c r="I467" s="74"/>
+      <c r="J467" s="74"/>
+      <c r="K467" s="74"/>
+      <c r="L467" s="63"/>
+      <c r="M467" s="63"/>
+      <c r="N467" s="63"/>
+      <c r="O467" s="47"/>
+    </row>
+    <row r="468" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C468" s="60"/>
+      <c r="D468" s="63"/>
+      <c r="E468" s="63"/>
+      <c r="F468" s="74"/>
+      <c r="G468" s="74"/>
+      <c r="H468" s="63"/>
+      <c r="I468" s="74"/>
+      <c r="J468" s="74"/>
+      <c r="K468" s="74"/>
+      <c r="L468" s="63"/>
+      <c r="M468" s="63"/>
+      <c r="N468" s="63"/>
+      <c r="O468" s="47"/>
+    </row>
+    <row r="469" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C469" s="60"/>
+      <c r="D469" s="63"/>
+      <c r="E469" s="63"/>
+      <c r="F469" s="74"/>
+      <c r="G469" s="74"/>
+      <c r="H469" s="63"/>
+      <c r="I469" s="74"/>
+      <c r="J469" s="74"/>
+      <c r="K469" s="74"/>
+      <c r="L469" s="63"/>
+      <c r="M469" s="63"/>
+      <c r="N469" s="63"/>
+      <c r="O469" s="47"/>
+    </row>
+    <row r="470" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C470" s="60"/>
+      <c r="D470" s="63"/>
+      <c r="E470" s="63"/>
+      <c r="F470" s="74"/>
+      <c r="G470" s="74"/>
+      <c r="H470" s="63"/>
+      <c r="I470" s="74"/>
+      <c r="J470" s="74"/>
+      <c r="K470" s="74"/>
+      <c r="L470" s="63"/>
+      <c r="M470" s="63"/>
+      <c r="N470" s="63"/>
+      <c r="O470" s="47"/>
+    </row>
+    <row r="471" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C471" s="60"/>
+      <c r="D471" s="63"/>
+      <c r="E471" s="63"/>
+      <c r="F471" s="74"/>
+      <c r="G471" s="74"/>
+      <c r="H471" s="63"/>
+      <c r="I471" s="74"/>
+      <c r="J471" s="74"/>
+      <c r="K471" s="74"/>
+      <c r="L471" s="63"/>
+      <c r="M471" s="63"/>
+      <c r="N471" s="63"/>
+      <c r="O471" s="47"/>
+    </row>
+    <row r="472" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C472" s="60"/>
+      <c r="D472" s="63"/>
+      <c r="E472" s="63"/>
+      <c r="F472" s="74"/>
+      <c r="G472" s="74"/>
+      <c r="H472" s="63"/>
+      <c r="I472" s="74"/>
+      <c r="J472" s="74"/>
+      <c r="K472" s="74"/>
+      <c r="L472" s="63"/>
+      <c r="M472" s="63"/>
+      <c r="N472" s="63"/>
+      <c r="O472" s="47"/>
+    </row>
+    <row r="473" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C473" s="60"/>
+      <c r="D473" s="63"/>
+      <c r="E473" s="63"/>
+      <c r="F473" s="74"/>
+      <c r="G473" s="74"/>
+      <c r="H473" s="63"/>
+      <c r="I473" s="74"/>
+      <c r="J473" s="74"/>
+      <c r="K473" s="74"/>
+      <c r="L473" s="63"/>
+      <c r="M473" s="63"/>
+      <c r="N473" s="63"/>
+      <c r="O473" s="47"/>
+    </row>
+    <row r="474" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C474" s="60"/>
+      <c r="D474" s="63"/>
+      <c r="E474" s="63"/>
+      <c r="F474" s="74"/>
+      <c r="G474" s="74"/>
+      <c r="H474" s="63"/>
+      <c r="I474" s="74"/>
+      <c r="J474" s="74"/>
+      <c r="K474" s="74"/>
+      <c r="L474" s="63"/>
+      <c r="M474" s="63"/>
+      <c r="N474" s="63"/>
+      <c r="O474" s="47"/>
+    </row>
+    <row r="475" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C475" s="60"/>
+      <c r="D475" s="63"/>
+      <c r="E475" s="63"/>
+      <c r="F475" s="74"/>
+      <c r="G475" s="74"/>
+      <c r="H475" s="63"/>
+      <c r="I475" s="74"/>
+      <c r="J475" s="74"/>
+      <c r="K475" s="74"/>
+      <c r="L475" s="63"/>
+      <c r="M475" s="63"/>
+      <c r="N475" s="63"/>
+      <c r="O475" s="47"/>
+    </row>
+    <row r="476" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C476" s="60"/>
+      <c r="D476" s="63"/>
+      <c r="E476" s="63"/>
+      <c r="F476" s="74"/>
+      <c r="G476" s="74"/>
+      <c r="H476" s="63"/>
+      <c r="I476" s="74"/>
+      <c r="J476" s="74"/>
+      <c r="K476" s="74"/>
+      <c r="L476" s="63"/>
+      <c r="M476" s="63"/>
+      <c r="N476" s="63"/>
+      <c r="O476" s="47"/>
+    </row>
+    <row r="477" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C477" s="60"/>
+      <c r="D477" s="63"/>
+      <c r="E477" s="63"/>
+      <c r="F477" s="74"/>
+      <c r="G477" s="74"/>
+      <c r="H477" s="63"/>
+      <c r="I477" s="74"/>
+      <c r="J477" s="74"/>
+      <c r="K477" s="74"/>
+      <c r="L477" s="63"/>
+      <c r="M477" s="63"/>
+      <c r="N477" s="63"/>
+      <c r="O477" s="47"/>
+    </row>
+    <row r="478" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C478" s="60"/>
+      <c r="D478" s="63"/>
+      <c r="E478" s="63"/>
+      <c r="F478" s="74"/>
+      <c r="G478" s="74"/>
+      <c r="H478" s="63"/>
+      <c r="I478" s="74"/>
+      <c r="J478" s="74"/>
+      <c r="K478" s="74"/>
+      <c r="L478" s="63"/>
+      <c r="M478" s="63"/>
+      <c r="N478" s="63"/>
+      <c r="O478" s="47"/>
+    </row>
+    <row r="479" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C479" s="60"/>
+      <c r="D479" s="63"/>
+      <c r="E479" s="63"/>
+      <c r="F479" s="74"/>
+      <c r="G479" s="74"/>
+      <c r="H479" s="63"/>
+      <c r="I479" s="74"/>
+      <c r="J479" s="74"/>
+      <c r="K479" s="74"/>
+      <c r="L479" s="63"/>
+      <c r="M479" s="63"/>
+      <c r="N479" s="63"/>
+      <c r="O479" s="47"/>
+    </row>
+    <row r="480" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C480" s="60"/>
+      <c r="D480" s="63"/>
+      <c r="E480" s="63"/>
+      <c r="F480" s="74"/>
+      <c r="G480" s="74"/>
+      <c r="H480" s="63"/>
+      <c r="I480" s="74"/>
+      <c r="J480" s="74"/>
+      <c r="K480" s="74"/>
+      <c r="L480" s="63"/>
+      <c r="M480" s="63"/>
+      <c r="N480" s="63"/>
+      <c r="O480" s="47"/>
+    </row>
+    <row r="481" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C481" s="60"/>
+      <c r="D481" s="63"/>
+      <c r="E481" s="63"/>
+      <c r="F481" s="74"/>
+      <c r="G481" s="74"/>
+      <c r="H481" s="63"/>
+      <c r="I481" s="74"/>
+      <c r="J481" s="74"/>
+      <c r="K481" s="74"/>
+      <c r="L481" s="63"/>
+      <c r="M481" s="63"/>
+      <c r="N481" s="63"/>
+      <c r="O481" s="47"/>
+    </row>
+    <row r="482" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C482" s="60"/>
+      <c r="D482" s="63"/>
+      <c r="E482" s="63"/>
+      <c r="F482" s="74"/>
+      <c r="G482" s="74"/>
+      <c r="H482" s="63"/>
+      <c r="I482" s="74"/>
+      <c r="J482" s="74"/>
+      <c r="K482" s="74"/>
+      <c r="L482" s="63"/>
+      <c r="M482" s="63"/>
+      <c r="N482" s="63"/>
+      <c r="O482" s="47"/>
+    </row>
+    <row r="483" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C483" s="60"/>
+      <c r="D483" s="63"/>
+      <c r="E483" s="63"/>
+      <c r="F483" s="74"/>
+      <c r="G483" s="74"/>
+      <c r="H483" s="63"/>
+      <c r="I483" s="74"/>
+      <c r="J483" s="74"/>
+      <c r="K483" s="74"/>
+      <c r="L483" s="63"/>
+      <c r="M483" s="63"/>
+      <c r="N483" s="63"/>
+      <c r="O483" s="47"/>
+    </row>
+    <row r="484" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C484" s="60"/>
+      <c r="D484" s="63"/>
+      <c r="E484" s="63"/>
+      <c r="F484" s="74"/>
+      <c r="G484" s="74"/>
+      <c r="H484" s="63"/>
+      <c r="I484" s="74"/>
+      <c r="J484" s="74"/>
+      <c r="K484" s="74"/>
+      <c r="L484" s="63"/>
+      <c r="M484" s="63"/>
+      <c r="N484" s="63"/>
+      <c r="O484" s="47"/>
+    </row>
+    <row r="485" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C485" s="60"/>
+      <c r="D485" s="63"/>
+      <c r="E485" s="63"/>
+      <c r="F485" s="74"/>
+      <c r="G485" s="74"/>
+      <c r="H485" s="63"/>
+      <c r="I485" s="74"/>
+      <c r="J485" s="74"/>
+      <c r="K485" s="74"/>
+      <c r="L485" s="63"/>
+      <c r="M485" s="63"/>
+      <c r="N485" s="63"/>
+      <c r="O485" s="47"/>
+    </row>
+    <row r="486" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C486" s="60"/>
+      <c r="D486" s="63"/>
+      <c r="E486" s="63"/>
+      <c r="F486" s="74"/>
+      <c r="G486" s="74"/>
+      <c r="H486" s="63"/>
+      <c r="I486" s="74"/>
+      <c r="J486" s="74"/>
+      <c r="K486" s="74"/>
+      <c r="L486" s="63"/>
+      <c r="M486" s="63"/>
+      <c r="N486" s="63"/>
+      <c r="O486" s="47"/>
+    </row>
+    <row r="487" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C487" s="60"/>
+      <c r="D487" s="63"/>
+      <c r="E487" s="63"/>
+      <c r="F487" s="74"/>
+      <c r="G487" s="74"/>
+      <c r="H487" s="63"/>
+      <c r="I487" s="74"/>
+      <c r="J487" s="74"/>
+      <c r="K487" s="74"/>
+      <c r="L487" s="63"/>
+      <c r="M487" s="63"/>
+      <c r="N487" s="63"/>
+      <c r="O487" s="47"/>
+    </row>
+    <row r="488" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C488" s="60"/>
+      <c r="D488" s="63"/>
+      <c r="E488" s="63"/>
+      <c r="F488" s="74"/>
+      <c r="G488" s="74"/>
+      <c r="H488" s="63"/>
+      <c r="I488" s="74"/>
+      <c r="J488" s="74"/>
+      <c r="K488" s="74"/>
+      <c r="L488" s="63"/>
+      <c r="M488" s="63"/>
+      <c r="N488" s="63"/>
+      <c r="O488" s="47"/>
+    </row>
+    <row r="489" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C489" s="60"/>
+      <c r="D489" s="63"/>
+      <c r="E489" s="63"/>
+      <c r="F489" s="74"/>
+      <c r="G489" s="74"/>
+      <c r="H489" s="63"/>
+      <c r="I489" s="74"/>
+      <c r="J489" s="74"/>
+      <c r="K489" s="74"/>
+      <c r="L489" s="63"/>
+      <c r="M489" s="63"/>
+      <c r="N489" s="63"/>
+      <c r="O489" s="47"/>
+    </row>
+    <row r="490" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C490" s="60"/>
+      <c r="D490" s="63"/>
+      <c r="E490" s="63"/>
+      <c r="F490" s="74"/>
+      <c r="G490" s="74"/>
+      <c r="H490" s="63"/>
+      <c r="I490" s="74"/>
+      <c r="J490" s="74"/>
+      <c r="K490" s="74"/>
+      <c r="L490" s="63"/>
+      <c r="M490" s="63"/>
+      <c r="N490" s="63"/>
+      <c r="O490" s="47"/>
+    </row>
+    <row r="491" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C491" s="60"/>
+      <c r="D491" s="63"/>
+      <c r="E491" s="63"/>
+      <c r="F491" s="74"/>
+      <c r="G491" s="74"/>
+      <c r="H491" s="63"/>
+      <c r="I491" s="74"/>
+      <c r="J491" s="74"/>
+      <c r="K491" s="74"/>
+      <c r="L491" s="63"/>
+      <c r="M491" s="63"/>
+      <c r="N491" s="63"/>
+      <c r="O491" s="47"/>
+    </row>
+    <row r="492" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C492" s="60"/>
+      <c r="D492" s="63"/>
+      <c r="E492" s="63"/>
+      <c r="F492" s="74"/>
+      <c r="G492" s="74"/>
+      <c r="H492" s="63"/>
+      <c r="I492" s="74"/>
+      <c r="J492" s="74"/>
+      <c r="K492" s="74"/>
+      <c r="L492" s="63"/>
+      <c r="M492" s="63"/>
+      <c r="N492" s="63"/>
+      <c r="O492" s="47"/>
+    </row>
+    <row r="493" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C493" s="60"/>
+      <c r="D493" s="63"/>
+      <c r="E493" s="63"/>
+      <c r="F493" s="74"/>
+      <c r="G493" s="74"/>
+      <c r="H493" s="63"/>
+      <c r="I493" s="74"/>
+      <c r="J493" s="74"/>
+      <c r="K493" s="74"/>
+      <c r="L493" s="63"/>
+      <c r="M493" s="63"/>
+      <c r="N493" s="63"/>
+      <c r="O493" s="47"/>
+    </row>
+    <row r="494" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C494" s="60"/>
+      <c r="D494" s="63"/>
+      <c r="E494" s="63"/>
+      <c r="F494" s="74"/>
+      <c r="G494" s="74"/>
+      <c r="H494" s="63"/>
+      <c r="I494" s="74"/>
+      <c r="J494" s="74"/>
+      <c r="K494" s="74"/>
+      <c r="L494" s="63"/>
+      <c r="M494" s="63"/>
+      <c r="N494" s="63"/>
+      <c r="O494" s="47"/>
+    </row>
+    <row r="495" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C495" s="60"/>
+      <c r="D495" s="63"/>
+      <c r="E495" s="63"/>
+      <c r="F495" s="74"/>
+      <c r="G495" s="74"/>
+      <c r="H495" s="63"/>
+      <c r="I495" s="74"/>
+      <c r="J495" s="74"/>
+      <c r="K495" s="74"/>
+      <c r="L495" s="63"/>
+      <c r="M495" s="63"/>
+      <c r="N495" s="63"/>
+      <c r="O495" s="47"/>
+    </row>
+    <row r="496" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C496" s="60"/>
+      <c r="D496" s="63"/>
+      <c r="E496" s="63"/>
+      <c r="F496" s="74"/>
+      <c r="G496" s="74"/>
+      <c r="H496" s="63"/>
+      <c r="I496" s="74"/>
+      <c r="J496" s="74"/>
+      <c r="K496" s="74"/>
+      <c r="L496" s="63"/>
+      <c r="M496" s="63"/>
+      <c r="N496" s="63"/>
+      <c r="O496" s="47"/>
+    </row>
+    <row r="497" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C497" s="60"/>
+      <c r="D497" s="63"/>
+      <c r="E497" s="63"/>
+      <c r="F497" s="74"/>
+      <c r="G497" s="74"/>
+      <c r="H497" s="63"/>
+      <c r="I497" s="74"/>
+      <c r="J497" s="74"/>
+      <c r="K497" s="74"/>
+      <c r="L497" s="63"/>
+      <c r="M497" s="63"/>
+      <c r="N497" s="63"/>
+      <c r="O497" s="47"/>
+    </row>
+    <row r="498" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C498" s="60"/>
+      <c r="D498" s="63"/>
+      <c r="E498" s="63"/>
+      <c r="F498" s="74"/>
+      <c r="G498" s="74"/>
+      <c r="H498" s="63"/>
+      <c r="I498" s="74"/>
+      <c r="J498" s="74"/>
+      <c r="K498" s="74"/>
+      <c r="L498" s="63"/>
+      <c r="M498" s="63"/>
+      <c r="N498" s="63"/>
+      <c r="O498" s="47"/>
+    </row>
+    <row r="499" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C499" s="60"/>
+      <c r="D499" s="63"/>
+      <c r="E499" s="63"/>
+      <c r="F499" s="74"/>
+      <c r="G499" s="74"/>
+      <c r="H499" s="63"/>
+      <c r="I499" s="74"/>
+      <c r="J499" s="74"/>
+      <c r="K499" s="74"/>
+      <c r="L499" s="63"/>
+      <c r="M499" s="63"/>
+      <c r="N499" s="63"/>
+      <c r="O499" s="47"/>
+    </row>
+    <row r="500" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C500" s="60"/>
+      <c r="D500" s="63"/>
+      <c r="E500" s="63"/>
+      <c r="F500" s="74"/>
+      <c r="G500" s="74"/>
+      <c r="H500" s="63"/>
+      <c r="I500" s="74"/>
+      <c r="J500" s="74"/>
+      <c r="K500" s="74"/>
+      <c r="L500" s="63"/>
+      <c r="M500" s="63"/>
+      <c r="N500" s="63"/>
+      <c r="O500" s="47"/>
+    </row>
+    <row r="501" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C501" s="60"/>
+      <c r="D501" s="63"/>
+      <c r="E501" s="63"/>
+      <c r="F501" s="74"/>
+      <c r="G501" s="74"/>
+      <c r="H501" s="63"/>
+      <c r="I501" s="74"/>
+      <c r="J501" s="74"/>
+      <c r="K501" s="74"/>
+      <c r="L501" s="63"/>
+      <c r="M501" s="63"/>
+      <c r="N501" s="63"/>
+      <c r="O501" s="47"/>
+    </row>
+    <row r="502" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C502" s="60"/>
+      <c r="D502" s="63"/>
+      <c r="E502" s="63"/>
+      <c r="F502" s="74"/>
+      <c r="G502" s="74"/>
+      <c r="H502" s="63"/>
+      <c r="I502" s="74"/>
+      <c r="J502" s="74"/>
+      <c r="K502" s="74"/>
+      <c r="L502" s="63"/>
+      <c r="M502" s="63"/>
+      <c r="N502" s="63"/>
+      <c r="O502" s="47"/>
+    </row>
+    <row r="503" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C503" s="60"/>
+      <c r="D503" s="63"/>
+      <c r="E503" s="63"/>
+      <c r="F503" s="74"/>
+      <c r="G503" s="74"/>
+      <c r="H503" s="63"/>
+      <c r="I503" s="74"/>
+      <c r="J503" s="74"/>
+      <c r="K503" s="74"/>
+      <c r="L503" s="63"/>
+      <c r="M503" s="63"/>
+      <c r="N503" s="63"/>
+      <c r="O503" s="47"/>
+    </row>
+    <row r="504" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C504" s="60"/>
+      <c r="D504" s="63"/>
+      <c r="E504" s="63"/>
+      <c r="F504" s="74"/>
+      <c r="G504" s="74"/>
+      <c r="H504" s="63"/>
+      <c r="I504" s="74"/>
+      <c r="J504" s="74"/>
+      <c r="K504" s="74"/>
+      <c r="L504" s="63"/>
+      <c r="M504" s="63"/>
+      <c r="N504" s="63"/>
+      <c r="O504" s="47"/>
+    </row>
+    <row r="505" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C505" s="60"/>
+      <c r="D505" s="63"/>
+      <c r="E505" s="63"/>
+      <c r="F505" s="74"/>
+      <c r="G505" s="74"/>
+      <c r="H505" s="63"/>
+      <c r="I505" s="74"/>
+      <c r="J505" s="74"/>
+      <c r="K505" s="74"/>
+      <c r="L505" s="63"/>
+      <c r="M505" s="63"/>
+      <c r="N505" s="63"/>
+      <c r="O505" s="47"/>
+    </row>
+    <row r="506" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C506" s="60"/>
+      <c r="D506" s="63"/>
+      <c r="E506" s="63"/>
+      <c r="F506" s="74"/>
+      <c r="G506" s="74"/>
+      <c r="H506" s="63"/>
+      <c r="I506" s="74"/>
+      <c r="J506" s="74"/>
+      <c r="K506" s="74"/>
+      <c r="L506" s="63"/>
+      <c r="M506" s="63"/>
+      <c r="N506" s="63"/>
+      <c r="O506" s="47"/>
+    </row>
+    <row r="507" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C507" s="60"/>
+      <c r="D507" s="63"/>
+      <c r="E507" s="63"/>
+      <c r="F507" s="74"/>
+      <c r="G507" s="74"/>
+      <c r="H507" s="63"/>
+      <c r="I507" s="74"/>
+      <c r="J507" s="74"/>
+      <c r="K507" s="74"/>
+      <c r="L507" s="63"/>
+      <c r="M507" s="63"/>
+      <c r="N507" s="63"/>
+      <c r="O507" s="47"/>
+    </row>
+    <row r="508" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C508" s="60"/>
+      <c r="D508" s="63"/>
+      <c r="E508" s="63"/>
+      <c r="F508" s="74"/>
+      <c r="G508" s="74"/>
+      <c r="H508" s="63"/>
+      <c r="I508" s="74"/>
+      <c r="J508" s="74"/>
+      <c r="K508" s="74"/>
+      <c r="L508" s="63"/>
+      <c r="M508" s="63"/>
+      <c r="N508" s="63"/>
+      <c r="O508" s="47"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C9:C508">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>AND(C9&lt;&gt;"",COUNTIF($C$9:$C$508,C9)&gt;1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="5">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Unusual scale" error="The usual scales are 1, 1000 and 1000000. Keep this value?" promptTitle="Amount scale" prompt="1 = units, 1000 = thousands, 1000000 = millions of the reporting currency." sqref="D4">
+      <formula1>"1,1000,1000000"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter an amount of zero or more." promptTitle="Absolute tolerance" prompt="Largest difference, in reporting-currency units, that still matches." sqref="D5">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid tolerance" error="Enter a number of zero or more." promptTitle="Relative tolerance" prompt="Largest difference as a share of the bank figure that still matches, for example 0.01% (0.0001)." sqref="D6">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Duplicate ID" error="This Trade ID is already listed. Keep it? It will not be compared." promptTitle="Trade ID" prompt="The Trade ID of the leg, as on Trades. A repeated ID is reported as DUPLICATE and not compared." sqref="C9:C508">
+      <formula1>COUNTIF($C$9:$C$508,C9)=1</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid figure" error="Enter a number, or leave the cell blank." promptTitle="Bank figure" prompt="The bank's figure; amounts in the scale above, the others as they are. Blank = not compared." sqref="D9:N508">
+      <formula1>ISNUMBER(D9)</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <sheetPr codeName="shTradeReconciliation">
+    <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="4" customWidth="1"/>
+    <col min="3" max="3" width="16.75" style="7" customWidth="1"/>
+    <col min="4" max="4" width="7.75" style="10" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="9" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="26.75" style="7" customWidth="1"/>
+    <col min="9" max="9" width="16.75" style="11" customWidth="1"/>
+    <col min="10" max="10" width="16.75" style="11" customWidth="1"/>
+    <col min="11" max="11" width="16.75" style="11" customWidth="1"/>
+    <col min="12" max="12" width="12.75" style="16" customWidth="1"/>
+    <col min="13" max="13" width="22.75" style="7" customWidth="1"/>
+    <col min="14" max="14" width="80.75" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+    </row>
+    <row r="2" spans="2:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="30" t="s">
+        <v>943</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+    </row>
+    <row r="3" spans="2:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C4" s="14" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C5" s="14" t="str" cm="1">
+        <f t="array" ref="C5">TradeReconciliationStatusText(SACCR_TradeReconInputs,SACCR_RunInputs,BankTrades!$1:$1048576,NettingSets!$C:$Q,Trades!$C:$AA,Params!$1:$1048576)</f>
+        <v>No reconciliation: enter bank figures on BankTrades and press Run SA-CCR.</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>927</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>166</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>930</v>

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -2823,7 +2823,7 @@
     <t>Trades: one row per derivative leg. Dropdowns guide the classification. Amounts can be in any currency of the FX table. Legs of one economic trade share an Economic trade ID; exactly one of them (MtM leg = Y) carries the MtM.</t>
   </si>
   <si>
-    <t>Click "Run SA-CCR" (macro RunSACCR). Results, HedgingSets, Buckets, TradeCalc and Checks are rebuilt; Reconciliation and TradeReconciliation compare the figures entered on BankNettingSets and BankTrades with Results and TradeCalc. "Validate inputs" only runs the checks; "Clear outputs" empties the output sheets.</t>
+    <t>Click "Run SA-CCR" (macro RunSACCR). Results, HedgingSets, Buckets, TradeCalc and Checks are rebuilt; Reconciliation and TradeReconciliation compare the figures entered on BankNettingSets and BankTrades with Results and TradeCalc; "Export evidence" on Reconciliation writes the evidence report of the run as a CSV file. "Validate inputs" only runs the checks; "Clear outputs" empties the output sheets.</t>
   </si>
   <si>
     <t>Positive amount; the sign comes from Direction. IR / CR: trade notional. FX: the notional of one leg, in that leg's currency (one of the pair): the foreign-currency leg or, when both legs are foreign, the larger one in reporting currency. EQ / CO: market price x units.</t>
@@ -2865,7 +2865,7 @@
     <t>Illustrative counterparties (NS-ALPHA, NS-GAMMA) and FX rates. BCBS-EX1..5 reproduce CRE99 / BCBS 279 Annex 4 (amounts in thousands); the other CRR-* and BCBS-* netting sets feed the TestCatalogue; DEMO-REJECTED shows how rejected trades withhold a netting set's EAD.</t>
   </si>
   <si>
-    <t>M_Main (macros), CORE_Engine (calculation), CORE_Reconcile (comparison with bank figures), SACCR_Formulas (public SACCR_* functions), CORE_Config (layout constants), CORE_Util (helpers). No external references: no Scripting.Dictionary, no WorksheetFunction. Supported on Windows Excel 64-bit; 32-bit is kept compiling but not certified; Mac and Excel for the web are not supported.</t>
+    <t>M_Main (macros), CORE_Engine (calculation), CORE_Reconcile (comparison with bank figures), CORE_Export (evidence report), SACCR_Formulas (public SACCR_* functions), CORE_Config (layout constants), CORE_Util (helpers). No external references: no Scripting.Dictionary, no WorksheetFunction. Supported on Windows Excel 64-bit; 32-bit is kept compiling but not certified; Mac and Excel for the web are not supported.</t>
   </si>
   <si>
     <t>Bank netting-set results</t>
@@ -4037,6 +4037,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
@@ -4696,6 +4700,79 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>1285875</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>285750</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5121" name="Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s5121"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000001140000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos"/>
+                </a:rPr>
+                <a:t>Export evidence</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -15224,7 +15301,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="shReconciliation">
     <tabColor rgb="FF2E75B6"/>
     <pageSetUpPr fitToPage="1"/>
@@ -15349,6 +15426,36 @@
   </conditionalFormatting>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="5121" r:id="rId3" name="Button 1">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!ExportEvidence">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>1285875</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>285750</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
 </worksheet>
 </file>
 

--- a/src/workbook/SACCR_Template.xlsx
+++ b/src/workbook/SACCR_Template.xlsx
@@ -23123,7 +23123,7 @@
     <tabColor rgb="FF2E75B6"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
@@ -23139,9 +23139,10 @@
     <col min="12" max="12" width="12.75" style="16" customWidth="1"/>
     <col min="13" max="13" width="22.75" style="7" customWidth="1"/>
     <col min="14" max="14" width="80.75" style="7" customWidth="1"/>
+    <col min="15" max="15" width="18.75" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
@@ -23157,8 +23158,9 @@
       <c r="L1" s="66"/>
       <c r="M1" s="66"/>
       <c r="N1" s="66"/>
-    </row>
-    <row r="2" spans="2:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O1" s="66"/>
+    </row>
+    <row r="2" spans="2:15" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
         <v>943</v>
       </c>
@@ -23174,22 +23176,23 @@
       <c r="L2" s="68"/>
       <c r="M2" s="68"/>
       <c r="N2" s="68"/>
-    </row>
-    <row r="3" spans="2:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O2" s="68"/>
+    </row>
+    <row r="3" spans="2:15" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C4" s="14" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C5" s="14" t="str" cm="1">
         <f t="array" ref="C5">TradeReconciliationStatusText(SACCR_TradeReconInputs,SACCR_RunInputs,BankTrades!$1:$1048576,NettingSets!$C:$Q,Trades!$C:$AA,Params!$1:$1048576)</f>
         <v>No reconciliation: enter bank figures on BankTrades and press Run SA-CCR.</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="15" t="s">
         <v>294</v>
       </c>
@@ -23225,6 +23228,9 @@
       </c>
       <c r="N6" s="15" t="s">
         <v>570</v>
+      </c>
+      <c r="O6" s="15" t="s">
+        <v>856</v>
       </c>
     </row>
   </sheetData>
